--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -31,30 +31,30 @@
     <t>codeforiati:global-name</t>
   </si>
   <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
     <t>codeforiati:region-name</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -67,27 +67,27 @@
     <t>World</t>
   </si>
   <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
     <t>Africa</t>
   </si>
   <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -169,21 +169,21 @@
     <t>014</t>
   </si>
   <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
     <t>IO</t>
   </si>
   <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
     <t>202</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
     <t>IOT</t>
   </si>
   <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -445,12 +445,12 @@
     <t>017</t>
   </si>
   <si>
+    <t>Middle Africa</t>
+  </si>
+  <si>
     <t>AO</t>
   </si>
   <si>
-    <t>Middle Africa</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
@@ -559,12 +559,12 @@
     <t>018</t>
   </si>
   <si>
+    <t>Southern Africa</t>
+  </si>
+  <si>
     <t>BW</t>
   </si>
   <si>
-    <t>Southern Africa</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>011</t>
   </si>
   <si>
+    <t>Western Africa</t>
+  </si>
+  <si>
     <t>BJ</t>
   </si>
   <si>
-    <t>Western Africa</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
@@ -835,27 +835,27 @@
     <t>029</t>
   </si>
   <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
     <t>Americas</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>AIA</t>
-  </si>
-  <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -1189,12 +1189,12 @@
     <t>013</t>
   </si>
   <si>
+    <t>Central America</t>
+  </si>
+  <si>
     <t>BZ</t>
   </si>
   <si>
-    <t>Central America</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>005</t>
   </si>
   <si>
+    <t>South America</t>
+  </si>
+  <si>
     <t>AR</t>
   </si>
   <si>
-    <t>South America</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -1492,12 +1492,12 @@
     <t>021</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
     <t>BMU</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1564,24 +1564,24 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>Asia</t>
   </si>
   <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>KAZ</t>
-  </si>
-  <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1642,12 +1642,12 @@
     <t>030</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
     <t>CHN</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1732,12 +1732,12 @@
     <t>035</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
     <t>BRN</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1870,12 +1870,12 @@
     <t>034</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
     <t>AFG</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1984,12 +1984,12 @@
     <t>145</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
     <t>ARM</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -2200,24 +2200,24 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>Europe</t>
   </si>
   <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2338,12 +2338,12 @@
     <t>154</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
     <t>ALA</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>830</t>
   </si>
   <si>
+    <t>Channel Islands</t>
+  </si>
+  <si>
     <t>GG</t>
   </si>
   <si>
-    <t>Channel Islands</t>
-  </si>
-  <si>
     <t>GGY</t>
   </si>
   <si>
@@ -2548,12 +2548,12 @@
     <t>039</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
     <t>ALB</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2746,12 +2746,12 @@
     <t>155</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
     <t>AUT</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2854,24 +2854,24 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
     <t>162</t>
   </si>
   <si>
@@ -2944,12 +2944,12 @@
     <t>054</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
     <t>FJI</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -3010,12 +3010,12 @@
     <t>057</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
     <t>GUM</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -3112,10 +3112,10 @@
     <t>061</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
     <t>ASM</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
   </si>
   <si>
     <t>184</t>
@@ -3612,10 +3612,10 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2" t="s">
@@ -3647,12 +3647,12 @@
       <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" t="s">
         <v>26</v>
       </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
       <c r="I3" t="s">
         <v>19</v>
       </c>
@@ -3660,10 +3660,10 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
         <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -3682,12 +3682,12 @@
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" t="s">
         <v>30</v>
       </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
       <c r="I4" t="s">
         <v>19</v>
       </c>
@@ -3695,10 +3695,10 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
         <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
       </c>
       <c r="M4" t="s">
         <v>23</v>
@@ -3717,12 +3717,12 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
       <c r="G5" t="s">
         <v>34</v>
       </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
       <c r="I5" t="s">
         <v>19</v>
       </c>
@@ -3730,10 +3730,10 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
         <v>35</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
       </c>
       <c r="M5" t="s">
         <v>23</v>
@@ -3752,12 +3752,12 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" t="s">
         <v>38</v>
       </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
@@ -3765,10 +3765,10 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
         <v>39</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -3787,12 +3787,12 @@
       <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
       <c r="G7" t="s">
         <v>42</v>
       </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
@@ -3800,10 +3800,10 @@
         <v>20</v>
       </c>
       <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
         <v>43</v>
-      </c>
-      <c r="L7" t="s">
-        <v>22</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
@@ -3822,12 +3822,12 @@
       <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
       <c r="G8" t="s">
         <v>46</v>
       </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
@@ -3835,10 +3835,10 @@
         <v>20</v>
       </c>
       <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
         <v>47</v>
-      </c>
-      <c r="L8" t="s">
-        <v>22</v>
       </c>
       <c r="M8" t="s">
         <v>23</v>
@@ -3861,13 +3861,13 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
@@ -3879,10 +3879,10 @@
         <v>54</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M9" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3902,13 +3902,13 @@
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
         <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
@@ -3917,13 +3917,13 @@
         <v>53</v>
       </c>
       <c r="K10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
         <v>59</v>
       </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3943,13 +3943,13 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
         <v>62</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
@@ -3958,13 +3958,13 @@
         <v>53</v>
       </c>
       <c r="K11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
         <v>63</v>
       </c>
-      <c r="L11" t="s">
-        <v>22</v>
-      </c>
       <c r="M11" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3984,13 +3984,13 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
         <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
@@ -3999,13 +3999,13 @@
         <v>53</v>
       </c>
       <c r="K12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" t="s">
         <v>67</v>
       </c>
-      <c r="L12" t="s">
-        <v>22</v>
-      </c>
       <c r="M12" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4025,13 +4025,13 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
         <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
@@ -4040,13 +4040,13 @@
         <v>53</v>
       </c>
       <c r="K13" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" t="s">
         <v>71</v>
       </c>
-      <c r="L13" t="s">
-        <v>22</v>
-      </c>
       <c r="M13" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -4066,13 +4066,13 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
         <v>74</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
@@ -4081,13 +4081,13 @@
         <v>53</v>
       </c>
       <c r="K14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" t="s">
         <v>75</v>
       </c>
-      <c r="L14" t="s">
-        <v>22</v>
-      </c>
       <c r="M14" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4107,13 +4107,13 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
         <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
@@ -4122,13 +4122,13 @@
         <v>53</v>
       </c>
       <c r="K15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" t="s">
         <v>79</v>
       </c>
-      <c r="L15" t="s">
-        <v>22</v>
-      </c>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4148,13 +4148,13 @@
         <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
         <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
@@ -4163,13 +4163,13 @@
         <v>53</v>
       </c>
       <c r="K16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s">
         <v>83</v>
       </c>
-      <c r="L16" t="s">
-        <v>22</v>
-      </c>
       <c r="M16" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4189,13 +4189,13 @@
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s">
         <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
         <v>19</v>
@@ -4204,13 +4204,13 @@
         <v>53</v>
       </c>
       <c r="K17" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" t="s">
         <v>87</v>
       </c>
-      <c r="L17" t="s">
-        <v>22</v>
-      </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4230,13 +4230,13 @@
         <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
         <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
         <v>19</v>
@@ -4245,13 +4245,13 @@
         <v>53</v>
       </c>
       <c r="K18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" t="s">
         <v>91</v>
       </c>
-      <c r="L18" t="s">
-        <v>22</v>
-      </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -4271,13 +4271,13 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
         <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
@@ -4286,13 +4286,13 @@
         <v>53</v>
       </c>
       <c r="K19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" t="s">
         <v>95</v>
       </c>
-      <c r="L19" t="s">
-        <v>22</v>
-      </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4312,13 +4312,13 @@
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
         <v>98</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
@@ -4327,13 +4327,13 @@
         <v>53</v>
       </c>
       <c r="K20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" t="s">
         <v>99</v>
       </c>
-      <c r="L20" t="s">
-        <v>22</v>
-      </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4353,13 +4353,13 @@
         <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
         <v>102</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
         <v>19</v>
@@ -4368,13 +4368,13 @@
         <v>53</v>
       </c>
       <c r="K21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" t="s">
         <v>103</v>
       </c>
-      <c r="L21" t="s">
-        <v>22</v>
-      </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4394,13 +4394,13 @@
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
         <v>106</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
         <v>19</v>
@@ -4409,13 +4409,13 @@
         <v>53</v>
       </c>
       <c r="K22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" t="s">
         <v>107</v>
       </c>
-      <c r="L22" t="s">
-        <v>22</v>
-      </c>
       <c r="M22" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4435,13 +4435,13 @@
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
         <v>110</v>
       </c>
       <c r="H23" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
         <v>19</v>
@@ -4450,13 +4450,13 @@
         <v>53</v>
       </c>
       <c r="K23" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" t="s">
         <v>111</v>
       </c>
-      <c r="L23" t="s">
-        <v>22</v>
-      </c>
       <c r="M23" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -4476,13 +4476,13 @@
         <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
         <v>114</v>
       </c>
       <c r="H24" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
         <v>19</v>
@@ -4491,13 +4491,13 @@
         <v>53</v>
       </c>
       <c r="K24" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" t="s">
         <v>115</v>
       </c>
-      <c r="L24" t="s">
-        <v>22</v>
-      </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -4517,13 +4517,13 @@
         <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
         <v>118</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
         <v>19</v>
@@ -4532,13 +4532,13 @@
         <v>53</v>
       </c>
       <c r="K25" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" t="s">
         <v>119</v>
       </c>
-      <c r="L25" t="s">
-        <v>22</v>
-      </c>
       <c r="M25" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -4558,13 +4558,13 @@
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G26" t="s">
         <v>122</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
         <v>19</v>
@@ -4573,13 +4573,13 @@
         <v>53</v>
       </c>
       <c r="K26" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" t="s">
         <v>123</v>
       </c>
-      <c r="L26" t="s">
-        <v>22</v>
-      </c>
       <c r="M26" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -4599,13 +4599,13 @@
         <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
         <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
         <v>19</v>
@@ -4614,13 +4614,13 @@
         <v>53</v>
       </c>
       <c r="K27" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" t="s">
         <v>127</v>
       </c>
-      <c r="L27" t="s">
-        <v>22</v>
-      </c>
       <c r="M27" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4640,13 +4640,13 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
         <v>130</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
@@ -4655,13 +4655,13 @@
         <v>53</v>
       </c>
       <c r="K28" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" t="s">
         <v>131</v>
       </c>
-      <c r="L28" t="s">
-        <v>22</v>
-      </c>
       <c r="M28" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4681,13 +4681,13 @@
         <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
         <v>134</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
@@ -4696,13 +4696,13 @@
         <v>53</v>
       </c>
       <c r="K29" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" t="s">
         <v>135</v>
       </c>
-      <c r="L29" t="s">
-        <v>22</v>
-      </c>
       <c r="M29" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -4722,13 +4722,13 @@
         <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G30" t="s">
         <v>138</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
         <v>19</v>
@@ -4737,13 +4737,13 @@
         <v>53</v>
       </c>
       <c r="K30" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" t="s">
         <v>139</v>
       </c>
-      <c r="L30" t="s">
-        <v>22</v>
-      </c>
       <c r="M30" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4763,13 +4763,13 @@
         <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H31" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
@@ -4778,13 +4778,13 @@
         <v>53</v>
       </c>
       <c r="K31" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" t="s">
         <v>145</v>
       </c>
-      <c r="L31" t="s">
-        <v>22</v>
-      </c>
       <c r="M31" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4804,13 +4804,13 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
         <v>148</v>
       </c>
       <c r="H32" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
         <v>19</v>
@@ -4819,13 +4819,13 @@
         <v>53</v>
       </c>
       <c r="K32" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" t="s">
         <v>149</v>
       </c>
-      <c r="L32" t="s">
-        <v>22</v>
-      </c>
       <c r="M32" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4845,13 +4845,13 @@
         <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
         <v>152</v>
       </c>
       <c r="H33" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
         <v>19</v>
@@ -4860,13 +4860,13 @@
         <v>53</v>
       </c>
       <c r="K33" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" t="s">
         <v>153</v>
       </c>
-      <c r="L33" t="s">
-        <v>22</v>
-      </c>
       <c r="M33" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4886,13 +4886,13 @@
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G34" t="s">
         <v>156</v>
       </c>
       <c r="H34" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
         <v>19</v>
@@ -4901,13 +4901,13 @@
         <v>53</v>
       </c>
       <c r="K34" t="s">
+        <v>54</v>
+      </c>
+      <c r="L34" t="s">
         <v>157</v>
       </c>
-      <c r="L34" t="s">
-        <v>22</v>
-      </c>
       <c r="M34" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -4927,13 +4927,13 @@
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G35" t="s">
         <v>160</v>
       </c>
       <c r="H35" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
         <v>19</v>
@@ -4942,13 +4942,13 @@
         <v>53</v>
       </c>
       <c r="K35" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" t="s">
         <v>161</v>
       </c>
-      <c r="L35" t="s">
-        <v>22</v>
-      </c>
       <c r="M35" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -4968,13 +4968,13 @@
         <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
         <v>164</v>
       </c>
       <c r="H36" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
@@ -4983,13 +4983,13 @@
         <v>53</v>
       </c>
       <c r="K36" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" t="s">
         <v>165</v>
       </c>
-      <c r="L36" t="s">
-        <v>22</v>
-      </c>
       <c r="M36" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5009,13 +5009,13 @@
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G37" t="s">
         <v>168</v>
       </c>
       <c r="H37" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
@@ -5024,13 +5024,13 @@
         <v>53</v>
       </c>
       <c r="K37" t="s">
+        <v>54</v>
+      </c>
+      <c r="L37" t="s">
         <v>169</v>
       </c>
-      <c r="L37" t="s">
-        <v>22</v>
-      </c>
       <c r="M37" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5050,13 +5050,13 @@
         <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G38" t="s">
         <v>172</v>
       </c>
       <c r="H38" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
@@ -5065,13 +5065,13 @@
         <v>53</v>
       </c>
       <c r="K38" t="s">
+        <v>54</v>
+      </c>
+      <c r="L38" t="s">
         <v>173</v>
       </c>
-      <c r="L38" t="s">
-        <v>22</v>
-      </c>
       <c r="M38" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -5091,13 +5091,13 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G39" t="s">
         <v>176</v>
       </c>
       <c r="H39" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
         <v>19</v>
@@ -5106,13 +5106,13 @@
         <v>53</v>
       </c>
       <c r="K39" t="s">
+        <v>54</v>
+      </c>
+      <c r="L39" t="s">
         <v>177</v>
       </c>
-      <c r="L39" t="s">
-        <v>22</v>
-      </c>
       <c r="M39" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -5132,13 +5132,13 @@
         <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="G40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H40" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
@@ -5147,13 +5147,13 @@
         <v>53</v>
       </c>
       <c r="K40" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" t="s">
         <v>183</v>
       </c>
-      <c r="L40" t="s">
-        <v>22</v>
-      </c>
       <c r="M40" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -5173,13 +5173,13 @@
         <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="G41" t="s">
         <v>186</v>
       </c>
       <c r="H41" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
         <v>19</v>
@@ -5188,13 +5188,13 @@
         <v>53</v>
       </c>
       <c r="K41" t="s">
+        <v>54</v>
+      </c>
+      <c r="L41" t="s">
         <v>187</v>
       </c>
-      <c r="L41" t="s">
-        <v>22</v>
-      </c>
       <c r="M41" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5214,13 +5214,13 @@
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="G42" t="s">
         <v>190</v>
       </c>
       <c r="H42" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
         <v>19</v>
@@ -5229,13 +5229,13 @@
         <v>53</v>
       </c>
       <c r="K42" t="s">
+        <v>54</v>
+      </c>
+      <c r="L42" t="s">
         <v>191</v>
       </c>
-      <c r="L42" t="s">
-        <v>22</v>
-      </c>
       <c r="M42" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5255,13 +5255,13 @@
         <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="G43" t="s">
         <v>194</v>
       </c>
       <c r="H43" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
         <v>19</v>
@@ -5270,13 +5270,13 @@
         <v>53</v>
       </c>
       <c r="K43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" t="s">
         <v>195</v>
       </c>
-      <c r="L43" t="s">
-        <v>22</v>
-      </c>
       <c r="M43" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5296,13 +5296,13 @@
         <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="G44" t="s">
         <v>198</v>
       </c>
       <c r="H44" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
         <v>19</v>
@@ -5311,13 +5311,13 @@
         <v>53</v>
       </c>
       <c r="K44" t="s">
+        <v>54</v>
+      </c>
+      <c r="L44" t="s">
         <v>199</v>
       </c>
-      <c r="L44" t="s">
-        <v>22</v>
-      </c>
       <c r="M44" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -5337,13 +5337,13 @@
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H45" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -5352,13 +5352,13 @@
         <v>53</v>
       </c>
       <c r="K45" t="s">
+        <v>54</v>
+      </c>
+      <c r="L45" t="s">
         <v>205</v>
       </c>
-      <c r="L45" t="s">
-        <v>22</v>
-      </c>
       <c r="M45" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -5378,13 +5378,13 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G46" t="s">
         <v>208</v>
       </c>
       <c r="H46" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -5393,13 +5393,13 @@
         <v>53</v>
       </c>
       <c r="K46" t="s">
+        <v>54</v>
+      </c>
+      <c r="L46" t="s">
         <v>209</v>
       </c>
-      <c r="L46" t="s">
-        <v>22</v>
-      </c>
       <c r="M46" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -5419,13 +5419,13 @@
         <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G47" t="s">
         <v>212</v>
       </c>
       <c r="H47" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -5434,13 +5434,13 @@
         <v>53</v>
       </c>
       <c r="K47" t="s">
+        <v>54</v>
+      </c>
+      <c r="L47" t="s">
         <v>213</v>
       </c>
-      <c r="L47" t="s">
-        <v>22</v>
-      </c>
       <c r="M47" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -5460,13 +5460,13 @@
         <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G48" t="s">
         <v>216</v>
       </c>
       <c r="H48" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -5475,13 +5475,13 @@
         <v>53</v>
       </c>
       <c r="K48" t="s">
+        <v>54</v>
+      </c>
+      <c r="L48" t="s">
         <v>217</v>
       </c>
-      <c r="L48" t="s">
-        <v>22</v>
-      </c>
       <c r="M48" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -5501,13 +5501,13 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G49" t="s">
         <v>220</v>
       </c>
       <c r="H49" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -5516,13 +5516,13 @@
         <v>53</v>
       </c>
       <c r="K49" t="s">
+        <v>54</v>
+      </c>
+      <c r="L49" t="s">
         <v>221</v>
       </c>
-      <c r="L49" t="s">
-        <v>22</v>
-      </c>
       <c r="M49" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -5542,13 +5542,13 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G50" t="s">
         <v>224</v>
       </c>
       <c r="H50" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -5557,13 +5557,13 @@
         <v>53</v>
       </c>
       <c r="K50" t="s">
+        <v>54</v>
+      </c>
+      <c r="L50" t="s">
         <v>225</v>
       </c>
-      <c r="L50" t="s">
-        <v>22</v>
-      </c>
       <c r="M50" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -5583,13 +5583,13 @@
         <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G51" t="s">
         <v>228</v>
       </c>
       <c r="H51" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
@@ -5598,13 +5598,13 @@
         <v>53</v>
       </c>
       <c r="K51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L51" t="s">
         <v>229</v>
       </c>
-      <c r="L51" t="s">
-        <v>22</v>
-      </c>
       <c r="M51" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -5624,13 +5624,13 @@
         <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G52" t="s">
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -5639,13 +5639,13 @@
         <v>53</v>
       </c>
       <c r="K52" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52" t="s">
         <v>233</v>
       </c>
-      <c r="L52" t="s">
-        <v>22</v>
-      </c>
       <c r="M52" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -5665,13 +5665,13 @@
         <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G53" t="s">
         <v>236</v>
       </c>
       <c r="H53" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
@@ -5680,13 +5680,13 @@
         <v>53</v>
       </c>
       <c r="K53" t="s">
+        <v>54</v>
+      </c>
+      <c r="L53" t="s">
         <v>237</v>
       </c>
-      <c r="L53" t="s">
-        <v>22</v>
-      </c>
       <c r="M53" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5706,13 +5706,13 @@
         <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G54" t="s">
         <v>240</v>
       </c>
       <c r="H54" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
         <v>19</v>
@@ -5721,13 +5721,13 @@
         <v>53</v>
       </c>
       <c r="K54" t="s">
+        <v>54</v>
+      </c>
+      <c r="L54" t="s">
         <v>241</v>
       </c>
-      <c r="L54" t="s">
-        <v>22</v>
-      </c>
       <c r="M54" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -5747,13 +5747,13 @@
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G55" t="s">
         <v>244</v>
       </c>
       <c r="H55" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -5762,13 +5762,13 @@
         <v>53</v>
       </c>
       <c r="K55" t="s">
+        <v>54</v>
+      </c>
+      <c r="L55" t="s">
         <v>245</v>
       </c>
-      <c r="L55" t="s">
-        <v>22</v>
-      </c>
       <c r="M55" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -5788,13 +5788,13 @@
         <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G56" t="s">
         <v>248</v>
       </c>
       <c r="H56" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
@@ -5803,13 +5803,13 @@
         <v>53</v>
       </c>
       <c r="K56" t="s">
+        <v>54</v>
+      </c>
+      <c r="L56" t="s">
         <v>249</v>
       </c>
-      <c r="L56" t="s">
-        <v>22</v>
-      </c>
       <c r="M56" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -5829,13 +5829,13 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G57" t="s">
         <v>252</v>
       </c>
       <c r="H57" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
         <v>19</v>
@@ -5844,13 +5844,13 @@
         <v>53</v>
       </c>
       <c r="K57" t="s">
+        <v>54</v>
+      </c>
+      <c r="L57" t="s">
         <v>253</v>
       </c>
-      <c r="L57" t="s">
-        <v>22</v>
-      </c>
       <c r="M57" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -5870,13 +5870,13 @@
         <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G58" t="s">
         <v>256</v>
       </c>
       <c r="H58" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
@@ -5885,13 +5885,13 @@
         <v>53</v>
       </c>
       <c r="K58" t="s">
+        <v>54</v>
+      </c>
+      <c r="L58" t="s">
         <v>257</v>
       </c>
-      <c r="L58" t="s">
-        <v>22</v>
-      </c>
       <c r="M58" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -5911,13 +5911,13 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G59" t="s">
         <v>260</v>
       </c>
       <c r="H59" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -5926,13 +5926,13 @@
         <v>53</v>
       </c>
       <c r="K59" t="s">
+        <v>54</v>
+      </c>
+      <c r="L59" t="s">
         <v>261</v>
       </c>
-      <c r="L59" t="s">
-        <v>22</v>
-      </c>
       <c r="M59" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -5952,13 +5952,13 @@
         <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G60" t="s">
         <v>264</v>
       </c>
       <c r="H60" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
@@ -5967,13 +5967,13 @@
         <v>53</v>
       </c>
       <c r="K60" t="s">
+        <v>54</v>
+      </c>
+      <c r="L60" t="s">
         <v>265</v>
       </c>
-      <c r="L60" t="s">
-        <v>22</v>
-      </c>
       <c r="M60" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -5993,13 +5993,13 @@
         <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G61" t="s">
         <v>268</v>
       </c>
       <c r="H61" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -6008,13 +6008,13 @@
         <v>53</v>
       </c>
       <c r="K61" t="s">
+        <v>54</v>
+      </c>
+      <c r="L61" t="s">
         <v>269</v>
       </c>
-      <c r="L61" t="s">
-        <v>22</v>
-      </c>
       <c r="M61" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6043,16 +6043,16 @@
         <v>275</v>
       </c>
       <c r="I62" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" t="s">
         <v>276</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>277</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>278</v>
-      </c>
-      <c r="L62" t="s">
-        <v>22</v>
       </c>
       <c r="M62" t="s">
         <v>279</v>
@@ -6084,16 +6084,16 @@
         <v>275</v>
       </c>
       <c r="I63" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" t="s">
         <v>276</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>277</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" t="s">
         <v>283</v>
-      </c>
-      <c r="L63" t="s">
-        <v>22</v>
       </c>
       <c r="M63" t="s">
         <v>279</v>
@@ -6125,16 +6125,16 @@
         <v>275</v>
       </c>
       <c r="I64" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" t="s">
         <v>276</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>277</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>287</v>
-      </c>
-      <c r="L64" t="s">
-        <v>22</v>
       </c>
       <c r="M64" t="s">
         <v>279</v>
@@ -6166,16 +6166,16 @@
         <v>275</v>
       </c>
       <c r="I65" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" t="s">
         <v>276</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>277</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>291</v>
-      </c>
-      <c r="L65" t="s">
-        <v>22</v>
       </c>
       <c r="M65" t="s">
         <v>279</v>
@@ -6207,16 +6207,16 @@
         <v>275</v>
       </c>
       <c r="I66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s">
         <v>276</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>277</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>295</v>
-      </c>
-      <c r="L66" t="s">
-        <v>22</v>
       </c>
       <c r="M66" t="s">
         <v>279</v>
@@ -6248,16 +6248,16 @@
         <v>275</v>
       </c>
       <c r="I67" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s">
         <v>276</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>277</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>299</v>
-      </c>
-      <c r="L67" t="s">
-        <v>22</v>
       </c>
       <c r="M67" t="s">
         <v>279</v>
@@ -6289,16 +6289,16 @@
         <v>275</v>
       </c>
       <c r="I68" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" t="s">
         <v>276</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>277</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>303</v>
-      </c>
-      <c r="L68" t="s">
-        <v>22</v>
       </c>
       <c r="M68" t="s">
         <v>279</v>
@@ -6330,16 +6330,16 @@
         <v>275</v>
       </c>
       <c r="I69" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" t="s">
         <v>276</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>277</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>307</v>
-      </c>
-      <c r="L69" t="s">
-        <v>22</v>
       </c>
       <c r="M69" t="s">
         <v>279</v>
@@ -6371,16 +6371,16 @@
         <v>275</v>
       </c>
       <c r="I70" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" t="s">
         <v>276</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>277</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>311</v>
-      </c>
-      <c r="L70" t="s">
-        <v>22</v>
       </c>
       <c r="M70" t="s">
         <v>279</v>
@@ -6412,16 +6412,16 @@
         <v>275</v>
       </c>
       <c r="I71" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" t="s">
         <v>276</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>277</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>315</v>
-      </c>
-      <c r="L71" t="s">
-        <v>22</v>
       </c>
       <c r="M71" t="s">
         <v>279</v>
@@ -6453,16 +6453,16 @@
         <v>275</v>
       </c>
       <c r="I72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" t="s">
         <v>276</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>277</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>319</v>
-      </c>
-      <c r="L72" t="s">
-        <v>22</v>
       </c>
       <c r="M72" t="s">
         <v>279</v>
@@ -6494,16 +6494,16 @@
         <v>275</v>
       </c>
       <c r="I73" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" t="s">
         <v>276</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>277</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>323</v>
-      </c>
-      <c r="L73" t="s">
-        <v>22</v>
       </c>
       <c r="M73" t="s">
         <v>279</v>
@@ -6535,16 +6535,16 @@
         <v>275</v>
       </c>
       <c r="I74" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" t="s">
         <v>276</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>277</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>327</v>
-      </c>
-      <c r="L74" t="s">
-        <v>22</v>
       </c>
       <c r="M74" t="s">
         <v>279</v>
@@ -6576,16 +6576,16 @@
         <v>275</v>
       </c>
       <c r="I75" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" t="s">
         <v>276</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>277</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>331</v>
-      </c>
-      <c r="L75" t="s">
-        <v>22</v>
       </c>
       <c r="M75" t="s">
         <v>279</v>
@@ -6617,16 +6617,16 @@
         <v>275</v>
       </c>
       <c r="I76" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" t="s">
         <v>276</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>277</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>335</v>
-      </c>
-      <c r="L76" t="s">
-        <v>22</v>
       </c>
       <c r="M76" t="s">
         <v>279</v>
@@ -6658,16 +6658,16 @@
         <v>275</v>
       </c>
       <c r="I77" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" t="s">
         <v>276</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>277</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>339</v>
-      </c>
-      <c r="L77" t="s">
-        <v>22</v>
       </c>
       <c r="M77" t="s">
         <v>279</v>
@@ -6699,16 +6699,16 @@
         <v>275</v>
       </c>
       <c r="I78" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s">
         <v>276</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>277</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>343</v>
-      </c>
-      <c r="L78" t="s">
-        <v>22</v>
       </c>
       <c r="M78" t="s">
         <v>279</v>
@@ -6740,16 +6740,16 @@
         <v>275</v>
       </c>
       <c r="I79" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" t="s">
         <v>276</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>277</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>347</v>
-      </c>
-      <c r="L79" t="s">
-        <v>22</v>
       </c>
       <c r="M79" t="s">
         <v>279</v>
@@ -6781,16 +6781,16 @@
         <v>275</v>
       </c>
       <c r="I80" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" t="s">
         <v>276</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>277</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>351</v>
-      </c>
-      <c r="L80" t="s">
-        <v>22</v>
       </c>
       <c r="M80" t="s">
         <v>279</v>
@@ -6822,16 +6822,16 @@
         <v>275</v>
       </c>
       <c r="I81" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" t="s">
         <v>276</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>277</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>355</v>
-      </c>
-      <c r="L81" t="s">
-        <v>22</v>
       </c>
       <c r="M81" t="s">
         <v>279</v>
@@ -6863,16 +6863,16 @@
         <v>275</v>
       </c>
       <c r="I82" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s">
         <v>276</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>277</v>
       </c>
-      <c r="K82" t="s">
+      <c r="L82" t="s">
         <v>359</v>
-      </c>
-      <c r="L82" t="s">
-        <v>22</v>
       </c>
       <c r="M82" t="s">
         <v>279</v>
@@ -6904,16 +6904,16 @@
         <v>275</v>
       </c>
       <c r="I83" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s">
         <v>276</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>277</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>363</v>
-      </c>
-      <c r="L83" t="s">
-        <v>22</v>
       </c>
       <c r="M83" t="s">
         <v>279</v>
@@ -6945,16 +6945,16 @@
         <v>275</v>
       </c>
       <c r="I84" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" t="s">
         <v>276</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>277</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>367</v>
-      </c>
-      <c r="L84" t="s">
-        <v>22</v>
       </c>
       <c r="M84" t="s">
         <v>279</v>
@@ -6986,16 +6986,16 @@
         <v>275</v>
       </c>
       <c r="I85" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s">
         <v>276</v>
       </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>277</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
         <v>371</v>
-      </c>
-      <c r="L85" t="s">
-        <v>22</v>
       </c>
       <c r="M85" t="s">
         <v>279</v>
@@ -7027,16 +7027,16 @@
         <v>275</v>
       </c>
       <c r="I86" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" t="s">
         <v>276</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>277</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>375</v>
-      </c>
-      <c r="L86" t="s">
-        <v>22</v>
       </c>
       <c r="M86" t="s">
         <v>279</v>
@@ -7068,16 +7068,16 @@
         <v>275</v>
       </c>
       <c r="I87" t="s">
+        <v>19</v>
+      </c>
+      <c r="J87" t="s">
         <v>276</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>277</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>379</v>
-      </c>
-      <c r="L87" t="s">
-        <v>22</v>
       </c>
       <c r="M87" t="s">
         <v>279</v>
@@ -7109,16 +7109,16 @@
         <v>275</v>
       </c>
       <c r="I88" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s">
         <v>276</v>
       </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>277</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" t="s">
         <v>383</v>
-      </c>
-      <c r="L88" t="s">
-        <v>22</v>
       </c>
       <c r="M88" t="s">
         <v>279</v>
@@ -7150,16 +7150,16 @@
         <v>275</v>
       </c>
       <c r="I89" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" t="s">
         <v>276</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>277</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" t="s">
         <v>387</v>
-      </c>
-      <c r="L89" t="s">
-        <v>22</v>
       </c>
       <c r="M89" t="s">
         <v>279</v>
@@ -7182,25 +7182,25 @@
         <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G90" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H90" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I90" t="s">
+        <v>19</v>
+      </c>
+      <c r="J90" t="s">
         <v>276</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>277</v>
       </c>
-      <c r="K90" t="s">
+      <c r="L90" t="s">
         <v>393</v>
-      </c>
-      <c r="L90" t="s">
-        <v>22</v>
       </c>
       <c r="M90" t="s">
         <v>279</v>
@@ -7223,25 +7223,25 @@
         <v>16</v>
       </c>
       <c r="F91" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G91" t="s">
         <v>396</v>
       </c>
       <c r="H91" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I91" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" t="s">
         <v>276</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>277</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" t="s">
         <v>397</v>
-      </c>
-      <c r="L91" t="s">
-        <v>22</v>
       </c>
       <c r="M91" t="s">
         <v>279</v>
@@ -7264,25 +7264,25 @@
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G92" t="s">
         <v>400</v>
       </c>
       <c r="H92" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I92" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" t="s">
         <v>276</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>277</v>
       </c>
-      <c r="K92" t="s">
+      <c r="L92" t="s">
         <v>401</v>
-      </c>
-      <c r="L92" t="s">
-        <v>22</v>
       </c>
       <c r="M92" t="s">
         <v>279</v>
@@ -7305,25 +7305,25 @@
         <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G93" t="s">
         <v>404</v>
       </c>
       <c r="H93" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I93" t="s">
+        <v>19</v>
+      </c>
+      <c r="J93" t="s">
         <v>276</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>277</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" t="s">
         <v>405</v>
-      </c>
-      <c r="L93" t="s">
-        <v>22</v>
       </c>
       <c r="M93" t="s">
         <v>279</v>
@@ -7346,25 +7346,25 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G94" t="s">
         <v>408</v>
       </c>
       <c r="H94" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I94" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" t="s">
         <v>276</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>277</v>
       </c>
-      <c r="K94" t="s">
+      <c r="L94" t="s">
         <v>409</v>
-      </c>
-      <c r="L94" t="s">
-        <v>22</v>
       </c>
       <c r="M94" t="s">
         <v>279</v>
@@ -7387,25 +7387,25 @@
         <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G95" t="s">
         <v>412</v>
       </c>
       <c r="H95" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I95" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s">
         <v>276</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>277</v>
       </c>
-      <c r="K95" t="s">
+      <c r="L95" t="s">
         <v>413</v>
-      </c>
-      <c r="L95" t="s">
-        <v>22</v>
       </c>
       <c r="M95" t="s">
         <v>279</v>
@@ -7428,25 +7428,25 @@
         <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G96" t="s">
         <v>416</v>
       </c>
       <c r="H96" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I96" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" t="s">
         <v>276</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>277</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" t="s">
         <v>417</v>
-      </c>
-      <c r="L96" t="s">
-        <v>22</v>
       </c>
       <c r="M96" t="s">
         <v>279</v>
@@ -7469,25 +7469,25 @@
         <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="G97" t="s">
         <v>420</v>
       </c>
       <c r="H97" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="I97" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" t="s">
         <v>276</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>277</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" t="s">
         <v>421</v>
-      </c>
-      <c r="L97" t="s">
-        <v>22</v>
       </c>
       <c r="M97" t="s">
         <v>279</v>
@@ -7510,25 +7510,25 @@
         <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G98" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H98" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I98" t="s">
+        <v>19</v>
+      </c>
+      <c r="J98" t="s">
         <v>276</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>277</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" t="s">
         <v>427</v>
-      </c>
-      <c r="L98" t="s">
-        <v>22</v>
       </c>
       <c r="M98" t="s">
         <v>279</v>
@@ -7551,25 +7551,25 @@
         <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G99" t="s">
         <v>430</v>
       </c>
       <c r="H99" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I99" t="s">
+        <v>19</v>
+      </c>
+      <c r="J99" t="s">
         <v>276</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>277</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>431</v>
-      </c>
-      <c r="L99" t="s">
-        <v>22</v>
       </c>
       <c r="M99" t="s">
         <v>279</v>
@@ -7592,25 +7592,25 @@
         <v>16</v>
       </c>
       <c r="F100" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G100" t="s">
         <v>434</v>
       </c>
       <c r="H100" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I100" t="s">
+        <v>19</v>
+      </c>
+      <c r="J100" t="s">
         <v>276</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>277</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" t="s">
         <v>435</v>
-      </c>
-      <c r="L100" t="s">
-        <v>22</v>
       </c>
       <c r="M100" t="s">
         <v>279</v>
@@ -7633,25 +7633,25 @@
         <v>16</v>
       </c>
       <c r="F101" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G101" t="s">
         <v>438</v>
       </c>
       <c r="H101" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s">
         <v>276</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>277</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" t="s">
         <v>439</v>
-      </c>
-      <c r="L101" t="s">
-        <v>22</v>
       </c>
       <c r="M101" t="s">
         <v>279</v>
@@ -7674,25 +7674,25 @@
         <v>16</v>
       </c>
       <c r="F102" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G102" t="s">
         <v>442</v>
       </c>
       <c r="H102" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I102" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s">
         <v>276</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>277</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>443</v>
-      </c>
-      <c r="L102" t="s">
-        <v>22</v>
       </c>
       <c r="M102" t="s">
         <v>279</v>
@@ -7715,25 +7715,25 @@
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G103" t="s">
         <v>446</v>
       </c>
       <c r="H103" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I103" t="s">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s">
         <v>276</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>277</v>
       </c>
-      <c r="K103" t="s">
+      <c r="L103" t="s">
         <v>447</v>
-      </c>
-      <c r="L103" t="s">
-        <v>22</v>
       </c>
       <c r="M103" t="s">
         <v>279</v>
@@ -7756,25 +7756,25 @@
         <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G104" t="s">
         <v>450</v>
       </c>
       <c r="H104" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I104" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s">
         <v>276</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>277</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" t="s">
         <v>451</v>
-      </c>
-      <c r="L104" t="s">
-        <v>22</v>
       </c>
       <c r="M104" t="s">
         <v>279</v>
@@ -7797,25 +7797,25 @@
         <v>16</v>
       </c>
       <c r="F105" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G105" t="s">
         <v>454</v>
       </c>
       <c r="H105" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I105" t="s">
+        <v>19</v>
+      </c>
+      <c r="J105" t="s">
         <v>276</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>277</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>455</v>
-      </c>
-      <c r="L105" t="s">
-        <v>22</v>
       </c>
       <c r="M105" t="s">
         <v>279</v>
@@ -7838,25 +7838,25 @@
         <v>16</v>
       </c>
       <c r="F106" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G106" t="s">
         <v>458</v>
       </c>
       <c r="H106" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" t="s">
         <v>276</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>277</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
         <v>459</v>
-      </c>
-      <c r="L106" t="s">
-        <v>22</v>
       </c>
       <c r="M106" t="s">
         <v>279</v>
@@ -7879,25 +7879,25 @@
         <v>16</v>
       </c>
       <c r="F107" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G107" t="s">
         <v>462</v>
       </c>
       <c r="H107" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I107" t="s">
+        <v>19</v>
+      </c>
+      <c r="J107" t="s">
         <v>276</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>277</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" t="s">
         <v>463</v>
-      </c>
-      <c r="L107" t="s">
-        <v>22</v>
       </c>
       <c r="M107" t="s">
         <v>279</v>
@@ -7920,25 +7920,25 @@
         <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G108" t="s">
         <v>466</v>
       </c>
       <c r="H108" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I108" t="s">
+        <v>19</v>
+      </c>
+      <c r="J108" t="s">
         <v>276</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>277</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" t="s">
         <v>467</v>
-      </c>
-      <c r="L108" t="s">
-        <v>22</v>
       </c>
       <c r="M108" t="s">
         <v>279</v>
@@ -7961,25 +7961,25 @@
         <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G109" t="s">
         <v>470</v>
       </c>
       <c r="H109" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I109" t="s">
+        <v>19</v>
+      </c>
+      <c r="J109" t="s">
         <v>276</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>277</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" t="s">
         <v>471</v>
-      </c>
-      <c r="L109" t="s">
-        <v>22</v>
       </c>
       <c r="M109" t="s">
         <v>279</v>
@@ -8002,25 +8002,25 @@
         <v>16</v>
       </c>
       <c r="F110" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G110" t="s">
         <v>474</v>
       </c>
       <c r="H110" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I110" t="s">
+        <v>19</v>
+      </c>
+      <c r="J110" t="s">
         <v>276</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>277</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" t="s">
         <v>475</v>
-      </c>
-      <c r="L110" t="s">
-        <v>22</v>
       </c>
       <c r="M110" t="s">
         <v>279</v>
@@ -8043,25 +8043,25 @@
         <v>16</v>
       </c>
       <c r="F111" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G111" t="s">
         <v>478</v>
       </c>
       <c r="H111" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I111" t="s">
+        <v>19</v>
+      </c>
+      <c r="J111" t="s">
         <v>276</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>277</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" t="s">
         <v>479</v>
-      </c>
-      <c r="L111" t="s">
-        <v>22</v>
       </c>
       <c r="M111" t="s">
         <v>279</v>
@@ -8084,25 +8084,25 @@
         <v>16</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G112" t="s">
         <v>482</v>
       </c>
       <c r="H112" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I112" t="s">
+        <v>19</v>
+      </c>
+      <c r="J112" t="s">
         <v>276</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>277</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" t="s">
         <v>483</v>
-      </c>
-      <c r="L112" t="s">
-        <v>22</v>
       </c>
       <c r="M112" t="s">
         <v>279</v>
@@ -8125,25 +8125,25 @@
         <v>16</v>
       </c>
       <c r="F113" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="G113" t="s">
         <v>486</v>
       </c>
       <c r="H113" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="I113" t="s">
+        <v>19</v>
+      </c>
+      <c r="J113" t="s">
         <v>276</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>277</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>487</v>
-      </c>
-      <c r="L113" t="s">
-        <v>22</v>
       </c>
       <c r="M113" t="s">
         <v>279</v>
@@ -8162,14 +8162,14 @@
       <c r="E114" t="s">
         <v>16</v>
       </c>
-      <c r="F114" t="s">
-        <v>273</v>
-      </c>
       <c r="G114" t="s">
         <v>490</v>
       </c>
+      <c r="H114" t="s">
+        <v>275</v>
+      </c>
       <c r="I114" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="J114" t="s">
         <v>491</v>
@@ -8178,10 +8178,10 @@
         <v>492</v>
       </c>
       <c r="L114" t="s">
-        <v>22</v>
+        <v>493</v>
       </c>
       <c r="M114" t="s">
-        <v>493</v>
+        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -8197,26 +8197,26 @@
       <c r="E115" t="s">
         <v>16</v>
       </c>
-      <c r="F115" t="s">
-        <v>273</v>
-      </c>
       <c r="G115" t="s">
         <v>496</v>
       </c>
+      <c r="H115" t="s">
+        <v>275</v>
+      </c>
       <c r="I115" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s">
         <v>491</v>
       </c>
       <c r="K115" t="s">
+        <v>492</v>
+      </c>
+      <c r="L115" t="s">
         <v>497</v>
       </c>
-      <c r="L115" t="s">
-        <v>22</v>
-      </c>
       <c r="M115" t="s">
-        <v>493</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -8232,26 +8232,26 @@
       <c r="E116" t="s">
         <v>16</v>
       </c>
-      <c r="F116" t="s">
-        <v>273</v>
-      </c>
       <c r="G116" t="s">
         <v>500</v>
       </c>
+      <c r="H116" t="s">
+        <v>275</v>
+      </c>
       <c r="I116" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="J116" t="s">
         <v>491</v>
       </c>
       <c r="K116" t="s">
+        <v>492</v>
+      </c>
+      <c r="L116" t="s">
         <v>501</v>
       </c>
-      <c r="L116" t="s">
-        <v>22</v>
-      </c>
       <c r="M116" t="s">
-        <v>493</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -8267,26 +8267,26 @@
       <c r="E117" t="s">
         <v>16</v>
       </c>
-      <c r="F117" t="s">
-        <v>273</v>
-      </c>
       <c r="G117" t="s">
         <v>504</v>
       </c>
+      <c r="H117" t="s">
+        <v>275</v>
+      </c>
       <c r="I117" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="J117" t="s">
         <v>491</v>
       </c>
       <c r="K117" t="s">
+        <v>492</v>
+      </c>
+      <c r="L117" t="s">
         <v>505</v>
       </c>
-      <c r="L117" t="s">
-        <v>22</v>
-      </c>
       <c r="M117" t="s">
-        <v>493</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -8302,26 +8302,26 @@
       <c r="E118" t="s">
         <v>16</v>
       </c>
-      <c r="F118" t="s">
-        <v>273</v>
-      </c>
       <c r="G118" t="s">
         <v>508</v>
       </c>
+      <c r="H118" t="s">
+        <v>275</v>
+      </c>
       <c r="I118" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="J118" t="s">
         <v>491</v>
       </c>
       <c r="K118" t="s">
+        <v>492</v>
+      </c>
+      <c r="L118" t="s">
         <v>509</v>
       </c>
-      <c r="L118" t="s">
-        <v>22</v>
-      </c>
       <c r="M118" t="s">
-        <v>493</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -8340,11 +8340,11 @@
       <c r="G119" t="s">
         <v>512</v>
       </c>
-      <c r="K119" t="s">
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+      <c r="L119" t="s">
         <v>513</v>
-      </c>
-      <c r="L119" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -8360,23 +8360,23 @@
       <c r="E120" t="s">
         <v>16</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>516</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>517</v>
       </c>
       <c r="I120" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" t="s">
         <v>518</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>519</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>520</v>
-      </c>
-      <c r="L120" t="s">
-        <v>22</v>
       </c>
       <c r="M120" t="s">
         <v>521</v>
@@ -8395,23 +8395,23 @@
       <c r="E121" t="s">
         <v>16</v>
       </c>
-      <c r="F121" t="s">
-        <v>516</v>
-      </c>
       <c r="G121" t="s">
         <v>524</v>
       </c>
+      <c r="H121" t="s">
+        <v>517</v>
+      </c>
       <c r="I121" t="s">
+        <v>19</v>
+      </c>
+      <c r="J121" t="s">
         <v>518</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>519</v>
       </c>
-      <c r="K121" t="s">
+      <c r="L121" t="s">
         <v>525</v>
-      </c>
-      <c r="L121" t="s">
-        <v>22</v>
       </c>
       <c r="M121" t="s">
         <v>521</v>
@@ -8430,23 +8430,23 @@
       <c r="E122" t="s">
         <v>16</v>
       </c>
-      <c r="F122" t="s">
-        <v>516</v>
-      </c>
       <c r="G122" t="s">
         <v>528</v>
       </c>
+      <c r="H122" t="s">
+        <v>517</v>
+      </c>
       <c r="I122" t="s">
+        <v>19</v>
+      </c>
+      <c r="J122" t="s">
         <v>518</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>519</v>
       </c>
-      <c r="K122" t="s">
+      <c r="L122" t="s">
         <v>529</v>
-      </c>
-      <c r="L122" t="s">
-        <v>22</v>
       </c>
       <c r="M122" t="s">
         <v>521</v>
@@ -8465,23 +8465,23 @@
       <c r="E123" t="s">
         <v>16</v>
       </c>
-      <c r="F123" t="s">
-        <v>516</v>
-      </c>
       <c r="G123" t="s">
         <v>532</v>
       </c>
+      <c r="H123" t="s">
+        <v>517</v>
+      </c>
       <c r="I123" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" t="s">
         <v>518</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>519</v>
       </c>
-      <c r="K123" t="s">
+      <c r="L123" t="s">
         <v>533</v>
-      </c>
-      <c r="L123" t="s">
-        <v>22</v>
       </c>
       <c r="M123" t="s">
         <v>521</v>
@@ -8500,23 +8500,23 @@
       <c r="E124" t="s">
         <v>16</v>
       </c>
-      <c r="F124" t="s">
-        <v>516</v>
-      </c>
       <c r="G124" t="s">
         <v>536</v>
       </c>
+      <c r="H124" t="s">
+        <v>517</v>
+      </c>
       <c r="I124" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" t="s">
         <v>518</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>519</v>
       </c>
-      <c r="K124" t="s">
+      <c r="L124" t="s">
         <v>537</v>
-      </c>
-      <c r="L124" t="s">
-        <v>22</v>
       </c>
       <c r="M124" t="s">
         <v>521</v>
@@ -8535,14 +8535,14 @@
       <c r="E125" t="s">
         <v>16</v>
       </c>
-      <c r="F125" t="s">
-        <v>516</v>
-      </c>
       <c r="G125" t="s">
         <v>540</v>
       </c>
+      <c r="H125" t="s">
+        <v>517</v>
+      </c>
       <c r="I125" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J125" t="s">
         <v>541</v>
@@ -8551,10 +8551,10 @@
         <v>542</v>
       </c>
       <c r="L125" t="s">
-        <v>22</v>
+        <v>543</v>
       </c>
       <c r="M125" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -8570,26 +8570,26 @@
       <c r="E126" t="s">
         <v>16</v>
       </c>
-      <c r="F126" t="s">
-        <v>516</v>
-      </c>
       <c r="G126" t="s">
         <v>546</v>
       </c>
+      <c r="H126" t="s">
+        <v>517</v>
+      </c>
       <c r="I126" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J126" t="s">
         <v>541</v>
       </c>
       <c r="K126" t="s">
+        <v>542</v>
+      </c>
+      <c r="L126" t="s">
         <v>547</v>
       </c>
-      <c r="L126" t="s">
-        <v>22</v>
-      </c>
       <c r="M126" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -8605,26 +8605,26 @@
       <c r="E127" t="s">
         <v>16</v>
       </c>
-      <c r="F127" t="s">
-        <v>516</v>
-      </c>
       <c r="G127" t="s">
         <v>550</v>
       </c>
+      <c r="H127" t="s">
+        <v>517</v>
+      </c>
       <c r="I127" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J127" t="s">
         <v>541</v>
       </c>
       <c r="K127" t="s">
+        <v>542</v>
+      </c>
+      <c r="L127" t="s">
         <v>551</v>
       </c>
-      <c r="L127" t="s">
-        <v>22</v>
-      </c>
       <c r="M127" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -8640,26 +8640,26 @@
       <c r="E128" t="s">
         <v>16</v>
       </c>
-      <c r="F128" t="s">
-        <v>516</v>
-      </c>
       <c r="G128" t="s">
         <v>554</v>
       </c>
+      <c r="H128" t="s">
+        <v>517</v>
+      </c>
       <c r="I128" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J128" t="s">
         <v>541</v>
       </c>
       <c r="K128" t="s">
+        <v>542</v>
+      </c>
+      <c r="L128" t="s">
         <v>555</v>
       </c>
-      <c r="L128" t="s">
-        <v>22</v>
-      </c>
       <c r="M128" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -8675,26 +8675,26 @@
       <c r="E129" t="s">
         <v>16</v>
       </c>
-      <c r="F129" t="s">
-        <v>516</v>
-      </c>
       <c r="G129" t="s">
         <v>558</v>
       </c>
+      <c r="H129" t="s">
+        <v>517</v>
+      </c>
       <c r="I129" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J129" t="s">
         <v>541</v>
       </c>
       <c r="K129" t="s">
+        <v>542</v>
+      </c>
+      <c r="L129" t="s">
         <v>559</v>
       </c>
-      <c r="L129" t="s">
-        <v>22</v>
-      </c>
       <c r="M129" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -8710,26 +8710,26 @@
       <c r="E130" t="s">
         <v>16</v>
       </c>
-      <c r="F130" t="s">
-        <v>516</v>
-      </c>
       <c r="G130" t="s">
         <v>562</v>
       </c>
+      <c r="H130" t="s">
+        <v>517</v>
+      </c>
       <c r="I130" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J130" t="s">
         <v>541</v>
       </c>
       <c r="K130" t="s">
+        <v>542</v>
+      </c>
+      <c r="L130" t="s">
         <v>563</v>
       </c>
-      <c r="L130" t="s">
-        <v>22</v>
-      </c>
       <c r="M130" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -8745,26 +8745,26 @@
       <c r="E131" t="s">
         <v>16</v>
       </c>
-      <c r="F131" t="s">
-        <v>516</v>
-      </c>
       <c r="G131" t="s">
         <v>566</v>
       </c>
+      <c r="H131" t="s">
+        <v>517</v>
+      </c>
       <c r="I131" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J131" t="s">
         <v>541</v>
       </c>
       <c r="K131" t="s">
+        <v>542</v>
+      </c>
+      <c r="L131" t="s">
         <v>567</v>
       </c>
-      <c r="L131" t="s">
-        <v>22</v>
-      </c>
       <c r="M131" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -8780,14 +8780,14 @@
       <c r="E132" t="s">
         <v>16</v>
       </c>
-      <c r="F132" t="s">
-        <v>516</v>
-      </c>
       <c r="G132" t="s">
         <v>570</v>
       </c>
+      <c r="H132" t="s">
+        <v>517</v>
+      </c>
       <c r="I132" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J132" t="s">
         <v>571</v>
@@ -8796,10 +8796,10 @@
         <v>572</v>
       </c>
       <c r="L132" t="s">
-        <v>22</v>
+        <v>573</v>
       </c>
       <c r="M132" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -8815,26 +8815,26 @@
       <c r="E133" t="s">
         <v>16</v>
       </c>
-      <c r="F133" t="s">
-        <v>516</v>
-      </c>
       <c r="G133" t="s">
         <v>576</v>
       </c>
+      <c r="H133" t="s">
+        <v>517</v>
+      </c>
       <c r="I133" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s">
         <v>571</v>
       </c>
       <c r="K133" t="s">
+        <v>572</v>
+      </c>
+      <c r="L133" t="s">
         <v>577</v>
       </c>
-      <c r="L133" t="s">
-        <v>22</v>
-      </c>
       <c r="M133" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -8850,26 +8850,26 @@
       <c r="E134" t="s">
         <v>16</v>
       </c>
-      <c r="F134" t="s">
-        <v>516</v>
-      </c>
       <c r="G134" t="s">
         <v>580</v>
       </c>
+      <c r="H134" t="s">
+        <v>517</v>
+      </c>
       <c r="I134" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J134" t="s">
         <v>571</v>
       </c>
       <c r="K134" t="s">
+        <v>572</v>
+      </c>
+      <c r="L134" t="s">
         <v>581</v>
       </c>
-      <c r="L134" t="s">
-        <v>22</v>
-      </c>
       <c r="M134" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -8885,26 +8885,26 @@
       <c r="E135" t="s">
         <v>16</v>
       </c>
-      <c r="F135" t="s">
-        <v>516</v>
-      </c>
       <c r="G135" t="s">
         <v>584</v>
       </c>
+      <c r="H135" t="s">
+        <v>517</v>
+      </c>
       <c r="I135" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J135" t="s">
         <v>571</v>
       </c>
       <c r="K135" t="s">
+        <v>572</v>
+      </c>
+      <c r="L135" t="s">
         <v>585</v>
       </c>
-      <c r="L135" t="s">
-        <v>22</v>
-      </c>
       <c r="M135" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -8920,26 +8920,26 @@
       <c r="E136" t="s">
         <v>16</v>
       </c>
-      <c r="F136" t="s">
-        <v>516</v>
-      </c>
       <c r="G136" t="s">
         <v>588</v>
       </c>
+      <c r="H136" t="s">
+        <v>517</v>
+      </c>
       <c r="I136" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J136" t="s">
         <v>571</v>
       </c>
       <c r="K136" t="s">
+        <v>572</v>
+      </c>
+      <c r="L136" t="s">
         <v>589</v>
       </c>
-      <c r="L136" t="s">
-        <v>22</v>
-      </c>
       <c r="M136" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -8955,26 +8955,26 @@
       <c r="E137" t="s">
         <v>16</v>
       </c>
-      <c r="F137" t="s">
-        <v>516</v>
-      </c>
       <c r="G137" t="s">
         <v>592</v>
       </c>
+      <c r="H137" t="s">
+        <v>517</v>
+      </c>
       <c r="I137" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J137" t="s">
         <v>571</v>
       </c>
       <c r="K137" t="s">
+        <v>572</v>
+      </c>
+      <c r="L137" t="s">
         <v>593</v>
       </c>
-      <c r="L137" t="s">
-        <v>22</v>
-      </c>
       <c r="M137" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -8990,26 +8990,26 @@
       <c r="E138" t="s">
         <v>16</v>
       </c>
-      <c r="F138" t="s">
-        <v>516</v>
-      </c>
       <c r="G138" t="s">
         <v>596</v>
       </c>
+      <c r="H138" t="s">
+        <v>517</v>
+      </c>
       <c r="I138" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J138" t="s">
         <v>571</v>
       </c>
       <c r="K138" t="s">
+        <v>572</v>
+      </c>
+      <c r="L138" t="s">
         <v>597</v>
       </c>
-      <c r="L138" t="s">
-        <v>22</v>
-      </c>
       <c r="M138" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -9025,26 +9025,26 @@
       <c r="E139" t="s">
         <v>16</v>
       </c>
-      <c r="F139" t="s">
-        <v>516</v>
-      </c>
       <c r="G139" t="s">
         <v>600</v>
       </c>
+      <c r="H139" t="s">
+        <v>517</v>
+      </c>
       <c r="I139" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J139" t="s">
         <v>571</v>
       </c>
       <c r="K139" t="s">
+        <v>572</v>
+      </c>
+      <c r="L139" t="s">
         <v>601</v>
       </c>
-      <c r="L139" t="s">
-        <v>22</v>
-      </c>
       <c r="M139" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -9060,26 +9060,26 @@
       <c r="E140" t="s">
         <v>16</v>
       </c>
-      <c r="F140" t="s">
-        <v>516</v>
-      </c>
       <c r="G140" t="s">
         <v>604</v>
       </c>
+      <c r="H140" t="s">
+        <v>517</v>
+      </c>
       <c r="I140" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J140" t="s">
         <v>571</v>
       </c>
       <c r="K140" t="s">
+        <v>572</v>
+      </c>
+      <c r="L140" t="s">
         <v>605</v>
       </c>
-      <c r="L140" t="s">
-        <v>22</v>
-      </c>
       <c r="M140" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -9095,26 +9095,26 @@
       <c r="E141" t="s">
         <v>16</v>
       </c>
-      <c r="F141" t="s">
-        <v>516</v>
-      </c>
       <c r="G141" t="s">
         <v>608</v>
       </c>
+      <c r="H141" t="s">
+        <v>517</v>
+      </c>
       <c r="I141" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J141" t="s">
         <v>571</v>
       </c>
       <c r="K141" t="s">
+        <v>572</v>
+      </c>
+      <c r="L141" t="s">
         <v>609</v>
       </c>
-      <c r="L141" t="s">
-        <v>22</v>
-      </c>
       <c r="M141" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -9130,26 +9130,26 @@
       <c r="E142" t="s">
         <v>16</v>
       </c>
-      <c r="F142" t="s">
-        <v>516</v>
-      </c>
       <c r="G142" t="s">
         <v>612</v>
       </c>
+      <c r="H142" t="s">
+        <v>517</v>
+      </c>
       <c r="I142" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J142" t="s">
         <v>571</v>
       </c>
       <c r="K142" t="s">
+        <v>572</v>
+      </c>
+      <c r="L142" t="s">
         <v>613</v>
       </c>
-      <c r="L142" t="s">
-        <v>22</v>
-      </c>
       <c r="M142" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -9165,14 +9165,14 @@
       <c r="E143" t="s">
         <v>16</v>
       </c>
-      <c r="F143" t="s">
-        <v>516</v>
-      </c>
       <c r="G143" t="s">
         <v>616</v>
       </c>
+      <c r="H143" t="s">
+        <v>517</v>
+      </c>
       <c r="I143" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J143" t="s">
         <v>617</v>
@@ -9181,10 +9181,10 @@
         <v>618</v>
       </c>
       <c r="L143" t="s">
-        <v>22</v>
+        <v>619</v>
       </c>
       <c r="M143" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -9200,26 +9200,26 @@
       <c r="E144" t="s">
         <v>16</v>
       </c>
-      <c r="F144" t="s">
-        <v>516</v>
-      </c>
       <c r="G144" t="s">
         <v>622</v>
       </c>
+      <c r="H144" t="s">
+        <v>517</v>
+      </c>
       <c r="I144" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J144" t="s">
         <v>617</v>
       </c>
       <c r="K144" t="s">
+        <v>618</v>
+      </c>
+      <c r="L144" t="s">
         <v>623</v>
       </c>
-      <c r="L144" t="s">
-        <v>22</v>
-      </c>
       <c r="M144" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -9235,26 +9235,26 @@
       <c r="E145" t="s">
         <v>16</v>
       </c>
-      <c r="F145" t="s">
-        <v>516</v>
-      </c>
       <c r="G145" t="s">
         <v>626</v>
       </c>
+      <c r="H145" t="s">
+        <v>517</v>
+      </c>
       <c r="I145" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J145" t="s">
         <v>617</v>
       </c>
       <c r="K145" t="s">
+        <v>618</v>
+      </c>
+      <c r="L145" t="s">
         <v>627</v>
       </c>
-      <c r="L145" t="s">
-        <v>22</v>
-      </c>
       <c r="M145" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -9270,26 +9270,26 @@
       <c r="E146" t="s">
         <v>16</v>
       </c>
-      <c r="F146" t="s">
-        <v>516</v>
-      </c>
       <c r="G146" t="s">
         <v>630</v>
       </c>
+      <c r="H146" t="s">
+        <v>517</v>
+      </c>
       <c r="I146" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J146" t="s">
         <v>617</v>
       </c>
       <c r="K146" t="s">
+        <v>618</v>
+      </c>
+      <c r="L146" t="s">
         <v>631</v>
       </c>
-      <c r="L146" t="s">
-        <v>22</v>
-      </c>
       <c r="M146" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -9305,26 +9305,26 @@
       <c r="E147" t="s">
         <v>16</v>
       </c>
-      <c r="F147" t="s">
-        <v>516</v>
-      </c>
       <c r="G147" t="s">
         <v>634</v>
       </c>
+      <c r="H147" t="s">
+        <v>517</v>
+      </c>
       <c r="I147" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J147" t="s">
         <v>617</v>
       </c>
       <c r="K147" t="s">
+        <v>618</v>
+      </c>
+      <c r="L147" t="s">
         <v>635</v>
       </c>
-      <c r="L147" t="s">
-        <v>22</v>
-      </c>
       <c r="M147" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -9340,26 +9340,26 @@
       <c r="E148" t="s">
         <v>16</v>
       </c>
-      <c r="F148" t="s">
-        <v>516</v>
-      </c>
       <c r="G148" t="s">
         <v>638</v>
       </c>
+      <c r="H148" t="s">
+        <v>517</v>
+      </c>
       <c r="I148" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J148" t="s">
         <v>617</v>
       </c>
       <c r="K148" t="s">
+        <v>618</v>
+      </c>
+      <c r="L148" t="s">
         <v>639</v>
       </c>
-      <c r="L148" t="s">
-        <v>22</v>
-      </c>
       <c r="M148" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -9375,26 +9375,26 @@
       <c r="E149" t="s">
         <v>16</v>
       </c>
-      <c r="F149" t="s">
-        <v>516</v>
-      </c>
       <c r="G149" t="s">
         <v>642</v>
       </c>
+      <c r="H149" t="s">
+        <v>517</v>
+      </c>
       <c r="I149" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J149" t="s">
         <v>617</v>
       </c>
       <c r="K149" t="s">
+        <v>618</v>
+      </c>
+      <c r="L149" t="s">
         <v>643</v>
       </c>
-      <c r="L149" t="s">
-        <v>22</v>
-      </c>
       <c r="M149" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -9410,26 +9410,26 @@
       <c r="E150" t="s">
         <v>16</v>
       </c>
-      <c r="F150" t="s">
-        <v>516</v>
-      </c>
       <c r="G150" t="s">
         <v>646</v>
       </c>
+      <c r="H150" t="s">
+        <v>517</v>
+      </c>
       <c r="I150" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J150" t="s">
         <v>617</v>
       </c>
       <c r="K150" t="s">
+        <v>618</v>
+      </c>
+      <c r="L150" t="s">
         <v>647</v>
       </c>
-      <c r="L150" t="s">
-        <v>22</v>
-      </c>
       <c r="M150" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -9445,26 +9445,26 @@
       <c r="E151" t="s">
         <v>16</v>
       </c>
-      <c r="F151" t="s">
-        <v>516</v>
-      </c>
       <c r="G151" t="s">
         <v>650</v>
       </c>
+      <c r="H151" t="s">
+        <v>517</v>
+      </c>
       <c r="I151" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J151" t="s">
         <v>617</v>
       </c>
       <c r="K151" t="s">
+        <v>618</v>
+      </c>
+      <c r="L151" t="s">
         <v>651</v>
       </c>
-      <c r="L151" t="s">
-        <v>22</v>
-      </c>
       <c r="M151" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -9480,14 +9480,14 @@
       <c r="E152" t="s">
         <v>16</v>
       </c>
-      <c r="F152" t="s">
-        <v>516</v>
-      </c>
       <c r="G152" t="s">
         <v>654</v>
       </c>
+      <c r="H152" t="s">
+        <v>517</v>
+      </c>
       <c r="I152" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J152" t="s">
         <v>655</v>
@@ -9496,10 +9496,10 @@
         <v>656</v>
       </c>
       <c r="L152" t="s">
-        <v>22</v>
+        <v>657</v>
       </c>
       <c r="M152" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -9515,26 +9515,26 @@
       <c r="E153" t="s">
         <v>16</v>
       </c>
-      <c r="F153" t="s">
-        <v>516</v>
-      </c>
       <c r="G153" t="s">
         <v>660</v>
       </c>
+      <c r="H153" t="s">
+        <v>517</v>
+      </c>
       <c r="I153" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J153" t="s">
         <v>655</v>
       </c>
       <c r="K153" t="s">
+        <v>656</v>
+      </c>
+      <c r="L153" t="s">
         <v>661</v>
       </c>
-      <c r="L153" t="s">
-        <v>22</v>
-      </c>
       <c r="M153" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -9550,26 +9550,26 @@
       <c r="E154" t="s">
         <v>16</v>
       </c>
-      <c r="F154" t="s">
-        <v>516</v>
-      </c>
       <c r="G154" t="s">
         <v>664</v>
       </c>
+      <c r="H154" t="s">
+        <v>517</v>
+      </c>
       <c r="I154" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J154" t="s">
         <v>655</v>
       </c>
       <c r="K154" t="s">
+        <v>656</v>
+      </c>
+      <c r="L154" t="s">
         <v>665</v>
       </c>
-      <c r="L154" t="s">
-        <v>22</v>
-      </c>
       <c r="M154" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -9585,26 +9585,26 @@
       <c r="E155" t="s">
         <v>16</v>
       </c>
-      <c r="F155" t="s">
-        <v>516</v>
-      </c>
       <c r="G155" t="s">
         <v>668</v>
       </c>
+      <c r="H155" t="s">
+        <v>517</v>
+      </c>
       <c r="I155" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J155" t="s">
         <v>655</v>
       </c>
       <c r="K155" t="s">
+        <v>656</v>
+      </c>
+      <c r="L155" t="s">
         <v>669</v>
       </c>
-      <c r="L155" t="s">
-        <v>22</v>
-      </c>
       <c r="M155" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -9620,26 +9620,26 @@
       <c r="E156" t="s">
         <v>16</v>
       </c>
-      <c r="F156" t="s">
-        <v>516</v>
-      </c>
       <c r="G156" t="s">
         <v>672</v>
       </c>
+      <c r="H156" t="s">
+        <v>517</v>
+      </c>
       <c r="I156" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J156" t="s">
         <v>655</v>
       </c>
       <c r="K156" t="s">
+        <v>656</v>
+      </c>
+      <c r="L156" t="s">
         <v>673</v>
       </c>
-      <c r="L156" t="s">
-        <v>22</v>
-      </c>
       <c r="M156" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -9655,26 +9655,26 @@
       <c r="E157" t="s">
         <v>16</v>
       </c>
-      <c r="F157" t="s">
-        <v>516</v>
-      </c>
       <c r="G157" t="s">
         <v>676</v>
       </c>
+      <c r="H157" t="s">
+        <v>517</v>
+      </c>
       <c r="I157" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J157" t="s">
         <v>655</v>
       </c>
       <c r="K157" t="s">
+        <v>656</v>
+      </c>
+      <c r="L157" t="s">
         <v>677</v>
       </c>
-      <c r="L157" t="s">
-        <v>22</v>
-      </c>
       <c r="M157" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -9690,26 +9690,26 @@
       <c r="E158" t="s">
         <v>16</v>
       </c>
-      <c r="F158" t="s">
-        <v>516</v>
-      </c>
       <c r="G158" t="s">
         <v>680</v>
       </c>
+      <c r="H158" t="s">
+        <v>517</v>
+      </c>
       <c r="I158" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J158" t="s">
         <v>655</v>
       </c>
       <c r="K158" t="s">
+        <v>656</v>
+      </c>
+      <c r="L158" t="s">
         <v>681</v>
       </c>
-      <c r="L158" t="s">
-        <v>22</v>
-      </c>
       <c r="M158" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -9725,26 +9725,26 @@
       <c r="E159" t="s">
         <v>16</v>
       </c>
-      <c r="F159" t="s">
-        <v>516</v>
-      </c>
       <c r="G159" t="s">
         <v>684</v>
       </c>
+      <c r="H159" t="s">
+        <v>517</v>
+      </c>
       <c r="I159" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J159" t="s">
         <v>655</v>
       </c>
       <c r="K159" t="s">
+        <v>656</v>
+      </c>
+      <c r="L159" t="s">
         <v>685</v>
       </c>
-      <c r="L159" t="s">
-        <v>22</v>
-      </c>
       <c r="M159" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -9760,26 +9760,26 @@
       <c r="E160" t="s">
         <v>16</v>
       </c>
-      <c r="F160" t="s">
-        <v>516</v>
-      </c>
       <c r="G160" t="s">
         <v>688</v>
       </c>
+      <c r="H160" t="s">
+        <v>517</v>
+      </c>
       <c r="I160" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J160" t="s">
         <v>655</v>
       </c>
       <c r="K160" t="s">
+        <v>656</v>
+      </c>
+      <c r="L160" t="s">
         <v>689</v>
       </c>
-      <c r="L160" t="s">
-        <v>22</v>
-      </c>
       <c r="M160" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -9795,26 +9795,26 @@
       <c r="E161" t="s">
         <v>16</v>
       </c>
-      <c r="F161" t="s">
-        <v>516</v>
-      </c>
       <c r="G161" t="s">
         <v>692</v>
       </c>
+      <c r="H161" t="s">
+        <v>517</v>
+      </c>
       <c r="I161" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J161" t="s">
         <v>655</v>
       </c>
       <c r="K161" t="s">
+        <v>656</v>
+      </c>
+      <c r="L161" t="s">
         <v>693</v>
       </c>
-      <c r="L161" t="s">
-        <v>22</v>
-      </c>
       <c r="M161" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -9830,26 +9830,26 @@
       <c r="E162" t="s">
         <v>16</v>
       </c>
-      <c r="F162" t="s">
-        <v>516</v>
-      </c>
       <c r="G162" t="s">
         <v>696</v>
       </c>
+      <c r="H162" t="s">
+        <v>517</v>
+      </c>
       <c r="I162" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J162" t="s">
         <v>655</v>
       </c>
       <c r="K162" t="s">
+        <v>656</v>
+      </c>
+      <c r="L162" t="s">
         <v>697</v>
       </c>
-      <c r="L162" t="s">
-        <v>22</v>
-      </c>
       <c r="M162" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -9865,26 +9865,26 @@
       <c r="E163" t="s">
         <v>16</v>
       </c>
-      <c r="F163" t="s">
-        <v>516</v>
-      </c>
       <c r="G163" t="s">
         <v>700</v>
       </c>
+      <c r="H163" t="s">
+        <v>517</v>
+      </c>
       <c r="I163" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J163" t="s">
         <v>655</v>
       </c>
       <c r="K163" t="s">
+        <v>656</v>
+      </c>
+      <c r="L163" t="s">
         <v>701</v>
       </c>
-      <c r="L163" t="s">
-        <v>22</v>
-      </c>
       <c r="M163" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -9900,26 +9900,26 @@
       <c r="E164" t="s">
         <v>16</v>
       </c>
-      <c r="F164" t="s">
-        <v>516</v>
-      </c>
       <c r="G164" t="s">
         <v>704</v>
       </c>
+      <c r="H164" t="s">
+        <v>517</v>
+      </c>
       <c r="I164" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J164" t="s">
         <v>655</v>
       </c>
       <c r="K164" t="s">
+        <v>656</v>
+      </c>
+      <c r="L164" t="s">
         <v>705</v>
       </c>
-      <c r="L164" t="s">
-        <v>22</v>
-      </c>
       <c r="M164" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -9935,26 +9935,26 @@
       <c r="E165" t="s">
         <v>16</v>
       </c>
-      <c r="F165" t="s">
-        <v>516</v>
-      </c>
       <c r="G165" t="s">
         <v>708</v>
       </c>
+      <c r="H165" t="s">
+        <v>517</v>
+      </c>
       <c r="I165" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J165" t="s">
         <v>655</v>
       </c>
       <c r="K165" t="s">
+        <v>656</v>
+      </c>
+      <c r="L165" t="s">
         <v>709</v>
       </c>
-      <c r="L165" t="s">
-        <v>22</v>
-      </c>
       <c r="M165" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -9970,26 +9970,26 @@
       <c r="E166" t="s">
         <v>16</v>
       </c>
-      <c r="F166" t="s">
-        <v>516</v>
-      </c>
       <c r="G166" t="s">
         <v>712</v>
       </c>
+      <c r="H166" t="s">
+        <v>517</v>
+      </c>
       <c r="I166" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J166" t="s">
         <v>655</v>
       </c>
       <c r="K166" t="s">
+        <v>656</v>
+      </c>
+      <c r="L166" t="s">
         <v>713</v>
       </c>
-      <c r="L166" t="s">
-        <v>22</v>
-      </c>
       <c r="M166" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -10005,26 +10005,26 @@
       <c r="E167" t="s">
         <v>16</v>
       </c>
-      <c r="F167" t="s">
-        <v>516</v>
-      </c>
       <c r="G167" t="s">
         <v>716</v>
       </c>
+      <c r="H167" t="s">
+        <v>517</v>
+      </c>
       <c r="I167" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J167" t="s">
         <v>655</v>
       </c>
       <c r="K167" t="s">
+        <v>656</v>
+      </c>
+      <c r="L167" t="s">
         <v>717</v>
       </c>
-      <c r="L167" t="s">
-        <v>22</v>
-      </c>
       <c r="M167" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -10040,26 +10040,26 @@
       <c r="E168" t="s">
         <v>16</v>
       </c>
-      <c r="F168" t="s">
-        <v>516</v>
-      </c>
       <c r="G168" t="s">
         <v>720</v>
       </c>
+      <c r="H168" t="s">
+        <v>517</v>
+      </c>
       <c r="I168" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J168" t="s">
         <v>655</v>
       </c>
       <c r="K168" t="s">
+        <v>656</v>
+      </c>
+      <c r="L168" t="s">
         <v>721</v>
       </c>
-      <c r="L168" t="s">
-        <v>22</v>
-      </c>
       <c r="M168" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -10075,26 +10075,26 @@
       <c r="E169" t="s">
         <v>16</v>
       </c>
-      <c r="F169" t="s">
-        <v>516</v>
-      </c>
       <c r="G169" t="s">
         <v>724</v>
       </c>
+      <c r="H169" t="s">
+        <v>517</v>
+      </c>
       <c r="I169" t="s">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="J169" t="s">
         <v>655</v>
       </c>
       <c r="K169" t="s">
+        <v>656</v>
+      </c>
+      <c r="L169" t="s">
         <v>725</v>
       </c>
-      <c r="L169" t="s">
-        <v>22</v>
-      </c>
       <c r="M169" t="s">
-        <v>657</v>
+        <v>521</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -10110,23 +10110,23 @@
       <c r="E170" t="s">
         <v>16</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>728</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>729</v>
       </c>
       <c r="I170" t="s">
+        <v>19</v>
+      </c>
+      <c r="J170" t="s">
         <v>730</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>731</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" t="s">
         <v>732</v>
-      </c>
-      <c r="L170" t="s">
-        <v>22</v>
       </c>
       <c r="M170" t="s">
         <v>733</v>
@@ -10145,23 +10145,23 @@
       <c r="E171" t="s">
         <v>16</v>
       </c>
-      <c r="F171" t="s">
-        <v>728</v>
-      </c>
       <c r="G171" t="s">
         <v>736</v>
       </c>
+      <c r="H171" t="s">
+        <v>729</v>
+      </c>
       <c r="I171" t="s">
+        <v>19</v>
+      </c>
+      <c r="J171" t="s">
         <v>730</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>731</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" t="s">
         <v>737</v>
-      </c>
-      <c r="L171" t="s">
-        <v>22</v>
       </c>
       <c r="M171" t="s">
         <v>733</v>
@@ -10180,23 +10180,23 @@
       <c r="E172" t="s">
         <v>16</v>
       </c>
-      <c r="F172" t="s">
-        <v>728</v>
-      </c>
       <c r="G172" t="s">
         <v>740</v>
       </c>
+      <c r="H172" t="s">
+        <v>729</v>
+      </c>
       <c r="I172" t="s">
+        <v>19</v>
+      </c>
+      <c r="J172" t="s">
         <v>730</v>
       </c>
-      <c r="J172" t="s">
+      <c r="K172" t="s">
         <v>731</v>
       </c>
-      <c r="K172" t="s">
+      <c r="L172" t="s">
         <v>741</v>
-      </c>
-      <c r="L172" t="s">
-        <v>22</v>
       </c>
       <c r="M172" t="s">
         <v>733</v>
@@ -10215,23 +10215,23 @@
       <c r="E173" t="s">
         <v>16</v>
       </c>
-      <c r="F173" t="s">
-        <v>728</v>
-      </c>
       <c r="G173" t="s">
         <v>744</v>
       </c>
+      <c r="H173" t="s">
+        <v>729</v>
+      </c>
       <c r="I173" t="s">
+        <v>19</v>
+      </c>
+      <c r="J173" t="s">
         <v>730</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>731</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" t="s">
         <v>745</v>
-      </c>
-      <c r="L173" t="s">
-        <v>22</v>
       </c>
       <c r="M173" t="s">
         <v>733</v>
@@ -10250,23 +10250,23 @@
       <c r="E174" t="s">
         <v>16</v>
       </c>
-      <c r="F174" t="s">
-        <v>728</v>
-      </c>
       <c r="G174" t="s">
         <v>748</v>
       </c>
+      <c r="H174" t="s">
+        <v>729</v>
+      </c>
       <c r="I174" t="s">
+        <v>19</v>
+      </c>
+      <c r="J174" t="s">
         <v>730</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>731</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" t="s">
         <v>749</v>
-      </c>
-      <c r="L174" t="s">
-        <v>22</v>
       </c>
       <c r="M174" t="s">
         <v>733</v>
@@ -10285,23 +10285,23 @@
       <c r="E175" t="s">
         <v>16</v>
       </c>
-      <c r="F175" t="s">
-        <v>728</v>
-      </c>
       <c r="G175" t="s">
         <v>752</v>
       </c>
+      <c r="H175" t="s">
+        <v>729</v>
+      </c>
       <c r="I175" t="s">
+        <v>19</v>
+      </c>
+      <c r="J175" t="s">
         <v>730</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>731</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" t="s">
         <v>753</v>
-      </c>
-      <c r="L175" t="s">
-        <v>22</v>
       </c>
       <c r="M175" t="s">
         <v>733</v>
@@ -10320,23 +10320,23 @@
       <c r="E176" t="s">
         <v>16</v>
       </c>
-      <c r="F176" t="s">
-        <v>728</v>
-      </c>
       <c r="G176" t="s">
         <v>756</v>
       </c>
+      <c r="H176" t="s">
+        <v>729</v>
+      </c>
       <c r="I176" t="s">
+        <v>19</v>
+      </c>
+      <c r="J176" t="s">
         <v>730</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>731</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" t="s">
         <v>757</v>
-      </c>
-      <c r="L176" t="s">
-        <v>22</v>
       </c>
       <c r="M176" t="s">
         <v>733</v>
@@ -10355,23 +10355,23 @@
       <c r="E177" t="s">
         <v>16</v>
       </c>
-      <c r="F177" t="s">
-        <v>728</v>
-      </c>
       <c r="G177" t="s">
         <v>760</v>
       </c>
+      <c r="H177" t="s">
+        <v>729</v>
+      </c>
       <c r="I177" t="s">
+        <v>19</v>
+      </c>
+      <c r="J177" t="s">
         <v>730</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>731</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" t="s">
         <v>761</v>
-      </c>
-      <c r="L177" t="s">
-        <v>22</v>
       </c>
       <c r="M177" t="s">
         <v>733</v>
@@ -10390,23 +10390,23 @@
       <c r="E178" t="s">
         <v>16</v>
       </c>
-      <c r="F178" t="s">
-        <v>728</v>
-      </c>
       <c r="G178" t="s">
         <v>764</v>
       </c>
+      <c r="H178" t="s">
+        <v>729</v>
+      </c>
       <c r="I178" t="s">
+        <v>19</v>
+      </c>
+      <c r="J178" t="s">
         <v>730</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>731</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" t="s">
         <v>765</v>
-      </c>
-      <c r="L178" t="s">
-        <v>22</v>
       </c>
       <c r="M178" t="s">
         <v>733</v>
@@ -10425,23 +10425,23 @@
       <c r="E179" t="s">
         <v>16</v>
       </c>
-      <c r="F179" t="s">
-        <v>728</v>
-      </c>
       <c r="G179" t="s">
         <v>768</v>
       </c>
+      <c r="H179" t="s">
+        <v>729</v>
+      </c>
       <c r="I179" t="s">
+        <v>19</v>
+      </c>
+      <c r="J179" t="s">
         <v>730</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>731</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" t="s">
         <v>769</v>
-      </c>
-      <c r="L179" t="s">
-        <v>22</v>
       </c>
       <c r="M179" t="s">
         <v>733</v>
@@ -10460,14 +10460,14 @@
       <c r="E180" t="s">
         <v>16</v>
       </c>
-      <c r="F180" t="s">
-        <v>728</v>
-      </c>
       <c r="G180" t="s">
         <v>772</v>
       </c>
+      <c r="H180" t="s">
+        <v>729</v>
+      </c>
       <c r="I180" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J180" t="s">
         <v>773</v>
@@ -10476,10 +10476,10 @@
         <v>774</v>
       </c>
       <c r="L180" t="s">
-        <v>22</v>
+        <v>775</v>
       </c>
       <c r="M180" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -10499,28 +10499,28 @@
         <v>16</v>
       </c>
       <c r="F181" t="s">
-        <v>728</v>
+        <v>779</v>
       </c>
       <c r="G181" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H181" t="s">
-        <v>780</v>
+        <v>729</v>
       </c>
       <c r="I181" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J181" t="s">
         <v>773</v>
       </c>
       <c r="K181" t="s">
+        <v>774</v>
+      </c>
+      <c r="L181" t="s">
         <v>781</v>
       </c>
-      <c r="L181" t="s">
-        <v>22</v>
-      </c>
       <c r="M181" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -10540,28 +10540,28 @@
         <v>16</v>
       </c>
       <c r="F182" t="s">
-        <v>728</v>
+        <v>779</v>
       </c>
       <c r="G182" t="s">
         <v>784</v>
       </c>
       <c r="H182" t="s">
-        <v>780</v>
+        <v>729</v>
       </c>
       <c r="I182" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J182" t="s">
         <v>773</v>
       </c>
       <c r="K182" t="s">
+        <v>774</v>
+      </c>
+      <c r="L182" t="s">
         <v>785</v>
       </c>
-      <c r="L182" t="s">
-        <v>22</v>
-      </c>
       <c r="M182" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -10581,22 +10581,22 @@
         <v>16</v>
       </c>
       <c r="F183" t="s">
-        <v>728</v>
+        <v>779</v>
       </c>
       <c r="H183" t="s">
-        <v>780</v>
+        <v>729</v>
       </c>
       <c r="I183" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J183" t="s">
         <v>773</v>
       </c>
-      <c r="L183" t="s">
-        <v>22</v>
+      <c r="K183" t="s">
+        <v>774</v>
       </c>
       <c r="M183" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -10612,26 +10612,26 @@
       <c r="E184" t="s">
         <v>16</v>
       </c>
-      <c r="F184" t="s">
-        <v>728</v>
-      </c>
       <c r="G184" t="s">
         <v>790</v>
       </c>
+      <c r="H184" t="s">
+        <v>729</v>
+      </c>
       <c r="I184" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J184" t="s">
         <v>773</v>
       </c>
       <c r="K184" t="s">
+        <v>774</v>
+      </c>
+      <c r="L184" t="s">
         <v>791</v>
       </c>
-      <c r="L184" t="s">
-        <v>22</v>
-      </c>
       <c r="M184" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -10647,26 +10647,26 @@
       <c r="E185" t="s">
         <v>16</v>
       </c>
-      <c r="F185" t="s">
-        <v>728</v>
-      </c>
       <c r="G185" t="s">
         <v>794</v>
       </c>
+      <c r="H185" t="s">
+        <v>729</v>
+      </c>
       <c r="I185" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J185" t="s">
         <v>773</v>
       </c>
       <c r="K185" t="s">
+        <v>774</v>
+      </c>
+      <c r="L185" t="s">
         <v>795</v>
       </c>
-      <c r="L185" t="s">
-        <v>22</v>
-      </c>
       <c r="M185" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -10682,26 +10682,26 @@
       <c r="E186" t="s">
         <v>16</v>
       </c>
-      <c r="F186" t="s">
-        <v>728</v>
-      </c>
       <c r="G186" t="s">
         <v>798</v>
       </c>
+      <c r="H186" t="s">
+        <v>729</v>
+      </c>
       <c r="I186" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J186" t="s">
         <v>773</v>
       </c>
       <c r="K186" t="s">
+        <v>774</v>
+      </c>
+      <c r="L186" t="s">
         <v>799</v>
       </c>
-      <c r="L186" t="s">
-        <v>22</v>
-      </c>
       <c r="M186" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -10717,26 +10717,26 @@
       <c r="E187" t="s">
         <v>16</v>
       </c>
-      <c r="F187" t="s">
-        <v>728</v>
-      </c>
       <c r="G187" t="s">
         <v>802</v>
       </c>
+      <c r="H187" t="s">
+        <v>729</v>
+      </c>
       <c r="I187" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J187" t="s">
         <v>773</v>
       </c>
       <c r="K187" t="s">
+        <v>774</v>
+      </c>
+      <c r="L187" t="s">
         <v>803</v>
       </c>
-      <c r="L187" t="s">
-        <v>22</v>
-      </c>
       <c r="M187" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -10752,26 +10752,26 @@
       <c r="E188" t="s">
         <v>16</v>
       </c>
-      <c r="F188" t="s">
-        <v>728</v>
-      </c>
       <c r="G188" t="s">
         <v>806</v>
       </c>
+      <c r="H188" t="s">
+        <v>729</v>
+      </c>
       <c r="I188" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J188" t="s">
         <v>773</v>
       </c>
       <c r="K188" t="s">
+        <v>774</v>
+      </c>
+      <c r="L188" t="s">
         <v>807</v>
       </c>
-      <c r="L188" t="s">
-        <v>22</v>
-      </c>
       <c r="M188" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -10787,26 +10787,26 @@
       <c r="E189" t="s">
         <v>16</v>
       </c>
-      <c r="F189" t="s">
-        <v>728</v>
-      </c>
       <c r="G189" t="s">
         <v>810</v>
       </c>
+      <c r="H189" t="s">
+        <v>729</v>
+      </c>
       <c r="I189" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J189" t="s">
         <v>773</v>
       </c>
       <c r="K189" t="s">
+        <v>774</v>
+      </c>
+      <c r="L189" t="s">
         <v>811</v>
       </c>
-      <c r="L189" t="s">
-        <v>22</v>
-      </c>
       <c r="M189" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -10822,26 +10822,26 @@
       <c r="E190" t="s">
         <v>16</v>
       </c>
-      <c r="F190" t="s">
-        <v>728</v>
-      </c>
       <c r="G190" t="s">
         <v>814</v>
       </c>
+      <c r="H190" t="s">
+        <v>729</v>
+      </c>
       <c r="I190" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J190" t="s">
         <v>773</v>
       </c>
       <c r="K190" t="s">
+        <v>774</v>
+      </c>
+      <c r="L190" t="s">
         <v>815</v>
       </c>
-      <c r="L190" t="s">
-        <v>22</v>
-      </c>
       <c r="M190" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -10857,26 +10857,26 @@
       <c r="E191" t="s">
         <v>16</v>
       </c>
-      <c r="F191" t="s">
-        <v>728</v>
-      </c>
       <c r="G191" t="s">
         <v>818</v>
       </c>
+      <c r="H191" t="s">
+        <v>729</v>
+      </c>
       <c r="I191" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J191" t="s">
         <v>773</v>
       </c>
       <c r="K191" t="s">
+        <v>774</v>
+      </c>
+      <c r="L191" t="s">
         <v>819</v>
       </c>
-      <c r="L191" t="s">
-        <v>22</v>
-      </c>
       <c r="M191" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -10892,26 +10892,26 @@
       <c r="E192" t="s">
         <v>16</v>
       </c>
-      <c r="F192" t="s">
-        <v>728</v>
-      </c>
       <c r="G192" t="s">
         <v>822</v>
       </c>
+      <c r="H192" t="s">
+        <v>729</v>
+      </c>
       <c r="I192" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J192" t="s">
         <v>773</v>
       </c>
       <c r="K192" t="s">
+        <v>774</v>
+      </c>
+      <c r="L192" t="s">
         <v>823</v>
       </c>
-      <c r="L192" t="s">
-        <v>22</v>
-      </c>
       <c r="M192" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -10927,26 +10927,26 @@
       <c r="E193" t="s">
         <v>16</v>
       </c>
-      <c r="F193" t="s">
-        <v>728</v>
-      </c>
       <c r="G193" t="s">
         <v>826</v>
       </c>
+      <c r="H193" t="s">
+        <v>729</v>
+      </c>
       <c r="I193" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J193" t="s">
         <v>773</v>
       </c>
       <c r="K193" t="s">
+        <v>774</v>
+      </c>
+      <c r="L193" t="s">
         <v>827</v>
       </c>
-      <c r="L193" t="s">
-        <v>22</v>
-      </c>
       <c r="M193" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -10962,26 +10962,26 @@
       <c r="E194" t="s">
         <v>16</v>
       </c>
-      <c r="F194" t="s">
-        <v>728</v>
-      </c>
       <c r="G194" t="s">
         <v>830</v>
       </c>
+      <c r="H194" t="s">
+        <v>729</v>
+      </c>
       <c r="I194" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J194" t="s">
         <v>773</v>
       </c>
       <c r="K194" t="s">
+        <v>774</v>
+      </c>
+      <c r="L194" t="s">
         <v>831</v>
       </c>
-      <c r="L194" t="s">
-        <v>22</v>
-      </c>
       <c r="M194" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -10997,26 +10997,26 @@
       <c r="E195" t="s">
         <v>16</v>
       </c>
-      <c r="F195" t="s">
-        <v>728</v>
-      </c>
       <c r="G195" t="s">
         <v>834</v>
       </c>
+      <c r="H195" t="s">
+        <v>729</v>
+      </c>
       <c r="I195" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J195" t="s">
         <v>773</v>
       </c>
       <c r="K195" t="s">
+        <v>774</v>
+      </c>
+      <c r="L195" t="s">
         <v>835</v>
       </c>
-      <c r="L195" t="s">
-        <v>22</v>
-      </c>
       <c r="M195" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -11032,26 +11032,26 @@
       <c r="E196" t="s">
         <v>16</v>
       </c>
-      <c r="F196" t="s">
-        <v>728</v>
-      </c>
       <c r="G196" t="s">
         <v>838</v>
       </c>
+      <c r="H196" t="s">
+        <v>729</v>
+      </c>
       <c r="I196" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J196" t="s">
         <v>773</v>
       </c>
       <c r="K196" t="s">
+        <v>774</v>
+      </c>
+      <c r="L196" t="s">
         <v>839</v>
       </c>
-      <c r="L196" t="s">
-        <v>22</v>
-      </c>
       <c r="M196" t="s">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -11067,14 +11067,14 @@
       <c r="E197" t="s">
         <v>16</v>
       </c>
-      <c r="F197" t="s">
-        <v>728</v>
-      </c>
       <c r="G197" t="s">
         <v>842</v>
       </c>
+      <c r="H197" t="s">
+        <v>729</v>
+      </c>
       <c r="I197" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J197" t="s">
         <v>843</v>
@@ -11083,10 +11083,10 @@
         <v>844</v>
       </c>
       <c r="L197" t="s">
-        <v>22</v>
+        <v>845</v>
       </c>
       <c r="M197" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -11102,26 +11102,26 @@
       <c r="E198" t="s">
         <v>16</v>
       </c>
-      <c r="F198" t="s">
-        <v>728</v>
-      </c>
       <c r="G198" t="s">
         <v>848</v>
       </c>
+      <c r="H198" t="s">
+        <v>729</v>
+      </c>
       <c r="I198" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J198" t="s">
         <v>843</v>
       </c>
       <c r="K198" t="s">
+        <v>844</v>
+      </c>
+      <c r="L198" t="s">
         <v>849</v>
       </c>
-      <c r="L198" t="s">
-        <v>22</v>
-      </c>
       <c r="M198" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -11137,26 +11137,26 @@
       <c r="E199" t="s">
         <v>16</v>
       </c>
-      <c r="F199" t="s">
-        <v>728</v>
-      </c>
       <c r="G199" t="s">
         <v>852</v>
       </c>
+      <c r="H199" t="s">
+        <v>729</v>
+      </c>
       <c r="I199" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J199" t="s">
         <v>843</v>
       </c>
       <c r="K199" t="s">
+        <v>844</v>
+      </c>
+      <c r="L199" t="s">
         <v>853</v>
       </c>
-      <c r="L199" t="s">
-        <v>22</v>
-      </c>
       <c r="M199" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -11172,26 +11172,26 @@
       <c r="E200" t="s">
         <v>16</v>
       </c>
-      <c r="F200" t="s">
-        <v>728</v>
-      </c>
       <c r="G200" t="s">
         <v>856</v>
       </c>
+      <c r="H200" t="s">
+        <v>729</v>
+      </c>
       <c r="I200" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J200" t="s">
         <v>843</v>
       </c>
       <c r="K200" t="s">
+        <v>844</v>
+      </c>
+      <c r="L200" t="s">
         <v>857</v>
       </c>
-      <c r="L200" t="s">
-        <v>22</v>
-      </c>
       <c r="M200" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -11207,26 +11207,26 @@
       <c r="E201" t="s">
         <v>16</v>
       </c>
-      <c r="F201" t="s">
-        <v>728</v>
-      </c>
       <c r="G201" t="s">
         <v>860</v>
       </c>
+      <c r="H201" t="s">
+        <v>729</v>
+      </c>
       <c r="I201" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J201" t="s">
         <v>843</v>
       </c>
       <c r="K201" t="s">
+        <v>844</v>
+      </c>
+      <c r="L201" t="s">
         <v>861</v>
       </c>
-      <c r="L201" t="s">
-        <v>22</v>
-      </c>
       <c r="M201" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -11242,26 +11242,26 @@
       <c r="E202" t="s">
         <v>16</v>
       </c>
-      <c r="F202" t="s">
-        <v>728</v>
-      </c>
       <c r="G202" t="s">
         <v>864</v>
       </c>
+      <c r="H202" t="s">
+        <v>729</v>
+      </c>
       <c r="I202" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J202" t="s">
         <v>843</v>
       </c>
       <c r="K202" t="s">
+        <v>844</v>
+      </c>
+      <c r="L202" t="s">
         <v>865</v>
       </c>
-      <c r="L202" t="s">
-        <v>22</v>
-      </c>
       <c r="M202" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -11277,26 +11277,26 @@
       <c r="E203" t="s">
         <v>16</v>
       </c>
-      <c r="F203" t="s">
-        <v>728</v>
-      </c>
       <c r="G203" t="s">
         <v>868</v>
       </c>
+      <c r="H203" t="s">
+        <v>729</v>
+      </c>
       <c r="I203" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J203" t="s">
         <v>843</v>
       </c>
       <c r="K203" t="s">
+        <v>844</v>
+      </c>
+      <c r="L203" t="s">
         <v>869</v>
       </c>
-      <c r="L203" t="s">
-        <v>22</v>
-      </c>
       <c r="M203" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -11312,26 +11312,26 @@
       <c r="E204" t="s">
         <v>16</v>
       </c>
-      <c r="F204" t="s">
-        <v>728</v>
-      </c>
       <c r="G204" t="s">
         <v>872</v>
       </c>
+      <c r="H204" t="s">
+        <v>729</v>
+      </c>
       <c r="I204" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J204" t="s">
         <v>843</v>
       </c>
       <c r="K204" t="s">
+        <v>844</v>
+      </c>
+      <c r="L204" t="s">
         <v>873</v>
       </c>
-      <c r="L204" t="s">
-        <v>22</v>
-      </c>
       <c r="M204" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -11347,26 +11347,26 @@
       <c r="E205" t="s">
         <v>16</v>
       </c>
-      <c r="F205" t="s">
-        <v>728</v>
-      </c>
       <c r="G205" t="s">
         <v>876</v>
       </c>
+      <c r="H205" t="s">
+        <v>729</v>
+      </c>
       <c r="I205" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J205" t="s">
         <v>843</v>
       </c>
       <c r="K205" t="s">
+        <v>844</v>
+      </c>
+      <c r="L205" t="s">
         <v>877</v>
       </c>
-      <c r="L205" t="s">
-        <v>22</v>
-      </c>
       <c r="M205" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -11382,26 +11382,26 @@
       <c r="E206" t="s">
         <v>16</v>
       </c>
-      <c r="F206" t="s">
-        <v>728</v>
-      </c>
       <c r="G206" t="s">
         <v>880</v>
       </c>
+      <c r="H206" t="s">
+        <v>729</v>
+      </c>
       <c r="I206" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J206" t="s">
         <v>843</v>
       </c>
       <c r="K206" t="s">
+        <v>844</v>
+      </c>
+      <c r="L206" t="s">
         <v>881</v>
       </c>
-      <c r="L206" t="s">
-        <v>22</v>
-      </c>
       <c r="M206" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -11417,26 +11417,26 @@
       <c r="E207" t="s">
         <v>16</v>
       </c>
-      <c r="F207" t="s">
-        <v>728</v>
-      </c>
       <c r="G207" t="s">
         <v>884</v>
       </c>
+      <c r="H207" t="s">
+        <v>729</v>
+      </c>
       <c r="I207" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J207" t="s">
         <v>843</v>
       </c>
       <c r="K207" t="s">
+        <v>844</v>
+      </c>
+      <c r="L207" t="s">
         <v>885</v>
       </c>
-      <c r="L207" t="s">
-        <v>22</v>
-      </c>
       <c r="M207" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -11452,26 +11452,26 @@
       <c r="E208" t="s">
         <v>16</v>
       </c>
-      <c r="F208" t="s">
-        <v>728</v>
-      </c>
       <c r="G208" t="s">
         <v>888</v>
       </c>
+      <c r="H208" t="s">
+        <v>729</v>
+      </c>
       <c r="I208" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J208" t="s">
         <v>843</v>
       </c>
       <c r="K208" t="s">
+        <v>844</v>
+      </c>
+      <c r="L208" t="s">
         <v>889</v>
       </c>
-      <c r="L208" t="s">
-        <v>22</v>
-      </c>
       <c r="M208" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -11487,26 +11487,26 @@
       <c r="E209" t="s">
         <v>16</v>
       </c>
-      <c r="F209" t="s">
-        <v>728</v>
-      </c>
       <c r="G209" t="s">
         <v>892</v>
       </c>
+      <c r="H209" t="s">
+        <v>729</v>
+      </c>
       <c r="I209" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J209" t="s">
         <v>843</v>
       </c>
       <c r="K209" t="s">
+        <v>844</v>
+      </c>
+      <c r="L209" t="s">
         <v>893</v>
       </c>
-      <c r="L209" t="s">
-        <v>22</v>
-      </c>
       <c r="M209" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -11522,26 +11522,26 @@
       <c r="E210" t="s">
         <v>16</v>
       </c>
-      <c r="F210" t="s">
-        <v>728</v>
-      </c>
       <c r="G210" t="s">
         <v>896</v>
       </c>
+      <c r="H210" t="s">
+        <v>729</v>
+      </c>
       <c r="I210" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J210" t="s">
         <v>843</v>
       </c>
       <c r="K210" t="s">
+        <v>844</v>
+      </c>
+      <c r="L210" t="s">
         <v>897</v>
       </c>
-      <c r="L210" t="s">
-        <v>22</v>
-      </c>
       <c r="M210" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -11557,26 +11557,26 @@
       <c r="E211" t="s">
         <v>16</v>
       </c>
-      <c r="F211" t="s">
-        <v>728</v>
-      </c>
       <c r="G211" t="s">
         <v>900</v>
       </c>
+      <c r="H211" t="s">
+        <v>729</v>
+      </c>
       <c r="I211" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J211" t="s">
         <v>843</v>
       </c>
       <c r="K211" t="s">
+        <v>844</v>
+      </c>
+      <c r="L211" t="s">
         <v>901</v>
       </c>
-      <c r="L211" t="s">
-        <v>22</v>
-      </c>
       <c r="M211" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -11592,26 +11592,26 @@
       <c r="E212" t="s">
         <v>16</v>
       </c>
-      <c r="F212" t="s">
-        <v>728</v>
-      </c>
       <c r="G212" t="s">
         <v>904</v>
       </c>
+      <c r="H212" t="s">
+        <v>729</v>
+      </c>
       <c r="I212" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J212" t="s">
         <v>843</v>
       </c>
       <c r="K212" t="s">
+        <v>844</v>
+      </c>
+      <c r="L212" t="s">
         <v>905</v>
       </c>
-      <c r="L212" t="s">
-        <v>22</v>
-      </c>
       <c r="M212" t="s">
-        <v>845</v>
+        <v>733</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -11627,14 +11627,14 @@
       <c r="E213" t="s">
         <v>16</v>
       </c>
-      <c r="F213" t="s">
-        <v>728</v>
-      </c>
       <c r="G213" t="s">
         <v>908</v>
       </c>
+      <c r="H213" t="s">
+        <v>729</v>
+      </c>
       <c r="I213" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J213" t="s">
         <v>909</v>
@@ -11643,10 +11643,10 @@
         <v>910</v>
       </c>
       <c r="L213" t="s">
-        <v>22</v>
+        <v>911</v>
       </c>
       <c r="M213" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -11662,26 +11662,26 @@
       <c r="E214" t="s">
         <v>16</v>
       </c>
-      <c r="F214" t="s">
-        <v>728</v>
-      </c>
       <c r="G214" t="s">
         <v>914</v>
       </c>
+      <c r="H214" t="s">
+        <v>729</v>
+      </c>
       <c r="I214" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J214" t="s">
         <v>909</v>
       </c>
       <c r="K214" t="s">
+        <v>910</v>
+      </c>
+      <c r="L214" t="s">
         <v>915</v>
       </c>
-      <c r="L214" t="s">
-        <v>22</v>
-      </c>
       <c r="M214" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -11697,26 +11697,26 @@
       <c r="E215" t="s">
         <v>16</v>
       </c>
-      <c r="F215" t="s">
-        <v>728</v>
-      </c>
       <c r="G215" t="s">
         <v>918</v>
       </c>
+      <c r="H215" t="s">
+        <v>729</v>
+      </c>
       <c r="I215" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J215" t="s">
         <v>909</v>
       </c>
       <c r="K215" t="s">
+        <v>910</v>
+      </c>
+      <c r="L215" t="s">
         <v>919</v>
       </c>
-      <c r="L215" t="s">
-        <v>22</v>
-      </c>
       <c r="M215" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -11732,26 +11732,26 @@
       <c r="E216" t="s">
         <v>16</v>
       </c>
-      <c r="F216" t="s">
-        <v>728</v>
-      </c>
       <c r="G216" t="s">
         <v>922</v>
       </c>
+      <c r="H216" t="s">
+        <v>729</v>
+      </c>
       <c r="I216" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J216" t="s">
         <v>909</v>
       </c>
       <c r="K216" t="s">
+        <v>910</v>
+      </c>
+      <c r="L216" t="s">
         <v>923</v>
       </c>
-      <c r="L216" t="s">
-        <v>22</v>
-      </c>
       <c r="M216" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -11767,26 +11767,26 @@
       <c r="E217" t="s">
         <v>16</v>
       </c>
-      <c r="F217" t="s">
-        <v>728</v>
-      </c>
       <c r="G217" t="s">
         <v>926</v>
       </c>
+      <c r="H217" t="s">
+        <v>729</v>
+      </c>
       <c r="I217" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J217" t="s">
         <v>909</v>
       </c>
       <c r="K217" t="s">
+        <v>910</v>
+      </c>
+      <c r="L217" t="s">
         <v>927</v>
       </c>
-      <c r="L217" t="s">
-        <v>22</v>
-      </c>
       <c r="M217" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -11802,26 +11802,26 @@
       <c r="E218" t="s">
         <v>16</v>
       </c>
-      <c r="F218" t="s">
-        <v>728</v>
-      </c>
       <c r="G218" t="s">
         <v>930</v>
       </c>
+      <c r="H218" t="s">
+        <v>729</v>
+      </c>
       <c r="I218" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J218" t="s">
         <v>909</v>
       </c>
       <c r="K218" t="s">
+        <v>910</v>
+      </c>
+      <c r="L218" t="s">
         <v>931</v>
       </c>
-      <c r="L218" t="s">
-        <v>22</v>
-      </c>
       <c r="M218" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -11837,26 +11837,26 @@
       <c r="E219" t="s">
         <v>16</v>
       </c>
-      <c r="F219" t="s">
-        <v>728</v>
-      </c>
       <c r="G219" t="s">
         <v>934</v>
       </c>
+      <c r="H219" t="s">
+        <v>729</v>
+      </c>
       <c r="I219" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J219" t="s">
         <v>909</v>
       </c>
       <c r="K219" t="s">
+        <v>910</v>
+      </c>
+      <c r="L219" t="s">
         <v>935</v>
       </c>
-      <c r="L219" t="s">
-        <v>22</v>
-      </c>
       <c r="M219" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -11872,26 +11872,26 @@
       <c r="E220" t="s">
         <v>16</v>
       </c>
-      <c r="F220" t="s">
-        <v>728</v>
-      </c>
       <c r="G220" t="s">
         <v>938</v>
       </c>
+      <c r="H220" t="s">
+        <v>729</v>
+      </c>
       <c r="I220" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J220" t="s">
         <v>909</v>
       </c>
       <c r="K220" t="s">
+        <v>910</v>
+      </c>
+      <c r="L220" t="s">
         <v>939</v>
       </c>
-      <c r="L220" t="s">
-        <v>22</v>
-      </c>
       <c r="M220" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -11907,26 +11907,26 @@
       <c r="E221" t="s">
         <v>16</v>
       </c>
-      <c r="F221" t="s">
-        <v>728</v>
-      </c>
       <c r="G221" t="s">
         <v>942</v>
       </c>
+      <c r="H221" t="s">
+        <v>729</v>
+      </c>
       <c r="I221" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="J221" t="s">
         <v>909</v>
       </c>
       <c r="K221" t="s">
+        <v>910</v>
+      </c>
+      <c r="L221" t="s">
         <v>943</v>
       </c>
-      <c r="L221" t="s">
-        <v>22</v>
-      </c>
       <c r="M221" t="s">
-        <v>911</v>
+        <v>733</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -11942,23 +11942,23 @@
       <c r="E222" t="s">
         <v>16</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>946</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>947</v>
       </c>
       <c r="I222" t="s">
+        <v>19</v>
+      </c>
+      <c r="J222" t="s">
         <v>948</v>
       </c>
-      <c r="J222" t="s">
+      <c r="K222" t="s">
         <v>949</v>
       </c>
-      <c r="K222" t="s">
+      <c r="L222" t="s">
         <v>950</v>
-      </c>
-      <c r="L222" t="s">
-        <v>22</v>
       </c>
       <c r="M222" t="s">
         <v>951</v>
@@ -11977,23 +11977,23 @@
       <c r="E223" t="s">
         <v>16</v>
       </c>
-      <c r="F223" t="s">
-        <v>946</v>
-      </c>
       <c r="G223" t="s">
         <v>954</v>
       </c>
+      <c r="H223" t="s">
+        <v>947</v>
+      </c>
       <c r="I223" t="s">
+        <v>19</v>
+      </c>
+      <c r="J223" t="s">
         <v>948</v>
       </c>
-      <c r="J223" t="s">
+      <c r="K223" t="s">
         <v>949</v>
       </c>
-      <c r="K223" t="s">
+      <c r="L223" t="s">
         <v>955</v>
-      </c>
-      <c r="L223" t="s">
-        <v>22</v>
       </c>
       <c r="M223" t="s">
         <v>951</v>
@@ -12012,23 +12012,23 @@
       <c r="E224" t="s">
         <v>16</v>
       </c>
-      <c r="F224" t="s">
-        <v>946</v>
-      </c>
       <c r="G224" t="s">
         <v>958</v>
       </c>
+      <c r="H224" t="s">
+        <v>947</v>
+      </c>
       <c r="I224" t="s">
+        <v>19</v>
+      </c>
+      <c r="J224" t="s">
         <v>948</v>
       </c>
-      <c r="J224" t="s">
+      <c r="K224" t="s">
         <v>949</v>
       </c>
-      <c r="K224" t="s">
+      <c r="L224" t="s">
         <v>959</v>
-      </c>
-      <c r="L224" t="s">
-        <v>22</v>
       </c>
       <c r="M224" t="s">
         <v>951</v>
@@ -12047,23 +12047,23 @@
       <c r="E225" t="s">
         <v>16</v>
       </c>
-      <c r="F225" t="s">
-        <v>946</v>
-      </c>
       <c r="G225" t="s">
         <v>962</v>
       </c>
+      <c r="H225" t="s">
+        <v>947</v>
+      </c>
       <c r="I225" t="s">
+        <v>19</v>
+      </c>
+      <c r="J225" t="s">
         <v>948</v>
       </c>
-      <c r="J225" t="s">
+      <c r="K225" t="s">
         <v>949</v>
       </c>
-      <c r="K225" t="s">
+      <c r="L225" t="s">
         <v>963</v>
-      </c>
-      <c r="L225" t="s">
-        <v>22</v>
       </c>
       <c r="M225" t="s">
         <v>951</v>
@@ -12082,23 +12082,23 @@
       <c r="E226" t="s">
         <v>16</v>
       </c>
-      <c r="F226" t="s">
-        <v>946</v>
-      </c>
       <c r="G226" t="s">
         <v>966</v>
       </c>
+      <c r="H226" t="s">
+        <v>947</v>
+      </c>
       <c r="I226" t="s">
+        <v>19</v>
+      </c>
+      <c r="J226" t="s">
         <v>948</v>
       </c>
-      <c r="J226" t="s">
+      <c r="K226" t="s">
         <v>949</v>
       </c>
-      <c r="K226" t="s">
+      <c r="L226" t="s">
         <v>967</v>
-      </c>
-      <c r="L226" t="s">
-        <v>22</v>
       </c>
       <c r="M226" t="s">
         <v>951</v>
@@ -12117,23 +12117,23 @@
       <c r="E227" t="s">
         <v>16</v>
       </c>
-      <c r="F227" t="s">
-        <v>946</v>
-      </c>
       <c r="G227" t="s">
         <v>970</v>
       </c>
+      <c r="H227" t="s">
+        <v>947</v>
+      </c>
       <c r="I227" t="s">
+        <v>19</v>
+      </c>
+      <c r="J227" t="s">
         <v>948</v>
       </c>
-      <c r="J227" t="s">
+      <c r="K227" t="s">
         <v>949</v>
       </c>
-      <c r="K227" t="s">
+      <c r="L227" t="s">
         <v>971</v>
-      </c>
-      <c r="L227" t="s">
-        <v>22</v>
       </c>
       <c r="M227" t="s">
         <v>951</v>
@@ -12152,14 +12152,14 @@
       <c r="E228" t="s">
         <v>16</v>
       </c>
-      <c r="F228" t="s">
-        <v>946</v>
-      </c>
       <c r="G228" t="s">
         <v>974</v>
       </c>
+      <c r="H228" t="s">
+        <v>947</v>
+      </c>
       <c r="I228" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J228" t="s">
         <v>975</v>
@@ -12168,10 +12168,10 @@
         <v>976</v>
       </c>
       <c r="L228" t="s">
-        <v>22</v>
+        <v>977</v>
       </c>
       <c r="M228" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -12187,26 +12187,26 @@
       <c r="E229" t="s">
         <v>16</v>
       </c>
-      <c r="F229" t="s">
-        <v>946</v>
-      </c>
       <c r="G229" t="s">
         <v>980</v>
       </c>
+      <c r="H229" t="s">
+        <v>947</v>
+      </c>
       <c r="I229" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J229" t="s">
         <v>975</v>
       </c>
       <c r="K229" t="s">
+        <v>976</v>
+      </c>
+      <c r="L229" t="s">
         <v>981</v>
       </c>
-      <c r="L229" t="s">
-        <v>22</v>
-      </c>
       <c r="M229" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -12222,26 +12222,26 @@
       <c r="E230" t="s">
         <v>16</v>
       </c>
-      <c r="F230" t="s">
-        <v>946</v>
-      </c>
       <c r="G230" t="s">
         <v>984</v>
       </c>
+      <c r="H230" t="s">
+        <v>947</v>
+      </c>
       <c r="I230" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J230" t="s">
         <v>975</v>
       </c>
       <c r="K230" t="s">
+        <v>976</v>
+      </c>
+      <c r="L230" t="s">
         <v>985</v>
       </c>
-      <c r="L230" t="s">
-        <v>22</v>
-      </c>
       <c r="M230" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -12257,26 +12257,26 @@
       <c r="E231" t="s">
         <v>16</v>
       </c>
-      <c r="F231" t="s">
-        <v>946</v>
-      </c>
       <c r="G231" t="s">
         <v>988</v>
       </c>
+      <c r="H231" t="s">
+        <v>947</v>
+      </c>
       <c r="I231" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J231" t="s">
         <v>975</v>
       </c>
       <c r="K231" t="s">
+        <v>976</v>
+      </c>
+      <c r="L231" t="s">
         <v>989</v>
       </c>
-      <c r="L231" t="s">
-        <v>22</v>
-      </c>
       <c r="M231" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -12292,26 +12292,26 @@
       <c r="E232" t="s">
         <v>16</v>
       </c>
-      <c r="F232" t="s">
-        <v>946</v>
-      </c>
       <c r="G232" t="s">
         <v>992</v>
       </c>
+      <c r="H232" t="s">
+        <v>947</v>
+      </c>
       <c r="I232" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J232" t="s">
         <v>975</v>
       </c>
       <c r="K232" t="s">
+        <v>976</v>
+      </c>
+      <c r="L232" t="s">
         <v>993</v>
       </c>
-      <c r="L232" t="s">
-        <v>22</v>
-      </c>
       <c r="M232" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -12327,14 +12327,14 @@
       <c r="E233" t="s">
         <v>16</v>
       </c>
-      <c r="F233" t="s">
-        <v>946</v>
-      </c>
       <c r="G233" t="s">
         <v>996</v>
       </c>
+      <c r="H233" t="s">
+        <v>947</v>
+      </c>
       <c r="I233" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J233" t="s">
         <v>997</v>
@@ -12343,10 +12343,10 @@
         <v>998</v>
       </c>
       <c r="L233" t="s">
-        <v>22</v>
+        <v>999</v>
       </c>
       <c r="M233" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -12362,26 +12362,26 @@
       <c r="E234" t="s">
         <v>16</v>
       </c>
-      <c r="F234" t="s">
-        <v>946</v>
-      </c>
       <c r="G234" t="s">
         <v>1002</v>
       </c>
+      <c r="H234" t="s">
+        <v>947</v>
+      </c>
       <c r="I234" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J234" t="s">
         <v>997</v>
       </c>
       <c r="K234" t="s">
+        <v>998</v>
+      </c>
+      <c r="L234" t="s">
         <v>1003</v>
       </c>
-      <c r="L234" t="s">
-        <v>22</v>
-      </c>
       <c r="M234" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -12397,26 +12397,26 @@
       <c r="E235" t="s">
         <v>16</v>
       </c>
-      <c r="F235" t="s">
-        <v>946</v>
-      </c>
       <c r="G235" t="s">
         <v>1006</v>
       </c>
+      <c r="H235" t="s">
+        <v>947</v>
+      </c>
       <c r="I235" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J235" t="s">
         <v>997</v>
       </c>
       <c r="K235" t="s">
+        <v>998</v>
+      </c>
+      <c r="L235" t="s">
         <v>1007</v>
       </c>
-      <c r="L235" t="s">
-        <v>22</v>
-      </c>
       <c r="M235" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -12432,26 +12432,26 @@
       <c r="E236" t="s">
         <v>16</v>
       </c>
-      <c r="F236" t="s">
-        <v>946</v>
-      </c>
       <c r="G236" t="s">
         <v>1010</v>
       </c>
+      <c r="H236" t="s">
+        <v>947</v>
+      </c>
       <c r="I236" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J236" t="s">
         <v>997</v>
       </c>
       <c r="K236" t="s">
+        <v>998</v>
+      </c>
+      <c r="L236" t="s">
         <v>1011</v>
       </c>
-      <c r="L236" t="s">
-        <v>22</v>
-      </c>
       <c r="M236" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -12467,26 +12467,26 @@
       <c r="E237" t="s">
         <v>16</v>
       </c>
-      <c r="F237" t="s">
-        <v>946</v>
-      </c>
       <c r="G237" t="s">
         <v>1014</v>
       </c>
+      <c r="H237" t="s">
+        <v>947</v>
+      </c>
       <c r="I237" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J237" t="s">
         <v>997</v>
       </c>
       <c r="K237" t="s">
+        <v>998</v>
+      </c>
+      <c r="L237" t="s">
         <v>1015</v>
       </c>
-      <c r="L237" t="s">
-        <v>22</v>
-      </c>
       <c r="M237" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -12502,26 +12502,26 @@
       <c r="E238" t="s">
         <v>16</v>
       </c>
-      <c r="F238" t="s">
-        <v>946</v>
-      </c>
       <c r="G238" t="s">
         <v>1018</v>
       </c>
+      <c r="H238" t="s">
+        <v>947</v>
+      </c>
       <c r="I238" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J238" t="s">
         <v>997</v>
       </c>
       <c r="K238" t="s">
+        <v>998</v>
+      </c>
+      <c r="L238" t="s">
         <v>1019</v>
       </c>
-      <c r="L238" t="s">
-        <v>22</v>
-      </c>
       <c r="M238" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -12537,26 +12537,26 @@
       <c r="E239" t="s">
         <v>16</v>
       </c>
-      <c r="F239" t="s">
-        <v>946</v>
-      </c>
       <c r="G239" t="s">
         <v>1022</v>
       </c>
+      <c r="H239" t="s">
+        <v>947</v>
+      </c>
       <c r="I239" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J239" t="s">
         <v>997</v>
       </c>
       <c r="K239" t="s">
+        <v>998</v>
+      </c>
+      <c r="L239" t="s">
         <v>1023</v>
       </c>
-      <c r="L239" t="s">
-        <v>22</v>
-      </c>
       <c r="M239" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -12572,26 +12572,26 @@
       <c r="E240" t="s">
         <v>16</v>
       </c>
-      <c r="F240" t="s">
-        <v>946</v>
-      </c>
       <c r="G240" t="s">
         <v>1026</v>
       </c>
+      <c r="H240" t="s">
+        <v>947</v>
+      </c>
       <c r="I240" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J240" t="s">
         <v>997</v>
       </c>
       <c r="K240" t="s">
+        <v>998</v>
+      </c>
+      <c r="L240" t="s">
         <v>1027</v>
       </c>
-      <c r="L240" t="s">
-        <v>22</v>
-      </c>
       <c r="M240" t="s">
-        <v>999</v>
+        <v>951</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -12607,14 +12607,14 @@
       <c r="E241" t="s">
         <v>16</v>
       </c>
-      <c r="F241" t="s">
-        <v>946</v>
-      </c>
       <c r="G241" t="s">
         <v>1030</v>
       </c>
+      <c r="H241" t="s">
+        <v>947</v>
+      </c>
       <c r="I241" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J241" t="s">
         <v>1031</v>
@@ -12623,10 +12623,10 @@
         <v>1032</v>
       </c>
       <c r="L241" t="s">
-        <v>22</v>
+        <v>1033</v>
       </c>
       <c r="M241" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -12642,26 +12642,26 @@
       <c r="E242" t="s">
         <v>16</v>
       </c>
-      <c r="F242" t="s">
-        <v>946</v>
-      </c>
       <c r="G242" t="s">
         <v>1036</v>
       </c>
+      <c r="H242" t="s">
+        <v>947</v>
+      </c>
       <c r="I242" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J242" t="s">
         <v>1031</v>
       </c>
       <c r="K242" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L242" t="s">
         <v>1037</v>
       </c>
-      <c r="L242" t="s">
-        <v>22</v>
-      </c>
       <c r="M242" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -12677,26 +12677,26 @@
       <c r="E243" t="s">
         <v>16</v>
       </c>
-      <c r="F243" t="s">
-        <v>946</v>
-      </c>
       <c r="G243" t="s">
         <v>1040</v>
       </c>
+      <c r="H243" t="s">
+        <v>947</v>
+      </c>
       <c r="I243" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J243" t="s">
         <v>1031</v>
       </c>
       <c r="K243" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L243" t="s">
         <v>1041</v>
       </c>
-      <c r="L243" t="s">
-        <v>22</v>
-      </c>
       <c r="M243" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -12712,26 +12712,26 @@
       <c r="E244" t="s">
         <v>16</v>
       </c>
-      <c r="F244" t="s">
-        <v>946</v>
-      </c>
       <c r="G244" t="s">
         <v>1044</v>
       </c>
+      <c r="H244" t="s">
+        <v>947</v>
+      </c>
       <c r="I244" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J244" t="s">
         <v>1031</v>
       </c>
       <c r="K244" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L244" t="s">
         <v>1045</v>
       </c>
-      <c r="L244" t="s">
-        <v>22</v>
-      </c>
       <c r="M244" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -12747,26 +12747,26 @@
       <c r="E245" t="s">
         <v>16</v>
       </c>
-      <c r="F245" t="s">
-        <v>946</v>
-      </c>
       <c r="G245" t="s">
         <v>1048</v>
       </c>
+      <c r="H245" t="s">
+        <v>947</v>
+      </c>
       <c r="I245" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J245" t="s">
         <v>1031</v>
       </c>
       <c r="K245" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L245" t="s">
         <v>1049</v>
       </c>
-      <c r="L245" t="s">
-        <v>22</v>
-      </c>
       <c r="M245" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -12782,26 +12782,26 @@
       <c r="E246" t="s">
         <v>16</v>
       </c>
-      <c r="F246" t="s">
-        <v>946</v>
-      </c>
       <c r="G246" t="s">
         <v>1052</v>
       </c>
+      <c r="H246" t="s">
+        <v>947</v>
+      </c>
       <c r="I246" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J246" t="s">
         <v>1031</v>
       </c>
       <c r="K246" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L246" t="s">
         <v>1053</v>
       </c>
-      <c r="L246" t="s">
-        <v>22</v>
-      </c>
       <c r="M246" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -12817,26 +12817,26 @@
       <c r="E247" t="s">
         <v>16</v>
       </c>
-      <c r="F247" t="s">
-        <v>946</v>
-      </c>
       <c r="G247" t="s">
         <v>1056</v>
       </c>
+      <c r="H247" t="s">
+        <v>947</v>
+      </c>
       <c r="I247" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J247" t="s">
         <v>1031</v>
       </c>
       <c r="K247" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L247" t="s">
         <v>1057</v>
       </c>
-      <c r="L247" t="s">
-        <v>22</v>
-      </c>
       <c r="M247" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -12852,26 +12852,26 @@
       <c r="E248" t="s">
         <v>16</v>
       </c>
-      <c r="F248" t="s">
-        <v>946</v>
-      </c>
       <c r="G248" t="s">
         <v>1060</v>
       </c>
+      <c r="H248" t="s">
+        <v>947</v>
+      </c>
       <c r="I248" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J248" t="s">
         <v>1031</v>
       </c>
       <c r="K248" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L248" t="s">
         <v>1061</v>
       </c>
-      <c r="L248" t="s">
-        <v>22</v>
-      </c>
       <c r="M248" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -12887,26 +12887,26 @@
       <c r="E249" t="s">
         <v>16</v>
       </c>
-      <c r="F249" t="s">
-        <v>946</v>
-      </c>
       <c r="G249" t="s">
         <v>1064</v>
       </c>
+      <c r="H249" t="s">
+        <v>947</v>
+      </c>
       <c r="I249" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J249" t="s">
         <v>1031</v>
       </c>
       <c r="K249" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L249" t="s">
         <v>1065</v>
       </c>
-      <c r="L249" t="s">
-        <v>22</v>
-      </c>
       <c r="M249" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -12922,26 +12922,26 @@
       <c r="E250" t="s">
         <v>16</v>
       </c>
-      <c r="F250" t="s">
-        <v>946</v>
-      </c>
       <c r="G250" t="s">
         <v>1068</v>
       </c>
+      <c r="H250" t="s">
+        <v>947</v>
+      </c>
       <c r="I250" t="s">
-        <v>948</v>
+        <v>19</v>
       </c>
       <c r="J250" t="s">
         <v>1031</v>
       </c>
       <c r="K250" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L250" t="s">
         <v>1069</v>
       </c>
-      <c r="L250" t="s">
-        <v>22</v>
-      </c>
       <c r="M250" t="s">
-        <v>1033</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,33 +25,33 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-code</t>
   </si>
   <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-name</t>
   </si>
   <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
@@ -64,27 +64,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
     <t>001</t>
   </si>
   <si>
+    <t>DZA</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
     <t>015</t>
   </si>
   <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -166,24 +166,24 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -445,15 +445,15 @@
     <t>AO</t>
   </si>
   <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Middle Africa</t>
+  </si>
+  <si>
     <t>AGO</t>
   </si>
   <si>
-    <t>Middle Africa</t>
-  </si>
-  <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -559,15 +559,15 @@
     <t>BW</t>
   </si>
   <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Southern Africa</t>
+  </si>
+  <si>
     <t>BWA</t>
   </si>
   <si>
-    <t>Southern Africa</t>
-  </si>
-  <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -625,15 +625,15 @@
     <t>BJ</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Western Africa</t>
+  </si>
+  <si>
     <t>BEN</t>
   </si>
   <si>
-    <t>Western Africa</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
     <t>419</t>
   </si>
   <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>AIA</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
     <t>019</t>
   </si>
   <si>
@@ -1189,15 +1189,15 @@
     <t>BZ</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>Central America</t>
+  </si>
+  <si>
     <t>BLZ</t>
   </si>
   <si>
-    <t>Central America</t>
-  </si>
-  <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -1291,15 +1291,15 @@
     <t>AR</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>South America</t>
+  </si>
+  <si>
     <t>ARG</t>
   </si>
   <si>
-    <t>South America</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1486,18 +1486,18 @@
     <t>Bermuda</t>
   </si>
   <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>Northern America</t>
+  </si>
+  <si>
+    <t>BMU</t>
+  </si>
+  <si>
     <t>021</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>BMU</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1564,21 +1564,21 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>KAZ</t>
-  </si>
-  <si>
     <t>142</t>
   </si>
   <si>
@@ -1636,18 +1636,18 @@
     <t>China</t>
   </si>
   <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>CHN</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1726,18 +1726,18 @@
     <t>Brunei Darussalam</t>
   </si>
   <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
+    <t>BRN</t>
+  </si>
+  <si>
     <t>035</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
-    <t>BN</t>
-  </si>
-  <si>
-    <t>BRN</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1864,18 +1864,18 @@
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
+    <t>AFG</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFG</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1978,18 +1978,18 @@
     <t>Armenia</t>
   </si>
   <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>ARM</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -2200,21 +2200,21 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -2332,18 +2332,18 @@
     <t>Åland Islands</t>
   </si>
   <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
+    <t>ALA</t>
+  </si>
+  <si>
     <t>154</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>ALA</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
@@ -2353,15 +2353,15 @@
     <t>GG</t>
   </si>
   <si>
+    <t>830</t>
+  </si>
+  <si>
+    <t>Channel Islands</t>
+  </si>
+  <si>
     <t>GGY</t>
   </si>
   <si>
-    <t>Channel Islands</t>
-  </si>
-  <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>832</t>
   </si>
   <si>
@@ -2542,18 +2542,18 @@
     <t>Albania</t>
   </si>
   <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
     <t>039</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2740,18 +2740,18 @@
     <t>Austria</t>
   </si>
   <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
-    <t>AT</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2854,21 +2854,21 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
     <t>009</t>
   </si>
   <si>
@@ -2938,18 +2938,18 @@
     <t>Fiji</t>
   </si>
   <si>
+    <t>FJ</t>
+  </si>
+  <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
+    <t>FJI</t>
+  </si>
+  <si>
     <t>054</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
-    <t>FJ</t>
-  </si>
-  <si>
-    <t>FJI</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -3004,18 +3004,18 @@
     <t>Guam</t>
   </si>
   <si>
+    <t>GU</t>
+  </si>
+  <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
+    <t>GUM</t>
+  </si>
+  <si>
     <t>057</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
-    <t>GU</t>
-  </si>
-  <si>
-    <t>GUM</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -3106,16 +3106,16 @@
     <t>American Samoa</t>
   </si>
   <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
+    <t>ASM</t>
+  </si>
+  <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>ASM</t>
   </si>
   <si>
     <t>184</t>
@@ -3618,16 +3618,16 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
       <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
       <c r="M2" t="s">
@@ -3648,22 +3648,22 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
       <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
         <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -3683,22 +3683,22 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
       <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s">
         <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
       </c>
       <c r="M4" t="s">
         <v>23</v>
@@ -3718,22 +3718,22 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
       <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
         <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
       </c>
       <c r="M5" t="s">
         <v>23</v>
@@ -3753,22 +3753,22 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
       <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
         <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -3788,22 +3788,22 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
       <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
@@ -3823,22 +3823,22 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
       <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
         <v>47</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
       </c>
       <c r="M8" t="s">
         <v>23</v>
@@ -3858,25 +3858,25 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>55</v>
@@ -3899,25 +3899,25 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J10" t="s">
         <v>59</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
         <v>55</v>
@@ -3940,25 +3940,25 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="J11" t="s">
         <v>63</v>
       </c>
       <c r="K11" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>55</v>
@@ -3981,25 +3981,25 @@
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J12" t="s">
         <v>67</v>
       </c>
       <c r="K12" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
         <v>55</v>
@@ -4022,25 +4022,25 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
         <v>55</v>
@@ -4063,25 +4063,25 @@
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
         <v>75</v>
       </c>
       <c r="K14" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L14" t="s">
         <v>55</v>
@@ -4104,25 +4104,25 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
         <v>79</v>
       </c>
       <c r="K15" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
         <v>55</v>
@@ -4145,25 +4145,25 @@
         <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="J16" t="s">
         <v>83</v>
       </c>
       <c r="K16" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L16" t="s">
         <v>55</v>
@@ -4186,25 +4186,25 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
         <v>87</v>
       </c>
       <c r="K17" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
@@ -4227,25 +4227,25 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
         <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L18" t="s">
         <v>55</v>
@@ -4268,25 +4268,25 @@
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="J19" t="s">
         <v>95</v>
       </c>
       <c r="K19" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L19" t="s">
         <v>55</v>
@@ -4309,25 +4309,25 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="J20" t="s">
         <v>99</v>
       </c>
       <c r="K20" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
         <v>55</v>
@@ -4350,25 +4350,25 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="J21" t="s">
         <v>103</v>
       </c>
       <c r="K21" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L21" t="s">
         <v>55</v>
@@ -4391,25 +4391,25 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="J22" t="s">
         <v>107</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L22" t="s">
         <v>55</v>
@@ -4432,25 +4432,25 @@
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="J23" t="s">
         <v>111</v>
       </c>
       <c r="K23" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L23" t="s">
         <v>55</v>
@@ -4473,25 +4473,25 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="J24" t="s">
         <v>115</v>
       </c>
       <c r="K24" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L24" t="s">
         <v>55</v>
@@ -4514,25 +4514,25 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I25" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="J25" t="s">
         <v>119</v>
       </c>
       <c r="K25" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
         <v>55</v>
@@ -4555,25 +4555,25 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="J26" t="s">
         <v>123</v>
       </c>
       <c r="K26" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
         <v>55</v>
@@ -4596,25 +4596,25 @@
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="J27" t="s">
         <v>127</v>
       </c>
       <c r="K27" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
         <v>55</v>
@@ -4637,25 +4637,25 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="J28" t="s">
         <v>131</v>
       </c>
       <c r="K28" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L28" t="s">
         <v>55</v>
@@ -4678,25 +4678,25 @@
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I29" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="J29" t="s">
         <v>135</v>
       </c>
       <c r="K29" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L29" t="s">
         <v>55</v>
@@ -4719,25 +4719,25 @@
         <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="J30" t="s">
         <v>139</v>
       </c>
       <c r="K30" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="L30" t="s">
         <v>55</v>
@@ -4760,28 +4760,28 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K31" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L31" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M31" t="s">
         <v>23</v>
@@ -4801,28 +4801,28 @@
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J32" t="s">
         <v>149</v>
       </c>
       <c r="K32" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M32" t="s">
         <v>23</v>
@@ -4842,28 +4842,28 @@
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="J33" t="s">
         <v>153</v>
       </c>
       <c r="K33" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M33" t="s">
         <v>23</v>
@@ -4883,28 +4883,28 @@
         <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="J34" t="s">
         <v>157</v>
       </c>
       <c r="K34" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M34" t="s">
         <v>23</v>
@@ -4924,28 +4924,28 @@
         <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="J35" t="s">
         <v>161</v>
       </c>
       <c r="K35" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L35" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M35" t="s">
         <v>23</v>
@@ -4965,28 +4965,28 @@
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="J36" t="s">
         <v>165</v>
       </c>
       <c r="K36" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M36" t="s">
         <v>23</v>
@@ -5006,28 +5006,28 @@
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I37" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="J37" t="s">
         <v>169</v>
       </c>
       <c r="K37" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L37" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M37" t="s">
         <v>23</v>
@@ -5047,28 +5047,28 @@
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="J38" t="s">
         <v>173</v>
       </c>
       <c r="K38" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -5088,28 +5088,28 @@
         <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I39" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="J39" t="s">
         <v>177</v>
       </c>
       <c r="K39" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -5129,28 +5129,28 @@
         <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J40" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K40" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="L40" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -5170,28 +5170,28 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G41" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J41" t="s">
         <v>187</v>
       </c>
       <c r="K41" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="L41" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -5211,28 +5211,28 @@
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>190</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G42" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="J42" t="s">
         <v>191</v>
       </c>
       <c r="K42" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="L42" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -5252,28 +5252,28 @@
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="F43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="J43" t="s">
         <v>195</v>
       </c>
       <c r="K43" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
@@ -5293,28 +5293,28 @@
         <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="F44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="J44" t="s">
         <v>199</v>
       </c>
       <c r="K44" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="L44" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
@@ -5334,28 +5334,28 @@
         <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J45" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K45" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L45" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -5375,28 +5375,28 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="F46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J46" t="s">
         <v>209</v>
       </c>
       <c r="K46" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L46" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -5416,28 +5416,28 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G47" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="J47" t="s">
         <v>213</v>
       </c>
       <c r="K47" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L47" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
@@ -5457,28 +5457,28 @@
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="J48" t="s">
         <v>217</v>
       </c>
       <c r="K48" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L48" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
@@ -5498,28 +5498,28 @@
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>220</v>
       </c>
       <c r="F49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G49" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="J49" t="s">
         <v>221</v>
       </c>
       <c r="K49" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L49" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
@@ -5539,28 +5539,28 @@
         <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="F50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="J50" t="s">
         <v>225</v>
       </c>
       <c r="K50" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L50" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
@@ -5580,28 +5580,28 @@
         <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G51" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="J51" t="s">
         <v>229</v>
       </c>
       <c r="K51" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L51" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -5621,28 +5621,28 @@
         <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="F52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="J52" t="s">
         <v>233</v>
       </c>
       <c r="K52" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L52" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -5662,28 +5662,28 @@
         <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>236</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G53" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="J53" t="s">
         <v>237</v>
       </c>
       <c r="K53" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L53" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M53" t="s">
         <v>23</v>
@@ -5703,28 +5703,28 @@
         <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="J54" t="s">
         <v>241</v>
       </c>
       <c r="K54" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L54" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M54" t="s">
         <v>23</v>
@@ -5744,28 +5744,28 @@
         <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>244</v>
       </c>
       <c r="F55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G55" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="J55" t="s">
         <v>245</v>
       </c>
       <c r="K55" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L55" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M55" t="s">
         <v>23</v>
@@ -5785,28 +5785,28 @@
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>248</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="J56" t="s">
         <v>249</v>
       </c>
       <c r="K56" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
@@ -5826,28 +5826,28 @@
         <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>252</v>
       </c>
       <c r="F57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G57" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="J57" t="s">
         <v>253</v>
       </c>
       <c r="K57" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L57" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
@@ -5867,28 +5867,28 @@
         <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="F58" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G58" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="J58" t="s">
         <v>257</v>
       </c>
       <c r="K58" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L58" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -5908,28 +5908,28 @@
         <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
       <c r="F59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G59" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I59" t="s">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="J59" t="s">
         <v>261</v>
       </c>
       <c r="K59" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L59" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
@@ -5949,28 +5949,28 @@
         <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="F60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G60" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="J60" t="s">
         <v>265</v>
       </c>
       <c r="K60" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
@@ -5990,28 +5990,28 @@
         <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>268</v>
       </c>
       <c r="F61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G61" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="J61" t="s">
         <v>269</v>
       </c>
       <c r="K61" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="L61" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -6028,28 +6028,28 @@
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F62" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G62" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H62" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K62" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L62" t="s">
         <v>278</v>
@@ -6069,28 +6069,28 @@
         <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>282</v>
       </c>
       <c r="F63" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G63" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H63" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I63" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J63" t="s">
         <v>283</v>
       </c>
       <c r="K63" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L63" t="s">
         <v>278</v>
@@ -6110,28 +6110,28 @@
         <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G64" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H64" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I64" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="J64" t="s">
         <v>287</v>
       </c>
       <c r="K64" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L64" t="s">
         <v>278</v>
@@ -6151,28 +6151,28 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>290</v>
       </c>
       <c r="F65" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G65" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H65" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I65" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="J65" t="s">
         <v>291</v>
       </c>
       <c r="K65" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L65" t="s">
         <v>278</v>
@@ -6192,28 +6192,28 @@
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>294</v>
       </c>
       <c r="F66" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G66" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H66" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I66" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="J66" t="s">
         <v>295</v>
       </c>
       <c r="K66" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L66" t="s">
         <v>278</v>
@@ -6233,28 +6233,28 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>298</v>
       </c>
       <c r="F67" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G67" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H67" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I67" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="J67" t="s">
         <v>299</v>
       </c>
       <c r="K67" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L67" t="s">
         <v>278</v>
@@ -6274,28 +6274,28 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="F68" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G68" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H68" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I68" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="J68" t="s">
         <v>303</v>
       </c>
       <c r="K68" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L68" t="s">
         <v>278</v>
@@ -6315,28 +6315,28 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c r="F69" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G69" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H69" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I69" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="J69" t="s">
         <v>307</v>
       </c>
       <c r="K69" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L69" t="s">
         <v>278</v>
@@ -6356,28 +6356,28 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="F70" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G70" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H70" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I70" t="s">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="J70" t="s">
         <v>311</v>
       </c>
       <c r="K70" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L70" t="s">
         <v>278</v>
@@ -6397,28 +6397,28 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>314</v>
       </c>
       <c r="F71" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G71" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H71" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I71" t="s">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="J71" t="s">
         <v>315</v>
       </c>
       <c r="K71" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L71" t="s">
         <v>278</v>
@@ -6438,28 +6438,28 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>318</v>
       </c>
       <c r="F72" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G72" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H72" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="J72" t="s">
         <v>319</v>
       </c>
       <c r="K72" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L72" t="s">
         <v>278</v>
@@ -6479,28 +6479,28 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>322</v>
       </c>
       <c r="F73" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G73" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H73" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I73" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="J73" t="s">
         <v>323</v>
       </c>
       <c r="K73" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L73" t="s">
         <v>278</v>
@@ -6520,28 +6520,28 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>326</v>
       </c>
       <c r="F74" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G74" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H74" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I74" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="J74" t="s">
         <v>327</v>
       </c>
       <c r="K74" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L74" t="s">
         <v>278</v>
@@ -6561,28 +6561,28 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>330</v>
       </c>
       <c r="F75" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G75" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H75" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I75" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="J75" t="s">
         <v>331</v>
       </c>
       <c r="K75" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L75" t="s">
         <v>278</v>
@@ -6602,28 +6602,28 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>334</v>
       </c>
       <c r="F76" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G76" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H76" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I76" t="s">
-        <v>334</v>
+        <v>276</v>
       </c>
       <c r="J76" t="s">
         <v>335</v>
       </c>
       <c r="K76" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L76" t="s">
         <v>278</v>
@@ -6643,28 +6643,28 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>338</v>
       </c>
       <c r="F77" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G77" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H77" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I77" t="s">
-        <v>338</v>
+        <v>276</v>
       </c>
       <c r="J77" t="s">
         <v>339</v>
       </c>
       <c r="K77" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L77" t="s">
         <v>278</v>
@@ -6684,28 +6684,28 @@
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>342</v>
       </c>
       <c r="F78" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G78" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H78" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I78" t="s">
-        <v>342</v>
+        <v>276</v>
       </c>
       <c r="J78" t="s">
         <v>343</v>
       </c>
       <c r="K78" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L78" t="s">
         <v>278</v>
@@ -6725,28 +6725,28 @@
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>346</v>
       </c>
       <c r="F79" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G79" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H79" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I79" t="s">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="J79" t="s">
         <v>347</v>
       </c>
       <c r="K79" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L79" t="s">
         <v>278</v>
@@ -6766,28 +6766,28 @@
         <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>350</v>
       </c>
       <c r="F80" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G80" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H80" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I80" t="s">
-        <v>350</v>
+        <v>276</v>
       </c>
       <c r="J80" t="s">
         <v>351</v>
       </c>
       <c r="K80" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L80" t="s">
         <v>278</v>
@@ -6807,28 +6807,28 @@
         <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>354</v>
       </c>
       <c r="F81" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G81" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H81" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I81" t="s">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="J81" t="s">
         <v>355</v>
       </c>
       <c r="K81" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L81" t="s">
         <v>278</v>
@@ -6848,28 +6848,28 @@
         <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>358</v>
       </c>
       <c r="F82" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G82" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H82" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I82" t="s">
-        <v>358</v>
+        <v>276</v>
       </c>
       <c r="J82" t="s">
         <v>359</v>
       </c>
       <c r="K82" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L82" t="s">
         <v>278</v>
@@ -6889,28 +6889,28 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>362</v>
       </c>
       <c r="F83" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H83" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I83" t="s">
-        <v>362</v>
+        <v>276</v>
       </c>
       <c r="J83" t="s">
         <v>363</v>
       </c>
       <c r="K83" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L83" t="s">
         <v>278</v>
@@ -6930,28 +6930,28 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>366</v>
       </c>
       <c r="F84" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G84" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H84" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I84" t="s">
-        <v>366</v>
+        <v>276</v>
       </c>
       <c r="J84" t="s">
         <v>367</v>
       </c>
       <c r="K84" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L84" t="s">
         <v>278</v>
@@ -6971,28 +6971,28 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>370</v>
       </c>
       <c r="F85" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G85" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H85" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I85" t="s">
-        <v>370</v>
+        <v>276</v>
       </c>
       <c r="J85" t="s">
         <v>371</v>
       </c>
       <c r="K85" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L85" t="s">
         <v>278</v>
@@ -7012,28 +7012,28 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>374</v>
       </c>
       <c r="F86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G86" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H86" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I86" t="s">
-        <v>374</v>
+        <v>276</v>
       </c>
       <c r="J86" t="s">
         <v>375</v>
       </c>
       <c r="K86" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L86" t="s">
         <v>278</v>
@@ -7053,28 +7053,28 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="F87" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H87" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I87" t="s">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="J87" t="s">
         <v>379</v>
       </c>
       <c r="K87" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L87" t="s">
         <v>278</v>
@@ -7094,28 +7094,28 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="F88" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G88" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H88" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I88" t="s">
-        <v>382</v>
+        <v>276</v>
       </c>
       <c r="J88" t="s">
         <v>383</v>
       </c>
       <c r="K88" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L88" t="s">
         <v>278</v>
@@ -7135,28 +7135,28 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>386</v>
       </c>
       <c r="F89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G89" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H89" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I89" t="s">
-        <v>386</v>
+        <v>276</v>
       </c>
       <c r="J89" t="s">
         <v>387</v>
       </c>
       <c r="K89" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="L89" t="s">
         <v>278</v>
@@ -7176,31 +7176,31 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>390</v>
       </c>
       <c r="F90" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G90" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H90" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J90" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K90" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L90" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M90" t="s">
         <v>279</v>
@@ -7217,31 +7217,31 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>396</v>
       </c>
       <c r="F91" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G91" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H91" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I91" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J91" t="s">
         <v>397</v>
       </c>
       <c r="K91" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L91" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M91" t="s">
         <v>279</v>
@@ -7258,31 +7258,31 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>400</v>
       </c>
       <c r="F92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G92" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H92" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I92" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="J92" t="s">
         <v>401</v>
       </c>
       <c r="K92" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L92" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M92" t="s">
         <v>279</v>
@@ -7299,31 +7299,31 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>404</v>
       </c>
       <c r="F93" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G93" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H93" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I93" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="J93" t="s">
         <v>405</v>
       </c>
       <c r="K93" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L93" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M93" t="s">
         <v>279</v>
@@ -7340,31 +7340,31 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F94" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G94" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H94" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I94" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="J94" t="s">
         <v>409</v>
       </c>
       <c r="K94" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L94" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M94" t="s">
         <v>279</v>
@@ -7381,31 +7381,31 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>412</v>
       </c>
       <c r="F95" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G95" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H95" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I95" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="J95" t="s">
         <v>413</v>
       </c>
       <c r="K95" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L95" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M95" t="s">
         <v>279</v>
@@ -7422,31 +7422,31 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>416</v>
       </c>
       <c r="F96" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G96" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H96" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I96" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="J96" t="s">
         <v>417</v>
       </c>
       <c r="K96" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L96" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M96" t="s">
         <v>279</v>
@@ -7463,31 +7463,31 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>420</v>
       </c>
       <c r="F97" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G97" t="s">
-        <v>273</v>
+        <v>391</v>
       </c>
       <c r="H97" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I97" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="J97" t="s">
         <v>421</v>
       </c>
       <c r="K97" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="L97" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="M97" t="s">
         <v>279</v>
@@ -7504,31 +7504,31 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>424</v>
       </c>
       <c r="F98" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G98" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H98" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I98" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J98" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K98" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L98" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M98" t="s">
         <v>279</v>
@@ -7545,31 +7545,31 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>430</v>
       </c>
       <c r="F99" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G99" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H99" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I99" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J99" t="s">
         <v>431</v>
       </c>
       <c r="K99" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L99" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M99" t="s">
         <v>279</v>
@@ -7586,31 +7586,31 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>434</v>
       </c>
       <c r="F100" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G100" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H100" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I100" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="J100" t="s">
         <v>435</v>
       </c>
       <c r="K100" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L100" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M100" t="s">
         <v>279</v>
@@ -7627,31 +7627,31 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>438</v>
       </c>
       <c r="F101" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G101" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H101" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I101" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="J101" t="s">
         <v>439</v>
       </c>
       <c r="K101" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L101" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M101" t="s">
         <v>279</v>
@@ -7668,31 +7668,31 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="F102" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G102" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H102" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I102" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="J102" t="s">
         <v>443</v>
       </c>
       <c r="K102" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L102" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M102" t="s">
         <v>279</v>
@@ -7709,31 +7709,31 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>446</v>
       </c>
       <c r="F103" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G103" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H103" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I103" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="J103" t="s">
         <v>447</v>
       </c>
       <c r="K103" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L103" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M103" t="s">
         <v>279</v>
@@ -7750,31 +7750,31 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>450</v>
       </c>
       <c r="F104" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G104" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H104" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I104" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="J104" t="s">
         <v>451</v>
       </c>
       <c r="K104" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L104" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M104" t="s">
         <v>279</v>
@@ -7791,31 +7791,31 @@
         <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>454</v>
       </c>
       <c r="F105" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G105" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H105" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I105" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="J105" t="s">
         <v>455</v>
       </c>
       <c r="K105" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L105" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M105" t="s">
         <v>279</v>
@@ -7832,31 +7832,31 @@
         <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="F106" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G106" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H106" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I106" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="J106" t="s">
         <v>459</v>
       </c>
       <c r="K106" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L106" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M106" t="s">
         <v>279</v>
@@ -7873,31 +7873,31 @@
         <v>15</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>462</v>
       </c>
       <c r="F107" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G107" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H107" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I107" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="J107" t="s">
         <v>463</v>
       </c>
       <c r="K107" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L107" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M107" t="s">
         <v>279</v>
@@ -7914,31 +7914,31 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>466</v>
       </c>
       <c r="F108" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G108" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H108" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I108" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
       <c r="J108" t="s">
         <v>467</v>
       </c>
       <c r="K108" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L108" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M108" t="s">
         <v>279</v>
@@ -7955,31 +7955,31 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>470</v>
       </c>
       <c r="F109" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G109" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H109" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I109" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="J109" t="s">
         <v>471</v>
       </c>
       <c r="K109" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L109" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M109" t="s">
         <v>279</v>
@@ -7996,31 +7996,31 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>474</v>
       </c>
       <c r="F110" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G110" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H110" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I110" t="s">
-        <v>474</v>
+        <v>426</v>
       </c>
       <c r="J110" t="s">
         <v>475</v>
       </c>
       <c r="K110" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L110" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M110" t="s">
         <v>279</v>
@@ -8037,31 +8037,31 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>478</v>
       </c>
       <c r="F111" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G111" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H111" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I111" t="s">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="J111" t="s">
         <v>479</v>
       </c>
       <c r="K111" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L111" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M111" t="s">
         <v>279</v>
@@ -8078,31 +8078,31 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>482</v>
       </c>
       <c r="F112" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H112" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I112" t="s">
-        <v>482</v>
+        <v>426</v>
       </c>
       <c r="J112" t="s">
         <v>483</v>
       </c>
       <c r="K112" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L112" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M112" t="s">
         <v>279</v>
@@ -8119,31 +8119,31 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>486</v>
       </c>
       <c r="F113" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G113" t="s">
-        <v>273</v>
+        <v>425</v>
       </c>
       <c r="H113" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="I113" t="s">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="J113" t="s">
         <v>487</v>
       </c>
       <c r="K113" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="L113" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="M113" t="s">
         <v>279</v>
@@ -8160,24 +8160,24 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>490</v>
       </c>
       <c r="F114" t="s">
-        <v>490</v>
-      </c>
-      <c r="G114" t="s">
         <v>491</v>
       </c>
       <c r="H114" t="s">
-        <v>274</v>
-      </c>
-      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+      <c r="J114" t="s">
         <v>492</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
+        <v>21</v>
+      </c>
+      <c r="L114" t="s">
         <v>493</v>
       </c>
       <c r="M114" t="s">
@@ -8195,25 +8195,25 @@
         <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>496</v>
       </c>
       <c r="F115" t="s">
-        <v>490</v>
-      </c>
-      <c r="G115" t="s">
         <v>491</v>
       </c>
       <c r="H115" t="s">
-        <v>274</v>
-      </c>
-      <c r="I115" t="s">
-        <v>496</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s">
         <v>497</v>
+      </c>
+      <c r="K115" t="s">
+        <v>21</v>
+      </c>
+      <c r="L115" t="s">
+        <v>493</v>
       </c>
       <c r="M115" t="s">
         <v>279</v>
@@ -8230,25 +8230,25 @@
         <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="F116" t="s">
-        <v>490</v>
-      </c>
-      <c r="G116" t="s">
         <v>491</v>
       </c>
       <c r="H116" t="s">
-        <v>274</v>
-      </c>
-      <c r="I116" t="s">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="J116" t="s">
         <v>501</v>
+      </c>
+      <c r="K116" t="s">
+        <v>21</v>
+      </c>
+      <c r="L116" t="s">
+        <v>493</v>
       </c>
       <c r="M116" t="s">
         <v>279</v>
@@ -8265,25 +8265,25 @@
         <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>504</v>
       </c>
       <c r="F117" t="s">
-        <v>490</v>
-      </c>
-      <c r="G117" t="s">
         <v>491</v>
       </c>
       <c r="H117" t="s">
-        <v>274</v>
-      </c>
-      <c r="I117" t="s">
-        <v>504</v>
+        <v>19</v>
       </c>
       <c r="J117" t="s">
         <v>505</v>
+      </c>
+      <c r="K117" t="s">
+        <v>21</v>
+      </c>
+      <c r="L117" t="s">
+        <v>493</v>
       </c>
       <c r="M117" t="s">
         <v>279</v>
@@ -8300,25 +8300,25 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>508</v>
       </c>
       <c r="F118" t="s">
-        <v>490</v>
-      </c>
-      <c r="G118" t="s">
         <v>491</v>
       </c>
       <c r="H118" t="s">
-        <v>274</v>
-      </c>
-      <c r="I118" t="s">
-        <v>508</v>
+        <v>19</v>
       </c>
       <c r="J118" t="s">
         <v>509</v>
+      </c>
+      <c r="K118" t="s">
+        <v>21</v>
+      </c>
+      <c r="L118" t="s">
+        <v>493</v>
       </c>
       <c r="M118" t="s">
         <v>279</v>
@@ -8334,17 +8334,17 @@
       <c r="C119" t="s">
         <v>15</v>
       </c>
-      <c r="D119" t="s">
-        <v>16</v>
-      </c>
       <c r="E119" t="s">
-        <v>17</v>
-      </c>
-      <c r="I119" t="s">
         <v>512</v>
+      </c>
+      <c r="H119" t="s">
+        <v>19</v>
       </c>
       <c r="J119" t="s">
         <v>513</v>
+      </c>
+      <c r="K119" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -8358,24 +8358,24 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="F120" t="s">
-        <v>516</v>
-      </c>
-      <c r="G120" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H120" t="s">
-        <v>518</v>
-      </c>
-      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" t="s">
         <v>519</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
+        <v>21</v>
+      </c>
+      <c r="L120" t="s">
         <v>520</v>
       </c>
       <c r="M120" t="s">
@@ -8393,25 +8393,25 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>524</v>
       </c>
       <c r="F121" t="s">
-        <v>516</v>
-      </c>
-      <c r="G121" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H121" t="s">
-        <v>518</v>
-      </c>
-      <c r="I121" t="s">
-        <v>524</v>
+        <v>19</v>
       </c>
       <c r="J121" t="s">
         <v>525</v>
+      </c>
+      <c r="K121" t="s">
+        <v>21</v>
+      </c>
+      <c r="L121" t="s">
+        <v>520</v>
       </c>
       <c r="M121" t="s">
         <v>521</v>
@@ -8428,25 +8428,25 @@
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>528</v>
       </c>
       <c r="F122" t="s">
-        <v>516</v>
-      </c>
-      <c r="G122" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H122" t="s">
-        <v>518</v>
-      </c>
-      <c r="I122" t="s">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="J122" t="s">
         <v>529</v>
+      </c>
+      <c r="K122" t="s">
+        <v>21</v>
+      </c>
+      <c r="L122" t="s">
+        <v>520</v>
       </c>
       <c r="M122" t="s">
         <v>521</v>
@@ -8463,25 +8463,25 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>532</v>
       </c>
       <c r="F123" t="s">
-        <v>516</v>
-      </c>
-      <c r="G123" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H123" t="s">
-        <v>518</v>
-      </c>
-      <c r="I123" t="s">
-        <v>532</v>
+        <v>19</v>
       </c>
       <c r="J123" t="s">
         <v>533</v>
+      </c>
+      <c r="K123" t="s">
+        <v>21</v>
+      </c>
+      <c r="L123" t="s">
+        <v>520</v>
       </c>
       <c r="M123" t="s">
         <v>521</v>
@@ -8498,25 +8498,25 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>536</v>
       </c>
       <c r="F124" t="s">
-        <v>516</v>
-      </c>
-      <c r="G124" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H124" t="s">
-        <v>518</v>
-      </c>
-      <c r="I124" t="s">
-        <v>536</v>
+        <v>19</v>
       </c>
       <c r="J124" t="s">
         <v>537</v>
+      </c>
+      <c r="K124" t="s">
+        <v>21</v>
+      </c>
+      <c r="L124" t="s">
+        <v>520</v>
       </c>
       <c r="M124" t="s">
         <v>521</v>
@@ -8533,24 +8533,24 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>540</v>
       </c>
       <c r="F125" t="s">
-        <v>540</v>
-      </c>
-      <c r="G125" t="s">
         <v>541</v>
       </c>
       <c r="H125" t="s">
-        <v>518</v>
-      </c>
-      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+      <c r="J125" t="s">
         <v>542</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
+        <v>21</v>
+      </c>
+      <c r="L125" t="s">
         <v>543</v>
       </c>
       <c r="M125" t="s">
@@ -8568,25 +8568,25 @@
         <v>15</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>546</v>
       </c>
       <c r="F126" t="s">
-        <v>540</v>
-      </c>
-      <c r="G126" t="s">
         <v>541</v>
       </c>
       <c r="H126" t="s">
-        <v>518</v>
-      </c>
-      <c r="I126" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="J126" t="s">
         <v>547</v>
+      </c>
+      <c r="K126" t="s">
+        <v>21</v>
+      </c>
+      <c r="L126" t="s">
+        <v>543</v>
       </c>
       <c r="M126" t="s">
         <v>521</v>
@@ -8603,25 +8603,25 @@
         <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E127" t="s">
-        <v>17</v>
+        <v>550</v>
       </c>
       <c r="F127" t="s">
-        <v>540</v>
-      </c>
-      <c r="G127" t="s">
         <v>541</v>
       </c>
       <c r="H127" t="s">
-        <v>518</v>
-      </c>
-      <c r="I127" t="s">
-        <v>550</v>
+        <v>19</v>
       </c>
       <c r="J127" t="s">
         <v>551</v>
+      </c>
+      <c r="K127" t="s">
+        <v>21</v>
+      </c>
+      <c r="L127" t="s">
+        <v>543</v>
       </c>
       <c r="M127" t="s">
         <v>521</v>
@@ -8638,25 +8638,25 @@
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E128" t="s">
-        <v>17</v>
+        <v>554</v>
       </c>
       <c r="F128" t="s">
-        <v>540</v>
-      </c>
-      <c r="G128" t="s">
         <v>541</v>
       </c>
       <c r="H128" t="s">
-        <v>518</v>
-      </c>
-      <c r="I128" t="s">
-        <v>554</v>
+        <v>19</v>
       </c>
       <c r="J128" t="s">
         <v>555</v>
+      </c>
+      <c r="K128" t="s">
+        <v>21</v>
+      </c>
+      <c r="L128" t="s">
+        <v>543</v>
       </c>
       <c r="M128" t="s">
         <v>521</v>
@@ -8673,25 +8673,25 @@
         <v>15</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E129" t="s">
-        <v>17</v>
+        <v>558</v>
       </c>
       <c r="F129" t="s">
-        <v>540</v>
-      </c>
-      <c r="G129" t="s">
         <v>541</v>
       </c>
       <c r="H129" t="s">
-        <v>518</v>
-      </c>
-      <c r="I129" t="s">
-        <v>558</v>
+        <v>19</v>
       </c>
       <c r="J129" t="s">
         <v>559</v>
+      </c>
+      <c r="K129" t="s">
+        <v>21</v>
+      </c>
+      <c r="L129" t="s">
+        <v>543</v>
       </c>
       <c r="M129" t="s">
         <v>521</v>
@@ -8708,25 +8708,25 @@
         <v>15</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>562</v>
       </c>
       <c r="F130" t="s">
-        <v>540</v>
-      </c>
-      <c r="G130" t="s">
         <v>541</v>
       </c>
       <c r="H130" t="s">
-        <v>518</v>
-      </c>
-      <c r="I130" t="s">
-        <v>562</v>
+        <v>19</v>
       </c>
       <c r="J130" t="s">
         <v>563</v>
+      </c>
+      <c r="K130" t="s">
+        <v>21</v>
+      </c>
+      <c r="L130" t="s">
+        <v>543</v>
       </c>
       <c r="M130" t="s">
         <v>521</v>
@@ -8743,25 +8743,25 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>566</v>
       </c>
       <c r="F131" t="s">
-        <v>540</v>
-      </c>
-      <c r="G131" t="s">
         <v>541</v>
       </c>
       <c r="H131" t="s">
-        <v>518</v>
-      </c>
-      <c r="I131" t="s">
-        <v>566</v>
+        <v>19</v>
       </c>
       <c r="J131" t="s">
         <v>567</v>
+      </c>
+      <c r="K131" t="s">
+        <v>21</v>
+      </c>
+      <c r="L131" t="s">
+        <v>543</v>
       </c>
       <c r="M131" t="s">
         <v>521</v>
@@ -8778,24 +8778,24 @@
         <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E132" t="s">
-        <v>17</v>
+        <v>570</v>
       </c>
       <c r="F132" t="s">
-        <v>570</v>
-      </c>
-      <c r="G132" t="s">
         <v>571</v>
       </c>
       <c r="H132" t="s">
-        <v>518</v>
-      </c>
-      <c r="I132" t="s">
+        <v>19</v>
+      </c>
+      <c r="J132" t="s">
         <v>572</v>
       </c>
-      <c r="J132" t="s">
+      <c r="K132" t="s">
+        <v>21</v>
+      </c>
+      <c r="L132" t="s">
         <v>573</v>
       </c>
       <c r="M132" t="s">
@@ -8813,25 +8813,25 @@
         <v>15</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E133" t="s">
-        <v>17</v>
+        <v>576</v>
       </c>
       <c r="F133" t="s">
-        <v>570</v>
-      </c>
-      <c r="G133" t="s">
         <v>571</v>
       </c>
       <c r="H133" t="s">
-        <v>518</v>
-      </c>
-      <c r="I133" t="s">
-        <v>576</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s">
         <v>577</v>
+      </c>
+      <c r="K133" t="s">
+        <v>21</v>
+      </c>
+      <c r="L133" t="s">
+        <v>573</v>
       </c>
       <c r="M133" t="s">
         <v>521</v>
@@ -8848,25 +8848,25 @@
         <v>15</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>580</v>
       </c>
       <c r="F134" t="s">
-        <v>570</v>
-      </c>
-      <c r="G134" t="s">
         <v>571</v>
       </c>
       <c r="H134" t="s">
-        <v>518</v>
-      </c>
-      <c r="I134" t="s">
-        <v>580</v>
+        <v>19</v>
       </c>
       <c r="J134" t="s">
         <v>581</v>
+      </c>
+      <c r="K134" t="s">
+        <v>21</v>
+      </c>
+      <c r="L134" t="s">
+        <v>573</v>
       </c>
       <c r="M134" t="s">
         <v>521</v>
@@ -8883,25 +8883,25 @@
         <v>15</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>584</v>
       </c>
       <c r="F135" t="s">
-        <v>570</v>
-      </c>
-      <c r="G135" t="s">
         <v>571</v>
       </c>
       <c r="H135" t="s">
-        <v>518</v>
-      </c>
-      <c r="I135" t="s">
-        <v>584</v>
+        <v>19</v>
       </c>
       <c r="J135" t="s">
         <v>585</v>
+      </c>
+      <c r="K135" t="s">
+        <v>21</v>
+      </c>
+      <c r="L135" t="s">
+        <v>573</v>
       </c>
       <c r="M135" t="s">
         <v>521</v>
@@ -8918,25 +8918,25 @@
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E136" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="F136" t="s">
-        <v>570</v>
-      </c>
-      <c r="G136" t="s">
         <v>571</v>
       </c>
       <c r="H136" t="s">
-        <v>518</v>
-      </c>
-      <c r="I136" t="s">
-        <v>588</v>
+        <v>19</v>
       </c>
       <c r="J136" t="s">
         <v>589</v>
+      </c>
+      <c r="K136" t="s">
+        <v>21</v>
+      </c>
+      <c r="L136" t="s">
+        <v>573</v>
       </c>
       <c r="M136" t="s">
         <v>521</v>
@@ -8953,25 +8953,25 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E137" t="s">
-        <v>17</v>
+        <v>592</v>
       </c>
       <c r="F137" t="s">
-        <v>570</v>
-      </c>
-      <c r="G137" t="s">
         <v>571</v>
       </c>
       <c r="H137" t="s">
-        <v>518</v>
-      </c>
-      <c r="I137" t="s">
-        <v>592</v>
+        <v>19</v>
       </c>
       <c r="J137" t="s">
         <v>593</v>
+      </c>
+      <c r="K137" t="s">
+        <v>21</v>
+      </c>
+      <c r="L137" t="s">
+        <v>573</v>
       </c>
       <c r="M137" t="s">
         <v>521</v>
@@ -8988,25 +8988,25 @@
         <v>15</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E138" t="s">
-        <v>17</v>
+        <v>596</v>
       </c>
       <c r="F138" t="s">
-        <v>570</v>
-      </c>
-      <c r="G138" t="s">
         <v>571</v>
       </c>
       <c r="H138" t="s">
-        <v>518</v>
-      </c>
-      <c r="I138" t="s">
-        <v>596</v>
+        <v>19</v>
       </c>
       <c r="J138" t="s">
         <v>597</v>
+      </c>
+      <c r="K138" t="s">
+        <v>21</v>
+      </c>
+      <c r="L138" t="s">
+        <v>573</v>
       </c>
       <c r="M138" t="s">
         <v>521</v>
@@ -9023,25 +9023,25 @@
         <v>15</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>600</v>
       </c>
       <c r="F139" t="s">
-        <v>570</v>
-      </c>
-      <c r="G139" t="s">
         <v>571</v>
       </c>
       <c r="H139" t="s">
-        <v>518</v>
-      </c>
-      <c r="I139" t="s">
-        <v>600</v>
+        <v>19</v>
       </c>
       <c r="J139" t="s">
         <v>601</v>
+      </c>
+      <c r="K139" t="s">
+        <v>21</v>
+      </c>
+      <c r="L139" t="s">
+        <v>573</v>
       </c>
       <c r="M139" t="s">
         <v>521</v>
@@ -9058,25 +9058,25 @@
         <v>15</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>604</v>
       </c>
       <c r="F140" t="s">
-        <v>570</v>
-      </c>
-      <c r="G140" t="s">
         <v>571</v>
       </c>
       <c r="H140" t="s">
-        <v>518</v>
-      </c>
-      <c r="I140" t="s">
-        <v>604</v>
+        <v>19</v>
       </c>
       <c r="J140" t="s">
         <v>605</v>
+      </c>
+      <c r="K140" t="s">
+        <v>21</v>
+      </c>
+      <c r="L140" t="s">
+        <v>573</v>
       </c>
       <c r="M140" t="s">
         <v>521</v>
@@ -9093,25 +9093,25 @@
         <v>15</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>608</v>
       </c>
       <c r="F141" t="s">
-        <v>570</v>
-      </c>
-      <c r="G141" t="s">
         <v>571</v>
       </c>
       <c r="H141" t="s">
-        <v>518</v>
-      </c>
-      <c r="I141" t="s">
-        <v>608</v>
+        <v>19</v>
       </c>
       <c r="J141" t="s">
         <v>609</v>
+      </c>
+      <c r="K141" t="s">
+        <v>21</v>
+      </c>
+      <c r="L141" t="s">
+        <v>573</v>
       </c>
       <c r="M141" t="s">
         <v>521</v>
@@ -9128,25 +9128,25 @@
         <v>15</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>612</v>
       </c>
       <c r="F142" t="s">
-        <v>570</v>
-      </c>
-      <c r="G142" t="s">
         <v>571</v>
       </c>
       <c r="H142" t="s">
-        <v>518</v>
-      </c>
-      <c r="I142" t="s">
-        <v>612</v>
+        <v>19</v>
       </c>
       <c r="J142" t="s">
         <v>613</v>
+      </c>
+      <c r="K142" t="s">
+        <v>21</v>
+      </c>
+      <c r="L142" t="s">
+        <v>573</v>
       </c>
       <c r="M142" t="s">
         <v>521</v>
@@ -9163,24 +9163,24 @@
         <v>15</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E143" t="s">
-        <v>17</v>
+        <v>616</v>
       </c>
       <c r="F143" t="s">
-        <v>616</v>
-      </c>
-      <c r="G143" t="s">
         <v>617</v>
       </c>
       <c r="H143" t="s">
-        <v>518</v>
-      </c>
-      <c r="I143" t="s">
+        <v>19</v>
+      </c>
+      <c r="J143" t="s">
         <v>618</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
+        <v>21</v>
+      </c>
+      <c r="L143" t="s">
         <v>619</v>
       </c>
       <c r="M143" t="s">
@@ -9198,25 +9198,25 @@
         <v>15</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E144" t="s">
-        <v>17</v>
+        <v>622</v>
       </c>
       <c r="F144" t="s">
-        <v>616</v>
-      </c>
-      <c r="G144" t="s">
         <v>617</v>
       </c>
       <c r="H144" t="s">
-        <v>518</v>
-      </c>
-      <c r="I144" t="s">
-        <v>622</v>
+        <v>19</v>
       </c>
       <c r="J144" t="s">
         <v>623</v>
+      </c>
+      <c r="K144" t="s">
+        <v>21</v>
+      </c>
+      <c r="L144" t="s">
+        <v>619</v>
       </c>
       <c r="M144" t="s">
         <v>521</v>
@@ -9233,25 +9233,25 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>626</v>
       </c>
       <c r="F145" t="s">
-        <v>616</v>
-      </c>
-      <c r="G145" t="s">
         <v>617</v>
       </c>
       <c r="H145" t="s">
-        <v>518</v>
-      </c>
-      <c r="I145" t="s">
-        <v>626</v>
+        <v>19</v>
       </c>
       <c r="J145" t="s">
         <v>627</v>
+      </c>
+      <c r="K145" t="s">
+        <v>21</v>
+      </c>
+      <c r="L145" t="s">
+        <v>619</v>
       </c>
       <c r="M145" t="s">
         <v>521</v>
@@ -9268,25 +9268,25 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E146" t="s">
-        <v>17</v>
+        <v>630</v>
       </c>
       <c r="F146" t="s">
-        <v>616</v>
-      </c>
-      <c r="G146" t="s">
         <v>617</v>
       </c>
       <c r="H146" t="s">
-        <v>518</v>
-      </c>
-      <c r="I146" t="s">
-        <v>630</v>
+        <v>19</v>
       </c>
       <c r="J146" t="s">
         <v>631</v>
+      </c>
+      <c r="K146" t="s">
+        <v>21</v>
+      </c>
+      <c r="L146" t="s">
+        <v>619</v>
       </c>
       <c r="M146" t="s">
         <v>521</v>
@@ -9303,25 +9303,25 @@
         <v>15</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>634</v>
       </c>
       <c r="F147" t="s">
-        <v>616</v>
-      </c>
-      <c r="G147" t="s">
         <v>617</v>
       </c>
       <c r="H147" t="s">
-        <v>518</v>
-      </c>
-      <c r="I147" t="s">
-        <v>634</v>
+        <v>19</v>
       </c>
       <c r="J147" t="s">
         <v>635</v>
+      </c>
+      <c r="K147" t="s">
+        <v>21</v>
+      </c>
+      <c r="L147" t="s">
+        <v>619</v>
       </c>
       <c r="M147" t="s">
         <v>521</v>
@@ -9338,25 +9338,25 @@
         <v>15</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E148" t="s">
-        <v>17</v>
+        <v>638</v>
       </c>
       <c r="F148" t="s">
-        <v>616</v>
-      </c>
-      <c r="G148" t="s">
         <v>617</v>
       </c>
       <c r="H148" t="s">
-        <v>518</v>
-      </c>
-      <c r="I148" t="s">
-        <v>638</v>
+        <v>19</v>
       </c>
       <c r="J148" t="s">
         <v>639</v>
+      </c>
+      <c r="K148" t="s">
+        <v>21</v>
+      </c>
+      <c r="L148" t="s">
+        <v>619</v>
       </c>
       <c r="M148" t="s">
         <v>521</v>
@@ -9373,25 +9373,25 @@
         <v>15</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E149" t="s">
-        <v>17</v>
+        <v>642</v>
       </c>
       <c r="F149" t="s">
-        <v>616</v>
-      </c>
-      <c r="G149" t="s">
         <v>617</v>
       </c>
       <c r="H149" t="s">
-        <v>518</v>
-      </c>
-      <c r="I149" t="s">
-        <v>642</v>
+        <v>19</v>
       </c>
       <c r="J149" t="s">
         <v>643</v>
+      </c>
+      <c r="K149" t="s">
+        <v>21</v>
+      </c>
+      <c r="L149" t="s">
+        <v>619</v>
       </c>
       <c r="M149" t="s">
         <v>521</v>
@@ -9408,25 +9408,25 @@
         <v>15</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E150" t="s">
-        <v>17</v>
+        <v>646</v>
       </c>
       <c r="F150" t="s">
-        <v>616</v>
-      </c>
-      <c r="G150" t="s">
         <v>617</v>
       </c>
       <c r="H150" t="s">
-        <v>518</v>
-      </c>
-      <c r="I150" t="s">
-        <v>646</v>
+        <v>19</v>
       </c>
       <c r="J150" t="s">
         <v>647</v>
+      </c>
+      <c r="K150" t="s">
+        <v>21</v>
+      </c>
+      <c r="L150" t="s">
+        <v>619</v>
       </c>
       <c r="M150" t="s">
         <v>521</v>
@@ -9443,25 +9443,25 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E151" t="s">
-        <v>17</v>
+        <v>650</v>
       </c>
       <c r="F151" t="s">
-        <v>616</v>
-      </c>
-      <c r="G151" t="s">
         <v>617</v>
       </c>
       <c r="H151" t="s">
-        <v>518</v>
-      </c>
-      <c r="I151" t="s">
-        <v>650</v>
+        <v>19</v>
       </c>
       <c r="J151" t="s">
         <v>651</v>
+      </c>
+      <c r="K151" t="s">
+        <v>21</v>
+      </c>
+      <c r="L151" t="s">
+        <v>619</v>
       </c>
       <c r="M151" t="s">
         <v>521</v>
@@ -9478,24 +9478,24 @@
         <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E152" t="s">
-        <v>17</v>
+        <v>654</v>
       </c>
       <c r="F152" t="s">
-        <v>654</v>
-      </c>
-      <c r="G152" t="s">
         <v>655</v>
       </c>
       <c r="H152" t="s">
-        <v>518</v>
-      </c>
-      <c r="I152" t="s">
+        <v>19</v>
+      </c>
+      <c r="J152" t="s">
         <v>656</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
+        <v>21</v>
+      </c>
+      <c r="L152" t="s">
         <v>657</v>
       </c>
       <c r="M152" t="s">
@@ -9513,25 +9513,25 @@
         <v>15</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E153" t="s">
-        <v>17</v>
+        <v>660</v>
       </c>
       <c r="F153" t="s">
-        <v>654</v>
-      </c>
-      <c r="G153" t="s">
         <v>655</v>
       </c>
       <c r="H153" t="s">
-        <v>518</v>
-      </c>
-      <c r="I153" t="s">
-        <v>660</v>
+        <v>19</v>
       </c>
       <c r="J153" t="s">
         <v>661</v>
+      </c>
+      <c r="K153" t="s">
+        <v>21</v>
+      </c>
+      <c r="L153" t="s">
+        <v>657</v>
       </c>
       <c r="M153" t="s">
         <v>521</v>
@@ -9548,25 +9548,25 @@
         <v>15</v>
       </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>664</v>
       </c>
       <c r="F154" t="s">
-        <v>654</v>
-      </c>
-      <c r="G154" t="s">
         <v>655</v>
       </c>
       <c r="H154" t="s">
-        <v>518</v>
-      </c>
-      <c r="I154" t="s">
-        <v>664</v>
+        <v>19</v>
       </c>
       <c r="J154" t="s">
         <v>665</v>
+      </c>
+      <c r="K154" t="s">
+        <v>21</v>
+      </c>
+      <c r="L154" t="s">
+        <v>657</v>
       </c>
       <c r="M154" t="s">
         <v>521</v>
@@ -9583,25 +9583,25 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>668</v>
       </c>
       <c r="F155" t="s">
-        <v>654</v>
-      </c>
-      <c r="G155" t="s">
         <v>655</v>
       </c>
       <c r="H155" t="s">
-        <v>518</v>
-      </c>
-      <c r="I155" t="s">
-        <v>668</v>
+        <v>19</v>
       </c>
       <c r="J155" t="s">
         <v>669</v>
+      </c>
+      <c r="K155" t="s">
+        <v>21</v>
+      </c>
+      <c r="L155" t="s">
+        <v>657</v>
       </c>
       <c r="M155" t="s">
         <v>521</v>
@@ -9618,25 +9618,25 @@
         <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E156" t="s">
-        <v>17</v>
+        <v>672</v>
       </c>
       <c r="F156" t="s">
-        <v>654</v>
-      </c>
-      <c r="G156" t="s">
         <v>655</v>
       </c>
       <c r="H156" t="s">
-        <v>518</v>
-      </c>
-      <c r="I156" t="s">
-        <v>672</v>
+        <v>19</v>
       </c>
       <c r="J156" t="s">
         <v>673</v>
+      </c>
+      <c r="K156" t="s">
+        <v>21</v>
+      </c>
+      <c r="L156" t="s">
+        <v>657</v>
       </c>
       <c r="M156" t="s">
         <v>521</v>
@@ -9653,25 +9653,25 @@
         <v>15</v>
       </c>
       <c r="D157" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>676</v>
       </c>
       <c r="F157" t="s">
-        <v>654</v>
-      </c>
-      <c r="G157" t="s">
         <v>655</v>
       </c>
       <c r="H157" t="s">
-        <v>518</v>
-      </c>
-      <c r="I157" t="s">
-        <v>676</v>
+        <v>19</v>
       </c>
       <c r="J157" t="s">
         <v>677</v>
+      </c>
+      <c r="K157" t="s">
+        <v>21</v>
+      </c>
+      <c r="L157" t="s">
+        <v>657</v>
       </c>
       <c r="M157" t="s">
         <v>521</v>
@@ -9688,25 +9688,25 @@
         <v>15</v>
       </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>680</v>
       </c>
       <c r="F158" t="s">
-        <v>654</v>
-      </c>
-      <c r="G158" t="s">
         <v>655</v>
       </c>
       <c r="H158" t="s">
-        <v>518</v>
-      </c>
-      <c r="I158" t="s">
-        <v>680</v>
+        <v>19</v>
       </c>
       <c r="J158" t="s">
         <v>681</v>
+      </c>
+      <c r="K158" t="s">
+        <v>21</v>
+      </c>
+      <c r="L158" t="s">
+        <v>657</v>
       </c>
       <c r="M158" t="s">
         <v>521</v>
@@ -9723,25 +9723,25 @@
         <v>15</v>
       </c>
       <c r="D159" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>684</v>
       </c>
       <c r="F159" t="s">
-        <v>654</v>
-      </c>
-      <c r="G159" t="s">
         <v>655</v>
       </c>
       <c r="H159" t="s">
-        <v>518</v>
-      </c>
-      <c r="I159" t="s">
-        <v>684</v>
+        <v>19</v>
       </c>
       <c r="J159" t="s">
         <v>685</v>
+      </c>
+      <c r="K159" t="s">
+        <v>21</v>
+      </c>
+      <c r="L159" t="s">
+        <v>657</v>
       </c>
       <c r="M159" t="s">
         <v>521</v>
@@ -9758,25 +9758,25 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>688</v>
       </c>
       <c r="F160" t="s">
-        <v>654</v>
-      </c>
-      <c r="G160" t="s">
         <v>655</v>
       </c>
       <c r="H160" t="s">
-        <v>518</v>
-      </c>
-      <c r="I160" t="s">
-        <v>688</v>
+        <v>19</v>
       </c>
       <c r="J160" t="s">
         <v>689</v>
+      </c>
+      <c r="K160" t="s">
+        <v>21</v>
+      </c>
+      <c r="L160" t="s">
+        <v>657</v>
       </c>
       <c r="M160" t="s">
         <v>521</v>
@@ -9793,25 +9793,25 @@
         <v>15</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>692</v>
       </c>
       <c r="F161" t="s">
-        <v>654</v>
-      </c>
-      <c r="G161" t="s">
         <v>655</v>
       </c>
       <c r="H161" t="s">
-        <v>518</v>
-      </c>
-      <c r="I161" t="s">
-        <v>692</v>
+        <v>19</v>
       </c>
       <c r="J161" t="s">
         <v>693</v>
+      </c>
+      <c r="K161" t="s">
+        <v>21</v>
+      </c>
+      <c r="L161" t="s">
+        <v>657</v>
       </c>
       <c r="M161" t="s">
         <v>521</v>
@@ -9828,25 +9828,25 @@
         <v>15</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>696</v>
       </c>
       <c r="F162" t="s">
-        <v>654</v>
-      </c>
-      <c r="G162" t="s">
         <v>655</v>
       </c>
       <c r="H162" t="s">
-        <v>518</v>
-      </c>
-      <c r="I162" t="s">
-        <v>696</v>
+        <v>19</v>
       </c>
       <c r="J162" t="s">
         <v>697</v>
+      </c>
+      <c r="K162" t="s">
+        <v>21</v>
+      </c>
+      <c r="L162" t="s">
+        <v>657</v>
       </c>
       <c r="M162" t="s">
         <v>521</v>
@@ -9863,25 +9863,25 @@
         <v>15</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>700</v>
       </c>
       <c r="F163" t="s">
-        <v>654</v>
-      </c>
-      <c r="G163" t="s">
         <v>655</v>
       </c>
       <c r="H163" t="s">
-        <v>518</v>
-      </c>
-      <c r="I163" t="s">
-        <v>700</v>
+        <v>19</v>
       </c>
       <c r="J163" t="s">
         <v>701</v>
+      </c>
+      <c r="K163" t="s">
+        <v>21</v>
+      </c>
+      <c r="L163" t="s">
+        <v>657</v>
       </c>
       <c r="M163" t="s">
         <v>521</v>
@@ -9898,25 +9898,25 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>704</v>
       </c>
       <c r="F164" t="s">
-        <v>654</v>
-      </c>
-      <c r="G164" t="s">
         <v>655</v>
       </c>
       <c r="H164" t="s">
-        <v>518</v>
-      </c>
-      <c r="I164" t="s">
-        <v>704</v>
+        <v>19</v>
       </c>
       <c r="J164" t="s">
         <v>705</v>
+      </c>
+      <c r="K164" t="s">
+        <v>21</v>
+      </c>
+      <c r="L164" t="s">
+        <v>657</v>
       </c>
       <c r="M164" t="s">
         <v>521</v>
@@ -9933,25 +9933,25 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>708</v>
       </c>
       <c r="F165" t="s">
-        <v>654</v>
-      </c>
-      <c r="G165" t="s">
         <v>655</v>
       </c>
       <c r="H165" t="s">
-        <v>518</v>
-      </c>
-      <c r="I165" t="s">
-        <v>708</v>
+        <v>19</v>
       </c>
       <c r="J165" t="s">
         <v>709</v>
+      </c>
+      <c r="K165" t="s">
+        <v>21</v>
+      </c>
+      <c r="L165" t="s">
+        <v>657</v>
       </c>
       <c r="M165" t="s">
         <v>521</v>
@@ -9968,25 +9968,25 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>712</v>
       </c>
       <c r="F166" t="s">
-        <v>654</v>
-      </c>
-      <c r="G166" t="s">
         <v>655</v>
       </c>
       <c r="H166" t="s">
-        <v>518</v>
-      </c>
-      <c r="I166" t="s">
-        <v>712</v>
+        <v>19</v>
       </c>
       <c r="J166" t="s">
         <v>713</v>
+      </c>
+      <c r="K166" t="s">
+        <v>21</v>
+      </c>
+      <c r="L166" t="s">
+        <v>657</v>
       </c>
       <c r="M166" t="s">
         <v>521</v>
@@ -10003,25 +10003,25 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E167" t="s">
-        <v>17</v>
+        <v>716</v>
       </c>
       <c r="F167" t="s">
-        <v>654</v>
-      </c>
-      <c r="G167" t="s">
         <v>655</v>
       </c>
       <c r="H167" t="s">
-        <v>518</v>
-      </c>
-      <c r="I167" t="s">
-        <v>716</v>
+        <v>19</v>
       </c>
       <c r="J167" t="s">
         <v>717</v>
+      </c>
+      <c r="K167" t="s">
+        <v>21</v>
+      </c>
+      <c r="L167" t="s">
+        <v>657</v>
       </c>
       <c r="M167" t="s">
         <v>521</v>
@@ -10038,25 +10038,25 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E168" t="s">
-        <v>17</v>
+        <v>720</v>
       </c>
       <c r="F168" t="s">
-        <v>654</v>
-      </c>
-      <c r="G168" t="s">
         <v>655</v>
       </c>
       <c r="H168" t="s">
-        <v>518</v>
-      </c>
-      <c r="I168" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="J168" t="s">
         <v>721</v>
+      </c>
+      <c r="K168" t="s">
+        <v>21</v>
+      </c>
+      <c r="L168" t="s">
+        <v>657</v>
       </c>
       <c r="M168" t="s">
         <v>521</v>
@@ -10073,25 +10073,25 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E169" t="s">
-        <v>17</v>
+        <v>724</v>
       </c>
       <c r="F169" t="s">
-        <v>654</v>
-      </c>
-      <c r="G169" t="s">
         <v>655</v>
       </c>
       <c r="H169" t="s">
-        <v>518</v>
-      </c>
-      <c r="I169" t="s">
-        <v>724</v>
+        <v>19</v>
       </c>
       <c r="J169" t="s">
         <v>725</v>
+      </c>
+      <c r="K169" t="s">
+        <v>21</v>
+      </c>
+      <c r="L169" t="s">
+        <v>657</v>
       </c>
       <c r="M169" t="s">
         <v>521</v>
@@ -10108,24 +10108,24 @@
         <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F170" t="s">
-        <v>728</v>
-      </c>
-      <c r="G170" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H170" t="s">
-        <v>730</v>
-      </c>
-      <c r="I170" t="s">
+        <v>19</v>
+      </c>
+      <c r="J170" t="s">
         <v>731</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
+        <v>21</v>
+      </c>
+      <c r="L170" t="s">
         <v>732</v>
       </c>
       <c r="M170" t="s">
@@ -10143,25 +10143,25 @@
         <v>15</v>
       </c>
       <c r="D171" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E171" t="s">
-        <v>17</v>
+        <v>736</v>
       </c>
       <c r="F171" t="s">
-        <v>728</v>
-      </c>
-      <c r="G171" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H171" t="s">
-        <v>730</v>
-      </c>
-      <c r="I171" t="s">
-        <v>736</v>
+        <v>19</v>
       </c>
       <c r="J171" t="s">
         <v>737</v>
+      </c>
+      <c r="K171" t="s">
+        <v>21</v>
+      </c>
+      <c r="L171" t="s">
+        <v>732</v>
       </c>
       <c r="M171" t="s">
         <v>733</v>
@@ -10178,25 +10178,25 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E172" t="s">
-        <v>17</v>
+        <v>740</v>
       </c>
       <c r="F172" t="s">
-        <v>728</v>
-      </c>
-      <c r="G172" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H172" t="s">
-        <v>730</v>
-      </c>
-      <c r="I172" t="s">
-        <v>740</v>
+        <v>19</v>
       </c>
       <c r="J172" t="s">
         <v>741</v>
+      </c>
+      <c r="K172" t="s">
+        <v>21</v>
+      </c>
+      <c r="L172" t="s">
+        <v>732</v>
       </c>
       <c r="M172" t="s">
         <v>733</v>
@@ -10213,25 +10213,25 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>744</v>
       </c>
       <c r="F173" t="s">
-        <v>728</v>
-      </c>
-      <c r="G173" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H173" t="s">
-        <v>730</v>
-      </c>
-      <c r="I173" t="s">
-        <v>744</v>
+        <v>19</v>
       </c>
       <c r="J173" t="s">
         <v>745</v>
+      </c>
+      <c r="K173" t="s">
+        <v>21</v>
+      </c>
+      <c r="L173" t="s">
+        <v>732</v>
       </c>
       <c r="M173" t="s">
         <v>733</v>
@@ -10248,25 +10248,25 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E174" t="s">
-        <v>17</v>
+        <v>748</v>
       </c>
       <c r="F174" t="s">
-        <v>728</v>
-      </c>
-      <c r="G174" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H174" t="s">
-        <v>730</v>
-      </c>
-      <c r="I174" t="s">
-        <v>748</v>
+        <v>19</v>
       </c>
       <c r="J174" t="s">
         <v>749</v>
+      </c>
+      <c r="K174" t="s">
+        <v>21</v>
+      </c>
+      <c r="L174" t="s">
+        <v>732</v>
       </c>
       <c r="M174" t="s">
         <v>733</v>
@@ -10283,25 +10283,25 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E175" t="s">
-        <v>17</v>
+        <v>752</v>
       </c>
       <c r="F175" t="s">
-        <v>728</v>
-      </c>
-      <c r="G175" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H175" t="s">
-        <v>730</v>
-      </c>
-      <c r="I175" t="s">
-        <v>752</v>
+        <v>19</v>
       </c>
       <c r="J175" t="s">
         <v>753</v>
+      </c>
+      <c r="K175" t="s">
+        <v>21</v>
+      </c>
+      <c r="L175" t="s">
+        <v>732</v>
       </c>
       <c r="M175" t="s">
         <v>733</v>
@@ -10318,25 +10318,25 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E176" t="s">
-        <v>17</v>
+        <v>756</v>
       </c>
       <c r="F176" t="s">
-        <v>728</v>
-      </c>
-      <c r="G176" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H176" t="s">
-        <v>730</v>
-      </c>
-      <c r="I176" t="s">
-        <v>756</v>
+        <v>19</v>
       </c>
       <c r="J176" t="s">
         <v>757</v>
+      </c>
+      <c r="K176" t="s">
+        <v>21</v>
+      </c>
+      <c r="L176" t="s">
+        <v>732</v>
       </c>
       <c r="M176" t="s">
         <v>733</v>
@@ -10353,25 +10353,25 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>760</v>
       </c>
       <c r="F177" t="s">
-        <v>728</v>
-      </c>
-      <c r="G177" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H177" t="s">
-        <v>730</v>
-      </c>
-      <c r="I177" t="s">
-        <v>760</v>
+        <v>19</v>
       </c>
       <c r="J177" t="s">
         <v>761</v>
+      </c>
+      <c r="K177" t="s">
+        <v>21</v>
+      </c>
+      <c r="L177" t="s">
+        <v>732</v>
       </c>
       <c r="M177" t="s">
         <v>733</v>
@@ -10388,25 +10388,25 @@
         <v>15</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>764</v>
       </c>
       <c r="F178" t="s">
-        <v>728</v>
-      </c>
-      <c r="G178" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H178" t="s">
-        <v>730</v>
-      </c>
-      <c r="I178" t="s">
-        <v>764</v>
+        <v>19</v>
       </c>
       <c r="J178" t="s">
         <v>765</v>
+      </c>
+      <c r="K178" t="s">
+        <v>21</v>
+      </c>
+      <c r="L178" t="s">
+        <v>732</v>
       </c>
       <c r="M178" t="s">
         <v>733</v>
@@ -10423,25 +10423,25 @@
         <v>15</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>768</v>
       </c>
       <c r="F179" t="s">
-        <v>728</v>
-      </c>
-      <c r="G179" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H179" t="s">
-        <v>730</v>
-      </c>
-      <c r="I179" t="s">
-        <v>768</v>
+        <v>19</v>
       </c>
       <c r="J179" t="s">
         <v>769</v>
+      </c>
+      <c r="K179" t="s">
+        <v>21</v>
+      </c>
+      <c r="L179" t="s">
+        <v>732</v>
       </c>
       <c r="M179" t="s">
         <v>733</v>
@@ -10458,24 +10458,24 @@
         <v>15</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>772</v>
       </c>
       <c r="F180" t="s">
-        <v>772</v>
-      </c>
-      <c r="G180" t="s">
         <v>773</v>
       </c>
       <c r="H180" t="s">
-        <v>730</v>
-      </c>
-      <c r="I180" t="s">
+        <v>19</v>
+      </c>
+      <c r="J180" t="s">
         <v>774</v>
       </c>
-      <c r="J180" t="s">
+      <c r="K180" t="s">
+        <v>21</v>
+      </c>
+      <c r="L180" t="s">
         <v>775</v>
       </c>
       <c r="M180" t="s">
@@ -10493,31 +10493,31 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>778</v>
       </c>
       <c r="F181" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G181" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H181" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="I181" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="J181" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="K181" t="s">
-        <v>780</v>
+        <v>21</v>
       </c>
       <c r="L181" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="M181" t="s">
         <v>733</v>
@@ -10534,31 +10534,31 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>784</v>
       </c>
       <c r="F182" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G182" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H182" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="I182" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="J182" t="s">
         <v>785</v>
       </c>
       <c r="K182" t="s">
-        <v>780</v>
+        <v>21</v>
       </c>
       <c r="L182" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="M182" t="s">
         <v>733</v>
@@ -10575,25 +10575,25 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
-        <v>16</v>
-      </c>
-      <c r="E183" t="s">
-        <v>17</v>
+        <v>728</v>
       </c>
       <c r="F183" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G183" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H183" t="s">
-        <v>730</v>
+        <v>19</v>
+      </c>
+      <c r="I183" t="s">
+        <v>780</v>
       </c>
       <c r="K183" t="s">
-        <v>780</v>
+        <v>21</v>
       </c>
       <c r="L183" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="M183" t="s">
         <v>733</v>
@@ -10610,25 +10610,25 @@
         <v>15</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>790</v>
       </c>
       <c r="F184" t="s">
-        <v>772</v>
-      </c>
-      <c r="G184" t="s">
         <v>773</v>
       </c>
       <c r="H184" t="s">
-        <v>730</v>
-      </c>
-      <c r="I184" t="s">
-        <v>790</v>
+        <v>19</v>
       </c>
       <c r="J184" t="s">
         <v>791</v>
+      </c>
+      <c r="K184" t="s">
+        <v>21</v>
+      </c>
+      <c r="L184" t="s">
+        <v>775</v>
       </c>
       <c r="M184" t="s">
         <v>733</v>
@@ -10645,25 +10645,25 @@
         <v>15</v>
       </c>
       <c r="D185" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E185" t="s">
-        <v>17</v>
+        <v>794</v>
       </c>
       <c r="F185" t="s">
-        <v>772</v>
-      </c>
-      <c r="G185" t="s">
         <v>773</v>
       </c>
       <c r="H185" t="s">
-        <v>730</v>
-      </c>
-      <c r="I185" t="s">
-        <v>794</v>
+        <v>19</v>
       </c>
       <c r="J185" t="s">
         <v>795</v>
+      </c>
+      <c r="K185" t="s">
+        <v>21</v>
+      </c>
+      <c r="L185" t="s">
+        <v>775</v>
       </c>
       <c r="M185" t="s">
         <v>733</v>
@@ -10680,25 +10680,25 @@
         <v>15</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E186" t="s">
-        <v>17</v>
+        <v>798</v>
       </c>
       <c r="F186" t="s">
-        <v>772</v>
-      </c>
-      <c r="G186" t="s">
         <v>773</v>
       </c>
       <c r="H186" t="s">
-        <v>730</v>
-      </c>
-      <c r="I186" t="s">
-        <v>798</v>
+        <v>19</v>
       </c>
       <c r="J186" t="s">
         <v>799</v>
+      </c>
+      <c r="K186" t="s">
+        <v>21</v>
+      </c>
+      <c r="L186" t="s">
+        <v>775</v>
       </c>
       <c r="M186" t="s">
         <v>733</v>
@@ -10715,25 +10715,25 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>802</v>
       </c>
       <c r="F187" t="s">
-        <v>772</v>
-      </c>
-      <c r="G187" t="s">
         <v>773</v>
       </c>
       <c r="H187" t="s">
-        <v>730</v>
-      </c>
-      <c r="I187" t="s">
-        <v>802</v>
+        <v>19</v>
       </c>
       <c r="J187" t="s">
         <v>803</v>
+      </c>
+      <c r="K187" t="s">
+        <v>21</v>
+      </c>
+      <c r="L187" t="s">
+        <v>775</v>
       </c>
       <c r="M187" t="s">
         <v>733</v>
@@ -10750,25 +10750,25 @@
         <v>15</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E188" t="s">
-        <v>17</v>
+        <v>806</v>
       </c>
       <c r="F188" t="s">
-        <v>772</v>
-      </c>
-      <c r="G188" t="s">
         <v>773</v>
       </c>
       <c r="H188" t="s">
-        <v>730</v>
-      </c>
-      <c r="I188" t="s">
-        <v>806</v>
+        <v>19</v>
       </c>
       <c r="J188" t="s">
         <v>807</v>
+      </c>
+      <c r="K188" t="s">
+        <v>21</v>
+      </c>
+      <c r="L188" t="s">
+        <v>775</v>
       </c>
       <c r="M188" t="s">
         <v>733</v>
@@ -10785,25 +10785,25 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E189" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="F189" t="s">
-        <v>772</v>
-      </c>
-      <c r="G189" t="s">
         <v>773</v>
       </c>
       <c r="H189" t="s">
-        <v>730</v>
-      </c>
-      <c r="I189" t="s">
-        <v>810</v>
+        <v>19</v>
       </c>
       <c r="J189" t="s">
         <v>811</v>
+      </c>
+      <c r="K189" t="s">
+        <v>21</v>
+      </c>
+      <c r="L189" t="s">
+        <v>775</v>
       </c>
       <c r="M189" t="s">
         <v>733</v>
@@ -10820,25 +10820,25 @@
         <v>15</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E190" t="s">
-        <v>17</v>
+        <v>814</v>
       </c>
       <c r="F190" t="s">
-        <v>772</v>
-      </c>
-      <c r="G190" t="s">
         <v>773</v>
       </c>
       <c r="H190" t="s">
-        <v>730</v>
-      </c>
-      <c r="I190" t="s">
-        <v>814</v>
+        <v>19</v>
       </c>
       <c r="J190" t="s">
         <v>815</v>
+      </c>
+      <c r="K190" t="s">
+        <v>21</v>
+      </c>
+      <c r="L190" t="s">
+        <v>775</v>
       </c>
       <c r="M190" t="s">
         <v>733</v>
@@ -10855,25 +10855,25 @@
         <v>15</v>
       </c>
       <c r="D191" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E191" t="s">
-        <v>17</v>
+        <v>818</v>
       </c>
       <c r="F191" t="s">
-        <v>772</v>
-      </c>
-      <c r="G191" t="s">
         <v>773</v>
       </c>
       <c r="H191" t="s">
-        <v>730</v>
-      </c>
-      <c r="I191" t="s">
-        <v>818</v>
+        <v>19</v>
       </c>
       <c r="J191" t="s">
         <v>819</v>
+      </c>
+      <c r="K191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L191" t="s">
+        <v>775</v>
       </c>
       <c r="M191" t="s">
         <v>733</v>
@@ -10890,25 +10890,25 @@
         <v>15</v>
       </c>
       <c r="D192" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>822</v>
       </c>
       <c r="F192" t="s">
-        <v>772</v>
-      </c>
-      <c r="G192" t="s">
         <v>773</v>
       </c>
       <c r="H192" t="s">
-        <v>730</v>
-      </c>
-      <c r="I192" t="s">
-        <v>822</v>
+        <v>19</v>
       </c>
       <c r="J192" t="s">
         <v>823</v>
+      </c>
+      <c r="K192" t="s">
+        <v>21</v>
+      </c>
+      <c r="L192" t="s">
+        <v>775</v>
       </c>
       <c r="M192" t="s">
         <v>733</v>
@@ -10925,25 +10925,25 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>826</v>
       </c>
       <c r="F193" t="s">
-        <v>772</v>
-      </c>
-      <c r="G193" t="s">
         <v>773</v>
       </c>
       <c r="H193" t="s">
-        <v>730</v>
-      </c>
-      <c r="I193" t="s">
-        <v>826</v>
+        <v>19</v>
       </c>
       <c r="J193" t="s">
         <v>827</v>
+      </c>
+      <c r="K193" t="s">
+        <v>21</v>
+      </c>
+      <c r="L193" t="s">
+        <v>775</v>
       </c>
       <c r="M193" t="s">
         <v>733</v>
@@ -10960,25 +10960,25 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>830</v>
       </c>
       <c r="F194" t="s">
-        <v>772</v>
-      </c>
-      <c r="G194" t="s">
         <v>773</v>
       </c>
       <c r="H194" t="s">
-        <v>730</v>
-      </c>
-      <c r="I194" t="s">
-        <v>830</v>
+        <v>19</v>
       </c>
       <c r="J194" t="s">
         <v>831</v>
+      </c>
+      <c r="K194" t="s">
+        <v>21</v>
+      </c>
+      <c r="L194" t="s">
+        <v>775</v>
       </c>
       <c r="M194" t="s">
         <v>733</v>
@@ -10995,25 +10995,25 @@
         <v>15</v>
       </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>834</v>
       </c>
       <c r="F195" t="s">
-        <v>772</v>
-      </c>
-      <c r="G195" t="s">
         <v>773</v>
       </c>
       <c r="H195" t="s">
-        <v>730</v>
-      </c>
-      <c r="I195" t="s">
-        <v>834</v>
+        <v>19</v>
       </c>
       <c r="J195" t="s">
         <v>835</v>
+      </c>
+      <c r="K195" t="s">
+        <v>21</v>
+      </c>
+      <c r="L195" t="s">
+        <v>775</v>
       </c>
       <c r="M195" t="s">
         <v>733</v>
@@ -11030,25 +11030,25 @@
         <v>15</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>838</v>
       </c>
       <c r="F196" t="s">
-        <v>772</v>
-      </c>
-      <c r="G196" t="s">
         <v>773</v>
       </c>
       <c r="H196" t="s">
-        <v>730</v>
-      </c>
-      <c r="I196" t="s">
-        <v>838</v>
+        <v>19</v>
       </c>
       <c r="J196" t="s">
         <v>839</v>
+      </c>
+      <c r="K196" t="s">
+        <v>21</v>
+      </c>
+      <c r="L196" t="s">
+        <v>775</v>
       </c>
       <c r="M196" t="s">
         <v>733</v>
@@ -11065,24 +11065,24 @@
         <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E197" t="s">
-        <v>17</v>
+        <v>842</v>
       </c>
       <c r="F197" t="s">
-        <v>842</v>
-      </c>
-      <c r="G197" t="s">
         <v>843</v>
       </c>
       <c r="H197" t="s">
-        <v>730</v>
-      </c>
-      <c r="I197" t="s">
+        <v>19</v>
+      </c>
+      <c r="J197" t="s">
         <v>844</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
+        <v>21</v>
+      </c>
+      <c r="L197" t="s">
         <v>845</v>
       </c>
       <c r="M197" t="s">
@@ -11100,25 +11100,25 @@
         <v>15</v>
       </c>
       <c r="D198" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E198" t="s">
-        <v>17</v>
+        <v>848</v>
       </c>
       <c r="F198" t="s">
-        <v>842</v>
-      </c>
-      <c r="G198" t="s">
         <v>843</v>
       </c>
       <c r="H198" t="s">
-        <v>730</v>
-      </c>
-      <c r="I198" t="s">
-        <v>848</v>
+        <v>19</v>
       </c>
       <c r="J198" t="s">
         <v>849</v>
+      </c>
+      <c r="K198" t="s">
+        <v>21</v>
+      </c>
+      <c r="L198" t="s">
+        <v>845</v>
       </c>
       <c r="M198" t="s">
         <v>733</v>
@@ -11135,25 +11135,25 @@
         <v>15</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>852</v>
       </c>
       <c r="F199" t="s">
-        <v>842</v>
-      </c>
-      <c r="G199" t="s">
         <v>843</v>
       </c>
       <c r="H199" t="s">
-        <v>730</v>
-      </c>
-      <c r="I199" t="s">
-        <v>852</v>
+        <v>19</v>
       </c>
       <c r="J199" t="s">
         <v>853</v>
+      </c>
+      <c r="K199" t="s">
+        <v>21</v>
+      </c>
+      <c r="L199" t="s">
+        <v>845</v>
       </c>
       <c r="M199" t="s">
         <v>733</v>
@@ -11170,25 +11170,25 @@
         <v>15</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E200" t="s">
-        <v>17</v>
+        <v>856</v>
       </c>
       <c r="F200" t="s">
-        <v>842</v>
-      </c>
-      <c r="G200" t="s">
         <v>843</v>
       </c>
       <c r="H200" t="s">
-        <v>730</v>
-      </c>
-      <c r="I200" t="s">
-        <v>856</v>
+        <v>19</v>
       </c>
       <c r="J200" t="s">
         <v>857</v>
+      </c>
+      <c r="K200" t="s">
+        <v>21</v>
+      </c>
+      <c r="L200" t="s">
+        <v>845</v>
       </c>
       <c r="M200" t="s">
         <v>733</v>
@@ -11205,25 +11205,25 @@
         <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>860</v>
       </c>
       <c r="F201" t="s">
-        <v>842</v>
-      </c>
-      <c r="G201" t="s">
         <v>843</v>
       </c>
       <c r="H201" t="s">
-        <v>730</v>
-      </c>
-      <c r="I201" t="s">
-        <v>860</v>
+        <v>19</v>
       </c>
       <c r="J201" t="s">
         <v>861</v>
+      </c>
+      <c r="K201" t="s">
+        <v>21</v>
+      </c>
+      <c r="L201" t="s">
+        <v>845</v>
       </c>
       <c r="M201" t="s">
         <v>733</v>
@@ -11240,25 +11240,25 @@
         <v>15</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>864</v>
       </c>
       <c r="F202" t="s">
-        <v>842</v>
-      </c>
-      <c r="G202" t="s">
         <v>843</v>
       </c>
       <c r="H202" t="s">
-        <v>730</v>
-      </c>
-      <c r="I202" t="s">
-        <v>864</v>
+        <v>19</v>
       </c>
       <c r="J202" t="s">
         <v>865</v>
+      </c>
+      <c r="K202" t="s">
+        <v>21</v>
+      </c>
+      <c r="L202" t="s">
+        <v>845</v>
       </c>
       <c r="M202" t="s">
         <v>733</v>
@@ -11275,25 +11275,25 @@
         <v>15</v>
       </c>
       <c r="D203" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>868</v>
       </c>
       <c r="F203" t="s">
-        <v>842</v>
-      </c>
-      <c r="G203" t="s">
         <v>843</v>
       </c>
       <c r="H203" t="s">
-        <v>730</v>
-      </c>
-      <c r="I203" t="s">
-        <v>868</v>
+        <v>19</v>
       </c>
       <c r="J203" t="s">
         <v>869</v>
+      </c>
+      <c r="K203" t="s">
+        <v>21</v>
+      </c>
+      <c r="L203" t="s">
+        <v>845</v>
       </c>
       <c r="M203" t="s">
         <v>733</v>
@@ -11310,25 +11310,25 @@
         <v>15</v>
       </c>
       <c r="D204" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>872</v>
       </c>
       <c r="F204" t="s">
-        <v>842</v>
-      </c>
-      <c r="G204" t="s">
         <v>843</v>
       </c>
       <c r="H204" t="s">
-        <v>730</v>
-      </c>
-      <c r="I204" t="s">
-        <v>872</v>
+        <v>19</v>
       </c>
       <c r="J204" t="s">
         <v>873</v>
+      </c>
+      <c r="K204" t="s">
+        <v>21</v>
+      </c>
+      <c r="L204" t="s">
+        <v>845</v>
       </c>
       <c r="M204" t="s">
         <v>733</v>
@@ -11345,25 +11345,25 @@
         <v>15</v>
       </c>
       <c r="D205" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>876</v>
       </c>
       <c r="F205" t="s">
-        <v>842</v>
-      </c>
-      <c r="G205" t="s">
         <v>843</v>
       </c>
       <c r="H205" t="s">
-        <v>730</v>
-      </c>
-      <c r="I205" t="s">
-        <v>876</v>
+        <v>19</v>
       </c>
       <c r="J205" t="s">
         <v>877</v>
+      </c>
+      <c r="K205" t="s">
+        <v>21</v>
+      </c>
+      <c r="L205" t="s">
+        <v>845</v>
       </c>
       <c r="M205" t="s">
         <v>733</v>
@@ -11380,25 +11380,25 @@
         <v>15</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E206" t="s">
-        <v>17</v>
+        <v>880</v>
       </c>
       <c r="F206" t="s">
-        <v>842</v>
-      </c>
-      <c r="G206" t="s">
         <v>843</v>
       </c>
       <c r="H206" t="s">
-        <v>730</v>
-      </c>
-      <c r="I206" t="s">
-        <v>880</v>
+        <v>19</v>
       </c>
       <c r="J206" t="s">
         <v>881</v>
+      </c>
+      <c r="K206" t="s">
+        <v>21</v>
+      </c>
+      <c r="L206" t="s">
+        <v>845</v>
       </c>
       <c r="M206" t="s">
         <v>733</v>
@@ -11415,25 +11415,25 @@
         <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E207" t="s">
-        <v>17</v>
+        <v>884</v>
       </c>
       <c r="F207" t="s">
-        <v>842</v>
-      </c>
-      <c r="G207" t="s">
         <v>843</v>
       </c>
       <c r="H207" t="s">
-        <v>730</v>
-      </c>
-      <c r="I207" t="s">
-        <v>884</v>
+        <v>19</v>
       </c>
       <c r="J207" t="s">
         <v>885</v>
+      </c>
+      <c r="K207" t="s">
+        <v>21</v>
+      </c>
+      <c r="L207" t="s">
+        <v>845</v>
       </c>
       <c r="M207" t="s">
         <v>733</v>
@@ -11450,25 +11450,25 @@
         <v>15</v>
       </c>
       <c r="D208" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>888</v>
       </c>
       <c r="F208" t="s">
-        <v>842</v>
-      </c>
-      <c r="G208" t="s">
         <v>843</v>
       </c>
       <c r="H208" t="s">
-        <v>730</v>
-      </c>
-      <c r="I208" t="s">
-        <v>888</v>
+        <v>19</v>
       </c>
       <c r="J208" t="s">
         <v>889</v>
+      </c>
+      <c r="K208" t="s">
+        <v>21</v>
+      </c>
+      <c r="L208" t="s">
+        <v>845</v>
       </c>
       <c r="M208" t="s">
         <v>733</v>
@@ -11485,25 +11485,25 @@
         <v>15</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>892</v>
       </c>
       <c r="F209" t="s">
-        <v>842</v>
-      </c>
-      <c r="G209" t="s">
         <v>843</v>
       </c>
       <c r="H209" t="s">
-        <v>730</v>
-      </c>
-      <c r="I209" t="s">
-        <v>892</v>
+        <v>19</v>
       </c>
       <c r="J209" t="s">
         <v>893</v>
+      </c>
+      <c r="K209" t="s">
+        <v>21</v>
+      </c>
+      <c r="L209" t="s">
+        <v>845</v>
       </c>
       <c r="M209" t="s">
         <v>733</v>
@@ -11520,25 +11520,25 @@
         <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E210" t="s">
-        <v>17</v>
+        <v>896</v>
       </c>
       <c r="F210" t="s">
-        <v>842</v>
-      </c>
-      <c r="G210" t="s">
         <v>843</v>
       </c>
       <c r="H210" t="s">
-        <v>730</v>
-      </c>
-      <c r="I210" t="s">
-        <v>896</v>
+        <v>19</v>
       </c>
       <c r="J210" t="s">
         <v>897</v>
+      </c>
+      <c r="K210" t="s">
+        <v>21</v>
+      </c>
+      <c r="L210" t="s">
+        <v>845</v>
       </c>
       <c r="M210" t="s">
         <v>733</v>
@@ -11555,25 +11555,25 @@
         <v>15</v>
       </c>
       <c r="D211" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>900</v>
       </c>
       <c r="F211" t="s">
-        <v>842</v>
-      </c>
-      <c r="G211" t="s">
         <v>843</v>
       </c>
       <c r="H211" t="s">
-        <v>730</v>
-      </c>
-      <c r="I211" t="s">
-        <v>900</v>
+        <v>19</v>
       </c>
       <c r="J211" t="s">
         <v>901</v>
+      </c>
+      <c r="K211" t="s">
+        <v>21</v>
+      </c>
+      <c r="L211" t="s">
+        <v>845</v>
       </c>
       <c r="M211" t="s">
         <v>733</v>
@@ -11590,25 +11590,25 @@
         <v>15</v>
       </c>
       <c r="D212" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>904</v>
       </c>
       <c r="F212" t="s">
-        <v>842</v>
-      </c>
-      <c r="G212" t="s">
         <v>843</v>
       </c>
       <c r="H212" t="s">
-        <v>730</v>
-      </c>
-      <c r="I212" t="s">
-        <v>904</v>
+        <v>19</v>
       </c>
       <c r="J212" t="s">
         <v>905</v>
+      </c>
+      <c r="K212" t="s">
+        <v>21</v>
+      </c>
+      <c r="L212" t="s">
+        <v>845</v>
       </c>
       <c r="M212" t="s">
         <v>733</v>
@@ -11625,24 +11625,24 @@
         <v>15</v>
       </c>
       <c r="D213" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>908</v>
       </c>
       <c r="F213" t="s">
-        <v>908</v>
-      </c>
-      <c r="G213" t="s">
         <v>909</v>
       </c>
       <c r="H213" t="s">
-        <v>730</v>
-      </c>
-      <c r="I213" t="s">
+        <v>19</v>
+      </c>
+      <c r="J213" t="s">
         <v>910</v>
       </c>
-      <c r="J213" t="s">
+      <c r="K213" t="s">
+        <v>21</v>
+      </c>
+      <c r="L213" t="s">
         <v>911</v>
       </c>
       <c r="M213" t="s">
@@ -11660,25 +11660,25 @@
         <v>15</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>914</v>
       </c>
       <c r="F214" t="s">
-        <v>908</v>
-      </c>
-      <c r="G214" t="s">
         <v>909</v>
       </c>
       <c r="H214" t="s">
-        <v>730</v>
-      </c>
-      <c r="I214" t="s">
-        <v>914</v>
+        <v>19</v>
       </c>
       <c r="J214" t="s">
         <v>915</v>
+      </c>
+      <c r="K214" t="s">
+        <v>21</v>
+      </c>
+      <c r="L214" t="s">
+        <v>911</v>
       </c>
       <c r="M214" t="s">
         <v>733</v>
@@ -11695,25 +11695,25 @@
         <v>15</v>
       </c>
       <c r="D215" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E215" t="s">
-        <v>17</v>
+        <v>918</v>
       </c>
       <c r="F215" t="s">
-        <v>908</v>
-      </c>
-      <c r="G215" t="s">
         <v>909</v>
       </c>
       <c r="H215" t="s">
-        <v>730</v>
-      </c>
-      <c r="I215" t="s">
-        <v>918</v>
+        <v>19</v>
       </c>
       <c r="J215" t="s">
         <v>919</v>
+      </c>
+      <c r="K215" t="s">
+        <v>21</v>
+      </c>
+      <c r="L215" t="s">
+        <v>911</v>
       </c>
       <c r="M215" t="s">
         <v>733</v>
@@ -11730,25 +11730,25 @@
         <v>15</v>
       </c>
       <c r="D216" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>922</v>
       </c>
       <c r="F216" t="s">
-        <v>908</v>
-      </c>
-      <c r="G216" t="s">
         <v>909</v>
       </c>
       <c r="H216" t="s">
-        <v>730</v>
-      </c>
-      <c r="I216" t="s">
-        <v>922</v>
+        <v>19</v>
       </c>
       <c r="J216" t="s">
         <v>923</v>
+      </c>
+      <c r="K216" t="s">
+        <v>21</v>
+      </c>
+      <c r="L216" t="s">
+        <v>911</v>
       </c>
       <c r="M216" t="s">
         <v>733</v>
@@ -11765,25 +11765,25 @@
         <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E217" t="s">
-        <v>17</v>
+        <v>926</v>
       </c>
       <c r="F217" t="s">
-        <v>908</v>
-      </c>
-      <c r="G217" t="s">
         <v>909</v>
       </c>
       <c r="H217" t="s">
-        <v>730</v>
-      </c>
-      <c r="I217" t="s">
-        <v>926</v>
+        <v>19</v>
       </c>
       <c r="J217" t="s">
         <v>927</v>
+      </c>
+      <c r="K217" t="s">
+        <v>21</v>
+      </c>
+      <c r="L217" t="s">
+        <v>911</v>
       </c>
       <c r="M217" t="s">
         <v>733</v>
@@ -11800,25 +11800,25 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>930</v>
       </c>
       <c r="F218" t="s">
-        <v>908</v>
-      </c>
-      <c r="G218" t="s">
         <v>909</v>
       </c>
       <c r="H218" t="s">
-        <v>730</v>
-      </c>
-      <c r="I218" t="s">
-        <v>930</v>
+        <v>19</v>
       </c>
       <c r="J218" t="s">
         <v>931</v>
+      </c>
+      <c r="K218" t="s">
+        <v>21</v>
+      </c>
+      <c r="L218" t="s">
+        <v>911</v>
       </c>
       <c r="M218" t="s">
         <v>733</v>
@@ -11835,25 +11835,25 @@
         <v>15</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E219" t="s">
-        <v>17</v>
+        <v>934</v>
       </c>
       <c r="F219" t="s">
-        <v>908</v>
-      </c>
-      <c r="G219" t="s">
         <v>909</v>
       </c>
       <c r="H219" t="s">
-        <v>730</v>
-      </c>
-      <c r="I219" t="s">
-        <v>934</v>
+        <v>19</v>
       </c>
       <c r="J219" t="s">
         <v>935</v>
+      </c>
+      <c r="K219" t="s">
+        <v>21</v>
+      </c>
+      <c r="L219" t="s">
+        <v>911</v>
       </c>
       <c r="M219" t="s">
         <v>733</v>
@@ -11870,25 +11870,25 @@
         <v>15</v>
       </c>
       <c r="D220" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E220" t="s">
-        <v>17</v>
+        <v>938</v>
       </c>
       <c r="F220" t="s">
-        <v>908</v>
-      </c>
-      <c r="G220" t="s">
         <v>909</v>
       </c>
       <c r="H220" t="s">
-        <v>730</v>
-      </c>
-      <c r="I220" t="s">
-        <v>938</v>
+        <v>19</v>
       </c>
       <c r="J220" t="s">
         <v>939</v>
+      </c>
+      <c r="K220" t="s">
+        <v>21</v>
+      </c>
+      <c r="L220" t="s">
+        <v>911</v>
       </c>
       <c r="M220" t="s">
         <v>733</v>
@@ -11905,25 +11905,25 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>942</v>
       </c>
       <c r="F221" t="s">
-        <v>908</v>
-      </c>
-      <c r="G221" t="s">
         <v>909</v>
       </c>
       <c r="H221" t="s">
-        <v>730</v>
-      </c>
-      <c r="I221" t="s">
-        <v>942</v>
+        <v>19</v>
       </c>
       <c r="J221" t="s">
         <v>943</v>
+      </c>
+      <c r="K221" t="s">
+        <v>21</v>
+      </c>
+      <c r="L221" t="s">
+        <v>911</v>
       </c>
       <c r="M221" t="s">
         <v>733</v>
@@ -11940,24 +11940,24 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E222" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F222" t="s">
-        <v>946</v>
-      </c>
-      <c r="G222" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H222" t="s">
-        <v>948</v>
-      </c>
-      <c r="I222" t="s">
+        <v>19</v>
+      </c>
+      <c r="J222" t="s">
         <v>949</v>
       </c>
-      <c r="J222" t="s">
+      <c r="K222" t="s">
+        <v>21</v>
+      </c>
+      <c r="L222" t="s">
         <v>950</v>
       </c>
       <c r="M222" t="s">
@@ -11975,25 +11975,25 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E223" t="s">
-        <v>17</v>
+        <v>954</v>
       </c>
       <c r="F223" t="s">
-        <v>946</v>
-      </c>
-      <c r="G223" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H223" t="s">
-        <v>948</v>
-      </c>
-      <c r="I223" t="s">
-        <v>954</v>
+        <v>19</v>
       </c>
       <c r="J223" t="s">
         <v>955</v>
+      </c>
+      <c r="K223" t="s">
+        <v>21</v>
+      </c>
+      <c r="L223" t="s">
+        <v>950</v>
       </c>
       <c r="M223" t="s">
         <v>951</v>
@@ -12010,25 +12010,25 @@
         <v>15</v>
       </c>
       <c r="D224" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E224" t="s">
-        <v>17</v>
+        <v>958</v>
       </c>
       <c r="F224" t="s">
-        <v>946</v>
-      </c>
-      <c r="G224" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H224" t="s">
-        <v>948</v>
-      </c>
-      <c r="I224" t="s">
-        <v>958</v>
+        <v>19</v>
       </c>
       <c r="J224" t="s">
         <v>959</v>
+      </c>
+      <c r="K224" t="s">
+        <v>21</v>
+      </c>
+      <c r="L224" t="s">
+        <v>950</v>
       </c>
       <c r="M224" t="s">
         <v>951</v>
@@ -12045,25 +12045,25 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E225" t="s">
-        <v>17</v>
+        <v>962</v>
       </c>
       <c r="F225" t="s">
-        <v>946</v>
-      </c>
-      <c r="G225" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H225" t="s">
-        <v>948</v>
-      </c>
-      <c r="I225" t="s">
-        <v>962</v>
+        <v>19</v>
       </c>
       <c r="J225" t="s">
         <v>963</v>
+      </c>
+      <c r="K225" t="s">
+        <v>21</v>
+      </c>
+      <c r="L225" t="s">
+        <v>950</v>
       </c>
       <c r="M225" t="s">
         <v>951</v>
@@ -12080,25 +12080,25 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>966</v>
       </c>
       <c r="F226" t="s">
-        <v>946</v>
-      </c>
-      <c r="G226" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H226" t="s">
-        <v>948</v>
-      </c>
-      <c r="I226" t="s">
-        <v>966</v>
+        <v>19</v>
       </c>
       <c r="J226" t="s">
         <v>967</v>
+      </c>
+      <c r="K226" t="s">
+        <v>21</v>
+      </c>
+      <c r="L226" t="s">
+        <v>950</v>
       </c>
       <c r="M226" t="s">
         <v>951</v>
@@ -12115,25 +12115,25 @@
         <v>15</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="F227" t="s">
-        <v>946</v>
-      </c>
-      <c r="G227" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H227" t="s">
-        <v>948</v>
-      </c>
-      <c r="I227" t="s">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="J227" t="s">
         <v>971</v>
+      </c>
+      <c r="K227" t="s">
+        <v>21</v>
+      </c>
+      <c r="L227" t="s">
+        <v>950</v>
       </c>
       <c r="M227" t="s">
         <v>951</v>
@@ -12150,24 +12150,24 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E228" t="s">
-        <v>17</v>
+        <v>974</v>
       </c>
       <c r="F228" t="s">
-        <v>974</v>
-      </c>
-      <c r="G228" t="s">
         <v>975</v>
       </c>
       <c r="H228" t="s">
-        <v>948</v>
-      </c>
-      <c r="I228" t="s">
+        <v>19</v>
+      </c>
+      <c r="J228" t="s">
         <v>976</v>
       </c>
-      <c r="J228" t="s">
+      <c r="K228" t="s">
+        <v>21</v>
+      </c>
+      <c r="L228" t="s">
         <v>977</v>
       </c>
       <c r="M228" t="s">
@@ -12185,25 +12185,25 @@
         <v>15</v>
       </c>
       <c r="D229" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E229" t="s">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="F229" t="s">
-        <v>974</v>
-      </c>
-      <c r="G229" t="s">
         <v>975</v>
       </c>
       <c r="H229" t="s">
-        <v>948</v>
-      </c>
-      <c r="I229" t="s">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="J229" t="s">
         <v>981</v>
+      </c>
+      <c r="K229" t="s">
+        <v>21</v>
+      </c>
+      <c r="L229" t="s">
+        <v>977</v>
       </c>
       <c r="M229" t="s">
         <v>951</v>
@@ -12220,25 +12220,25 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E230" t="s">
-        <v>17</v>
+        <v>984</v>
       </c>
       <c r="F230" t="s">
-        <v>974</v>
-      </c>
-      <c r="G230" t="s">
         <v>975</v>
       </c>
       <c r="H230" t="s">
-        <v>948</v>
-      </c>
-      <c r="I230" t="s">
-        <v>984</v>
+        <v>19</v>
       </c>
       <c r="J230" t="s">
         <v>985</v>
+      </c>
+      <c r="K230" t="s">
+        <v>21</v>
+      </c>
+      <c r="L230" t="s">
+        <v>977</v>
       </c>
       <c r="M230" t="s">
         <v>951</v>
@@ -12255,25 +12255,25 @@
         <v>15</v>
       </c>
       <c r="D231" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>988</v>
       </c>
       <c r="F231" t="s">
-        <v>974</v>
-      </c>
-      <c r="G231" t="s">
         <v>975</v>
       </c>
       <c r="H231" t="s">
-        <v>948</v>
-      </c>
-      <c r="I231" t="s">
-        <v>988</v>
+        <v>19</v>
       </c>
       <c r="J231" t="s">
         <v>989</v>
+      </c>
+      <c r="K231" t="s">
+        <v>21</v>
+      </c>
+      <c r="L231" t="s">
+        <v>977</v>
       </c>
       <c r="M231" t="s">
         <v>951</v>
@@ -12290,25 +12290,25 @@
         <v>15</v>
       </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E232" t="s">
-        <v>17</v>
+        <v>992</v>
       </c>
       <c r="F232" t="s">
-        <v>974</v>
-      </c>
-      <c r="G232" t="s">
         <v>975</v>
       </c>
       <c r="H232" t="s">
-        <v>948</v>
-      </c>
-      <c r="I232" t="s">
-        <v>992</v>
+        <v>19</v>
       </c>
       <c r="J232" t="s">
         <v>993</v>
+      </c>
+      <c r="K232" t="s">
+        <v>21</v>
+      </c>
+      <c r="L232" t="s">
+        <v>977</v>
       </c>
       <c r="M232" t="s">
         <v>951</v>
@@ -12325,24 +12325,24 @@
         <v>15</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E233" t="s">
-        <v>17</v>
+        <v>996</v>
       </c>
       <c r="F233" t="s">
-        <v>996</v>
-      </c>
-      <c r="G233" t="s">
         <v>997</v>
       </c>
       <c r="H233" t="s">
-        <v>948</v>
-      </c>
-      <c r="I233" t="s">
+        <v>19</v>
+      </c>
+      <c r="J233" t="s">
         <v>998</v>
       </c>
-      <c r="J233" t="s">
+      <c r="K233" t="s">
+        <v>21</v>
+      </c>
+      <c r="L233" t="s">
         <v>999</v>
       </c>
       <c r="M233" t="s">
@@ -12360,25 +12360,25 @@
         <v>15</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E234" t="s">
-        <v>17</v>
+        <v>1002</v>
       </c>
       <c r="F234" t="s">
-        <v>996</v>
-      </c>
-      <c r="G234" t="s">
         <v>997</v>
       </c>
       <c r="H234" t="s">
-        <v>948</v>
-      </c>
-      <c r="I234" t="s">
-        <v>1002</v>
+        <v>19</v>
       </c>
       <c r="J234" t="s">
         <v>1003</v>
+      </c>
+      <c r="K234" t="s">
+        <v>21</v>
+      </c>
+      <c r="L234" t="s">
+        <v>999</v>
       </c>
       <c r="M234" t="s">
         <v>951</v>
@@ -12395,25 +12395,25 @@
         <v>15</v>
       </c>
       <c r="D235" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E235" t="s">
-        <v>17</v>
+        <v>1006</v>
       </c>
       <c r="F235" t="s">
-        <v>996</v>
-      </c>
-      <c r="G235" t="s">
         <v>997</v>
       </c>
       <c r="H235" t="s">
-        <v>948</v>
-      </c>
-      <c r="I235" t="s">
-        <v>1006</v>
+        <v>19</v>
       </c>
       <c r="J235" t="s">
         <v>1007</v>
+      </c>
+      <c r="K235" t="s">
+        <v>21</v>
+      </c>
+      <c r="L235" t="s">
+        <v>999</v>
       </c>
       <c r="M235" t="s">
         <v>951</v>
@@ -12430,25 +12430,25 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E236" t="s">
-        <v>17</v>
+        <v>1010</v>
       </c>
       <c r="F236" t="s">
-        <v>996</v>
-      </c>
-      <c r="G236" t="s">
         <v>997</v>
       </c>
       <c r="H236" t="s">
-        <v>948</v>
-      </c>
-      <c r="I236" t="s">
-        <v>1010</v>
+        <v>19</v>
       </c>
       <c r="J236" t="s">
         <v>1011</v>
+      </c>
+      <c r="K236" t="s">
+        <v>21</v>
+      </c>
+      <c r="L236" t="s">
+        <v>999</v>
       </c>
       <c r="M236" t="s">
         <v>951</v>
@@ -12465,25 +12465,25 @@
         <v>15</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E237" t="s">
-        <v>17</v>
+        <v>1014</v>
       </c>
       <c r="F237" t="s">
-        <v>996</v>
-      </c>
-      <c r="G237" t="s">
         <v>997</v>
       </c>
       <c r="H237" t="s">
-        <v>948</v>
-      </c>
-      <c r="I237" t="s">
-        <v>1014</v>
+        <v>19</v>
       </c>
       <c r="J237" t="s">
         <v>1015</v>
+      </c>
+      <c r="K237" t="s">
+        <v>21</v>
+      </c>
+      <c r="L237" t="s">
+        <v>999</v>
       </c>
       <c r="M237" t="s">
         <v>951</v>
@@ -12500,25 +12500,25 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E238" t="s">
-        <v>17</v>
+        <v>1018</v>
       </c>
       <c r="F238" t="s">
-        <v>996</v>
-      </c>
-      <c r="G238" t="s">
         <v>997</v>
       </c>
       <c r="H238" t="s">
-        <v>948</v>
-      </c>
-      <c r="I238" t="s">
-        <v>1018</v>
+        <v>19</v>
       </c>
       <c r="J238" t="s">
         <v>1019</v>
+      </c>
+      <c r="K238" t="s">
+        <v>21</v>
+      </c>
+      <c r="L238" t="s">
+        <v>999</v>
       </c>
       <c r="M238" t="s">
         <v>951</v>
@@ -12535,25 +12535,25 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E239" t="s">
-        <v>17</v>
+        <v>1022</v>
       </c>
       <c r="F239" t="s">
-        <v>996</v>
-      </c>
-      <c r="G239" t="s">
         <v>997</v>
       </c>
       <c r="H239" t="s">
-        <v>948</v>
-      </c>
-      <c r="I239" t="s">
-        <v>1022</v>
+        <v>19</v>
       </c>
       <c r="J239" t="s">
         <v>1023</v>
+      </c>
+      <c r="K239" t="s">
+        <v>21</v>
+      </c>
+      <c r="L239" t="s">
+        <v>999</v>
       </c>
       <c r="M239" t="s">
         <v>951</v>
@@ -12570,25 +12570,25 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E240" t="s">
-        <v>17</v>
+        <v>1026</v>
       </c>
       <c r="F240" t="s">
-        <v>996</v>
-      </c>
-      <c r="G240" t="s">
         <v>997</v>
       </c>
       <c r="H240" t="s">
-        <v>948</v>
-      </c>
-      <c r="I240" t="s">
-        <v>1026</v>
+        <v>19</v>
       </c>
       <c r="J240" t="s">
         <v>1027</v>
+      </c>
+      <c r="K240" t="s">
+        <v>21</v>
+      </c>
+      <c r="L240" t="s">
+        <v>999</v>
       </c>
       <c r="M240" t="s">
         <v>951</v>
@@ -12605,24 +12605,24 @@
         <v>15</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>1030</v>
       </c>
       <c r="F241" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G241" t="s">
         <v>1031</v>
       </c>
       <c r="H241" t="s">
-        <v>948</v>
-      </c>
-      <c r="I241" t="s">
+        <v>19</v>
+      </c>
+      <c r="J241" t="s">
         <v>1032</v>
       </c>
-      <c r="J241" t="s">
+      <c r="K241" t="s">
+        <v>21</v>
+      </c>
+      <c r="L241" t="s">
         <v>1033</v>
       </c>
       <c r="M241" t="s">
@@ -12640,25 +12640,25 @@
         <v>15</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E242" t="s">
-        <v>17</v>
+        <v>1036</v>
       </c>
       <c r="F242" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G242" t="s">
         <v>1031</v>
       </c>
       <c r="H242" t="s">
-        <v>948</v>
-      </c>
-      <c r="I242" t="s">
-        <v>1036</v>
+        <v>19</v>
       </c>
       <c r="J242" t="s">
         <v>1037</v>
+      </c>
+      <c r="K242" t="s">
+        <v>21</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1033</v>
       </c>
       <c r="M242" t="s">
         <v>951</v>
@@ -12675,25 +12675,25 @@
         <v>15</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E243" t="s">
-        <v>17</v>
+        <v>1040</v>
       </c>
       <c r="F243" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G243" t="s">
         <v>1031</v>
       </c>
       <c r="H243" t="s">
-        <v>948</v>
-      </c>
-      <c r="I243" t="s">
-        <v>1040</v>
+        <v>19</v>
       </c>
       <c r="J243" t="s">
         <v>1041</v>
+      </c>
+      <c r="K243" t="s">
+        <v>21</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1033</v>
       </c>
       <c r="M243" t="s">
         <v>951</v>
@@ -12710,25 +12710,25 @@
         <v>15</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E244" t="s">
-        <v>17</v>
+        <v>1044</v>
       </c>
       <c r="F244" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G244" t="s">
         <v>1031</v>
       </c>
       <c r="H244" t="s">
-        <v>948</v>
-      </c>
-      <c r="I244" t="s">
-        <v>1044</v>
+        <v>19</v>
       </c>
       <c r="J244" t="s">
         <v>1045</v>
+      </c>
+      <c r="K244" t="s">
+        <v>21</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1033</v>
       </c>
       <c r="M244" t="s">
         <v>951</v>
@@ -12745,25 +12745,25 @@
         <v>15</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E245" t="s">
-        <v>17</v>
+        <v>1048</v>
       </c>
       <c r="F245" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G245" t="s">
         <v>1031</v>
       </c>
       <c r="H245" t="s">
-        <v>948</v>
-      </c>
-      <c r="I245" t="s">
-        <v>1048</v>
+        <v>19</v>
       </c>
       <c r="J245" t="s">
         <v>1049</v>
+      </c>
+      <c r="K245" t="s">
+        <v>21</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1033</v>
       </c>
       <c r="M245" t="s">
         <v>951</v>
@@ -12780,25 +12780,25 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E246" t="s">
-        <v>17</v>
+        <v>1052</v>
       </c>
       <c r="F246" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G246" t="s">
         <v>1031</v>
       </c>
       <c r="H246" t="s">
-        <v>948</v>
-      </c>
-      <c r="I246" t="s">
-        <v>1052</v>
+        <v>19</v>
       </c>
       <c r="J246" t="s">
         <v>1053</v>
+      </c>
+      <c r="K246" t="s">
+        <v>21</v>
+      </c>
+      <c r="L246" t="s">
+        <v>1033</v>
       </c>
       <c r="M246" t="s">
         <v>951</v>
@@ -12815,25 +12815,25 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E247" t="s">
-        <v>17</v>
+        <v>1056</v>
       </c>
       <c r="F247" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G247" t="s">
         <v>1031</v>
       </c>
       <c r="H247" t="s">
-        <v>948</v>
-      </c>
-      <c r="I247" t="s">
-        <v>1056</v>
+        <v>19</v>
       </c>
       <c r="J247" t="s">
         <v>1057</v>
+      </c>
+      <c r="K247" t="s">
+        <v>21</v>
+      </c>
+      <c r="L247" t="s">
+        <v>1033</v>
       </c>
       <c r="M247" t="s">
         <v>951</v>
@@ -12850,25 +12850,25 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>1060</v>
       </c>
       <c r="F248" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G248" t="s">
         <v>1031</v>
       </c>
       <c r="H248" t="s">
-        <v>948</v>
-      </c>
-      <c r="I248" t="s">
-        <v>1060</v>
+        <v>19</v>
       </c>
       <c r="J248" t="s">
         <v>1061</v>
+      </c>
+      <c r="K248" t="s">
+        <v>21</v>
+      </c>
+      <c r="L248" t="s">
+        <v>1033</v>
       </c>
       <c r="M248" t="s">
         <v>951</v>
@@ -12885,25 +12885,25 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E249" t="s">
-        <v>17</v>
+        <v>1064</v>
       </c>
       <c r="F249" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G249" t="s">
         <v>1031</v>
       </c>
       <c r="H249" t="s">
-        <v>948</v>
-      </c>
-      <c r="I249" t="s">
-        <v>1064</v>
+        <v>19</v>
       </c>
       <c r="J249" t="s">
         <v>1065</v>
+      </c>
+      <c r="K249" t="s">
+        <v>21</v>
+      </c>
+      <c r="L249" t="s">
+        <v>1033</v>
       </c>
       <c r="M249" t="s">
         <v>951</v>
@@ -12920,25 +12920,25 @@
         <v>15</v>
       </c>
       <c r="D250" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E250" t="s">
-        <v>17</v>
+        <v>1068</v>
       </c>
       <c r="F250" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G250" t="s">
         <v>1031</v>
       </c>
       <c r="H250" t="s">
-        <v>948</v>
-      </c>
-      <c r="I250" t="s">
-        <v>1068</v>
+        <v>19</v>
       </c>
       <c r="J250" t="s">
         <v>1069</v>
+      </c>
+      <c r="K250" t="s">
+        <v>21</v>
+      </c>
+      <c r="L250" t="s">
+        <v>1033</v>
       </c>
       <c r="M250" t="s">
         <v>951</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,33 +25,33 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:global-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
     <t>codeforiati:global-code</t>
   </si>
   <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
     <t>codeforiati:intermediate-region-name</t>
   </si>
   <si>
@@ -64,30 +64,30 @@
     <t>active</t>
   </si>
   <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
     <t>002</t>
   </si>
   <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
     <t>001</t>
   </si>
   <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>IOT</t>
   </si>
   <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>IO</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
     <t>Sub-Saharan Africa</t>
   </si>
   <si>
@@ -445,12 +445,12 @@
     <t>AGO</t>
   </si>
   <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>AO</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>Middle Africa</t>
   </si>
   <si>
@@ -559,12 +559,12 @@
     <t>BWA</t>
   </si>
   <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>BW</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>Southern Africa</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>BEN</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>BJ</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>Western Africa</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
     <t>019</t>
   </si>
   <si>
-    <t>AIA</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
     <t>Caribbean</t>
   </si>
   <si>
@@ -1189,12 +1189,12 @@
     <t>BLZ</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>BZ</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>Central America</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>ARG</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>AR</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>South America</t>
   </si>
   <si>
@@ -1489,12 +1489,12 @@
     <t>BMU</t>
   </si>
   <si>
+    <t>021</t>
+  </si>
+  <si>
     <t>BM</t>
   </si>
   <si>
-    <t>021</t>
-  </si>
-  <si>
     <t>Northern America</t>
   </si>
   <si>
@@ -1564,24 +1564,24 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
     <t>142</t>
   </si>
   <si>
-    <t>KAZ</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1639,12 +1639,12 @@
     <t>CHN</t>
   </si>
   <si>
+    <t>030</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
-    <t>030</t>
-  </si>
-  <si>
     <t>Eastern Asia</t>
   </si>
   <si>
@@ -1729,12 +1729,12 @@
     <t>BRN</t>
   </si>
   <si>
+    <t>035</t>
+  </si>
+  <si>
     <t>BN</t>
   </si>
   <si>
-    <t>035</t>
-  </si>
-  <si>
     <t>South-eastern Asia</t>
   </si>
   <si>
@@ -1867,12 +1867,12 @@
     <t>AFG</t>
   </si>
   <si>
+    <t>034</t>
+  </si>
+  <si>
     <t>AF</t>
   </si>
   <si>
-    <t>034</t>
-  </si>
-  <si>
     <t>Southern Asia</t>
   </si>
   <si>
@@ -1981,12 +1981,12 @@
     <t>ARM</t>
   </si>
   <si>
+    <t>145</t>
+  </si>
+  <si>
     <t>AM</t>
   </si>
   <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>Western Asia</t>
   </si>
   <si>
@@ -2200,24 +2200,24 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>ALA</t>
   </si>
   <si>
+    <t>154</t>
+  </si>
+  <si>
     <t>AX</t>
   </si>
   <si>
-    <t>154</t>
-  </si>
-  <si>
     <t>Northern Europe</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>GGY</t>
   </si>
   <si>
+    <t>830</t>
+  </si>
+  <si>
     <t>GG</t>
   </si>
   <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>Channel Islands</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>ALB</t>
   </si>
   <si>
+    <t>039</t>
+  </si>
+  <si>
     <t>AL</t>
   </si>
   <si>
-    <t>039</t>
-  </si>
-  <si>
     <t>Southern Europe</t>
   </si>
   <si>
@@ -2743,12 +2743,12 @@
     <t>AUT</t>
   </si>
   <si>
+    <t>155</t>
+  </si>
+  <si>
     <t>AT</t>
   </si>
   <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>Western Europe</t>
   </si>
   <si>
@@ -2854,24 +2854,24 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
     <t>009</t>
   </si>
   <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
     <t>162</t>
   </si>
   <si>
@@ -2941,12 +2941,12 @@
     <t>FJI</t>
   </si>
   <si>
+    <t>054</t>
+  </si>
+  <si>
     <t>FJ</t>
   </si>
   <si>
-    <t>054</t>
-  </si>
-  <si>
     <t>Melanesia</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>GUM</t>
   </si>
   <si>
+    <t>057</t>
+  </si>
+  <si>
     <t>GU</t>
   </si>
   <si>
-    <t>057</t>
-  </si>
-  <si>
     <t>Micronesia</t>
   </si>
   <si>
@@ -3109,10 +3109,10 @@
     <t>ASM</t>
   </si>
   <si>
+    <t>061</t>
+  </si>
+  <si>
     <t>AS</t>
-  </si>
-  <si>
-    <t>061</t>
   </si>
   <si>
     <t>Polynesia</t>
@@ -3618,7 +3618,7 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
       <c r="I2" t="s">
@@ -3651,13 +3651,13 @@
         <v>26</v>
       </c>
       <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
         <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
@@ -3686,13 +3686,13 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
@@ -3721,13 +3721,13 @@
         <v>34</v>
       </c>
       <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
         <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
@@ -3756,13 +3756,13 @@
         <v>38</v>
       </c>
       <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
         <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
       </c>
       <c r="J6" t="s">
         <v>21</v>
@@ -3791,13 +3791,13 @@
         <v>42</v>
       </c>
       <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
         <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
       </c>
       <c r="J7" t="s">
         <v>21</v>
@@ -3826,13 +3826,13 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s">
         <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
       </c>
       <c r="J8" t="s">
         <v>21</v>
@@ -3864,22 +3864,22 @@
         <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
         <v>55</v>
@@ -3902,25 +3902,25 @@
         <v>58</v>
       </c>
       <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
         <v>59</v>
       </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
         <v>55</v>
@@ -3943,25 +3943,25 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
         <v>63</v>
       </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
         <v>55</v>
@@ -3984,25 +3984,25 @@
         <v>66</v>
       </c>
       <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
         <v>67</v>
       </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
         <v>55</v>
@@ -4025,25 +4025,25 @@
         <v>70</v>
       </c>
       <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
         <v>71</v>
       </c>
-      <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M13" t="s">
         <v>55</v>
@@ -4066,25 +4066,25 @@
         <v>74</v>
       </c>
       <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
         <v>75</v>
       </c>
-      <c r="G14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L14" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
         <v>55</v>
@@ -4107,25 +4107,25 @@
         <v>78</v>
       </c>
       <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
         <v>79</v>
       </c>
-      <c r="G15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L15" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
         <v>55</v>
@@ -4148,25 +4148,25 @@
         <v>82</v>
       </c>
       <c r="F16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
         <v>83</v>
       </c>
-      <c r="G16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L16" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
         <v>55</v>
@@ -4189,25 +4189,25 @@
         <v>86</v>
       </c>
       <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
         <v>87</v>
       </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
       <c r="J17" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L17" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
         <v>55</v>
@@ -4230,25 +4230,25 @@
         <v>90</v>
       </c>
       <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
         <v>91</v>
       </c>
-      <c r="G18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
       <c r="J18" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L18" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
         <v>55</v>
@@ -4271,25 +4271,25 @@
         <v>94</v>
       </c>
       <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
         <v>95</v>
       </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L19" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
         <v>55</v>
@@ -4312,25 +4312,25 @@
         <v>98</v>
       </c>
       <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
         <v>99</v>
       </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
       <c r="J20" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L20" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
         <v>55</v>
@@ -4353,25 +4353,25 @@
         <v>102</v>
       </c>
       <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
         <v>103</v>
       </c>
-      <c r="G21" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
       <c r="J21" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L21" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
         <v>55</v>
@@ -4394,25 +4394,25 @@
         <v>106</v>
       </c>
       <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
         <v>107</v>
       </c>
-      <c r="G22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" t="s">
-        <v>52</v>
-      </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
       <c r="J22" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L22" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
         <v>55</v>
@@ -4435,25 +4435,25 @@
         <v>110</v>
       </c>
       <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
         <v>111</v>
       </c>
-      <c r="G23" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" t="s">
-        <v>52</v>
-      </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
       <c r="J23" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L23" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
         <v>55</v>
@@ -4476,25 +4476,25 @@
         <v>114</v>
       </c>
       <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
         <v>115</v>
       </c>
-      <c r="G24" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" t="s">
-        <v>20</v>
-      </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
         <v>55</v>
@@ -4517,25 +4517,25 @@
         <v>118</v>
       </c>
       <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
         <v>119</v>
       </c>
-      <c r="G25" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" t="s">
-        <v>20</v>
-      </c>
       <c r="J25" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L25" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
         <v>55</v>
@@ -4558,25 +4558,25 @@
         <v>122</v>
       </c>
       <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
         <v>123</v>
       </c>
-      <c r="G26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" t="s">
-        <v>52</v>
-      </c>
-      <c r="I26" t="s">
-        <v>20</v>
-      </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L26" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
         <v>55</v>
@@ -4599,25 +4599,25 @@
         <v>126</v>
       </c>
       <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
         <v>127</v>
       </c>
-      <c r="G27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I27" t="s">
-        <v>20</v>
-      </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L27" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M27" t="s">
         <v>55</v>
@@ -4640,25 +4640,25 @@
         <v>130</v>
       </c>
       <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" t="s">
         <v>131</v>
       </c>
-      <c r="G28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" t="s">
-        <v>52</v>
-      </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
       <c r="J28" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L28" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M28" t="s">
         <v>55</v>
@@ -4681,25 +4681,25 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" t="s">
         <v>135</v>
       </c>
-      <c r="G29" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" t="s">
-        <v>52</v>
-      </c>
-      <c r="I29" t="s">
-        <v>20</v>
-      </c>
       <c r="J29" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L29" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M29" t="s">
         <v>55</v>
@@ -4722,25 +4722,25 @@
         <v>138</v>
       </c>
       <c r="F30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s">
         <v>139</v>
       </c>
-      <c r="G30" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" t="s">
-        <v>52</v>
-      </c>
-      <c r="I30" t="s">
-        <v>20</v>
-      </c>
       <c r="J30" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L30" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M30" t="s">
         <v>55</v>
@@ -4763,25 +4763,25 @@
         <v>142</v>
       </c>
       <c r="F31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" t="s">
         <v>143</v>
       </c>
-      <c r="G31" t="s">
-        <v>19</v>
-      </c>
       <c r="H31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" t="s">
         <v>144</v>
       </c>
-      <c r="I31" t="s">
-        <v>20</v>
-      </c>
       <c r="J31" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L31" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M31" t="s">
         <v>145</v>
@@ -4804,25 +4804,25 @@
         <v>148</v>
       </c>
       <c r="F32" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" t="s">
+        <v>143</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" t="s">
         <v>149</v>
       </c>
-      <c r="G32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" t="s">
-        <v>144</v>
-      </c>
-      <c r="I32" t="s">
-        <v>20</v>
-      </c>
       <c r="J32" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M32" t="s">
         <v>145</v>
@@ -4845,25 +4845,25 @@
         <v>152</v>
       </c>
       <c r="F33" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" t="s">
         <v>153</v>
       </c>
-      <c r="G33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" t="s">
-        <v>144</v>
-      </c>
-      <c r="I33" t="s">
-        <v>20</v>
-      </c>
       <c r="J33" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L33" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M33" t="s">
         <v>145</v>
@@ -4886,25 +4886,25 @@
         <v>156</v>
       </c>
       <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" t="s">
+        <v>143</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" t="s">
         <v>157</v>
       </c>
-      <c r="G34" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" t="s">
-        <v>144</v>
-      </c>
-      <c r="I34" t="s">
-        <v>20</v>
-      </c>
       <c r="J34" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L34" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M34" t="s">
         <v>145</v>
@@ -4927,25 +4927,25 @@
         <v>160</v>
       </c>
       <c r="F35" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" t="s">
+        <v>143</v>
+      </c>
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" t="s">
         <v>161</v>
       </c>
-      <c r="G35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" t="s">
-        <v>144</v>
-      </c>
-      <c r="I35" t="s">
-        <v>20</v>
-      </c>
       <c r="J35" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L35" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M35" t="s">
         <v>145</v>
@@ -4968,25 +4968,25 @@
         <v>164</v>
       </c>
       <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" t="s">
+        <v>143</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" t="s">
         <v>165</v>
       </c>
-      <c r="G36" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" t="s">
-        <v>144</v>
-      </c>
-      <c r="I36" t="s">
-        <v>20</v>
-      </c>
       <c r="J36" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L36" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
         <v>145</v>
@@ -5009,25 +5009,25 @@
         <v>168</v>
       </c>
       <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" t="s">
+        <v>143</v>
+      </c>
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" t="s">
         <v>169</v>
       </c>
-      <c r="G37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" t="s">
-        <v>144</v>
-      </c>
-      <c r="I37" t="s">
-        <v>20</v>
-      </c>
       <c r="J37" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L37" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M37" t="s">
         <v>145</v>
@@ -5050,25 +5050,25 @@
         <v>172</v>
       </c>
       <c r="F38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" t="s">
+        <v>143</v>
+      </c>
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" t="s">
         <v>173</v>
       </c>
-      <c r="G38" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" t="s">
-        <v>20</v>
-      </c>
       <c r="J38" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L38" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
         <v>145</v>
@@ -5091,25 +5091,25 @@
         <v>176</v>
       </c>
       <c r="F39" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" t="s">
+        <v>143</v>
+      </c>
+      <c r="H39" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" t="s">
         <v>177</v>
       </c>
-      <c r="G39" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" t="s">
-        <v>144</v>
-      </c>
-      <c r="I39" t="s">
-        <v>20</v>
-      </c>
       <c r="J39" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L39" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
         <v>145</v>
@@ -5132,25 +5132,25 @@
         <v>180</v>
       </c>
       <c r="F40" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" t="s">
         <v>181</v>
       </c>
-      <c r="G40" t="s">
-        <v>19</v>
-      </c>
       <c r="H40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
         <v>182</v>
       </c>
-      <c r="I40" t="s">
-        <v>20</v>
-      </c>
       <c r="J40" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L40" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
         <v>183</v>
@@ -5173,25 +5173,25 @@
         <v>186</v>
       </c>
       <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" t="s">
+        <v>181</v>
+      </c>
+      <c r="H41" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" t="s">
         <v>187</v>
       </c>
-      <c r="G41" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" t="s">
-        <v>182</v>
-      </c>
-      <c r="I41" t="s">
-        <v>20</v>
-      </c>
       <c r="J41" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L41" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
         <v>183</v>
@@ -5214,25 +5214,25 @@
         <v>190</v>
       </c>
       <c r="F42" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" t="s">
+        <v>181</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" t="s">
         <v>191</v>
       </c>
-      <c r="G42" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" t="s">
-        <v>182</v>
-      </c>
-      <c r="I42" t="s">
-        <v>20</v>
-      </c>
       <c r="J42" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L42" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
         <v>183</v>
@@ -5255,25 +5255,25 @@
         <v>194</v>
       </c>
       <c r="F43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" t="s">
+        <v>181</v>
+      </c>
+      <c r="H43" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" t="s">
         <v>195</v>
       </c>
-      <c r="G43" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43" t="s">
-        <v>182</v>
-      </c>
-      <c r="I43" t="s">
-        <v>20</v>
-      </c>
       <c r="J43" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L43" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
         <v>183</v>
@@ -5296,25 +5296,25 @@
         <v>198</v>
       </c>
       <c r="F44" t="s">
+        <v>51</v>
+      </c>
+      <c r="G44" t="s">
+        <v>181</v>
+      </c>
+      <c r="H44" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" t="s">
         <v>199</v>
       </c>
-      <c r="G44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" t="s">
-        <v>182</v>
-      </c>
-      <c r="I44" t="s">
-        <v>20</v>
-      </c>
       <c r="J44" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L44" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
         <v>183</v>
@@ -5337,25 +5337,25 @@
         <v>202</v>
       </c>
       <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" t="s">
         <v>203</v>
       </c>
-      <c r="G45" t="s">
-        <v>19</v>
-      </c>
       <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
         <v>204</v>
       </c>
-      <c r="I45" t="s">
-        <v>20</v>
-      </c>
       <c r="J45" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L45" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
         <v>205</v>
@@ -5378,25 +5378,25 @@
         <v>208</v>
       </c>
       <c r="F46" t="s">
+        <v>51</v>
+      </c>
+      <c r="G46" t="s">
+        <v>203</v>
+      </c>
+      <c r="H46" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" t="s">
         <v>209</v>
       </c>
-      <c r="G46" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" t="s">
-        <v>204</v>
-      </c>
-      <c r="I46" t="s">
-        <v>20</v>
-      </c>
       <c r="J46" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L46" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
         <v>205</v>
@@ -5419,25 +5419,25 @@
         <v>212</v>
       </c>
       <c r="F47" t="s">
+        <v>51</v>
+      </c>
+      <c r="G47" t="s">
+        <v>203</v>
+      </c>
+      <c r="H47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" t="s">
         <v>213</v>
       </c>
-      <c r="G47" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" t="s">
-        <v>204</v>
-      </c>
-      <c r="I47" t="s">
-        <v>20</v>
-      </c>
       <c r="J47" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L47" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
         <v>205</v>
@@ -5460,25 +5460,25 @@
         <v>216</v>
       </c>
       <c r="F48" t="s">
+        <v>51</v>
+      </c>
+      <c r="G48" t="s">
+        <v>203</v>
+      </c>
+      <c r="H48" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" t="s">
         <v>217</v>
       </c>
-      <c r="G48" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" t="s">
-        <v>204</v>
-      </c>
-      <c r="I48" t="s">
-        <v>20</v>
-      </c>
       <c r="J48" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L48" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
         <v>205</v>
@@ -5501,25 +5501,25 @@
         <v>220</v>
       </c>
       <c r="F49" t="s">
+        <v>51</v>
+      </c>
+      <c r="G49" t="s">
+        <v>203</v>
+      </c>
+      <c r="H49" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" t="s">
         <v>221</v>
       </c>
-      <c r="G49" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" t="s">
-        <v>204</v>
-      </c>
-      <c r="I49" t="s">
-        <v>20</v>
-      </c>
       <c r="J49" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L49" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
         <v>205</v>
@@ -5542,25 +5542,25 @@
         <v>224</v>
       </c>
       <c r="F50" t="s">
+        <v>51</v>
+      </c>
+      <c r="G50" t="s">
+        <v>203</v>
+      </c>
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" t="s">
         <v>225</v>
       </c>
-      <c r="G50" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" t="s">
-        <v>204</v>
-      </c>
-      <c r="I50" t="s">
-        <v>20</v>
-      </c>
       <c r="J50" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L50" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M50" t="s">
         <v>205</v>
@@ -5583,25 +5583,25 @@
         <v>228</v>
       </c>
       <c r="F51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G51" t="s">
+        <v>203</v>
+      </c>
+      <c r="H51" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" t="s">
         <v>229</v>
       </c>
-      <c r="G51" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" t="s">
-        <v>204</v>
-      </c>
-      <c r="I51" t="s">
-        <v>20</v>
-      </c>
       <c r="J51" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L51" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
         <v>205</v>
@@ -5624,25 +5624,25 @@
         <v>232</v>
       </c>
       <c r="F52" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" t="s">
+        <v>203</v>
+      </c>
+      <c r="H52" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" t="s">
         <v>233</v>
       </c>
-      <c r="G52" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" t="s">
-        <v>204</v>
-      </c>
-      <c r="I52" t="s">
-        <v>20</v>
-      </c>
       <c r="J52" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L52" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
         <v>205</v>
@@ -5665,25 +5665,25 @@
         <v>236</v>
       </c>
       <c r="F53" t="s">
+        <v>51</v>
+      </c>
+      <c r="G53" t="s">
+        <v>203</v>
+      </c>
+      <c r="H53" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" t="s">
         <v>237</v>
       </c>
-      <c r="G53" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" t="s">
-        <v>204</v>
-      </c>
-      <c r="I53" t="s">
-        <v>20</v>
-      </c>
       <c r="J53" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L53" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M53" t="s">
         <v>205</v>
@@ -5706,25 +5706,25 @@
         <v>240</v>
       </c>
       <c r="F54" t="s">
+        <v>51</v>
+      </c>
+      <c r="G54" t="s">
+        <v>203</v>
+      </c>
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" t="s">
         <v>241</v>
       </c>
-      <c r="G54" t="s">
-        <v>19</v>
-      </c>
-      <c r="H54" t="s">
-        <v>204</v>
-      </c>
-      <c r="I54" t="s">
-        <v>20</v>
-      </c>
       <c r="J54" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L54" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
         <v>205</v>
@@ -5747,25 +5747,25 @@
         <v>244</v>
       </c>
       <c r="F55" t="s">
+        <v>51</v>
+      </c>
+      <c r="G55" t="s">
+        <v>203</v>
+      </c>
+      <c r="H55" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" t="s">
         <v>245</v>
       </c>
-      <c r="G55" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" t="s">
-        <v>204</v>
-      </c>
-      <c r="I55" t="s">
-        <v>20</v>
-      </c>
       <c r="J55" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L55" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M55" t="s">
         <v>205</v>
@@ -5788,25 +5788,25 @@
         <v>248</v>
       </c>
       <c r="F56" t="s">
+        <v>51</v>
+      </c>
+      <c r="G56" t="s">
+        <v>203</v>
+      </c>
+      <c r="H56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" t="s">
         <v>249</v>
       </c>
-      <c r="G56" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" t="s">
-        <v>204</v>
-      </c>
-      <c r="I56" t="s">
-        <v>20</v>
-      </c>
       <c r="J56" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L56" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
         <v>205</v>
@@ -5829,25 +5829,25 @@
         <v>252</v>
       </c>
       <c r="F57" t="s">
+        <v>51</v>
+      </c>
+      <c r="G57" t="s">
+        <v>203</v>
+      </c>
+      <c r="H57" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" t="s">
         <v>253</v>
       </c>
-      <c r="G57" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" t="s">
-        <v>204</v>
-      </c>
-      <c r="I57" t="s">
-        <v>20</v>
-      </c>
       <c r="J57" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L57" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
         <v>205</v>
@@ -5870,25 +5870,25 @@
         <v>256</v>
       </c>
       <c r="F58" t="s">
+        <v>51</v>
+      </c>
+      <c r="G58" t="s">
+        <v>203</v>
+      </c>
+      <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" t="s">
         <v>257</v>
       </c>
-      <c r="G58" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" t="s">
-        <v>204</v>
-      </c>
-      <c r="I58" t="s">
-        <v>20</v>
-      </c>
       <c r="J58" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L58" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
         <v>205</v>
@@ -5911,25 +5911,25 @@
         <v>260</v>
       </c>
       <c r="F59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G59" t="s">
+        <v>203</v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" t="s">
         <v>261</v>
       </c>
-      <c r="G59" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" t="s">
-        <v>204</v>
-      </c>
-      <c r="I59" t="s">
-        <v>20</v>
-      </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L59" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M59" t="s">
         <v>205</v>
@@ -5952,25 +5952,25 @@
         <v>264</v>
       </c>
       <c r="F60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G60" t="s">
+        <v>203</v>
+      </c>
+      <c r="H60" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" t="s">
         <v>265</v>
       </c>
-      <c r="G60" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" t="s">
-        <v>204</v>
-      </c>
-      <c r="I60" t="s">
-        <v>20</v>
-      </c>
       <c r="J60" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L60" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M60" t="s">
         <v>205</v>
@@ -5993,25 +5993,25 @@
         <v>268</v>
       </c>
       <c r="F61" t="s">
+        <v>51</v>
+      </c>
+      <c r="G61" t="s">
+        <v>203</v>
+      </c>
+      <c r="H61" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" t="s">
         <v>269</v>
       </c>
-      <c r="G61" t="s">
-        <v>19</v>
-      </c>
-      <c r="H61" t="s">
-        <v>204</v>
-      </c>
-      <c r="I61" t="s">
-        <v>20</v>
-      </c>
       <c r="J61" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L61" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M61" t="s">
         <v>205</v>
@@ -6037,22 +6037,22 @@
         <v>274</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="H62" t="s">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
         <v>276</v>
       </c>
       <c r="J62" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L62" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
         <v>279</v>
@@ -6075,25 +6075,25 @@
         <v>282</v>
       </c>
       <c r="F63" t="s">
+        <v>274</v>
+      </c>
+      <c r="G63" t="s">
+        <v>275</v>
+      </c>
+      <c r="H63" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" t="s">
         <v>283</v>
       </c>
-      <c r="G63" t="s">
-        <v>19</v>
-      </c>
-      <c r="H63" t="s">
-        <v>275</v>
-      </c>
-      <c r="I63" t="s">
-        <v>276</v>
-      </c>
       <c r="J63" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L63" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
         <v>279</v>
@@ -6116,25 +6116,25 @@
         <v>286</v>
       </c>
       <c r="F64" t="s">
+        <v>274</v>
+      </c>
+      <c r="G64" t="s">
+        <v>275</v>
+      </c>
+      <c r="H64" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" t="s">
         <v>287</v>
       </c>
-      <c r="G64" t="s">
-        <v>19</v>
-      </c>
-      <c r="H64" t="s">
-        <v>275</v>
-      </c>
-      <c r="I64" t="s">
-        <v>276</v>
-      </c>
       <c r="J64" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K64" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L64" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M64" t="s">
         <v>279</v>
@@ -6157,25 +6157,25 @@
         <v>290</v>
       </c>
       <c r="F65" t="s">
+        <v>274</v>
+      </c>
+      <c r="G65" t="s">
+        <v>275</v>
+      </c>
+      <c r="H65" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" t="s">
         <v>291</v>
       </c>
-      <c r="G65" t="s">
-        <v>19</v>
-      </c>
-      <c r="H65" t="s">
-        <v>275</v>
-      </c>
-      <c r="I65" t="s">
-        <v>276</v>
-      </c>
       <c r="J65" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L65" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M65" t="s">
         <v>279</v>
@@ -6198,25 +6198,25 @@
         <v>294</v>
       </c>
       <c r="F66" t="s">
+        <v>274</v>
+      </c>
+      <c r="G66" t="s">
+        <v>275</v>
+      </c>
+      <c r="H66" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" t="s">
         <v>295</v>
       </c>
-      <c r="G66" t="s">
-        <v>19</v>
-      </c>
-      <c r="H66" t="s">
-        <v>275</v>
-      </c>
-      <c r="I66" t="s">
-        <v>276</v>
-      </c>
       <c r="J66" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K66" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L66" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M66" t="s">
         <v>279</v>
@@ -6239,25 +6239,25 @@
         <v>298</v>
       </c>
       <c r="F67" t="s">
+        <v>274</v>
+      </c>
+      <c r="G67" t="s">
+        <v>275</v>
+      </c>
+      <c r="H67" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" t="s">
         <v>299</v>
       </c>
-      <c r="G67" t="s">
-        <v>19</v>
-      </c>
-      <c r="H67" t="s">
-        <v>275</v>
-      </c>
-      <c r="I67" t="s">
-        <v>276</v>
-      </c>
       <c r="J67" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L67" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M67" t="s">
         <v>279</v>
@@ -6280,25 +6280,25 @@
         <v>302</v>
       </c>
       <c r="F68" t="s">
+        <v>274</v>
+      </c>
+      <c r="G68" t="s">
+        <v>275</v>
+      </c>
+      <c r="H68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" t="s">
         <v>303</v>
       </c>
-      <c r="G68" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" t="s">
-        <v>275</v>
-      </c>
-      <c r="I68" t="s">
-        <v>276</v>
-      </c>
       <c r="J68" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L68" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M68" t="s">
         <v>279</v>
@@ -6321,25 +6321,25 @@
         <v>306</v>
       </c>
       <c r="F69" t="s">
+        <v>274</v>
+      </c>
+      <c r="G69" t="s">
+        <v>275</v>
+      </c>
+      <c r="H69" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" t="s">
         <v>307</v>
       </c>
-      <c r="G69" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" t="s">
-        <v>275</v>
-      </c>
-      <c r="I69" t="s">
-        <v>276</v>
-      </c>
       <c r="J69" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L69" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
         <v>279</v>
@@ -6362,25 +6362,25 @@
         <v>310</v>
       </c>
       <c r="F70" t="s">
+        <v>274</v>
+      </c>
+      <c r="G70" t="s">
+        <v>275</v>
+      </c>
+      <c r="H70" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" t="s">
         <v>311</v>
       </c>
-      <c r="G70" t="s">
-        <v>19</v>
-      </c>
-      <c r="H70" t="s">
-        <v>275</v>
-      </c>
-      <c r="I70" t="s">
-        <v>276</v>
-      </c>
       <c r="J70" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L70" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M70" t="s">
         <v>279</v>
@@ -6403,25 +6403,25 @@
         <v>314</v>
       </c>
       <c r="F71" t="s">
+        <v>274</v>
+      </c>
+      <c r="G71" t="s">
+        <v>275</v>
+      </c>
+      <c r="H71" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" t="s">
         <v>315</v>
       </c>
-      <c r="G71" t="s">
-        <v>19</v>
-      </c>
-      <c r="H71" t="s">
-        <v>275</v>
-      </c>
-      <c r="I71" t="s">
-        <v>276</v>
-      </c>
       <c r="J71" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K71" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L71" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M71" t="s">
         <v>279</v>
@@ -6444,25 +6444,25 @@
         <v>318</v>
       </c>
       <c r="F72" t="s">
+        <v>274</v>
+      </c>
+      <c r="G72" t="s">
+        <v>275</v>
+      </c>
+      <c r="H72" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" t="s">
         <v>319</v>
       </c>
-      <c r="G72" t="s">
-        <v>19</v>
-      </c>
-      <c r="H72" t="s">
-        <v>275</v>
-      </c>
-      <c r="I72" t="s">
-        <v>276</v>
-      </c>
       <c r="J72" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K72" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L72" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M72" t="s">
         <v>279</v>
@@ -6485,25 +6485,25 @@
         <v>322</v>
       </c>
       <c r="F73" t="s">
+        <v>274</v>
+      </c>
+      <c r="G73" t="s">
+        <v>275</v>
+      </c>
+      <c r="H73" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" t="s">
         <v>323</v>
       </c>
-      <c r="G73" t="s">
-        <v>19</v>
-      </c>
-      <c r="H73" t="s">
-        <v>275</v>
-      </c>
-      <c r="I73" t="s">
-        <v>276</v>
-      </c>
       <c r="J73" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L73" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
         <v>279</v>
@@ -6526,25 +6526,25 @@
         <v>326</v>
       </c>
       <c r="F74" t="s">
+        <v>274</v>
+      </c>
+      <c r="G74" t="s">
+        <v>275</v>
+      </c>
+      <c r="H74" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" t="s">
         <v>327</v>
       </c>
-      <c r="G74" t="s">
-        <v>19</v>
-      </c>
-      <c r="H74" t="s">
-        <v>275</v>
-      </c>
-      <c r="I74" t="s">
-        <v>276</v>
-      </c>
       <c r="J74" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L74" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M74" t="s">
         <v>279</v>
@@ -6567,25 +6567,25 @@
         <v>330</v>
       </c>
       <c r="F75" t="s">
+        <v>274</v>
+      </c>
+      <c r="G75" t="s">
+        <v>275</v>
+      </c>
+      <c r="H75" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" t="s">
         <v>331</v>
       </c>
-      <c r="G75" t="s">
-        <v>19</v>
-      </c>
-      <c r="H75" t="s">
-        <v>275</v>
-      </c>
-      <c r="I75" t="s">
-        <v>276</v>
-      </c>
       <c r="J75" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L75" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M75" t="s">
         <v>279</v>
@@ -6608,25 +6608,25 @@
         <v>334</v>
       </c>
       <c r="F76" t="s">
+        <v>274</v>
+      </c>
+      <c r="G76" t="s">
+        <v>275</v>
+      </c>
+      <c r="H76" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" t="s">
         <v>335</v>
       </c>
-      <c r="G76" t="s">
-        <v>19</v>
-      </c>
-      <c r="H76" t="s">
-        <v>275</v>
-      </c>
-      <c r="I76" t="s">
-        <v>276</v>
-      </c>
       <c r="J76" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K76" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L76" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M76" t="s">
         <v>279</v>
@@ -6649,25 +6649,25 @@
         <v>338</v>
       </c>
       <c r="F77" t="s">
+        <v>274</v>
+      </c>
+      <c r="G77" t="s">
+        <v>275</v>
+      </c>
+      <c r="H77" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" t="s">
         <v>339</v>
       </c>
-      <c r="G77" t="s">
-        <v>19</v>
-      </c>
-      <c r="H77" t="s">
-        <v>275</v>
-      </c>
-      <c r="I77" t="s">
-        <v>276</v>
-      </c>
       <c r="J77" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K77" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L77" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M77" t="s">
         <v>279</v>
@@ -6690,25 +6690,25 @@
         <v>342</v>
       </c>
       <c r="F78" t="s">
+        <v>274</v>
+      </c>
+      <c r="G78" t="s">
+        <v>275</v>
+      </c>
+      <c r="H78" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" t="s">
         <v>343</v>
       </c>
-      <c r="G78" t="s">
-        <v>19</v>
-      </c>
-      <c r="H78" t="s">
-        <v>275</v>
-      </c>
-      <c r="I78" t="s">
-        <v>276</v>
-      </c>
       <c r="J78" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L78" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M78" t="s">
         <v>279</v>
@@ -6731,25 +6731,25 @@
         <v>346</v>
       </c>
       <c r="F79" t="s">
+        <v>274</v>
+      </c>
+      <c r="G79" t="s">
+        <v>275</v>
+      </c>
+      <c r="H79" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" t="s">
         <v>347</v>
       </c>
-      <c r="G79" t="s">
-        <v>19</v>
-      </c>
-      <c r="H79" t="s">
-        <v>275</v>
-      </c>
-      <c r="I79" t="s">
-        <v>276</v>
-      </c>
       <c r="J79" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K79" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L79" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M79" t="s">
         <v>279</v>
@@ -6772,25 +6772,25 @@
         <v>350</v>
       </c>
       <c r="F80" t="s">
+        <v>274</v>
+      </c>
+      <c r="G80" t="s">
+        <v>275</v>
+      </c>
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" t="s">
         <v>351</v>
       </c>
-      <c r="G80" t="s">
-        <v>19</v>
-      </c>
-      <c r="H80" t="s">
-        <v>275</v>
-      </c>
-      <c r="I80" t="s">
-        <v>276</v>
-      </c>
       <c r="J80" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L80" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M80" t="s">
         <v>279</v>
@@ -6813,25 +6813,25 @@
         <v>354</v>
       </c>
       <c r="F81" t="s">
+        <v>274</v>
+      </c>
+      <c r="G81" t="s">
+        <v>275</v>
+      </c>
+      <c r="H81" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" t="s">
         <v>355</v>
       </c>
-      <c r="G81" t="s">
-        <v>19</v>
-      </c>
-      <c r="H81" t="s">
-        <v>275</v>
-      </c>
-      <c r="I81" t="s">
-        <v>276</v>
-      </c>
       <c r="J81" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L81" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M81" t="s">
         <v>279</v>
@@ -6854,25 +6854,25 @@
         <v>358</v>
       </c>
       <c r="F82" t="s">
+        <v>274</v>
+      </c>
+      <c r="G82" t="s">
+        <v>275</v>
+      </c>
+      <c r="H82" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" t="s">
         <v>359</v>
       </c>
-      <c r="G82" t="s">
-        <v>19</v>
-      </c>
-      <c r="H82" t="s">
-        <v>275</v>
-      </c>
-      <c r="I82" t="s">
-        <v>276</v>
-      </c>
       <c r="J82" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K82" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L82" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M82" t="s">
         <v>279</v>
@@ -6895,25 +6895,25 @@
         <v>362</v>
       </c>
       <c r="F83" t="s">
+        <v>274</v>
+      </c>
+      <c r="G83" t="s">
+        <v>275</v>
+      </c>
+      <c r="H83" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" t="s">
         <v>363</v>
       </c>
-      <c r="G83" t="s">
-        <v>19</v>
-      </c>
-      <c r="H83" t="s">
-        <v>275</v>
-      </c>
-      <c r="I83" t="s">
-        <v>276</v>
-      </c>
       <c r="J83" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L83" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M83" t="s">
         <v>279</v>
@@ -6936,25 +6936,25 @@
         <v>366</v>
       </c>
       <c r="F84" t="s">
+        <v>274</v>
+      </c>
+      <c r="G84" t="s">
+        <v>275</v>
+      </c>
+      <c r="H84" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" t="s">
         <v>367</v>
       </c>
-      <c r="G84" t="s">
-        <v>19</v>
-      </c>
-      <c r="H84" t="s">
-        <v>275</v>
-      </c>
-      <c r="I84" t="s">
-        <v>276</v>
-      </c>
       <c r="J84" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L84" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M84" t="s">
         <v>279</v>
@@ -6977,25 +6977,25 @@
         <v>370</v>
       </c>
       <c r="F85" t="s">
+        <v>274</v>
+      </c>
+      <c r="G85" t="s">
+        <v>275</v>
+      </c>
+      <c r="H85" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s">
         <v>371</v>
       </c>
-      <c r="G85" t="s">
-        <v>19</v>
-      </c>
-      <c r="H85" t="s">
-        <v>275</v>
-      </c>
-      <c r="I85" t="s">
-        <v>276</v>
-      </c>
       <c r="J85" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L85" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M85" t="s">
         <v>279</v>
@@ -7018,25 +7018,25 @@
         <v>374</v>
       </c>
       <c r="F86" t="s">
+        <v>274</v>
+      </c>
+      <c r="G86" t="s">
+        <v>275</v>
+      </c>
+      <c r="H86" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s">
         <v>375</v>
       </c>
-      <c r="G86" t="s">
-        <v>19</v>
-      </c>
-      <c r="H86" t="s">
-        <v>275</v>
-      </c>
-      <c r="I86" t="s">
-        <v>276</v>
-      </c>
       <c r="J86" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L86" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M86" t="s">
         <v>279</v>
@@ -7059,25 +7059,25 @@
         <v>378</v>
       </c>
       <c r="F87" t="s">
+        <v>274</v>
+      </c>
+      <c r="G87" t="s">
+        <v>275</v>
+      </c>
+      <c r="H87" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" t="s">
         <v>379</v>
       </c>
-      <c r="G87" t="s">
-        <v>19</v>
-      </c>
-      <c r="H87" t="s">
-        <v>275</v>
-      </c>
-      <c r="I87" t="s">
-        <v>276</v>
-      </c>
       <c r="J87" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K87" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L87" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M87" t="s">
         <v>279</v>
@@ -7100,25 +7100,25 @@
         <v>382</v>
       </c>
       <c r="F88" t="s">
+        <v>274</v>
+      </c>
+      <c r="G88" t="s">
+        <v>275</v>
+      </c>
+      <c r="H88" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" t="s">
         <v>383</v>
       </c>
-      <c r="G88" t="s">
-        <v>19</v>
-      </c>
-      <c r="H88" t="s">
-        <v>275</v>
-      </c>
-      <c r="I88" t="s">
-        <v>276</v>
-      </c>
       <c r="J88" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K88" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L88" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M88" t="s">
         <v>279</v>
@@ -7141,25 +7141,25 @@
         <v>386</v>
       </c>
       <c r="F89" t="s">
+        <v>274</v>
+      </c>
+      <c r="G89" t="s">
+        <v>275</v>
+      </c>
+      <c r="H89" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" t="s">
         <v>387</v>
       </c>
-      <c r="G89" t="s">
-        <v>19</v>
-      </c>
-      <c r="H89" t="s">
-        <v>275</v>
-      </c>
-      <c r="I89" t="s">
-        <v>276</v>
-      </c>
       <c r="J89" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L89" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M89" t="s">
         <v>279</v>
@@ -7182,25 +7182,25 @@
         <v>390</v>
       </c>
       <c r="F90" t="s">
+        <v>274</v>
+      </c>
+      <c r="G90" t="s">
         <v>391</v>
       </c>
-      <c r="G90" t="s">
-        <v>19</v>
-      </c>
       <c r="H90" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" t="s">
         <v>392</v>
       </c>
-      <c r="I90" t="s">
-        <v>276</v>
-      </c>
       <c r="J90" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K90" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L90" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M90" t="s">
         <v>393</v>
@@ -7223,25 +7223,25 @@
         <v>396</v>
       </c>
       <c r="F91" t="s">
+        <v>274</v>
+      </c>
+      <c r="G91" t="s">
+        <v>391</v>
+      </c>
+      <c r="H91" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" t="s">
         <v>397</v>
       </c>
-      <c r="G91" t="s">
-        <v>19</v>
-      </c>
-      <c r="H91" t="s">
-        <v>392</v>
-      </c>
-      <c r="I91" t="s">
-        <v>276</v>
-      </c>
       <c r="J91" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K91" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L91" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M91" t="s">
         <v>393</v>
@@ -7264,25 +7264,25 @@
         <v>400</v>
       </c>
       <c r="F92" t="s">
+        <v>274</v>
+      </c>
+      <c r="G92" t="s">
+        <v>391</v>
+      </c>
+      <c r="H92" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" t="s">
         <v>401</v>
       </c>
-      <c r="G92" t="s">
-        <v>19</v>
-      </c>
-      <c r="H92" t="s">
-        <v>392</v>
-      </c>
-      <c r="I92" t="s">
-        <v>276</v>
-      </c>
       <c r="J92" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L92" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M92" t="s">
         <v>393</v>
@@ -7305,25 +7305,25 @@
         <v>404</v>
       </c>
       <c r="F93" t="s">
+        <v>274</v>
+      </c>
+      <c r="G93" t="s">
+        <v>391</v>
+      </c>
+      <c r="H93" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" t="s">
         <v>405</v>
       </c>
-      <c r="G93" t="s">
-        <v>19</v>
-      </c>
-      <c r="H93" t="s">
-        <v>392</v>
-      </c>
-      <c r="I93" t="s">
-        <v>276</v>
-      </c>
       <c r="J93" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L93" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M93" t="s">
         <v>393</v>
@@ -7346,25 +7346,25 @@
         <v>408</v>
       </c>
       <c r="F94" t="s">
+        <v>274</v>
+      </c>
+      <c r="G94" t="s">
+        <v>391</v>
+      </c>
+      <c r="H94" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" t="s">
         <v>409</v>
       </c>
-      <c r="G94" t="s">
-        <v>19</v>
-      </c>
-      <c r="H94" t="s">
-        <v>392</v>
-      </c>
-      <c r="I94" t="s">
-        <v>276</v>
-      </c>
       <c r="J94" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K94" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L94" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M94" t="s">
         <v>393</v>
@@ -7387,25 +7387,25 @@
         <v>412</v>
       </c>
       <c r="F95" t="s">
+        <v>274</v>
+      </c>
+      <c r="G95" t="s">
+        <v>391</v>
+      </c>
+      <c r="H95" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95" t="s">
         <v>413</v>
       </c>
-      <c r="G95" t="s">
-        <v>19</v>
-      </c>
-      <c r="H95" t="s">
-        <v>392</v>
-      </c>
-      <c r="I95" t="s">
-        <v>276</v>
-      </c>
       <c r="J95" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K95" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L95" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M95" t="s">
         <v>393</v>
@@ -7428,25 +7428,25 @@
         <v>416</v>
       </c>
       <c r="F96" t="s">
+        <v>274</v>
+      </c>
+      <c r="G96" t="s">
+        <v>391</v>
+      </c>
+      <c r="H96" t="s">
+        <v>19</v>
+      </c>
+      <c r="I96" t="s">
         <v>417</v>
       </c>
-      <c r="G96" t="s">
-        <v>19</v>
-      </c>
-      <c r="H96" t="s">
-        <v>392</v>
-      </c>
-      <c r="I96" t="s">
-        <v>276</v>
-      </c>
       <c r="J96" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K96" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M96" t="s">
         <v>393</v>
@@ -7469,25 +7469,25 @@
         <v>420</v>
       </c>
       <c r="F97" t="s">
+        <v>274</v>
+      </c>
+      <c r="G97" t="s">
+        <v>391</v>
+      </c>
+      <c r="H97" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" t="s">
         <v>421</v>
       </c>
-      <c r="G97" t="s">
-        <v>19</v>
-      </c>
-      <c r="H97" t="s">
-        <v>392</v>
-      </c>
-      <c r="I97" t="s">
-        <v>276</v>
-      </c>
       <c r="J97" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L97" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M97" t="s">
         <v>393</v>
@@ -7510,25 +7510,25 @@
         <v>424</v>
       </c>
       <c r="F98" t="s">
+        <v>274</v>
+      </c>
+      <c r="G98" t="s">
         <v>425</v>
       </c>
-      <c r="G98" t="s">
-        <v>19</v>
-      </c>
       <c r="H98" t="s">
+        <v>19</v>
+      </c>
+      <c r="I98" t="s">
         <v>426</v>
       </c>
-      <c r="I98" t="s">
-        <v>276</v>
-      </c>
       <c r="J98" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K98" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L98" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M98" t="s">
         <v>427</v>
@@ -7551,25 +7551,25 @@
         <v>430</v>
       </c>
       <c r="F99" t="s">
+        <v>274</v>
+      </c>
+      <c r="G99" t="s">
+        <v>425</v>
+      </c>
+      <c r="H99" t="s">
+        <v>19</v>
+      </c>
+      <c r="I99" t="s">
         <v>431</v>
       </c>
-      <c r="G99" t="s">
-        <v>19</v>
-      </c>
-      <c r="H99" t="s">
-        <v>426</v>
-      </c>
-      <c r="I99" t="s">
-        <v>276</v>
-      </c>
       <c r="J99" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L99" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M99" t="s">
         <v>427</v>
@@ -7592,25 +7592,25 @@
         <v>434</v>
       </c>
       <c r="F100" t="s">
+        <v>274</v>
+      </c>
+      <c r="G100" t="s">
+        <v>425</v>
+      </c>
+      <c r="H100" t="s">
+        <v>19</v>
+      </c>
+      <c r="I100" t="s">
         <v>435</v>
       </c>
-      <c r="G100" t="s">
-        <v>19</v>
-      </c>
-      <c r="H100" t="s">
-        <v>426</v>
-      </c>
-      <c r="I100" t="s">
-        <v>276</v>
-      </c>
       <c r="J100" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L100" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M100" t="s">
         <v>427</v>
@@ -7633,25 +7633,25 @@
         <v>438</v>
       </c>
       <c r="F101" t="s">
+        <v>274</v>
+      </c>
+      <c r="G101" t="s">
+        <v>425</v>
+      </c>
+      <c r="H101" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101" t="s">
         <v>439</v>
       </c>
-      <c r="G101" t="s">
-        <v>19</v>
-      </c>
-      <c r="H101" t="s">
-        <v>426</v>
-      </c>
-      <c r="I101" t="s">
-        <v>276</v>
-      </c>
       <c r="J101" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L101" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M101" t="s">
         <v>427</v>
@@ -7674,25 +7674,25 @@
         <v>442</v>
       </c>
       <c r="F102" t="s">
+        <v>274</v>
+      </c>
+      <c r="G102" t="s">
+        <v>425</v>
+      </c>
+      <c r="H102" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102" t="s">
         <v>443</v>
       </c>
-      <c r="G102" t="s">
-        <v>19</v>
-      </c>
-      <c r="H102" t="s">
-        <v>426</v>
-      </c>
-      <c r="I102" t="s">
-        <v>276</v>
-      </c>
       <c r="J102" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L102" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M102" t="s">
         <v>427</v>
@@ -7715,25 +7715,25 @@
         <v>446</v>
       </c>
       <c r="F103" t="s">
+        <v>274</v>
+      </c>
+      <c r="G103" t="s">
+        <v>425</v>
+      </c>
+      <c r="H103" t="s">
+        <v>19</v>
+      </c>
+      <c r="I103" t="s">
         <v>447</v>
       </c>
-      <c r="G103" t="s">
-        <v>19</v>
-      </c>
-      <c r="H103" t="s">
-        <v>426</v>
-      </c>
-      <c r="I103" t="s">
-        <v>276</v>
-      </c>
       <c r="J103" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K103" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L103" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M103" t="s">
         <v>427</v>
@@ -7756,25 +7756,25 @@
         <v>450</v>
       </c>
       <c r="F104" t="s">
+        <v>274</v>
+      </c>
+      <c r="G104" t="s">
+        <v>425</v>
+      </c>
+      <c r="H104" t="s">
+        <v>19</v>
+      </c>
+      <c r="I104" t="s">
         <v>451</v>
       </c>
-      <c r="G104" t="s">
-        <v>19</v>
-      </c>
-      <c r="H104" t="s">
-        <v>426</v>
-      </c>
-      <c r="I104" t="s">
-        <v>276</v>
-      </c>
       <c r="J104" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K104" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L104" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M104" t="s">
         <v>427</v>
@@ -7797,25 +7797,25 @@
         <v>454</v>
       </c>
       <c r="F105" t="s">
+        <v>274</v>
+      </c>
+      <c r="G105" t="s">
+        <v>425</v>
+      </c>
+      <c r="H105" t="s">
+        <v>19</v>
+      </c>
+      <c r="I105" t="s">
         <v>455</v>
       </c>
-      <c r="G105" t="s">
-        <v>19</v>
-      </c>
-      <c r="H105" t="s">
-        <v>426</v>
-      </c>
-      <c r="I105" t="s">
-        <v>276</v>
-      </c>
       <c r="J105" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K105" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L105" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M105" t="s">
         <v>427</v>
@@ -7838,25 +7838,25 @@
         <v>458</v>
       </c>
       <c r="F106" t="s">
+        <v>274</v>
+      </c>
+      <c r="G106" t="s">
+        <v>425</v>
+      </c>
+      <c r="H106" t="s">
+        <v>19</v>
+      </c>
+      <c r="I106" t="s">
         <v>459</v>
       </c>
-      <c r="G106" t="s">
-        <v>19</v>
-      </c>
-      <c r="H106" t="s">
-        <v>426</v>
-      </c>
-      <c r="I106" t="s">
-        <v>276</v>
-      </c>
       <c r="J106" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K106" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L106" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M106" t="s">
         <v>427</v>
@@ -7879,25 +7879,25 @@
         <v>462</v>
       </c>
       <c r="F107" t="s">
+        <v>274</v>
+      </c>
+      <c r="G107" t="s">
+        <v>425</v>
+      </c>
+      <c r="H107" t="s">
+        <v>19</v>
+      </c>
+      <c r="I107" t="s">
         <v>463</v>
       </c>
-      <c r="G107" t="s">
-        <v>19</v>
-      </c>
-      <c r="H107" t="s">
-        <v>426</v>
-      </c>
-      <c r="I107" t="s">
-        <v>276</v>
-      </c>
       <c r="J107" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L107" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M107" t="s">
         <v>427</v>
@@ -7920,25 +7920,25 @@
         <v>466</v>
       </c>
       <c r="F108" t="s">
+        <v>274</v>
+      </c>
+      <c r="G108" t="s">
+        <v>425</v>
+      </c>
+      <c r="H108" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108" t="s">
         <v>467</v>
       </c>
-      <c r="G108" t="s">
-        <v>19</v>
-      </c>
-      <c r="H108" t="s">
-        <v>426</v>
-      </c>
-      <c r="I108" t="s">
-        <v>276</v>
-      </c>
       <c r="J108" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L108" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M108" t="s">
         <v>427</v>
@@ -7961,25 +7961,25 @@
         <v>470</v>
       </c>
       <c r="F109" t="s">
+        <v>274</v>
+      </c>
+      <c r="G109" t="s">
+        <v>425</v>
+      </c>
+      <c r="H109" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109" t="s">
         <v>471</v>
       </c>
-      <c r="G109" t="s">
-        <v>19</v>
-      </c>
-      <c r="H109" t="s">
-        <v>426</v>
-      </c>
-      <c r="I109" t="s">
-        <v>276</v>
-      </c>
       <c r="J109" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K109" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L109" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M109" t="s">
         <v>427</v>
@@ -8002,25 +8002,25 @@
         <v>474</v>
       </c>
       <c r="F110" t="s">
+        <v>274</v>
+      </c>
+      <c r="G110" t="s">
+        <v>425</v>
+      </c>
+      <c r="H110" t="s">
+        <v>19</v>
+      </c>
+      <c r="I110" t="s">
         <v>475</v>
       </c>
-      <c r="G110" t="s">
-        <v>19</v>
-      </c>
-      <c r="H110" t="s">
-        <v>426</v>
-      </c>
-      <c r="I110" t="s">
-        <v>276</v>
-      </c>
       <c r="J110" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L110" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M110" t="s">
         <v>427</v>
@@ -8043,25 +8043,25 @@
         <v>478</v>
       </c>
       <c r="F111" t="s">
+        <v>274</v>
+      </c>
+      <c r="G111" t="s">
+        <v>425</v>
+      </c>
+      <c r="H111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I111" t="s">
         <v>479</v>
       </c>
-      <c r="G111" t="s">
-        <v>19</v>
-      </c>
-      <c r="H111" t="s">
-        <v>426</v>
-      </c>
-      <c r="I111" t="s">
-        <v>276</v>
-      </c>
       <c r="J111" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L111" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M111" t="s">
         <v>427</v>
@@ -8084,25 +8084,25 @@
         <v>482</v>
       </c>
       <c r="F112" t="s">
+        <v>274</v>
+      </c>
+      <c r="G112" t="s">
+        <v>425</v>
+      </c>
+      <c r="H112" t="s">
+        <v>19</v>
+      </c>
+      <c r="I112" t="s">
         <v>483</v>
       </c>
-      <c r="G112" t="s">
-        <v>19</v>
-      </c>
-      <c r="H112" t="s">
-        <v>426</v>
-      </c>
-      <c r="I112" t="s">
-        <v>276</v>
-      </c>
       <c r="J112" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K112" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L112" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M112" t="s">
         <v>427</v>
@@ -8125,25 +8125,25 @@
         <v>486</v>
       </c>
       <c r="F113" t="s">
+        <v>274</v>
+      </c>
+      <c r="G113" t="s">
+        <v>425</v>
+      </c>
+      <c r="H113" t="s">
+        <v>19</v>
+      </c>
+      <c r="I113" t="s">
         <v>487</v>
       </c>
-      <c r="G113" t="s">
-        <v>19</v>
-      </c>
-      <c r="H113" t="s">
-        <v>426</v>
-      </c>
-      <c r="I113" t="s">
-        <v>276</v>
-      </c>
       <c r="J113" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L113" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="M113" t="s">
         <v>427</v>
@@ -8168,20 +8168,20 @@
       <c r="F114" t="s">
         <v>491</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>19</v>
       </c>
       <c r="I114" t="s">
-        <v>276</v>
+        <v>492</v>
       </c>
       <c r="J114" t="s">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="K114" t="s">
-        <v>492</v>
+        <v>278</v>
       </c>
       <c r="L114" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -8201,22 +8201,22 @@
         <v>496</v>
       </c>
       <c r="F115" t="s">
+        <v>491</v>
+      </c>
+      <c r="H115" t="s">
+        <v>19</v>
+      </c>
+      <c r="I115" t="s">
         <v>497</v>
       </c>
-      <c r="G115" t="s">
-        <v>19</v>
-      </c>
-      <c r="I115" t="s">
-        <v>276</v>
-      </c>
       <c r="J115" t="s">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="K115" t="s">
-        <v>492</v>
+        <v>278</v>
       </c>
       <c r="L115" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -8236,22 +8236,22 @@
         <v>500</v>
       </c>
       <c r="F116" t="s">
+        <v>491</v>
+      </c>
+      <c r="H116" t="s">
+        <v>19</v>
+      </c>
+      <c r="I116" t="s">
         <v>501</v>
       </c>
-      <c r="G116" t="s">
-        <v>19</v>
-      </c>
-      <c r="I116" t="s">
-        <v>276</v>
-      </c>
       <c r="J116" t="s">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="K116" t="s">
-        <v>492</v>
+        <v>278</v>
       </c>
       <c r="L116" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -8271,22 +8271,22 @@
         <v>504</v>
       </c>
       <c r="F117" t="s">
+        <v>491</v>
+      </c>
+      <c r="H117" t="s">
+        <v>19</v>
+      </c>
+      <c r="I117" t="s">
         <v>505</v>
       </c>
-      <c r="G117" t="s">
-        <v>19</v>
-      </c>
-      <c r="I117" t="s">
-        <v>276</v>
-      </c>
       <c r="J117" t="s">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="K117" t="s">
-        <v>492</v>
+        <v>278</v>
       </c>
       <c r="L117" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -8306,22 +8306,22 @@
         <v>508</v>
       </c>
       <c r="F118" t="s">
+        <v>491</v>
+      </c>
+      <c r="H118" t="s">
+        <v>19</v>
+      </c>
+      <c r="I118" t="s">
         <v>509</v>
       </c>
-      <c r="G118" t="s">
-        <v>19</v>
-      </c>
-      <c r="I118" t="s">
-        <v>276</v>
-      </c>
       <c r="J118" t="s">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="K118" t="s">
-        <v>492</v>
+        <v>278</v>
       </c>
       <c r="L118" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -8337,14 +8337,14 @@
       <c r="E119" t="s">
         <v>512</v>
       </c>
-      <c r="F119" t="s">
+      <c r="H119" t="s">
+        <v>19</v>
+      </c>
+      <c r="I119" t="s">
         <v>513</v>
       </c>
-      <c r="G119" t="s">
-        <v>19</v>
-      </c>
-      <c r="J119" t="s">
-        <v>21</v>
+      <c r="L119" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -8366,20 +8366,20 @@
       <c r="F120" t="s">
         <v>518</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>19</v>
       </c>
       <c r="I120" t="s">
         <v>519</v>
       </c>
       <c r="J120" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="K120" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L120" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -8399,22 +8399,22 @@
         <v>524</v>
       </c>
       <c r="F121" t="s">
+        <v>518</v>
+      </c>
+      <c r="H121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I121" t="s">
         <v>525</v>
       </c>
-      <c r="G121" t="s">
-        <v>19</v>
-      </c>
-      <c r="I121" t="s">
-        <v>519</v>
-      </c>
       <c r="J121" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="K121" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L121" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -8434,22 +8434,22 @@
         <v>528</v>
       </c>
       <c r="F122" t="s">
+        <v>518</v>
+      </c>
+      <c r="H122" t="s">
+        <v>19</v>
+      </c>
+      <c r="I122" t="s">
         <v>529</v>
       </c>
-      <c r="G122" t="s">
-        <v>19</v>
-      </c>
-      <c r="I122" t="s">
-        <v>519</v>
-      </c>
       <c r="J122" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="K122" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L122" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -8469,22 +8469,22 @@
         <v>532</v>
       </c>
       <c r="F123" t="s">
+        <v>518</v>
+      </c>
+      <c r="H123" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" t="s">
         <v>533</v>
       </c>
-      <c r="G123" t="s">
-        <v>19</v>
-      </c>
-      <c r="I123" t="s">
-        <v>519</v>
-      </c>
       <c r="J123" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="K123" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L123" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -8504,22 +8504,22 @@
         <v>536</v>
       </c>
       <c r="F124" t="s">
+        <v>518</v>
+      </c>
+      <c r="H124" t="s">
+        <v>19</v>
+      </c>
+      <c r="I124" t="s">
         <v>537</v>
       </c>
-      <c r="G124" t="s">
-        <v>19</v>
-      </c>
-      <c r="I124" t="s">
-        <v>519</v>
-      </c>
       <c r="J124" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="K124" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L124" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -8541,20 +8541,20 @@
       <c r="F125" t="s">
         <v>541</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>19</v>
       </c>
       <c r="I125" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="J125" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K125" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L125" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -8574,22 +8574,22 @@
         <v>546</v>
       </c>
       <c r="F126" t="s">
+        <v>541</v>
+      </c>
+      <c r="H126" t="s">
+        <v>19</v>
+      </c>
+      <c r="I126" t="s">
         <v>547</v>
       </c>
-      <c r="G126" t="s">
-        <v>19</v>
-      </c>
-      <c r="I126" t="s">
-        <v>519</v>
-      </c>
       <c r="J126" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K126" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L126" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -8609,22 +8609,22 @@
         <v>550</v>
       </c>
       <c r="F127" t="s">
+        <v>541</v>
+      </c>
+      <c r="H127" t="s">
+        <v>19</v>
+      </c>
+      <c r="I127" t="s">
         <v>551</v>
       </c>
-      <c r="G127" t="s">
-        <v>19</v>
-      </c>
-      <c r="I127" t="s">
-        <v>519</v>
-      </c>
       <c r="J127" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K127" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L127" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -8644,22 +8644,22 @@
         <v>554</v>
       </c>
       <c r="F128" t="s">
+        <v>541</v>
+      </c>
+      <c r="H128" t="s">
+        <v>19</v>
+      </c>
+      <c r="I128" t="s">
         <v>555</v>
       </c>
-      <c r="G128" t="s">
-        <v>19</v>
-      </c>
-      <c r="I128" t="s">
-        <v>519</v>
-      </c>
       <c r="J128" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K128" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L128" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -8679,22 +8679,22 @@
         <v>558</v>
       </c>
       <c r="F129" t="s">
+        <v>541</v>
+      </c>
+      <c r="H129" t="s">
+        <v>19</v>
+      </c>
+      <c r="I129" t="s">
         <v>559</v>
       </c>
-      <c r="G129" t="s">
-        <v>19</v>
-      </c>
-      <c r="I129" t="s">
-        <v>519</v>
-      </c>
       <c r="J129" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K129" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L129" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -8714,22 +8714,22 @@
         <v>562</v>
       </c>
       <c r="F130" t="s">
+        <v>541</v>
+      </c>
+      <c r="H130" t="s">
+        <v>19</v>
+      </c>
+      <c r="I130" t="s">
         <v>563</v>
       </c>
-      <c r="G130" t="s">
-        <v>19</v>
-      </c>
-      <c r="I130" t="s">
-        <v>519</v>
-      </c>
       <c r="J130" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K130" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L130" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -8749,22 +8749,22 @@
         <v>566</v>
       </c>
       <c r="F131" t="s">
+        <v>541</v>
+      </c>
+      <c r="H131" t="s">
+        <v>19</v>
+      </c>
+      <c r="I131" t="s">
         <v>567</v>
       </c>
-      <c r="G131" t="s">
-        <v>19</v>
-      </c>
-      <c r="I131" t="s">
-        <v>519</v>
-      </c>
       <c r="J131" t="s">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="K131" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="L131" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -8786,20 +8786,20 @@
       <c r="F132" t="s">
         <v>571</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>19</v>
       </c>
       <c r="I132" t="s">
-        <v>519</v>
+        <v>572</v>
       </c>
       <c r="J132" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K132" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L132" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -8819,22 +8819,22 @@
         <v>576</v>
       </c>
       <c r="F133" t="s">
+        <v>571</v>
+      </c>
+      <c r="H133" t="s">
+        <v>19</v>
+      </c>
+      <c r="I133" t="s">
         <v>577</v>
       </c>
-      <c r="G133" t="s">
-        <v>19</v>
-      </c>
-      <c r="I133" t="s">
-        <v>519</v>
-      </c>
       <c r="J133" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K133" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L133" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -8854,22 +8854,22 @@
         <v>580</v>
       </c>
       <c r="F134" t="s">
+        <v>571</v>
+      </c>
+      <c r="H134" t="s">
+        <v>19</v>
+      </c>
+      <c r="I134" t="s">
         <v>581</v>
       </c>
-      <c r="G134" t="s">
-        <v>19</v>
-      </c>
-      <c r="I134" t="s">
-        <v>519</v>
-      </c>
       <c r="J134" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K134" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L134" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -8889,22 +8889,22 @@
         <v>584</v>
       </c>
       <c r="F135" t="s">
+        <v>571</v>
+      </c>
+      <c r="H135" t="s">
+        <v>19</v>
+      </c>
+      <c r="I135" t="s">
         <v>585</v>
       </c>
-      <c r="G135" t="s">
-        <v>19</v>
-      </c>
-      <c r="I135" t="s">
-        <v>519</v>
-      </c>
       <c r="J135" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K135" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L135" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -8924,22 +8924,22 @@
         <v>588</v>
       </c>
       <c r="F136" t="s">
+        <v>571</v>
+      </c>
+      <c r="H136" t="s">
+        <v>19</v>
+      </c>
+      <c r="I136" t="s">
         <v>589</v>
       </c>
-      <c r="G136" t="s">
-        <v>19</v>
-      </c>
-      <c r="I136" t="s">
-        <v>519</v>
-      </c>
       <c r="J136" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K136" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L136" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -8959,22 +8959,22 @@
         <v>592</v>
       </c>
       <c r="F137" t="s">
+        <v>571</v>
+      </c>
+      <c r="H137" t="s">
+        <v>19</v>
+      </c>
+      <c r="I137" t="s">
         <v>593</v>
       </c>
-      <c r="G137" t="s">
-        <v>19</v>
-      </c>
-      <c r="I137" t="s">
-        <v>519</v>
-      </c>
       <c r="J137" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K137" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L137" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -8994,22 +8994,22 @@
         <v>596</v>
       </c>
       <c r="F138" t="s">
+        <v>571</v>
+      </c>
+      <c r="H138" t="s">
+        <v>19</v>
+      </c>
+      <c r="I138" t="s">
         <v>597</v>
       </c>
-      <c r="G138" t="s">
-        <v>19</v>
-      </c>
-      <c r="I138" t="s">
-        <v>519</v>
-      </c>
       <c r="J138" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K138" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L138" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -9029,22 +9029,22 @@
         <v>600</v>
       </c>
       <c r="F139" t="s">
+        <v>571</v>
+      </c>
+      <c r="H139" t="s">
+        <v>19</v>
+      </c>
+      <c r="I139" t="s">
         <v>601</v>
       </c>
-      <c r="G139" t="s">
-        <v>19</v>
-      </c>
-      <c r="I139" t="s">
-        <v>519</v>
-      </c>
       <c r="J139" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K139" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L139" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -9064,22 +9064,22 @@
         <v>604</v>
       </c>
       <c r="F140" t="s">
+        <v>571</v>
+      </c>
+      <c r="H140" t="s">
+        <v>19</v>
+      </c>
+      <c r="I140" t="s">
         <v>605</v>
       </c>
-      <c r="G140" t="s">
-        <v>19</v>
-      </c>
-      <c r="I140" t="s">
-        <v>519</v>
-      </c>
       <c r="J140" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K140" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L140" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -9099,22 +9099,22 @@
         <v>608</v>
       </c>
       <c r="F141" t="s">
+        <v>571</v>
+      </c>
+      <c r="H141" t="s">
+        <v>19</v>
+      </c>
+      <c r="I141" t="s">
         <v>609</v>
       </c>
-      <c r="G141" t="s">
-        <v>19</v>
-      </c>
-      <c r="I141" t="s">
-        <v>519</v>
-      </c>
       <c r="J141" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K141" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L141" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -9134,22 +9134,22 @@
         <v>612</v>
       </c>
       <c r="F142" t="s">
+        <v>571</v>
+      </c>
+      <c r="H142" t="s">
+        <v>19</v>
+      </c>
+      <c r="I142" t="s">
         <v>613</v>
       </c>
-      <c r="G142" t="s">
-        <v>19</v>
-      </c>
-      <c r="I142" t="s">
-        <v>519</v>
-      </c>
       <c r="J142" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="K142" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="L142" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -9171,20 +9171,20 @@
       <c r="F143" t="s">
         <v>617</v>
       </c>
-      <c r="G143" t="s">
+      <c r="H143" t="s">
         <v>19</v>
       </c>
       <c r="I143" t="s">
-        <v>519</v>
+        <v>618</v>
       </c>
       <c r="J143" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K143" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L143" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -9204,22 +9204,22 @@
         <v>622</v>
       </c>
       <c r="F144" t="s">
+        <v>617</v>
+      </c>
+      <c r="H144" t="s">
+        <v>19</v>
+      </c>
+      <c r="I144" t="s">
         <v>623</v>
       </c>
-      <c r="G144" t="s">
-        <v>19</v>
-      </c>
-      <c r="I144" t="s">
-        <v>519</v>
-      </c>
       <c r="J144" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K144" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L144" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -9239,22 +9239,22 @@
         <v>626</v>
       </c>
       <c r="F145" t="s">
+        <v>617</v>
+      </c>
+      <c r="H145" t="s">
+        <v>19</v>
+      </c>
+      <c r="I145" t="s">
         <v>627</v>
       </c>
-      <c r="G145" t="s">
-        <v>19</v>
-      </c>
-      <c r="I145" t="s">
-        <v>519</v>
-      </c>
       <c r="J145" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K145" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L145" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -9274,22 +9274,22 @@
         <v>630</v>
       </c>
       <c r="F146" t="s">
+        <v>617</v>
+      </c>
+      <c r="H146" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" t="s">
         <v>631</v>
       </c>
-      <c r="G146" t="s">
-        <v>19</v>
-      </c>
-      <c r="I146" t="s">
-        <v>519</v>
-      </c>
       <c r="J146" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K146" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L146" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -9309,22 +9309,22 @@
         <v>634</v>
       </c>
       <c r="F147" t="s">
+        <v>617</v>
+      </c>
+      <c r="H147" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" t="s">
         <v>635</v>
       </c>
-      <c r="G147" t="s">
-        <v>19</v>
-      </c>
-      <c r="I147" t="s">
-        <v>519</v>
-      </c>
       <c r="J147" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K147" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L147" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -9344,22 +9344,22 @@
         <v>638</v>
       </c>
       <c r="F148" t="s">
+        <v>617</v>
+      </c>
+      <c r="H148" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" t="s">
         <v>639</v>
       </c>
-      <c r="G148" t="s">
-        <v>19</v>
-      </c>
-      <c r="I148" t="s">
-        <v>519</v>
-      </c>
       <c r="J148" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K148" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L148" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -9379,22 +9379,22 @@
         <v>642</v>
       </c>
       <c r="F149" t="s">
+        <v>617</v>
+      </c>
+      <c r="H149" t="s">
+        <v>19</v>
+      </c>
+      <c r="I149" t="s">
         <v>643</v>
       </c>
-      <c r="G149" t="s">
-        <v>19</v>
-      </c>
-      <c r="I149" t="s">
-        <v>519</v>
-      </c>
       <c r="J149" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K149" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L149" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -9414,22 +9414,22 @@
         <v>646</v>
       </c>
       <c r="F150" t="s">
+        <v>617</v>
+      </c>
+      <c r="H150" t="s">
+        <v>19</v>
+      </c>
+      <c r="I150" t="s">
         <v>647</v>
       </c>
-      <c r="G150" t="s">
-        <v>19</v>
-      </c>
-      <c r="I150" t="s">
-        <v>519</v>
-      </c>
       <c r="J150" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K150" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L150" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -9449,22 +9449,22 @@
         <v>650</v>
       </c>
       <c r="F151" t="s">
+        <v>617</v>
+      </c>
+      <c r="H151" t="s">
+        <v>19</v>
+      </c>
+      <c r="I151" t="s">
         <v>651</v>
       </c>
-      <c r="G151" t="s">
-        <v>19</v>
-      </c>
-      <c r="I151" t="s">
-        <v>519</v>
-      </c>
       <c r="J151" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="K151" t="s">
-        <v>618</v>
+        <v>521</v>
       </c>
       <c r="L151" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -9486,20 +9486,20 @@
       <c r="F152" t="s">
         <v>655</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>19</v>
       </c>
       <c r="I152" t="s">
-        <v>519</v>
+        <v>656</v>
       </c>
       <c r="J152" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K152" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L152" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -9519,22 +9519,22 @@
         <v>660</v>
       </c>
       <c r="F153" t="s">
+        <v>655</v>
+      </c>
+      <c r="H153" t="s">
+        <v>19</v>
+      </c>
+      <c r="I153" t="s">
         <v>661</v>
       </c>
-      <c r="G153" t="s">
-        <v>19</v>
-      </c>
-      <c r="I153" t="s">
-        <v>519</v>
-      </c>
       <c r="J153" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K153" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L153" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -9554,22 +9554,22 @@
         <v>664</v>
       </c>
       <c r="F154" t="s">
+        <v>655</v>
+      </c>
+      <c r="H154" t="s">
+        <v>19</v>
+      </c>
+      <c r="I154" t="s">
         <v>665</v>
       </c>
-      <c r="G154" t="s">
-        <v>19</v>
-      </c>
-      <c r="I154" t="s">
-        <v>519</v>
-      </c>
       <c r="J154" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K154" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L154" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -9589,22 +9589,22 @@
         <v>668</v>
       </c>
       <c r="F155" t="s">
+        <v>655</v>
+      </c>
+      <c r="H155" t="s">
+        <v>19</v>
+      </c>
+      <c r="I155" t="s">
         <v>669</v>
       </c>
-      <c r="G155" t="s">
-        <v>19</v>
-      </c>
-      <c r="I155" t="s">
-        <v>519</v>
-      </c>
       <c r="J155" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K155" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L155" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -9624,22 +9624,22 @@
         <v>672</v>
       </c>
       <c r="F156" t="s">
+        <v>655</v>
+      </c>
+      <c r="H156" t="s">
+        <v>19</v>
+      </c>
+      <c r="I156" t="s">
         <v>673</v>
       </c>
-      <c r="G156" t="s">
-        <v>19</v>
-      </c>
-      <c r="I156" t="s">
-        <v>519</v>
-      </c>
       <c r="J156" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K156" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L156" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -9659,22 +9659,22 @@
         <v>676</v>
       </c>
       <c r="F157" t="s">
+        <v>655</v>
+      </c>
+      <c r="H157" t="s">
+        <v>19</v>
+      </c>
+      <c r="I157" t="s">
         <v>677</v>
       </c>
-      <c r="G157" t="s">
-        <v>19</v>
-      </c>
-      <c r="I157" t="s">
-        <v>519</v>
-      </c>
       <c r="J157" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K157" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L157" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -9694,22 +9694,22 @@
         <v>680</v>
       </c>
       <c r="F158" t="s">
+        <v>655</v>
+      </c>
+      <c r="H158" t="s">
+        <v>19</v>
+      </c>
+      <c r="I158" t="s">
         <v>681</v>
       </c>
-      <c r="G158" t="s">
-        <v>19</v>
-      </c>
-      <c r="I158" t="s">
-        <v>519</v>
-      </c>
       <c r="J158" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K158" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L158" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -9729,22 +9729,22 @@
         <v>684</v>
       </c>
       <c r="F159" t="s">
+        <v>655</v>
+      </c>
+      <c r="H159" t="s">
+        <v>19</v>
+      </c>
+      <c r="I159" t="s">
         <v>685</v>
       </c>
-      <c r="G159" t="s">
-        <v>19</v>
-      </c>
-      <c r="I159" t="s">
-        <v>519</v>
-      </c>
       <c r="J159" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K159" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L159" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -9764,22 +9764,22 @@
         <v>688</v>
       </c>
       <c r="F160" t="s">
+        <v>655</v>
+      </c>
+      <c r="H160" t="s">
+        <v>19</v>
+      </c>
+      <c r="I160" t="s">
         <v>689</v>
       </c>
-      <c r="G160" t="s">
-        <v>19</v>
-      </c>
-      <c r="I160" t="s">
-        <v>519</v>
-      </c>
       <c r="J160" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K160" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L160" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -9799,22 +9799,22 @@
         <v>692</v>
       </c>
       <c r="F161" t="s">
+        <v>655</v>
+      </c>
+      <c r="H161" t="s">
+        <v>19</v>
+      </c>
+      <c r="I161" t="s">
         <v>693</v>
       </c>
-      <c r="G161" t="s">
-        <v>19</v>
-      </c>
-      <c r="I161" t="s">
-        <v>519</v>
-      </c>
       <c r="J161" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K161" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L161" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -9834,22 +9834,22 @@
         <v>696</v>
       </c>
       <c r="F162" t="s">
+        <v>655</v>
+      </c>
+      <c r="H162" t="s">
+        <v>19</v>
+      </c>
+      <c r="I162" t="s">
         <v>697</v>
       </c>
-      <c r="G162" t="s">
-        <v>19</v>
-      </c>
-      <c r="I162" t="s">
-        <v>519</v>
-      </c>
       <c r="J162" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K162" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L162" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -9869,22 +9869,22 @@
         <v>700</v>
       </c>
       <c r="F163" t="s">
+        <v>655</v>
+      </c>
+      <c r="H163" t="s">
+        <v>19</v>
+      </c>
+      <c r="I163" t="s">
         <v>701</v>
       </c>
-      <c r="G163" t="s">
-        <v>19</v>
-      </c>
-      <c r="I163" t="s">
-        <v>519</v>
-      </c>
       <c r="J163" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K163" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L163" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -9904,22 +9904,22 @@
         <v>704</v>
       </c>
       <c r="F164" t="s">
+        <v>655</v>
+      </c>
+      <c r="H164" t="s">
+        <v>19</v>
+      </c>
+      <c r="I164" t="s">
         <v>705</v>
       </c>
-      <c r="G164" t="s">
-        <v>19</v>
-      </c>
-      <c r="I164" t="s">
-        <v>519</v>
-      </c>
       <c r="J164" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K164" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L164" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -9939,22 +9939,22 @@
         <v>708</v>
       </c>
       <c r="F165" t="s">
+        <v>655</v>
+      </c>
+      <c r="H165" t="s">
+        <v>19</v>
+      </c>
+      <c r="I165" t="s">
         <v>709</v>
       </c>
-      <c r="G165" t="s">
-        <v>19</v>
-      </c>
-      <c r="I165" t="s">
-        <v>519</v>
-      </c>
       <c r="J165" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K165" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L165" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -9974,22 +9974,22 @@
         <v>712</v>
       </c>
       <c r="F166" t="s">
+        <v>655</v>
+      </c>
+      <c r="H166" t="s">
+        <v>19</v>
+      </c>
+      <c r="I166" t="s">
         <v>713</v>
       </c>
-      <c r="G166" t="s">
-        <v>19</v>
-      </c>
-      <c r="I166" t="s">
-        <v>519</v>
-      </c>
       <c r="J166" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K166" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L166" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -10009,22 +10009,22 @@
         <v>716</v>
       </c>
       <c r="F167" t="s">
+        <v>655</v>
+      </c>
+      <c r="H167" t="s">
+        <v>19</v>
+      </c>
+      <c r="I167" t="s">
         <v>717</v>
       </c>
-      <c r="G167" t="s">
-        <v>19</v>
-      </c>
-      <c r="I167" t="s">
-        <v>519</v>
-      </c>
       <c r="J167" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K167" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L167" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -10044,22 +10044,22 @@
         <v>720</v>
       </c>
       <c r="F168" t="s">
+        <v>655</v>
+      </c>
+      <c r="H168" t="s">
+        <v>19</v>
+      </c>
+      <c r="I168" t="s">
         <v>721</v>
       </c>
-      <c r="G168" t="s">
-        <v>19</v>
-      </c>
-      <c r="I168" t="s">
-        <v>519</v>
-      </c>
       <c r="J168" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K168" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L168" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -10079,22 +10079,22 @@
         <v>724</v>
       </c>
       <c r="F169" t="s">
+        <v>655</v>
+      </c>
+      <c r="H169" t="s">
+        <v>19</v>
+      </c>
+      <c r="I169" t="s">
         <v>725</v>
       </c>
-      <c r="G169" t="s">
-        <v>19</v>
-      </c>
-      <c r="I169" t="s">
-        <v>519</v>
-      </c>
       <c r="J169" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="K169" t="s">
-        <v>656</v>
+        <v>521</v>
       </c>
       <c r="L169" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -10116,20 +10116,20 @@
       <c r="F170" t="s">
         <v>730</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>19</v>
       </c>
       <c r="I170" t="s">
         <v>731</v>
       </c>
       <c r="J170" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K170" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L170" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -10149,22 +10149,22 @@
         <v>736</v>
       </c>
       <c r="F171" t="s">
+        <v>730</v>
+      </c>
+      <c r="H171" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" t="s">
         <v>737</v>
       </c>
-      <c r="G171" t="s">
-        <v>19</v>
-      </c>
-      <c r="I171" t="s">
-        <v>731</v>
-      </c>
       <c r="J171" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K171" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L171" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -10184,22 +10184,22 @@
         <v>740</v>
       </c>
       <c r="F172" t="s">
+        <v>730</v>
+      </c>
+      <c r="H172" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" t="s">
         <v>741</v>
       </c>
-      <c r="G172" t="s">
-        <v>19</v>
-      </c>
-      <c r="I172" t="s">
-        <v>731</v>
-      </c>
       <c r="J172" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K172" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L172" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -10219,22 +10219,22 @@
         <v>744</v>
       </c>
       <c r="F173" t="s">
+        <v>730</v>
+      </c>
+      <c r="H173" t="s">
+        <v>19</v>
+      </c>
+      <c r="I173" t="s">
         <v>745</v>
       </c>
-      <c r="G173" t="s">
-        <v>19</v>
-      </c>
-      <c r="I173" t="s">
-        <v>731</v>
-      </c>
       <c r="J173" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K173" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L173" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -10254,22 +10254,22 @@
         <v>748</v>
       </c>
       <c r="F174" t="s">
+        <v>730</v>
+      </c>
+      <c r="H174" t="s">
+        <v>19</v>
+      </c>
+      <c r="I174" t="s">
         <v>749</v>
       </c>
-      <c r="G174" t="s">
-        <v>19</v>
-      </c>
-      <c r="I174" t="s">
-        <v>731</v>
-      </c>
       <c r="J174" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K174" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L174" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -10289,22 +10289,22 @@
         <v>752</v>
       </c>
       <c r="F175" t="s">
+        <v>730</v>
+      </c>
+      <c r="H175" t="s">
+        <v>19</v>
+      </c>
+      <c r="I175" t="s">
         <v>753</v>
       </c>
-      <c r="G175" t="s">
-        <v>19</v>
-      </c>
-      <c r="I175" t="s">
-        <v>731</v>
-      </c>
       <c r="J175" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K175" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L175" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -10324,22 +10324,22 @@
         <v>756</v>
       </c>
       <c r="F176" t="s">
+        <v>730</v>
+      </c>
+      <c r="H176" t="s">
+        <v>19</v>
+      </c>
+      <c r="I176" t="s">
         <v>757</v>
       </c>
-      <c r="G176" t="s">
-        <v>19</v>
-      </c>
-      <c r="I176" t="s">
-        <v>731</v>
-      </c>
       <c r="J176" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K176" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L176" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -10359,22 +10359,22 @@
         <v>760</v>
       </c>
       <c r="F177" t="s">
+        <v>730</v>
+      </c>
+      <c r="H177" t="s">
+        <v>19</v>
+      </c>
+      <c r="I177" t="s">
         <v>761</v>
       </c>
-      <c r="G177" t="s">
-        <v>19</v>
-      </c>
-      <c r="I177" t="s">
-        <v>731</v>
-      </c>
       <c r="J177" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K177" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L177" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -10394,22 +10394,22 @@
         <v>764</v>
       </c>
       <c r="F178" t="s">
+        <v>730</v>
+      </c>
+      <c r="H178" t="s">
+        <v>19</v>
+      </c>
+      <c r="I178" t="s">
         <v>765</v>
       </c>
-      <c r="G178" t="s">
-        <v>19</v>
-      </c>
-      <c r="I178" t="s">
-        <v>731</v>
-      </c>
       <c r="J178" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K178" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L178" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -10429,22 +10429,22 @@
         <v>768</v>
       </c>
       <c r="F179" t="s">
+        <v>730</v>
+      </c>
+      <c r="H179" t="s">
+        <v>19</v>
+      </c>
+      <c r="I179" t="s">
         <v>769</v>
       </c>
-      <c r="G179" t="s">
-        <v>19</v>
-      </c>
-      <c r="I179" t="s">
-        <v>731</v>
-      </c>
       <c r="J179" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="K179" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L179" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -10466,20 +10466,20 @@
       <c r="F180" t="s">
         <v>773</v>
       </c>
-      <c r="G180" t="s">
+      <c r="H180" t="s">
         <v>19</v>
       </c>
       <c r="I180" t="s">
-        <v>731</v>
+        <v>774</v>
       </c>
       <c r="J180" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K180" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L180" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -10499,25 +10499,25 @@
         <v>778</v>
       </c>
       <c r="F181" t="s">
+        <v>773</v>
+      </c>
+      <c r="G181" t="s">
         <v>779</v>
       </c>
-      <c r="G181" t="s">
-        <v>19</v>
-      </c>
       <c r="H181" t="s">
+        <v>19</v>
+      </c>
+      <c r="I181" t="s">
         <v>780</v>
       </c>
-      <c r="I181" t="s">
-        <v>731</v>
-      </c>
       <c r="J181" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K181" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L181" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
       <c r="M181" t="s">
         <v>781</v>
@@ -10540,25 +10540,25 @@
         <v>784</v>
       </c>
       <c r="F182" t="s">
+        <v>773</v>
+      </c>
+      <c r="G182" t="s">
+        <v>779</v>
+      </c>
+      <c r="H182" t="s">
+        <v>19</v>
+      </c>
+      <c r="I182" t="s">
         <v>785</v>
       </c>
-      <c r="G182" t="s">
-        <v>19</v>
-      </c>
-      <c r="H182" t="s">
-        <v>780</v>
-      </c>
-      <c r="I182" t="s">
-        <v>731</v>
-      </c>
       <c r="J182" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K182" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L182" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
       <c r="M182" t="s">
         <v>781</v>
@@ -10577,23 +10577,23 @@
       <c r="D183" t="s">
         <v>728</v>
       </c>
+      <c r="F183" t="s">
+        <v>773</v>
+      </c>
       <c r="G183" t="s">
-        <v>19</v>
+        <v>779</v>
       </c>
       <c r="H183" t="s">
-        <v>780</v>
-      </c>
-      <c r="I183" t="s">
-        <v>731</v>
+        <v>19</v>
       </c>
       <c r="J183" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K183" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L183" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
       <c r="M183" t="s">
         <v>781</v>
@@ -10616,22 +10616,22 @@
         <v>790</v>
       </c>
       <c r="F184" t="s">
+        <v>773</v>
+      </c>
+      <c r="H184" t="s">
+        <v>19</v>
+      </c>
+      <c r="I184" t="s">
         <v>791</v>
       </c>
-      <c r="G184" t="s">
-        <v>19</v>
-      </c>
-      <c r="I184" t="s">
-        <v>731</v>
-      </c>
       <c r="J184" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K184" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L184" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -10651,22 +10651,22 @@
         <v>794</v>
       </c>
       <c r="F185" t="s">
+        <v>773</v>
+      </c>
+      <c r="H185" t="s">
+        <v>19</v>
+      </c>
+      <c r="I185" t="s">
         <v>795</v>
       </c>
-      <c r="G185" t="s">
-        <v>19</v>
-      </c>
-      <c r="I185" t="s">
-        <v>731</v>
-      </c>
       <c r="J185" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K185" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L185" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -10686,22 +10686,22 @@
         <v>798</v>
       </c>
       <c r="F186" t="s">
+        <v>773</v>
+      </c>
+      <c r="H186" t="s">
+        <v>19</v>
+      </c>
+      <c r="I186" t="s">
         <v>799</v>
       </c>
-      <c r="G186" t="s">
-        <v>19</v>
-      </c>
-      <c r="I186" t="s">
-        <v>731</v>
-      </c>
       <c r="J186" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K186" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L186" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -10721,22 +10721,22 @@
         <v>802</v>
       </c>
       <c r="F187" t="s">
+        <v>773</v>
+      </c>
+      <c r="H187" t="s">
+        <v>19</v>
+      </c>
+      <c r="I187" t="s">
         <v>803</v>
       </c>
-      <c r="G187" t="s">
-        <v>19</v>
-      </c>
-      <c r="I187" t="s">
-        <v>731</v>
-      </c>
       <c r="J187" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K187" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L187" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -10756,22 +10756,22 @@
         <v>806</v>
       </c>
       <c r="F188" t="s">
+        <v>773</v>
+      </c>
+      <c r="H188" t="s">
+        <v>19</v>
+      </c>
+      <c r="I188" t="s">
         <v>807</v>
       </c>
-      <c r="G188" t="s">
-        <v>19</v>
-      </c>
-      <c r="I188" t="s">
-        <v>731</v>
-      </c>
       <c r="J188" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K188" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L188" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -10791,22 +10791,22 @@
         <v>810</v>
       </c>
       <c r="F189" t="s">
+        <v>773</v>
+      </c>
+      <c r="H189" t="s">
+        <v>19</v>
+      </c>
+      <c r="I189" t="s">
         <v>811</v>
       </c>
-      <c r="G189" t="s">
-        <v>19</v>
-      </c>
-      <c r="I189" t="s">
-        <v>731</v>
-      </c>
       <c r="J189" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K189" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L189" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -10826,22 +10826,22 @@
         <v>814</v>
       </c>
       <c r="F190" t="s">
+        <v>773</v>
+      </c>
+      <c r="H190" t="s">
+        <v>19</v>
+      </c>
+      <c r="I190" t="s">
         <v>815</v>
       </c>
-      <c r="G190" t="s">
-        <v>19</v>
-      </c>
-      <c r="I190" t="s">
-        <v>731</v>
-      </c>
       <c r="J190" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K190" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L190" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -10861,22 +10861,22 @@
         <v>818</v>
       </c>
       <c r="F191" t="s">
+        <v>773</v>
+      </c>
+      <c r="H191" t="s">
+        <v>19</v>
+      </c>
+      <c r="I191" t="s">
         <v>819</v>
       </c>
-      <c r="G191" t="s">
-        <v>19</v>
-      </c>
-      <c r="I191" t="s">
-        <v>731</v>
-      </c>
       <c r="J191" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K191" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L191" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -10896,22 +10896,22 @@
         <v>822</v>
       </c>
       <c r="F192" t="s">
+        <v>773</v>
+      </c>
+      <c r="H192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I192" t="s">
         <v>823</v>
       </c>
-      <c r="G192" t="s">
-        <v>19</v>
-      </c>
-      <c r="I192" t="s">
-        <v>731</v>
-      </c>
       <c r="J192" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K192" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L192" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -10931,22 +10931,22 @@
         <v>826</v>
       </c>
       <c r="F193" t="s">
+        <v>773</v>
+      </c>
+      <c r="H193" t="s">
+        <v>19</v>
+      </c>
+      <c r="I193" t="s">
         <v>827</v>
       </c>
-      <c r="G193" t="s">
-        <v>19</v>
-      </c>
-      <c r="I193" t="s">
-        <v>731</v>
-      </c>
       <c r="J193" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K193" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L193" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -10966,22 +10966,22 @@
         <v>830</v>
       </c>
       <c r="F194" t="s">
+        <v>773</v>
+      </c>
+      <c r="H194" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" t="s">
         <v>831</v>
       </c>
-      <c r="G194" t="s">
-        <v>19</v>
-      </c>
-      <c r="I194" t="s">
-        <v>731</v>
-      </c>
       <c r="J194" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K194" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L194" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -11001,22 +11001,22 @@
         <v>834</v>
       </c>
       <c r="F195" t="s">
+        <v>773</v>
+      </c>
+      <c r="H195" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" t="s">
         <v>835</v>
       </c>
-      <c r="G195" t="s">
-        <v>19</v>
-      </c>
-      <c r="I195" t="s">
-        <v>731</v>
-      </c>
       <c r="J195" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K195" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L195" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -11036,22 +11036,22 @@
         <v>838</v>
       </c>
       <c r="F196" t="s">
+        <v>773</v>
+      </c>
+      <c r="H196" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196" t="s">
         <v>839</v>
       </c>
-      <c r="G196" t="s">
-        <v>19</v>
-      </c>
-      <c r="I196" t="s">
-        <v>731</v>
-      </c>
       <c r="J196" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="K196" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="L196" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -11073,20 +11073,20 @@
       <c r="F197" t="s">
         <v>843</v>
       </c>
-      <c r="G197" t="s">
+      <c r="H197" t="s">
         <v>19</v>
       </c>
       <c r="I197" t="s">
-        <v>731</v>
+        <v>844</v>
       </c>
       <c r="J197" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K197" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L197" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -11106,22 +11106,22 @@
         <v>848</v>
       </c>
       <c r="F198" t="s">
+        <v>843</v>
+      </c>
+      <c r="H198" t="s">
+        <v>19</v>
+      </c>
+      <c r="I198" t="s">
         <v>849</v>
       </c>
-      <c r="G198" t="s">
-        <v>19</v>
-      </c>
-      <c r="I198" t="s">
-        <v>731</v>
-      </c>
       <c r="J198" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K198" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L198" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -11141,22 +11141,22 @@
         <v>852</v>
       </c>
       <c r="F199" t="s">
+        <v>843</v>
+      </c>
+      <c r="H199" t="s">
+        <v>19</v>
+      </c>
+      <c r="I199" t="s">
         <v>853</v>
       </c>
-      <c r="G199" t="s">
-        <v>19</v>
-      </c>
-      <c r="I199" t="s">
-        <v>731</v>
-      </c>
       <c r="J199" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K199" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L199" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -11176,22 +11176,22 @@
         <v>856</v>
       </c>
       <c r="F200" t="s">
+        <v>843</v>
+      </c>
+      <c r="H200" t="s">
+        <v>19</v>
+      </c>
+      <c r="I200" t="s">
         <v>857</v>
       </c>
-      <c r="G200" t="s">
-        <v>19</v>
-      </c>
-      <c r="I200" t="s">
-        <v>731</v>
-      </c>
       <c r="J200" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K200" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L200" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -11211,22 +11211,22 @@
         <v>860</v>
       </c>
       <c r="F201" t="s">
+        <v>843</v>
+      </c>
+      <c r="H201" t="s">
+        <v>19</v>
+      </c>
+      <c r="I201" t="s">
         <v>861</v>
       </c>
-      <c r="G201" t="s">
-        <v>19</v>
-      </c>
-      <c r="I201" t="s">
-        <v>731</v>
-      </c>
       <c r="J201" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K201" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L201" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -11246,22 +11246,22 @@
         <v>864</v>
       </c>
       <c r="F202" t="s">
+        <v>843</v>
+      </c>
+      <c r="H202" t="s">
+        <v>19</v>
+      </c>
+      <c r="I202" t="s">
         <v>865</v>
       </c>
-      <c r="G202" t="s">
-        <v>19</v>
-      </c>
-      <c r="I202" t="s">
-        <v>731</v>
-      </c>
       <c r="J202" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K202" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L202" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -11281,22 +11281,22 @@
         <v>868</v>
       </c>
       <c r="F203" t="s">
+        <v>843</v>
+      </c>
+      <c r="H203" t="s">
+        <v>19</v>
+      </c>
+      <c r="I203" t="s">
         <v>869</v>
       </c>
-      <c r="G203" t="s">
-        <v>19</v>
-      </c>
-      <c r="I203" t="s">
-        <v>731</v>
-      </c>
       <c r="J203" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K203" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L203" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -11316,22 +11316,22 @@
         <v>872</v>
       </c>
       <c r="F204" t="s">
+        <v>843</v>
+      </c>
+      <c r="H204" t="s">
+        <v>19</v>
+      </c>
+      <c r="I204" t="s">
         <v>873</v>
       </c>
-      <c r="G204" t="s">
-        <v>19</v>
-      </c>
-      <c r="I204" t="s">
-        <v>731</v>
-      </c>
       <c r="J204" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K204" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L204" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -11351,22 +11351,22 @@
         <v>876</v>
       </c>
       <c r="F205" t="s">
+        <v>843</v>
+      </c>
+      <c r="H205" t="s">
+        <v>19</v>
+      </c>
+      <c r="I205" t="s">
         <v>877</v>
       </c>
-      <c r="G205" t="s">
-        <v>19</v>
-      </c>
-      <c r="I205" t="s">
-        <v>731</v>
-      </c>
       <c r="J205" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K205" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L205" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -11386,22 +11386,22 @@
         <v>880</v>
       </c>
       <c r="F206" t="s">
+        <v>843</v>
+      </c>
+      <c r="H206" t="s">
+        <v>19</v>
+      </c>
+      <c r="I206" t="s">
         <v>881</v>
       </c>
-      <c r="G206" t="s">
-        <v>19</v>
-      </c>
-      <c r="I206" t="s">
-        <v>731</v>
-      </c>
       <c r="J206" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K206" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L206" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -11421,22 +11421,22 @@
         <v>884</v>
       </c>
       <c r="F207" t="s">
+        <v>843</v>
+      </c>
+      <c r="H207" t="s">
+        <v>19</v>
+      </c>
+      <c r="I207" t="s">
         <v>885</v>
       </c>
-      <c r="G207" t="s">
-        <v>19</v>
-      </c>
-      <c r="I207" t="s">
-        <v>731</v>
-      </c>
       <c r="J207" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K207" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L207" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -11456,22 +11456,22 @@
         <v>888</v>
       </c>
       <c r="F208" t="s">
+        <v>843</v>
+      </c>
+      <c r="H208" t="s">
+        <v>19</v>
+      </c>
+      <c r="I208" t="s">
         <v>889</v>
       </c>
-      <c r="G208" t="s">
-        <v>19</v>
-      </c>
-      <c r="I208" t="s">
-        <v>731</v>
-      </c>
       <c r="J208" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K208" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L208" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -11491,22 +11491,22 @@
         <v>892</v>
       </c>
       <c r="F209" t="s">
+        <v>843</v>
+      </c>
+      <c r="H209" t="s">
+        <v>19</v>
+      </c>
+      <c r="I209" t="s">
         <v>893</v>
       </c>
-      <c r="G209" t="s">
-        <v>19</v>
-      </c>
-      <c r="I209" t="s">
-        <v>731</v>
-      </c>
       <c r="J209" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K209" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L209" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -11526,22 +11526,22 @@
         <v>896</v>
       </c>
       <c r="F210" t="s">
+        <v>843</v>
+      </c>
+      <c r="H210" t="s">
+        <v>19</v>
+      </c>
+      <c r="I210" t="s">
         <v>897</v>
       </c>
-      <c r="G210" t="s">
-        <v>19</v>
-      </c>
-      <c r="I210" t="s">
-        <v>731</v>
-      </c>
       <c r="J210" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K210" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L210" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -11561,22 +11561,22 @@
         <v>900</v>
       </c>
       <c r="F211" t="s">
+        <v>843</v>
+      </c>
+      <c r="H211" t="s">
+        <v>19</v>
+      </c>
+      <c r="I211" t="s">
         <v>901</v>
       </c>
-      <c r="G211" t="s">
-        <v>19</v>
-      </c>
-      <c r="I211" t="s">
-        <v>731</v>
-      </c>
       <c r="J211" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K211" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L211" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -11596,22 +11596,22 @@
         <v>904</v>
       </c>
       <c r="F212" t="s">
+        <v>843</v>
+      </c>
+      <c r="H212" t="s">
+        <v>19</v>
+      </c>
+      <c r="I212" t="s">
         <v>905</v>
       </c>
-      <c r="G212" t="s">
-        <v>19</v>
-      </c>
-      <c r="I212" t="s">
-        <v>731</v>
-      </c>
       <c r="J212" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="K212" t="s">
-        <v>844</v>
+        <v>733</v>
       </c>
       <c r="L212" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -11633,20 +11633,20 @@
       <c r="F213" t="s">
         <v>909</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>19</v>
       </c>
       <c r="I213" t="s">
-        <v>731</v>
+        <v>910</v>
       </c>
       <c r="J213" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K213" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L213" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -11666,22 +11666,22 @@
         <v>914</v>
       </c>
       <c r="F214" t="s">
+        <v>909</v>
+      </c>
+      <c r="H214" t="s">
+        <v>19</v>
+      </c>
+      <c r="I214" t="s">
         <v>915</v>
       </c>
-      <c r="G214" t="s">
-        <v>19</v>
-      </c>
-      <c r="I214" t="s">
-        <v>731</v>
-      </c>
       <c r="J214" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K214" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L214" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -11701,22 +11701,22 @@
         <v>918</v>
       </c>
       <c r="F215" t="s">
+        <v>909</v>
+      </c>
+      <c r="H215" t="s">
+        <v>19</v>
+      </c>
+      <c r="I215" t="s">
         <v>919</v>
       </c>
-      <c r="G215" t="s">
-        <v>19</v>
-      </c>
-      <c r="I215" t="s">
-        <v>731</v>
-      </c>
       <c r="J215" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K215" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L215" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -11736,22 +11736,22 @@
         <v>922</v>
       </c>
       <c r="F216" t="s">
+        <v>909</v>
+      </c>
+      <c r="H216" t="s">
+        <v>19</v>
+      </c>
+      <c r="I216" t="s">
         <v>923</v>
       </c>
-      <c r="G216" t="s">
-        <v>19</v>
-      </c>
-      <c r="I216" t="s">
-        <v>731</v>
-      </c>
       <c r="J216" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K216" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L216" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -11771,22 +11771,22 @@
         <v>926</v>
       </c>
       <c r="F217" t="s">
+        <v>909</v>
+      </c>
+      <c r="H217" t="s">
+        <v>19</v>
+      </c>
+      <c r="I217" t="s">
         <v>927</v>
       </c>
-      <c r="G217" t="s">
-        <v>19</v>
-      </c>
-      <c r="I217" t="s">
-        <v>731</v>
-      </c>
       <c r="J217" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K217" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L217" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -11806,22 +11806,22 @@
         <v>930</v>
       </c>
       <c r="F218" t="s">
+        <v>909</v>
+      </c>
+      <c r="H218" t="s">
+        <v>19</v>
+      </c>
+      <c r="I218" t="s">
         <v>931</v>
       </c>
-      <c r="G218" t="s">
-        <v>19</v>
-      </c>
-      <c r="I218" t="s">
-        <v>731</v>
-      </c>
       <c r="J218" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K218" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L218" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -11841,22 +11841,22 @@
         <v>934</v>
       </c>
       <c r="F219" t="s">
+        <v>909</v>
+      </c>
+      <c r="H219" t="s">
+        <v>19</v>
+      </c>
+      <c r="I219" t="s">
         <v>935</v>
       </c>
-      <c r="G219" t="s">
-        <v>19</v>
-      </c>
-      <c r="I219" t="s">
-        <v>731</v>
-      </c>
       <c r="J219" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K219" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L219" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -11876,22 +11876,22 @@
         <v>938</v>
       </c>
       <c r="F220" t="s">
+        <v>909</v>
+      </c>
+      <c r="H220" t="s">
+        <v>19</v>
+      </c>
+      <c r="I220" t="s">
         <v>939</v>
       </c>
-      <c r="G220" t="s">
-        <v>19</v>
-      </c>
-      <c r="I220" t="s">
-        <v>731</v>
-      </c>
       <c r="J220" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K220" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L220" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -11911,22 +11911,22 @@
         <v>942</v>
       </c>
       <c r="F221" t="s">
+        <v>909</v>
+      </c>
+      <c r="H221" t="s">
+        <v>19</v>
+      </c>
+      <c r="I221" t="s">
         <v>943</v>
       </c>
-      <c r="G221" t="s">
-        <v>19</v>
-      </c>
-      <c r="I221" t="s">
-        <v>731</v>
-      </c>
       <c r="J221" t="s">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="K221" t="s">
-        <v>910</v>
+        <v>733</v>
       </c>
       <c r="L221" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -11948,20 +11948,20 @@
       <c r="F222" t="s">
         <v>948</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>19</v>
       </c>
       <c r="I222" t="s">
         <v>949</v>
       </c>
       <c r="J222" t="s">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="K222" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L222" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -11981,22 +11981,22 @@
         <v>954</v>
       </c>
       <c r="F223" t="s">
+        <v>948</v>
+      </c>
+      <c r="H223" t="s">
+        <v>19</v>
+      </c>
+      <c r="I223" t="s">
         <v>955</v>
       </c>
-      <c r="G223" t="s">
-        <v>19</v>
-      </c>
-      <c r="I223" t="s">
-        <v>949</v>
-      </c>
       <c r="J223" t="s">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="K223" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L223" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -12016,22 +12016,22 @@
         <v>958</v>
       </c>
       <c r="F224" t="s">
+        <v>948</v>
+      </c>
+      <c r="H224" t="s">
+        <v>19</v>
+      </c>
+      <c r="I224" t="s">
         <v>959</v>
       </c>
-      <c r="G224" t="s">
-        <v>19</v>
-      </c>
-      <c r="I224" t="s">
-        <v>949</v>
-      </c>
       <c r="J224" t="s">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="K224" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L224" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -12051,22 +12051,22 @@
         <v>962</v>
       </c>
       <c r="F225" t="s">
+        <v>948</v>
+      </c>
+      <c r="H225" t="s">
+        <v>19</v>
+      </c>
+      <c r="I225" t="s">
         <v>963</v>
       </c>
-      <c r="G225" t="s">
-        <v>19</v>
-      </c>
-      <c r="I225" t="s">
-        <v>949</v>
-      </c>
       <c r="J225" t="s">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="K225" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L225" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -12086,22 +12086,22 @@
         <v>966</v>
       </c>
       <c r="F226" t="s">
+        <v>948</v>
+      </c>
+      <c r="H226" t="s">
+        <v>19</v>
+      </c>
+      <c r="I226" t="s">
         <v>967</v>
       </c>
-      <c r="G226" t="s">
-        <v>19</v>
-      </c>
-      <c r="I226" t="s">
-        <v>949</v>
-      </c>
       <c r="J226" t="s">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="K226" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L226" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -12121,22 +12121,22 @@
         <v>970</v>
       </c>
       <c r="F227" t="s">
+        <v>948</v>
+      </c>
+      <c r="H227" t="s">
+        <v>19</v>
+      </c>
+      <c r="I227" t="s">
         <v>971</v>
       </c>
-      <c r="G227" t="s">
-        <v>19</v>
-      </c>
-      <c r="I227" t="s">
-        <v>949</v>
-      </c>
       <c r="J227" t="s">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="K227" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L227" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -12158,20 +12158,20 @@
       <c r="F228" t="s">
         <v>975</v>
       </c>
-      <c r="G228" t="s">
+      <c r="H228" t="s">
         <v>19</v>
       </c>
       <c r="I228" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="J228" t="s">
-        <v>21</v>
+        <v>977</v>
       </c>
       <c r="K228" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="L228" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -12191,22 +12191,22 @@
         <v>980</v>
       </c>
       <c r="F229" t="s">
+        <v>975</v>
+      </c>
+      <c r="H229" t="s">
+        <v>19</v>
+      </c>
+      <c r="I229" t="s">
         <v>981</v>
       </c>
-      <c r="G229" t="s">
-        <v>19</v>
-      </c>
-      <c r="I229" t="s">
-        <v>949</v>
-      </c>
       <c r="J229" t="s">
-        <v>21</v>
+        <v>977</v>
       </c>
       <c r="K229" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="L229" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -12226,22 +12226,22 @@
         <v>984</v>
       </c>
       <c r="F230" t="s">
+        <v>975</v>
+      </c>
+      <c r="H230" t="s">
+        <v>19</v>
+      </c>
+      <c r="I230" t="s">
         <v>985</v>
       </c>
-      <c r="G230" t="s">
-        <v>19</v>
-      </c>
-      <c r="I230" t="s">
-        <v>949</v>
-      </c>
       <c r="J230" t="s">
-        <v>21</v>
+        <v>977</v>
       </c>
       <c r="K230" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="L230" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -12261,22 +12261,22 @@
         <v>988</v>
       </c>
       <c r="F231" t="s">
+        <v>975</v>
+      </c>
+      <c r="H231" t="s">
+        <v>19</v>
+      </c>
+      <c r="I231" t="s">
         <v>989</v>
       </c>
-      <c r="G231" t="s">
-        <v>19</v>
-      </c>
-      <c r="I231" t="s">
-        <v>949</v>
-      </c>
       <c r="J231" t="s">
-        <v>21</v>
+        <v>977</v>
       </c>
       <c r="K231" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="L231" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -12296,22 +12296,22 @@
         <v>992</v>
       </c>
       <c r="F232" t="s">
+        <v>975</v>
+      </c>
+      <c r="H232" t="s">
+        <v>19</v>
+      </c>
+      <c r="I232" t="s">
         <v>993</v>
       </c>
-      <c r="G232" t="s">
-        <v>19</v>
-      </c>
-      <c r="I232" t="s">
-        <v>949</v>
-      </c>
       <c r="J232" t="s">
-        <v>21</v>
+        <v>977</v>
       </c>
       <c r="K232" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="L232" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -12333,20 +12333,20 @@
       <c r="F233" t="s">
         <v>997</v>
       </c>
-      <c r="G233" t="s">
+      <c r="H233" t="s">
         <v>19</v>
       </c>
       <c r="I233" t="s">
-        <v>949</v>
+        <v>998</v>
       </c>
       <c r="J233" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K233" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L233" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -12366,22 +12366,22 @@
         <v>1002</v>
       </c>
       <c r="F234" t="s">
+        <v>997</v>
+      </c>
+      <c r="H234" t="s">
+        <v>19</v>
+      </c>
+      <c r="I234" t="s">
         <v>1003</v>
       </c>
-      <c r="G234" t="s">
-        <v>19</v>
-      </c>
-      <c r="I234" t="s">
-        <v>949</v>
-      </c>
       <c r="J234" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K234" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L234" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -12401,22 +12401,22 @@
         <v>1006</v>
       </c>
       <c r="F235" t="s">
+        <v>997</v>
+      </c>
+      <c r="H235" t="s">
+        <v>19</v>
+      </c>
+      <c r="I235" t="s">
         <v>1007</v>
       </c>
-      <c r="G235" t="s">
-        <v>19</v>
-      </c>
-      <c r="I235" t="s">
-        <v>949</v>
-      </c>
       <c r="J235" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K235" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L235" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -12436,22 +12436,22 @@
         <v>1010</v>
       </c>
       <c r="F236" t="s">
+        <v>997</v>
+      </c>
+      <c r="H236" t="s">
+        <v>19</v>
+      </c>
+      <c r="I236" t="s">
         <v>1011</v>
       </c>
-      <c r="G236" t="s">
-        <v>19</v>
-      </c>
-      <c r="I236" t="s">
-        <v>949</v>
-      </c>
       <c r="J236" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K236" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L236" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -12471,22 +12471,22 @@
         <v>1014</v>
       </c>
       <c r="F237" t="s">
+        <v>997</v>
+      </c>
+      <c r="H237" t="s">
+        <v>19</v>
+      </c>
+      <c r="I237" t="s">
         <v>1015</v>
       </c>
-      <c r="G237" t="s">
-        <v>19</v>
-      </c>
-      <c r="I237" t="s">
-        <v>949</v>
-      </c>
       <c r="J237" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K237" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L237" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -12506,22 +12506,22 @@
         <v>1018</v>
       </c>
       <c r="F238" t="s">
+        <v>997</v>
+      </c>
+      <c r="H238" t="s">
+        <v>19</v>
+      </c>
+      <c r="I238" t="s">
         <v>1019</v>
       </c>
-      <c r="G238" t="s">
-        <v>19</v>
-      </c>
-      <c r="I238" t="s">
-        <v>949</v>
-      </c>
       <c r="J238" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K238" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L238" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -12541,22 +12541,22 @@
         <v>1022</v>
       </c>
       <c r="F239" t="s">
+        <v>997</v>
+      </c>
+      <c r="H239" t="s">
+        <v>19</v>
+      </c>
+      <c r="I239" t="s">
         <v>1023</v>
       </c>
-      <c r="G239" t="s">
-        <v>19</v>
-      </c>
-      <c r="I239" t="s">
-        <v>949</v>
-      </c>
       <c r="J239" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K239" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L239" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -12576,22 +12576,22 @@
         <v>1026</v>
       </c>
       <c r="F240" t="s">
+        <v>997</v>
+      </c>
+      <c r="H240" t="s">
+        <v>19</v>
+      </c>
+      <c r="I240" t="s">
         <v>1027</v>
       </c>
-      <c r="G240" t="s">
-        <v>19</v>
-      </c>
-      <c r="I240" t="s">
-        <v>949</v>
-      </c>
       <c r="J240" t="s">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="K240" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
       <c r="L240" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -12613,20 +12613,20 @@
       <c r="F241" t="s">
         <v>1031</v>
       </c>
-      <c r="G241" t="s">
+      <c r="H241" t="s">
         <v>19</v>
       </c>
       <c r="I241" t="s">
-        <v>949</v>
+        <v>1032</v>
       </c>
       <c r="J241" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K241" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L241" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -12646,22 +12646,22 @@
         <v>1036</v>
       </c>
       <c r="F242" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H242" t="s">
+        <v>19</v>
+      </c>
+      <c r="I242" t="s">
         <v>1037</v>
       </c>
-      <c r="G242" t="s">
-        <v>19</v>
-      </c>
-      <c r="I242" t="s">
-        <v>949</v>
-      </c>
       <c r="J242" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K242" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L242" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -12681,22 +12681,22 @@
         <v>1040</v>
       </c>
       <c r="F243" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H243" t="s">
+        <v>19</v>
+      </c>
+      <c r="I243" t="s">
         <v>1041</v>
       </c>
-      <c r="G243" t="s">
-        <v>19</v>
-      </c>
-      <c r="I243" t="s">
-        <v>949</v>
-      </c>
       <c r="J243" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K243" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L243" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -12716,22 +12716,22 @@
         <v>1044</v>
       </c>
       <c r="F244" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H244" t="s">
+        <v>19</v>
+      </c>
+      <c r="I244" t="s">
         <v>1045</v>
       </c>
-      <c r="G244" t="s">
-        <v>19</v>
-      </c>
-      <c r="I244" t="s">
-        <v>949</v>
-      </c>
       <c r="J244" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K244" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L244" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -12751,22 +12751,22 @@
         <v>1048</v>
       </c>
       <c r="F245" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H245" t="s">
+        <v>19</v>
+      </c>
+      <c r="I245" t="s">
         <v>1049</v>
       </c>
-      <c r="G245" t="s">
-        <v>19</v>
-      </c>
-      <c r="I245" t="s">
-        <v>949</v>
-      </c>
       <c r="J245" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K245" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L245" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -12786,22 +12786,22 @@
         <v>1052</v>
       </c>
       <c r="F246" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H246" t="s">
+        <v>19</v>
+      </c>
+      <c r="I246" t="s">
         <v>1053</v>
       </c>
-      <c r="G246" t="s">
-        <v>19</v>
-      </c>
-      <c r="I246" t="s">
-        <v>949</v>
-      </c>
       <c r="J246" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K246" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L246" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -12821,22 +12821,22 @@
         <v>1056</v>
       </c>
       <c r="F247" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H247" t="s">
+        <v>19</v>
+      </c>
+      <c r="I247" t="s">
         <v>1057</v>
       </c>
-      <c r="G247" t="s">
-        <v>19</v>
-      </c>
-      <c r="I247" t="s">
-        <v>949</v>
-      </c>
       <c r="J247" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K247" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L247" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -12856,22 +12856,22 @@
         <v>1060</v>
       </c>
       <c r="F248" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H248" t="s">
+        <v>19</v>
+      </c>
+      <c r="I248" t="s">
         <v>1061</v>
       </c>
-      <c r="G248" t="s">
-        <v>19</v>
-      </c>
-      <c r="I248" t="s">
-        <v>949</v>
-      </c>
       <c r="J248" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K248" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L248" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -12891,22 +12891,22 @@
         <v>1064</v>
       </c>
       <c r="F249" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H249" t="s">
+        <v>19</v>
+      </c>
+      <c r="I249" t="s">
         <v>1065</v>
       </c>
-      <c r="G249" t="s">
-        <v>19</v>
-      </c>
-      <c r="I249" t="s">
-        <v>949</v>
-      </c>
       <c r="J249" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K249" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L249" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -12926,22 +12926,22 @@
         <v>1068</v>
       </c>
       <c r="F250" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H250" t="s">
+        <v>19</v>
+      </c>
+      <c r="I250" t="s">
         <v>1069</v>
       </c>
-      <c r="G250" t="s">
-        <v>19</v>
-      </c>
-      <c r="I250" t="s">
-        <v>949</v>
-      </c>
       <c r="J250" t="s">
-        <v>21</v>
+        <v>1033</v>
       </c>
       <c r="K250" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="L250" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,36 +25,36 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-name</t>
   </si>
   <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -64,30 +64,30 @@
     <t>active</t>
   </si>
   <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
     <t>015</t>
   </si>
   <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -166,24 +166,24 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
     <t>014</t>
   </si>
   <si>
     <t>IO</t>
   </si>
   <si>
+    <t>IOT</t>
+  </si>
+  <si>
     <t>Eastern Africa</t>
   </si>
   <si>
-    <t>IOT</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -448,12 +448,12 @@
     <t>AO</t>
   </si>
   <si>
+    <t>AGO</t>
+  </si>
+  <si>
     <t>Middle Africa</t>
   </si>
   <si>
-    <t>AGO</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>BW</t>
   </si>
   <si>
+    <t>BWA</t>
+  </si>
+  <si>
     <t>Southern Africa</t>
   </si>
   <si>
-    <t>BWA</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -628,12 +628,12 @@
     <t>BJ</t>
   </si>
   <si>
+    <t>BEN</t>
+  </si>
+  <si>
     <t>Western Africa</t>
   </si>
   <si>
-    <t>BEN</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
     <t>419</t>
   </si>
   <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
     <t>Americas</t>
   </si>
   <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>AIA</t>
-  </si>
-  <si>
     <t>019</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>BZ</t>
   </si>
   <si>
+    <t>BLZ</t>
+  </si>
+  <si>
     <t>Central America</t>
   </si>
   <si>
-    <t>BLZ</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>AR</t>
   </si>
   <si>
+    <t>ARG</t>
+  </si>
+  <si>
     <t>South America</t>
   </si>
   <si>
-    <t>ARG</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Bermuda</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
     <t>021</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
     <t>BM</t>
   </si>
   <si>
@@ -1564,21 +1564,21 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>Asia</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>KAZ</t>
-  </si>
-  <si>
     <t>142</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>China</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
     <t>CN</t>
   </si>
   <si>
@@ -1726,12 +1726,12 @@
     <t>Brunei Darussalam</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
     <t>035</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
     <t>BN</t>
   </si>
   <si>
@@ -1864,12 +1864,12 @@
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -1978,12 +1978,12 @@
     <t>Armenia</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
     <t>AM</t>
   </si>
   <si>
@@ -2200,21 +2200,21 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>Europe</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -2332,12 +2332,12 @@
     <t>Åland Islands</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
     <t>154</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
     <t>AX</t>
   </si>
   <si>
@@ -2356,12 +2356,12 @@
     <t>GG</t>
   </si>
   <si>
+    <t>GGY</t>
+  </si>
+  <si>
     <t>Channel Islands</t>
   </si>
   <si>
-    <t>GGY</t>
-  </si>
-  <si>
     <t>832</t>
   </si>
   <si>
@@ -2542,12 +2542,12 @@
     <t>Albania</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
     <t>039</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
     <t>AL</t>
   </si>
   <si>
@@ -2740,12 +2740,12 @@
     <t>Austria</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
     <t>AT</t>
   </si>
   <si>
@@ -2854,21 +2854,21 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
     <t>009</t>
   </si>
   <si>
@@ -2938,12 +2938,12 @@
     <t>Fiji</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
     <t>054</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
     <t>FJ</t>
   </si>
   <si>
@@ -3004,12 +3004,12 @@
     <t>Guam</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
     <t>057</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
     <t>GU</t>
   </si>
   <si>
@@ -3106,10 +3106,10 @@
     <t>American Samoa</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
   </si>
   <si>
     <t>AS</t>
@@ -3618,7 +3618,7 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
       <c r="I2" t="s">
@@ -3653,14 +3653,14 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
+      <c r="H3" t="s">
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -3688,14 +3688,14 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
+      <c r="H4" t="s">
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -3723,14 +3723,14 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
+      <c r="H5" t="s">
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -3758,14 +3758,14 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6" t="s">
-        <v>19</v>
+      <c r="H6" t="s">
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
         <v>22</v>
@@ -3793,14 +3793,14 @@
       <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" t="s">
-        <v>19</v>
+      <c r="H7" t="s">
+        <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s">
         <v>22</v>
@@ -3828,14 +3828,14 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" t="s">
-        <v>19</v>
+      <c r="H8" t="s">
+        <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
         <v>22</v>
@@ -3855,28 +3855,28 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
         <v>50</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>22</v>
@@ -3896,28 +3896,28 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
         <v>22</v>
@@ -3937,28 +3937,28 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
         <v>50</v>
       </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>22</v>
@@ -3978,28 +3978,28 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K12" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
         <v>22</v>
@@ -4019,28 +4019,28 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
         <v>50</v>
       </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -4060,28 +4060,28 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
         <v>50</v>
       </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
@@ -4101,28 +4101,28 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
@@ -4142,28 +4142,28 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
         <v>50</v>
       </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
@@ -4183,28 +4183,28 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
         <v>50</v>
       </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="L17" t="s">
         <v>22</v>
@@ -4224,28 +4224,28 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
         <v>50</v>
       </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="L18" t="s">
         <v>22</v>
@@ -4265,28 +4265,28 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
         <v>50</v>
       </c>
-      <c r="E19" t="s">
-        <v>17</v>
-      </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="L19" t="s">
         <v>22</v>
@@ -4306,28 +4306,28 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="s">
         <v>50</v>
       </c>
-      <c r="E20" t="s">
-        <v>17</v>
-      </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K20" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
@@ -4347,28 +4347,28 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
         <v>50</v>
       </c>
-      <c r="E21" t="s">
-        <v>17</v>
-      </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K21" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="L21" t="s">
         <v>22</v>
@@ -4388,28 +4388,28 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
         <v>50</v>
       </c>
-      <c r="E22" t="s">
-        <v>17</v>
-      </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K22" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
@@ -4429,28 +4429,28 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
         <v>50</v>
       </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="I23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K23" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
@@ -4470,28 +4470,28 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
         <v>50</v>
       </c>
-      <c r="E24" t="s">
-        <v>17</v>
-      </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K24" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="L24" t="s">
         <v>22</v>
@@ -4511,28 +4511,28 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
         <v>50</v>
       </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K25" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
         <v>22</v>
@@ -4552,28 +4552,28 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
         <v>50</v>
       </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K26" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
         <v>22</v>
@@ -4593,28 +4593,28 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
         <v>50</v>
       </c>
-      <c r="E27" t="s">
-        <v>17</v>
-      </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K27" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
         <v>22</v>
@@ -4634,28 +4634,28 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
         <v>50</v>
       </c>
-      <c r="E28" t="s">
-        <v>17</v>
-      </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="L28" t="s">
         <v>22</v>
@@ -4675,28 +4675,28 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
         <v>50</v>
       </c>
-      <c r="E29" t="s">
-        <v>17</v>
-      </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K29" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="L29" t="s">
         <v>22</v>
@@ -4716,28 +4716,28 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
         <v>50</v>
       </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K30" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="L30" t="s">
         <v>22</v>
@@ -4757,28 +4757,28 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
         <v>50</v>
       </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K31" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
@@ -4798,28 +4798,28 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
         <v>50</v>
       </c>
-      <c r="E32" t="s">
-        <v>17</v>
-      </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K32" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -4839,28 +4839,28 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
         <v>50</v>
       </c>
-      <c r="E33" t="s">
-        <v>17</v>
-      </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H33" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K33" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -4880,28 +4880,28 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
         <v>50</v>
       </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H34" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K34" t="s">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
@@ -4921,28 +4921,28 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" t="s">
         <v>50</v>
       </c>
-      <c r="E35" t="s">
-        <v>17</v>
-      </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H35" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="I35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K35" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
@@ -4962,28 +4962,28 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
         <v>50</v>
       </c>
-      <c r="E36" t="s">
-        <v>17</v>
-      </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H36" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="I36" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K36" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="L36" t="s">
         <v>22</v>
@@ -5003,28 +5003,28 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
         <v>50</v>
       </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K37" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="L37" t="s">
         <v>22</v>
@@ -5044,28 +5044,28 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" t="s">
         <v>50</v>
       </c>
-      <c r="E38" t="s">
-        <v>17</v>
-      </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H38" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K38" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="L38" t="s">
         <v>22</v>
@@ -5085,28 +5085,28 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" t="s">
         <v>50</v>
       </c>
-      <c r="E39" t="s">
-        <v>17</v>
-      </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="H39" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="I39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K39" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="L39" t="s">
         <v>22</v>
@@ -5126,28 +5126,28 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="s">
         <v>50</v>
       </c>
-      <c r="E40" t="s">
-        <v>17</v>
-      </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="H40" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K40" t="s">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="L40" t="s">
         <v>22</v>
@@ -5167,28 +5167,28 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
         <v>50</v>
       </c>
-      <c r="E41" t="s">
-        <v>17</v>
-      </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G41" t="s">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="H41" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="I41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K41" t="s">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -5208,28 +5208,28 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" t="s">
         <v>50</v>
       </c>
-      <c r="E42" t="s">
-        <v>17</v>
-      </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G42" t="s">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="H42" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K42" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="L42" t="s">
         <v>22</v>
@@ -5249,28 +5249,28 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
         <v>50</v>
       </c>
-      <c r="E43" t="s">
-        <v>17</v>
-      </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="I43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J43" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K43" t="s">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
@@ -5290,28 +5290,28 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
         <v>50</v>
       </c>
-      <c r="E44" t="s">
-        <v>17</v>
-      </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="H44" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="I44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K44" t="s">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
@@ -5331,28 +5331,28 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
         <v>50</v>
       </c>
-      <c r="E45" t="s">
-        <v>17</v>
-      </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K45" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -5372,28 +5372,28 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" t="s">
         <v>50</v>
       </c>
-      <c r="E46" t="s">
-        <v>17</v>
-      </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H46" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K46" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="L46" t="s">
         <v>22</v>
@@ -5413,28 +5413,28 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" t="s">
         <v>50</v>
       </c>
-      <c r="E47" t="s">
-        <v>17</v>
-      </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G47" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H47" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K47" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="L47" t="s">
         <v>22</v>
@@ -5454,28 +5454,28 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" t="s">
         <v>50</v>
       </c>
-      <c r="E48" t="s">
-        <v>17</v>
-      </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H48" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J48" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K48" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="L48" t="s">
         <v>22</v>
@@ -5495,28 +5495,28 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" t="s">
         <v>50</v>
       </c>
-      <c r="E49" t="s">
-        <v>17</v>
-      </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G49" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H49" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="I49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J49" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K49" t="s">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="L49" t="s">
         <v>22</v>
@@ -5536,28 +5536,28 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
         <v>50</v>
       </c>
-      <c r="E50" t="s">
-        <v>17</v>
-      </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H50" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="I50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K50" t="s">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="L50" t="s">
         <v>22</v>
@@ -5577,28 +5577,28 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" t="s">
         <v>50</v>
       </c>
-      <c r="E51" t="s">
-        <v>17</v>
-      </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G51" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H51" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="I51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K51" t="s">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="L51" t="s">
         <v>22</v>
@@ -5618,28 +5618,28 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" t="s">
         <v>50</v>
       </c>
-      <c r="E52" t="s">
-        <v>17</v>
-      </c>
       <c r="F52" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H52" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="I52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K52" t="s">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="L52" t="s">
         <v>22</v>
@@ -5659,28 +5659,28 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
         <v>50</v>
       </c>
-      <c r="E53" t="s">
-        <v>17</v>
-      </c>
       <c r="F53" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G53" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H53" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="I53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J53" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K53" t="s">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="L53" t="s">
         <v>22</v>
@@ -5700,28 +5700,28 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" t="s">
         <v>50</v>
       </c>
-      <c r="E54" t="s">
-        <v>17</v>
-      </c>
       <c r="F54" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H54" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="I54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K54" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="L54" t="s">
         <v>22</v>
@@ -5741,28 +5741,28 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" t="s">
         <v>50</v>
       </c>
-      <c r="E55" t="s">
-        <v>17</v>
-      </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G55" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H55" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="I55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K55" t="s">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="L55" t="s">
         <v>22</v>
@@ -5782,28 +5782,28 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" t="s">
         <v>50</v>
       </c>
-      <c r="E56" t="s">
-        <v>17</v>
-      </c>
       <c r="F56" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H56" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="I56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K56" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="L56" t="s">
         <v>22</v>
@@ -5823,28 +5823,28 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
         <v>50</v>
       </c>
-      <c r="E57" t="s">
-        <v>17</v>
-      </c>
       <c r="F57" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G57" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H57" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="I57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K57" t="s">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="L57" t="s">
         <v>22</v>
@@ -5864,28 +5864,28 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" t="s">
         <v>50</v>
       </c>
-      <c r="E58" t="s">
-        <v>17</v>
-      </c>
       <c r="F58" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G58" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H58" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="I58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K58" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="L58" t="s">
         <v>22</v>
@@ -5905,28 +5905,28 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
         <v>50</v>
       </c>
-      <c r="E59" t="s">
-        <v>17</v>
-      </c>
       <c r="F59" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G59" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H59" t="s">
-        <v>202</v>
+        <v>260</v>
       </c>
       <c r="I59" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K59" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="L59" t="s">
         <v>22</v>
@@ -5946,28 +5946,28 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" t="s">
         <v>50</v>
       </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
       <c r="F60" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G60" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H60" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="I60" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K60" t="s">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="L60" t="s">
         <v>22</v>
@@ -5987,28 +5987,28 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
         <v>50</v>
       </c>
-      <c r="E61" t="s">
-        <v>17</v>
-      </c>
       <c r="F61" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G61" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H61" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="I61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K61" t="s">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="L61" t="s">
         <v>22</v>
@@ -6028,10 +6028,10 @@
         <v>15</v>
       </c>
       <c r="D62" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" t="s">
         <v>272</v>
-      </c>
-      <c r="E62" t="s">
-        <v>17</v>
       </c>
       <c r="F62" t="s">
         <v>273</v>
@@ -6069,10 +6069,10 @@
         <v>15</v>
       </c>
       <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
         <v>272</v>
-      </c>
-      <c r="E63" t="s">
-        <v>17</v>
       </c>
       <c r="F63" t="s">
         <v>273</v>
@@ -6081,16 +6081,16 @@
         <v>274</v>
       </c>
       <c r="H63" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="I63" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J63" t="s">
         <v>277</v>
       </c>
       <c r="K63" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="L63" t="s">
         <v>279</v>
@@ -6110,10 +6110,10 @@
         <v>15</v>
       </c>
       <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" t="s">
         <v>272</v>
-      </c>
-      <c r="E64" t="s">
-        <v>17</v>
       </c>
       <c r="F64" t="s">
         <v>273</v>
@@ -6122,16 +6122,16 @@
         <v>274</v>
       </c>
       <c r="H64" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="I64" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J64" t="s">
         <v>277</v>
       </c>
       <c r="K64" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="L64" t="s">
         <v>279</v>
@@ -6151,10 +6151,10 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" t="s">
         <v>272</v>
-      </c>
-      <c r="E65" t="s">
-        <v>17</v>
       </c>
       <c r="F65" t="s">
         <v>273</v>
@@ -6163,16 +6163,16 @@
         <v>274</v>
       </c>
       <c r="H65" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="I65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J65" t="s">
         <v>277</v>
       </c>
       <c r="K65" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="L65" t="s">
         <v>279</v>
@@ -6192,10 +6192,10 @@
         <v>15</v>
       </c>
       <c r="D66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" t="s">
         <v>272</v>
-      </c>
-      <c r="E66" t="s">
-        <v>17</v>
       </c>
       <c r="F66" t="s">
         <v>273</v>
@@ -6204,16 +6204,16 @@
         <v>274</v>
       </c>
       <c r="H66" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="I66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J66" t="s">
         <v>277</v>
       </c>
       <c r="K66" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="L66" t="s">
         <v>279</v>
@@ -6233,10 +6233,10 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" t="s">
         <v>272</v>
-      </c>
-      <c r="E67" t="s">
-        <v>17</v>
       </c>
       <c r="F67" t="s">
         <v>273</v>
@@ -6245,16 +6245,16 @@
         <v>274</v>
       </c>
       <c r="H67" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="I67" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J67" t="s">
         <v>277</v>
       </c>
       <c r="K67" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="L67" t="s">
         <v>279</v>
@@ -6274,10 +6274,10 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" t="s">
         <v>272</v>
-      </c>
-      <c r="E68" t="s">
-        <v>17</v>
       </c>
       <c r="F68" t="s">
         <v>273</v>
@@ -6286,16 +6286,16 @@
         <v>274</v>
       </c>
       <c r="H68" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="I68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J68" t="s">
         <v>277</v>
       </c>
       <c r="K68" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="L68" t="s">
         <v>279</v>
@@ -6315,10 +6315,10 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
         <v>272</v>
-      </c>
-      <c r="E69" t="s">
-        <v>17</v>
       </c>
       <c r="F69" t="s">
         <v>273</v>
@@ -6327,16 +6327,16 @@
         <v>274</v>
       </c>
       <c r="H69" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="I69" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J69" t="s">
         <v>277</v>
       </c>
       <c r="K69" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="L69" t="s">
         <v>279</v>
@@ -6356,10 +6356,10 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" t="s">
         <v>272</v>
-      </c>
-      <c r="E70" t="s">
-        <v>17</v>
       </c>
       <c r="F70" t="s">
         <v>273</v>
@@ -6368,16 +6368,16 @@
         <v>274</v>
       </c>
       <c r="H70" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="I70" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J70" t="s">
         <v>277</v>
       </c>
       <c r="K70" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="L70" t="s">
         <v>279</v>
@@ -6397,10 +6397,10 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
         <v>272</v>
-      </c>
-      <c r="E71" t="s">
-        <v>17</v>
       </c>
       <c r="F71" t="s">
         <v>273</v>
@@ -6409,16 +6409,16 @@
         <v>274</v>
       </c>
       <c r="H71" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="I71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J71" t="s">
         <v>277</v>
       </c>
       <c r="K71" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="L71" t="s">
         <v>279</v>
@@ -6438,10 +6438,10 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
         <v>272</v>
-      </c>
-      <c r="E72" t="s">
-        <v>17</v>
       </c>
       <c r="F72" t="s">
         <v>273</v>
@@ -6450,16 +6450,16 @@
         <v>274</v>
       </c>
       <c r="H72" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="I72" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J72" t="s">
         <v>277</v>
       </c>
       <c r="K72" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="L72" t="s">
         <v>279</v>
@@ -6479,10 +6479,10 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" t="s">
         <v>272</v>
-      </c>
-      <c r="E73" t="s">
-        <v>17</v>
       </c>
       <c r="F73" t="s">
         <v>273</v>
@@ -6491,16 +6491,16 @@
         <v>274</v>
       </c>
       <c r="H73" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="I73" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J73" t="s">
         <v>277</v>
       </c>
       <c r="K73" t="s">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="L73" t="s">
         <v>279</v>
@@ -6520,10 +6520,10 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" t="s">
         <v>272</v>
-      </c>
-      <c r="E74" t="s">
-        <v>17</v>
       </c>
       <c r="F74" t="s">
         <v>273</v>
@@ -6532,16 +6532,16 @@
         <v>274</v>
       </c>
       <c r="H74" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="I74" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J74" t="s">
         <v>277</v>
       </c>
       <c r="K74" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="L74" t="s">
         <v>279</v>
@@ -6561,10 +6561,10 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" t="s">
         <v>272</v>
-      </c>
-      <c r="E75" t="s">
-        <v>17</v>
       </c>
       <c r="F75" t="s">
         <v>273</v>
@@ -6573,16 +6573,16 @@
         <v>274</v>
       </c>
       <c r="H75" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="I75" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J75" t="s">
         <v>277</v>
       </c>
       <c r="K75" t="s">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="L75" t="s">
         <v>279</v>
@@ -6602,10 +6602,10 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" t="s">
         <v>272</v>
-      </c>
-      <c r="E76" t="s">
-        <v>17</v>
       </c>
       <c r="F76" t="s">
         <v>273</v>
@@ -6614,16 +6614,16 @@
         <v>274</v>
       </c>
       <c r="H76" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="I76" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J76" t="s">
         <v>277</v>
       </c>
       <c r="K76" t="s">
-        <v>335</v>
+        <v>278</v>
       </c>
       <c r="L76" t="s">
         <v>279</v>
@@ -6643,10 +6643,10 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s">
         <v>272</v>
-      </c>
-      <c r="E77" t="s">
-        <v>17</v>
       </c>
       <c r="F77" t="s">
         <v>273</v>
@@ -6655,16 +6655,16 @@
         <v>274</v>
       </c>
       <c r="H77" t="s">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="I77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J77" t="s">
         <v>277</v>
       </c>
       <c r="K77" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="L77" t="s">
         <v>279</v>
@@ -6684,10 +6684,10 @@
         <v>15</v>
       </c>
       <c r="D78" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" t="s">
         <v>272</v>
-      </c>
-      <c r="E78" t="s">
-        <v>17</v>
       </c>
       <c r="F78" t="s">
         <v>273</v>
@@ -6696,16 +6696,16 @@
         <v>274</v>
       </c>
       <c r="H78" t="s">
-        <v>275</v>
+        <v>342</v>
       </c>
       <c r="I78" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J78" t="s">
         <v>277</v>
       </c>
       <c r="K78" t="s">
-        <v>343</v>
+        <v>278</v>
       </c>
       <c r="L78" t="s">
         <v>279</v>
@@ -6725,10 +6725,10 @@
         <v>15</v>
       </c>
       <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
         <v>272</v>
-      </c>
-      <c r="E79" t="s">
-        <v>17</v>
       </c>
       <c r="F79" t="s">
         <v>273</v>
@@ -6737,16 +6737,16 @@
         <v>274</v>
       </c>
       <c r="H79" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="I79" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J79" t="s">
         <v>277</v>
       </c>
       <c r="K79" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="L79" t="s">
         <v>279</v>
@@ -6766,10 +6766,10 @@
         <v>15</v>
       </c>
       <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" t="s">
         <v>272</v>
-      </c>
-      <c r="E80" t="s">
-        <v>17</v>
       </c>
       <c r="F80" t="s">
         <v>273</v>
@@ -6778,16 +6778,16 @@
         <v>274</v>
       </c>
       <c r="H80" t="s">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="I80" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J80" t="s">
         <v>277</v>
       </c>
       <c r="K80" t="s">
-        <v>351</v>
+        <v>278</v>
       </c>
       <c r="L80" t="s">
         <v>279</v>
@@ -6807,10 +6807,10 @@
         <v>15</v>
       </c>
       <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" t="s">
         <v>272</v>
-      </c>
-      <c r="E81" t="s">
-        <v>17</v>
       </c>
       <c r="F81" t="s">
         <v>273</v>
@@ -6819,16 +6819,16 @@
         <v>274</v>
       </c>
       <c r="H81" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="I81" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J81" t="s">
         <v>277</v>
       </c>
       <c r="K81" t="s">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="L81" t="s">
         <v>279</v>
@@ -6848,10 +6848,10 @@
         <v>15</v>
       </c>
       <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
         <v>272</v>
-      </c>
-      <c r="E82" t="s">
-        <v>17</v>
       </c>
       <c r="F82" t="s">
         <v>273</v>
@@ -6860,16 +6860,16 @@
         <v>274</v>
       </c>
       <c r="H82" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
       <c r="I82" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J82" t="s">
         <v>277</v>
       </c>
       <c r="K82" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="L82" t="s">
         <v>279</v>
@@ -6889,10 +6889,10 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" t="s">
         <v>272</v>
-      </c>
-      <c r="E83" t="s">
-        <v>17</v>
       </c>
       <c r="F83" t="s">
         <v>273</v>
@@ -6901,16 +6901,16 @@
         <v>274</v>
       </c>
       <c r="H83" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="I83" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J83" t="s">
         <v>277</v>
       </c>
       <c r="K83" t="s">
-        <v>363</v>
+        <v>278</v>
       </c>
       <c r="L83" t="s">
         <v>279</v>
@@ -6930,10 +6930,10 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" t="s">
         <v>272</v>
-      </c>
-      <c r="E84" t="s">
-        <v>17</v>
       </c>
       <c r="F84" t="s">
         <v>273</v>
@@ -6942,16 +6942,16 @@
         <v>274</v>
       </c>
       <c r="H84" t="s">
-        <v>275</v>
+        <v>366</v>
       </c>
       <c r="I84" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J84" t="s">
         <v>277</v>
       </c>
       <c r="K84" t="s">
-        <v>367</v>
+        <v>278</v>
       </c>
       <c r="L84" t="s">
         <v>279</v>
@@ -6971,10 +6971,10 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" t="s">
         <v>272</v>
-      </c>
-      <c r="E85" t="s">
-        <v>17</v>
       </c>
       <c r="F85" t="s">
         <v>273</v>
@@ -6983,16 +6983,16 @@
         <v>274</v>
       </c>
       <c r="H85" t="s">
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="I85" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J85" t="s">
         <v>277</v>
       </c>
       <c r="K85" t="s">
-        <v>371</v>
+        <v>278</v>
       </c>
       <c r="L85" t="s">
         <v>279</v>
@@ -7012,10 +7012,10 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" t="s">
         <v>272</v>
-      </c>
-      <c r="E86" t="s">
-        <v>17</v>
       </c>
       <c r="F86" t="s">
         <v>273</v>
@@ -7024,16 +7024,16 @@
         <v>274</v>
       </c>
       <c r="H86" t="s">
-        <v>275</v>
+        <v>374</v>
       </c>
       <c r="I86" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J86" t="s">
         <v>277</v>
       </c>
       <c r="K86" t="s">
-        <v>375</v>
+        <v>278</v>
       </c>
       <c r="L86" t="s">
         <v>279</v>
@@ -7053,10 +7053,10 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" t="s">
         <v>272</v>
-      </c>
-      <c r="E87" t="s">
-        <v>17</v>
       </c>
       <c r="F87" t="s">
         <v>273</v>
@@ -7065,16 +7065,16 @@
         <v>274</v>
       </c>
       <c r="H87" t="s">
-        <v>275</v>
+        <v>378</v>
       </c>
       <c r="I87" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J87" t="s">
         <v>277</v>
       </c>
       <c r="K87" t="s">
-        <v>379</v>
+        <v>278</v>
       </c>
       <c r="L87" t="s">
         <v>279</v>
@@ -7094,10 +7094,10 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" t="s">
         <v>272</v>
-      </c>
-      <c r="E88" t="s">
-        <v>17</v>
       </c>
       <c r="F88" t="s">
         <v>273</v>
@@ -7106,16 +7106,16 @@
         <v>274</v>
       </c>
       <c r="H88" t="s">
-        <v>275</v>
+        <v>382</v>
       </c>
       <c r="I88" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J88" t="s">
         <v>277</v>
       </c>
       <c r="K88" t="s">
-        <v>383</v>
+        <v>278</v>
       </c>
       <c r="L88" t="s">
         <v>279</v>
@@ -7135,10 +7135,10 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" t="s">
         <v>272</v>
-      </c>
-      <c r="E89" t="s">
-        <v>17</v>
       </c>
       <c r="F89" t="s">
         <v>273</v>
@@ -7147,16 +7147,16 @@
         <v>274</v>
       </c>
       <c r="H89" t="s">
-        <v>275</v>
+        <v>386</v>
       </c>
       <c r="I89" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J89" t="s">
         <v>277</v>
       </c>
       <c r="K89" t="s">
-        <v>387</v>
+        <v>278</v>
       </c>
       <c r="L89" t="s">
         <v>279</v>
@@ -7176,28 +7176,28 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
         <v>272</v>
-      </c>
-      <c r="E90" t="s">
-        <v>17</v>
       </c>
       <c r="F90" t="s">
         <v>273</v>
       </c>
       <c r="G90" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H90" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I90" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J90" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K90" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L90" t="s">
         <v>279</v>
@@ -7217,28 +7217,28 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" t="s">
         <v>272</v>
-      </c>
-      <c r="E91" t="s">
-        <v>17</v>
       </c>
       <c r="F91" t="s">
         <v>273</v>
       </c>
       <c r="G91" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H91" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="I91" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J91" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K91" t="s">
-        <v>397</v>
+        <v>278</v>
       </c>
       <c r="L91" t="s">
         <v>279</v>
@@ -7258,28 +7258,28 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
         <v>272</v>
-      </c>
-      <c r="E92" t="s">
-        <v>17</v>
       </c>
       <c r="F92" t="s">
         <v>273</v>
       </c>
       <c r="G92" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H92" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="I92" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J92" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K92" t="s">
-        <v>401</v>
+        <v>278</v>
       </c>
       <c r="L92" t="s">
         <v>279</v>
@@ -7299,28 +7299,28 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
         <v>272</v>
-      </c>
-      <c r="E93" t="s">
-        <v>17</v>
       </c>
       <c r="F93" t="s">
         <v>273</v>
       </c>
       <c r="G93" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H93" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I93" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J93" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K93" t="s">
-        <v>405</v>
+        <v>278</v>
       </c>
       <c r="L93" t="s">
         <v>279</v>
@@ -7340,28 +7340,28 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" t="s">
         <v>272</v>
-      </c>
-      <c r="E94" t="s">
-        <v>17</v>
       </c>
       <c r="F94" t="s">
         <v>273</v>
       </c>
       <c r="G94" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H94" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="I94" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J94" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K94" t="s">
-        <v>409</v>
+        <v>278</v>
       </c>
       <c r="L94" t="s">
         <v>279</v>
@@ -7381,28 +7381,28 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
         <v>272</v>
-      </c>
-      <c r="E95" t="s">
-        <v>17</v>
       </c>
       <c r="F95" t="s">
         <v>273</v>
       </c>
       <c r="G95" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H95" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="I95" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J95" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K95" t="s">
-        <v>413</v>
+        <v>278</v>
       </c>
       <c r="L95" t="s">
         <v>279</v>
@@ -7422,28 +7422,28 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" t="s">
         <v>272</v>
-      </c>
-      <c r="E96" t="s">
-        <v>17</v>
       </c>
       <c r="F96" t="s">
         <v>273</v>
       </c>
       <c r="G96" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H96" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="I96" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J96" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K96" t="s">
-        <v>417</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s">
         <v>279</v>
@@ -7463,28 +7463,28 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" t="s">
         <v>272</v>
-      </c>
-      <c r="E97" t="s">
-        <v>17</v>
       </c>
       <c r="F97" t="s">
         <v>273</v>
       </c>
       <c r="G97" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="H97" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="I97" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J97" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K97" t="s">
-        <v>421</v>
+        <v>278</v>
       </c>
       <c r="L97" t="s">
         <v>279</v>
@@ -7504,28 +7504,28 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
         <v>272</v>
-      </c>
-      <c r="E98" t="s">
-        <v>17</v>
       </c>
       <c r="F98" t="s">
         <v>273</v>
       </c>
       <c r="G98" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H98" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I98" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J98" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K98" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L98" t="s">
         <v>279</v>
@@ -7545,28 +7545,28 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" t="s">
         <v>272</v>
-      </c>
-      <c r="E99" t="s">
-        <v>17</v>
       </c>
       <c r="F99" t="s">
         <v>273</v>
       </c>
       <c r="G99" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H99" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="I99" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J99" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K99" t="s">
-        <v>431</v>
+        <v>278</v>
       </c>
       <c r="L99" t="s">
         <v>279</v>
@@ -7586,28 +7586,28 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" t="s">
         <v>272</v>
-      </c>
-      <c r="E100" t="s">
-        <v>17</v>
       </c>
       <c r="F100" t="s">
         <v>273</v>
       </c>
       <c r="G100" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H100" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="I100" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J100" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K100" t="s">
-        <v>435</v>
+        <v>278</v>
       </c>
       <c r="L100" t="s">
         <v>279</v>
@@ -7627,28 +7627,28 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" t="s">
         <v>272</v>
-      </c>
-      <c r="E101" t="s">
-        <v>17</v>
       </c>
       <c r="F101" t="s">
         <v>273</v>
       </c>
       <c r="G101" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H101" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="I101" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J101" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K101" t="s">
-        <v>439</v>
+        <v>278</v>
       </c>
       <c r="L101" t="s">
         <v>279</v>
@@ -7668,28 +7668,28 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
         <v>272</v>
-      </c>
-      <c r="E102" t="s">
-        <v>17</v>
       </c>
       <c r="F102" t="s">
         <v>273</v>
       </c>
       <c r="G102" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H102" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="I102" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J102" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K102" t="s">
-        <v>443</v>
+        <v>278</v>
       </c>
       <c r="L102" t="s">
         <v>279</v>
@@ -7709,28 +7709,28 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
         <v>272</v>
-      </c>
-      <c r="E103" t="s">
-        <v>17</v>
       </c>
       <c r="F103" t="s">
         <v>273</v>
       </c>
       <c r="G103" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H103" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="I103" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J103" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K103" t="s">
-        <v>447</v>
+        <v>278</v>
       </c>
       <c r="L103" t="s">
         <v>279</v>
@@ -7750,28 +7750,28 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" t="s">
         <v>272</v>
-      </c>
-      <c r="E104" t="s">
-        <v>17</v>
       </c>
       <c r="F104" t="s">
         <v>273</v>
       </c>
       <c r="G104" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H104" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="I104" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J104" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K104" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="L104" t="s">
         <v>279</v>
@@ -7791,28 +7791,28 @@
         <v>15</v>
       </c>
       <c r="D105" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" t="s">
         <v>272</v>
-      </c>
-      <c r="E105" t="s">
-        <v>17</v>
       </c>
       <c r="F105" t="s">
         <v>273</v>
       </c>
       <c r="G105" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H105" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="I105" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J105" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K105" t="s">
-        <v>455</v>
+        <v>278</v>
       </c>
       <c r="L105" t="s">
         <v>279</v>
@@ -7832,28 +7832,28 @@
         <v>15</v>
       </c>
       <c r="D106" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" t="s">
         <v>272</v>
-      </c>
-      <c r="E106" t="s">
-        <v>17</v>
       </c>
       <c r="F106" t="s">
         <v>273</v>
       </c>
       <c r="G106" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H106" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="I106" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J106" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K106" t="s">
-        <v>459</v>
+        <v>278</v>
       </c>
       <c r="L106" t="s">
         <v>279</v>
@@ -7873,28 +7873,28 @@
         <v>15</v>
       </c>
       <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
         <v>272</v>
-      </c>
-      <c r="E107" t="s">
-        <v>17</v>
       </c>
       <c r="F107" t="s">
         <v>273</v>
       </c>
       <c r="G107" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H107" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="I107" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J107" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K107" t="s">
-        <v>463</v>
+        <v>278</v>
       </c>
       <c r="L107" t="s">
         <v>279</v>
@@ -7914,28 +7914,28 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
         <v>272</v>
-      </c>
-      <c r="E108" t="s">
-        <v>17</v>
       </c>
       <c r="F108" t="s">
         <v>273</v>
       </c>
       <c r="G108" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H108" t="s">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="I108" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J108" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K108" t="s">
-        <v>467</v>
+        <v>278</v>
       </c>
       <c r="L108" t="s">
         <v>279</v>
@@ -7955,28 +7955,28 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
         <v>272</v>
-      </c>
-      <c r="E109" t="s">
-        <v>17</v>
       </c>
       <c r="F109" t="s">
         <v>273</v>
       </c>
       <c r="G109" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H109" t="s">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="I109" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J109" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K109" t="s">
-        <v>471</v>
+        <v>278</v>
       </c>
       <c r="L109" t="s">
         <v>279</v>
@@ -7996,28 +7996,28 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" t="s">
         <v>272</v>
-      </c>
-      <c r="E110" t="s">
-        <v>17</v>
       </c>
       <c r="F110" t="s">
         <v>273</v>
       </c>
       <c r="G110" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H110" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="I110" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J110" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K110" t="s">
-        <v>475</v>
+        <v>278</v>
       </c>
       <c r="L110" t="s">
         <v>279</v>
@@ -8037,28 +8037,28 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" t="s">
         <v>272</v>
-      </c>
-      <c r="E111" t="s">
-        <v>17</v>
       </c>
       <c r="F111" t="s">
         <v>273</v>
       </c>
       <c r="G111" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H111" t="s">
-        <v>424</v>
+        <v>478</v>
       </c>
       <c r="I111" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J111" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K111" t="s">
-        <v>479</v>
+        <v>278</v>
       </c>
       <c r="L111" t="s">
         <v>279</v>
@@ -8078,28 +8078,28 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" t="s">
         <v>272</v>
-      </c>
-      <c r="E112" t="s">
-        <v>17</v>
       </c>
       <c r="F112" t="s">
         <v>273</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H112" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="I112" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J112" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K112" t="s">
-        <v>483</v>
+        <v>278</v>
       </c>
       <c r="L112" t="s">
         <v>279</v>
@@ -8119,28 +8119,28 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
         <v>272</v>
-      </c>
-      <c r="E113" t="s">
-        <v>17</v>
       </c>
       <c r="F113" t="s">
         <v>273</v>
       </c>
       <c r="G113" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="H113" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="I113" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J113" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K113" t="s">
-        <v>487</v>
+        <v>278</v>
       </c>
       <c r="L113" t="s">
         <v>279</v>
@@ -8160,22 +8160,22 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
         <v>490</v>
       </c>
-      <c r="E114" t="s">
-        <v>17</v>
-      </c>
       <c r="F114" t="s">
-        <v>273</v>
-      </c>
-      <c r="G114" t="s">
         <v>491</v>
       </c>
+      <c r="H114" t="s">
+        <v>492</v>
+      </c>
       <c r="I114" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K114" t="s">
-        <v>493</v>
+        <v>278</v>
       </c>
       <c r="L114" t="s">
         <v>279</v>
@@ -8195,22 +8195,22 @@
         <v>15</v>
       </c>
       <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
         <v>490</v>
       </c>
-      <c r="E115" t="s">
-        <v>17</v>
-      </c>
       <c r="F115" t="s">
-        <v>273</v>
-      </c>
-      <c r="G115" t="s">
         <v>491</v>
       </c>
+      <c r="H115" t="s">
+        <v>496</v>
+      </c>
       <c r="I115" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K115" t="s">
-        <v>497</v>
+        <v>278</v>
       </c>
       <c r="L115" t="s">
         <v>279</v>
@@ -8230,22 +8230,22 @@
         <v>15</v>
       </c>
       <c r="D116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" t="s">
         <v>490</v>
       </c>
-      <c r="E116" t="s">
-        <v>17</v>
-      </c>
       <c r="F116" t="s">
-        <v>273</v>
-      </c>
-      <c r="G116" t="s">
         <v>491</v>
       </c>
+      <c r="H116" t="s">
+        <v>500</v>
+      </c>
       <c r="I116" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K116" t="s">
-        <v>501</v>
+        <v>278</v>
       </c>
       <c r="L116" t="s">
         <v>279</v>
@@ -8265,22 +8265,22 @@
         <v>15</v>
       </c>
       <c r="D117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" t="s">
         <v>490</v>
       </c>
-      <c r="E117" t="s">
-        <v>17</v>
-      </c>
       <c r="F117" t="s">
-        <v>273</v>
-      </c>
-      <c r="G117" t="s">
         <v>491</v>
       </c>
+      <c r="H117" t="s">
+        <v>504</v>
+      </c>
       <c r="I117" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K117" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="L117" t="s">
         <v>279</v>
@@ -8300,22 +8300,22 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" t="s">
         <v>490</v>
       </c>
-      <c r="E118" t="s">
-        <v>17</v>
-      </c>
       <c r="F118" t="s">
-        <v>273</v>
-      </c>
-      <c r="G118" t="s">
         <v>491</v>
       </c>
+      <c r="H118" t="s">
+        <v>508</v>
+      </c>
       <c r="I118" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K118" t="s">
-        <v>509</v>
+        <v>278</v>
       </c>
       <c r="L118" t="s">
         <v>279</v>
@@ -8334,13 +8334,13 @@
       <c r="C119" t="s">
         <v>15</v>
       </c>
-      <c r="E119" t="s">
-        <v>17</v>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="H119" t="s">
+        <v>512</v>
       </c>
       <c r="I119" t="s">
-        <v>512</v>
-      </c>
-      <c r="K119" t="s">
         <v>513</v>
       </c>
       <c r="M119" t="s">
@@ -8358,15 +8358,15 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
         <v>516</v>
-      </c>
-      <c r="E120" t="s">
-        <v>17</v>
       </c>
       <c r="F120" t="s">
         <v>517</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>518</v>
       </c>
       <c r="I120" t="s">
@@ -8393,22 +8393,22 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" t="s">
         <v>516</v>
-      </c>
-      <c r="E121" t="s">
-        <v>17</v>
       </c>
       <c r="F121" t="s">
         <v>517</v>
       </c>
-      <c r="G121" t="s">
-        <v>518</v>
+      <c r="H121" t="s">
+        <v>524</v>
       </c>
       <c r="I121" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K121" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="L121" t="s">
         <v>521</v>
@@ -8428,22 +8428,22 @@
         <v>15</v>
       </c>
       <c r="D122" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" t="s">
         <v>516</v>
-      </c>
-      <c r="E122" t="s">
-        <v>17</v>
       </c>
       <c r="F122" t="s">
         <v>517</v>
       </c>
-      <c r="G122" t="s">
-        <v>518</v>
+      <c r="H122" t="s">
+        <v>528</v>
       </c>
       <c r="I122" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K122" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="L122" t="s">
         <v>521</v>
@@ -8463,22 +8463,22 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" t="s">
         <v>516</v>
-      </c>
-      <c r="E123" t="s">
-        <v>17</v>
       </c>
       <c r="F123" t="s">
         <v>517</v>
       </c>
-      <c r="G123" t="s">
-        <v>518</v>
+      <c r="H123" t="s">
+        <v>532</v>
       </c>
       <c r="I123" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K123" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="L123" t="s">
         <v>521</v>
@@ -8498,22 +8498,22 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" t="s">
         <v>516</v>
-      </c>
-      <c r="E124" t="s">
-        <v>17</v>
       </c>
       <c r="F124" t="s">
         <v>517</v>
       </c>
-      <c r="G124" t="s">
-        <v>518</v>
+      <c r="H124" t="s">
+        <v>536</v>
       </c>
       <c r="I124" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K124" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="L124" t="s">
         <v>521</v>
@@ -8533,22 +8533,22 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" t="s">
         <v>540</v>
       </c>
-      <c r="E125" t="s">
-        <v>17</v>
-      </c>
       <c r="F125" t="s">
-        <v>517</v>
-      </c>
-      <c r="G125" t="s">
         <v>541</v>
       </c>
+      <c r="H125" t="s">
+        <v>542</v>
+      </c>
       <c r="I125" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K125" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="L125" t="s">
         <v>521</v>
@@ -8568,22 +8568,22 @@
         <v>15</v>
       </c>
       <c r="D126" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" t="s">
         <v>540</v>
       </c>
-      <c r="E126" t="s">
-        <v>17</v>
-      </c>
       <c r="F126" t="s">
-        <v>517</v>
-      </c>
-      <c r="G126" t="s">
         <v>541</v>
       </c>
+      <c r="H126" t="s">
+        <v>546</v>
+      </c>
       <c r="I126" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K126" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="L126" t="s">
         <v>521</v>
@@ -8603,22 +8603,22 @@
         <v>15</v>
       </c>
       <c r="D127" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" t="s">
         <v>540</v>
       </c>
-      <c r="E127" t="s">
-        <v>17</v>
-      </c>
       <c r="F127" t="s">
-        <v>517</v>
-      </c>
-      <c r="G127" t="s">
         <v>541</v>
       </c>
+      <c r="H127" t="s">
+        <v>550</v>
+      </c>
       <c r="I127" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K127" t="s">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="L127" t="s">
         <v>521</v>
@@ -8638,22 +8638,22 @@
         <v>15</v>
       </c>
       <c r="D128" t="s">
+        <v>16</v>
+      </c>
+      <c r="E128" t="s">
         <v>540</v>
       </c>
-      <c r="E128" t="s">
-        <v>17</v>
-      </c>
       <c r="F128" t="s">
-        <v>517</v>
-      </c>
-      <c r="G128" t="s">
         <v>541</v>
       </c>
+      <c r="H128" t="s">
+        <v>554</v>
+      </c>
       <c r="I128" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K128" t="s">
-        <v>555</v>
+        <v>520</v>
       </c>
       <c r="L128" t="s">
         <v>521</v>
@@ -8673,22 +8673,22 @@
         <v>15</v>
       </c>
       <c r="D129" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" t="s">
         <v>540</v>
       </c>
-      <c r="E129" t="s">
-        <v>17</v>
-      </c>
       <c r="F129" t="s">
-        <v>517</v>
-      </c>
-      <c r="G129" t="s">
         <v>541</v>
       </c>
+      <c r="H129" t="s">
+        <v>558</v>
+      </c>
       <c r="I129" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K129" t="s">
-        <v>559</v>
+        <v>520</v>
       </c>
       <c r="L129" t="s">
         <v>521</v>
@@ -8708,22 +8708,22 @@
         <v>15</v>
       </c>
       <c r="D130" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" t="s">
         <v>540</v>
       </c>
-      <c r="E130" t="s">
-        <v>17</v>
-      </c>
       <c r="F130" t="s">
-        <v>517</v>
-      </c>
-      <c r="G130" t="s">
         <v>541</v>
       </c>
+      <c r="H130" t="s">
+        <v>562</v>
+      </c>
       <c r="I130" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K130" t="s">
-        <v>563</v>
+        <v>520</v>
       </c>
       <c r="L130" t="s">
         <v>521</v>
@@ -8743,22 +8743,22 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
+        <v>16</v>
+      </c>
+      <c r="E131" t="s">
         <v>540</v>
       </c>
-      <c r="E131" t="s">
-        <v>17</v>
-      </c>
       <c r="F131" t="s">
-        <v>517</v>
-      </c>
-      <c r="G131" t="s">
         <v>541</v>
       </c>
+      <c r="H131" t="s">
+        <v>566</v>
+      </c>
       <c r="I131" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K131" t="s">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="L131" t="s">
         <v>521</v>
@@ -8778,22 +8778,22 @@
         <v>15</v>
       </c>
       <c r="D132" t="s">
+        <v>16</v>
+      </c>
+      <c r="E132" t="s">
         <v>570</v>
       </c>
-      <c r="E132" t="s">
-        <v>17</v>
-      </c>
       <c r="F132" t="s">
-        <v>517</v>
-      </c>
-      <c r="G132" t="s">
         <v>571</v>
       </c>
+      <c r="H132" t="s">
+        <v>572</v>
+      </c>
       <c r="I132" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K132" t="s">
-        <v>573</v>
+        <v>520</v>
       </c>
       <c r="L132" t="s">
         <v>521</v>
@@ -8813,22 +8813,22 @@
         <v>15</v>
       </c>
       <c r="D133" t="s">
+        <v>16</v>
+      </c>
+      <c r="E133" t="s">
         <v>570</v>
       </c>
-      <c r="E133" t="s">
-        <v>17</v>
-      </c>
       <c r="F133" t="s">
-        <v>517</v>
-      </c>
-      <c r="G133" t="s">
         <v>571</v>
       </c>
+      <c r="H133" t="s">
+        <v>576</v>
+      </c>
       <c r="I133" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K133" t="s">
-        <v>577</v>
+        <v>520</v>
       </c>
       <c r="L133" t="s">
         <v>521</v>
@@ -8848,22 +8848,22 @@
         <v>15</v>
       </c>
       <c r="D134" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" t="s">
         <v>570</v>
       </c>
-      <c r="E134" t="s">
-        <v>17</v>
-      </c>
       <c r="F134" t="s">
-        <v>517</v>
-      </c>
-      <c r="G134" t="s">
         <v>571</v>
       </c>
+      <c r="H134" t="s">
+        <v>580</v>
+      </c>
       <c r="I134" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K134" t="s">
-        <v>581</v>
+        <v>520</v>
       </c>
       <c r="L134" t="s">
         <v>521</v>
@@ -8883,22 +8883,22 @@
         <v>15</v>
       </c>
       <c r="D135" t="s">
+        <v>16</v>
+      </c>
+      <c r="E135" t="s">
         <v>570</v>
       </c>
-      <c r="E135" t="s">
-        <v>17</v>
-      </c>
       <c r="F135" t="s">
-        <v>517</v>
-      </c>
-      <c r="G135" t="s">
         <v>571</v>
       </c>
+      <c r="H135" t="s">
+        <v>584</v>
+      </c>
       <c r="I135" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="K135" t="s">
-        <v>585</v>
+        <v>520</v>
       </c>
       <c r="L135" t="s">
         <v>521</v>
@@ -8918,22 +8918,22 @@
         <v>15</v>
       </c>
       <c r="D136" t="s">
+        <v>16</v>
+      </c>
+      <c r="E136" t="s">
         <v>570</v>
       </c>
-      <c r="E136" t="s">
-        <v>17</v>
-      </c>
       <c r="F136" t="s">
-        <v>517</v>
-      </c>
-      <c r="G136" t="s">
         <v>571</v>
       </c>
+      <c r="H136" t="s">
+        <v>588</v>
+      </c>
       <c r="I136" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K136" t="s">
-        <v>589</v>
+        <v>520</v>
       </c>
       <c r="L136" t="s">
         <v>521</v>
@@ -8953,22 +8953,22 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
+        <v>16</v>
+      </c>
+      <c r="E137" t="s">
         <v>570</v>
       </c>
-      <c r="E137" t="s">
-        <v>17</v>
-      </c>
       <c r="F137" t="s">
-        <v>517</v>
-      </c>
-      <c r="G137" t="s">
         <v>571</v>
       </c>
+      <c r="H137" t="s">
+        <v>592</v>
+      </c>
       <c r="I137" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K137" t="s">
-        <v>593</v>
+        <v>520</v>
       </c>
       <c r="L137" t="s">
         <v>521</v>
@@ -8988,22 +8988,22 @@
         <v>15</v>
       </c>
       <c r="D138" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" t="s">
         <v>570</v>
       </c>
-      <c r="E138" t="s">
-        <v>17</v>
-      </c>
       <c r="F138" t="s">
-        <v>517</v>
-      </c>
-      <c r="G138" t="s">
         <v>571</v>
       </c>
+      <c r="H138" t="s">
+        <v>596</v>
+      </c>
       <c r="I138" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K138" t="s">
-        <v>597</v>
+        <v>520</v>
       </c>
       <c r="L138" t="s">
         <v>521</v>
@@ -9023,22 +9023,22 @@
         <v>15</v>
       </c>
       <c r="D139" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" t="s">
         <v>570</v>
       </c>
-      <c r="E139" t="s">
-        <v>17</v>
-      </c>
       <c r="F139" t="s">
-        <v>517</v>
-      </c>
-      <c r="G139" t="s">
         <v>571</v>
       </c>
+      <c r="H139" t="s">
+        <v>600</v>
+      </c>
       <c r="I139" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="K139" t="s">
-        <v>601</v>
+        <v>520</v>
       </c>
       <c r="L139" t="s">
         <v>521</v>
@@ -9058,22 +9058,22 @@
         <v>15</v>
       </c>
       <c r="D140" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" t="s">
         <v>570</v>
       </c>
-      <c r="E140" t="s">
-        <v>17</v>
-      </c>
       <c r="F140" t="s">
-        <v>517</v>
-      </c>
-      <c r="G140" t="s">
         <v>571</v>
       </c>
+      <c r="H140" t="s">
+        <v>604</v>
+      </c>
       <c r="I140" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K140" t="s">
-        <v>605</v>
+        <v>520</v>
       </c>
       <c r="L140" t="s">
         <v>521</v>
@@ -9093,22 +9093,22 @@
         <v>15</v>
       </c>
       <c r="D141" t="s">
+        <v>16</v>
+      </c>
+      <c r="E141" t="s">
         <v>570</v>
       </c>
-      <c r="E141" t="s">
-        <v>17</v>
-      </c>
       <c r="F141" t="s">
-        <v>517</v>
-      </c>
-      <c r="G141" t="s">
         <v>571</v>
       </c>
+      <c r="H141" t="s">
+        <v>608</v>
+      </c>
       <c r="I141" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K141" t="s">
-        <v>609</v>
+        <v>520</v>
       </c>
       <c r="L141" t="s">
         <v>521</v>
@@ -9128,22 +9128,22 @@
         <v>15</v>
       </c>
       <c r="D142" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142" t="s">
         <v>570</v>
       </c>
-      <c r="E142" t="s">
-        <v>17</v>
-      </c>
       <c r="F142" t="s">
-        <v>517</v>
-      </c>
-      <c r="G142" t="s">
         <v>571</v>
       </c>
+      <c r="H142" t="s">
+        <v>612</v>
+      </c>
       <c r="I142" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K142" t="s">
-        <v>613</v>
+        <v>520</v>
       </c>
       <c r="L142" t="s">
         <v>521</v>
@@ -9163,22 +9163,22 @@
         <v>15</v>
       </c>
       <c r="D143" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" t="s">
         <v>616</v>
       </c>
-      <c r="E143" t="s">
-        <v>17</v>
-      </c>
       <c r="F143" t="s">
-        <v>517</v>
-      </c>
-      <c r="G143" t="s">
         <v>617</v>
       </c>
+      <c r="H143" t="s">
+        <v>618</v>
+      </c>
       <c r="I143" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="K143" t="s">
-        <v>619</v>
+        <v>520</v>
       </c>
       <c r="L143" t="s">
         <v>521</v>
@@ -9198,22 +9198,22 @@
         <v>15</v>
       </c>
       <c r="D144" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" t="s">
         <v>616</v>
       </c>
-      <c r="E144" t="s">
-        <v>17</v>
-      </c>
       <c r="F144" t="s">
-        <v>517</v>
-      </c>
-      <c r="G144" t="s">
         <v>617</v>
       </c>
+      <c r="H144" t="s">
+        <v>622</v>
+      </c>
       <c r="I144" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K144" t="s">
-        <v>623</v>
+        <v>520</v>
       </c>
       <c r="L144" t="s">
         <v>521</v>
@@ -9233,22 +9233,22 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" t="s">
         <v>616</v>
       </c>
-      <c r="E145" t="s">
-        <v>17</v>
-      </c>
       <c r="F145" t="s">
-        <v>517</v>
-      </c>
-      <c r="G145" t="s">
         <v>617</v>
       </c>
+      <c r="H145" t="s">
+        <v>626</v>
+      </c>
       <c r="I145" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="K145" t="s">
-        <v>627</v>
+        <v>520</v>
       </c>
       <c r="L145" t="s">
         <v>521</v>
@@ -9268,22 +9268,22 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
+        <v>16</v>
+      </c>
+      <c r="E146" t="s">
         <v>616</v>
       </c>
-      <c r="E146" t="s">
-        <v>17</v>
-      </c>
       <c r="F146" t="s">
-        <v>517</v>
-      </c>
-      <c r="G146" t="s">
         <v>617</v>
       </c>
+      <c r="H146" t="s">
+        <v>630</v>
+      </c>
       <c r="I146" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="K146" t="s">
-        <v>631</v>
+        <v>520</v>
       </c>
       <c r="L146" t="s">
         <v>521</v>
@@ -9303,22 +9303,22 @@
         <v>15</v>
       </c>
       <c r="D147" t="s">
+        <v>16</v>
+      </c>
+      <c r="E147" t="s">
         <v>616</v>
       </c>
-      <c r="E147" t="s">
-        <v>17</v>
-      </c>
       <c r="F147" t="s">
-        <v>517</v>
-      </c>
-      <c r="G147" t="s">
         <v>617</v>
       </c>
+      <c r="H147" t="s">
+        <v>634</v>
+      </c>
       <c r="I147" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K147" t="s">
-        <v>635</v>
+        <v>520</v>
       </c>
       <c r="L147" t="s">
         <v>521</v>
@@ -9338,22 +9338,22 @@
         <v>15</v>
       </c>
       <c r="D148" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" t="s">
         <v>616</v>
       </c>
-      <c r="E148" t="s">
-        <v>17</v>
-      </c>
       <c r="F148" t="s">
-        <v>517</v>
-      </c>
-      <c r="G148" t="s">
         <v>617</v>
       </c>
+      <c r="H148" t="s">
+        <v>638</v>
+      </c>
       <c r="I148" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K148" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="L148" t="s">
         <v>521</v>
@@ -9373,22 +9373,22 @@
         <v>15</v>
       </c>
       <c r="D149" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" t="s">
         <v>616</v>
       </c>
-      <c r="E149" t="s">
-        <v>17</v>
-      </c>
       <c r="F149" t="s">
-        <v>517</v>
-      </c>
-      <c r="G149" t="s">
         <v>617</v>
       </c>
+      <c r="H149" t="s">
+        <v>642</v>
+      </c>
       <c r="I149" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K149" t="s">
-        <v>643</v>
+        <v>520</v>
       </c>
       <c r="L149" t="s">
         <v>521</v>
@@ -9408,22 +9408,22 @@
         <v>15</v>
       </c>
       <c r="D150" t="s">
+        <v>16</v>
+      </c>
+      <c r="E150" t="s">
         <v>616</v>
       </c>
-      <c r="E150" t="s">
-        <v>17</v>
-      </c>
       <c r="F150" t="s">
-        <v>517</v>
-      </c>
-      <c r="G150" t="s">
         <v>617</v>
       </c>
+      <c r="H150" t="s">
+        <v>646</v>
+      </c>
       <c r="I150" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K150" t="s">
-        <v>647</v>
+        <v>520</v>
       </c>
       <c r="L150" t="s">
         <v>521</v>
@@ -9443,22 +9443,22 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
+        <v>16</v>
+      </c>
+      <c r="E151" t="s">
         <v>616</v>
       </c>
-      <c r="E151" t="s">
-        <v>17</v>
-      </c>
       <c r="F151" t="s">
-        <v>517</v>
-      </c>
-      <c r="G151" t="s">
         <v>617</v>
       </c>
+      <c r="H151" t="s">
+        <v>650</v>
+      </c>
       <c r="I151" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K151" t="s">
-        <v>651</v>
+        <v>520</v>
       </c>
       <c r="L151" t="s">
         <v>521</v>
@@ -9478,22 +9478,22 @@
         <v>15</v>
       </c>
       <c r="D152" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" t="s">
         <v>654</v>
       </c>
-      <c r="E152" t="s">
-        <v>17</v>
-      </c>
       <c r="F152" t="s">
-        <v>517</v>
-      </c>
-      <c r="G152" t="s">
         <v>655</v>
       </c>
+      <c r="H152" t="s">
+        <v>656</v>
+      </c>
       <c r="I152" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K152" t="s">
-        <v>657</v>
+        <v>520</v>
       </c>
       <c r="L152" t="s">
         <v>521</v>
@@ -9513,22 +9513,22 @@
         <v>15</v>
       </c>
       <c r="D153" t="s">
+        <v>16</v>
+      </c>
+      <c r="E153" t="s">
         <v>654</v>
       </c>
-      <c r="E153" t="s">
-        <v>17</v>
-      </c>
       <c r="F153" t="s">
-        <v>517</v>
-      </c>
-      <c r="G153" t="s">
         <v>655</v>
       </c>
+      <c r="H153" t="s">
+        <v>660</v>
+      </c>
       <c r="I153" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="K153" t="s">
-        <v>661</v>
+        <v>520</v>
       </c>
       <c r="L153" t="s">
         <v>521</v>
@@ -9548,22 +9548,22 @@
         <v>15</v>
       </c>
       <c r="D154" t="s">
+        <v>16</v>
+      </c>
+      <c r="E154" t="s">
         <v>654</v>
       </c>
-      <c r="E154" t="s">
-        <v>17</v>
-      </c>
       <c r="F154" t="s">
-        <v>517</v>
-      </c>
-      <c r="G154" t="s">
         <v>655</v>
       </c>
+      <c r="H154" t="s">
+        <v>664</v>
+      </c>
       <c r="I154" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K154" t="s">
-        <v>665</v>
+        <v>520</v>
       </c>
       <c r="L154" t="s">
         <v>521</v>
@@ -9583,22 +9583,22 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
+        <v>16</v>
+      </c>
+      <c r="E155" t="s">
         <v>654</v>
       </c>
-      <c r="E155" t="s">
-        <v>17</v>
-      </c>
       <c r="F155" t="s">
-        <v>517</v>
-      </c>
-      <c r="G155" t="s">
         <v>655</v>
       </c>
+      <c r="H155" t="s">
+        <v>668</v>
+      </c>
       <c r="I155" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="K155" t="s">
-        <v>669</v>
+        <v>520</v>
       </c>
       <c r="L155" t="s">
         <v>521</v>
@@ -9618,22 +9618,22 @@
         <v>15</v>
       </c>
       <c r="D156" t="s">
+        <v>16</v>
+      </c>
+      <c r="E156" t="s">
         <v>654</v>
       </c>
-      <c r="E156" t="s">
-        <v>17</v>
-      </c>
       <c r="F156" t="s">
-        <v>517</v>
-      </c>
-      <c r="G156" t="s">
         <v>655</v>
       </c>
+      <c r="H156" t="s">
+        <v>672</v>
+      </c>
       <c r="I156" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K156" t="s">
-        <v>673</v>
+        <v>520</v>
       </c>
       <c r="L156" t="s">
         <v>521</v>
@@ -9653,22 +9653,22 @@
         <v>15</v>
       </c>
       <c r="D157" t="s">
+        <v>16</v>
+      </c>
+      <c r="E157" t="s">
         <v>654</v>
       </c>
-      <c r="E157" t="s">
-        <v>17</v>
-      </c>
       <c r="F157" t="s">
-        <v>517</v>
-      </c>
-      <c r="G157" t="s">
         <v>655</v>
       </c>
+      <c r="H157" t="s">
+        <v>676</v>
+      </c>
       <c r="I157" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K157" t="s">
-        <v>677</v>
+        <v>520</v>
       </c>
       <c r="L157" t="s">
         <v>521</v>
@@ -9688,22 +9688,22 @@
         <v>15</v>
       </c>
       <c r="D158" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158" t="s">
         <v>654</v>
       </c>
-      <c r="E158" t="s">
-        <v>17</v>
-      </c>
       <c r="F158" t="s">
-        <v>517</v>
-      </c>
-      <c r="G158" t="s">
         <v>655</v>
       </c>
+      <c r="H158" t="s">
+        <v>680</v>
+      </c>
       <c r="I158" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="K158" t="s">
-        <v>681</v>
+        <v>520</v>
       </c>
       <c r="L158" t="s">
         <v>521</v>
@@ -9723,22 +9723,22 @@
         <v>15</v>
       </c>
       <c r="D159" t="s">
+        <v>16</v>
+      </c>
+      <c r="E159" t="s">
         <v>654</v>
       </c>
-      <c r="E159" t="s">
-        <v>17</v>
-      </c>
       <c r="F159" t="s">
-        <v>517</v>
-      </c>
-      <c r="G159" t="s">
         <v>655</v>
       </c>
+      <c r="H159" t="s">
+        <v>684</v>
+      </c>
       <c r="I159" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K159" t="s">
-        <v>685</v>
+        <v>520</v>
       </c>
       <c r="L159" t="s">
         <v>521</v>
@@ -9758,22 +9758,22 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" t="s">
         <v>654</v>
       </c>
-      <c r="E160" t="s">
-        <v>17</v>
-      </c>
       <c r="F160" t="s">
-        <v>517</v>
-      </c>
-      <c r="G160" t="s">
         <v>655</v>
       </c>
+      <c r="H160" t="s">
+        <v>688</v>
+      </c>
       <c r="I160" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K160" t="s">
-        <v>689</v>
+        <v>520</v>
       </c>
       <c r="L160" t="s">
         <v>521</v>
@@ -9793,22 +9793,22 @@
         <v>15</v>
       </c>
       <c r="D161" t="s">
+        <v>16</v>
+      </c>
+      <c r="E161" t="s">
         <v>654</v>
       </c>
-      <c r="E161" t="s">
-        <v>17</v>
-      </c>
       <c r="F161" t="s">
-        <v>517</v>
-      </c>
-      <c r="G161" t="s">
         <v>655</v>
       </c>
+      <c r="H161" t="s">
+        <v>692</v>
+      </c>
       <c r="I161" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="K161" t="s">
-        <v>693</v>
+        <v>520</v>
       </c>
       <c r="L161" t="s">
         <v>521</v>
@@ -9828,22 +9828,22 @@
         <v>15</v>
       </c>
       <c r="D162" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" t="s">
         <v>654</v>
       </c>
-      <c r="E162" t="s">
-        <v>17</v>
-      </c>
       <c r="F162" t="s">
-        <v>517</v>
-      </c>
-      <c r="G162" t="s">
         <v>655</v>
       </c>
+      <c r="H162" t="s">
+        <v>696</v>
+      </c>
       <c r="I162" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K162" t="s">
-        <v>697</v>
+        <v>520</v>
       </c>
       <c r="L162" t="s">
         <v>521</v>
@@ -9863,22 +9863,22 @@
         <v>15</v>
       </c>
       <c r="D163" t="s">
+        <v>16</v>
+      </c>
+      <c r="E163" t="s">
         <v>654</v>
       </c>
-      <c r="E163" t="s">
-        <v>17</v>
-      </c>
       <c r="F163" t="s">
-        <v>517</v>
-      </c>
-      <c r="G163" t="s">
         <v>655</v>
       </c>
+      <c r="H163" t="s">
+        <v>700</v>
+      </c>
       <c r="I163" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K163" t="s">
-        <v>701</v>
+        <v>520</v>
       </c>
       <c r="L163" t="s">
         <v>521</v>
@@ -9898,22 +9898,22 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" t="s">
         <v>654</v>
       </c>
-      <c r="E164" t="s">
-        <v>17</v>
-      </c>
       <c r="F164" t="s">
-        <v>517</v>
-      </c>
-      <c r="G164" t="s">
         <v>655</v>
       </c>
+      <c r="H164" t="s">
+        <v>704</v>
+      </c>
       <c r="I164" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K164" t="s">
-        <v>705</v>
+        <v>520</v>
       </c>
       <c r="L164" t="s">
         <v>521</v>
@@ -9933,22 +9933,22 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
+        <v>16</v>
+      </c>
+      <c r="E165" t="s">
         <v>654</v>
       </c>
-      <c r="E165" t="s">
-        <v>17</v>
-      </c>
       <c r="F165" t="s">
-        <v>517</v>
-      </c>
-      <c r="G165" t="s">
         <v>655</v>
       </c>
+      <c r="H165" t="s">
+        <v>708</v>
+      </c>
       <c r="I165" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K165" t="s">
-        <v>709</v>
+        <v>520</v>
       </c>
       <c r="L165" t="s">
         <v>521</v>
@@ -9968,22 +9968,22 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" t="s">
         <v>654</v>
       </c>
-      <c r="E166" t="s">
-        <v>17</v>
-      </c>
       <c r="F166" t="s">
-        <v>517</v>
-      </c>
-      <c r="G166" t="s">
         <v>655</v>
       </c>
+      <c r="H166" t="s">
+        <v>712</v>
+      </c>
       <c r="I166" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K166" t="s">
-        <v>713</v>
+        <v>520</v>
       </c>
       <c r="L166" t="s">
         <v>521</v>
@@ -10003,22 +10003,22 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" t="s">
         <v>654</v>
       </c>
-      <c r="E167" t="s">
-        <v>17</v>
-      </c>
       <c r="F167" t="s">
-        <v>517</v>
-      </c>
-      <c r="G167" t="s">
         <v>655</v>
       </c>
+      <c r="H167" t="s">
+        <v>716</v>
+      </c>
       <c r="I167" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="K167" t="s">
-        <v>717</v>
+        <v>520</v>
       </c>
       <c r="L167" t="s">
         <v>521</v>
@@ -10038,22 +10038,22 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168" t="s">
         <v>654</v>
       </c>
-      <c r="E168" t="s">
-        <v>17</v>
-      </c>
       <c r="F168" t="s">
-        <v>517</v>
-      </c>
-      <c r="G168" t="s">
         <v>655</v>
       </c>
+      <c r="H168" t="s">
+        <v>720</v>
+      </c>
       <c r="I168" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K168" t="s">
-        <v>721</v>
+        <v>520</v>
       </c>
       <c r="L168" t="s">
         <v>521</v>
@@ -10073,22 +10073,22 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
+        <v>16</v>
+      </c>
+      <c r="E169" t="s">
         <v>654</v>
       </c>
-      <c r="E169" t="s">
-        <v>17</v>
-      </c>
       <c r="F169" t="s">
-        <v>517</v>
-      </c>
-      <c r="G169" t="s">
         <v>655</v>
       </c>
+      <c r="H169" t="s">
+        <v>724</v>
+      </c>
       <c r="I169" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K169" t="s">
-        <v>725</v>
+        <v>520</v>
       </c>
       <c r="L169" t="s">
         <v>521</v>
@@ -10108,15 +10108,15 @@
         <v>15</v>
       </c>
       <c r="D170" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" t="s">
         <v>728</v>
-      </c>
-      <c r="E170" t="s">
-        <v>17</v>
       </c>
       <c r="F170" t="s">
         <v>729</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>730</v>
       </c>
       <c r="I170" t="s">
@@ -10143,22 +10143,22 @@
         <v>15</v>
       </c>
       <c r="D171" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" t="s">
         <v>728</v>
-      </c>
-      <c r="E171" t="s">
-        <v>17</v>
       </c>
       <c r="F171" t="s">
         <v>729</v>
       </c>
-      <c r="G171" t="s">
-        <v>730</v>
+      <c r="H171" t="s">
+        <v>736</v>
       </c>
       <c r="I171" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K171" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="L171" t="s">
         <v>733</v>
@@ -10178,22 +10178,22 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" t="s">
         <v>728</v>
-      </c>
-      <c r="E172" t="s">
-        <v>17</v>
       </c>
       <c r="F172" t="s">
         <v>729</v>
       </c>
-      <c r="G172" t="s">
-        <v>730</v>
+      <c r="H172" t="s">
+        <v>740</v>
       </c>
       <c r="I172" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K172" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="L172" t="s">
         <v>733</v>
@@ -10213,22 +10213,22 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173" t="s">
         <v>728</v>
-      </c>
-      <c r="E173" t="s">
-        <v>17</v>
       </c>
       <c r="F173" t="s">
         <v>729</v>
       </c>
-      <c r="G173" t="s">
-        <v>730</v>
+      <c r="H173" t="s">
+        <v>744</v>
       </c>
       <c r="I173" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K173" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="L173" t="s">
         <v>733</v>
@@ -10248,22 +10248,22 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" t="s">
         <v>728</v>
-      </c>
-      <c r="E174" t="s">
-        <v>17</v>
       </c>
       <c r="F174" t="s">
         <v>729</v>
       </c>
-      <c r="G174" t="s">
-        <v>730</v>
+      <c r="H174" t="s">
+        <v>748</v>
       </c>
       <c r="I174" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="K174" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="L174" t="s">
         <v>733</v>
@@ -10283,22 +10283,22 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" t="s">
         <v>728</v>
-      </c>
-      <c r="E175" t="s">
-        <v>17</v>
       </c>
       <c r="F175" t="s">
         <v>729</v>
       </c>
-      <c r="G175" t="s">
-        <v>730</v>
+      <c r="H175" t="s">
+        <v>752</v>
       </c>
       <c r="I175" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="K175" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="L175" t="s">
         <v>733</v>
@@ -10318,22 +10318,22 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" t="s">
         <v>728</v>
-      </c>
-      <c r="E176" t="s">
-        <v>17</v>
       </c>
       <c r="F176" t="s">
         <v>729</v>
       </c>
-      <c r="G176" t="s">
-        <v>730</v>
+      <c r="H176" t="s">
+        <v>756</v>
       </c>
       <c r="I176" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="K176" t="s">
-        <v>757</v>
+        <v>732</v>
       </c>
       <c r="L176" t="s">
         <v>733</v>
@@ -10353,22 +10353,22 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" t="s">
         <v>728</v>
-      </c>
-      <c r="E177" t="s">
-        <v>17</v>
       </c>
       <c r="F177" t="s">
         <v>729</v>
       </c>
-      <c r="G177" t="s">
-        <v>730</v>
+      <c r="H177" t="s">
+        <v>760</v>
       </c>
       <c r="I177" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="K177" t="s">
-        <v>761</v>
+        <v>732</v>
       </c>
       <c r="L177" t="s">
         <v>733</v>
@@ -10388,22 +10388,22 @@
         <v>15</v>
       </c>
       <c r="D178" t="s">
+        <v>16</v>
+      </c>
+      <c r="E178" t="s">
         <v>728</v>
-      </c>
-      <c r="E178" t="s">
-        <v>17</v>
       </c>
       <c r="F178" t="s">
         <v>729</v>
       </c>
-      <c r="G178" t="s">
-        <v>730</v>
+      <c r="H178" t="s">
+        <v>764</v>
       </c>
       <c r="I178" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="K178" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="L178" t="s">
         <v>733</v>
@@ -10423,22 +10423,22 @@
         <v>15</v>
       </c>
       <c r="D179" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" t="s">
         <v>728</v>
-      </c>
-      <c r="E179" t="s">
-        <v>17</v>
       </c>
       <c r="F179" t="s">
         <v>729</v>
       </c>
-      <c r="G179" t="s">
-        <v>730</v>
+      <c r="H179" t="s">
+        <v>768</v>
       </c>
       <c r="I179" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K179" t="s">
-        <v>769</v>
+        <v>732</v>
       </c>
       <c r="L179" t="s">
         <v>733</v>
@@ -10458,22 +10458,22 @@
         <v>15</v>
       </c>
       <c r="D180" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" t="s">
         <v>772</v>
       </c>
-      <c r="E180" t="s">
-        <v>17</v>
-      </c>
       <c r="F180" t="s">
-        <v>729</v>
-      </c>
-      <c r="G180" t="s">
         <v>773</v>
       </c>
+      <c r="H180" t="s">
+        <v>774</v>
+      </c>
       <c r="I180" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="K180" t="s">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="L180" t="s">
         <v>733</v>
@@ -10493,28 +10493,28 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
+        <v>16</v>
+      </c>
+      <c r="E181" t="s">
         <v>772</v>
       </c>
-      <c r="E181" t="s">
-        <v>17</v>
-      </c>
       <c r="F181" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="G181" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="H181" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I181" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J181" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="K181" t="s">
-        <v>781</v>
+        <v>732</v>
       </c>
       <c r="L181" t="s">
         <v>733</v>
@@ -10534,28 +10534,28 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" t="s">
         <v>772</v>
       </c>
-      <c r="E182" t="s">
-        <v>17</v>
-      </c>
       <c r="F182" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="G182" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="H182" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="I182" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J182" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="K182" t="s">
-        <v>785</v>
+        <v>732</v>
       </c>
       <c r="L182" t="s">
         <v>733</v>
@@ -10575,22 +10575,22 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" t="s">
         <v>772</v>
       </c>
-      <c r="E183" t="s">
-        <v>17</v>
-      </c>
       <c r="F183" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="G183" t="s">
-        <v>773</v>
-      </c>
-      <c r="H183" t="s">
         <v>778</v>
       </c>
       <c r="J183" t="s">
-        <v>780</v>
+        <v>781</v>
+      </c>
+      <c r="K183" t="s">
+        <v>732</v>
       </c>
       <c r="L183" t="s">
         <v>733</v>
@@ -10610,22 +10610,22 @@
         <v>15</v>
       </c>
       <c r="D184" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" t="s">
         <v>772</v>
       </c>
-      <c r="E184" t="s">
-        <v>17</v>
-      </c>
       <c r="F184" t="s">
-        <v>729</v>
-      </c>
-      <c r="G184" t="s">
         <v>773</v>
       </c>
+      <c r="H184" t="s">
+        <v>790</v>
+      </c>
       <c r="I184" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K184" t="s">
-        <v>791</v>
+        <v>732</v>
       </c>
       <c r="L184" t="s">
         <v>733</v>
@@ -10645,22 +10645,22 @@
         <v>15</v>
       </c>
       <c r="D185" t="s">
+        <v>16</v>
+      </c>
+      <c r="E185" t="s">
         <v>772</v>
       </c>
-      <c r="E185" t="s">
-        <v>17</v>
-      </c>
       <c r="F185" t="s">
-        <v>729</v>
-      </c>
-      <c r="G185" t="s">
         <v>773</v>
       </c>
+      <c r="H185" t="s">
+        <v>794</v>
+      </c>
       <c r="I185" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="K185" t="s">
-        <v>795</v>
+        <v>732</v>
       </c>
       <c r="L185" t="s">
         <v>733</v>
@@ -10680,22 +10680,22 @@
         <v>15</v>
       </c>
       <c r="D186" t="s">
+        <v>16</v>
+      </c>
+      <c r="E186" t="s">
         <v>772</v>
       </c>
-      <c r="E186" t="s">
-        <v>17</v>
-      </c>
       <c r="F186" t="s">
-        <v>729</v>
-      </c>
-      <c r="G186" t="s">
         <v>773</v>
       </c>
+      <c r="H186" t="s">
+        <v>798</v>
+      </c>
       <c r="I186" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K186" t="s">
-        <v>799</v>
+        <v>732</v>
       </c>
       <c r="L186" t="s">
         <v>733</v>
@@ -10715,22 +10715,22 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" t="s">
         <v>772</v>
       </c>
-      <c r="E187" t="s">
-        <v>17</v>
-      </c>
       <c r="F187" t="s">
-        <v>729</v>
-      </c>
-      <c r="G187" t="s">
         <v>773</v>
       </c>
+      <c r="H187" t="s">
+        <v>802</v>
+      </c>
       <c r="I187" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K187" t="s">
-        <v>803</v>
+        <v>732</v>
       </c>
       <c r="L187" t="s">
         <v>733</v>
@@ -10750,22 +10750,22 @@
         <v>15</v>
       </c>
       <c r="D188" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188" t="s">
         <v>772</v>
       </c>
-      <c r="E188" t="s">
-        <v>17</v>
-      </c>
       <c r="F188" t="s">
-        <v>729</v>
-      </c>
-      <c r="G188" t="s">
         <v>773</v>
       </c>
+      <c r="H188" t="s">
+        <v>806</v>
+      </c>
       <c r="I188" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="K188" t="s">
-        <v>807</v>
+        <v>732</v>
       </c>
       <c r="L188" t="s">
         <v>733</v>
@@ -10785,22 +10785,22 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
+        <v>16</v>
+      </c>
+      <c r="E189" t="s">
         <v>772</v>
       </c>
-      <c r="E189" t="s">
-        <v>17</v>
-      </c>
       <c r="F189" t="s">
-        <v>729</v>
-      </c>
-      <c r="G189" t="s">
         <v>773</v>
       </c>
+      <c r="H189" t="s">
+        <v>810</v>
+      </c>
       <c r="I189" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K189" t="s">
-        <v>811</v>
+        <v>732</v>
       </c>
       <c r="L189" t="s">
         <v>733</v>
@@ -10820,22 +10820,22 @@
         <v>15</v>
       </c>
       <c r="D190" t="s">
+        <v>16</v>
+      </c>
+      <c r="E190" t="s">
         <v>772</v>
       </c>
-      <c r="E190" t="s">
-        <v>17</v>
-      </c>
       <c r="F190" t="s">
-        <v>729</v>
-      </c>
-      <c r="G190" t="s">
         <v>773</v>
       </c>
+      <c r="H190" t="s">
+        <v>814</v>
+      </c>
       <c r="I190" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="K190" t="s">
-        <v>815</v>
+        <v>732</v>
       </c>
       <c r="L190" t="s">
         <v>733</v>
@@ -10855,22 +10855,22 @@
         <v>15</v>
       </c>
       <c r="D191" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" t="s">
         <v>772</v>
       </c>
-      <c r="E191" t="s">
-        <v>17</v>
-      </c>
       <c r="F191" t="s">
-        <v>729</v>
-      </c>
-      <c r="G191" t="s">
         <v>773</v>
       </c>
+      <c r="H191" t="s">
+        <v>818</v>
+      </c>
       <c r="I191" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="K191" t="s">
-        <v>819</v>
+        <v>732</v>
       </c>
       <c r="L191" t="s">
         <v>733</v>
@@ -10890,22 +10890,22 @@
         <v>15</v>
       </c>
       <c r="D192" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192" t="s">
         <v>772</v>
       </c>
-      <c r="E192" t="s">
-        <v>17</v>
-      </c>
       <c r="F192" t="s">
-        <v>729</v>
-      </c>
-      <c r="G192" t="s">
         <v>773</v>
       </c>
+      <c r="H192" t="s">
+        <v>822</v>
+      </c>
       <c r="I192" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K192" t="s">
-        <v>823</v>
+        <v>732</v>
       </c>
       <c r="L192" t="s">
         <v>733</v>
@@ -10925,22 +10925,22 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193" t="s">
         <v>772</v>
       </c>
-      <c r="E193" t="s">
-        <v>17</v>
-      </c>
       <c r="F193" t="s">
-        <v>729</v>
-      </c>
-      <c r="G193" t="s">
         <v>773</v>
       </c>
+      <c r="H193" t="s">
+        <v>826</v>
+      </c>
       <c r="I193" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K193" t="s">
-        <v>827</v>
+        <v>732</v>
       </c>
       <c r="L193" t="s">
         <v>733</v>
@@ -10960,22 +10960,22 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" t="s">
         <v>772</v>
       </c>
-      <c r="E194" t="s">
-        <v>17</v>
-      </c>
       <c r="F194" t="s">
-        <v>729</v>
-      </c>
-      <c r="G194" t="s">
         <v>773</v>
       </c>
+      <c r="H194" t="s">
+        <v>830</v>
+      </c>
       <c r="I194" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K194" t="s">
-        <v>831</v>
+        <v>732</v>
       </c>
       <c r="L194" t="s">
         <v>733</v>
@@ -10995,22 +10995,22 @@
         <v>15</v>
       </c>
       <c r="D195" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195" t="s">
         <v>772</v>
       </c>
-      <c r="E195" t="s">
-        <v>17</v>
-      </c>
       <c r="F195" t="s">
-        <v>729</v>
-      </c>
-      <c r="G195" t="s">
         <v>773</v>
       </c>
+      <c r="H195" t="s">
+        <v>834</v>
+      </c>
       <c r="I195" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="K195" t="s">
-        <v>835</v>
+        <v>732</v>
       </c>
       <c r="L195" t="s">
         <v>733</v>
@@ -11030,22 +11030,22 @@
         <v>15</v>
       </c>
       <c r="D196" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" t="s">
         <v>772</v>
       </c>
-      <c r="E196" t="s">
-        <v>17</v>
-      </c>
       <c r="F196" t="s">
-        <v>729</v>
-      </c>
-      <c r="G196" t="s">
         <v>773</v>
       </c>
+      <c r="H196" t="s">
+        <v>838</v>
+      </c>
       <c r="I196" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K196" t="s">
-        <v>839</v>
+        <v>732</v>
       </c>
       <c r="L196" t="s">
         <v>733</v>
@@ -11065,22 +11065,22 @@
         <v>15</v>
       </c>
       <c r="D197" t="s">
+        <v>16</v>
+      </c>
+      <c r="E197" t="s">
         <v>842</v>
       </c>
-      <c r="E197" t="s">
-        <v>17</v>
-      </c>
       <c r="F197" t="s">
-        <v>729</v>
-      </c>
-      <c r="G197" t="s">
         <v>843</v>
       </c>
+      <c r="H197" t="s">
+        <v>844</v>
+      </c>
       <c r="I197" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K197" t="s">
-        <v>845</v>
+        <v>732</v>
       </c>
       <c r="L197" t="s">
         <v>733</v>
@@ -11100,22 +11100,22 @@
         <v>15</v>
       </c>
       <c r="D198" t="s">
+        <v>16</v>
+      </c>
+      <c r="E198" t="s">
         <v>842</v>
       </c>
-      <c r="E198" t="s">
-        <v>17</v>
-      </c>
       <c r="F198" t="s">
-        <v>729</v>
-      </c>
-      <c r="G198" t="s">
         <v>843</v>
       </c>
+      <c r="H198" t="s">
+        <v>848</v>
+      </c>
       <c r="I198" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="K198" t="s">
-        <v>849</v>
+        <v>732</v>
       </c>
       <c r="L198" t="s">
         <v>733</v>
@@ -11135,22 +11135,22 @@
         <v>15</v>
       </c>
       <c r="D199" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" t="s">
         <v>842</v>
       </c>
-      <c r="E199" t="s">
-        <v>17</v>
-      </c>
       <c r="F199" t="s">
-        <v>729</v>
-      </c>
-      <c r="G199" t="s">
         <v>843</v>
       </c>
+      <c r="H199" t="s">
+        <v>852</v>
+      </c>
       <c r="I199" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K199" t="s">
-        <v>853</v>
+        <v>732</v>
       </c>
       <c r="L199" t="s">
         <v>733</v>
@@ -11170,22 +11170,22 @@
         <v>15</v>
       </c>
       <c r="D200" t="s">
+        <v>16</v>
+      </c>
+      <c r="E200" t="s">
         <v>842</v>
       </c>
-      <c r="E200" t="s">
-        <v>17</v>
-      </c>
       <c r="F200" t="s">
-        <v>729</v>
-      </c>
-      <c r="G200" t="s">
         <v>843</v>
       </c>
+      <c r="H200" t="s">
+        <v>856</v>
+      </c>
       <c r="I200" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="K200" t="s">
-        <v>857</v>
+        <v>732</v>
       </c>
       <c r="L200" t="s">
         <v>733</v>
@@ -11205,22 +11205,22 @@
         <v>15</v>
       </c>
       <c r="D201" t="s">
+        <v>16</v>
+      </c>
+      <c r="E201" t="s">
         <v>842</v>
       </c>
-      <c r="E201" t="s">
-        <v>17</v>
-      </c>
       <c r="F201" t="s">
-        <v>729</v>
-      </c>
-      <c r="G201" t="s">
         <v>843</v>
       </c>
+      <c r="H201" t="s">
+        <v>860</v>
+      </c>
       <c r="I201" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K201" t="s">
-        <v>861</v>
+        <v>732</v>
       </c>
       <c r="L201" t="s">
         <v>733</v>
@@ -11240,22 +11240,22 @@
         <v>15</v>
       </c>
       <c r="D202" t="s">
+        <v>16</v>
+      </c>
+      <c r="E202" t="s">
         <v>842</v>
       </c>
-      <c r="E202" t="s">
-        <v>17</v>
-      </c>
       <c r="F202" t="s">
-        <v>729</v>
-      </c>
-      <c r="G202" t="s">
         <v>843</v>
       </c>
+      <c r="H202" t="s">
+        <v>864</v>
+      </c>
       <c r="I202" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K202" t="s">
-        <v>865</v>
+        <v>732</v>
       </c>
       <c r="L202" t="s">
         <v>733</v>
@@ -11275,22 +11275,22 @@
         <v>15</v>
       </c>
       <c r="D203" t="s">
+        <v>16</v>
+      </c>
+      <c r="E203" t="s">
         <v>842</v>
       </c>
-      <c r="E203" t="s">
-        <v>17</v>
-      </c>
       <c r="F203" t="s">
-        <v>729</v>
-      </c>
-      <c r="G203" t="s">
         <v>843</v>
       </c>
+      <c r="H203" t="s">
+        <v>868</v>
+      </c>
       <c r="I203" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="K203" t="s">
-        <v>869</v>
+        <v>732</v>
       </c>
       <c r="L203" t="s">
         <v>733</v>
@@ -11310,22 +11310,22 @@
         <v>15</v>
       </c>
       <c r="D204" t="s">
+        <v>16</v>
+      </c>
+      <c r="E204" t="s">
         <v>842</v>
       </c>
-      <c r="E204" t="s">
-        <v>17</v>
-      </c>
       <c r="F204" t="s">
-        <v>729</v>
-      </c>
-      <c r="G204" t="s">
         <v>843</v>
       </c>
+      <c r="H204" t="s">
+        <v>872</v>
+      </c>
       <c r="I204" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="K204" t="s">
-        <v>873</v>
+        <v>732</v>
       </c>
       <c r="L204" t="s">
         <v>733</v>
@@ -11345,22 +11345,22 @@
         <v>15</v>
       </c>
       <c r="D205" t="s">
+        <v>16</v>
+      </c>
+      <c r="E205" t="s">
         <v>842</v>
       </c>
-      <c r="E205" t="s">
-        <v>17</v>
-      </c>
       <c r="F205" t="s">
-        <v>729</v>
-      </c>
-      <c r="G205" t="s">
         <v>843</v>
       </c>
+      <c r="H205" t="s">
+        <v>876</v>
+      </c>
       <c r="I205" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K205" t="s">
-        <v>877</v>
+        <v>732</v>
       </c>
       <c r="L205" t="s">
         <v>733</v>
@@ -11380,22 +11380,22 @@
         <v>15</v>
       </c>
       <c r="D206" t="s">
+        <v>16</v>
+      </c>
+      <c r="E206" t="s">
         <v>842</v>
       </c>
-      <c r="E206" t="s">
-        <v>17</v>
-      </c>
       <c r="F206" t="s">
-        <v>729</v>
-      </c>
-      <c r="G206" t="s">
         <v>843</v>
       </c>
+      <c r="H206" t="s">
+        <v>880</v>
+      </c>
       <c r="I206" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="K206" t="s">
-        <v>881</v>
+        <v>732</v>
       </c>
       <c r="L206" t="s">
         <v>733</v>
@@ -11415,22 +11415,22 @@
         <v>15</v>
       </c>
       <c r="D207" t="s">
+        <v>16</v>
+      </c>
+      <c r="E207" t="s">
         <v>842</v>
       </c>
-      <c r="E207" t="s">
-        <v>17</v>
-      </c>
       <c r="F207" t="s">
-        <v>729</v>
-      </c>
-      <c r="G207" t="s">
         <v>843</v>
       </c>
+      <c r="H207" t="s">
+        <v>884</v>
+      </c>
       <c r="I207" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="K207" t="s">
-        <v>885</v>
+        <v>732</v>
       </c>
       <c r="L207" t="s">
         <v>733</v>
@@ -11450,22 +11450,22 @@
         <v>15</v>
       </c>
       <c r="D208" t="s">
+        <v>16</v>
+      </c>
+      <c r="E208" t="s">
         <v>842</v>
       </c>
-      <c r="E208" t="s">
-        <v>17</v>
-      </c>
       <c r="F208" t="s">
-        <v>729</v>
-      </c>
-      <c r="G208" t="s">
         <v>843</v>
       </c>
+      <c r="H208" t="s">
+        <v>888</v>
+      </c>
       <c r="I208" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="K208" t="s">
-        <v>889</v>
+        <v>732</v>
       </c>
       <c r="L208" t="s">
         <v>733</v>
@@ -11485,22 +11485,22 @@
         <v>15</v>
       </c>
       <c r="D209" t="s">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
         <v>842</v>
       </c>
-      <c r="E209" t="s">
-        <v>17</v>
-      </c>
       <c r="F209" t="s">
-        <v>729</v>
-      </c>
-      <c r="G209" t="s">
         <v>843</v>
       </c>
+      <c r="H209" t="s">
+        <v>892</v>
+      </c>
       <c r="I209" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="K209" t="s">
-        <v>893</v>
+        <v>732</v>
       </c>
       <c r="L209" t="s">
         <v>733</v>
@@ -11520,22 +11520,22 @@
         <v>15</v>
       </c>
       <c r="D210" t="s">
+        <v>16</v>
+      </c>
+      <c r="E210" t="s">
         <v>842</v>
       </c>
-      <c r="E210" t="s">
-        <v>17</v>
-      </c>
       <c r="F210" t="s">
-        <v>729</v>
-      </c>
-      <c r="G210" t="s">
         <v>843</v>
       </c>
+      <c r="H210" t="s">
+        <v>896</v>
+      </c>
       <c r="I210" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K210" t="s">
-        <v>897</v>
+        <v>732</v>
       </c>
       <c r="L210" t="s">
         <v>733</v>
@@ -11555,22 +11555,22 @@
         <v>15</v>
       </c>
       <c r="D211" t="s">
+        <v>16</v>
+      </c>
+      <c r="E211" t="s">
         <v>842</v>
       </c>
-      <c r="E211" t="s">
-        <v>17</v>
-      </c>
       <c r="F211" t="s">
-        <v>729</v>
-      </c>
-      <c r="G211" t="s">
         <v>843</v>
       </c>
+      <c r="H211" t="s">
+        <v>900</v>
+      </c>
       <c r="I211" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="K211" t="s">
-        <v>901</v>
+        <v>732</v>
       </c>
       <c r="L211" t="s">
         <v>733</v>
@@ -11590,22 +11590,22 @@
         <v>15</v>
       </c>
       <c r="D212" t="s">
+        <v>16</v>
+      </c>
+      <c r="E212" t="s">
         <v>842</v>
       </c>
-      <c r="E212" t="s">
-        <v>17</v>
-      </c>
       <c r="F212" t="s">
-        <v>729</v>
-      </c>
-      <c r="G212" t="s">
         <v>843</v>
       </c>
+      <c r="H212" t="s">
+        <v>904</v>
+      </c>
       <c r="I212" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="K212" t="s">
-        <v>905</v>
+        <v>732</v>
       </c>
       <c r="L212" t="s">
         <v>733</v>
@@ -11625,22 +11625,22 @@
         <v>15</v>
       </c>
       <c r="D213" t="s">
+        <v>16</v>
+      </c>
+      <c r="E213" t="s">
         <v>908</v>
       </c>
-      <c r="E213" t="s">
-        <v>17</v>
-      </c>
       <c r="F213" t="s">
-        <v>729</v>
-      </c>
-      <c r="G213" t="s">
         <v>909</v>
       </c>
+      <c r="H213" t="s">
+        <v>910</v>
+      </c>
       <c r="I213" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K213" t="s">
-        <v>911</v>
+        <v>732</v>
       </c>
       <c r="L213" t="s">
         <v>733</v>
@@ -11660,22 +11660,22 @@
         <v>15</v>
       </c>
       <c r="D214" t="s">
+        <v>16</v>
+      </c>
+      <c r="E214" t="s">
         <v>908</v>
       </c>
-      <c r="E214" t="s">
-        <v>17</v>
-      </c>
       <c r="F214" t="s">
-        <v>729</v>
-      </c>
-      <c r="G214" t="s">
         <v>909</v>
       </c>
+      <c r="H214" t="s">
+        <v>914</v>
+      </c>
       <c r="I214" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="K214" t="s">
-        <v>915</v>
+        <v>732</v>
       </c>
       <c r="L214" t="s">
         <v>733</v>
@@ -11695,22 +11695,22 @@
         <v>15</v>
       </c>
       <c r="D215" t="s">
+        <v>16</v>
+      </c>
+      <c r="E215" t="s">
         <v>908</v>
       </c>
-      <c r="E215" t="s">
-        <v>17</v>
-      </c>
       <c r="F215" t="s">
-        <v>729</v>
-      </c>
-      <c r="G215" t="s">
         <v>909</v>
       </c>
+      <c r="H215" t="s">
+        <v>918</v>
+      </c>
       <c r="I215" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="K215" t="s">
-        <v>919</v>
+        <v>732</v>
       </c>
       <c r="L215" t="s">
         <v>733</v>
@@ -11730,22 +11730,22 @@
         <v>15</v>
       </c>
       <c r="D216" t="s">
+        <v>16</v>
+      </c>
+      <c r="E216" t="s">
         <v>908</v>
       </c>
-      <c r="E216" t="s">
-        <v>17</v>
-      </c>
       <c r="F216" t="s">
-        <v>729</v>
-      </c>
-      <c r="G216" t="s">
         <v>909</v>
       </c>
+      <c r="H216" t="s">
+        <v>922</v>
+      </c>
       <c r="I216" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="K216" t="s">
-        <v>923</v>
+        <v>732</v>
       </c>
       <c r="L216" t="s">
         <v>733</v>
@@ -11765,22 +11765,22 @@
         <v>15</v>
       </c>
       <c r="D217" t="s">
+        <v>16</v>
+      </c>
+      <c r="E217" t="s">
         <v>908</v>
       </c>
-      <c r="E217" t="s">
-        <v>17</v>
-      </c>
       <c r="F217" t="s">
-        <v>729</v>
-      </c>
-      <c r="G217" t="s">
         <v>909</v>
       </c>
+      <c r="H217" t="s">
+        <v>926</v>
+      </c>
       <c r="I217" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="K217" t="s">
-        <v>927</v>
+        <v>732</v>
       </c>
       <c r="L217" t="s">
         <v>733</v>
@@ -11800,22 +11800,22 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
+        <v>16</v>
+      </c>
+      <c r="E218" t="s">
         <v>908</v>
       </c>
-      <c r="E218" t="s">
-        <v>17</v>
-      </c>
       <c r="F218" t="s">
-        <v>729</v>
-      </c>
-      <c r="G218" t="s">
         <v>909</v>
       </c>
+      <c r="H218" t="s">
+        <v>930</v>
+      </c>
       <c r="I218" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="K218" t="s">
-        <v>931</v>
+        <v>732</v>
       </c>
       <c r="L218" t="s">
         <v>733</v>
@@ -11835,22 +11835,22 @@
         <v>15</v>
       </c>
       <c r="D219" t="s">
+        <v>16</v>
+      </c>
+      <c r="E219" t="s">
         <v>908</v>
       </c>
-      <c r="E219" t="s">
-        <v>17</v>
-      </c>
       <c r="F219" t="s">
-        <v>729</v>
-      </c>
-      <c r="G219" t="s">
         <v>909</v>
       </c>
+      <c r="H219" t="s">
+        <v>934</v>
+      </c>
       <c r="I219" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="K219" t="s">
-        <v>935</v>
+        <v>732</v>
       </c>
       <c r="L219" t="s">
         <v>733</v>
@@ -11870,22 +11870,22 @@
         <v>15</v>
       </c>
       <c r="D220" t="s">
+        <v>16</v>
+      </c>
+      <c r="E220" t="s">
         <v>908</v>
       </c>
-      <c r="E220" t="s">
-        <v>17</v>
-      </c>
       <c r="F220" t="s">
-        <v>729</v>
-      </c>
-      <c r="G220" t="s">
         <v>909</v>
       </c>
+      <c r="H220" t="s">
+        <v>938</v>
+      </c>
       <c r="I220" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="K220" t="s">
-        <v>939</v>
+        <v>732</v>
       </c>
       <c r="L220" t="s">
         <v>733</v>
@@ -11905,22 +11905,22 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
+        <v>16</v>
+      </c>
+      <c r="E221" t="s">
         <v>908</v>
       </c>
-      <c r="E221" t="s">
-        <v>17</v>
-      </c>
       <c r="F221" t="s">
-        <v>729</v>
-      </c>
-      <c r="G221" t="s">
         <v>909</v>
       </c>
+      <c r="H221" t="s">
+        <v>942</v>
+      </c>
       <c r="I221" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="K221" t="s">
-        <v>943</v>
+        <v>732</v>
       </c>
       <c r="L221" t="s">
         <v>733</v>
@@ -11940,15 +11940,15 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
+        <v>16</v>
+      </c>
+      <c r="E222" t="s">
         <v>946</v>
-      </c>
-      <c r="E222" t="s">
-        <v>17</v>
       </c>
       <c r="F222" t="s">
         <v>947</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>948</v>
       </c>
       <c r="I222" t="s">
@@ -11975,22 +11975,22 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
+        <v>16</v>
+      </c>
+      <c r="E223" t="s">
         <v>946</v>
-      </c>
-      <c r="E223" t="s">
-        <v>17</v>
       </c>
       <c r="F223" t="s">
         <v>947</v>
       </c>
-      <c r="G223" t="s">
-        <v>948</v>
+      <c r="H223" t="s">
+        <v>954</v>
       </c>
       <c r="I223" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="K223" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="L223" t="s">
         <v>951</v>
@@ -12010,22 +12010,22 @@
         <v>15</v>
       </c>
       <c r="D224" t="s">
+        <v>16</v>
+      </c>
+      <c r="E224" t="s">
         <v>946</v>
-      </c>
-      <c r="E224" t="s">
-        <v>17</v>
       </c>
       <c r="F224" t="s">
         <v>947</v>
       </c>
-      <c r="G224" t="s">
-        <v>948</v>
+      <c r="H224" t="s">
+        <v>958</v>
       </c>
       <c r="I224" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="K224" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="L224" t="s">
         <v>951</v>
@@ -12045,22 +12045,22 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
+        <v>16</v>
+      </c>
+      <c r="E225" t="s">
         <v>946</v>
-      </c>
-      <c r="E225" t="s">
-        <v>17</v>
       </c>
       <c r="F225" t="s">
         <v>947</v>
       </c>
-      <c r="G225" t="s">
-        <v>948</v>
+      <c r="H225" t="s">
+        <v>962</v>
       </c>
       <c r="I225" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K225" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="L225" t="s">
         <v>951</v>
@@ -12080,22 +12080,22 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
+        <v>16</v>
+      </c>
+      <c r="E226" t="s">
         <v>946</v>
-      </c>
-      <c r="E226" t="s">
-        <v>17</v>
       </c>
       <c r="F226" t="s">
         <v>947</v>
       </c>
-      <c r="G226" t="s">
-        <v>948</v>
+      <c r="H226" t="s">
+        <v>966</v>
       </c>
       <c r="I226" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="K226" t="s">
-        <v>967</v>
+        <v>950</v>
       </c>
       <c r="L226" t="s">
         <v>951</v>
@@ -12115,22 +12115,22 @@
         <v>15</v>
       </c>
       <c r="D227" t="s">
+        <v>16</v>
+      </c>
+      <c r="E227" t="s">
         <v>946</v>
-      </c>
-      <c r="E227" t="s">
-        <v>17</v>
       </c>
       <c r="F227" t="s">
         <v>947</v>
       </c>
-      <c r="G227" t="s">
-        <v>948</v>
+      <c r="H227" t="s">
+        <v>970</v>
       </c>
       <c r="I227" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K227" t="s">
-        <v>971</v>
+        <v>950</v>
       </c>
       <c r="L227" t="s">
         <v>951</v>
@@ -12150,22 +12150,22 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
+        <v>16</v>
+      </c>
+      <c r="E228" t="s">
         <v>974</v>
       </c>
-      <c r="E228" t="s">
-        <v>17</v>
-      </c>
       <c r="F228" t="s">
-        <v>947</v>
-      </c>
-      <c r="G228" t="s">
         <v>975</v>
       </c>
+      <c r="H228" t="s">
+        <v>976</v>
+      </c>
       <c r="I228" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="K228" t="s">
-        <v>977</v>
+        <v>950</v>
       </c>
       <c r="L228" t="s">
         <v>951</v>
@@ -12185,22 +12185,22 @@
         <v>15</v>
       </c>
       <c r="D229" t="s">
+        <v>16</v>
+      </c>
+      <c r="E229" t="s">
         <v>974</v>
       </c>
-      <c r="E229" t="s">
-        <v>17</v>
-      </c>
       <c r="F229" t="s">
-        <v>947</v>
-      </c>
-      <c r="G229" t="s">
         <v>975</v>
       </c>
+      <c r="H229" t="s">
+        <v>980</v>
+      </c>
       <c r="I229" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="K229" t="s">
-        <v>981</v>
+        <v>950</v>
       </c>
       <c r="L229" t="s">
         <v>951</v>
@@ -12220,22 +12220,22 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
+        <v>16</v>
+      </c>
+      <c r="E230" t="s">
         <v>974</v>
       </c>
-      <c r="E230" t="s">
-        <v>17</v>
-      </c>
       <c r="F230" t="s">
-        <v>947</v>
-      </c>
-      <c r="G230" t="s">
         <v>975</v>
       </c>
+      <c r="H230" t="s">
+        <v>984</v>
+      </c>
       <c r="I230" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="K230" t="s">
-        <v>985</v>
+        <v>950</v>
       </c>
       <c r="L230" t="s">
         <v>951</v>
@@ -12255,22 +12255,22 @@
         <v>15</v>
       </c>
       <c r="D231" t="s">
+        <v>16</v>
+      </c>
+      <c r="E231" t="s">
         <v>974</v>
       </c>
-      <c r="E231" t="s">
-        <v>17</v>
-      </c>
       <c r="F231" t="s">
-        <v>947</v>
-      </c>
-      <c r="G231" t="s">
         <v>975</v>
       </c>
+      <c r="H231" t="s">
+        <v>988</v>
+      </c>
       <c r="I231" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="K231" t="s">
-        <v>989</v>
+        <v>950</v>
       </c>
       <c r="L231" t="s">
         <v>951</v>
@@ -12290,22 +12290,22 @@
         <v>15</v>
       </c>
       <c r="D232" t="s">
+        <v>16</v>
+      </c>
+      <c r="E232" t="s">
         <v>974</v>
       </c>
-      <c r="E232" t="s">
-        <v>17</v>
-      </c>
       <c r="F232" t="s">
-        <v>947</v>
-      </c>
-      <c r="G232" t="s">
         <v>975</v>
       </c>
+      <c r="H232" t="s">
+        <v>992</v>
+      </c>
       <c r="I232" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="K232" t="s">
-        <v>993</v>
+        <v>950</v>
       </c>
       <c r="L232" t="s">
         <v>951</v>
@@ -12325,22 +12325,22 @@
         <v>15</v>
       </c>
       <c r="D233" t="s">
+        <v>16</v>
+      </c>
+      <c r="E233" t="s">
         <v>996</v>
       </c>
-      <c r="E233" t="s">
-        <v>17</v>
-      </c>
       <c r="F233" t="s">
-        <v>947</v>
-      </c>
-      <c r="G233" t="s">
         <v>997</v>
       </c>
+      <c r="H233" t="s">
+        <v>998</v>
+      </c>
       <c r="I233" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="K233" t="s">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="L233" t="s">
         <v>951</v>
@@ -12360,22 +12360,22 @@
         <v>15</v>
       </c>
       <c r="D234" t="s">
+        <v>16</v>
+      </c>
+      <c r="E234" t="s">
         <v>996</v>
       </c>
-      <c r="E234" t="s">
-        <v>17</v>
-      </c>
       <c r="F234" t="s">
-        <v>947</v>
-      </c>
-      <c r="G234" t="s">
         <v>997</v>
       </c>
+      <c r="H234" t="s">
+        <v>1002</v>
+      </c>
       <c r="I234" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K234" t="s">
-        <v>1003</v>
+        <v>950</v>
       </c>
       <c r="L234" t="s">
         <v>951</v>
@@ -12395,22 +12395,22 @@
         <v>15</v>
       </c>
       <c r="D235" t="s">
+        <v>16</v>
+      </c>
+      <c r="E235" t="s">
         <v>996</v>
       </c>
-      <c r="E235" t="s">
-        <v>17</v>
-      </c>
       <c r="F235" t="s">
-        <v>947</v>
-      </c>
-      <c r="G235" t="s">
         <v>997</v>
       </c>
+      <c r="H235" t="s">
+        <v>1006</v>
+      </c>
       <c r="I235" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K235" t="s">
-        <v>1007</v>
+        <v>950</v>
       </c>
       <c r="L235" t="s">
         <v>951</v>
@@ -12430,22 +12430,22 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
+        <v>16</v>
+      </c>
+      <c r="E236" t="s">
         <v>996</v>
       </c>
-      <c r="E236" t="s">
-        <v>17</v>
-      </c>
       <c r="F236" t="s">
-        <v>947</v>
-      </c>
-      <c r="G236" t="s">
         <v>997</v>
       </c>
+      <c r="H236" t="s">
+        <v>1010</v>
+      </c>
       <c r="I236" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K236" t="s">
-        <v>1011</v>
+        <v>950</v>
       </c>
       <c r="L236" t="s">
         <v>951</v>
@@ -12465,22 +12465,22 @@
         <v>15</v>
       </c>
       <c r="D237" t="s">
+        <v>16</v>
+      </c>
+      <c r="E237" t="s">
         <v>996</v>
       </c>
-      <c r="E237" t="s">
-        <v>17</v>
-      </c>
       <c r="F237" t="s">
-        <v>947</v>
-      </c>
-      <c r="G237" t="s">
         <v>997</v>
       </c>
+      <c r="H237" t="s">
+        <v>1014</v>
+      </c>
       <c r="I237" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K237" t="s">
-        <v>1015</v>
+        <v>950</v>
       </c>
       <c r="L237" t="s">
         <v>951</v>
@@ -12500,22 +12500,22 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
+        <v>16</v>
+      </c>
+      <c r="E238" t="s">
         <v>996</v>
       </c>
-      <c r="E238" t="s">
-        <v>17</v>
-      </c>
       <c r="F238" t="s">
-        <v>947</v>
-      </c>
-      <c r="G238" t="s">
         <v>997</v>
       </c>
+      <c r="H238" t="s">
+        <v>1018</v>
+      </c>
       <c r="I238" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K238" t="s">
-        <v>1019</v>
+        <v>950</v>
       </c>
       <c r="L238" t="s">
         <v>951</v>
@@ -12535,22 +12535,22 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
+        <v>16</v>
+      </c>
+      <c r="E239" t="s">
         <v>996</v>
       </c>
-      <c r="E239" t="s">
-        <v>17</v>
-      </c>
       <c r="F239" t="s">
-        <v>947</v>
-      </c>
-      <c r="G239" t="s">
         <v>997</v>
       </c>
+      <c r="H239" t="s">
+        <v>1022</v>
+      </c>
       <c r="I239" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="K239" t="s">
-        <v>1023</v>
+        <v>950</v>
       </c>
       <c r="L239" t="s">
         <v>951</v>
@@ -12570,22 +12570,22 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
+        <v>16</v>
+      </c>
+      <c r="E240" t="s">
         <v>996</v>
       </c>
-      <c r="E240" t="s">
-        <v>17</v>
-      </c>
       <c r="F240" t="s">
-        <v>947</v>
-      </c>
-      <c r="G240" t="s">
         <v>997</v>
       </c>
+      <c r="H240" t="s">
+        <v>1026</v>
+      </c>
       <c r="I240" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="K240" t="s">
-        <v>1027</v>
+        <v>950</v>
       </c>
       <c r="L240" t="s">
         <v>951</v>
@@ -12605,22 +12605,22 @@
         <v>15</v>
       </c>
       <c r="D241" t="s">
+        <v>16</v>
+      </c>
+      <c r="E241" t="s">
         <v>1030</v>
       </c>
-      <c r="E241" t="s">
-        <v>17</v>
-      </c>
       <c r="F241" t="s">
-        <v>947</v>
-      </c>
-      <c r="G241" t="s">
         <v>1031</v>
       </c>
+      <c r="H241" t="s">
+        <v>1032</v>
+      </c>
       <c r="I241" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="K241" t="s">
-        <v>1033</v>
+        <v>950</v>
       </c>
       <c r="L241" t="s">
         <v>951</v>
@@ -12640,22 +12640,22 @@
         <v>15</v>
       </c>
       <c r="D242" t="s">
+        <v>16</v>
+      </c>
+      <c r="E242" t="s">
         <v>1030</v>
       </c>
-      <c r="E242" t="s">
-        <v>17</v>
-      </c>
       <c r="F242" t="s">
-        <v>947</v>
-      </c>
-      <c r="G242" t="s">
         <v>1031</v>
       </c>
+      <c r="H242" t="s">
+        <v>1036</v>
+      </c>
       <c r="I242" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="K242" t="s">
-        <v>1037</v>
+        <v>950</v>
       </c>
       <c r="L242" t="s">
         <v>951</v>
@@ -12675,22 +12675,22 @@
         <v>15</v>
       </c>
       <c r="D243" t="s">
+        <v>16</v>
+      </c>
+      <c r="E243" t="s">
         <v>1030</v>
       </c>
-      <c r="E243" t="s">
-        <v>17</v>
-      </c>
       <c r="F243" t="s">
-        <v>947</v>
-      </c>
-      <c r="G243" t="s">
         <v>1031</v>
       </c>
+      <c r="H243" t="s">
+        <v>1040</v>
+      </c>
       <c r="I243" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="K243" t="s">
-        <v>1041</v>
+        <v>950</v>
       </c>
       <c r="L243" t="s">
         <v>951</v>
@@ -12710,22 +12710,22 @@
         <v>15</v>
       </c>
       <c r="D244" t="s">
+        <v>16</v>
+      </c>
+      <c r="E244" t="s">
         <v>1030</v>
       </c>
-      <c r="E244" t="s">
-        <v>17</v>
-      </c>
       <c r="F244" t="s">
-        <v>947</v>
-      </c>
-      <c r="G244" t="s">
         <v>1031</v>
       </c>
+      <c r="H244" t="s">
+        <v>1044</v>
+      </c>
       <c r="I244" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="K244" t="s">
-        <v>1045</v>
+        <v>950</v>
       </c>
       <c r="L244" t="s">
         <v>951</v>
@@ -12745,22 +12745,22 @@
         <v>15</v>
       </c>
       <c r="D245" t="s">
+        <v>16</v>
+      </c>
+      <c r="E245" t="s">
         <v>1030</v>
       </c>
-      <c r="E245" t="s">
-        <v>17</v>
-      </c>
       <c r="F245" t="s">
-        <v>947</v>
-      </c>
-      <c r="G245" t="s">
         <v>1031</v>
       </c>
+      <c r="H245" t="s">
+        <v>1048</v>
+      </c>
       <c r="I245" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="K245" t="s">
-        <v>1049</v>
+        <v>950</v>
       </c>
       <c r="L245" t="s">
         <v>951</v>
@@ -12780,22 +12780,22 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
+        <v>16</v>
+      </c>
+      <c r="E246" t="s">
         <v>1030</v>
       </c>
-      <c r="E246" t="s">
-        <v>17</v>
-      </c>
       <c r="F246" t="s">
-        <v>947</v>
-      </c>
-      <c r="G246" t="s">
         <v>1031</v>
       </c>
+      <c r="H246" t="s">
+        <v>1052</v>
+      </c>
       <c r="I246" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K246" t="s">
-        <v>1053</v>
+        <v>950</v>
       </c>
       <c r="L246" t="s">
         <v>951</v>
@@ -12815,22 +12815,22 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
+        <v>16</v>
+      </c>
+      <c r="E247" t="s">
         <v>1030</v>
       </c>
-      <c r="E247" t="s">
-        <v>17</v>
-      </c>
       <c r="F247" t="s">
-        <v>947</v>
-      </c>
-      <c r="G247" t="s">
         <v>1031</v>
       </c>
+      <c r="H247" t="s">
+        <v>1056</v>
+      </c>
       <c r="I247" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="K247" t="s">
-        <v>1057</v>
+        <v>950</v>
       </c>
       <c r="L247" t="s">
         <v>951</v>
@@ -12850,22 +12850,22 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
+        <v>16</v>
+      </c>
+      <c r="E248" t="s">
         <v>1030</v>
       </c>
-      <c r="E248" t="s">
-        <v>17</v>
-      </c>
       <c r="F248" t="s">
-        <v>947</v>
-      </c>
-      <c r="G248" t="s">
         <v>1031</v>
       </c>
+      <c r="H248" t="s">
+        <v>1060</v>
+      </c>
       <c r="I248" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="K248" t="s">
-        <v>1061</v>
+        <v>950</v>
       </c>
       <c r="L248" t="s">
         <v>951</v>
@@ -12885,22 +12885,22 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
+        <v>16</v>
+      </c>
+      <c r="E249" t="s">
         <v>1030</v>
       </c>
-      <c r="E249" t="s">
-        <v>17</v>
-      </c>
       <c r="F249" t="s">
-        <v>947</v>
-      </c>
-      <c r="G249" t="s">
         <v>1031</v>
       </c>
+      <c r="H249" t="s">
+        <v>1064</v>
+      </c>
       <c r="I249" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="K249" t="s">
-        <v>1065</v>
+        <v>950</v>
       </c>
       <c r="L249" t="s">
         <v>951</v>
@@ -12920,22 +12920,22 @@
         <v>15</v>
       </c>
       <c r="D250" t="s">
+        <v>16</v>
+      </c>
+      <c r="E250" t="s">
         <v>1030</v>
       </c>
-      <c r="E250" t="s">
-        <v>17</v>
-      </c>
       <c r="F250" t="s">
-        <v>947</v>
-      </c>
-      <c r="G250" t="s">
         <v>1031</v>
       </c>
+      <c r="H250" t="s">
+        <v>1068</v>
+      </c>
       <c r="I250" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="K250" t="s">
-        <v>1069</v>
+        <v>950</v>
       </c>
       <c r="L250" t="s">
         <v>951</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -28,33 +28,33 @@
     <t>codeforiati:global-code</t>
   </si>
   <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-name</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
     <t>codeforiati:sub-region-name</t>
   </si>
   <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
-    <t>codeforiati:global-name</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -67,27 +67,27 @@
     <t>001</t>
   </si>
   <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
     <t>Northern Africa</t>
   </si>
   <si>
     <t>015</t>
   </si>
   <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
-    <t>World</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -166,24 +166,24 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>Sub-Saharan Africa</t>
   </si>
   <si>
     <t>202</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -442,18 +442,18 @@
     <t>Angola</t>
   </si>
   <si>
+    <t>Middle Africa</t>
+  </si>
+  <si>
+    <t>AO</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
-    <t>AO</t>
-  </si>
-  <si>
-    <t>AGO</t>
-  </si>
-  <si>
-    <t>Middle Africa</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -556,18 +556,18 @@
     <t>Botswana</t>
   </si>
   <si>
+    <t>Southern Africa</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>BWA</t>
+  </si>
+  <si>
     <t>018</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>BWA</t>
-  </si>
-  <si>
-    <t>Southern Africa</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -622,18 +622,18 @@
     <t>Benin</t>
   </si>
   <si>
+    <t>Western Africa</t>
+  </si>
+  <si>
+    <t>BJ</t>
+  </si>
+  <si>
+    <t>BEN</t>
+  </si>
+  <si>
     <t>011</t>
   </si>
   <si>
-    <t>BJ</t>
-  </si>
-  <si>
-    <t>BEN</t>
-  </si>
-  <si>
-    <t>Western Africa</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
     <t>Latin America and the Caribbean</t>
   </si>
   <si>
     <t>419</t>
   </si>
   <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>AIA</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
     <t>019</t>
   </si>
   <si>
@@ -1186,18 +1186,18 @@
     <t>Belize</t>
   </si>
   <si>
+    <t>Central America</t>
+  </si>
+  <si>
+    <t>BZ</t>
+  </si>
+  <si>
+    <t>BLZ</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
-    <t>BZ</t>
-  </si>
-  <si>
-    <t>BLZ</t>
-  </si>
-  <si>
-    <t>Central America</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -1288,18 +1288,18 @@
     <t>Argentina</t>
   </si>
   <si>
+    <t>South America</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>ARG</t>
-  </si>
-  <si>
-    <t>South America</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1486,18 +1486,18 @@
     <t>Bermuda</t>
   </si>
   <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>BMU</t>
+  </si>
+  <si>
     <t>Northern America</t>
   </si>
   <si>
     <t>021</t>
   </si>
   <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>BMU</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1564,21 +1564,21 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>Central Asia</t>
   </si>
   <si>
     <t>143</t>
   </si>
   <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>KAZ</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>142</t>
   </si>
   <si>
@@ -1636,18 +1636,18 @@
     <t>China</t>
   </si>
   <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
     <t>Eastern Asia</t>
   </si>
   <si>
     <t>030</t>
   </si>
   <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>CHN</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1726,18 +1726,18 @@
     <t>Brunei Darussalam</t>
   </si>
   <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>BRN</t>
+  </si>
+  <si>
     <t>South-eastern Asia</t>
   </si>
   <si>
     <t>035</t>
   </si>
   <si>
-    <t>BN</t>
-  </si>
-  <si>
-    <t>BRN</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1864,18 +1864,18 @@
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFG</t>
+  </si>
+  <si>
     <t>Southern Asia</t>
   </si>
   <si>
     <t>034</t>
   </si>
   <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFG</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1978,18 +1978,18 @@
     <t>Armenia</t>
   </si>
   <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
     <t>Western Asia</t>
   </si>
   <si>
     <t>145</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>ARM</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -2200,21 +2200,21 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>Eastern Europe</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -2332,36 +2332,36 @@
     <t>Åland Islands</t>
   </si>
   <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>ALA</t>
+  </si>
+  <si>
     <t>Northern Europe</t>
   </si>
   <si>
     <t>154</t>
   </si>
   <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>ALA</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
     <t>Guernsey</t>
   </si>
   <si>
+    <t>Channel Islands</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>GGY</t>
+  </si>
+  <si>
     <t>830</t>
   </si>
   <si>
-    <t>GG</t>
-  </si>
-  <si>
-    <t>GGY</t>
-  </si>
-  <si>
-    <t>Channel Islands</t>
-  </si>
-  <si>
     <t>832</t>
   </si>
   <si>
@@ -2542,18 +2542,18 @@
     <t>Albania</t>
   </si>
   <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
     <t>Southern Europe</t>
   </si>
   <si>
     <t>039</t>
   </si>
   <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2740,18 +2740,18 @@
     <t>Austria</t>
   </si>
   <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
     <t>Western Europe</t>
   </si>
   <si>
     <t>155</t>
   </si>
   <si>
-    <t>AT</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2854,21 +2854,21 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
     <t>Australia and New Zealand</t>
   </si>
   <si>
     <t>053</t>
   </si>
   <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
     <t>009</t>
   </si>
   <si>
@@ -2938,18 +2938,18 @@
     <t>Fiji</t>
   </si>
   <si>
+    <t>FJ</t>
+  </si>
+  <si>
+    <t>FJI</t>
+  </si>
+  <si>
     <t>Melanesia</t>
   </si>
   <si>
     <t>054</t>
   </si>
   <si>
-    <t>FJ</t>
-  </si>
-  <si>
-    <t>FJI</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -3004,18 +3004,18 @@
     <t>Guam</t>
   </si>
   <si>
+    <t>GU</t>
+  </si>
+  <si>
+    <t>GUM</t>
+  </si>
+  <si>
     <t>Micronesia</t>
   </si>
   <si>
     <t>057</t>
   </si>
   <si>
-    <t>GU</t>
-  </si>
-  <si>
-    <t>GUM</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -3106,16 +3106,16 @@
     <t>American Samoa</t>
   </si>
   <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>ASM</t>
+  </si>
+  <si>
     <t>Polynesia</t>
   </si>
   <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>ASM</t>
   </si>
   <si>
     <t>184</t>
@@ -3858,28 +3858,28 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
         <v>50</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>51</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>52</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>53</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>54</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>55</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" t="s">
-        <v>22</v>
       </c>
       <c r="M9" t="s">
         <v>23</v>
@@ -3899,13 +3899,13 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
         <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" t="s">
-        <v>52</v>
       </c>
       <c r="H10" t="s">
         <v>58</v>
@@ -3914,13 +3914,13 @@
         <v>59</v>
       </c>
       <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
         <v>55</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" t="s">
-        <v>22</v>
       </c>
       <c r="M10" t="s">
         <v>23</v>
@@ -3940,13 +3940,13 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
         <v>50</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>52</v>
       </c>
       <c r="H11" t="s">
         <v>62</v>
@@ -3955,13 +3955,13 @@
         <v>63</v>
       </c>
       <c r="J11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
         <v>55</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" t="s">
-        <v>22</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
@@ -3981,13 +3981,13 @@
         <v>16</v>
       </c>
       <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
         <v>50</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" t="s">
-        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>66</v>
@@ -3996,13 +3996,13 @@
         <v>67</v>
       </c>
       <c r="J12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" t="s">
         <v>55</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" t="s">
-        <v>22</v>
       </c>
       <c r="M12" t="s">
         <v>23</v>
@@ -4022,13 +4022,13 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
         <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
@@ -4037,13 +4037,13 @@
         <v>71</v>
       </c>
       <c r="J13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" t="s">
         <v>55</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" t="s">
-        <v>22</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
@@ -4063,13 +4063,13 @@
         <v>16</v>
       </c>
       <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
         <v>50</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
       </c>
       <c r="H14" t="s">
         <v>74</v>
@@ -4078,13 +4078,13 @@
         <v>75</v>
       </c>
       <c r="J14" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" t="s">
         <v>55</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" t="s">
-        <v>22</v>
       </c>
       <c r="M14" t="s">
         <v>23</v>
@@ -4104,13 +4104,13 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
         <v>50</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" t="s">
-        <v>52</v>
       </c>
       <c r="H15" t="s">
         <v>78</v>
@@ -4119,13 +4119,13 @@
         <v>79</v>
       </c>
       <c r="J15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" t="s">
         <v>55</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" t="s">
-        <v>22</v>
       </c>
       <c r="M15" t="s">
         <v>23</v>
@@ -4145,13 +4145,13 @@
         <v>16</v>
       </c>
       <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
         <v>50</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" t="s">
-        <v>52</v>
       </c>
       <c r="H16" t="s">
         <v>82</v>
@@ -4160,13 +4160,13 @@
         <v>83</v>
       </c>
       <c r="J16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s">
         <v>55</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" t="s">
-        <v>22</v>
       </c>
       <c r="M16" t="s">
         <v>23</v>
@@ -4186,13 +4186,13 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" t="s">
-        <v>52</v>
       </c>
       <c r="H17" t="s">
         <v>86</v>
@@ -4201,13 +4201,13 @@
         <v>87</v>
       </c>
       <c r="J17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" t="s">
         <v>55</v>
-      </c>
-      <c r="K17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" t="s">
-        <v>22</v>
       </c>
       <c r="M17" t="s">
         <v>23</v>
@@ -4227,13 +4227,13 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
         <v>50</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" t="s">
-        <v>52</v>
       </c>
       <c r="H18" t="s">
         <v>90</v>
@@ -4242,13 +4242,13 @@
         <v>91</v>
       </c>
       <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" t="s">
         <v>55</v>
-      </c>
-      <c r="K18" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" t="s">
-        <v>22</v>
       </c>
       <c r="M18" t="s">
         <v>23</v>
@@ -4268,13 +4268,13 @@
         <v>16</v>
       </c>
       <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
         <v>50</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" t="s">
-        <v>52</v>
       </c>
       <c r="H19" t="s">
         <v>94</v>
@@ -4283,13 +4283,13 @@
         <v>95</v>
       </c>
       <c r="J19" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" t="s">
         <v>55</v>
-      </c>
-      <c r="K19" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" t="s">
-        <v>22</v>
       </c>
       <c r="M19" t="s">
         <v>23</v>
@@ -4309,13 +4309,13 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
         <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" t="s">
-        <v>52</v>
       </c>
       <c r="H20" t="s">
         <v>98</v>
@@ -4324,13 +4324,13 @@
         <v>99</v>
       </c>
       <c r="J20" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" t="s">
         <v>55</v>
-      </c>
-      <c r="K20" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" t="s">
-        <v>22</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -4350,13 +4350,13 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
         <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" t="s">
-        <v>52</v>
       </c>
       <c r="H21" t="s">
         <v>102</v>
@@ -4365,13 +4365,13 @@
         <v>103</v>
       </c>
       <c r="J21" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" t="s">
         <v>55</v>
-      </c>
-      <c r="K21" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" t="s">
-        <v>22</v>
       </c>
       <c r="M21" t="s">
         <v>23</v>
@@ -4391,13 +4391,13 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
         <v>50</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" t="s">
-        <v>52</v>
       </c>
       <c r="H22" t="s">
         <v>106</v>
@@ -4406,13 +4406,13 @@
         <v>107</v>
       </c>
       <c r="J22" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" t="s">
         <v>55</v>
-      </c>
-      <c r="K22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" t="s">
-        <v>22</v>
       </c>
       <c r="M22" t="s">
         <v>23</v>
@@ -4432,13 +4432,13 @@
         <v>16</v>
       </c>
       <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
         <v>50</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" t="s">
-        <v>52</v>
       </c>
       <c r="H23" t="s">
         <v>110</v>
@@ -4447,13 +4447,13 @@
         <v>111</v>
       </c>
       <c r="J23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K23" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" t="s">
         <v>55</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" t="s">
-        <v>22</v>
       </c>
       <c r="M23" t="s">
         <v>23</v>
@@ -4473,13 +4473,13 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
         <v>50</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" t="s">
-        <v>52</v>
       </c>
       <c r="H24" t="s">
         <v>114</v>
@@ -4488,13 +4488,13 @@
         <v>115</v>
       </c>
       <c r="J24" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" t="s">
         <v>55</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" t="s">
-        <v>22</v>
       </c>
       <c r="M24" t="s">
         <v>23</v>
@@ -4514,13 +4514,13 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
         <v>50</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" t="s">
-        <v>52</v>
       </c>
       <c r="H25" t="s">
         <v>118</v>
@@ -4529,13 +4529,13 @@
         <v>119</v>
       </c>
       <c r="J25" t="s">
+        <v>53</v>
+      </c>
+      <c r="K25" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" t="s">
         <v>55</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" t="s">
-        <v>22</v>
       </c>
       <c r="M25" t="s">
         <v>23</v>
@@ -4555,13 +4555,13 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
         <v>50</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" t="s">
-        <v>52</v>
       </c>
       <c r="H26" t="s">
         <v>122</v>
@@ -4570,13 +4570,13 @@
         <v>123</v>
       </c>
       <c r="J26" t="s">
+        <v>53</v>
+      </c>
+      <c r="K26" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" t="s">
         <v>55</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" t="s">
-        <v>22</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -4596,13 +4596,13 @@
         <v>16</v>
       </c>
       <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
         <v>50</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" t="s">
-        <v>52</v>
       </c>
       <c r="H27" t="s">
         <v>126</v>
@@ -4611,13 +4611,13 @@
         <v>127</v>
       </c>
       <c r="J27" t="s">
+        <v>53</v>
+      </c>
+      <c r="K27" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" t="s">
         <v>55</v>
-      </c>
-      <c r="K27" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" t="s">
-        <v>22</v>
       </c>
       <c r="M27" t="s">
         <v>23</v>
@@ -4637,13 +4637,13 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
         <v>50</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" t="s">
-        <v>52</v>
       </c>
       <c r="H28" t="s">
         <v>130</v>
@@ -4652,13 +4652,13 @@
         <v>131</v>
       </c>
       <c r="J28" t="s">
+        <v>53</v>
+      </c>
+      <c r="K28" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" t="s">
         <v>55</v>
-      </c>
-      <c r="K28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" t="s">
-        <v>22</v>
       </c>
       <c r="M28" t="s">
         <v>23</v>
@@ -4678,13 +4678,13 @@
         <v>16</v>
       </c>
       <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
         <v>50</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" t="s">
-        <v>52</v>
       </c>
       <c r="H29" t="s">
         <v>134</v>
@@ -4693,13 +4693,13 @@
         <v>135</v>
       </c>
       <c r="J29" t="s">
+        <v>53</v>
+      </c>
+      <c r="K29" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" t="s">
         <v>55</v>
-      </c>
-      <c r="K29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" t="s">
-        <v>22</v>
       </c>
       <c r="M29" t="s">
         <v>23</v>
@@ -4719,13 +4719,13 @@
         <v>16</v>
       </c>
       <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
         <v>50</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30" t="s">
-        <v>52</v>
       </c>
       <c r="H30" t="s">
         <v>138</v>
@@ -4734,13 +4734,13 @@
         <v>139</v>
       </c>
       <c r="J30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" t="s">
         <v>55</v>
-      </c>
-      <c r="K30" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" t="s">
-        <v>22</v>
       </c>
       <c r="M30" t="s">
         <v>23</v>
@@ -4760,10 +4760,10 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
         <v>142</v>
@@ -4778,10 +4778,10 @@
         <v>145</v>
       </c>
       <c r="K31" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L31" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M31" t="s">
         <v>23</v>
@@ -4801,10 +4801,10 @@
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
         <v>142</v>
@@ -4819,10 +4819,10 @@
         <v>145</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L32" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M32" t="s">
         <v>23</v>
@@ -4842,10 +4842,10 @@
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G33" t="s">
         <v>142</v>
@@ -4860,10 +4860,10 @@
         <v>145</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L33" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M33" t="s">
         <v>23</v>
@@ -4883,10 +4883,10 @@
         <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
         <v>142</v>
@@ -4901,10 +4901,10 @@
         <v>145</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L34" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M34" t="s">
         <v>23</v>
@@ -4924,10 +4924,10 @@
         <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
         <v>142</v>
@@ -4942,10 +4942,10 @@
         <v>145</v>
       </c>
       <c r="K35" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L35" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M35" t="s">
         <v>23</v>
@@ -4965,10 +4965,10 @@
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G36" t="s">
         <v>142</v>
@@ -4983,10 +4983,10 @@
         <v>145</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L36" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M36" t="s">
         <v>23</v>
@@ -5006,10 +5006,10 @@
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G37" t="s">
         <v>142</v>
@@ -5024,10 +5024,10 @@
         <v>145</v>
       </c>
       <c r="K37" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L37" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M37" t="s">
         <v>23</v>
@@ -5047,10 +5047,10 @@
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
         <v>142</v>
@@ -5065,10 +5065,10 @@
         <v>145</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L38" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -5088,10 +5088,10 @@
         <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
         <v>142</v>
@@ -5106,10 +5106,10 @@
         <v>145</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L39" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -5129,10 +5129,10 @@
         <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
         <v>180</v>
@@ -5147,10 +5147,10 @@
         <v>183</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L40" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -5170,10 +5170,10 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
         <v>180</v>
@@ -5188,10 +5188,10 @@
         <v>183</v>
       </c>
       <c r="K41" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L41" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -5211,10 +5211,10 @@
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
         <v>180</v>
@@ -5229,10 +5229,10 @@
         <v>183</v>
       </c>
       <c r="K42" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L42" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -5252,10 +5252,10 @@
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
         <v>180</v>
@@ -5270,10 +5270,10 @@
         <v>183</v>
       </c>
       <c r="K43" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L43" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
@@ -5293,10 +5293,10 @@
         <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
         <v>180</v>
@@ -5311,10 +5311,10 @@
         <v>183</v>
       </c>
       <c r="K44" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L44" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
@@ -5334,10 +5334,10 @@
         <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
         <v>202</v>
@@ -5352,10 +5352,10 @@
         <v>205</v>
       </c>
       <c r="K45" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L45" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -5375,10 +5375,10 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
         <v>202</v>
@@ -5393,10 +5393,10 @@
         <v>205</v>
       </c>
       <c r="K46" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L46" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -5416,10 +5416,10 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
         <v>202</v>
@@ -5434,10 +5434,10 @@
         <v>205</v>
       </c>
       <c r="K47" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L47" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
@@ -5457,10 +5457,10 @@
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s">
         <v>202</v>
@@ -5475,10 +5475,10 @@
         <v>205</v>
       </c>
       <c r="K48" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L48" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
@@ -5498,10 +5498,10 @@
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
         <v>202</v>
@@ -5516,10 +5516,10 @@
         <v>205</v>
       </c>
       <c r="K49" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L49" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
@@ -5539,10 +5539,10 @@
         <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
         <v>202</v>
@@ -5557,10 +5557,10 @@
         <v>205</v>
       </c>
       <c r="K50" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L50" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
@@ -5580,10 +5580,10 @@
         <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
         <v>202</v>
@@ -5598,10 +5598,10 @@
         <v>205</v>
       </c>
       <c r="K51" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L51" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -5621,10 +5621,10 @@
         <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G52" t="s">
         <v>202</v>
@@ -5639,10 +5639,10 @@
         <v>205</v>
       </c>
       <c r="K52" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L52" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -5662,10 +5662,10 @@
         <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G53" t="s">
         <v>202</v>
@@ -5680,10 +5680,10 @@
         <v>205</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L53" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M53" t="s">
         <v>23</v>
@@ -5703,10 +5703,10 @@
         <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s">
         <v>202</v>
@@ -5721,10 +5721,10 @@
         <v>205</v>
       </c>
       <c r="K54" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L54" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M54" t="s">
         <v>23</v>
@@ -5744,10 +5744,10 @@
         <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G55" t="s">
         <v>202</v>
@@ -5762,10 +5762,10 @@
         <v>205</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L55" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M55" t="s">
         <v>23</v>
@@ -5785,10 +5785,10 @@
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G56" t="s">
         <v>202</v>
@@ -5803,10 +5803,10 @@
         <v>205</v>
       </c>
       <c r="K56" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L56" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
@@ -5826,10 +5826,10 @@
         <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F57" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G57" t="s">
         <v>202</v>
@@ -5844,10 +5844,10 @@
         <v>205</v>
       </c>
       <c r="K57" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L57" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
@@ -5867,10 +5867,10 @@
         <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G58" t="s">
         <v>202</v>
@@ -5885,10 +5885,10 @@
         <v>205</v>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L58" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -5908,10 +5908,10 @@
         <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
         <v>202</v>
@@ -5926,10 +5926,10 @@
         <v>205</v>
       </c>
       <c r="K59" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L59" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
@@ -5949,10 +5949,10 @@
         <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G60" t="s">
         <v>202</v>
@@ -5967,10 +5967,10 @@
         <v>205</v>
       </c>
       <c r="K60" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L60" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
@@ -5990,10 +5990,10 @@
         <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
         <v>202</v>
@@ -6008,10 +6008,10 @@
         <v>205</v>
       </c>
       <c r="K61" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L61" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -6034,28 +6034,28 @@
         <v>272</v>
       </c>
       <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
         <v>273</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>274</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
         <v>275</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>276</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>277</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>278</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>279</v>
-      </c>
-      <c r="M62" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6075,10 +6075,10 @@
         <v>272</v>
       </c>
       <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
         <v>273</v>
-      </c>
-      <c r="G63" t="s">
-        <v>274</v>
       </c>
       <c r="H63" t="s">
         <v>282</v>
@@ -6087,16 +6087,16 @@
         <v>283</v>
       </c>
       <c r="J63" t="s">
+        <v>276</v>
+      </c>
+      <c r="K63" t="s">
         <v>277</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" t="s">
         <v>278</v>
       </c>
-      <c r="L63" t="s">
+      <c r="M63" t="s">
         <v>279</v>
-      </c>
-      <c r="M63" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6116,10 +6116,10 @@
         <v>272</v>
       </c>
       <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
         <v>273</v>
-      </c>
-      <c r="G64" t="s">
-        <v>274</v>
       </c>
       <c r="H64" t="s">
         <v>286</v>
@@ -6128,16 +6128,16 @@
         <v>287</v>
       </c>
       <c r="J64" t="s">
+        <v>276</v>
+      </c>
+      <c r="K64" t="s">
         <v>277</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>278</v>
       </c>
-      <c r="L64" t="s">
+      <c r="M64" t="s">
         <v>279</v>
-      </c>
-      <c r="M64" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6157,10 +6157,10 @@
         <v>272</v>
       </c>
       <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
         <v>273</v>
-      </c>
-      <c r="G65" t="s">
-        <v>274</v>
       </c>
       <c r="H65" t="s">
         <v>290</v>
@@ -6169,16 +6169,16 @@
         <v>291</v>
       </c>
       <c r="J65" t="s">
+        <v>276</v>
+      </c>
+      <c r="K65" t="s">
         <v>277</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>278</v>
       </c>
-      <c r="L65" t="s">
+      <c r="M65" t="s">
         <v>279</v>
-      </c>
-      <c r="M65" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6198,10 +6198,10 @@
         <v>272</v>
       </c>
       <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
         <v>273</v>
-      </c>
-      <c r="G66" t="s">
-        <v>274</v>
       </c>
       <c r="H66" t="s">
         <v>294</v>
@@ -6210,16 +6210,16 @@
         <v>295</v>
       </c>
       <c r="J66" t="s">
+        <v>276</v>
+      </c>
+      <c r="K66" t="s">
         <v>277</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>278</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>279</v>
-      </c>
-      <c r="M66" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6239,10 +6239,10 @@
         <v>272</v>
       </c>
       <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
         <v>273</v>
-      </c>
-      <c r="G67" t="s">
-        <v>274</v>
       </c>
       <c r="H67" t="s">
         <v>298</v>
@@ -6251,16 +6251,16 @@
         <v>299</v>
       </c>
       <c r="J67" t="s">
+        <v>276</v>
+      </c>
+      <c r="K67" t="s">
         <v>277</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>278</v>
       </c>
-      <c r="L67" t="s">
+      <c r="M67" t="s">
         <v>279</v>
-      </c>
-      <c r="M67" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6280,10 +6280,10 @@
         <v>272</v>
       </c>
       <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
         <v>273</v>
-      </c>
-      <c r="G68" t="s">
-        <v>274</v>
       </c>
       <c r="H68" t="s">
         <v>302</v>
@@ -6292,16 +6292,16 @@
         <v>303</v>
       </c>
       <c r="J68" t="s">
+        <v>276</v>
+      </c>
+      <c r="K68" t="s">
         <v>277</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>278</v>
       </c>
-      <c r="L68" t="s">
+      <c r="M68" t="s">
         <v>279</v>
-      </c>
-      <c r="M68" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6321,10 +6321,10 @@
         <v>272</v>
       </c>
       <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
         <v>273</v>
-      </c>
-      <c r="G69" t="s">
-        <v>274</v>
       </c>
       <c r="H69" t="s">
         <v>306</v>
@@ -6333,16 +6333,16 @@
         <v>307</v>
       </c>
       <c r="J69" t="s">
+        <v>276</v>
+      </c>
+      <c r="K69" t="s">
         <v>277</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>278</v>
       </c>
-      <c r="L69" t="s">
+      <c r="M69" t="s">
         <v>279</v>
-      </c>
-      <c r="M69" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6362,10 +6362,10 @@
         <v>272</v>
       </c>
       <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
         <v>273</v>
-      </c>
-      <c r="G70" t="s">
-        <v>274</v>
       </c>
       <c r="H70" t="s">
         <v>310</v>
@@ -6374,16 +6374,16 @@
         <v>311</v>
       </c>
       <c r="J70" t="s">
+        <v>276</v>
+      </c>
+      <c r="K70" t="s">
         <v>277</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>278</v>
       </c>
-      <c r="L70" t="s">
+      <c r="M70" t="s">
         <v>279</v>
-      </c>
-      <c r="M70" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6403,10 +6403,10 @@
         <v>272</v>
       </c>
       <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
         <v>273</v>
-      </c>
-      <c r="G71" t="s">
-        <v>274</v>
       </c>
       <c r="H71" t="s">
         <v>314</v>
@@ -6415,16 +6415,16 @@
         <v>315</v>
       </c>
       <c r="J71" t="s">
+        <v>276</v>
+      </c>
+      <c r="K71" t="s">
         <v>277</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>278</v>
       </c>
-      <c r="L71" t="s">
+      <c r="M71" t="s">
         <v>279</v>
-      </c>
-      <c r="M71" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -6444,10 +6444,10 @@
         <v>272</v>
       </c>
       <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
         <v>273</v>
-      </c>
-      <c r="G72" t="s">
-        <v>274</v>
       </c>
       <c r="H72" t="s">
         <v>318</v>
@@ -6456,16 +6456,16 @@
         <v>319</v>
       </c>
       <c r="J72" t="s">
+        <v>276</v>
+      </c>
+      <c r="K72" t="s">
         <v>277</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>278</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>279</v>
-      </c>
-      <c r="M72" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -6485,10 +6485,10 @@
         <v>272</v>
       </c>
       <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
         <v>273</v>
-      </c>
-      <c r="G73" t="s">
-        <v>274</v>
       </c>
       <c r="H73" t="s">
         <v>322</v>
@@ -6497,16 +6497,16 @@
         <v>323</v>
       </c>
       <c r="J73" t="s">
+        <v>276</v>
+      </c>
+      <c r="K73" t="s">
         <v>277</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>278</v>
       </c>
-      <c r="L73" t="s">
+      <c r="M73" t="s">
         <v>279</v>
-      </c>
-      <c r="M73" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -6526,10 +6526,10 @@
         <v>272</v>
       </c>
       <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
         <v>273</v>
-      </c>
-      <c r="G74" t="s">
-        <v>274</v>
       </c>
       <c r="H74" t="s">
         <v>326</v>
@@ -6538,16 +6538,16 @@
         <v>327</v>
       </c>
       <c r="J74" t="s">
+        <v>276</v>
+      </c>
+      <c r="K74" t="s">
         <v>277</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>278</v>
       </c>
-      <c r="L74" t="s">
+      <c r="M74" t="s">
         <v>279</v>
-      </c>
-      <c r="M74" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -6567,10 +6567,10 @@
         <v>272</v>
       </c>
       <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
         <v>273</v>
-      </c>
-      <c r="G75" t="s">
-        <v>274</v>
       </c>
       <c r="H75" t="s">
         <v>330</v>
@@ -6579,16 +6579,16 @@
         <v>331</v>
       </c>
       <c r="J75" t="s">
+        <v>276</v>
+      </c>
+      <c r="K75" t="s">
         <v>277</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>278</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>279</v>
-      </c>
-      <c r="M75" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -6608,10 +6608,10 @@
         <v>272</v>
       </c>
       <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
         <v>273</v>
-      </c>
-      <c r="G76" t="s">
-        <v>274</v>
       </c>
       <c r="H76" t="s">
         <v>334</v>
@@ -6620,16 +6620,16 @@
         <v>335</v>
       </c>
       <c r="J76" t="s">
+        <v>276</v>
+      </c>
+      <c r="K76" t="s">
         <v>277</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>278</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
         <v>279</v>
-      </c>
-      <c r="M76" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -6649,10 +6649,10 @@
         <v>272</v>
       </c>
       <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
         <v>273</v>
-      </c>
-      <c r="G77" t="s">
-        <v>274</v>
       </c>
       <c r="H77" t="s">
         <v>338</v>
@@ -6661,16 +6661,16 @@
         <v>339</v>
       </c>
       <c r="J77" t="s">
+        <v>276</v>
+      </c>
+      <c r="K77" t="s">
         <v>277</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>278</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>279</v>
-      </c>
-      <c r="M77" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6690,10 +6690,10 @@
         <v>272</v>
       </c>
       <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
         <v>273</v>
-      </c>
-      <c r="G78" t="s">
-        <v>274</v>
       </c>
       <c r="H78" t="s">
         <v>342</v>
@@ -6702,16 +6702,16 @@
         <v>343</v>
       </c>
       <c r="J78" t="s">
+        <v>276</v>
+      </c>
+      <c r="K78" t="s">
         <v>277</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>278</v>
       </c>
-      <c r="L78" t="s">
+      <c r="M78" t="s">
         <v>279</v>
-      </c>
-      <c r="M78" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -6731,10 +6731,10 @@
         <v>272</v>
       </c>
       <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
         <v>273</v>
-      </c>
-      <c r="G79" t="s">
-        <v>274</v>
       </c>
       <c r="H79" t="s">
         <v>346</v>
@@ -6743,16 +6743,16 @@
         <v>347</v>
       </c>
       <c r="J79" t="s">
+        <v>276</v>
+      </c>
+      <c r="K79" t="s">
         <v>277</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>278</v>
       </c>
-      <c r="L79" t="s">
+      <c r="M79" t="s">
         <v>279</v>
-      </c>
-      <c r="M79" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -6772,10 +6772,10 @@
         <v>272</v>
       </c>
       <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
         <v>273</v>
-      </c>
-      <c r="G80" t="s">
-        <v>274</v>
       </c>
       <c r="H80" t="s">
         <v>350</v>
@@ -6784,16 +6784,16 @@
         <v>351</v>
       </c>
       <c r="J80" t="s">
+        <v>276</v>
+      </c>
+      <c r="K80" t="s">
         <v>277</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>278</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
         <v>279</v>
-      </c>
-      <c r="M80" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -6813,10 +6813,10 @@
         <v>272</v>
       </c>
       <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
         <v>273</v>
-      </c>
-      <c r="G81" t="s">
-        <v>274</v>
       </c>
       <c r="H81" t="s">
         <v>354</v>
@@ -6825,16 +6825,16 @@
         <v>355</v>
       </c>
       <c r="J81" t="s">
+        <v>276</v>
+      </c>
+      <c r="K81" t="s">
         <v>277</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>278</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>279</v>
-      </c>
-      <c r="M81" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -6854,10 +6854,10 @@
         <v>272</v>
       </c>
       <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
         <v>273</v>
-      </c>
-      <c r="G82" t="s">
-        <v>274</v>
       </c>
       <c r="H82" t="s">
         <v>358</v>
@@ -6866,16 +6866,16 @@
         <v>359</v>
       </c>
       <c r="J82" t="s">
+        <v>276</v>
+      </c>
+      <c r="K82" t="s">
         <v>277</v>
       </c>
-      <c r="K82" t="s">
+      <c r="L82" t="s">
         <v>278</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>279</v>
-      </c>
-      <c r="M82" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6895,10 +6895,10 @@
         <v>272</v>
       </c>
       <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
         <v>273</v>
-      </c>
-      <c r="G83" t="s">
-        <v>274</v>
       </c>
       <c r="H83" t="s">
         <v>362</v>
@@ -6907,16 +6907,16 @@
         <v>363</v>
       </c>
       <c r="J83" t="s">
+        <v>276</v>
+      </c>
+      <c r="K83" t="s">
         <v>277</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>278</v>
       </c>
-      <c r="L83" t="s">
+      <c r="M83" t="s">
         <v>279</v>
-      </c>
-      <c r="M83" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -6936,10 +6936,10 @@
         <v>272</v>
       </c>
       <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
         <v>273</v>
-      </c>
-      <c r="G84" t="s">
-        <v>274</v>
       </c>
       <c r="H84" t="s">
         <v>366</v>
@@ -6948,16 +6948,16 @@
         <v>367</v>
       </c>
       <c r="J84" t="s">
+        <v>276</v>
+      </c>
+      <c r="K84" t="s">
         <v>277</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>278</v>
       </c>
-      <c r="L84" t="s">
+      <c r="M84" t="s">
         <v>279</v>
-      </c>
-      <c r="M84" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -6977,10 +6977,10 @@
         <v>272</v>
       </c>
       <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
         <v>273</v>
-      </c>
-      <c r="G85" t="s">
-        <v>274</v>
       </c>
       <c r="H85" t="s">
         <v>370</v>
@@ -6989,16 +6989,16 @@
         <v>371</v>
       </c>
       <c r="J85" t="s">
+        <v>276</v>
+      </c>
+      <c r="K85" t="s">
         <v>277</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
         <v>278</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>279</v>
-      </c>
-      <c r="M85" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7018,10 +7018,10 @@
         <v>272</v>
       </c>
       <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
         <v>273</v>
-      </c>
-      <c r="G86" t="s">
-        <v>274</v>
       </c>
       <c r="H86" t="s">
         <v>374</v>
@@ -7030,16 +7030,16 @@
         <v>375</v>
       </c>
       <c r="J86" t="s">
+        <v>276</v>
+      </c>
+      <c r="K86" t="s">
         <v>277</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>278</v>
       </c>
-      <c r="L86" t="s">
+      <c r="M86" t="s">
         <v>279</v>
-      </c>
-      <c r="M86" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7059,10 +7059,10 @@
         <v>272</v>
       </c>
       <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
         <v>273</v>
-      </c>
-      <c r="G87" t="s">
-        <v>274</v>
       </c>
       <c r="H87" t="s">
         <v>378</v>
@@ -7071,16 +7071,16 @@
         <v>379</v>
       </c>
       <c r="J87" t="s">
+        <v>276</v>
+      </c>
+      <c r="K87" t="s">
         <v>277</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>278</v>
       </c>
-      <c r="L87" t="s">
+      <c r="M87" t="s">
         <v>279</v>
-      </c>
-      <c r="M87" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7100,10 +7100,10 @@
         <v>272</v>
       </c>
       <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
         <v>273</v>
-      </c>
-      <c r="G88" t="s">
-        <v>274</v>
       </c>
       <c r="H88" t="s">
         <v>382</v>
@@ -7112,16 +7112,16 @@
         <v>383</v>
       </c>
       <c r="J88" t="s">
+        <v>276</v>
+      </c>
+      <c r="K88" t="s">
         <v>277</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" t="s">
         <v>278</v>
       </c>
-      <c r="L88" t="s">
+      <c r="M88" t="s">
         <v>279</v>
-      </c>
-      <c r="M88" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7141,10 +7141,10 @@
         <v>272</v>
       </c>
       <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
         <v>273</v>
-      </c>
-      <c r="G89" t="s">
-        <v>274</v>
       </c>
       <c r="H89" t="s">
         <v>386</v>
@@ -7153,16 +7153,16 @@
         <v>387</v>
       </c>
       <c r="J89" t="s">
+        <v>276</v>
+      </c>
+      <c r="K89" t="s">
         <v>277</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" t="s">
         <v>278</v>
       </c>
-      <c r="L89" t="s">
+      <c r="M89" t="s">
         <v>279</v>
-      </c>
-      <c r="M89" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7182,7 +7182,7 @@
         <v>272</v>
       </c>
       <c r="F90" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G90" t="s">
         <v>390</v>
@@ -7197,13 +7197,13 @@
         <v>393</v>
       </c>
       <c r="K90" t="s">
+        <v>277</v>
+      </c>
+      <c r="L90" t="s">
         <v>278</v>
       </c>
-      <c r="L90" t="s">
+      <c r="M90" t="s">
         <v>279</v>
-      </c>
-      <c r="M90" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7223,7 +7223,7 @@
         <v>272</v>
       </c>
       <c r="F91" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G91" t="s">
         <v>390</v>
@@ -7238,13 +7238,13 @@
         <v>393</v>
       </c>
       <c r="K91" t="s">
+        <v>277</v>
+      </c>
+      <c r="L91" t="s">
         <v>278</v>
       </c>
-      <c r="L91" t="s">
+      <c r="M91" t="s">
         <v>279</v>
-      </c>
-      <c r="M91" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7264,7 +7264,7 @@
         <v>272</v>
       </c>
       <c r="F92" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G92" t="s">
         <v>390</v>
@@ -7279,13 +7279,13 @@
         <v>393</v>
       </c>
       <c r="K92" t="s">
+        <v>277</v>
+      </c>
+      <c r="L92" t="s">
         <v>278</v>
       </c>
-      <c r="L92" t="s">
+      <c r="M92" t="s">
         <v>279</v>
-      </c>
-      <c r="M92" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7305,7 +7305,7 @@
         <v>272</v>
       </c>
       <c r="F93" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
         <v>390</v>
@@ -7320,13 +7320,13 @@
         <v>393</v>
       </c>
       <c r="K93" t="s">
+        <v>277</v>
+      </c>
+      <c r="L93" t="s">
         <v>278</v>
       </c>
-      <c r="L93" t="s">
+      <c r="M93" t="s">
         <v>279</v>
-      </c>
-      <c r="M93" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7346,7 +7346,7 @@
         <v>272</v>
       </c>
       <c r="F94" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
         <v>390</v>
@@ -7361,13 +7361,13 @@
         <v>393</v>
       </c>
       <c r="K94" t="s">
+        <v>277</v>
+      </c>
+      <c r="L94" t="s">
         <v>278</v>
       </c>
-      <c r="L94" t="s">
+      <c r="M94" t="s">
         <v>279</v>
-      </c>
-      <c r="M94" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7387,7 +7387,7 @@
         <v>272</v>
       </c>
       <c r="F95" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G95" t="s">
         <v>390</v>
@@ -7402,13 +7402,13 @@
         <v>393</v>
       </c>
       <c r="K95" t="s">
+        <v>277</v>
+      </c>
+      <c r="L95" t="s">
         <v>278</v>
       </c>
-      <c r="L95" t="s">
+      <c r="M95" t="s">
         <v>279</v>
-      </c>
-      <c r="M95" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7428,7 +7428,7 @@
         <v>272</v>
       </c>
       <c r="F96" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
         <v>390</v>
@@ -7443,13 +7443,13 @@
         <v>393</v>
       </c>
       <c r="K96" t="s">
+        <v>277</v>
+      </c>
+      <c r="L96" t="s">
         <v>278</v>
       </c>
-      <c r="L96" t="s">
+      <c r="M96" t="s">
         <v>279</v>
-      </c>
-      <c r="M96" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -7469,7 +7469,7 @@
         <v>272</v>
       </c>
       <c r="F97" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G97" t="s">
         <v>390</v>
@@ -7484,13 +7484,13 @@
         <v>393</v>
       </c>
       <c r="K97" t="s">
+        <v>277</v>
+      </c>
+      <c r="L97" t="s">
         <v>278</v>
       </c>
-      <c r="L97" t="s">
+      <c r="M97" t="s">
         <v>279</v>
-      </c>
-      <c r="M97" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7510,7 +7510,7 @@
         <v>272</v>
       </c>
       <c r="F98" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G98" t="s">
         <v>424</v>
@@ -7525,13 +7525,13 @@
         <v>427</v>
       </c>
       <c r="K98" t="s">
+        <v>277</v>
+      </c>
+      <c r="L98" t="s">
         <v>278</v>
       </c>
-      <c r="L98" t="s">
+      <c r="M98" t="s">
         <v>279</v>
-      </c>
-      <c r="M98" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -7551,7 +7551,7 @@
         <v>272</v>
       </c>
       <c r="F99" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G99" t="s">
         <v>424</v>
@@ -7566,13 +7566,13 @@
         <v>427</v>
       </c>
       <c r="K99" t="s">
+        <v>277</v>
+      </c>
+      <c r="L99" t="s">
         <v>278</v>
       </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>279</v>
-      </c>
-      <c r="M99" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -7592,7 +7592,7 @@
         <v>272</v>
       </c>
       <c r="F100" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G100" t="s">
         <v>424</v>
@@ -7607,13 +7607,13 @@
         <v>427</v>
       </c>
       <c r="K100" t="s">
+        <v>277</v>
+      </c>
+      <c r="L100" t="s">
         <v>278</v>
       </c>
-      <c r="L100" t="s">
+      <c r="M100" t="s">
         <v>279</v>
-      </c>
-      <c r="M100" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -7633,7 +7633,7 @@
         <v>272</v>
       </c>
       <c r="F101" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
         <v>424</v>
@@ -7648,13 +7648,13 @@
         <v>427</v>
       </c>
       <c r="K101" t="s">
+        <v>277</v>
+      </c>
+      <c r="L101" t="s">
         <v>278</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
         <v>279</v>
-      </c>
-      <c r="M101" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -7674,7 +7674,7 @@
         <v>272</v>
       </c>
       <c r="F102" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
         <v>424</v>
@@ -7689,13 +7689,13 @@
         <v>427</v>
       </c>
       <c r="K102" t="s">
+        <v>277</v>
+      </c>
+      <c r="L102" t="s">
         <v>278</v>
       </c>
-      <c r="L102" t="s">
+      <c r="M102" t="s">
         <v>279</v>
-      </c>
-      <c r="M102" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -7715,7 +7715,7 @@
         <v>272</v>
       </c>
       <c r="F103" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G103" t="s">
         <v>424</v>
@@ -7730,13 +7730,13 @@
         <v>427</v>
       </c>
       <c r="K103" t="s">
+        <v>277</v>
+      </c>
+      <c r="L103" t="s">
         <v>278</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
         <v>279</v>
-      </c>
-      <c r="M103" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -7756,7 +7756,7 @@
         <v>272</v>
       </c>
       <c r="F104" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
         <v>424</v>
@@ -7771,13 +7771,13 @@
         <v>427</v>
       </c>
       <c r="K104" t="s">
+        <v>277</v>
+      </c>
+      <c r="L104" t="s">
         <v>278</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>279</v>
-      </c>
-      <c r="M104" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -7797,7 +7797,7 @@
         <v>272</v>
       </c>
       <c r="F105" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
         <v>424</v>
@@ -7812,13 +7812,13 @@
         <v>427</v>
       </c>
       <c r="K105" t="s">
+        <v>277</v>
+      </c>
+      <c r="L105" t="s">
         <v>278</v>
       </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>279</v>
-      </c>
-      <c r="M105" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -7838,7 +7838,7 @@
         <v>272</v>
       </c>
       <c r="F106" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
         <v>424</v>
@@ -7853,13 +7853,13 @@
         <v>427</v>
       </c>
       <c r="K106" t="s">
+        <v>277</v>
+      </c>
+      <c r="L106" t="s">
         <v>278</v>
       </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>279</v>
-      </c>
-      <c r="M106" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -7879,7 +7879,7 @@
         <v>272</v>
       </c>
       <c r="F107" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G107" t="s">
         <v>424</v>
@@ -7894,13 +7894,13 @@
         <v>427</v>
       </c>
       <c r="K107" t="s">
+        <v>277</v>
+      </c>
+      <c r="L107" t="s">
         <v>278</v>
       </c>
-      <c r="L107" t="s">
+      <c r="M107" t="s">
         <v>279</v>
-      </c>
-      <c r="M107" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -7920,7 +7920,7 @@
         <v>272</v>
       </c>
       <c r="F108" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
         <v>424</v>
@@ -7935,13 +7935,13 @@
         <v>427</v>
       </c>
       <c r="K108" t="s">
+        <v>277</v>
+      </c>
+      <c r="L108" t="s">
         <v>278</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
         <v>279</v>
-      </c>
-      <c r="M108" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -7961,7 +7961,7 @@
         <v>272</v>
       </c>
       <c r="F109" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
         <v>424</v>
@@ -7976,13 +7976,13 @@
         <v>427</v>
       </c>
       <c r="K109" t="s">
+        <v>277</v>
+      </c>
+      <c r="L109" t="s">
         <v>278</v>
       </c>
-      <c r="L109" t="s">
+      <c r="M109" t="s">
         <v>279</v>
-      </c>
-      <c r="M109" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -8002,7 +8002,7 @@
         <v>272</v>
       </c>
       <c r="F110" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G110" t="s">
         <v>424</v>
@@ -8017,13 +8017,13 @@
         <v>427</v>
       </c>
       <c r="K110" t="s">
+        <v>277</v>
+      </c>
+      <c r="L110" t="s">
         <v>278</v>
       </c>
-      <c r="L110" t="s">
+      <c r="M110" t="s">
         <v>279</v>
-      </c>
-      <c r="M110" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -8043,7 +8043,7 @@
         <v>272</v>
       </c>
       <c r="F111" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G111" t="s">
         <v>424</v>
@@ -8058,13 +8058,13 @@
         <v>427</v>
       </c>
       <c r="K111" t="s">
+        <v>277</v>
+      </c>
+      <c r="L111" t="s">
         <v>278</v>
       </c>
-      <c r="L111" t="s">
+      <c r="M111" t="s">
         <v>279</v>
-      </c>
-      <c r="M111" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -8084,7 +8084,7 @@
         <v>272</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G112" t="s">
         <v>424</v>
@@ -8099,13 +8099,13 @@
         <v>427</v>
       </c>
       <c r="K112" t="s">
+        <v>277</v>
+      </c>
+      <c r="L112" t="s">
         <v>278</v>
       </c>
-      <c r="L112" t="s">
+      <c r="M112" t="s">
         <v>279</v>
-      </c>
-      <c r="M112" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -8125,7 +8125,7 @@
         <v>272</v>
       </c>
       <c r="F113" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G113" t="s">
         <v>424</v>
@@ -8140,13 +8140,13 @@
         <v>427</v>
       </c>
       <c r="K113" t="s">
+        <v>277</v>
+      </c>
+      <c r="L113" t="s">
         <v>278</v>
       </c>
-      <c r="L113" t="s">
+      <c r="M113" t="s">
         <v>279</v>
-      </c>
-      <c r="M113" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -8163,25 +8163,25 @@
         <v>16</v>
       </c>
       <c r="E114" t="s">
+        <v>272</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H114" t="s">
         <v>490</v>
       </c>
-      <c r="F114" t="s">
+      <c r="I114" t="s">
         <v>491</v>
       </c>
-      <c r="H114" t="s">
+      <c r="K114" t="s">
         <v>492</v>
       </c>
-      <c r="I114" t="s">
+      <c r="L114" t="s">
         <v>493</v>
       </c>
-      <c r="K114" t="s">
-        <v>278</v>
-      </c>
-      <c r="L114" t="s">
+      <c r="M114" t="s">
         <v>279</v>
-      </c>
-      <c r="M114" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -8198,10 +8198,10 @@
         <v>16</v>
       </c>
       <c r="E115" t="s">
-        <v>490</v>
+        <v>272</v>
       </c>
       <c r="F115" t="s">
-        <v>491</v>
+        <v>18</v>
       </c>
       <c r="H115" t="s">
         <v>496</v>
@@ -8210,13 +8210,13 @@
         <v>497</v>
       </c>
       <c r="K115" t="s">
-        <v>278</v>
+        <v>492</v>
       </c>
       <c r="L115" t="s">
+        <v>493</v>
+      </c>
+      <c r="M115" t="s">
         <v>279</v>
-      </c>
-      <c r="M115" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -8233,10 +8233,10 @@
         <v>16</v>
       </c>
       <c r="E116" t="s">
-        <v>490</v>
+        <v>272</v>
       </c>
       <c r="F116" t="s">
-        <v>491</v>
+        <v>18</v>
       </c>
       <c r="H116" t="s">
         <v>500</v>
@@ -8245,13 +8245,13 @@
         <v>501</v>
       </c>
       <c r="K116" t="s">
-        <v>278</v>
+        <v>492</v>
       </c>
       <c r="L116" t="s">
+        <v>493</v>
+      </c>
+      <c r="M116" t="s">
         <v>279</v>
-      </c>
-      <c r="M116" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -8268,10 +8268,10 @@
         <v>16</v>
       </c>
       <c r="E117" t="s">
-        <v>490</v>
+        <v>272</v>
       </c>
       <c r="F117" t="s">
-        <v>491</v>
+        <v>18</v>
       </c>
       <c r="H117" t="s">
         <v>504</v>
@@ -8280,13 +8280,13 @@
         <v>505</v>
       </c>
       <c r="K117" t="s">
-        <v>278</v>
+        <v>492</v>
       </c>
       <c r="L117" t="s">
+        <v>493</v>
+      </c>
+      <c r="M117" t="s">
         <v>279</v>
-      </c>
-      <c r="M117" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -8303,10 +8303,10 @@
         <v>16</v>
       </c>
       <c r="E118" t="s">
-        <v>490</v>
+        <v>272</v>
       </c>
       <c r="F118" t="s">
-        <v>491</v>
+        <v>18</v>
       </c>
       <c r="H118" t="s">
         <v>508</v>
@@ -8315,13 +8315,13 @@
         <v>509</v>
       </c>
       <c r="K118" t="s">
-        <v>278</v>
+        <v>492</v>
       </c>
       <c r="L118" t="s">
+        <v>493</v>
+      </c>
+      <c r="M118" t="s">
         <v>279</v>
-      </c>
-      <c r="M118" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -8337,14 +8337,14 @@
       <c r="D119" t="s">
         <v>16</v>
       </c>
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
       <c r="H119" t="s">
         <v>512</v>
       </c>
       <c r="I119" t="s">
         <v>513</v>
-      </c>
-      <c r="M119" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -8364,22 +8364,22 @@
         <v>516</v>
       </c>
       <c r="F120" t="s">
+        <v>18</v>
+      </c>
+      <c r="H120" t="s">
         <v>517</v>
       </c>
-      <c r="H120" t="s">
+      <c r="I120" t="s">
         <v>518</v>
       </c>
-      <c r="I120" t="s">
+      <c r="K120" t="s">
         <v>519</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>520</v>
       </c>
-      <c r="L120" t="s">
+      <c r="M120" t="s">
         <v>521</v>
-      </c>
-      <c r="M120" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -8399,7 +8399,7 @@
         <v>516</v>
       </c>
       <c r="F121" t="s">
-        <v>517</v>
+        <v>18</v>
       </c>
       <c r="H121" t="s">
         <v>524</v>
@@ -8408,13 +8408,13 @@
         <v>525</v>
       </c>
       <c r="K121" t="s">
+        <v>519</v>
+      </c>
+      <c r="L121" t="s">
         <v>520</v>
       </c>
-      <c r="L121" t="s">
+      <c r="M121" t="s">
         <v>521</v>
-      </c>
-      <c r="M121" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -8434,7 +8434,7 @@
         <v>516</v>
       </c>
       <c r="F122" t="s">
-        <v>517</v>
+        <v>18</v>
       </c>
       <c r="H122" t="s">
         <v>528</v>
@@ -8443,13 +8443,13 @@
         <v>529</v>
       </c>
       <c r="K122" t="s">
+        <v>519</v>
+      </c>
+      <c r="L122" t="s">
         <v>520</v>
       </c>
-      <c r="L122" t="s">
+      <c r="M122" t="s">
         <v>521</v>
-      </c>
-      <c r="M122" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -8469,7 +8469,7 @@
         <v>516</v>
       </c>
       <c r="F123" t="s">
-        <v>517</v>
+        <v>18</v>
       </c>
       <c r="H123" t="s">
         <v>532</v>
@@ -8478,13 +8478,13 @@
         <v>533</v>
       </c>
       <c r="K123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L123" t="s">
         <v>520</v>
       </c>
-      <c r="L123" t="s">
+      <c r="M123" t="s">
         <v>521</v>
-      </c>
-      <c r="M123" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -8504,7 +8504,7 @@
         <v>516</v>
       </c>
       <c r="F124" t="s">
-        <v>517</v>
+        <v>18</v>
       </c>
       <c r="H124" t="s">
         <v>536</v>
@@ -8513,13 +8513,13 @@
         <v>537</v>
       </c>
       <c r="K124" t="s">
+        <v>519</v>
+      </c>
+      <c r="L124" t="s">
         <v>520</v>
       </c>
-      <c r="L124" t="s">
+      <c r="M124" t="s">
         <v>521</v>
-      </c>
-      <c r="M124" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -8536,25 +8536,25 @@
         <v>16</v>
       </c>
       <c r="E125" t="s">
+        <v>516</v>
+      </c>
+      <c r="F125" t="s">
+        <v>18</v>
+      </c>
+      <c r="H125" t="s">
         <v>540</v>
       </c>
-      <c r="F125" t="s">
+      <c r="I125" t="s">
         <v>541</v>
       </c>
-      <c r="H125" t="s">
+      <c r="K125" t="s">
         <v>542</v>
       </c>
-      <c r="I125" t="s">
+      <c r="L125" t="s">
         <v>543</v>
       </c>
-      <c r="K125" t="s">
-        <v>520</v>
-      </c>
-      <c r="L125" t="s">
+      <c r="M125" t="s">
         <v>521</v>
-      </c>
-      <c r="M125" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -8571,10 +8571,10 @@
         <v>16</v>
       </c>
       <c r="E126" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F126" t="s">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="H126" t="s">
         <v>546</v>
@@ -8583,13 +8583,13 @@
         <v>547</v>
       </c>
       <c r="K126" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L126" t="s">
+        <v>543</v>
+      </c>
+      <c r="M126" t="s">
         <v>521</v>
-      </c>
-      <c r="M126" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -8606,10 +8606,10 @@
         <v>16</v>
       </c>
       <c r="E127" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F127" t="s">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="H127" t="s">
         <v>550</v>
@@ -8618,13 +8618,13 @@
         <v>551</v>
       </c>
       <c r="K127" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L127" t="s">
+        <v>543</v>
+      </c>
+      <c r="M127" t="s">
         <v>521</v>
-      </c>
-      <c r="M127" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -8641,10 +8641,10 @@
         <v>16</v>
       </c>
       <c r="E128" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F128" t="s">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="H128" t="s">
         <v>554</v>
@@ -8653,13 +8653,13 @@
         <v>555</v>
       </c>
       <c r="K128" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L128" t="s">
+        <v>543</v>
+      </c>
+      <c r="M128" t="s">
         <v>521</v>
-      </c>
-      <c r="M128" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -8676,10 +8676,10 @@
         <v>16</v>
       </c>
       <c r="E129" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F129" t="s">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="H129" t="s">
         <v>558</v>
@@ -8688,13 +8688,13 @@
         <v>559</v>
       </c>
       <c r="K129" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L129" t="s">
+        <v>543</v>
+      </c>
+      <c r="M129" t="s">
         <v>521</v>
-      </c>
-      <c r="M129" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -8711,10 +8711,10 @@
         <v>16</v>
       </c>
       <c r="E130" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F130" t="s">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="H130" t="s">
         <v>562</v>
@@ -8723,13 +8723,13 @@
         <v>563</v>
       </c>
       <c r="K130" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L130" t="s">
+        <v>543</v>
+      </c>
+      <c r="M130" t="s">
         <v>521</v>
-      </c>
-      <c r="M130" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -8746,10 +8746,10 @@
         <v>16</v>
       </c>
       <c r="E131" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="F131" t="s">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="H131" t="s">
         <v>566</v>
@@ -8758,13 +8758,13 @@
         <v>567</v>
       </c>
       <c r="K131" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="L131" t="s">
+        <v>543</v>
+      </c>
+      <c r="M131" t="s">
         <v>521</v>
-      </c>
-      <c r="M131" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -8781,25 +8781,25 @@
         <v>16</v>
       </c>
       <c r="E132" t="s">
+        <v>516</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="H132" t="s">
         <v>570</v>
       </c>
-      <c r="F132" t="s">
+      <c r="I132" t="s">
         <v>571</v>
       </c>
-      <c r="H132" t="s">
+      <c r="K132" t="s">
         <v>572</v>
       </c>
-      <c r="I132" t="s">
+      <c r="L132" t="s">
         <v>573</v>
       </c>
-      <c r="K132" t="s">
-        <v>520</v>
-      </c>
-      <c r="L132" t="s">
+      <c r="M132" t="s">
         <v>521</v>
-      </c>
-      <c r="M132" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -8816,10 +8816,10 @@
         <v>16</v>
       </c>
       <c r="E133" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F133" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H133" t="s">
         <v>576</v>
@@ -8828,13 +8828,13 @@
         <v>577</v>
       </c>
       <c r="K133" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L133" t="s">
+        <v>573</v>
+      </c>
+      <c r="M133" t="s">
         <v>521</v>
-      </c>
-      <c r="M133" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -8851,10 +8851,10 @@
         <v>16</v>
       </c>
       <c r="E134" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F134" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H134" t="s">
         <v>580</v>
@@ -8863,13 +8863,13 @@
         <v>581</v>
       </c>
       <c r="K134" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L134" t="s">
+        <v>573</v>
+      </c>
+      <c r="M134" t="s">
         <v>521</v>
-      </c>
-      <c r="M134" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -8886,10 +8886,10 @@
         <v>16</v>
       </c>
       <c r="E135" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F135" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H135" t="s">
         <v>584</v>
@@ -8898,13 +8898,13 @@
         <v>585</v>
       </c>
       <c r="K135" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L135" t="s">
+        <v>573</v>
+      </c>
+      <c r="M135" t="s">
         <v>521</v>
-      </c>
-      <c r="M135" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -8921,10 +8921,10 @@
         <v>16</v>
       </c>
       <c r="E136" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F136" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H136" t="s">
         <v>588</v>
@@ -8933,13 +8933,13 @@
         <v>589</v>
       </c>
       <c r="K136" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L136" t="s">
+        <v>573</v>
+      </c>
+      <c r="M136" t="s">
         <v>521</v>
-      </c>
-      <c r="M136" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -8956,10 +8956,10 @@
         <v>16</v>
       </c>
       <c r="E137" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F137" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H137" t="s">
         <v>592</v>
@@ -8968,13 +8968,13 @@
         <v>593</v>
       </c>
       <c r="K137" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L137" t="s">
+        <v>573</v>
+      </c>
+      <c r="M137" t="s">
         <v>521</v>
-      </c>
-      <c r="M137" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -8991,10 +8991,10 @@
         <v>16</v>
       </c>
       <c r="E138" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F138" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H138" t="s">
         <v>596</v>
@@ -9003,13 +9003,13 @@
         <v>597</v>
       </c>
       <c r="K138" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L138" t="s">
+        <v>573</v>
+      </c>
+      <c r="M138" t="s">
         <v>521</v>
-      </c>
-      <c r="M138" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -9026,10 +9026,10 @@
         <v>16</v>
       </c>
       <c r="E139" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F139" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H139" t="s">
         <v>600</v>
@@ -9038,13 +9038,13 @@
         <v>601</v>
       </c>
       <c r="K139" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L139" t="s">
+        <v>573</v>
+      </c>
+      <c r="M139" t="s">
         <v>521</v>
-      </c>
-      <c r="M139" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -9061,10 +9061,10 @@
         <v>16</v>
       </c>
       <c r="E140" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F140" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H140" t="s">
         <v>604</v>
@@ -9073,13 +9073,13 @@
         <v>605</v>
       </c>
       <c r="K140" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L140" t="s">
+        <v>573</v>
+      </c>
+      <c r="M140" t="s">
         <v>521</v>
-      </c>
-      <c r="M140" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -9096,10 +9096,10 @@
         <v>16</v>
       </c>
       <c r="E141" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F141" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H141" t="s">
         <v>608</v>
@@ -9108,13 +9108,13 @@
         <v>609</v>
       </c>
       <c r="K141" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L141" t="s">
+        <v>573</v>
+      </c>
+      <c r="M141" t="s">
         <v>521</v>
-      </c>
-      <c r="M141" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -9131,10 +9131,10 @@
         <v>16</v>
       </c>
       <c r="E142" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F142" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="H142" t="s">
         <v>612</v>
@@ -9143,13 +9143,13 @@
         <v>613</v>
       </c>
       <c r="K142" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="L142" t="s">
+        <v>573</v>
+      </c>
+      <c r="M142" t="s">
         <v>521</v>
-      </c>
-      <c r="M142" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -9166,25 +9166,25 @@
         <v>16</v>
       </c>
       <c r="E143" t="s">
+        <v>516</v>
+      </c>
+      <c r="F143" t="s">
+        <v>18</v>
+      </c>
+      <c r="H143" t="s">
         <v>616</v>
       </c>
-      <c r="F143" t="s">
+      <c r="I143" t="s">
         <v>617</v>
       </c>
-      <c r="H143" t="s">
+      <c r="K143" t="s">
         <v>618</v>
       </c>
-      <c r="I143" t="s">
+      <c r="L143" t="s">
         <v>619</v>
       </c>
-      <c r="K143" t="s">
-        <v>520</v>
-      </c>
-      <c r="L143" t="s">
+      <c r="M143" t="s">
         <v>521</v>
-      </c>
-      <c r="M143" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -9201,10 +9201,10 @@
         <v>16</v>
       </c>
       <c r="E144" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F144" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H144" t="s">
         <v>622</v>
@@ -9213,13 +9213,13 @@
         <v>623</v>
       </c>
       <c r="K144" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L144" t="s">
+        <v>619</v>
+      </c>
+      <c r="M144" t="s">
         <v>521</v>
-      </c>
-      <c r="M144" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -9236,10 +9236,10 @@
         <v>16</v>
       </c>
       <c r="E145" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F145" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H145" t="s">
         <v>626</v>
@@ -9248,13 +9248,13 @@
         <v>627</v>
       </c>
       <c r="K145" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L145" t="s">
+        <v>619</v>
+      </c>
+      <c r="M145" t="s">
         <v>521</v>
-      </c>
-      <c r="M145" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -9271,10 +9271,10 @@
         <v>16</v>
       </c>
       <c r="E146" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F146" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H146" t="s">
         <v>630</v>
@@ -9283,13 +9283,13 @@
         <v>631</v>
       </c>
       <c r="K146" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L146" t="s">
+        <v>619</v>
+      </c>
+      <c r="M146" t="s">
         <v>521</v>
-      </c>
-      <c r="M146" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -9306,10 +9306,10 @@
         <v>16</v>
       </c>
       <c r="E147" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F147" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H147" t="s">
         <v>634</v>
@@ -9318,13 +9318,13 @@
         <v>635</v>
       </c>
       <c r="K147" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L147" t="s">
+        <v>619</v>
+      </c>
+      <c r="M147" t="s">
         <v>521</v>
-      </c>
-      <c r="M147" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -9341,10 +9341,10 @@
         <v>16</v>
       </c>
       <c r="E148" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F148" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H148" t="s">
         <v>638</v>
@@ -9353,13 +9353,13 @@
         <v>639</v>
       </c>
       <c r="K148" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L148" t="s">
+        <v>619</v>
+      </c>
+      <c r="M148" t="s">
         <v>521</v>
-      </c>
-      <c r="M148" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -9376,10 +9376,10 @@
         <v>16</v>
       </c>
       <c r="E149" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F149" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H149" t="s">
         <v>642</v>
@@ -9388,13 +9388,13 @@
         <v>643</v>
       </c>
       <c r="K149" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L149" t="s">
+        <v>619</v>
+      </c>
+      <c r="M149" t="s">
         <v>521</v>
-      </c>
-      <c r="M149" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -9411,10 +9411,10 @@
         <v>16</v>
       </c>
       <c r="E150" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F150" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H150" t="s">
         <v>646</v>
@@ -9423,13 +9423,13 @@
         <v>647</v>
       </c>
       <c r="K150" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L150" t="s">
+        <v>619</v>
+      </c>
+      <c r="M150" t="s">
         <v>521</v>
-      </c>
-      <c r="M150" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -9446,10 +9446,10 @@
         <v>16</v>
       </c>
       <c r="E151" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="F151" t="s">
-        <v>617</v>
+        <v>18</v>
       </c>
       <c r="H151" t="s">
         <v>650</v>
@@ -9458,13 +9458,13 @@
         <v>651</v>
       </c>
       <c r="K151" t="s">
-        <v>520</v>
+        <v>618</v>
       </c>
       <c r="L151" t="s">
+        <v>619</v>
+      </c>
+      <c r="M151" t="s">
         <v>521</v>
-      </c>
-      <c r="M151" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -9481,25 +9481,25 @@
         <v>16</v>
       </c>
       <c r="E152" t="s">
+        <v>516</v>
+      </c>
+      <c r="F152" t="s">
+        <v>18</v>
+      </c>
+      <c r="H152" t="s">
         <v>654</v>
       </c>
-      <c r="F152" t="s">
+      <c r="I152" t="s">
         <v>655</v>
       </c>
-      <c r="H152" t="s">
+      <c r="K152" t="s">
         <v>656</v>
       </c>
-      <c r="I152" t="s">
+      <c r="L152" t="s">
         <v>657</v>
       </c>
-      <c r="K152" t="s">
-        <v>520</v>
-      </c>
-      <c r="L152" t="s">
+      <c r="M152" t="s">
         <v>521</v>
-      </c>
-      <c r="M152" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -9516,10 +9516,10 @@
         <v>16</v>
       </c>
       <c r="E153" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F153" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H153" t="s">
         <v>660</v>
@@ -9528,13 +9528,13 @@
         <v>661</v>
       </c>
       <c r="K153" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L153" t="s">
+        <v>657</v>
+      </c>
+      <c r="M153" t="s">
         <v>521</v>
-      </c>
-      <c r="M153" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -9551,10 +9551,10 @@
         <v>16</v>
       </c>
       <c r="E154" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F154" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H154" t="s">
         <v>664</v>
@@ -9563,13 +9563,13 @@
         <v>665</v>
       </c>
       <c r="K154" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L154" t="s">
+        <v>657</v>
+      </c>
+      <c r="M154" t="s">
         <v>521</v>
-      </c>
-      <c r="M154" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -9586,10 +9586,10 @@
         <v>16</v>
       </c>
       <c r="E155" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F155" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H155" t="s">
         <v>668</v>
@@ -9598,13 +9598,13 @@
         <v>669</v>
       </c>
       <c r="K155" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L155" t="s">
+        <v>657</v>
+      </c>
+      <c r="M155" t="s">
         <v>521</v>
-      </c>
-      <c r="M155" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -9621,10 +9621,10 @@
         <v>16</v>
       </c>
       <c r="E156" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F156" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H156" t="s">
         <v>672</v>
@@ -9633,13 +9633,13 @@
         <v>673</v>
       </c>
       <c r="K156" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L156" t="s">
+        <v>657</v>
+      </c>
+      <c r="M156" t="s">
         <v>521</v>
-      </c>
-      <c r="M156" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -9656,10 +9656,10 @@
         <v>16</v>
       </c>
       <c r="E157" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F157" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H157" t="s">
         <v>676</v>
@@ -9668,13 +9668,13 @@
         <v>677</v>
       </c>
       <c r="K157" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L157" t="s">
+        <v>657</v>
+      </c>
+      <c r="M157" t="s">
         <v>521</v>
-      </c>
-      <c r="M157" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -9691,10 +9691,10 @@
         <v>16</v>
       </c>
       <c r="E158" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F158" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H158" t="s">
         <v>680</v>
@@ -9703,13 +9703,13 @@
         <v>681</v>
       </c>
       <c r="K158" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L158" t="s">
+        <v>657</v>
+      </c>
+      <c r="M158" t="s">
         <v>521</v>
-      </c>
-      <c r="M158" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -9726,10 +9726,10 @@
         <v>16</v>
       </c>
       <c r="E159" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F159" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H159" t="s">
         <v>684</v>
@@ -9738,13 +9738,13 @@
         <v>685</v>
       </c>
       <c r="K159" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L159" t="s">
+        <v>657</v>
+      </c>
+      <c r="M159" t="s">
         <v>521</v>
-      </c>
-      <c r="M159" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -9761,10 +9761,10 @@
         <v>16</v>
       </c>
       <c r="E160" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F160" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H160" t="s">
         <v>688</v>
@@ -9773,13 +9773,13 @@
         <v>689</v>
       </c>
       <c r="K160" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L160" t="s">
+        <v>657</v>
+      </c>
+      <c r="M160" t="s">
         <v>521</v>
-      </c>
-      <c r="M160" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -9796,10 +9796,10 @@
         <v>16</v>
       </c>
       <c r="E161" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F161" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H161" t="s">
         <v>692</v>
@@ -9808,13 +9808,13 @@
         <v>693</v>
       </c>
       <c r="K161" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L161" t="s">
+        <v>657</v>
+      </c>
+      <c r="M161" t="s">
         <v>521</v>
-      </c>
-      <c r="M161" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -9831,10 +9831,10 @@
         <v>16</v>
       </c>
       <c r="E162" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F162" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H162" t="s">
         <v>696</v>
@@ -9843,13 +9843,13 @@
         <v>697</v>
       </c>
       <c r="K162" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L162" t="s">
+        <v>657</v>
+      </c>
+      <c r="M162" t="s">
         <v>521</v>
-      </c>
-      <c r="M162" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -9866,10 +9866,10 @@
         <v>16</v>
       </c>
       <c r="E163" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F163" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H163" t="s">
         <v>700</v>
@@ -9878,13 +9878,13 @@
         <v>701</v>
       </c>
       <c r="K163" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L163" t="s">
+        <v>657</v>
+      </c>
+      <c r="M163" t="s">
         <v>521</v>
-      </c>
-      <c r="M163" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -9901,10 +9901,10 @@
         <v>16</v>
       </c>
       <c r="E164" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F164" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H164" t="s">
         <v>704</v>
@@ -9913,13 +9913,13 @@
         <v>705</v>
       </c>
       <c r="K164" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L164" t="s">
+        <v>657</v>
+      </c>
+      <c r="M164" t="s">
         <v>521</v>
-      </c>
-      <c r="M164" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -9936,10 +9936,10 @@
         <v>16</v>
       </c>
       <c r="E165" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F165" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H165" t="s">
         <v>708</v>
@@ -9948,13 +9948,13 @@
         <v>709</v>
       </c>
       <c r="K165" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L165" t="s">
+        <v>657</v>
+      </c>
+      <c r="M165" t="s">
         <v>521</v>
-      </c>
-      <c r="M165" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -9971,10 +9971,10 @@
         <v>16</v>
       </c>
       <c r="E166" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F166" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H166" t="s">
         <v>712</v>
@@ -9983,13 +9983,13 @@
         <v>713</v>
       </c>
       <c r="K166" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L166" t="s">
+        <v>657</v>
+      </c>
+      <c r="M166" t="s">
         <v>521</v>
-      </c>
-      <c r="M166" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -10006,10 +10006,10 @@
         <v>16</v>
       </c>
       <c r="E167" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F167" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H167" t="s">
         <v>716</v>
@@ -10018,13 +10018,13 @@
         <v>717</v>
       </c>
       <c r="K167" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L167" t="s">
+        <v>657</v>
+      </c>
+      <c r="M167" t="s">
         <v>521</v>
-      </c>
-      <c r="M167" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -10041,10 +10041,10 @@
         <v>16</v>
       </c>
       <c r="E168" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F168" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H168" t="s">
         <v>720</v>
@@ -10053,13 +10053,13 @@
         <v>721</v>
       </c>
       <c r="K168" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L168" t="s">
+        <v>657</v>
+      </c>
+      <c r="M168" t="s">
         <v>521</v>
-      </c>
-      <c r="M168" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -10076,10 +10076,10 @@
         <v>16</v>
       </c>
       <c r="E169" t="s">
-        <v>654</v>
+        <v>516</v>
       </c>
       <c r="F169" t="s">
-        <v>655</v>
+        <v>18</v>
       </c>
       <c r="H169" t="s">
         <v>724</v>
@@ -10088,13 +10088,13 @@
         <v>725</v>
       </c>
       <c r="K169" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="L169" t="s">
+        <v>657</v>
+      </c>
+      <c r="M169" t="s">
         <v>521</v>
-      </c>
-      <c r="M169" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -10114,22 +10114,22 @@
         <v>728</v>
       </c>
       <c r="F170" t="s">
+        <v>18</v>
+      </c>
+      <c r="H170" t="s">
         <v>729</v>
       </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
         <v>730</v>
       </c>
-      <c r="I170" t="s">
+      <c r="K170" t="s">
         <v>731</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" t="s">
         <v>732</v>
       </c>
-      <c r="L170" t="s">
+      <c r="M170" t="s">
         <v>733</v>
-      </c>
-      <c r="M170" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -10149,7 +10149,7 @@
         <v>728</v>
       </c>
       <c r="F171" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H171" t="s">
         <v>736</v>
@@ -10158,13 +10158,13 @@
         <v>737</v>
       </c>
       <c r="K171" t="s">
+        <v>731</v>
+      </c>
+      <c r="L171" t="s">
         <v>732</v>
       </c>
-      <c r="L171" t="s">
+      <c r="M171" t="s">
         <v>733</v>
-      </c>
-      <c r="M171" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:13">
@@ -10184,7 +10184,7 @@
         <v>728</v>
       </c>
       <c r="F172" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H172" t="s">
         <v>740</v>
@@ -10193,13 +10193,13 @@
         <v>741</v>
       </c>
       <c r="K172" t="s">
+        <v>731</v>
+      </c>
+      <c r="L172" t="s">
         <v>732</v>
       </c>
-      <c r="L172" t="s">
+      <c r="M172" t="s">
         <v>733</v>
-      </c>
-      <c r="M172" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -10219,7 +10219,7 @@
         <v>728</v>
       </c>
       <c r="F173" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H173" t="s">
         <v>744</v>
@@ -10228,13 +10228,13 @@
         <v>745</v>
       </c>
       <c r="K173" t="s">
+        <v>731</v>
+      </c>
+      <c r="L173" t="s">
         <v>732</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M173" t="s">
         <v>733</v>
-      </c>
-      <c r="M173" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -10254,7 +10254,7 @@
         <v>728</v>
       </c>
       <c r="F174" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H174" t="s">
         <v>748</v>
@@ -10263,13 +10263,13 @@
         <v>749</v>
       </c>
       <c r="K174" t="s">
+        <v>731</v>
+      </c>
+      <c r="L174" t="s">
         <v>732</v>
       </c>
-      <c r="L174" t="s">
+      <c r="M174" t="s">
         <v>733</v>
-      </c>
-      <c r="M174" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -10289,7 +10289,7 @@
         <v>728</v>
       </c>
       <c r="F175" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H175" t="s">
         <v>752</v>
@@ -10298,13 +10298,13 @@
         <v>753</v>
       </c>
       <c r="K175" t="s">
+        <v>731</v>
+      </c>
+      <c r="L175" t="s">
         <v>732</v>
       </c>
-      <c r="L175" t="s">
+      <c r="M175" t="s">
         <v>733</v>
-      </c>
-      <c r="M175" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -10324,7 +10324,7 @@
         <v>728</v>
       </c>
       <c r="F176" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H176" t="s">
         <v>756</v>
@@ -10333,13 +10333,13 @@
         <v>757</v>
       </c>
       <c r="K176" t="s">
+        <v>731</v>
+      </c>
+      <c r="L176" t="s">
         <v>732</v>
       </c>
-      <c r="L176" t="s">
+      <c r="M176" t="s">
         <v>733</v>
-      </c>
-      <c r="M176" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -10359,7 +10359,7 @@
         <v>728</v>
       </c>
       <c r="F177" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H177" t="s">
         <v>760</v>
@@ -10368,13 +10368,13 @@
         <v>761</v>
       </c>
       <c r="K177" t="s">
+        <v>731</v>
+      </c>
+      <c r="L177" t="s">
         <v>732</v>
       </c>
-      <c r="L177" t="s">
+      <c r="M177" t="s">
         <v>733</v>
-      </c>
-      <c r="M177" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>728</v>
       </c>
       <c r="F178" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H178" t="s">
         <v>764</v>
@@ -10403,13 +10403,13 @@
         <v>765</v>
       </c>
       <c r="K178" t="s">
+        <v>731</v>
+      </c>
+      <c r="L178" t="s">
         <v>732</v>
       </c>
-      <c r="L178" t="s">
+      <c r="M178" t="s">
         <v>733</v>
-      </c>
-      <c r="M178" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -10429,7 +10429,7 @@
         <v>728</v>
       </c>
       <c r="F179" t="s">
-        <v>729</v>
+        <v>18</v>
       </c>
       <c r="H179" t="s">
         <v>768</v>
@@ -10438,13 +10438,13 @@
         <v>769</v>
       </c>
       <c r="K179" t="s">
+        <v>731</v>
+      </c>
+      <c r="L179" t="s">
         <v>732</v>
       </c>
-      <c r="L179" t="s">
+      <c r="M179" t="s">
         <v>733</v>
-      </c>
-      <c r="M179" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -10461,25 +10461,25 @@
         <v>16</v>
       </c>
       <c r="E180" t="s">
+        <v>728</v>
+      </c>
+      <c r="F180" t="s">
+        <v>18</v>
+      </c>
+      <c r="H180" t="s">
         <v>772</v>
       </c>
-      <c r="F180" t="s">
+      <c r="I180" t="s">
         <v>773</v>
       </c>
-      <c r="H180" t="s">
+      <c r="K180" t="s">
         <v>774</v>
       </c>
-      <c r="I180" t="s">
+      <c r="L180" t="s">
         <v>775</v>
       </c>
-      <c r="K180" t="s">
-        <v>732</v>
-      </c>
-      <c r="L180" t="s">
+      <c r="M180" t="s">
         <v>733</v>
-      </c>
-      <c r="M180" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -10496,10 +10496,10 @@
         <v>16</v>
       </c>
       <c r="E181" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F181" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="G181" t="s">
         <v>778</v>
@@ -10514,13 +10514,13 @@
         <v>781</v>
       </c>
       <c r="K181" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L181" t="s">
+        <v>775</v>
+      </c>
+      <c r="M181" t="s">
         <v>733</v>
-      </c>
-      <c r="M181" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -10537,10 +10537,10 @@
         <v>16</v>
       </c>
       <c r="E182" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F182" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="G182" t="s">
         <v>778</v>
@@ -10555,13 +10555,13 @@
         <v>781</v>
       </c>
       <c r="K182" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L182" t="s">
+        <v>775</v>
+      </c>
+      <c r="M182" t="s">
         <v>733</v>
-      </c>
-      <c r="M182" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -10578,10 +10578,10 @@
         <v>16</v>
       </c>
       <c r="E183" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F183" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="G183" t="s">
         <v>778</v>
@@ -10590,13 +10590,13 @@
         <v>781</v>
       </c>
       <c r="K183" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L183" t="s">
+        <v>775</v>
+      </c>
+      <c r="M183" t="s">
         <v>733</v>
-      </c>
-      <c r="M183" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -10613,10 +10613,10 @@
         <v>16</v>
       </c>
       <c r="E184" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F184" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H184" t="s">
         <v>790</v>
@@ -10625,13 +10625,13 @@
         <v>791</v>
       </c>
       <c r="K184" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L184" t="s">
+        <v>775</v>
+      </c>
+      <c r="M184" t="s">
         <v>733</v>
-      </c>
-      <c r="M184" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -10648,10 +10648,10 @@
         <v>16</v>
       </c>
       <c r="E185" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F185" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H185" t="s">
         <v>794</v>
@@ -10660,13 +10660,13 @@
         <v>795</v>
       </c>
       <c r="K185" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L185" t="s">
+        <v>775</v>
+      </c>
+      <c r="M185" t="s">
         <v>733</v>
-      </c>
-      <c r="M185" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -10683,10 +10683,10 @@
         <v>16</v>
       </c>
       <c r="E186" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F186" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H186" t="s">
         <v>798</v>
@@ -10695,13 +10695,13 @@
         <v>799</v>
       </c>
       <c r="K186" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L186" t="s">
+        <v>775</v>
+      </c>
+      <c r="M186" t="s">
         <v>733</v>
-      </c>
-      <c r="M186" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -10718,10 +10718,10 @@
         <v>16</v>
       </c>
       <c r="E187" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F187" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H187" t="s">
         <v>802</v>
@@ -10730,13 +10730,13 @@
         <v>803</v>
       </c>
       <c r="K187" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L187" t="s">
+        <v>775</v>
+      </c>
+      <c r="M187" t="s">
         <v>733</v>
-      </c>
-      <c r="M187" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -10753,10 +10753,10 @@
         <v>16</v>
       </c>
       <c r="E188" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F188" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H188" t="s">
         <v>806</v>
@@ -10765,13 +10765,13 @@
         <v>807</v>
       </c>
       <c r="K188" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L188" t="s">
+        <v>775</v>
+      </c>
+      <c r="M188" t="s">
         <v>733</v>
-      </c>
-      <c r="M188" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -10788,10 +10788,10 @@
         <v>16</v>
       </c>
       <c r="E189" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F189" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H189" t="s">
         <v>810</v>
@@ -10800,13 +10800,13 @@
         <v>811</v>
       </c>
       <c r="K189" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L189" t="s">
+        <v>775</v>
+      </c>
+      <c r="M189" t="s">
         <v>733</v>
-      </c>
-      <c r="M189" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -10823,10 +10823,10 @@
         <v>16</v>
       </c>
       <c r="E190" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F190" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H190" t="s">
         <v>814</v>
@@ -10835,13 +10835,13 @@
         <v>815</v>
       </c>
       <c r="K190" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L190" t="s">
+        <v>775</v>
+      </c>
+      <c r="M190" t="s">
         <v>733</v>
-      </c>
-      <c r="M190" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -10858,10 +10858,10 @@
         <v>16</v>
       </c>
       <c r="E191" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F191" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H191" t="s">
         <v>818</v>
@@ -10870,13 +10870,13 @@
         <v>819</v>
       </c>
       <c r="K191" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L191" t="s">
+        <v>775</v>
+      </c>
+      <c r="M191" t="s">
         <v>733</v>
-      </c>
-      <c r="M191" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -10893,10 +10893,10 @@
         <v>16</v>
       </c>
       <c r="E192" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F192" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H192" t="s">
         <v>822</v>
@@ -10905,13 +10905,13 @@
         <v>823</v>
       </c>
       <c r="K192" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L192" t="s">
+        <v>775</v>
+      </c>
+      <c r="M192" t="s">
         <v>733</v>
-      </c>
-      <c r="M192" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -10928,10 +10928,10 @@
         <v>16</v>
       </c>
       <c r="E193" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F193" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H193" t="s">
         <v>826</v>
@@ -10940,13 +10940,13 @@
         <v>827</v>
       </c>
       <c r="K193" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L193" t="s">
+        <v>775</v>
+      </c>
+      <c r="M193" t="s">
         <v>733</v>
-      </c>
-      <c r="M193" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -10963,10 +10963,10 @@
         <v>16</v>
       </c>
       <c r="E194" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F194" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H194" t="s">
         <v>830</v>
@@ -10975,13 +10975,13 @@
         <v>831</v>
       </c>
       <c r="K194" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L194" t="s">
+        <v>775</v>
+      </c>
+      <c r="M194" t="s">
         <v>733</v>
-      </c>
-      <c r="M194" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -10998,10 +10998,10 @@
         <v>16</v>
       </c>
       <c r="E195" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F195" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H195" t="s">
         <v>834</v>
@@ -11010,13 +11010,13 @@
         <v>835</v>
       </c>
       <c r="K195" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L195" t="s">
+        <v>775</v>
+      </c>
+      <c r="M195" t="s">
         <v>733</v>
-      </c>
-      <c r="M195" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -11033,10 +11033,10 @@
         <v>16</v>
       </c>
       <c r="E196" t="s">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="F196" t="s">
-        <v>773</v>
+        <v>18</v>
       </c>
       <c r="H196" t="s">
         <v>838</v>
@@ -11045,13 +11045,13 @@
         <v>839</v>
       </c>
       <c r="K196" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="L196" t="s">
+        <v>775</v>
+      </c>
+      <c r="M196" t="s">
         <v>733</v>
-      </c>
-      <c r="M196" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -11068,25 +11068,25 @@
         <v>16</v>
       </c>
       <c r="E197" t="s">
+        <v>728</v>
+      </c>
+      <c r="F197" t="s">
+        <v>18</v>
+      </c>
+      <c r="H197" t="s">
         <v>842</v>
       </c>
-      <c r="F197" t="s">
+      <c r="I197" t="s">
         <v>843</v>
       </c>
-      <c r="H197" t="s">
+      <c r="K197" t="s">
         <v>844</v>
       </c>
-      <c r="I197" t="s">
+      <c r="L197" t="s">
         <v>845</v>
       </c>
-      <c r="K197" t="s">
-        <v>732</v>
-      </c>
-      <c r="L197" t="s">
+      <c r="M197" t="s">
         <v>733</v>
-      </c>
-      <c r="M197" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -11103,10 +11103,10 @@
         <v>16</v>
       </c>
       <c r="E198" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F198" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H198" t="s">
         <v>848</v>
@@ -11115,13 +11115,13 @@
         <v>849</v>
       </c>
       <c r="K198" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L198" t="s">
+        <v>845</v>
+      </c>
+      <c r="M198" t="s">
         <v>733</v>
-      </c>
-      <c r="M198" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -11138,10 +11138,10 @@
         <v>16</v>
       </c>
       <c r="E199" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F199" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H199" t="s">
         <v>852</v>
@@ -11150,13 +11150,13 @@
         <v>853</v>
       </c>
       <c r="K199" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L199" t="s">
+        <v>845</v>
+      </c>
+      <c r="M199" t="s">
         <v>733</v>
-      </c>
-      <c r="M199" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -11173,10 +11173,10 @@
         <v>16</v>
       </c>
       <c r="E200" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F200" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H200" t="s">
         <v>856</v>
@@ -11185,13 +11185,13 @@
         <v>857</v>
       </c>
       <c r="K200" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L200" t="s">
+        <v>845</v>
+      </c>
+      <c r="M200" t="s">
         <v>733</v>
-      </c>
-      <c r="M200" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -11208,10 +11208,10 @@
         <v>16</v>
       </c>
       <c r="E201" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F201" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H201" t="s">
         <v>860</v>
@@ -11220,13 +11220,13 @@
         <v>861</v>
       </c>
       <c r="K201" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L201" t="s">
+        <v>845</v>
+      </c>
+      <c r="M201" t="s">
         <v>733</v>
-      </c>
-      <c r="M201" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -11243,10 +11243,10 @@
         <v>16</v>
       </c>
       <c r="E202" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F202" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H202" t="s">
         <v>864</v>
@@ -11255,13 +11255,13 @@
         <v>865</v>
       </c>
       <c r="K202" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L202" t="s">
+        <v>845</v>
+      </c>
+      <c r="M202" t="s">
         <v>733</v>
-      </c>
-      <c r="M202" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -11278,10 +11278,10 @@
         <v>16</v>
       </c>
       <c r="E203" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F203" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H203" t="s">
         <v>868</v>
@@ -11290,13 +11290,13 @@
         <v>869</v>
       </c>
       <c r="K203" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L203" t="s">
+        <v>845</v>
+      </c>
+      <c r="M203" t="s">
         <v>733</v>
-      </c>
-      <c r="M203" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -11313,10 +11313,10 @@
         <v>16</v>
       </c>
       <c r="E204" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F204" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H204" t="s">
         <v>872</v>
@@ -11325,13 +11325,13 @@
         <v>873</v>
       </c>
       <c r="K204" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L204" t="s">
+        <v>845</v>
+      </c>
+      <c r="M204" t="s">
         <v>733</v>
-      </c>
-      <c r="M204" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -11348,10 +11348,10 @@
         <v>16</v>
       </c>
       <c r="E205" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F205" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H205" t="s">
         <v>876</v>
@@ -11360,13 +11360,13 @@
         <v>877</v>
       </c>
       <c r="K205" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L205" t="s">
+        <v>845</v>
+      </c>
+      <c r="M205" t="s">
         <v>733</v>
-      </c>
-      <c r="M205" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -11383,10 +11383,10 @@
         <v>16</v>
       </c>
       <c r="E206" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F206" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H206" t="s">
         <v>880</v>
@@ -11395,13 +11395,13 @@
         <v>881</v>
       </c>
       <c r="K206" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L206" t="s">
+        <v>845</v>
+      </c>
+      <c r="M206" t="s">
         <v>733</v>
-      </c>
-      <c r="M206" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -11418,10 +11418,10 @@
         <v>16</v>
       </c>
       <c r="E207" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F207" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H207" t="s">
         <v>884</v>
@@ -11430,13 +11430,13 @@
         <v>885</v>
       </c>
       <c r="K207" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L207" t="s">
+        <v>845</v>
+      </c>
+      <c r="M207" t="s">
         <v>733</v>
-      </c>
-      <c r="M207" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -11453,10 +11453,10 @@
         <v>16</v>
       </c>
       <c r="E208" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F208" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H208" t="s">
         <v>888</v>
@@ -11465,13 +11465,13 @@
         <v>889</v>
       </c>
       <c r="K208" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L208" t="s">
+        <v>845</v>
+      </c>
+      <c r="M208" t="s">
         <v>733</v>
-      </c>
-      <c r="M208" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -11488,10 +11488,10 @@
         <v>16</v>
       </c>
       <c r="E209" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F209" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H209" t="s">
         <v>892</v>
@@ -11500,13 +11500,13 @@
         <v>893</v>
       </c>
       <c r="K209" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L209" t="s">
+        <v>845</v>
+      </c>
+      <c r="M209" t="s">
         <v>733</v>
-      </c>
-      <c r="M209" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -11523,10 +11523,10 @@
         <v>16</v>
       </c>
       <c r="E210" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F210" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H210" t="s">
         <v>896</v>
@@ -11535,13 +11535,13 @@
         <v>897</v>
       </c>
       <c r="K210" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L210" t="s">
+        <v>845</v>
+      </c>
+      <c r="M210" t="s">
         <v>733</v>
-      </c>
-      <c r="M210" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -11558,10 +11558,10 @@
         <v>16</v>
       </c>
       <c r="E211" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F211" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H211" t="s">
         <v>900</v>
@@ -11570,13 +11570,13 @@
         <v>901</v>
       </c>
       <c r="K211" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L211" t="s">
+        <v>845</v>
+      </c>
+      <c r="M211" t="s">
         <v>733</v>
-      </c>
-      <c r="M211" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -11593,10 +11593,10 @@
         <v>16</v>
       </c>
       <c r="E212" t="s">
-        <v>842</v>
+        <v>728</v>
       </c>
       <c r="F212" t="s">
-        <v>843</v>
+        <v>18</v>
       </c>
       <c r="H212" t="s">
         <v>904</v>
@@ -11605,13 +11605,13 @@
         <v>905</v>
       </c>
       <c r="K212" t="s">
-        <v>732</v>
+        <v>844</v>
       </c>
       <c r="L212" t="s">
+        <v>845</v>
+      </c>
+      <c r="M212" t="s">
         <v>733</v>
-      </c>
-      <c r="M212" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -11628,25 +11628,25 @@
         <v>16</v>
       </c>
       <c r="E213" t="s">
+        <v>728</v>
+      </c>
+      <c r="F213" t="s">
+        <v>18</v>
+      </c>
+      <c r="H213" t="s">
         <v>908</v>
       </c>
-      <c r="F213" t="s">
+      <c r="I213" t="s">
         <v>909</v>
       </c>
-      <c r="H213" t="s">
+      <c r="K213" t="s">
         <v>910</v>
       </c>
-      <c r="I213" t="s">
+      <c r="L213" t="s">
         <v>911</v>
       </c>
-      <c r="K213" t="s">
-        <v>732</v>
-      </c>
-      <c r="L213" t="s">
+      <c r="M213" t="s">
         <v>733</v>
-      </c>
-      <c r="M213" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -11663,10 +11663,10 @@
         <v>16</v>
       </c>
       <c r="E214" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F214" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H214" t="s">
         <v>914</v>
@@ -11675,13 +11675,13 @@
         <v>915</v>
       </c>
       <c r="K214" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L214" t="s">
+        <v>911</v>
+      </c>
+      <c r="M214" t="s">
         <v>733</v>
-      </c>
-      <c r="M214" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -11698,10 +11698,10 @@
         <v>16</v>
       </c>
       <c r="E215" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F215" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H215" t="s">
         <v>918</v>
@@ -11710,13 +11710,13 @@
         <v>919</v>
       </c>
       <c r="K215" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L215" t="s">
+        <v>911</v>
+      </c>
+      <c r="M215" t="s">
         <v>733</v>
-      </c>
-      <c r="M215" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -11733,10 +11733,10 @@
         <v>16</v>
       </c>
       <c r="E216" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F216" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H216" t="s">
         <v>922</v>
@@ -11745,13 +11745,13 @@
         <v>923</v>
       </c>
       <c r="K216" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L216" t="s">
+        <v>911</v>
+      </c>
+      <c r="M216" t="s">
         <v>733</v>
-      </c>
-      <c r="M216" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -11768,10 +11768,10 @@
         <v>16</v>
       </c>
       <c r="E217" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F217" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H217" t="s">
         <v>926</v>
@@ -11780,13 +11780,13 @@
         <v>927</v>
       </c>
       <c r="K217" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L217" t="s">
+        <v>911</v>
+      </c>
+      <c r="M217" t="s">
         <v>733</v>
-      </c>
-      <c r="M217" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -11803,10 +11803,10 @@
         <v>16</v>
       </c>
       <c r="E218" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F218" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H218" t="s">
         <v>930</v>
@@ -11815,13 +11815,13 @@
         <v>931</v>
       </c>
       <c r="K218" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L218" t="s">
+        <v>911</v>
+      </c>
+      <c r="M218" t="s">
         <v>733</v>
-      </c>
-      <c r="M218" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -11838,10 +11838,10 @@
         <v>16</v>
       </c>
       <c r="E219" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F219" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H219" t="s">
         <v>934</v>
@@ -11850,13 +11850,13 @@
         <v>935</v>
       </c>
       <c r="K219" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L219" t="s">
+        <v>911</v>
+      </c>
+      <c r="M219" t="s">
         <v>733</v>
-      </c>
-      <c r="M219" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -11873,10 +11873,10 @@
         <v>16</v>
       </c>
       <c r="E220" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F220" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H220" t="s">
         <v>938</v>
@@ -11885,13 +11885,13 @@
         <v>939</v>
       </c>
       <c r="K220" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L220" t="s">
+        <v>911</v>
+      </c>
+      <c r="M220" t="s">
         <v>733</v>
-      </c>
-      <c r="M220" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -11908,10 +11908,10 @@
         <v>16</v>
       </c>
       <c r="E221" t="s">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="F221" t="s">
-        <v>909</v>
+        <v>18</v>
       </c>
       <c r="H221" t="s">
         <v>942</v>
@@ -11920,13 +11920,13 @@
         <v>943</v>
       </c>
       <c r="K221" t="s">
-        <v>732</v>
+        <v>910</v>
       </c>
       <c r="L221" t="s">
+        <v>911</v>
+      </c>
+      <c r="M221" t="s">
         <v>733</v>
-      </c>
-      <c r="M221" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -11946,22 +11946,22 @@
         <v>946</v>
       </c>
       <c r="F222" t="s">
+        <v>18</v>
+      </c>
+      <c r="H222" t="s">
         <v>947</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>948</v>
       </c>
-      <c r="I222" t="s">
+      <c r="K222" t="s">
         <v>949</v>
       </c>
-      <c r="K222" t="s">
+      <c r="L222" t="s">
         <v>950</v>
       </c>
-      <c r="L222" t="s">
+      <c r="M222" t="s">
         <v>951</v>
-      </c>
-      <c r="M222" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -11981,7 +11981,7 @@
         <v>946</v>
       </c>
       <c r="F223" t="s">
-        <v>947</v>
+        <v>18</v>
       </c>
       <c r="H223" t="s">
         <v>954</v>
@@ -11990,13 +11990,13 @@
         <v>955</v>
       </c>
       <c r="K223" t="s">
+        <v>949</v>
+      </c>
+      <c r="L223" t="s">
         <v>950</v>
       </c>
-      <c r="L223" t="s">
+      <c r="M223" t="s">
         <v>951</v>
-      </c>
-      <c r="M223" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -12016,7 +12016,7 @@
         <v>946</v>
       </c>
       <c r="F224" t="s">
-        <v>947</v>
+        <v>18</v>
       </c>
       <c r="H224" t="s">
         <v>958</v>
@@ -12025,13 +12025,13 @@
         <v>959</v>
       </c>
       <c r="K224" t="s">
+        <v>949</v>
+      </c>
+      <c r="L224" t="s">
         <v>950</v>
       </c>
-      <c r="L224" t="s">
+      <c r="M224" t="s">
         <v>951</v>
-      </c>
-      <c r="M224" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -12051,7 +12051,7 @@
         <v>946</v>
       </c>
       <c r="F225" t="s">
-        <v>947</v>
+        <v>18</v>
       </c>
       <c r="H225" t="s">
         <v>962</v>
@@ -12060,13 +12060,13 @@
         <v>963</v>
       </c>
       <c r="K225" t="s">
+        <v>949</v>
+      </c>
+      <c r="L225" t="s">
         <v>950</v>
       </c>
-      <c r="L225" t="s">
+      <c r="M225" t="s">
         <v>951</v>
-      </c>
-      <c r="M225" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -12086,7 +12086,7 @@
         <v>946</v>
       </c>
       <c r="F226" t="s">
-        <v>947</v>
+        <v>18</v>
       </c>
       <c r="H226" t="s">
         <v>966</v>
@@ -12095,13 +12095,13 @@
         <v>967</v>
       </c>
       <c r="K226" t="s">
+        <v>949</v>
+      </c>
+      <c r="L226" t="s">
         <v>950</v>
       </c>
-      <c r="L226" t="s">
+      <c r="M226" t="s">
         <v>951</v>
-      </c>
-      <c r="M226" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -12121,7 +12121,7 @@
         <v>946</v>
       </c>
       <c r="F227" t="s">
-        <v>947</v>
+        <v>18</v>
       </c>
       <c r="H227" t="s">
         <v>970</v>
@@ -12130,13 +12130,13 @@
         <v>971</v>
       </c>
       <c r="K227" t="s">
+        <v>949</v>
+      </c>
+      <c r="L227" t="s">
         <v>950</v>
       </c>
-      <c r="L227" t="s">
+      <c r="M227" t="s">
         <v>951</v>
-      </c>
-      <c r="M227" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -12153,25 +12153,25 @@
         <v>16</v>
       </c>
       <c r="E228" t="s">
+        <v>946</v>
+      </c>
+      <c r="F228" t="s">
+        <v>18</v>
+      </c>
+      <c r="H228" t="s">
         <v>974</v>
       </c>
-      <c r="F228" t="s">
+      <c r="I228" t="s">
         <v>975</v>
       </c>
-      <c r="H228" t="s">
+      <c r="K228" t="s">
         <v>976</v>
       </c>
-      <c r="I228" t="s">
+      <c r="L228" t="s">
         <v>977</v>
       </c>
-      <c r="K228" t="s">
-        <v>950</v>
-      </c>
-      <c r="L228" t="s">
+      <c r="M228" t="s">
         <v>951</v>
-      </c>
-      <c r="M228" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -12188,10 +12188,10 @@
         <v>16</v>
       </c>
       <c r="E229" t="s">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="F229" t="s">
-        <v>975</v>
+        <v>18</v>
       </c>
       <c r="H229" t="s">
         <v>980</v>
@@ -12200,13 +12200,13 @@
         <v>981</v>
       </c>
       <c r="K229" t="s">
-        <v>950</v>
+        <v>976</v>
       </c>
       <c r="L229" t="s">
+        <v>977</v>
+      </c>
+      <c r="M229" t="s">
         <v>951</v>
-      </c>
-      <c r="M229" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -12223,10 +12223,10 @@
         <v>16</v>
       </c>
       <c r="E230" t="s">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="F230" t="s">
-        <v>975</v>
+        <v>18</v>
       </c>
       <c r="H230" t="s">
         <v>984</v>
@@ -12235,13 +12235,13 @@
         <v>985</v>
       </c>
       <c r="K230" t="s">
-        <v>950</v>
+        <v>976</v>
       </c>
       <c r="L230" t="s">
+        <v>977</v>
+      </c>
+      <c r="M230" t="s">
         <v>951</v>
-      </c>
-      <c r="M230" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -12258,10 +12258,10 @@
         <v>16</v>
       </c>
       <c r="E231" t="s">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="F231" t="s">
-        <v>975</v>
+        <v>18</v>
       </c>
       <c r="H231" t="s">
         <v>988</v>
@@ -12270,13 +12270,13 @@
         <v>989</v>
       </c>
       <c r="K231" t="s">
-        <v>950</v>
+        <v>976</v>
       </c>
       <c r="L231" t="s">
+        <v>977</v>
+      </c>
+      <c r="M231" t="s">
         <v>951</v>
-      </c>
-      <c r="M231" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -12293,10 +12293,10 @@
         <v>16</v>
       </c>
       <c r="E232" t="s">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="F232" t="s">
-        <v>975</v>
+        <v>18</v>
       </c>
       <c r="H232" t="s">
         <v>992</v>
@@ -12305,13 +12305,13 @@
         <v>993</v>
       </c>
       <c r="K232" t="s">
-        <v>950</v>
+        <v>976</v>
       </c>
       <c r="L232" t="s">
+        <v>977</v>
+      </c>
+      <c r="M232" t="s">
         <v>951</v>
-      </c>
-      <c r="M232" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -12328,25 +12328,25 @@
         <v>16</v>
       </c>
       <c r="E233" t="s">
+        <v>946</v>
+      </c>
+      <c r="F233" t="s">
+        <v>18</v>
+      </c>
+      <c r="H233" t="s">
         <v>996</v>
       </c>
-      <c r="F233" t="s">
+      <c r="I233" t="s">
         <v>997</v>
       </c>
-      <c r="H233" t="s">
+      <c r="K233" t="s">
         <v>998</v>
       </c>
-      <c r="I233" t="s">
+      <c r="L233" t="s">
         <v>999</v>
       </c>
-      <c r="K233" t="s">
-        <v>950</v>
-      </c>
-      <c r="L233" t="s">
+      <c r="M233" t="s">
         <v>951</v>
-      </c>
-      <c r="M233" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -12363,10 +12363,10 @@
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F234" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H234" t="s">
         <v>1002</v>
@@ -12375,13 +12375,13 @@
         <v>1003</v>
       </c>
       <c r="K234" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L234" t="s">
+        <v>999</v>
+      </c>
+      <c r="M234" t="s">
         <v>951</v>
-      </c>
-      <c r="M234" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -12398,10 +12398,10 @@
         <v>16</v>
       </c>
       <c r="E235" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F235" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H235" t="s">
         <v>1006</v>
@@ -12410,13 +12410,13 @@
         <v>1007</v>
       </c>
       <c r="K235" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L235" t="s">
+        <v>999</v>
+      </c>
+      <c r="M235" t="s">
         <v>951</v>
-      </c>
-      <c r="M235" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -12433,10 +12433,10 @@
         <v>16</v>
       </c>
       <c r="E236" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F236" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H236" t="s">
         <v>1010</v>
@@ -12445,13 +12445,13 @@
         <v>1011</v>
       </c>
       <c r="K236" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L236" t="s">
+        <v>999</v>
+      </c>
+      <c r="M236" t="s">
         <v>951</v>
-      </c>
-      <c r="M236" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -12468,10 +12468,10 @@
         <v>16</v>
       </c>
       <c r="E237" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F237" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H237" t="s">
         <v>1014</v>
@@ -12480,13 +12480,13 @@
         <v>1015</v>
       </c>
       <c r="K237" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L237" t="s">
+        <v>999</v>
+      </c>
+      <c r="M237" t="s">
         <v>951</v>
-      </c>
-      <c r="M237" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -12503,10 +12503,10 @@
         <v>16</v>
       </c>
       <c r="E238" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F238" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H238" t="s">
         <v>1018</v>
@@ -12515,13 +12515,13 @@
         <v>1019</v>
       </c>
       <c r="K238" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L238" t="s">
+        <v>999</v>
+      </c>
+      <c r="M238" t="s">
         <v>951</v>
-      </c>
-      <c r="M238" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -12538,10 +12538,10 @@
         <v>16</v>
       </c>
       <c r="E239" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F239" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H239" t="s">
         <v>1022</v>
@@ -12550,13 +12550,13 @@
         <v>1023</v>
       </c>
       <c r="K239" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L239" t="s">
+        <v>999</v>
+      </c>
+      <c r="M239" t="s">
         <v>951</v>
-      </c>
-      <c r="M239" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -12573,10 +12573,10 @@
         <v>16</v>
       </c>
       <c r="E240" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="F240" t="s">
-        <v>997</v>
+        <v>18</v>
       </c>
       <c r="H240" t="s">
         <v>1026</v>
@@ -12585,13 +12585,13 @@
         <v>1027</v>
       </c>
       <c r="K240" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="L240" t="s">
+        <v>999</v>
+      </c>
+      <c r="M240" t="s">
         <v>951</v>
-      </c>
-      <c r="M240" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -12608,25 +12608,25 @@
         <v>16</v>
       </c>
       <c r="E241" t="s">
+        <v>946</v>
+      </c>
+      <c r="F241" t="s">
+        <v>18</v>
+      </c>
+      <c r="H241" t="s">
         <v>1030</v>
       </c>
-      <c r="F241" t="s">
+      <c r="I241" t="s">
         <v>1031</v>
       </c>
-      <c r="H241" t="s">
+      <c r="K241" t="s">
         <v>1032</v>
       </c>
-      <c r="I241" t="s">
+      <c r="L241" t="s">
         <v>1033</v>
       </c>
-      <c r="K241" t="s">
-        <v>950</v>
-      </c>
-      <c r="L241" t="s">
+      <c r="M241" t="s">
         <v>951</v>
-      </c>
-      <c r="M241" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -12643,10 +12643,10 @@
         <v>16</v>
       </c>
       <c r="E242" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F242" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H242" t="s">
         <v>1036</v>
@@ -12655,13 +12655,13 @@
         <v>1037</v>
       </c>
       <c r="K242" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L242" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M242" t="s">
         <v>951</v>
-      </c>
-      <c r="M242" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -12678,10 +12678,10 @@
         <v>16</v>
       </c>
       <c r="E243" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F243" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H243" t="s">
         <v>1040</v>
@@ -12690,13 +12690,13 @@
         <v>1041</v>
       </c>
       <c r="K243" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L243" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M243" t="s">
         <v>951</v>
-      </c>
-      <c r="M243" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -12713,10 +12713,10 @@
         <v>16</v>
       </c>
       <c r="E244" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F244" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H244" t="s">
         <v>1044</v>
@@ -12725,13 +12725,13 @@
         <v>1045</v>
       </c>
       <c r="K244" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L244" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M244" t="s">
         <v>951</v>
-      </c>
-      <c r="M244" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -12748,10 +12748,10 @@
         <v>16</v>
       </c>
       <c r="E245" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F245" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H245" t="s">
         <v>1048</v>
@@ -12760,13 +12760,13 @@
         <v>1049</v>
       </c>
       <c r="K245" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L245" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M245" t="s">
         <v>951</v>
-      </c>
-      <c r="M245" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -12783,10 +12783,10 @@
         <v>16</v>
       </c>
       <c r="E246" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F246" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H246" t="s">
         <v>1052</v>
@@ -12795,13 +12795,13 @@
         <v>1053</v>
       </c>
       <c r="K246" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L246" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M246" t="s">
         <v>951</v>
-      </c>
-      <c r="M246" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -12818,10 +12818,10 @@
         <v>16</v>
       </c>
       <c r="E247" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F247" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H247" t="s">
         <v>1056</v>
@@ -12830,13 +12830,13 @@
         <v>1057</v>
       </c>
       <c r="K247" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L247" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M247" t="s">
         <v>951</v>
-      </c>
-      <c r="M247" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -12853,10 +12853,10 @@
         <v>16</v>
       </c>
       <c r="E248" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F248" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H248" t="s">
         <v>1060</v>
@@ -12865,13 +12865,13 @@
         <v>1061</v>
       </c>
       <c r="K248" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L248" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M248" t="s">
         <v>951</v>
-      </c>
-      <c r="M248" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -12888,10 +12888,10 @@
         <v>16</v>
       </c>
       <c r="E249" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F249" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H249" t="s">
         <v>1064</v>
@@ -12900,13 +12900,13 @@
         <v>1065</v>
       </c>
       <c r="K249" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L249" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M249" t="s">
         <v>951</v>
-      </c>
-      <c r="M249" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -12923,10 +12923,10 @@
         <v>16</v>
       </c>
       <c r="E250" t="s">
-        <v>1030</v>
+        <v>946</v>
       </c>
       <c r="F250" t="s">
-        <v>1031</v>
+        <v>18</v>
       </c>
       <c r="H250" t="s">
         <v>1068</v>
@@ -12935,13 +12935,13 @@
         <v>1069</v>
       </c>
       <c r="K250" t="s">
-        <v>950</v>
+        <v>1032</v>
       </c>
       <c r="L250" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M250" t="s">
         <v>951</v>
-      </c>
-      <c r="M250" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,33 +25,33 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-code</t>
   </si>
   <si>
+    <t>codeforiati:global-name</t>
+  </si>
+  <si>
     <t>codeforiati:region-name</t>
   </si>
   <si>
-    <t>codeforiati:global-name</t>
+    <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
     <t>codeforiati:intermediate-region-name</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
   </si>
   <si>
     <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
@@ -64,27 +64,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>DZ</t>
+  </si>
+  <si>
     <t>001</t>
   </si>
   <si>
+    <t>World</t>
+  </si>
+  <si>
     <t>Africa</t>
   </si>
   <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>DZ</t>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>015</t>
   </si>
   <si>
     <t>DZA</t>
   </si>
   <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -166,24 +166,24 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>Eastern Africa</t>
   </si>
   <si>
-    <t>IO</t>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t>202</t>
   </si>
   <si>
     <t>IOT</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -442,18 +442,18 @@
     <t>Angola</t>
   </si>
   <si>
+    <t>AO</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>Middle Africa</t>
   </si>
   <si>
-    <t>AO</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -556,18 +556,18 @@
     <t>Botswana</t>
   </si>
   <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>Southern Africa</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -622,18 +622,18 @@
     <t>Benin</t>
   </si>
   <si>
+    <t>BJ</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>Western Africa</t>
   </si>
   <si>
-    <t>BJ</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>Americas</t>
   </si>
   <si>
+    <t>029</t>
+  </si>
+  <si>
     <t>Caribbean</t>
   </si>
   <si>
-    <t>AI</t>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>419</t>
   </si>
   <si>
     <t>AIA</t>
   </si>
   <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
     <t>019</t>
   </si>
   <si>
@@ -1186,18 +1186,18 @@
     <t>Belize</t>
   </si>
   <si>
+    <t>BZ</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>Central America</t>
   </si>
   <si>
-    <t>BZ</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -1288,18 +1288,18 @@
     <t>Argentina</t>
   </si>
   <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>South America</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1489,15 +1489,15 @@
     <t>BM</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
     <t>BMU</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
-    <t>021</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1564,21 +1564,21 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>KZ</t>
+  </si>
+  <si>
     <t>Asia</t>
   </si>
   <si>
-    <t>KZ</t>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>143</t>
   </si>
   <si>
     <t>KAZ</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
     <t>142</t>
   </si>
   <si>
@@ -1639,15 +1639,15 @@
     <t>CN</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
     <t>CHN</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1729,15 +1729,15 @@
     <t>BN</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
     <t>BRN</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1867,15 +1867,15 @@
     <t>AF</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
     <t>AFG</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1981,15 +1981,15 @@
     <t>AM</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
     <t>ARM</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -2200,21 +2200,21 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>BY</t>
+  </si>
+  <si>
     <t>Europe</t>
   </si>
   <si>
-    <t>BY</t>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>151</t>
   </si>
   <si>
     <t>BLR</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -2335,33 +2335,33 @@
     <t>AX</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
     <t>ALA</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
     <t>Guernsey</t>
   </si>
   <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
     <t>Channel Islands</t>
   </si>
   <si>
-    <t>GG</t>
-  </si>
-  <si>
     <t>GGY</t>
   </si>
   <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>832</t>
   </si>
   <si>
@@ -2545,15 +2545,15 @@
     <t>AL</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
     <t>ALB</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2743,15 +2743,15 @@
     <t>AT</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
     <t>AUT</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2854,21 +2854,21 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>AU</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
-    <t>AU</t>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>053</t>
   </si>
   <si>
     <t>AUS</t>
   </si>
   <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
     <t>009</t>
   </si>
   <si>
@@ -2941,15 +2941,15 @@
     <t>FJ</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
     <t>FJI</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
-    <t>054</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -3007,15 +3007,15 @@
     <t>GU</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
     <t>GUM</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -3109,13 +3109,13 @@
     <t>AS</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
     <t>ASM</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
-  </si>
-  <si>
-    <t>061</t>
   </si>
   <si>
     <t>184</t>
@@ -3618,10 +3618,10 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" t="s">
@@ -3645,7 +3645,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -3653,17 +3653,17 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -3680,7 +3680,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -3688,17 +3688,17 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s">
         <v>23</v>
@@ -3715,7 +3715,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -3723,17 +3723,17 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
         <v>23</v>
@@ -3750,7 +3750,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -3758,17 +3758,17 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="H6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -3785,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -3793,17 +3793,17 @@
       <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
@@ -3820,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -3828,17 +3828,17 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M8" t="s">
         <v>23</v>
@@ -3855,7 +3855,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -3864,7 +3864,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
         <v>51</v>
@@ -3896,7 +3896,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -3905,13 +3905,13 @@
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
         <v>53</v>
@@ -3920,7 +3920,7 @@
         <v>54</v>
       </c>
       <c r="L10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M10" t="s">
         <v>23</v>
@@ -3937,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -3946,13 +3946,13 @@
         <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="J11" t="s">
         <v>53</v>
@@ -3961,7 +3961,7 @@
         <v>54</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
@@ -3978,7 +3978,7 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -3987,13 +3987,13 @@
         <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
         <v>53</v>
@@ -4002,7 +4002,7 @@
         <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="M12" t="s">
         <v>23</v>
@@ -4019,7 +4019,7 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -4028,13 +4028,13 @@
         <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="J13" t="s">
         <v>53</v>
@@ -4043,7 +4043,7 @@
         <v>54</v>
       </c>
       <c r="L13" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
@@ -4060,7 +4060,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -4069,13 +4069,13 @@
         <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="I14" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="J14" t="s">
         <v>53</v>
@@ -4084,7 +4084,7 @@
         <v>54</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="M14" t="s">
         <v>23</v>
@@ -4101,7 +4101,7 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -4110,13 +4110,13 @@
         <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="J15" t="s">
         <v>53</v>
@@ -4125,7 +4125,7 @@
         <v>54</v>
       </c>
       <c r="L15" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="M15" t="s">
         <v>23</v>
@@ -4142,7 +4142,7 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -4151,13 +4151,13 @@
         <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="J16" t="s">
         <v>53</v>
@@ -4166,7 +4166,7 @@
         <v>54</v>
       </c>
       <c r="L16" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="M16" t="s">
         <v>23</v>
@@ -4183,7 +4183,7 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -4192,13 +4192,13 @@
         <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="J17" t="s">
         <v>53</v>
@@ -4207,7 +4207,7 @@
         <v>54</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
         <v>23</v>
@@ -4224,7 +4224,7 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -4233,13 +4233,13 @@
         <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="I18" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="J18" t="s">
         <v>53</v>
@@ -4248,7 +4248,7 @@
         <v>54</v>
       </c>
       <c r="L18" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s">
         <v>23</v>
@@ -4265,7 +4265,7 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -4274,13 +4274,13 @@
         <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="I19" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="J19" t="s">
         <v>53</v>
@@ -4289,7 +4289,7 @@
         <v>54</v>
       </c>
       <c r="L19" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="M19" t="s">
         <v>23</v>
@@ -4306,7 +4306,7 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -4315,13 +4315,13 @@
         <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="I20" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="J20" t="s">
         <v>53</v>
@@ -4330,7 +4330,7 @@
         <v>54</v>
       </c>
       <c r="L20" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -4356,13 +4356,13 @@
         <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="I21" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="J21" t="s">
         <v>53</v>
@@ -4371,7 +4371,7 @@
         <v>54</v>
       </c>
       <c r="L21" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="M21" t="s">
         <v>23</v>
@@ -4388,7 +4388,7 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -4397,13 +4397,13 @@
         <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="I22" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="J22" t="s">
         <v>53</v>
@@ -4412,7 +4412,7 @@
         <v>54</v>
       </c>
       <c r="L22" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="M22" t="s">
         <v>23</v>
@@ -4429,7 +4429,7 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -4438,13 +4438,13 @@
         <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="J23" t="s">
         <v>53</v>
@@ -4453,7 +4453,7 @@
         <v>54</v>
       </c>
       <c r="L23" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="M23" t="s">
         <v>23</v>
@@ -4470,7 +4470,7 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -4479,13 +4479,13 @@
         <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="I24" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="J24" t="s">
         <v>53</v>
@@ -4494,7 +4494,7 @@
         <v>54</v>
       </c>
       <c r="L24" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="M24" t="s">
         <v>23</v>
@@ -4511,7 +4511,7 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -4520,13 +4520,13 @@
         <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="J25" t="s">
         <v>53</v>
@@ -4535,7 +4535,7 @@
         <v>54</v>
       </c>
       <c r="L25" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="M25" t="s">
         <v>23</v>
@@ -4552,7 +4552,7 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -4561,13 +4561,13 @@
         <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="I26" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="J26" t="s">
         <v>53</v>
@@ -4576,7 +4576,7 @@
         <v>54</v>
       </c>
       <c r="L26" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -4593,7 +4593,7 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -4602,13 +4602,13 @@
         <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="I27" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="J27" t="s">
         <v>53</v>
@@ -4617,7 +4617,7 @@
         <v>54</v>
       </c>
       <c r="L27" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="M27" t="s">
         <v>23</v>
@@ -4634,7 +4634,7 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -4643,13 +4643,13 @@
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="I28" t="s">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="J28" t="s">
         <v>53</v>
@@ -4658,7 +4658,7 @@
         <v>54</v>
       </c>
       <c r="L28" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="M28" t="s">
         <v>23</v>
@@ -4675,7 +4675,7 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -4684,13 +4684,13 @@
         <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="I29" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="J29" t="s">
         <v>53</v>
@@ -4699,7 +4699,7 @@
         <v>54</v>
       </c>
       <c r="L29" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="M29" t="s">
         <v>23</v>
@@ -4716,7 +4716,7 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -4725,13 +4725,13 @@
         <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H30" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="I30" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="J30" t="s">
         <v>53</v>
@@ -4740,7 +4740,7 @@
         <v>54</v>
       </c>
       <c r="L30" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="M30" t="s">
         <v>23</v>
@@ -4757,7 +4757,7 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -4766,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H31" t="s">
         <v>143</v>
@@ -4775,13 +4775,13 @@
         <v>144</v>
       </c>
       <c r="J31" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K31" t="s">
         <v>54</v>
       </c>
       <c r="L31" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="M31" t="s">
         <v>23</v>
@@ -4798,7 +4798,7 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -4807,22 +4807,22 @@
         <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I32" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J32" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K32" t="s">
         <v>54</v>
       </c>
       <c r="L32" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="M32" t="s">
         <v>23</v>
@@ -4839,7 +4839,7 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -4848,22 +4848,22 @@
         <v>18</v>
       </c>
       <c r="G33" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I33" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="J33" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K33" t="s">
         <v>54</v>
       </c>
       <c r="L33" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="M33" t="s">
         <v>23</v>
@@ -4880,7 +4880,7 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -4889,22 +4889,22 @@
         <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="I34" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="J34" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K34" t="s">
         <v>54</v>
       </c>
       <c r="L34" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="M34" t="s">
         <v>23</v>
@@ -4921,7 +4921,7 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
@@ -4930,22 +4930,22 @@
         <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="I35" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="J35" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K35" t="s">
         <v>54</v>
       </c>
       <c r="L35" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="M35" t="s">
         <v>23</v>
@@ -4962,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -4971,22 +4971,22 @@
         <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="I36" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="J36" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K36" t="s">
         <v>54</v>
       </c>
       <c r="L36" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="M36" t="s">
         <v>23</v>
@@ -5003,7 +5003,7 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -5012,22 +5012,22 @@
         <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="I37" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="J37" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K37" t="s">
         <v>54</v>
       </c>
       <c r="L37" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="M37" t="s">
         <v>23</v>
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -5053,22 +5053,22 @@
         <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="I38" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="J38" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K38" t="s">
         <v>54</v>
       </c>
       <c r="L38" t="s">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -5085,7 +5085,7 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -5094,22 +5094,22 @@
         <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="I39" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="J39" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K39" t="s">
         <v>54</v>
       </c>
       <c r="L39" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -5126,7 +5126,7 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -5135,7 +5135,7 @@
         <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
         <v>181</v>
@@ -5144,13 +5144,13 @@
         <v>182</v>
       </c>
       <c r="J40" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="K40" t="s">
         <v>54</v>
       </c>
       <c r="L40" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -5167,7 +5167,7 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
@@ -5176,22 +5176,22 @@
         <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I41" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J41" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="K41" t="s">
         <v>54</v>
       </c>
       <c r="L41" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -5208,7 +5208,7 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -5217,22 +5217,22 @@
         <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I42" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="J42" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="K42" t="s">
         <v>54</v>
       </c>
       <c r="L42" t="s">
-        <v>55</v>
+        <v>191</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -5249,7 +5249,7 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -5258,22 +5258,22 @@
         <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="I43" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="J43" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="K43" t="s">
         <v>54</v>
       </c>
       <c r="L43" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
@@ -5290,7 +5290,7 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -5299,22 +5299,22 @@
         <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I44" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J44" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="K44" t="s">
         <v>54</v>
       </c>
       <c r="L44" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
@@ -5331,7 +5331,7 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -5340,7 +5340,7 @@
         <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H45" t="s">
         <v>203</v>
@@ -5349,13 +5349,13 @@
         <v>204</v>
       </c>
       <c r="J45" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K45" t="s">
         <v>54</v>
       </c>
       <c r="L45" t="s">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -5372,7 +5372,7 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -5381,22 +5381,22 @@
         <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I46" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J46" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K46" t="s">
         <v>54</v>
       </c>
       <c r="L46" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -5413,7 +5413,7 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -5422,22 +5422,22 @@
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="I47" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="J47" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K47" t="s">
         <v>54</v>
       </c>
       <c r="L47" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
@@ -5454,7 +5454,7 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>216</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -5463,22 +5463,22 @@
         <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H48" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="J48" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K48" t="s">
         <v>54</v>
       </c>
       <c r="L48" t="s">
-        <v>55</v>
+        <v>217</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
@@ -5495,7 +5495,7 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -5504,22 +5504,22 @@
         <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H49" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="J49" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K49" t="s">
         <v>54</v>
       </c>
       <c r="L49" t="s">
-        <v>55</v>
+        <v>221</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
@@ -5536,7 +5536,7 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>224</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -5545,22 +5545,22 @@
         <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="I50" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="J50" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K50" t="s">
         <v>54</v>
       </c>
       <c r="L50" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
@@ -5577,7 +5577,7 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -5586,22 +5586,22 @@
         <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="I51" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="J51" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K51" t="s">
         <v>54</v>
       </c>
       <c r="L51" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -5618,7 +5618,7 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>232</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -5627,22 +5627,22 @@
         <v>18</v>
       </c>
       <c r="G52" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="I52" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="J52" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K52" t="s">
         <v>54</v>
       </c>
       <c r="L52" t="s">
-        <v>55</v>
+        <v>233</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -5659,7 +5659,7 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="E53" t="s">
         <v>17</v>
@@ -5668,22 +5668,22 @@
         <v>18</v>
       </c>
       <c r="G53" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="I53" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="J53" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K53" t="s">
         <v>54</v>
       </c>
       <c r="L53" t="s">
-        <v>55</v>
+        <v>237</v>
       </c>
       <c r="M53" t="s">
         <v>23</v>
@@ -5700,7 +5700,7 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="E54" t="s">
         <v>17</v>
@@ -5709,22 +5709,22 @@
         <v>18</v>
       </c>
       <c r="G54" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H54" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="I54" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="J54" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K54" t="s">
         <v>54</v>
       </c>
       <c r="L54" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="M54" t="s">
         <v>23</v>
@@ -5741,7 +5741,7 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="E55" t="s">
         <v>17</v>
@@ -5750,22 +5750,22 @@
         <v>18</v>
       </c>
       <c r="G55" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H55" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
       <c r="I55" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="J55" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K55" t="s">
         <v>54</v>
       </c>
       <c r="L55" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="M55" t="s">
         <v>23</v>
@@ -5782,7 +5782,7 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>248</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
@@ -5791,22 +5791,22 @@
         <v>18</v>
       </c>
       <c r="G56" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H56" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="I56" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="J56" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K56" t="s">
         <v>54</v>
       </c>
       <c r="L56" t="s">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
@@ -5823,7 +5823,7 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>252</v>
       </c>
       <c r="E57" t="s">
         <v>17</v>
@@ -5832,22 +5832,22 @@
         <v>18</v>
       </c>
       <c r="G57" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H57" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="I57" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="J57" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K57" t="s">
         <v>54</v>
       </c>
       <c r="L57" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
@@ -5864,7 +5864,7 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -5873,22 +5873,22 @@
         <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H58" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="I58" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="J58" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K58" t="s">
         <v>54</v>
       </c>
       <c r="L58" t="s">
-        <v>55</v>
+        <v>257</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -5905,7 +5905,7 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
@@ -5914,22 +5914,22 @@
         <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="I59" t="s">
-        <v>261</v>
+        <v>204</v>
       </c>
       <c r="J59" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K59" t="s">
         <v>54</v>
       </c>
       <c r="L59" t="s">
-        <v>55</v>
+        <v>261</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
@@ -5946,7 +5946,7 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>264</v>
       </c>
       <c r="E60" t="s">
         <v>17</v>
@@ -5955,22 +5955,22 @@
         <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H60" t="s">
-        <v>264</v>
+        <v>203</v>
       </c>
       <c r="I60" t="s">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="J60" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K60" t="s">
         <v>54</v>
       </c>
       <c r="L60" t="s">
-        <v>55</v>
+        <v>265</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
@@ -5987,7 +5987,7 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c r="E61" t="s">
         <v>17</v>
@@ -5996,22 +5996,22 @@
         <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H61" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="I61" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="J61" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="K61" t="s">
         <v>54</v>
       </c>
       <c r="L61" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -6028,10 +6028,10 @@
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F62" t="s">
         <v>18</v>
@@ -6069,10 +6069,10 @@
         <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>282</v>
       </c>
       <c r="E63" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -6081,10 +6081,10 @@
         <v>273</v>
       </c>
       <c r="H63" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I63" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="J63" t="s">
         <v>276</v>
@@ -6093,7 +6093,7 @@
         <v>277</v>
       </c>
       <c r="L63" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="M63" t="s">
         <v>279</v>
@@ -6110,10 +6110,10 @@
         <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="E64" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
@@ -6122,10 +6122,10 @@
         <v>273</v>
       </c>
       <c r="H64" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="I64" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J64" t="s">
         <v>276</v>
@@ -6134,7 +6134,7 @@
         <v>277</v>
       </c>
       <c r="L64" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="M64" t="s">
         <v>279</v>
@@ -6151,10 +6151,10 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>290</v>
       </c>
       <c r="E65" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
         <v>18</v>
@@ -6163,10 +6163,10 @@
         <v>273</v>
       </c>
       <c r="H65" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="I65" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="J65" t="s">
         <v>276</v>
@@ -6175,7 +6175,7 @@
         <v>277</v>
       </c>
       <c r="L65" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="M65" t="s">
         <v>279</v>
@@ -6192,10 +6192,10 @@
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>294</v>
       </c>
       <c r="E66" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F66" t="s">
         <v>18</v>
@@ -6204,10 +6204,10 @@
         <v>273</v>
       </c>
       <c r="H66" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="I66" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="J66" t="s">
         <v>276</v>
@@ -6216,7 +6216,7 @@
         <v>277</v>
       </c>
       <c r="L66" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="M66" t="s">
         <v>279</v>
@@ -6233,10 +6233,10 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
@@ -6245,10 +6245,10 @@
         <v>273</v>
       </c>
       <c r="H67" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="I67" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="J67" t="s">
         <v>276</v>
@@ -6257,7 +6257,7 @@
         <v>277</v>
       </c>
       <c r="L67" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="M67" t="s">
         <v>279</v>
@@ -6274,10 +6274,10 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c r="E68" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
@@ -6286,10 +6286,10 @@
         <v>273</v>
       </c>
       <c r="H68" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="I68" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="J68" t="s">
         <v>276</v>
@@ -6298,7 +6298,7 @@
         <v>277</v>
       </c>
       <c r="L68" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="M68" t="s">
         <v>279</v>
@@ -6315,10 +6315,10 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>306</v>
       </c>
       <c r="E69" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
         <v>18</v>
@@ -6327,10 +6327,10 @@
         <v>273</v>
       </c>
       <c r="H69" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="I69" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="J69" t="s">
         <v>276</v>
@@ -6339,7 +6339,7 @@
         <v>277</v>
       </c>
       <c r="L69" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="M69" t="s">
         <v>279</v>
@@ -6356,10 +6356,10 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="E70" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F70" t="s">
         <v>18</v>
@@ -6368,10 +6368,10 @@
         <v>273</v>
       </c>
       <c r="H70" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="I70" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="J70" t="s">
         <v>276</v>
@@ -6380,7 +6380,7 @@
         <v>277</v>
       </c>
       <c r="L70" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="M70" t="s">
         <v>279</v>
@@ -6397,10 +6397,10 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>314</v>
       </c>
       <c r="E71" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -6409,10 +6409,10 @@
         <v>273</v>
       </c>
       <c r="H71" t="s">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="I71" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="J71" t="s">
         <v>276</v>
@@ -6421,7 +6421,7 @@
         <v>277</v>
       </c>
       <c r="L71" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="M71" t="s">
         <v>279</v>
@@ -6438,10 +6438,10 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="E72" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -6450,10 +6450,10 @@
         <v>273</v>
       </c>
       <c r="H72" t="s">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c r="I72" t="s">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="J72" t="s">
         <v>276</v>
@@ -6462,7 +6462,7 @@
         <v>277</v>
       </c>
       <c r="L72" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="M72" t="s">
         <v>279</v>
@@ -6479,10 +6479,10 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>322</v>
       </c>
       <c r="E73" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
@@ -6491,10 +6491,10 @@
         <v>273</v>
       </c>
       <c r="H73" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="I73" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="J73" t="s">
         <v>276</v>
@@ -6503,7 +6503,7 @@
         <v>277</v>
       </c>
       <c r="L73" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="M73" t="s">
         <v>279</v>
@@ -6520,10 +6520,10 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c r="E74" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F74" t="s">
         <v>18</v>
@@ -6532,10 +6532,10 @@
         <v>273</v>
       </c>
       <c r="H74" t="s">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="I74" t="s">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="J74" t="s">
         <v>276</v>
@@ -6544,7 +6544,7 @@
         <v>277</v>
       </c>
       <c r="L74" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="M74" t="s">
         <v>279</v>
@@ -6561,10 +6561,10 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -6573,10 +6573,10 @@
         <v>273</v>
       </c>
       <c r="H75" t="s">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="I75" t="s">
-        <v>331</v>
+        <v>275</v>
       </c>
       <c r="J75" t="s">
         <v>276</v>
@@ -6585,7 +6585,7 @@
         <v>277</v>
       </c>
       <c r="L75" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="M75" t="s">
         <v>279</v>
@@ -6602,10 +6602,10 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>334</v>
       </c>
       <c r="E76" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s">
         <v>18</v>
@@ -6614,10 +6614,10 @@
         <v>273</v>
       </c>
       <c r="H76" t="s">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="I76" t="s">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="J76" t="s">
         <v>276</v>
@@ -6626,7 +6626,7 @@
         <v>277</v>
       </c>
       <c r="L76" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="M76" t="s">
         <v>279</v>
@@ -6643,10 +6643,10 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>338</v>
       </c>
       <c r="E77" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F77" t="s">
         <v>18</v>
@@ -6655,10 +6655,10 @@
         <v>273</v>
       </c>
       <c r="H77" t="s">
-        <v>338</v>
+        <v>274</v>
       </c>
       <c r="I77" t="s">
-        <v>339</v>
+        <v>275</v>
       </c>
       <c r="J77" t="s">
         <v>276</v>
@@ -6667,7 +6667,7 @@
         <v>277</v>
       </c>
       <c r="L77" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="M77" t="s">
         <v>279</v>
@@ -6684,10 +6684,10 @@
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>342</v>
       </c>
       <c r="E78" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F78" t="s">
         <v>18</v>
@@ -6696,10 +6696,10 @@
         <v>273</v>
       </c>
       <c r="H78" t="s">
-        <v>342</v>
+        <v>274</v>
       </c>
       <c r="I78" t="s">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="J78" t="s">
         <v>276</v>
@@ -6708,7 +6708,7 @@
         <v>277</v>
       </c>
       <c r="L78" t="s">
-        <v>278</v>
+        <v>343</v>
       </c>
       <c r="M78" t="s">
         <v>279</v>
@@ -6725,10 +6725,10 @@
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>346</v>
       </c>
       <c r="E79" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F79" t="s">
         <v>18</v>
@@ -6737,10 +6737,10 @@
         <v>273</v>
       </c>
       <c r="H79" t="s">
-        <v>346</v>
+        <v>274</v>
       </c>
       <c r="I79" t="s">
-        <v>347</v>
+        <v>275</v>
       </c>
       <c r="J79" t="s">
         <v>276</v>
@@ -6749,7 +6749,7 @@
         <v>277</v>
       </c>
       <c r="L79" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
       <c r="M79" t="s">
         <v>279</v>
@@ -6766,10 +6766,10 @@
         <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c r="E80" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F80" t="s">
         <v>18</v>
@@ -6778,10 +6778,10 @@
         <v>273</v>
       </c>
       <c r="H80" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="I80" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="J80" t="s">
         <v>276</v>
@@ -6790,7 +6790,7 @@
         <v>277</v>
       </c>
       <c r="L80" t="s">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="M80" t="s">
         <v>279</v>
@@ -6807,10 +6807,10 @@
         <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="E81" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F81" t="s">
         <v>18</v>
@@ -6819,10 +6819,10 @@
         <v>273</v>
       </c>
       <c r="H81" t="s">
-        <v>354</v>
+        <v>274</v>
       </c>
       <c r="I81" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="J81" t="s">
         <v>276</v>
@@ -6831,7 +6831,7 @@
         <v>277</v>
       </c>
       <c r="L81" t="s">
-        <v>278</v>
+        <v>355</v>
       </c>
       <c r="M81" t="s">
         <v>279</v>
@@ -6848,10 +6848,10 @@
         <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>358</v>
       </c>
       <c r="E82" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F82" t="s">
         <v>18</v>
@@ -6860,10 +6860,10 @@
         <v>273</v>
       </c>
       <c r="H82" t="s">
-        <v>358</v>
+        <v>274</v>
       </c>
       <c r="I82" t="s">
-        <v>359</v>
+        <v>275</v>
       </c>
       <c r="J82" t="s">
         <v>276</v>
@@ -6872,7 +6872,7 @@
         <v>277</v>
       </c>
       <c r="L82" t="s">
-        <v>278</v>
+        <v>359</v>
       </c>
       <c r="M82" t="s">
         <v>279</v>
@@ -6889,10 +6889,10 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>362</v>
       </c>
       <c r="E83" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
         <v>18</v>
@@ -6901,10 +6901,10 @@
         <v>273</v>
       </c>
       <c r="H83" t="s">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="I83" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="J83" t="s">
         <v>276</v>
@@ -6913,7 +6913,7 @@
         <v>277</v>
       </c>
       <c r="L83" t="s">
-        <v>278</v>
+        <v>363</v>
       </c>
       <c r="M83" t="s">
         <v>279</v>
@@ -6930,10 +6930,10 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>366</v>
       </c>
       <c r="E84" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F84" t="s">
         <v>18</v>
@@ -6942,10 +6942,10 @@
         <v>273</v>
       </c>
       <c r="H84" t="s">
-        <v>366</v>
+        <v>274</v>
       </c>
       <c r="I84" t="s">
-        <v>367</v>
+        <v>275</v>
       </c>
       <c r="J84" t="s">
         <v>276</v>
@@ -6954,7 +6954,7 @@
         <v>277</v>
       </c>
       <c r="L84" t="s">
-        <v>278</v>
+        <v>367</v>
       </c>
       <c r="M84" t="s">
         <v>279</v>
@@ -6971,10 +6971,10 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>370</v>
       </c>
       <c r="E85" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F85" t="s">
         <v>18</v>
@@ -6983,10 +6983,10 @@
         <v>273</v>
       </c>
       <c r="H85" t="s">
-        <v>370</v>
+        <v>274</v>
       </c>
       <c r="I85" t="s">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c r="J85" t="s">
         <v>276</v>
@@ -6995,7 +6995,7 @@
         <v>277</v>
       </c>
       <c r="L85" t="s">
-        <v>278</v>
+        <v>371</v>
       </c>
       <c r="M85" t="s">
         <v>279</v>
@@ -7012,10 +7012,10 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>374</v>
       </c>
       <c r="E86" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
@@ -7024,10 +7024,10 @@
         <v>273</v>
       </c>
       <c r="H86" t="s">
-        <v>374</v>
+        <v>274</v>
       </c>
       <c r="I86" t="s">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="J86" t="s">
         <v>276</v>
@@ -7036,7 +7036,7 @@
         <v>277</v>
       </c>
       <c r="L86" t="s">
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="M86" t="s">
         <v>279</v>
@@ -7053,10 +7053,10 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>378</v>
       </c>
       <c r="E87" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F87" t="s">
         <v>18</v>
@@ -7065,10 +7065,10 @@
         <v>273</v>
       </c>
       <c r="H87" t="s">
-        <v>378</v>
+        <v>274</v>
       </c>
       <c r="I87" t="s">
-        <v>379</v>
+        <v>275</v>
       </c>
       <c r="J87" t="s">
         <v>276</v>
@@ -7077,7 +7077,7 @@
         <v>277</v>
       </c>
       <c r="L87" t="s">
-        <v>278</v>
+        <v>379</v>
       </c>
       <c r="M87" t="s">
         <v>279</v>
@@ -7094,10 +7094,10 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>382</v>
       </c>
       <c r="E88" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F88" t="s">
         <v>18</v>
@@ -7106,10 +7106,10 @@
         <v>273</v>
       </c>
       <c r="H88" t="s">
-        <v>382</v>
+        <v>274</v>
       </c>
       <c r="I88" t="s">
-        <v>383</v>
+        <v>275</v>
       </c>
       <c r="J88" t="s">
         <v>276</v>
@@ -7118,7 +7118,7 @@
         <v>277</v>
       </c>
       <c r="L88" t="s">
-        <v>278</v>
+        <v>383</v>
       </c>
       <c r="M88" t="s">
         <v>279</v>
@@ -7135,10 +7135,10 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="E89" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
         <v>18</v>
@@ -7147,10 +7147,10 @@
         <v>273</v>
       </c>
       <c r="H89" t="s">
-        <v>386</v>
+        <v>274</v>
       </c>
       <c r="I89" t="s">
-        <v>387</v>
+        <v>275</v>
       </c>
       <c r="J89" t="s">
         <v>276</v>
@@ -7159,7 +7159,7 @@
         <v>277</v>
       </c>
       <c r="L89" t="s">
-        <v>278</v>
+        <v>387</v>
       </c>
       <c r="M89" t="s">
         <v>279</v>
@@ -7176,16 +7176,16 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>390</v>
       </c>
       <c r="E90" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F90" t="s">
         <v>18</v>
       </c>
       <c r="G90" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H90" t="s">
         <v>391</v>
@@ -7194,13 +7194,13 @@
         <v>392</v>
       </c>
       <c r="J90" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K90" t="s">
         <v>277</v>
       </c>
       <c r="L90" t="s">
-        <v>278</v>
+        <v>393</v>
       </c>
       <c r="M90" t="s">
         <v>279</v>
@@ -7217,31 +7217,31 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="E91" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F91" t="s">
         <v>18</v>
       </c>
       <c r="G91" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H91" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I91" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="J91" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K91" t="s">
         <v>277</v>
       </c>
       <c r="L91" t="s">
-        <v>278</v>
+        <v>397</v>
       </c>
       <c r="M91" t="s">
         <v>279</v>
@@ -7258,31 +7258,31 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="E92" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F92" t="s">
         <v>18</v>
       </c>
       <c r="G92" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H92" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I92" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="J92" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K92" t="s">
         <v>277</v>
       </c>
       <c r="L92" t="s">
-        <v>278</v>
+        <v>401</v>
       </c>
       <c r="M92" t="s">
         <v>279</v>
@@ -7299,31 +7299,31 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="E93" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F93" t="s">
         <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H93" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="I93" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="J93" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K93" t="s">
         <v>277</v>
       </c>
       <c r="L93" t="s">
-        <v>278</v>
+        <v>405</v>
       </c>
       <c r="M93" t="s">
         <v>279</v>
@@ -7340,31 +7340,31 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>408</v>
       </c>
       <c r="E94" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
         <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H94" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="I94" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="J94" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K94" t="s">
         <v>277</v>
       </c>
       <c r="L94" t="s">
-        <v>278</v>
+        <v>409</v>
       </c>
       <c r="M94" t="s">
         <v>279</v>
@@ -7381,31 +7381,31 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>412</v>
       </c>
       <c r="E95" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F95" t="s">
         <v>18</v>
       </c>
       <c r="G95" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H95" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="I95" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="J95" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K95" t="s">
         <v>277</v>
       </c>
       <c r="L95" t="s">
-        <v>278</v>
+        <v>413</v>
       </c>
       <c r="M95" t="s">
         <v>279</v>
@@ -7422,31 +7422,31 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="E96" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F96" t="s">
         <v>18</v>
       </c>
       <c r="G96" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H96" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="I96" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="J96" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K96" t="s">
         <v>277</v>
       </c>
       <c r="L96" t="s">
-        <v>278</v>
+        <v>417</v>
       </c>
       <c r="M96" t="s">
         <v>279</v>
@@ -7463,31 +7463,31 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>420</v>
       </c>
       <c r="E97" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="H97" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="I97" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="J97" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K97" t="s">
         <v>277</v>
       </c>
       <c r="L97" t="s">
-        <v>278</v>
+        <v>421</v>
       </c>
       <c r="M97" t="s">
         <v>279</v>
@@ -7504,16 +7504,16 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>424</v>
       </c>
       <c r="E98" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F98" t="s">
         <v>18</v>
       </c>
       <c r="G98" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H98" t="s">
         <v>425</v>
@@ -7522,13 +7522,13 @@
         <v>426</v>
       </c>
       <c r="J98" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K98" t="s">
         <v>277</v>
       </c>
       <c r="L98" t="s">
-        <v>278</v>
+        <v>427</v>
       </c>
       <c r="M98" t="s">
         <v>279</v>
@@ -7545,31 +7545,31 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
       <c r="E99" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F99" t="s">
         <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H99" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="I99" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="J99" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K99" t="s">
         <v>277</v>
       </c>
       <c r="L99" t="s">
-        <v>278</v>
+        <v>431</v>
       </c>
       <c r="M99" t="s">
         <v>279</v>
@@ -7586,31 +7586,31 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>434</v>
       </c>
       <c r="E100" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F100" t="s">
         <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H100" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="I100" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="J100" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K100" t="s">
         <v>277</v>
       </c>
       <c r="L100" t="s">
-        <v>278</v>
+        <v>435</v>
       </c>
       <c r="M100" t="s">
         <v>279</v>
@@ -7627,31 +7627,31 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>438</v>
       </c>
       <c r="E101" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F101" t="s">
         <v>18</v>
       </c>
       <c r="G101" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H101" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="I101" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="J101" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K101" t="s">
         <v>277</v>
       </c>
       <c r="L101" t="s">
-        <v>278</v>
+        <v>439</v>
       </c>
       <c r="M101" t="s">
         <v>279</v>
@@ -7668,31 +7668,31 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>442</v>
       </c>
       <c r="E102" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F102" t="s">
         <v>18</v>
       </c>
       <c r="G102" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H102" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="I102" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="J102" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K102" t="s">
         <v>277</v>
       </c>
       <c r="L102" t="s">
-        <v>278</v>
+        <v>443</v>
       </c>
       <c r="M102" t="s">
         <v>279</v>
@@ -7709,31 +7709,31 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>446</v>
       </c>
       <c r="E103" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F103" t="s">
         <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H103" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="I103" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="J103" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K103" t="s">
         <v>277</v>
       </c>
       <c r="L103" t="s">
-        <v>278</v>
+        <v>447</v>
       </c>
       <c r="M103" t="s">
         <v>279</v>
@@ -7750,31 +7750,31 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>450</v>
       </c>
       <c r="E104" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
         <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H104" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="I104" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="J104" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K104" t="s">
         <v>277</v>
       </c>
       <c r="L104" t="s">
-        <v>278</v>
+        <v>451</v>
       </c>
       <c r="M104" t="s">
         <v>279</v>
@@ -7791,31 +7791,31 @@
         <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>454</v>
       </c>
       <c r="E105" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F105" t="s">
         <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H105" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="I105" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="J105" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K105" t="s">
         <v>277</v>
       </c>
       <c r="L105" t="s">
-        <v>278</v>
+        <v>455</v>
       </c>
       <c r="M105" t="s">
         <v>279</v>
@@ -7832,31 +7832,31 @@
         <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>458</v>
       </c>
       <c r="E106" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F106" t="s">
         <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H106" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="I106" t="s">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="J106" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K106" t="s">
         <v>277</v>
       </c>
       <c r="L106" t="s">
-        <v>278</v>
+        <v>459</v>
       </c>
       <c r="M106" t="s">
         <v>279</v>
@@ -7873,31 +7873,31 @@
         <v>15</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>462</v>
       </c>
       <c r="E107" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F107" t="s">
         <v>18</v>
       </c>
       <c r="G107" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H107" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="I107" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="J107" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K107" t="s">
         <v>277</v>
       </c>
       <c r="L107" t="s">
-        <v>278</v>
+        <v>463</v>
       </c>
       <c r="M107" t="s">
         <v>279</v>
@@ -7914,31 +7914,31 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>466</v>
       </c>
       <c r="E108" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F108" t="s">
         <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H108" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="I108" t="s">
-        <v>467</v>
+        <v>426</v>
       </c>
       <c r="J108" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K108" t="s">
         <v>277</v>
       </c>
       <c r="L108" t="s">
-        <v>278</v>
+        <v>467</v>
       </c>
       <c r="M108" t="s">
         <v>279</v>
@@ -7955,31 +7955,31 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>16</v>
+        <v>470</v>
       </c>
       <c r="E109" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F109" t="s">
         <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H109" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="I109" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="J109" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K109" t="s">
         <v>277</v>
       </c>
       <c r="L109" t="s">
-        <v>278</v>
+        <v>471</v>
       </c>
       <c r="M109" t="s">
         <v>279</v>
@@ -7996,31 +7996,31 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>474</v>
       </c>
       <c r="E110" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F110" t="s">
         <v>18</v>
       </c>
       <c r="G110" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H110" t="s">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="I110" t="s">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="J110" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K110" t="s">
         <v>277</v>
       </c>
       <c r="L110" t="s">
-        <v>278</v>
+        <v>475</v>
       </c>
       <c r="M110" t="s">
         <v>279</v>
@@ -8037,31 +8037,31 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>478</v>
       </c>
       <c r="E111" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F111" t="s">
         <v>18</v>
       </c>
       <c r="G111" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H111" t="s">
-        <v>478</v>
+        <v>425</v>
       </c>
       <c r="I111" t="s">
-        <v>479</v>
+        <v>426</v>
       </c>
       <c r="J111" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K111" t="s">
         <v>277</v>
       </c>
       <c r="L111" t="s">
-        <v>278</v>
+        <v>479</v>
       </c>
       <c r="M111" t="s">
         <v>279</v>
@@ -8078,31 +8078,31 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>482</v>
       </c>
       <c r="E112" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F112" t="s">
         <v>18</v>
       </c>
       <c r="G112" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H112" t="s">
-        <v>482</v>
+        <v>425</v>
       </c>
       <c r="I112" t="s">
-        <v>483</v>
+        <v>426</v>
       </c>
       <c r="J112" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K112" t="s">
         <v>277</v>
       </c>
       <c r="L112" t="s">
-        <v>278</v>
+        <v>483</v>
       </c>
       <c r="M112" t="s">
         <v>279</v>
@@ -8119,31 +8119,31 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>486</v>
       </c>
       <c r="E113" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F113" t="s">
         <v>18</v>
       </c>
       <c r="G113" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="H113" t="s">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="I113" t="s">
-        <v>487</v>
+        <v>426</v>
       </c>
       <c r="J113" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="K113" t="s">
         <v>277</v>
       </c>
       <c r="L113" t="s">
-        <v>278</v>
+        <v>487</v>
       </c>
       <c r="M113" t="s">
         <v>279</v>
@@ -8160,18 +8160,18 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E114" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F114" t="s">
         <v>18</v>
       </c>
-      <c r="H114" t="s">
-        <v>490</v>
-      </c>
-      <c r="I114" t="s">
+      <c r="G114" t="s">
+        <v>273</v>
+      </c>
+      <c r="J114" t="s">
         <v>491</v>
       </c>
       <c r="K114" t="s">
@@ -8195,25 +8195,25 @@
         <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>496</v>
       </c>
       <c r="E115" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F115" t="s">
         <v>18</v>
       </c>
-      <c r="H115" t="s">
-        <v>496</v>
-      </c>
-      <c r="I115" t="s">
-        <v>497</v>
+      <c r="G115" t="s">
+        <v>273</v>
+      </c>
+      <c r="J115" t="s">
+        <v>491</v>
       </c>
       <c r="K115" t="s">
         <v>492</v>
       </c>
       <c r="L115" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M115" t="s">
         <v>279</v>
@@ -8230,25 +8230,25 @@
         <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="E116" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F116" t="s">
         <v>18</v>
       </c>
-      <c r="H116" t="s">
-        <v>500</v>
-      </c>
-      <c r="I116" t="s">
-        <v>501</v>
+      <c r="G116" t="s">
+        <v>273</v>
+      </c>
+      <c r="J116" t="s">
+        <v>491</v>
       </c>
       <c r="K116" t="s">
         <v>492</v>
       </c>
       <c r="L116" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="M116" t="s">
         <v>279</v>
@@ -8265,25 +8265,25 @@
         <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="E117" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F117" t="s">
         <v>18</v>
       </c>
-      <c r="H117" t="s">
-        <v>504</v>
-      </c>
-      <c r="I117" t="s">
-        <v>505</v>
+      <c r="G117" t="s">
+        <v>273</v>
+      </c>
+      <c r="J117" t="s">
+        <v>491</v>
       </c>
       <c r="K117" t="s">
         <v>492</v>
       </c>
       <c r="L117" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="M117" t="s">
         <v>279</v>
@@ -8300,25 +8300,25 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E118" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F118" t="s">
         <v>18</v>
       </c>
-      <c r="H118" t="s">
-        <v>508</v>
-      </c>
-      <c r="I118" t="s">
-        <v>509</v>
+      <c r="G118" t="s">
+        <v>273</v>
+      </c>
+      <c r="J118" t="s">
+        <v>491</v>
       </c>
       <c r="K118" t="s">
         <v>492</v>
       </c>
       <c r="L118" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="M118" t="s">
         <v>279</v>
@@ -8335,15 +8335,15 @@
         <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>512</v>
+      </c>
+      <c r="E119" t="s">
+        <v>17</v>
       </c>
       <c r="F119" t="s">
         <v>18</v>
       </c>
-      <c r="H119" t="s">
-        <v>512</v>
-      </c>
-      <c r="I119" t="s">
+      <c r="L119" t="s">
         <v>513</v>
       </c>
     </row>
@@ -8358,18 +8358,18 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E120" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F120" t="s">
         <v>18</v>
       </c>
-      <c r="H120" t="s">
+      <c r="G120" t="s">
         <v>517</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>518</v>
       </c>
       <c r="K120" t="s">
@@ -8393,25 +8393,25 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>524</v>
       </c>
       <c r="E121" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F121" t="s">
         <v>18</v>
       </c>
-      <c r="H121" t="s">
-        <v>524</v>
-      </c>
-      <c r="I121" t="s">
-        <v>525</v>
+      <c r="G121" t="s">
+        <v>517</v>
+      </c>
+      <c r="J121" t="s">
+        <v>518</v>
       </c>
       <c r="K121" t="s">
         <v>519</v>
       </c>
       <c r="L121" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="M121" t="s">
         <v>521</v>
@@ -8428,25 +8428,25 @@
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>528</v>
       </c>
       <c r="E122" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F122" t="s">
         <v>18</v>
       </c>
-      <c r="H122" t="s">
-        <v>528</v>
-      </c>
-      <c r="I122" t="s">
-        <v>529</v>
+      <c r="G122" t="s">
+        <v>517</v>
+      </c>
+      <c r="J122" t="s">
+        <v>518</v>
       </c>
       <c r="K122" t="s">
         <v>519</v>
       </c>
       <c r="L122" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="M122" t="s">
         <v>521</v>
@@ -8463,25 +8463,25 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>532</v>
       </c>
       <c r="E123" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F123" t="s">
         <v>18</v>
       </c>
-      <c r="H123" t="s">
-        <v>532</v>
-      </c>
-      <c r="I123" t="s">
-        <v>533</v>
+      <c r="G123" t="s">
+        <v>517</v>
+      </c>
+      <c r="J123" t="s">
+        <v>518</v>
       </c>
       <c r="K123" t="s">
         <v>519</v>
       </c>
       <c r="L123" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="M123" t="s">
         <v>521</v>
@@ -8498,25 +8498,25 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>536</v>
       </c>
       <c r="E124" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F124" t="s">
         <v>18</v>
       </c>
-      <c r="H124" t="s">
-        <v>536</v>
-      </c>
-      <c r="I124" t="s">
-        <v>537</v>
+      <c r="G124" t="s">
+        <v>517</v>
+      </c>
+      <c r="J124" t="s">
+        <v>518</v>
       </c>
       <c r="K124" t="s">
         <v>519</v>
       </c>
       <c r="L124" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="M124" t="s">
         <v>521</v>
@@ -8533,18 +8533,18 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E125" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F125" t="s">
         <v>18</v>
       </c>
-      <c r="H125" t="s">
-        <v>540</v>
-      </c>
-      <c r="I125" t="s">
+      <c r="G125" t="s">
+        <v>517</v>
+      </c>
+      <c r="J125" t="s">
         <v>541</v>
       </c>
       <c r="K125" t="s">
@@ -8568,25 +8568,25 @@
         <v>15</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>546</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F126" t="s">
         <v>18</v>
       </c>
-      <c r="H126" t="s">
-        <v>546</v>
-      </c>
-      <c r="I126" t="s">
-        <v>547</v>
+      <c r="G126" t="s">
+        <v>517</v>
+      </c>
+      <c r="J126" t="s">
+        <v>541</v>
       </c>
       <c r="K126" t="s">
         <v>542</v>
       </c>
       <c r="L126" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M126" t="s">
         <v>521</v>
@@ -8603,25 +8603,25 @@
         <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>550</v>
       </c>
       <c r="E127" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F127" t="s">
         <v>18</v>
       </c>
-      <c r="H127" t="s">
-        <v>550</v>
-      </c>
-      <c r="I127" t="s">
-        <v>551</v>
+      <c r="G127" t="s">
+        <v>517</v>
+      </c>
+      <c r="J127" t="s">
+        <v>541</v>
       </c>
       <c r="K127" t="s">
         <v>542</v>
       </c>
       <c r="L127" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="M127" t="s">
         <v>521</v>
@@ -8638,25 +8638,25 @@
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>554</v>
       </c>
       <c r="E128" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F128" t="s">
         <v>18</v>
       </c>
-      <c r="H128" t="s">
-        <v>554</v>
-      </c>
-      <c r="I128" t="s">
-        <v>555</v>
+      <c r="G128" t="s">
+        <v>517</v>
+      </c>
+      <c r="J128" t="s">
+        <v>541</v>
       </c>
       <c r="K128" t="s">
         <v>542</v>
       </c>
       <c r="L128" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="M128" t="s">
         <v>521</v>
@@ -8673,25 +8673,25 @@
         <v>15</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>558</v>
       </c>
       <c r="E129" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F129" t="s">
         <v>18</v>
       </c>
-      <c r="H129" t="s">
-        <v>558</v>
-      </c>
-      <c r="I129" t="s">
-        <v>559</v>
+      <c r="G129" t="s">
+        <v>517</v>
+      </c>
+      <c r="J129" t="s">
+        <v>541</v>
       </c>
       <c r="K129" t="s">
         <v>542</v>
       </c>
       <c r="L129" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="M129" t="s">
         <v>521</v>
@@ -8708,25 +8708,25 @@
         <v>15</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>562</v>
       </c>
       <c r="E130" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F130" t="s">
         <v>18</v>
       </c>
-      <c r="H130" t="s">
-        <v>562</v>
-      </c>
-      <c r="I130" t="s">
-        <v>563</v>
+      <c r="G130" t="s">
+        <v>517</v>
+      </c>
+      <c r="J130" t="s">
+        <v>541</v>
       </c>
       <c r="K130" t="s">
         <v>542</v>
       </c>
       <c r="L130" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="M130" t="s">
         <v>521</v>
@@ -8743,25 +8743,25 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>566</v>
       </c>
       <c r="E131" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F131" t="s">
         <v>18</v>
       </c>
-      <c r="H131" t="s">
-        <v>566</v>
-      </c>
-      <c r="I131" t="s">
-        <v>567</v>
+      <c r="G131" t="s">
+        <v>517</v>
+      </c>
+      <c r="J131" t="s">
+        <v>541</v>
       </c>
       <c r="K131" t="s">
         <v>542</v>
       </c>
       <c r="L131" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="M131" t="s">
         <v>521</v>
@@ -8778,18 +8778,18 @@
         <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E132" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F132" t="s">
         <v>18</v>
       </c>
-      <c r="H132" t="s">
-        <v>570</v>
-      </c>
-      <c r="I132" t="s">
+      <c r="G132" t="s">
+        <v>517</v>
+      </c>
+      <c r="J132" t="s">
         <v>571</v>
       </c>
       <c r="K132" t="s">
@@ -8813,25 +8813,25 @@
         <v>15</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>576</v>
       </c>
       <c r="E133" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F133" t="s">
         <v>18</v>
       </c>
-      <c r="H133" t="s">
-        <v>576</v>
-      </c>
-      <c r="I133" t="s">
-        <v>577</v>
+      <c r="G133" t="s">
+        <v>517</v>
+      </c>
+      <c r="J133" t="s">
+        <v>571</v>
       </c>
       <c r="K133" t="s">
         <v>572</v>
       </c>
       <c r="L133" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="M133" t="s">
         <v>521</v>
@@ -8848,25 +8848,25 @@
         <v>15</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>580</v>
       </c>
       <c r="E134" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F134" t="s">
         <v>18</v>
       </c>
-      <c r="H134" t="s">
-        <v>580</v>
-      </c>
-      <c r="I134" t="s">
-        <v>581</v>
+      <c r="G134" t="s">
+        <v>517</v>
+      </c>
+      <c r="J134" t="s">
+        <v>571</v>
       </c>
       <c r="K134" t="s">
         <v>572</v>
       </c>
       <c r="L134" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="M134" t="s">
         <v>521</v>
@@ -8883,25 +8883,25 @@
         <v>15</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>584</v>
       </c>
       <c r="E135" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F135" t="s">
         <v>18</v>
       </c>
-      <c r="H135" t="s">
-        <v>584</v>
-      </c>
-      <c r="I135" t="s">
-        <v>585</v>
+      <c r="G135" t="s">
+        <v>517</v>
+      </c>
+      <c r="J135" t="s">
+        <v>571</v>
       </c>
       <c r="K135" t="s">
         <v>572</v>
       </c>
       <c r="L135" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="M135" t="s">
         <v>521</v>
@@ -8918,25 +8918,25 @@
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>588</v>
       </c>
       <c r="E136" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F136" t="s">
         <v>18</v>
       </c>
-      <c r="H136" t="s">
-        <v>588</v>
-      </c>
-      <c r="I136" t="s">
-        <v>589</v>
+      <c r="G136" t="s">
+        <v>517</v>
+      </c>
+      <c r="J136" t="s">
+        <v>571</v>
       </c>
       <c r="K136" t="s">
         <v>572</v>
       </c>
       <c r="L136" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="M136" t="s">
         <v>521</v>
@@ -8953,25 +8953,25 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>592</v>
       </c>
       <c r="E137" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F137" t="s">
         <v>18</v>
       </c>
-      <c r="H137" t="s">
-        <v>592</v>
-      </c>
-      <c r="I137" t="s">
-        <v>593</v>
+      <c r="G137" t="s">
+        <v>517</v>
+      </c>
+      <c r="J137" t="s">
+        <v>571</v>
       </c>
       <c r="K137" t="s">
         <v>572</v>
       </c>
       <c r="L137" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="M137" t="s">
         <v>521</v>
@@ -8988,25 +8988,25 @@
         <v>15</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>596</v>
       </c>
       <c r="E138" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F138" t="s">
         <v>18</v>
       </c>
-      <c r="H138" t="s">
-        <v>596</v>
-      </c>
-      <c r="I138" t="s">
-        <v>597</v>
+      <c r="G138" t="s">
+        <v>517</v>
+      </c>
+      <c r="J138" t="s">
+        <v>571</v>
       </c>
       <c r="K138" t="s">
         <v>572</v>
       </c>
       <c r="L138" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="M138" t="s">
         <v>521</v>
@@ -9023,25 +9023,25 @@
         <v>15</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="E139" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F139" t="s">
         <v>18</v>
       </c>
-      <c r="H139" t="s">
-        <v>600</v>
-      </c>
-      <c r="I139" t="s">
-        <v>601</v>
+      <c r="G139" t="s">
+        <v>517</v>
+      </c>
+      <c r="J139" t="s">
+        <v>571</v>
       </c>
       <c r="K139" t="s">
         <v>572</v>
       </c>
       <c r="L139" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="M139" t="s">
         <v>521</v>
@@ -9058,25 +9058,25 @@
         <v>15</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="E140" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F140" t="s">
         <v>18</v>
       </c>
-      <c r="H140" t="s">
-        <v>604</v>
-      </c>
-      <c r="I140" t="s">
-        <v>605</v>
+      <c r="G140" t="s">
+        <v>517</v>
+      </c>
+      <c r="J140" t="s">
+        <v>571</v>
       </c>
       <c r="K140" t="s">
         <v>572</v>
       </c>
       <c r="L140" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="M140" t="s">
         <v>521</v>
@@ -9093,25 +9093,25 @@
         <v>15</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>608</v>
       </c>
       <c r="E141" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F141" t="s">
         <v>18</v>
       </c>
-      <c r="H141" t="s">
-        <v>608</v>
-      </c>
-      <c r="I141" t="s">
-        <v>609</v>
+      <c r="G141" t="s">
+        <v>517</v>
+      </c>
+      <c r="J141" t="s">
+        <v>571</v>
       </c>
       <c r="K141" t="s">
         <v>572</v>
       </c>
       <c r="L141" t="s">
-        <v>573</v>
+        <v>609</v>
       </c>
       <c r="M141" t="s">
         <v>521</v>
@@ -9128,25 +9128,25 @@
         <v>15</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>612</v>
       </c>
       <c r="E142" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F142" t="s">
         <v>18</v>
       </c>
-      <c r="H142" t="s">
-        <v>612</v>
-      </c>
-      <c r="I142" t="s">
-        <v>613</v>
+      <c r="G142" t="s">
+        <v>517</v>
+      </c>
+      <c r="J142" t="s">
+        <v>571</v>
       </c>
       <c r="K142" t="s">
         <v>572</v>
       </c>
       <c r="L142" t="s">
-        <v>573</v>
+        <v>613</v>
       </c>
       <c r="M142" t="s">
         <v>521</v>
@@ -9163,18 +9163,18 @@
         <v>15</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E143" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F143" t="s">
         <v>18</v>
       </c>
-      <c r="H143" t="s">
-        <v>616</v>
-      </c>
-      <c r="I143" t="s">
+      <c r="G143" t="s">
+        <v>517</v>
+      </c>
+      <c r="J143" t="s">
         <v>617</v>
       </c>
       <c r="K143" t="s">
@@ -9198,25 +9198,25 @@
         <v>15</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>622</v>
       </c>
       <c r="E144" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F144" t="s">
         <v>18</v>
       </c>
-      <c r="H144" t="s">
-        <v>622</v>
-      </c>
-      <c r="I144" t="s">
-        <v>623</v>
+      <c r="G144" t="s">
+        <v>517</v>
+      </c>
+      <c r="J144" t="s">
+        <v>617</v>
       </c>
       <c r="K144" t="s">
         <v>618</v>
       </c>
       <c r="L144" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="M144" t="s">
         <v>521</v>
@@ -9233,25 +9233,25 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="E145" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F145" t="s">
         <v>18</v>
       </c>
-      <c r="H145" t="s">
-        <v>626</v>
-      </c>
-      <c r="I145" t="s">
-        <v>627</v>
+      <c r="G145" t="s">
+        <v>517</v>
+      </c>
+      <c r="J145" t="s">
+        <v>617</v>
       </c>
       <c r="K145" t="s">
         <v>618</v>
       </c>
       <c r="L145" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="M145" t="s">
         <v>521</v>
@@ -9268,25 +9268,25 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>630</v>
       </c>
       <c r="E146" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F146" t="s">
         <v>18</v>
       </c>
-      <c r="H146" t="s">
-        <v>630</v>
-      </c>
-      <c r="I146" t="s">
-        <v>631</v>
+      <c r="G146" t="s">
+        <v>517</v>
+      </c>
+      <c r="J146" t="s">
+        <v>617</v>
       </c>
       <c r="K146" t="s">
         <v>618</v>
       </c>
       <c r="L146" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="M146" t="s">
         <v>521</v>
@@ -9303,25 +9303,25 @@
         <v>15</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>634</v>
       </c>
       <c r="E147" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F147" t="s">
         <v>18</v>
       </c>
-      <c r="H147" t="s">
-        <v>634</v>
-      </c>
-      <c r="I147" t="s">
-        <v>635</v>
+      <c r="G147" t="s">
+        <v>517</v>
+      </c>
+      <c r="J147" t="s">
+        <v>617</v>
       </c>
       <c r="K147" t="s">
         <v>618</v>
       </c>
       <c r="L147" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="M147" t="s">
         <v>521</v>
@@ -9338,25 +9338,25 @@
         <v>15</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
+        <v>638</v>
       </c>
       <c r="E148" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F148" t="s">
         <v>18</v>
       </c>
-      <c r="H148" t="s">
-        <v>638</v>
-      </c>
-      <c r="I148" t="s">
-        <v>639</v>
+      <c r="G148" t="s">
+        <v>517</v>
+      </c>
+      <c r="J148" t="s">
+        <v>617</v>
       </c>
       <c r="K148" t="s">
         <v>618</v>
       </c>
       <c r="L148" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="M148" t="s">
         <v>521</v>
@@ -9373,25 +9373,25 @@
         <v>15</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>642</v>
       </c>
       <c r="E149" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F149" t="s">
         <v>18</v>
       </c>
-      <c r="H149" t="s">
-        <v>642</v>
-      </c>
-      <c r="I149" t="s">
-        <v>643</v>
+      <c r="G149" t="s">
+        <v>517</v>
+      </c>
+      <c r="J149" t="s">
+        <v>617</v>
       </c>
       <c r="K149" t="s">
         <v>618</v>
       </c>
       <c r="L149" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="M149" t="s">
         <v>521</v>
@@ -9408,25 +9408,25 @@
         <v>15</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>646</v>
       </c>
       <c r="E150" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F150" t="s">
         <v>18</v>
       </c>
-      <c r="H150" t="s">
-        <v>646</v>
-      </c>
-      <c r="I150" t="s">
-        <v>647</v>
+      <c r="G150" t="s">
+        <v>517</v>
+      </c>
+      <c r="J150" t="s">
+        <v>617</v>
       </c>
       <c r="K150" t="s">
         <v>618</v>
       </c>
       <c r="L150" t="s">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="M150" t="s">
         <v>521</v>
@@ -9443,25 +9443,25 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>16</v>
+        <v>650</v>
       </c>
       <c r="E151" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F151" t="s">
         <v>18</v>
       </c>
-      <c r="H151" t="s">
-        <v>650</v>
-      </c>
-      <c r="I151" t="s">
-        <v>651</v>
+      <c r="G151" t="s">
+        <v>517</v>
+      </c>
+      <c r="J151" t="s">
+        <v>617</v>
       </c>
       <c r="K151" t="s">
         <v>618</v>
       </c>
       <c r="L151" t="s">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="M151" t="s">
         <v>521</v>
@@ -9478,18 +9478,18 @@
         <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E152" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F152" t="s">
         <v>18</v>
       </c>
-      <c r="H152" t="s">
-        <v>654</v>
-      </c>
-      <c r="I152" t="s">
+      <c r="G152" t="s">
+        <v>517</v>
+      </c>
+      <c r="J152" t="s">
         <v>655</v>
       </c>
       <c r="K152" t="s">
@@ -9513,25 +9513,25 @@
         <v>15</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>660</v>
       </c>
       <c r="E153" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F153" t="s">
         <v>18</v>
       </c>
-      <c r="H153" t="s">
-        <v>660</v>
-      </c>
-      <c r="I153" t="s">
-        <v>661</v>
+      <c r="G153" t="s">
+        <v>517</v>
+      </c>
+      <c r="J153" t="s">
+        <v>655</v>
       </c>
       <c r="K153" t="s">
         <v>656</v>
       </c>
       <c r="L153" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="M153" t="s">
         <v>521</v>
@@ -9548,25 +9548,25 @@
         <v>15</v>
       </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>664</v>
       </c>
       <c r="E154" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F154" t="s">
         <v>18</v>
       </c>
-      <c r="H154" t="s">
-        <v>664</v>
-      </c>
-      <c r="I154" t="s">
-        <v>665</v>
+      <c r="G154" t="s">
+        <v>517</v>
+      </c>
+      <c r="J154" t="s">
+        <v>655</v>
       </c>
       <c r="K154" t="s">
         <v>656</v>
       </c>
       <c r="L154" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="M154" t="s">
         <v>521</v>
@@ -9583,25 +9583,25 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>668</v>
       </c>
       <c r="E155" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F155" t="s">
         <v>18</v>
       </c>
-      <c r="H155" t="s">
-        <v>668</v>
-      </c>
-      <c r="I155" t="s">
-        <v>669</v>
+      <c r="G155" t="s">
+        <v>517</v>
+      </c>
+      <c r="J155" t="s">
+        <v>655</v>
       </c>
       <c r="K155" t="s">
         <v>656</v>
       </c>
       <c r="L155" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="M155" t="s">
         <v>521</v>
@@ -9618,25 +9618,25 @@
         <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>16</v>
+        <v>672</v>
       </c>
       <c r="E156" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F156" t="s">
         <v>18</v>
       </c>
-      <c r="H156" t="s">
-        <v>672</v>
-      </c>
-      <c r="I156" t="s">
-        <v>673</v>
+      <c r="G156" t="s">
+        <v>517</v>
+      </c>
+      <c r="J156" t="s">
+        <v>655</v>
       </c>
       <c r="K156" t="s">
         <v>656</v>
       </c>
       <c r="L156" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="M156" t="s">
         <v>521</v>
@@ -9653,25 +9653,25 @@
         <v>15</v>
       </c>
       <c r="D157" t="s">
-        <v>16</v>
+        <v>676</v>
       </c>
       <c r="E157" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F157" t="s">
         <v>18</v>
       </c>
-      <c r="H157" t="s">
-        <v>676</v>
-      </c>
-      <c r="I157" t="s">
-        <v>677</v>
+      <c r="G157" t="s">
+        <v>517</v>
+      </c>
+      <c r="J157" t="s">
+        <v>655</v>
       </c>
       <c r="K157" t="s">
         <v>656</v>
       </c>
       <c r="L157" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="M157" t="s">
         <v>521</v>
@@ -9688,25 +9688,25 @@
         <v>15</v>
       </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>680</v>
       </c>
       <c r="E158" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F158" t="s">
         <v>18</v>
       </c>
-      <c r="H158" t="s">
-        <v>680</v>
-      </c>
-      <c r="I158" t="s">
-        <v>681</v>
+      <c r="G158" t="s">
+        <v>517</v>
+      </c>
+      <c r="J158" t="s">
+        <v>655</v>
       </c>
       <c r="K158" t="s">
         <v>656</v>
       </c>
       <c r="L158" t="s">
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="M158" t="s">
         <v>521</v>
@@ -9723,25 +9723,25 @@
         <v>15</v>
       </c>
       <c r="D159" t="s">
-        <v>16</v>
+        <v>684</v>
       </c>
       <c r="E159" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F159" t="s">
         <v>18</v>
       </c>
-      <c r="H159" t="s">
-        <v>684</v>
-      </c>
-      <c r="I159" t="s">
-        <v>685</v>
+      <c r="G159" t="s">
+        <v>517</v>
+      </c>
+      <c r="J159" t="s">
+        <v>655</v>
       </c>
       <c r="K159" t="s">
         <v>656</v>
       </c>
       <c r="L159" t="s">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="M159" t="s">
         <v>521</v>
@@ -9758,25 +9758,25 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>688</v>
       </c>
       <c r="E160" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F160" t="s">
         <v>18</v>
       </c>
-      <c r="H160" t="s">
-        <v>688</v>
-      </c>
-      <c r="I160" t="s">
-        <v>689</v>
+      <c r="G160" t="s">
+        <v>517</v>
+      </c>
+      <c r="J160" t="s">
+        <v>655</v>
       </c>
       <c r="K160" t="s">
         <v>656</v>
       </c>
       <c r="L160" t="s">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="M160" t="s">
         <v>521</v>
@@ -9793,25 +9793,25 @@
         <v>15</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>692</v>
       </c>
       <c r="E161" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F161" t="s">
         <v>18</v>
       </c>
-      <c r="H161" t="s">
-        <v>692</v>
-      </c>
-      <c r="I161" t="s">
-        <v>693</v>
+      <c r="G161" t="s">
+        <v>517</v>
+      </c>
+      <c r="J161" t="s">
+        <v>655</v>
       </c>
       <c r="K161" t="s">
         <v>656</v>
       </c>
       <c r="L161" t="s">
-        <v>657</v>
+        <v>693</v>
       </c>
       <c r="M161" t="s">
         <v>521</v>
@@ -9828,25 +9828,25 @@
         <v>15</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>696</v>
       </c>
       <c r="E162" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F162" t="s">
         <v>18</v>
       </c>
-      <c r="H162" t="s">
-        <v>696</v>
-      </c>
-      <c r="I162" t="s">
-        <v>697</v>
+      <c r="G162" t="s">
+        <v>517</v>
+      </c>
+      <c r="J162" t="s">
+        <v>655</v>
       </c>
       <c r="K162" t="s">
         <v>656</v>
       </c>
       <c r="L162" t="s">
-        <v>657</v>
+        <v>697</v>
       </c>
       <c r="M162" t="s">
         <v>521</v>
@@ -9863,25 +9863,25 @@
         <v>15</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>700</v>
       </c>
       <c r="E163" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F163" t="s">
         <v>18</v>
       </c>
-      <c r="H163" t="s">
-        <v>700</v>
-      </c>
-      <c r="I163" t="s">
-        <v>701</v>
+      <c r="G163" t="s">
+        <v>517</v>
+      </c>
+      <c r="J163" t="s">
+        <v>655</v>
       </c>
       <c r="K163" t="s">
         <v>656</v>
       </c>
       <c r="L163" t="s">
-        <v>657</v>
+        <v>701</v>
       </c>
       <c r="M163" t="s">
         <v>521</v>
@@ -9898,25 +9898,25 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="E164" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F164" t="s">
         <v>18</v>
       </c>
-      <c r="H164" t="s">
-        <v>704</v>
-      </c>
-      <c r="I164" t="s">
-        <v>705</v>
+      <c r="G164" t="s">
+        <v>517</v>
+      </c>
+      <c r="J164" t="s">
+        <v>655</v>
       </c>
       <c r="K164" t="s">
         <v>656</v>
       </c>
       <c r="L164" t="s">
-        <v>657</v>
+        <v>705</v>
       </c>
       <c r="M164" t="s">
         <v>521</v>
@@ -9933,25 +9933,25 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>708</v>
       </c>
       <c r="E165" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F165" t="s">
         <v>18</v>
       </c>
-      <c r="H165" t="s">
-        <v>708</v>
-      </c>
-      <c r="I165" t="s">
-        <v>709</v>
+      <c r="G165" t="s">
+        <v>517</v>
+      </c>
+      <c r="J165" t="s">
+        <v>655</v>
       </c>
       <c r="K165" t="s">
         <v>656</v>
       </c>
       <c r="L165" t="s">
-        <v>657</v>
+        <v>709</v>
       </c>
       <c r="M165" t="s">
         <v>521</v>
@@ -9968,25 +9968,25 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>712</v>
       </c>
       <c r="E166" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F166" t="s">
         <v>18</v>
       </c>
-      <c r="H166" t="s">
-        <v>712</v>
-      </c>
-      <c r="I166" t="s">
-        <v>713</v>
+      <c r="G166" t="s">
+        <v>517</v>
+      </c>
+      <c r="J166" t="s">
+        <v>655</v>
       </c>
       <c r="K166" t="s">
         <v>656</v>
       </c>
       <c r="L166" t="s">
-        <v>657</v>
+        <v>713</v>
       </c>
       <c r="M166" t="s">
         <v>521</v>
@@ -10003,25 +10003,25 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>716</v>
       </c>
       <c r="E167" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F167" t="s">
         <v>18</v>
       </c>
-      <c r="H167" t="s">
-        <v>716</v>
-      </c>
-      <c r="I167" t="s">
-        <v>717</v>
+      <c r="G167" t="s">
+        <v>517</v>
+      </c>
+      <c r="J167" t="s">
+        <v>655</v>
       </c>
       <c r="K167" t="s">
         <v>656</v>
       </c>
       <c r="L167" t="s">
-        <v>657</v>
+        <v>717</v>
       </c>
       <c r="M167" t="s">
         <v>521</v>
@@ -10038,25 +10038,25 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>16</v>
+        <v>720</v>
       </c>
       <c r="E168" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F168" t="s">
         <v>18</v>
       </c>
-      <c r="H168" t="s">
-        <v>720</v>
-      </c>
-      <c r="I168" t="s">
-        <v>721</v>
+      <c r="G168" t="s">
+        <v>517</v>
+      </c>
+      <c r="J168" t="s">
+        <v>655</v>
       </c>
       <c r="K168" t="s">
         <v>656</v>
       </c>
       <c r="L168" t="s">
-        <v>657</v>
+        <v>721</v>
       </c>
       <c r="M168" t="s">
         <v>521</v>
@@ -10073,25 +10073,25 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>724</v>
       </c>
       <c r="E169" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="F169" t="s">
         <v>18</v>
       </c>
-      <c r="H169" t="s">
-        <v>724</v>
-      </c>
-      <c r="I169" t="s">
-        <v>725</v>
+      <c r="G169" t="s">
+        <v>517</v>
+      </c>
+      <c r="J169" t="s">
+        <v>655</v>
       </c>
       <c r="K169" t="s">
         <v>656</v>
       </c>
       <c r="L169" t="s">
-        <v>657</v>
+        <v>725</v>
       </c>
       <c r="M169" t="s">
         <v>521</v>
@@ -10108,18 +10108,18 @@
         <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E170" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F170" t="s">
         <v>18</v>
       </c>
-      <c r="H170" t="s">
+      <c r="G170" t="s">
         <v>729</v>
       </c>
-      <c r="I170" t="s">
+      <c r="J170" t="s">
         <v>730</v>
       </c>
       <c r="K170" t="s">
@@ -10143,25 +10143,25 @@
         <v>15</v>
       </c>
       <c r="D171" t="s">
-        <v>16</v>
+        <v>736</v>
       </c>
       <c r="E171" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F171" t="s">
         <v>18</v>
       </c>
-      <c r="H171" t="s">
-        <v>736</v>
-      </c>
-      <c r="I171" t="s">
-        <v>737</v>
+      <c r="G171" t="s">
+        <v>729</v>
+      </c>
+      <c r="J171" t="s">
+        <v>730</v>
       </c>
       <c r="K171" t="s">
         <v>731</v>
       </c>
       <c r="L171" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="M171" t="s">
         <v>733</v>
@@ -10178,25 +10178,25 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>16</v>
+        <v>740</v>
       </c>
       <c r="E172" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F172" t="s">
         <v>18</v>
       </c>
-      <c r="H172" t="s">
-        <v>740</v>
-      </c>
-      <c r="I172" t="s">
-        <v>741</v>
+      <c r="G172" t="s">
+        <v>729</v>
+      </c>
+      <c r="J172" t="s">
+        <v>730</v>
       </c>
       <c r="K172" t="s">
         <v>731</v>
       </c>
       <c r="L172" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="M172" t="s">
         <v>733</v>
@@ -10213,25 +10213,25 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>744</v>
       </c>
       <c r="E173" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F173" t="s">
         <v>18</v>
       </c>
-      <c r="H173" t="s">
-        <v>744</v>
-      </c>
-      <c r="I173" t="s">
-        <v>745</v>
+      <c r="G173" t="s">
+        <v>729</v>
+      </c>
+      <c r="J173" t="s">
+        <v>730</v>
       </c>
       <c r="K173" t="s">
         <v>731</v>
       </c>
       <c r="L173" t="s">
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="M173" t="s">
         <v>733</v>
@@ -10248,25 +10248,25 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>16</v>
+        <v>748</v>
       </c>
       <c r="E174" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F174" t="s">
         <v>18</v>
       </c>
-      <c r="H174" t="s">
-        <v>748</v>
-      </c>
-      <c r="I174" t="s">
-        <v>749</v>
+      <c r="G174" t="s">
+        <v>729</v>
+      </c>
+      <c r="J174" t="s">
+        <v>730</v>
       </c>
       <c r="K174" t="s">
         <v>731</v>
       </c>
       <c r="L174" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="M174" t="s">
         <v>733</v>
@@ -10283,25 +10283,25 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>752</v>
       </c>
       <c r="E175" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F175" t="s">
         <v>18</v>
       </c>
-      <c r="H175" t="s">
-        <v>752</v>
-      </c>
-      <c r="I175" t="s">
-        <v>753</v>
+      <c r="G175" t="s">
+        <v>729</v>
+      </c>
+      <c r="J175" t="s">
+        <v>730</v>
       </c>
       <c r="K175" t="s">
         <v>731</v>
       </c>
       <c r="L175" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="M175" t="s">
         <v>733</v>
@@ -10318,25 +10318,25 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>16</v>
+        <v>756</v>
       </c>
       <c r="E176" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F176" t="s">
         <v>18</v>
       </c>
-      <c r="H176" t="s">
-        <v>756</v>
-      </c>
-      <c r="I176" t="s">
-        <v>757</v>
+      <c r="G176" t="s">
+        <v>729</v>
+      </c>
+      <c r="J176" t="s">
+        <v>730</v>
       </c>
       <c r="K176" t="s">
         <v>731</v>
       </c>
       <c r="L176" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="M176" t="s">
         <v>733</v>
@@ -10353,25 +10353,25 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>760</v>
       </c>
       <c r="E177" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F177" t="s">
         <v>18</v>
       </c>
-      <c r="H177" t="s">
-        <v>760</v>
-      </c>
-      <c r="I177" t="s">
-        <v>761</v>
+      <c r="G177" t="s">
+        <v>729</v>
+      </c>
+      <c r="J177" t="s">
+        <v>730</v>
       </c>
       <c r="K177" t="s">
         <v>731</v>
       </c>
       <c r="L177" t="s">
-        <v>732</v>
+        <v>761</v>
       </c>
       <c r="M177" t="s">
         <v>733</v>
@@ -10388,25 +10388,25 @@
         <v>15</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="E178" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F178" t="s">
         <v>18</v>
       </c>
-      <c r="H178" t="s">
-        <v>764</v>
-      </c>
-      <c r="I178" t="s">
-        <v>765</v>
+      <c r="G178" t="s">
+        <v>729</v>
+      </c>
+      <c r="J178" t="s">
+        <v>730</v>
       </c>
       <c r="K178" t="s">
         <v>731</v>
       </c>
       <c r="L178" t="s">
-        <v>732</v>
+        <v>765</v>
       </c>
       <c r="M178" t="s">
         <v>733</v>
@@ -10423,25 +10423,25 @@
         <v>15</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
+        <v>768</v>
       </c>
       <c r="E179" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F179" t="s">
         <v>18</v>
       </c>
-      <c r="H179" t="s">
-        <v>768</v>
-      </c>
-      <c r="I179" t="s">
-        <v>769</v>
+      <c r="G179" t="s">
+        <v>729</v>
+      </c>
+      <c r="J179" t="s">
+        <v>730</v>
       </c>
       <c r="K179" t="s">
         <v>731</v>
       </c>
       <c r="L179" t="s">
-        <v>732</v>
+        <v>769</v>
       </c>
       <c r="M179" t="s">
         <v>733</v>
@@ -10458,18 +10458,18 @@
         <v>15</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E180" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F180" t="s">
         <v>18</v>
       </c>
-      <c r="H180" t="s">
-        <v>772</v>
-      </c>
-      <c r="I180" t="s">
+      <c r="G180" t="s">
+        <v>729</v>
+      </c>
+      <c r="J180" t="s">
         <v>773</v>
       </c>
       <c r="K180" t="s">
@@ -10493,16 +10493,16 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E181" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F181" t="s">
         <v>18</v>
       </c>
       <c r="G181" t="s">
-        <v>778</v>
+        <v>729</v>
       </c>
       <c r="H181" t="s">
         <v>779</v>
@@ -10511,13 +10511,13 @@
         <v>780</v>
       </c>
       <c r="J181" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="K181" t="s">
         <v>774</v>
       </c>
       <c r="L181" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="M181" t="s">
         <v>733</v>
@@ -10534,31 +10534,31 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
-        <v>16</v>
+        <v>784</v>
       </c>
       <c r="E182" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
       </c>
       <c r="G182" t="s">
-        <v>778</v>
+        <v>729</v>
       </c>
       <c r="H182" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="I182" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="J182" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="K182" t="s">
         <v>774</v>
       </c>
       <c r="L182" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="M182" t="s">
         <v>733</v>
@@ -10574,26 +10574,26 @@
       <c r="C183" t="s">
         <v>15</v>
       </c>
-      <c r="D183" t="s">
-        <v>16</v>
-      </c>
       <c r="E183" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F183" t="s">
         <v>18</v>
       </c>
       <c r="G183" t="s">
-        <v>778</v>
+        <v>729</v>
+      </c>
+      <c r="H183" t="s">
+        <v>779</v>
+      </c>
+      <c r="I183" t="s">
+        <v>780</v>
       </c>
       <c r="J183" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="K183" t="s">
         <v>774</v>
-      </c>
-      <c r="L183" t="s">
-        <v>775</v>
       </c>
       <c r="M183" t="s">
         <v>733</v>
@@ -10610,25 +10610,25 @@
         <v>15</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>790</v>
       </c>
       <c r="E184" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F184" t="s">
         <v>18</v>
       </c>
-      <c r="H184" t="s">
-        <v>790</v>
-      </c>
-      <c r="I184" t="s">
-        <v>791</v>
+      <c r="G184" t="s">
+        <v>729</v>
+      </c>
+      <c r="J184" t="s">
+        <v>773</v>
       </c>
       <c r="K184" t="s">
         <v>774</v>
       </c>
       <c r="L184" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="M184" t="s">
         <v>733</v>
@@ -10645,25 +10645,25 @@
         <v>15</v>
       </c>
       <c r="D185" t="s">
-        <v>16</v>
+        <v>794</v>
       </c>
       <c r="E185" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F185" t="s">
         <v>18</v>
       </c>
-      <c r="H185" t="s">
-        <v>794</v>
-      </c>
-      <c r="I185" t="s">
-        <v>795</v>
+      <c r="G185" t="s">
+        <v>729</v>
+      </c>
+      <c r="J185" t="s">
+        <v>773</v>
       </c>
       <c r="K185" t="s">
         <v>774</v>
       </c>
       <c r="L185" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="M185" t="s">
         <v>733</v>
@@ -10680,25 +10680,25 @@
         <v>15</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>798</v>
       </c>
       <c r="E186" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F186" t="s">
         <v>18</v>
       </c>
-      <c r="H186" t="s">
-        <v>798</v>
-      </c>
-      <c r="I186" t="s">
-        <v>799</v>
+      <c r="G186" t="s">
+        <v>729</v>
+      </c>
+      <c r="J186" t="s">
+        <v>773</v>
       </c>
       <c r="K186" t="s">
         <v>774</v>
       </c>
       <c r="L186" t="s">
-        <v>775</v>
+        <v>799</v>
       </c>
       <c r="M186" t="s">
         <v>733</v>
@@ -10715,25 +10715,25 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>802</v>
       </c>
       <c r="E187" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F187" t="s">
         <v>18</v>
       </c>
-      <c r="H187" t="s">
-        <v>802</v>
-      </c>
-      <c r="I187" t="s">
-        <v>803</v>
+      <c r="G187" t="s">
+        <v>729</v>
+      </c>
+      <c r="J187" t="s">
+        <v>773</v>
       </c>
       <c r="K187" t="s">
         <v>774</v>
       </c>
       <c r="L187" t="s">
-        <v>775</v>
+        <v>803</v>
       </c>
       <c r="M187" t="s">
         <v>733</v>
@@ -10750,25 +10750,25 @@
         <v>15</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
+        <v>806</v>
       </c>
       <c r="E188" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F188" t="s">
         <v>18</v>
       </c>
-      <c r="H188" t="s">
-        <v>806</v>
-      </c>
-      <c r="I188" t="s">
-        <v>807</v>
+      <c r="G188" t="s">
+        <v>729</v>
+      </c>
+      <c r="J188" t="s">
+        <v>773</v>
       </c>
       <c r="K188" t="s">
         <v>774</v>
       </c>
       <c r="L188" t="s">
-        <v>775</v>
+        <v>807</v>
       </c>
       <c r="M188" t="s">
         <v>733</v>
@@ -10785,25 +10785,25 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="E189" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F189" t="s">
         <v>18</v>
       </c>
-      <c r="H189" t="s">
-        <v>810</v>
-      </c>
-      <c r="I189" t="s">
-        <v>811</v>
+      <c r="G189" t="s">
+        <v>729</v>
+      </c>
+      <c r="J189" t="s">
+        <v>773</v>
       </c>
       <c r="K189" t="s">
         <v>774</v>
       </c>
       <c r="L189" t="s">
-        <v>775</v>
+        <v>811</v>
       </c>
       <c r="M189" t="s">
         <v>733</v>
@@ -10820,25 +10820,25 @@
         <v>15</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>814</v>
       </c>
       <c r="E190" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F190" t="s">
         <v>18</v>
       </c>
-      <c r="H190" t="s">
-        <v>814</v>
-      </c>
-      <c r="I190" t="s">
-        <v>815</v>
+      <c r="G190" t="s">
+        <v>729</v>
+      </c>
+      <c r="J190" t="s">
+        <v>773</v>
       </c>
       <c r="K190" t="s">
         <v>774</v>
       </c>
       <c r="L190" t="s">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="M190" t="s">
         <v>733</v>
@@ -10855,25 +10855,25 @@
         <v>15</v>
       </c>
       <c r="D191" t="s">
-        <v>16</v>
+        <v>818</v>
       </c>
       <c r="E191" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F191" t="s">
         <v>18</v>
       </c>
-      <c r="H191" t="s">
-        <v>818</v>
-      </c>
-      <c r="I191" t="s">
-        <v>819</v>
+      <c r="G191" t="s">
+        <v>729</v>
+      </c>
+      <c r="J191" t="s">
+        <v>773</v>
       </c>
       <c r="K191" t="s">
         <v>774</v>
       </c>
       <c r="L191" t="s">
-        <v>775</v>
+        <v>819</v>
       </c>
       <c r="M191" t="s">
         <v>733</v>
@@ -10890,25 +10890,25 @@
         <v>15</v>
       </c>
       <c r="D192" t="s">
-        <v>16</v>
+        <v>822</v>
       </c>
       <c r="E192" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F192" t="s">
         <v>18</v>
       </c>
-      <c r="H192" t="s">
-        <v>822</v>
-      </c>
-      <c r="I192" t="s">
-        <v>823</v>
+      <c r="G192" t="s">
+        <v>729</v>
+      </c>
+      <c r="J192" t="s">
+        <v>773</v>
       </c>
       <c r="K192" t="s">
         <v>774</v>
       </c>
       <c r="L192" t="s">
-        <v>775</v>
+        <v>823</v>
       </c>
       <c r="M192" t="s">
         <v>733</v>
@@ -10925,25 +10925,25 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>826</v>
       </c>
       <c r="E193" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F193" t="s">
         <v>18</v>
       </c>
-      <c r="H193" t="s">
-        <v>826</v>
-      </c>
-      <c r="I193" t="s">
-        <v>827</v>
+      <c r="G193" t="s">
+        <v>729</v>
+      </c>
+      <c r="J193" t="s">
+        <v>773</v>
       </c>
       <c r="K193" t="s">
         <v>774</v>
       </c>
       <c r="L193" t="s">
-        <v>775</v>
+        <v>827</v>
       </c>
       <c r="M193" t="s">
         <v>733</v>
@@ -10960,25 +10960,25 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>830</v>
       </c>
       <c r="E194" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F194" t="s">
         <v>18</v>
       </c>
-      <c r="H194" t="s">
-        <v>830</v>
-      </c>
-      <c r="I194" t="s">
-        <v>831</v>
+      <c r="G194" t="s">
+        <v>729</v>
+      </c>
+      <c r="J194" t="s">
+        <v>773</v>
       </c>
       <c r="K194" t="s">
         <v>774</v>
       </c>
       <c r="L194" t="s">
-        <v>775</v>
+        <v>831</v>
       </c>
       <c r="M194" t="s">
         <v>733</v>
@@ -10995,25 +10995,25 @@
         <v>15</v>
       </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>834</v>
       </c>
       <c r="E195" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F195" t="s">
         <v>18</v>
       </c>
-      <c r="H195" t="s">
-        <v>834</v>
-      </c>
-      <c r="I195" t="s">
-        <v>835</v>
+      <c r="G195" t="s">
+        <v>729</v>
+      </c>
+      <c r="J195" t="s">
+        <v>773</v>
       </c>
       <c r="K195" t="s">
         <v>774</v>
       </c>
       <c r="L195" t="s">
-        <v>775</v>
+        <v>835</v>
       </c>
       <c r="M195" t="s">
         <v>733</v>
@@ -11030,25 +11030,25 @@
         <v>15</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>838</v>
       </c>
       <c r="E196" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F196" t="s">
         <v>18</v>
       </c>
-      <c r="H196" t="s">
-        <v>838</v>
-      </c>
-      <c r="I196" t="s">
-        <v>839</v>
+      <c r="G196" t="s">
+        <v>729</v>
+      </c>
+      <c r="J196" t="s">
+        <v>773</v>
       </c>
       <c r="K196" t="s">
         <v>774</v>
       </c>
       <c r="L196" t="s">
-        <v>775</v>
+        <v>839</v>
       </c>
       <c r="M196" t="s">
         <v>733</v>
@@ -11065,18 +11065,18 @@
         <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E197" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F197" t="s">
         <v>18</v>
       </c>
-      <c r="H197" t="s">
-        <v>842</v>
-      </c>
-      <c r="I197" t="s">
+      <c r="G197" t="s">
+        <v>729</v>
+      </c>
+      <c r="J197" t="s">
         <v>843</v>
       </c>
       <c r="K197" t="s">
@@ -11100,25 +11100,25 @@
         <v>15</v>
       </c>
       <c r="D198" t="s">
-        <v>16</v>
+        <v>848</v>
       </c>
       <c r="E198" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F198" t="s">
         <v>18</v>
       </c>
-      <c r="H198" t="s">
-        <v>848</v>
-      </c>
-      <c r="I198" t="s">
-        <v>849</v>
+      <c r="G198" t="s">
+        <v>729</v>
+      </c>
+      <c r="J198" t="s">
+        <v>843</v>
       </c>
       <c r="K198" t="s">
         <v>844</v>
       </c>
       <c r="L198" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="M198" t="s">
         <v>733</v>
@@ -11135,25 +11135,25 @@
         <v>15</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>852</v>
       </c>
       <c r="E199" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F199" t="s">
         <v>18</v>
       </c>
-      <c r="H199" t="s">
-        <v>852</v>
-      </c>
-      <c r="I199" t="s">
-        <v>853</v>
+      <c r="G199" t="s">
+        <v>729</v>
+      </c>
+      <c r="J199" t="s">
+        <v>843</v>
       </c>
       <c r="K199" t="s">
         <v>844</v>
       </c>
       <c r="L199" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="M199" t="s">
         <v>733</v>
@@ -11170,25 +11170,25 @@
         <v>15</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
+        <v>856</v>
       </c>
       <c r="E200" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F200" t="s">
         <v>18</v>
       </c>
-      <c r="H200" t="s">
-        <v>856</v>
-      </c>
-      <c r="I200" t="s">
-        <v>857</v>
+      <c r="G200" t="s">
+        <v>729</v>
+      </c>
+      <c r="J200" t="s">
+        <v>843</v>
       </c>
       <c r="K200" t="s">
         <v>844</v>
       </c>
       <c r="L200" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="M200" t="s">
         <v>733</v>
@@ -11205,25 +11205,25 @@
         <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>860</v>
       </c>
       <c r="E201" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F201" t="s">
         <v>18</v>
       </c>
-      <c r="H201" t="s">
-        <v>860</v>
-      </c>
-      <c r="I201" t="s">
-        <v>861</v>
+      <c r="G201" t="s">
+        <v>729</v>
+      </c>
+      <c r="J201" t="s">
+        <v>843</v>
       </c>
       <c r="K201" t="s">
         <v>844</v>
       </c>
       <c r="L201" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
       <c r="M201" t="s">
         <v>733</v>
@@ -11240,25 +11240,25 @@
         <v>15</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
+        <v>864</v>
       </c>
       <c r="E202" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F202" t="s">
         <v>18</v>
       </c>
-      <c r="H202" t="s">
-        <v>864</v>
-      </c>
-      <c r="I202" t="s">
-        <v>865</v>
+      <c r="G202" t="s">
+        <v>729</v>
+      </c>
+      <c r="J202" t="s">
+        <v>843</v>
       </c>
       <c r="K202" t="s">
         <v>844</v>
       </c>
       <c r="L202" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="M202" t="s">
         <v>733</v>
@@ -11275,25 +11275,25 @@
         <v>15</v>
       </c>
       <c r="D203" t="s">
-        <v>16</v>
+        <v>868</v>
       </c>
       <c r="E203" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F203" t="s">
         <v>18</v>
       </c>
-      <c r="H203" t="s">
-        <v>868</v>
-      </c>
-      <c r="I203" t="s">
-        <v>869</v>
+      <c r="G203" t="s">
+        <v>729</v>
+      </c>
+      <c r="J203" t="s">
+        <v>843</v>
       </c>
       <c r="K203" t="s">
         <v>844</v>
       </c>
       <c r="L203" t="s">
-        <v>845</v>
+        <v>869</v>
       </c>
       <c r="M203" t="s">
         <v>733</v>
@@ -11310,25 +11310,25 @@
         <v>15</v>
       </c>
       <c r="D204" t="s">
-        <v>16</v>
+        <v>872</v>
       </c>
       <c r="E204" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F204" t="s">
         <v>18</v>
       </c>
-      <c r="H204" t="s">
-        <v>872</v>
-      </c>
-      <c r="I204" t="s">
-        <v>873</v>
+      <c r="G204" t="s">
+        <v>729</v>
+      </c>
+      <c r="J204" t="s">
+        <v>843</v>
       </c>
       <c r="K204" t="s">
         <v>844</v>
       </c>
       <c r="L204" t="s">
-        <v>845</v>
+        <v>873</v>
       </c>
       <c r="M204" t="s">
         <v>733</v>
@@ -11345,25 +11345,25 @@
         <v>15</v>
       </c>
       <c r="D205" t="s">
-        <v>16</v>
+        <v>876</v>
       </c>
       <c r="E205" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F205" t="s">
         <v>18</v>
       </c>
-      <c r="H205" t="s">
-        <v>876</v>
-      </c>
-      <c r="I205" t="s">
-        <v>877</v>
+      <c r="G205" t="s">
+        <v>729</v>
+      </c>
+      <c r="J205" t="s">
+        <v>843</v>
       </c>
       <c r="K205" t="s">
         <v>844</v>
       </c>
       <c r="L205" t="s">
-        <v>845</v>
+        <v>877</v>
       </c>
       <c r="M205" t="s">
         <v>733</v>
@@ -11380,25 +11380,25 @@
         <v>15</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="E206" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F206" t="s">
         <v>18</v>
       </c>
-      <c r="H206" t="s">
-        <v>880</v>
-      </c>
-      <c r="I206" t="s">
-        <v>881</v>
+      <c r="G206" t="s">
+        <v>729</v>
+      </c>
+      <c r="J206" t="s">
+        <v>843</v>
       </c>
       <c r="K206" t="s">
         <v>844</v>
       </c>
       <c r="L206" t="s">
-        <v>845</v>
+        <v>881</v>
       </c>
       <c r="M206" t="s">
         <v>733</v>
@@ -11415,25 +11415,25 @@
         <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>16</v>
+        <v>884</v>
       </c>
       <c r="E207" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F207" t="s">
         <v>18</v>
       </c>
-      <c r="H207" t="s">
-        <v>884</v>
-      </c>
-      <c r="I207" t="s">
-        <v>885</v>
+      <c r="G207" t="s">
+        <v>729</v>
+      </c>
+      <c r="J207" t="s">
+        <v>843</v>
       </c>
       <c r="K207" t="s">
         <v>844</v>
       </c>
       <c r="L207" t="s">
-        <v>845</v>
+        <v>885</v>
       </c>
       <c r="M207" t="s">
         <v>733</v>
@@ -11450,25 +11450,25 @@
         <v>15</v>
       </c>
       <c r="D208" t="s">
-        <v>16</v>
+        <v>888</v>
       </c>
       <c r="E208" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F208" t="s">
         <v>18</v>
       </c>
-      <c r="H208" t="s">
-        <v>888</v>
-      </c>
-      <c r="I208" t="s">
-        <v>889</v>
+      <c r="G208" t="s">
+        <v>729</v>
+      </c>
+      <c r="J208" t="s">
+        <v>843</v>
       </c>
       <c r="K208" t="s">
         <v>844</v>
       </c>
       <c r="L208" t="s">
-        <v>845</v>
+        <v>889</v>
       </c>
       <c r="M208" t="s">
         <v>733</v>
@@ -11485,25 +11485,25 @@
         <v>15</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
+        <v>892</v>
       </c>
       <c r="E209" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F209" t="s">
         <v>18</v>
       </c>
-      <c r="H209" t="s">
-        <v>892</v>
-      </c>
-      <c r="I209" t="s">
-        <v>893</v>
+      <c r="G209" t="s">
+        <v>729</v>
+      </c>
+      <c r="J209" t="s">
+        <v>843</v>
       </c>
       <c r="K209" t="s">
         <v>844</v>
       </c>
       <c r="L209" t="s">
-        <v>845</v>
+        <v>893</v>
       </c>
       <c r="M209" t="s">
         <v>733</v>
@@ -11520,25 +11520,25 @@
         <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>16</v>
+        <v>896</v>
       </c>
       <c r="E210" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F210" t="s">
         <v>18</v>
       </c>
-      <c r="H210" t="s">
-        <v>896</v>
-      </c>
-      <c r="I210" t="s">
-        <v>897</v>
+      <c r="G210" t="s">
+        <v>729</v>
+      </c>
+      <c r="J210" t="s">
+        <v>843</v>
       </c>
       <c r="K210" t="s">
         <v>844</v>
       </c>
       <c r="L210" t="s">
-        <v>845</v>
+        <v>897</v>
       </c>
       <c r="M210" t="s">
         <v>733</v>
@@ -11555,25 +11555,25 @@
         <v>15</v>
       </c>
       <c r="D211" t="s">
-        <v>16</v>
+        <v>900</v>
       </c>
       <c r="E211" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F211" t="s">
         <v>18</v>
       </c>
-      <c r="H211" t="s">
-        <v>900</v>
-      </c>
-      <c r="I211" t="s">
-        <v>901</v>
+      <c r="G211" t="s">
+        <v>729</v>
+      </c>
+      <c r="J211" t="s">
+        <v>843</v>
       </c>
       <c r="K211" t="s">
         <v>844</v>
       </c>
       <c r="L211" t="s">
-        <v>845</v>
+        <v>901</v>
       </c>
       <c r="M211" t="s">
         <v>733</v>
@@ -11590,25 +11590,25 @@
         <v>15</v>
       </c>
       <c r="D212" t="s">
-        <v>16</v>
+        <v>904</v>
       </c>
       <c r="E212" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F212" t="s">
         <v>18</v>
       </c>
-      <c r="H212" t="s">
-        <v>904</v>
-      </c>
-      <c r="I212" t="s">
-        <v>905</v>
+      <c r="G212" t="s">
+        <v>729</v>
+      </c>
+      <c r="J212" t="s">
+        <v>843</v>
       </c>
       <c r="K212" t="s">
         <v>844</v>
       </c>
       <c r="L212" t="s">
-        <v>845</v>
+        <v>905</v>
       </c>
       <c r="M212" t="s">
         <v>733</v>
@@ -11625,18 +11625,18 @@
         <v>15</v>
       </c>
       <c r="D213" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E213" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F213" t="s">
         <v>18</v>
       </c>
-      <c r="H213" t="s">
-        <v>908</v>
-      </c>
-      <c r="I213" t="s">
+      <c r="G213" t="s">
+        <v>729</v>
+      </c>
+      <c r="J213" t="s">
         <v>909</v>
       </c>
       <c r="K213" t="s">
@@ -11660,25 +11660,25 @@
         <v>15</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>914</v>
       </c>
       <c r="E214" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F214" t="s">
         <v>18</v>
       </c>
-      <c r="H214" t="s">
-        <v>914</v>
-      </c>
-      <c r="I214" t="s">
-        <v>915</v>
+      <c r="G214" t="s">
+        <v>729</v>
+      </c>
+      <c r="J214" t="s">
+        <v>909</v>
       </c>
       <c r="K214" t="s">
         <v>910</v>
       </c>
       <c r="L214" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="M214" t="s">
         <v>733</v>
@@ -11695,25 +11695,25 @@
         <v>15</v>
       </c>
       <c r="D215" t="s">
-        <v>16</v>
+        <v>918</v>
       </c>
       <c r="E215" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F215" t="s">
         <v>18</v>
       </c>
-      <c r="H215" t="s">
-        <v>918</v>
-      </c>
-      <c r="I215" t="s">
-        <v>919</v>
+      <c r="G215" t="s">
+        <v>729</v>
+      </c>
+      <c r="J215" t="s">
+        <v>909</v>
       </c>
       <c r="K215" t="s">
         <v>910</v>
       </c>
       <c r="L215" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="M215" t="s">
         <v>733</v>
@@ -11730,25 +11730,25 @@
         <v>15</v>
       </c>
       <c r="D216" t="s">
-        <v>16</v>
+        <v>922</v>
       </c>
       <c r="E216" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F216" t="s">
         <v>18</v>
       </c>
-      <c r="H216" t="s">
-        <v>922</v>
-      </c>
-      <c r="I216" t="s">
-        <v>923</v>
+      <c r="G216" t="s">
+        <v>729</v>
+      </c>
+      <c r="J216" t="s">
+        <v>909</v>
       </c>
       <c r="K216" t="s">
         <v>910</v>
       </c>
       <c r="L216" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="M216" t="s">
         <v>733</v>
@@ -11765,25 +11765,25 @@
         <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
+        <v>926</v>
       </c>
       <c r="E217" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F217" t="s">
         <v>18</v>
       </c>
-      <c r="H217" t="s">
-        <v>926</v>
-      </c>
-      <c r="I217" t="s">
-        <v>927</v>
+      <c r="G217" t="s">
+        <v>729</v>
+      </c>
+      <c r="J217" t="s">
+        <v>909</v>
       </c>
       <c r="K217" t="s">
         <v>910</v>
       </c>
       <c r="L217" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="M217" t="s">
         <v>733</v>
@@ -11800,25 +11800,25 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>930</v>
       </c>
       <c r="E218" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F218" t="s">
         <v>18</v>
       </c>
-      <c r="H218" t="s">
-        <v>930</v>
-      </c>
-      <c r="I218" t="s">
-        <v>931</v>
+      <c r="G218" t="s">
+        <v>729</v>
+      </c>
+      <c r="J218" t="s">
+        <v>909</v>
       </c>
       <c r="K218" t="s">
         <v>910</v>
       </c>
       <c r="L218" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="M218" t="s">
         <v>733</v>
@@ -11835,25 +11835,25 @@
         <v>15</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>934</v>
       </c>
       <c r="E219" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F219" t="s">
         <v>18</v>
       </c>
-      <c r="H219" t="s">
-        <v>934</v>
-      </c>
-      <c r="I219" t="s">
-        <v>935</v>
+      <c r="G219" t="s">
+        <v>729</v>
+      </c>
+      <c r="J219" t="s">
+        <v>909</v>
       </c>
       <c r="K219" t="s">
         <v>910</v>
       </c>
       <c r="L219" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="M219" t="s">
         <v>733</v>
@@ -11870,25 +11870,25 @@
         <v>15</v>
       </c>
       <c r="D220" t="s">
-        <v>16</v>
+        <v>938</v>
       </c>
       <c r="E220" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F220" t="s">
         <v>18</v>
       </c>
-      <c r="H220" t="s">
-        <v>938</v>
-      </c>
-      <c r="I220" t="s">
-        <v>939</v>
+      <c r="G220" t="s">
+        <v>729</v>
+      </c>
+      <c r="J220" t="s">
+        <v>909</v>
       </c>
       <c r="K220" t="s">
         <v>910</v>
       </c>
       <c r="L220" t="s">
-        <v>911</v>
+        <v>939</v>
       </c>
       <c r="M220" t="s">
         <v>733</v>
@@ -11905,25 +11905,25 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>942</v>
       </c>
       <c r="E221" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
       <c r="F221" t="s">
         <v>18</v>
       </c>
-      <c r="H221" t="s">
-        <v>942</v>
-      </c>
-      <c r="I221" t="s">
-        <v>943</v>
+      <c r="G221" t="s">
+        <v>729</v>
+      </c>
+      <c r="J221" t="s">
+        <v>909</v>
       </c>
       <c r="K221" t="s">
         <v>910</v>
       </c>
       <c r="L221" t="s">
-        <v>911</v>
+        <v>943</v>
       </c>
       <c r="M221" t="s">
         <v>733</v>
@@ -11940,18 +11940,18 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E222" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F222" t="s">
         <v>18</v>
       </c>
-      <c r="H222" t="s">
+      <c r="G222" t="s">
         <v>947</v>
       </c>
-      <c r="I222" t="s">
+      <c r="J222" t="s">
         <v>948</v>
       </c>
       <c r="K222" t="s">
@@ -11975,25 +11975,25 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
-        <v>16</v>
+        <v>954</v>
       </c>
       <c r="E223" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F223" t="s">
         <v>18</v>
       </c>
-      <c r="H223" t="s">
-        <v>954</v>
-      </c>
-      <c r="I223" t="s">
-        <v>955</v>
+      <c r="G223" t="s">
+        <v>947</v>
+      </c>
+      <c r="J223" t="s">
+        <v>948</v>
       </c>
       <c r="K223" t="s">
         <v>949</v>
       </c>
       <c r="L223" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="M223" t="s">
         <v>951</v>
@@ -12010,25 +12010,25 @@
         <v>15</v>
       </c>
       <c r="D224" t="s">
-        <v>16</v>
+        <v>958</v>
       </c>
       <c r="E224" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F224" t="s">
         <v>18</v>
       </c>
-      <c r="H224" t="s">
-        <v>958</v>
-      </c>
-      <c r="I224" t="s">
-        <v>959</v>
+      <c r="G224" t="s">
+        <v>947</v>
+      </c>
+      <c r="J224" t="s">
+        <v>948</v>
       </c>
       <c r="K224" t="s">
         <v>949</v>
       </c>
       <c r="L224" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="M224" t="s">
         <v>951</v>
@@ -12045,25 +12045,25 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>16</v>
+        <v>962</v>
       </c>
       <c r="E225" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F225" t="s">
         <v>18</v>
       </c>
-      <c r="H225" t="s">
-        <v>962</v>
-      </c>
-      <c r="I225" t="s">
-        <v>963</v>
+      <c r="G225" t="s">
+        <v>947</v>
+      </c>
+      <c r="J225" t="s">
+        <v>948</v>
       </c>
       <c r="K225" t="s">
         <v>949</v>
       </c>
       <c r="L225" t="s">
-        <v>950</v>
+        <v>963</v>
       </c>
       <c r="M225" t="s">
         <v>951</v>
@@ -12080,25 +12080,25 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>966</v>
       </c>
       <c r="E226" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F226" t="s">
         <v>18</v>
       </c>
-      <c r="H226" t="s">
-        <v>966</v>
-      </c>
-      <c r="I226" t="s">
-        <v>967</v>
+      <c r="G226" t="s">
+        <v>947</v>
+      </c>
+      <c r="J226" t="s">
+        <v>948</v>
       </c>
       <c r="K226" t="s">
         <v>949</v>
       </c>
       <c r="L226" t="s">
-        <v>950</v>
+        <v>967</v>
       </c>
       <c r="M226" t="s">
         <v>951</v>
@@ -12115,25 +12115,25 @@
         <v>15</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="E227" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F227" t="s">
         <v>18</v>
       </c>
-      <c r="H227" t="s">
-        <v>970</v>
-      </c>
-      <c r="I227" t="s">
-        <v>971</v>
+      <c r="G227" t="s">
+        <v>947</v>
+      </c>
+      <c r="J227" t="s">
+        <v>948</v>
       </c>
       <c r="K227" t="s">
         <v>949</v>
       </c>
       <c r="L227" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="M227" t="s">
         <v>951</v>
@@ -12150,18 +12150,18 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E228" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F228" t="s">
         <v>18</v>
       </c>
-      <c r="H228" t="s">
-        <v>974</v>
-      </c>
-      <c r="I228" t="s">
+      <c r="G228" t="s">
+        <v>947</v>
+      </c>
+      <c r="J228" t="s">
         <v>975</v>
       </c>
       <c r="K228" t="s">
@@ -12185,25 +12185,25 @@
         <v>15</v>
       </c>
       <c r="D229" t="s">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="E229" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F229" t="s">
         <v>18</v>
       </c>
-      <c r="H229" t="s">
-        <v>980</v>
-      </c>
-      <c r="I229" t="s">
-        <v>981</v>
+      <c r="G229" t="s">
+        <v>947</v>
+      </c>
+      <c r="J229" t="s">
+        <v>975</v>
       </c>
       <c r="K229" t="s">
         <v>976</v>
       </c>
       <c r="L229" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="M229" t="s">
         <v>951</v>
@@ -12220,25 +12220,25 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>984</v>
       </c>
       <c r="E230" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F230" t="s">
         <v>18</v>
       </c>
-      <c r="H230" t="s">
-        <v>984</v>
-      </c>
-      <c r="I230" t="s">
-        <v>985</v>
+      <c r="G230" t="s">
+        <v>947</v>
+      </c>
+      <c r="J230" t="s">
+        <v>975</v>
       </c>
       <c r="K230" t="s">
         <v>976</v>
       </c>
       <c r="L230" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="M230" t="s">
         <v>951</v>
@@ -12255,25 +12255,25 @@
         <v>15</v>
       </c>
       <c r="D231" t="s">
-        <v>16</v>
+        <v>988</v>
       </c>
       <c r="E231" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F231" t="s">
         <v>18</v>
       </c>
-      <c r="H231" t="s">
-        <v>988</v>
-      </c>
-      <c r="I231" t="s">
-        <v>989</v>
+      <c r="G231" t="s">
+        <v>947</v>
+      </c>
+      <c r="J231" t="s">
+        <v>975</v>
       </c>
       <c r="K231" t="s">
         <v>976</v>
       </c>
       <c r="L231" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="M231" t="s">
         <v>951</v>
@@ -12290,25 +12290,25 @@
         <v>15</v>
       </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>992</v>
       </c>
       <c r="E232" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F232" t="s">
         <v>18</v>
       </c>
-      <c r="H232" t="s">
-        <v>992</v>
-      </c>
-      <c r="I232" t="s">
-        <v>993</v>
+      <c r="G232" t="s">
+        <v>947</v>
+      </c>
+      <c r="J232" t="s">
+        <v>975</v>
       </c>
       <c r="K232" t="s">
         <v>976</v>
       </c>
       <c r="L232" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="M232" t="s">
         <v>951</v>
@@ -12325,18 +12325,18 @@
         <v>15</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E233" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F233" t="s">
         <v>18</v>
       </c>
-      <c r="H233" t="s">
-        <v>996</v>
-      </c>
-      <c r="I233" t="s">
+      <c r="G233" t="s">
+        <v>947</v>
+      </c>
+      <c r="J233" t="s">
         <v>997</v>
       </c>
       <c r="K233" t="s">
@@ -12360,25 +12360,25 @@
         <v>15</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
+        <v>1002</v>
       </c>
       <c r="E234" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F234" t="s">
         <v>18</v>
       </c>
-      <c r="H234" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I234" t="s">
-        <v>1003</v>
+      <c r="G234" t="s">
+        <v>947</v>
+      </c>
+      <c r="J234" t="s">
+        <v>997</v>
       </c>
       <c r="K234" t="s">
         <v>998</v>
       </c>
       <c r="L234" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="M234" t="s">
         <v>951</v>
@@ -12395,25 +12395,25 @@
         <v>15</v>
       </c>
       <c r="D235" t="s">
-        <v>16</v>
+        <v>1006</v>
       </c>
       <c r="E235" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F235" t="s">
         <v>18</v>
       </c>
-      <c r="H235" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I235" t="s">
-        <v>1007</v>
+      <c r="G235" t="s">
+        <v>947</v>
+      </c>
+      <c r="J235" t="s">
+        <v>997</v>
       </c>
       <c r="K235" t="s">
         <v>998</v>
       </c>
       <c r="L235" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="M235" t="s">
         <v>951</v>
@@ -12430,25 +12430,25 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>1010</v>
       </c>
       <c r="E236" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F236" t="s">
         <v>18</v>
       </c>
-      <c r="H236" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I236" t="s">
-        <v>1011</v>
+      <c r="G236" t="s">
+        <v>947</v>
+      </c>
+      <c r="J236" t="s">
+        <v>997</v>
       </c>
       <c r="K236" t="s">
         <v>998</v>
       </c>
       <c r="L236" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="M236" t="s">
         <v>951</v>
@@ -12465,25 +12465,25 @@
         <v>15</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>1014</v>
       </c>
       <c r="E237" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F237" t="s">
         <v>18</v>
       </c>
-      <c r="H237" t="s">
-        <v>1014</v>
-      </c>
-      <c r="I237" t="s">
-        <v>1015</v>
+      <c r="G237" t="s">
+        <v>947</v>
+      </c>
+      <c r="J237" t="s">
+        <v>997</v>
       </c>
       <c r="K237" t="s">
         <v>998</v>
       </c>
       <c r="L237" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="M237" t="s">
         <v>951</v>
@@ -12500,25 +12500,25 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>16</v>
+        <v>1018</v>
       </c>
       <c r="E238" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F238" t="s">
         <v>18</v>
       </c>
-      <c r="H238" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I238" t="s">
-        <v>1019</v>
+      <c r="G238" t="s">
+        <v>947</v>
+      </c>
+      <c r="J238" t="s">
+        <v>997</v>
       </c>
       <c r="K238" t="s">
         <v>998</v>
       </c>
       <c r="L238" t="s">
-        <v>999</v>
+        <v>1019</v>
       </c>
       <c r="M238" t="s">
         <v>951</v>
@@ -12535,25 +12535,25 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>16</v>
+        <v>1022</v>
       </c>
       <c r="E239" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F239" t="s">
         <v>18</v>
       </c>
-      <c r="H239" t="s">
-        <v>1022</v>
-      </c>
-      <c r="I239" t="s">
-        <v>1023</v>
+      <c r="G239" t="s">
+        <v>947</v>
+      </c>
+      <c r="J239" t="s">
+        <v>997</v>
       </c>
       <c r="K239" t="s">
         <v>998</v>
       </c>
       <c r="L239" t="s">
-        <v>999</v>
+        <v>1023</v>
       </c>
       <c r="M239" t="s">
         <v>951</v>
@@ -12570,25 +12570,25 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>16</v>
+        <v>1026</v>
       </c>
       <c r="E240" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F240" t="s">
         <v>18</v>
       </c>
-      <c r="H240" t="s">
-        <v>1026</v>
-      </c>
-      <c r="I240" t="s">
-        <v>1027</v>
+      <c r="G240" t="s">
+        <v>947</v>
+      </c>
+      <c r="J240" t="s">
+        <v>997</v>
       </c>
       <c r="K240" t="s">
         <v>998</v>
       </c>
       <c r="L240" t="s">
-        <v>999</v>
+        <v>1027</v>
       </c>
       <c r="M240" t="s">
         <v>951</v>
@@ -12605,18 +12605,18 @@
         <v>15</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E241" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F241" t="s">
         <v>18</v>
       </c>
-      <c r="H241" t="s">
-        <v>1030</v>
-      </c>
-      <c r="I241" t="s">
+      <c r="G241" t="s">
+        <v>947</v>
+      </c>
+      <c r="J241" t="s">
         <v>1031</v>
       </c>
       <c r="K241" t="s">
@@ -12640,25 +12640,25 @@
         <v>15</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>1036</v>
       </c>
       <c r="E242" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F242" t="s">
         <v>18</v>
       </c>
-      <c r="H242" t="s">
-        <v>1036</v>
-      </c>
-      <c r="I242" t="s">
-        <v>1037</v>
+      <c r="G242" t="s">
+        <v>947</v>
+      </c>
+      <c r="J242" t="s">
+        <v>1031</v>
       </c>
       <c r="K242" t="s">
         <v>1032</v>
       </c>
       <c r="L242" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="M242" t="s">
         <v>951</v>
@@ -12675,25 +12675,25 @@
         <v>15</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
+        <v>1040</v>
       </c>
       <c r="E243" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F243" t="s">
         <v>18</v>
       </c>
-      <c r="H243" t="s">
-        <v>1040</v>
-      </c>
-      <c r="I243" t="s">
-        <v>1041</v>
+      <c r="G243" t="s">
+        <v>947</v>
+      </c>
+      <c r="J243" t="s">
+        <v>1031</v>
       </c>
       <c r="K243" t="s">
         <v>1032</v>
       </c>
       <c r="L243" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="M243" t="s">
         <v>951</v>
@@ -12710,25 +12710,25 @@
         <v>15</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
+        <v>1044</v>
       </c>
       <c r="E244" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F244" t="s">
         <v>18</v>
       </c>
-      <c r="H244" t="s">
-        <v>1044</v>
-      </c>
-      <c r="I244" t="s">
-        <v>1045</v>
+      <c r="G244" t="s">
+        <v>947</v>
+      </c>
+      <c r="J244" t="s">
+        <v>1031</v>
       </c>
       <c r="K244" t="s">
         <v>1032</v>
       </c>
       <c r="L244" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="M244" t="s">
         <v>951</v>
@@ -12745,25 +12745,25 @@
         <v>15</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>1048</v>
       </c>
       <c r="E245" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F245" t="s">
         <v>18</v>
       </c>
-      <c r="H245" t="s">
-        <v>1048</v>
-      </c>
-      <c r="I245" t="s">
-        <v>1049</v>
+      <c r="G245" t="s">
+        <v>947</v>
+      </c>
+      <c r="J245" t="s">
+        <v>1031</v>
       </c>
       <c r="K245" t="s">
         <v>1032</v>
       </c>
       <c r="L245" t="s">
-        <v>1033</v>
+        <v>1049</v>
       </c>
       <c r="M245" t="s">
         <v>951</v>
@@ -12780,25 +12780,25 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>1052</v>
       </c>
       <c r="E246" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F246" t="s">
         <v>18</v>
       </c>
-      <c r="H246" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I246" t="s">
-        <v>1053</v>
+      <c r="G246" t="s">
+        <v>947</v>
+      </c>
+      <c r="J246" t="s">
+        <v>1031</v>
       </c>
       <c r="K246" t="s">
         <v>1032</v>
       </c>
       <c r="L246" t="s">
-        <v>1033</v>
+        <v>1053</v>
       </c>
       <c r="M246" t="s">
         <v>951</v>
@@ -12815,25 +12815,25 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>1056</v>
       </c>
       <c r="E247" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F247" t="s">
         <v>18</v>
       </c>
-      <c r="H247" t="s">
-        <v>1056</v>
-      </c>
-      <c r="I247" t="s">
-        <v>1057</v>
+      <c r="G247" t="s">
+        <v>947</v>
+      </c>
+      <c r="J247" t="s">
+        <v>1031</v>
       </c>
       <c r="K247" t="s">
         <v>1032</v>
       </c>
       <c r="L247" t="s">
-        <v>1033</v>
+        <v>1057</v>
       </c>
       <c r="M247" t="s">
         <v>951</v>
@@ -12850,25 +12850,25 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>1060</v>
       </c>
       <c r="E248" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F248" t="s">
         <v>18</v>
       </c>
-      <c r="H248" t="s">
-        <v>1060</v>
-      </c>
-      <c r="I248" t="s">
-        <v>1061</v>
+      <c r="G248" t="s">
+        <v>947</v>
+      </c>
+      <c r="J248" t="s">
+        <v>1031</v>
       </c>
       <c r="K248" t="s">
         <v>1032</v>
       </c>
       <c r="L248" t="s">
-        <v>1033</v>
+        <v>1061</v>
       </c>
       <c r="M248" t="s">
         <v>951</v>
@@ -12885,25 +12885,25 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>1064</v>
       </c>
       <c r="E249" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
       </c>
-      <c r="H249" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I249" t="s">
-        <v>1065</v>
+      <c r="G249" t="s">
+        <v>947</v>
+      </c>
+      <c r="J249" t="s">
+        <v>1031</v>
       </c>
       <c r="K249" t="s">
         <v>1032</v>
       </c>
       <c r="L249" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="M249" t="s">
         <v>951</v>
@@ -12920,25 +12920,25 @@
         <v>15</v>
       </c>
       <c r="D250" t="s">
-        <v>16</v>
+        <v>1068</v>
       </c>
       <c r="E250" t="s">
-        <v>946</v>
+        <v>17</v>
       </c>
       <c r="F250" t="s">
         <v>18</v>
       </c>
-      <c r="H250" t="s">
-        <v>1068</v>
-      </c>
-      <c r="I250" t="s">
-        <v>1069</v>
+      <c r="G250" t="s">
+        <v>947</v>
+      </c>
+      <c r="J250" t="s">
+        <v>1031</v>
       </c>
       <c r="K250" t="s">
         <v>1032</v>
       </c>
       <c r="L250" t="s">
-        <v>1033</v>
+        <v>1069</v>
       </c>
       <c r="M250" t="s">
         <v>951</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,30 +25,30 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
     <t>codeforiati:sub-region-name</t>
   </si>
   <si>
     <t>codeforiati:iso-alpha-2-code</t>
   </si>
   <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
-    <t>codeforiati:global-name</t>
-  </si>
-  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
@@ -64,24 +64,24 @@
     <t>active</t>
   </si>
   <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
     <t>015</t>
   </si>
   <si>
-    <t>Africa</t>
-  </si>
-  <si>
     <t>Northern Africa</t>
   </si>
   <si>
     <t>DZ</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>World</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -166,12 +166,12 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
     <t>Sub-Saharan Africa</t>
   </si>
   <si>
@@ -832,15 +832,15 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>Americas</t>
+  </si>
+  <si>
     <t>419</t>
   </si>
   <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
     <t>Latin America and the Caribbean</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>Central Asia</t>
   </si>
   <si>
@@ -2200,12 +2200,12 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Europe</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Europe</t>
-  </si>
-  <si>
     <t>Eastern Europe</t>
   </si>
   <si>
@@ -2854,10 +2854,10 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
     <t>053</t>
-  </si>
-  <si>
-    <t>Oceania</t>
   </si>
   <si>
     <t>Australia and New Zealand</t>
@@ -3609,10 +3609,10 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
@@ -3624,7 +3624,7 @@
       <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="L2" t="s">
@@ -3644,23 +3644,23 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
+      <c r="J3" t="s">
+        <v>26</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -3679,23 +3679,23 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
+      <c r="J4" t="s">
+        <v>30</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -3714,23 +3714,23 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="s">
-        <v>21</v>
+      <c r="J5" t="s">
+        <v>34</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -3749,23 +3749,23 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
-      <c r="K6" t="s">
-        <v>21</v>
+      <c r="J6" t="s">
+        <v>38</v>
       </c>
       <c r="L6" t="s">
         <v>22</v>
@@ -3784,23 +3784,23 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="K7" t="s">
-        <v>21</v>
+      <c r="J7" t="s">
+        <v>42</v>
       </c>
       <c r="L7" t="s">
         <v>22</v>
@@ -3819,23 +3819,23 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
       </c>
-      <c r="K8" t="s">
-        <v>21</v>
+      <c r="J8" t="s">
+        <v>46</v>
       </c>
       <c r="L8" t="s">
         <v>22</v>
@@ -3858,25 +3858,25 @@
         <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
         <v>51</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>52</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>53</v>
       </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>54</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>22</v>
@@ -3899,25 +3899,25 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
         <v>51</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>52</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>58</v>
       </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>54</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
       </c>
       <c r="L10" t="s">
         <v>22</v>
@@ -3940,25 +3940,25 @@
         <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
         <v>51</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>52</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>62</v>
       </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>54</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>22</v>
@@ -3981,25 +3981,25 @@
         <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s">
         <v>51</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>52</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>66</v>
       </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>54</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
       </c>
       <c r="L12" t="s">
         <v>22</v>
@@ -4022,25 +4022,25 @@
         <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" t="s">
         <v>51</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>52</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>70</v>
       </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>54</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -4063,25 +4063,25 @@
         <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
         <v>51</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>52</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>74</v>
       </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>54</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
@@ -4104,25 +4104,25 @@
         <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
         <v>51</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>52</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>78</v>
       </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>54</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
@@ -4145,25 +4145,25 @@
         <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" t="s">
         <v>51</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>52</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>82</v>
       </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>54</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
@@ -4186,25 +4186,25 @@
         <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" t="s">
         <v>51</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>52</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>86</v>
       </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>54</v>
-      </c>
-      <c r="K17" t="s">
-        <v>21</v>
       </c>
       <c r="L17" t="s">
         <v>22</v>
@@ -4227,25 +4227,25 @@
         <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" t="s">
         <v>51</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>52</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>90</v>
       </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>54</v>
-      </c>
-      <c r="K18" t="s">
-        <v>21</v>
       </c>
       <c r="L18" t="s">
         <v>22</v>
@@ -4268,25 +4268,25 @@
         <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" t="s">
         <v>51</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>52</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
         <v>94</v>
       </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>54</v>
-      </c>
-      <c r="K19" t="s">
-        <v>21</v>
       </c>
       <c r="L19" t="s">
         <v>22</v>
@@ -4309,25 +4309,25 @@
         <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" t="s">
         <v>51</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>52</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>98</v>
       </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>54</v>
-      </c>
-      <c r="K20" t="s">
-        <v>21</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
@@ -4350,25 +4350,25 @@
         <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
         <v>51</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>52</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>102</v>
       </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>54</v>
-      </c>
-      <c r="K21" t="s">
-        <v>21</v>
       </c>
       <c r="L21" t="s">
         <v>22</v>
@@ -4391,25 +4391,25 @@
         <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" t="s">
         <v>51</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>52</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>106</v>
       </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>54</v>
-      </c>
-      <c r="K22" t="s">
-        <v>21</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
@@ -4432,25 +4432,25 @@
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
         <v>51</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>52</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>110</v>
       </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>54</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
@@ -4473,25 +4473,25 @@
         <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
         <v>51</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>52</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>114</v>
       </c>
-      <c r="I24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>54</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
       </c>
       <c r="L24" t="s">
         <v>22</v>
@@ -4514,25 +4514,25 @@
         <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" t="s">
         <v>51</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>52</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>118</v>
       </c>
-      <c r="I25" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>54</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
       </c>
       <c r="L25" t="s">
         <v>22</v>
@@ -4555,25 +4555,25 @@
         <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" t="s">
         <v>51</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>52</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>122</v>
       </c>
-      <c r="I26" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>54</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
       </c>
       <c r="L26" t="s">
         <v>22</v>
@@ -4596,25 +4596,25 @@
         <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" t="s">
         <v>51</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
         <v>52</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" t="s">
         <v>126</v>
       </c>
-      <c r="I27" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>54</v>
-      </c>
-      <c r="K27" t="s">
-        <v>21</v>
       </c>
       <c r="L27" t="s">
         <v>22</v>
@@ -4637,25 +4637,25 @@
         <v>50</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
         <v>51</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>52</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>130</v>
       </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>54</v>
-      </c>
-      <c r="K28" t="s">
-        <v>21</v>
       </c>
       <c r="L28" t="s">
         <v>22</v>
@@ -4678,25 +4678,25 @@
         <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" t="s">
         <v>51</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>52</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>134</v>
       </c>
-      <c r="I29" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>54</v>
-      </c>
-      <c r="K29" t="s">
-        <v>21</v>
       </c>
       <c r="L29" t="s">
         <v>22</v>
@@ -4719,25 +4719,25 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" t="s">
         <v>51</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>52</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
         <v>138</v>
       </c>
-      <c r="I30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>54</v>
-      </c>
-      <c r="K30" t="s">
-        <v>21</v>
       </c>
       <c r="L30" t="s">
         <v>22</v>
@@ -4757,28 +4757,28 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" t="s">
         <v>52</v>
       </c>
-      <c r="H31" t="s">
+      <c r="J31" t="s">
         <v>143</v>
       </c>
-      <c r="I31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>144</v>
-      </c>
-      <c r="K31" t="s">
-        <v>21</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
@@ -4798,28 +4798,28 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" t="s">
         <v>52</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
         <v>148</v>
       </c>
-      <c r="I32" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>144</v>
-      </c>
-      <c r="K32" t="s">
-        <v>21</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -4839,28 +4839,28 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" t="s">
         <v>52</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>152</v>
       </c>
-      <c r="I33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>144</v>
-      </c>
-      <c r="K33" t="s">
-        <v>21</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -4880,28 +4880,28 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" t="s">
         <v>52</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>156</v>
       </c>
-      <c r="I34" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>144</v>
-      </c>
-      <c r="K34" t="s">
-        <v>21</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
@@ -4921,28 +4921,28 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" t="s">
         <v>52</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>160</v>
       </c>
-      <c r="I35" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>144</v>
-      </c>
-      <c r="K35" t="s">
-        <v>21</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
@@ -4962,28 +4962,28 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" t="s">
         <v>52</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" t="s">
         <v>164</v>
       </c>
-      <c r="I36" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>144</v>
-      </c>
-      <c r="K36" t="s">
-        <v>21</v>
       </c>
       <c r="L36" t="s">
         <v>22</v>
@@ -5003,28 +5003,28 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" t="s">
         <v>52</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>168</v>
       </c>
-      <c r="I37" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>144</v>
-      </c>
-      <c r="K37" t="s">
-        <v>21</v>
       </c>
       <c r="L37" t="s">
         <v>22</v>
@@ -5044,28 +5044,28 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" t="s">
+        <v>51</v>
+      </c>
+      <c r="I38" t="s">
         <v>52</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
         <v>172</v>
       </c>
-      <c r="I38" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>144</v>
-      </c>
-      <c r="K38" t="s">
-        <v>21</v>
       </c>
       <c r="L38" t="s">
         <v>22</v>
@@ -5085,28 +5085,28 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" t="s">
+        <v>51</v>
+      </c>
+      <c r="I39" t="s">
         <v>52</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>176</v>
       </c>
-      <c r="I39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>144</v>
-      </c>
-      <c r="K39" t="s">
-        <v>21</v>
       </c>
       <c r="L39" t="s">
         <v>22</v>
@@ -5126,28 +5126,28 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" t="s">
         <v>52</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
         <v>181</v>
       </c>
-      <c r="I40" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>182</v>
-      </c>
-      <c r="K40" t="s">
-        <v>21</v>
       </c>
       <c r="L40" t="s">
         <v>22</v>
@@ -5167,28 +5167,28 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" t="s">
         <v>52</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
         <v>186</v>
       </c>
-      <c r="I41" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>182</v>
-      </c>
-      <c r="K41" t="s">
-        <v>21</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -5208,28 +5208,28 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" t="s">
         <v>52</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
         <v>190</v>
       </c>
-      <c r="I42" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>182</v>
-      </c>
-      <c r="K42" t="s">
-        <v>21</v>
       </c>
       <c r="L42" t="s">
         <v>22</v>
@@ -5249,28 +5249,28 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43" t="s">
         <v>52</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>194</v>
       </c>
-      <c r="I43" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>182</v>
-      </c>
-      <c r="K43" t="s">
-        <v>21</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
@@ -5290,28 +5290,28 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" t="s">
+        <v>51</v>
+      </c>
+      <c r="I44" t="s">
         <v>52</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>198</v>
       </c>
-      <c r="I44" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>182</v>
-      </c>
-      <c r="K44" t="s">
-        <v>21</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
@@ -5331,28 +5331,28 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" t="s">
+        <v>51</v>
+      </c>
+      <c r="I45" t="s">
         <v>52</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>203</v>
       </c>
-      <c r="I45" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>204</v>
-      </c>
-      <c r="K45" t="s">
-        <v>21</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -5372,28 +5372,28 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" t="s">
+        <v>51</v>
+      </c>
+      <c r="I46" t="s">
         <v>52</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>208</v>
       </c>
-      <c r="I46" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>204</v>
-      </c>
-      <c r="K46" t="s">
-        <v>21</v>
       </c>
       <c r="L46" t="s">
         <v>22</v>
@@ -5413,28 +5413,28 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" t="s">
+        <v>51</v>
+      </c>
+      <c r="I47" t="s">
         <v>52</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
         <v>212</v>
       </c>
-      <c r="I47" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>204</v>
-      </c>
-      <c r="K47" t="s">
-        <v>21</v>
       </c>
       <c r="L47" t="s">
         <v>22</v>
@@ -5454,28 +5454,28 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I48" t="s">
         <v>52</v>
       </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>216</v>
       </c>
-      <c r="I48" t="s">
-        <v>20</v>
-      </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>204</v>
-      </c>
-      <c r="K48" t="s">
-        <v>21</v>
       </c>
       <c r="L48" t="s">
         <v>22</v>
@@ -5495,28 +5495,28 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" t="s">
+        <v>51</v>
+      </c>
+      <c r="I49" t="s">
         <v>52</v>
       </c>
-      <c r="H49" t="s">
+      <c r="J49" t="s">
         <v>220</v>
       </c>
-      <c r="I49" t="s">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>204</v>
-      </c>
-      <c r="K49" t="s">
-        <v>21</v>
       </c>
       <c r="L49" t="s">
         <v>22</v>
@@ -5536,28 +5536,28 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" t="s">
+        <v>51</v>
+      </c>
+      <c r="I50" t="s">
         <v>52</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>224</v>
       </c>
-      <c r="I50" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>204</v>
-      </c>
-      <c r="K50" t="s">
-        <v>21</v>
       </c>
       <c r="L50" t="s">
         <v>22</v>
@@ -5577,28 +5577,28 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51" t="s">
         <v>52</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>228</v>
       </c>
-      <c r="I51" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>204</v>
-      </c>
-      <c r="K51" t="s">
-        <v>21</v>
       </c>
       <c r="L51" t="s">
         <v>22</v>
@@ -5618,28 +5618,28 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" t="s">
+        <v>51</v>
+      </c>
+      <c r="I52" t="s">
         <v>52</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
         <v>232</v>
       </c>
-      <c r="I52" t="s">
-        <v>20</v>
-      </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>204</v>
-      </c>
-      <c r="K52" t="s">
-        <v>21</v>
       </c>
       <c r="L52" t="s">
         <v>22</v>
@@ -5659,28 +5659,28 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" t="s">
+        <v>51</v>
+      </c>
+      <c r="I53" t="s">
         <v>52</v>
       </c>
-      <c r="H53" t="s">
+      <c r="J53" t="s">
         <v>236</v>
       </c>
-      <c r="I53" t="s">
-        <v>20</v>
-      </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>204</v>
-      </c>
-      <c r="K53" t="s">
-        <v>21</v>
       </c>
       <c r="L53" t="s">
         <v>22</v>
@@ -5700,28 +5700,28 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" t="s">
+        <v>51</v>
+      </c>
+      <c r="I54" t="s">
         <v>52</v>
       </c>
-      <c r="H54" t="s">
+      <c r="J54" t="s">
         <v>240</v>
       </c>
-      <c r="I54" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>204</v>
-      </c>
-      <c r="K54" t="s">
-        <v>21</v>
       </c>
       <c r="L54" t="s">
         <v>22</v>
@@ -5741,28 +5741,28 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I55" t="s">
         <v>52</v>
       </c>
-      <c r="H55" t="s">
+      <c r="J55" t="s">
         <v>244</v>
       </c>
-      <c r="I55" t="s">
-        <v>20</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>204</v>
-      </c>
-      <c r="K55" t="s">
-        <v>21</v>
       </c>
       <c r="L55" t="s">
         <v>22</v>
@@ -5782,28 +5782,28 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G56" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" t="s">
+        <v>51</v>
+      </c>
+      <c r="I56" t="s">
         <v>52</v>
       </c>
-      <c r="H56" t="s">
+      <c r="J56" t="s">
         <v>248</v>
       </c>
-      <c r="I56" t="s">
-        <v>20</v>
-      </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>204</v>
-      </c>
-      <c r="K56" t="s">
-        <v>21</v>
       </c>
       <c r="L56" t="s">
         <v>22</v>
@@ -5823,28 +5823,28 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G57" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I57" t="s">
         <v>52</v>
       </c>
-      <c r="H57" t="s">
+      <c r="J57" t="s">
         <v>252</v>
       </c>
-      <c r="I57" t="s">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>204</v>
-      </c>
-      <c r="K57" t="s">
-        <v>21</v>
       </c>
       <c r="L57" t="s">
         <v>22</v>
@@ -5864,28 +5864,28 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58" t="s">
         <v>52</v>
       </c>
-      <c r="H58" t="s">
+      <c r="J58" t="s">
         <v>256</v>
       </c>
-      <c r="I58" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>204</v>
-      </c>
-      <c r="K58" t="s">
-        <v>21</v>
       </c>
       <c r="L58" t="s">
         <v>22</v>
@@ -5905,28 +5905,28 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" t="s">
+        <v>51</v>
+      </c>
+      <c r="I59" t="s">
         <v>52</v>
       </c>
-      <c r="H59" t="s">
+      <c r="J59" t="s">
         <v>260</v>
       </c>
-      <c r="I59" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>204</v>
-      </c>
-      <c r="K59" t="s">
-        <v>21</v>
       </c>
       <c r="L59" t="s">
         <v>22</v>
@@ -5946,28 +5946,28 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" t="s">
+        <v>51</v>
+      </c>
+      <c r="I60" t="s">
         <v>52</v>
       </c>
-      <c r="H60" t="s">
+      <c r="J60" t="s">
         <v>264</v>
       </c>
-      <c r="I60" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>204</v>
-      </c>
-      <c r="K60" t="s">
-        <v>21</v>
       </c>
       <c r="L60" t="s">
         <v>22</v>
@@ -5987,28 +5987,28 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" t="s">
+        <v>51</v>
+      </c>
+      <c r="I61" t="s">
         <v>52</v>
       </c>
-      <c r="H61" t="s">
+      <c r="J61" t="s">
         <v>268</v>
       </c>
-      <c r="I61" t="s">
-        <v>20</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>204</v>
-      </c>
-      <c r="K61" t="s">
-        <v>21</v>
       </c>
       <c r="L61" t="s">
         <v>22</v>
@@ -6034,22 +6034,22 @@
         <v>273</v>
       </c>
       <c r="F62" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" t="s">
         <v>274</v>
       </c>
-      <c r="G62" t="s">
+      <c r="I62" t="s">
         <v>275</v>
       </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
         <v>276</v>
       </c>
-      <c r="I62" t="s">
-        <v>20</v>
-      </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>277</v>
-      </c>
-      <c r="K62" t="s">
-        <v>21</v>
       </c>
       <c r="L62" t="s">
         <v>278</v>
@@ -6075,22 +6075,22 @@
         <v>273</v>
       </c>
       <c r="F63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" t="s">
         <v>274</v>
       </c>
-      <c r="G63" t="s">
+      <c r="I63" t="s">
         <v>275</v>
       </c>
-      <c r="H63" t="s">
+      <c r="J63" t="s">
         <v>282</v>
       </c>
-      <c r="I63" t="s">
-        <v>20</v>
-      </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>277</v>
-      </c>
-      <c r="K63" t="s">
-        <v>21</v>
       </c>
       <c r="L63" t="s">
         <v>278</v>
@@ -6116,22 +6116,22 @@
         <v>273</v>
       </c>
       <c r="F64" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" t="s">
         <v>274</v>
       </c>
-      <c r="G64" t="s">
+      <c r="I64" t="s">
         <v>275</v>
       </c>
-      <c r="H64" t="s">
+      <c r="J64" t="s">
         <v>286</v>
       </c>
-      <c r="I64" t="s">
-        <v>20</v>
-      </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>277</v>
-      </c>
-      <c r="K64" t="s">
-        <v>21</v>
       </c>
       <c r="L64" t="s">
         <v>278</v>
@@ -6157,22 +6157,22 @@
         <v>273</v>
       </c>
       <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" t="s">
         <v>274</v>
       </c>
-      <c r="G65" t="s">
+      <c r="I65" t="s">
         <v>275</v>
       </c>
-      <c r="H65" t="s">
+      <c r="J65" t="s">
         <v>290</v>
       </c>
-      <c r="I65" t="s">
-        <v>20</v>
-      </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>277</v>
-      </c>
-      <c r="K65" t="s">
-        <v>21</v>
       </c>
       <c r="L65" t="s">
         <v>278</v>
@@ -6198,22 +6198,22 @@
         <v>273</v>
       </c>
       <c r="F66" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" t="s">
         <v>274</v>
       </c>
-      <c r="G66" t="s">
+      <c r="I66" t="s">
         <v>275</v>
       </c>
-      <c r="H66" t="s">
+      <c r="J66" t="s">
         <v>294</v>
       </c>
-      <c r="I66" t="s">
-        <v>20</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>277</v>
-      </c>
-      <c r="K66" t="s">
-        <v>21</v>
       </c>
       <c r="L66" t="s">
         <v>278</v>
@@ -6239,22 +6239,22 @@
         <v>273</v>
       </c>
       <c r="F67" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" t="s">
         <v>274</v>
       </c>
-      <c r="G67" t="s">
+      <c r="I67" t="s">
         <v>275</v>
       </c>
-      <c r="H67" t="s">
+      <c r="J67" t="s">
         <v>298</v>
       </c>
-      <c r="I67" t="s">
-        <v>20</v>
-      </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>277</v>
-      </c>
-      <c r="K67" t="s">
-        <v>21</v>
       </c>
       <c r="L67" t="s">
         <v>278</v>
@@ -6280,22 +6280,22 @@
         <v>273</v>
       </c>
       <c r="F68" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" t="s">
         <v>274</v>
       </c>
-      <c r="G68" t="s">
+      <c r="I68" t="s">
         <v>275</v>
       </c>
-      <c r="H68" t="s">
+      <c r="J68" t="s">
         <v>302</v>
       </c>
-      <c r="I68" t="s">
-        <v>20</v>
-      </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>277</v>
-      </c>
-      <c r="K68" t="s">
-        <v>21</v>
       </c>
       <c r="L68" t="s">
         <v>278</v>
@@ -6321,22 +6321,22 @@
         <v>273</v>
       </c>
       <c r="F69" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" t="s">
         <v>274</v>
       </c>
-      <c r="G69" t="s">
+      <c r="I69" t="s">
         <v>275</v>
       </c>
-      <c r="H69" t="s">
+      <c r="J69" t="s">
         <v>306</v>
       </c>
-      <c r="I69" t="s">
-        <v>20</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>277</v>
-      </c>
-      <c r="K69" t="s">
-        <v>21</v>
       </c>
       <c r="L69" t="s">
         <v>278</v>
@@ -6362,22 +6362,22 @@
         <v>273</v>
       </c>
       <c r="F70" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" t="s">
         <v>274</v>
       </c>
-      <c r="G70" t="s">
+      <c r="I70" t="s">
         <v>275</v>
       </c>
-      <c r="H70" t="s">
+      <c r="J70" t="s">
         <v>310</v>
       </c>
-      <c r="I70" t="s">
-        <v>20</v>
-      </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>277</v>
-      </c>
-      <c r="K70" t="s">
-        <v>21</v>
       </c>
       <c r="L70" t="s">
         <v>278</v>
@@ -6403,22 +6403,22 @@
         <v>273</v>
       </c>
       <c r="F71" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" t="s">
         <v>274</v>
       </c>
-      <c r="G71" t="s">
+      <c r="I71" t="s">
         <v>275</v>
       </c>
-      <c r="H71" t="s">
+      <c r="J71" t="s">
         <v>314</v>
       </c>
-      <c r="I71" t="s">
-        <v>20</v>
-      </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>277</v>
-      </c>
-      <c r="K71" t="s">
-        <v>21</v>
       </c>
       <c r="L71" t="s">
         <v>278</v>
@@ -6444,22 +6444,22 @@
         <v>273</v>
       </c>
       <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" t="s">
         <v>274</v>
       </c>
-      <c r="G72" t="s">
+      <c r="I72" t="s">
         <v>275</v>
       </c>
-      <c r="H72" t="s">
+      <c r="J72" t="s">
         <v>318</v>
       </c>
-      <c r="I72" t="s">
-        <v>20</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>277</v>
-      </c>
-      <c r="K72" t="s">
-        <v>21</v>
       </c>
       <c r="L72" t="s">
         <v>278</v>
@@ -6485,22 +6485,22 @@
         <v>273</v>
       </c>
       <c r="F73" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" t="s">
         <v>274</v>
       </c>
-      <c r="G73" t="s">
+      <c r="I73" t="s">
         <v>275</v>
       </c>
-      <c r="H73" t="s">
+      <c r="J73" t="s">
         <v>322</v>
       </c>
-      <c r="I73" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>277</v>
-      </c>
-      <c r="K73" t="s">
-        <v>21</v>
       </c>
       <c r="L73" t="s">
         <v>278</v>
@@ -6526,22 +6526,22 @@
         <v>273</v>
       </c>
       <c r="F74" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" t="s">
         <v>274</v>
       </c>
-      <c r="G74" t="s">
+      <c r="I74" t="s">
         <v>275</v>
       </c>
-      <c r="H74" t="s">
+      <c r="J74" t="s">
         <v>326</v>
       </c>
-      <c r="I74" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>277</v>
-      </c>
-      <c r="K74" t="s">
-        <v>21</v>
       </c>
       <c r="L74" t="s">
         <v>278</v>
@@ -6567,22 +6567,22 @@
         <v>273</v>
       </c>
       <c r="F75" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" t="s">
         <v>274</v>
       </c>
-      <c r="G75" t="s">
+      <c r="I75" t="s">
         <v>275</v>
       </c>
-      <c r="H75" t="s">
+      <c r="J75" t="s">
         <v>330</v>
       </c>
-      <c r="I75" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>277</v>
-      </c>
-      <c r="K75" t="s">
-        <v>21</v>
       </c>
       <c r="L75" t="s">
         <v>278</v>
@@ -6608,22 +6608,22 @@
         <v>273</v>
       </c>
       <c r="F76" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" t="s">
         <v>274</v>
       </c>
-      <c r="G76" t="s">
+      <c r="I76" t="s">
         <v>275</v>
       </c>
-      <c r="H76" t="s">
+      <c r="J76" t="s">
         <v>334</v>
       </c>
-      <c r="I76" t="s">
-        <v>20</v>
-      </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>277</v>
-      </c>
-      <c r="K76" t="s">
-        <v>21</v>
       </c>
       <c r="L76" t="s">
         <v>278</v>
@@ -6649,22 +6649,22 @@
         <v>273</v>
       </c>
       <c r="F77" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" t="s">
         <v>274</v>
       </c>
-      <c r="G77" t="s">
+      <c r="I77" t="s">
         <v>275</v>
       </c>
-      <c r="H77" t="s">
+      <c r="J77" t="s">
         <v>338</v>
       </c>
-      <c r="I77" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>277</v>
-      </c>
-      <c r="K77" t="s">
-        <v>21</v>
       </c>
       <c r="L77" t="s">
         <v>278</v>
@@ -6690,22 +6690,22 @@
         <v>273</v>
       </c>
       <c r="F78" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" t="s">
         <v>274</v>
       </c>
-      <c r="G78" t="s">
+      <c r="I78" t="s">
         <v>275</v>
       </c>
-      <c r="H78" t="s">
+      <c r="J78" t="s">
         <v>342</v>
       </c>
-      <c r="I78" t="s">
-        <v>20</v>
-      </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>277</v>
-      </c>
-      <c r="K78" t="s">
-        <v>21</v>
       </c>
       <c r="L78" t="s">
         <v>278</v>
@@ -6731,22 +6731,22 @@
         <v>273</v>
       </c>
       <c r="F79" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" t="s">
         <v>274</v>
       </c>
-      <c r="G79" t="s">
+      <c r="I79" t="s">
         <v>275</v>
       </c>
-      <c r="H79" t="s">
+      <c r="J79" t="s">
         <v>346</v>
       </c>
-      <c r="I79" t="s">
-        <v>20</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>277</v>
-      </c>
-      <c r="K79" t="s">
-        <v>21</v>
       </c>
       <c r="L79" t="s">
         <v>278</v>
@@ -6772,22 +6772,22 @@
         <v>273</v>
       </c>
       <c r="F80" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" t="s">
         <v>274</v>
       </c>
-      <c r="G80" t="s">
+      <c r="I80" t="s">
         <v>275</v>
       </c>
-      <c r="H80" t="s">
+      <c r="J80" t="s">
         <v>350</v>
       </c>
-      <c r="I80" t="s">
-        <v>20</v>
-      </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>277</v>
-      </c>
-      <c r="K80" t="s">
-        <v>21</v>
       </c>
       <c r="L80" t="s">
         <v>278</v>
@@ -6813,22 +6813,22 @@
         <v>273</v>
       </c>
       <c r="F81" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" t="s">
         <v>274</v>
       </c>
-      <c r="G81" t="s">
+      <c r="I81" t="s">
         <v>275</v>
       </c>
-      <c r="H81" t="s">
+      <c r="J81" t="s">
         <v>354</v>
       </c>
-      <c r="I81" t="s">
-        <v>20</v>
-      </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>277</v>
-      </c>
-      <c r="K81" t="s">
-        <v>21</v>
       </c>
       <c r="L81" t="s">
         <v>278</v>
@@ -6854,22 +6854,22 @@
         <v>273</v>
       </c>
       <c r="F82" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" t="s">
         <v>274</v>
       </c>
-      <c r="G82" t="s">
+      <c r="I82" t="s">
         <v>275</v>
       </c>
-      <c r="H82" t="s">
+      <c r="J82" t="s">
         <v>358</v>
       </c>
-      <c r="I82" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>277</v>
-      </c>
-      <c r="K82" t="s">
-        <v>21</v>
       </c>
       <c r="L82" t="s">
         <v>278</v>
@@ -6895,22 +6895,22 @@
         <v>273</v>
       </c>
       <c r="F83" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" t="s">
         <v>274</v>
       </c>
-      <c r="G83" t="s">
+      <c r="I83" t="s">
         <v>275</v>
       </c>
-      <c r="H83" t="s">
+      <c r="J83" t="s">
         <v>362</v>
       </c>
-      <c r="I83" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>277</v>
-      </c>
-      <c r="K83" t="s">
-        <v>21</v>
       </c>
       <c r="L83" t="s">
         <v>278</v>
@@ -6936,22 +6936,22 @@
         <v>273</v>
       </c>
       <c r="F84" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" t="s">
         <v>274</v>
       </c>
-      <c r="G84" t="s">
+      <c r="I84" t="s">
         <v>275</v>
       </c>
-      <c r="H84" t="s">
+      <c r="J84" t="s">
         <v>366</v>
       </c>
-      <c r="I84" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>277</v>
-      </c>
-      <c r="K84" t="s">
-        <v>21</v>
       </c>
       <c r="L84" t="s">
         <v>278</v>
@@ -6977,22 +6977,22 @@
         <v>273</v>
       </c>
       <c r="F85" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" t="s">
         <v>274</v>
       </c>
-      <c r="G85" t="s">
+      <c r="I85" t="s">
         <v>275</v>
       </c>
-      <c r="H85" t="s">
+      <c r="J85" t="s">
         <v>370</v>
       </c>
-      <c r="I85" t="s">
-        <v>20</v>
-      </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>277</v>
-      </c>
-      <c r="K85" t="s">
-        <v>21</v>
       </c>
       <c r="L85" t="s">
         <v>278</v>
@@ -7018,22 +7018,22 @@
         <v>273</v>
       </c>
       <c r="F86" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86" t="s">
         <v>274</v>
       </c>
-      <c r="G86" t="s">
+      <c r="I86" t="s">
         <v>275</v>
       </c>
-      <c r="H86" t="s">
+      <c r="J86" t="s">
         <v>374</v>
       </c>
-      <c r="I86" t="s">
-        <v>20</v>
-      </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>277</v>
-      </c>
-      <c r="K86" t="s">
-        <v>21</v>
       </c>
       <c r="L86" t="s">
         <v>278</v>
@@ -7059,22 +7059,22 @@
         <v>273</v>
       </c>
       <c r="F87" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" t="s">
         <v>274</v>
       </c>
-      <c r="G87" t="s">
+      <c r="I87" t="s">
         <v>275</v>
       </c>
-      <c r="H87" t="s">
+      <c r="J87" t="s">
         <v>378</v>
       </c>
-      <c r="I87" t="s">
-        <v>20</v>
-      </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>277</v>
-      </c>
-      <c r="K87" t="s">
-        <v>21</v>
       </c>
       <c r="L87" t="s">
         <v>278</v>
@@ -7100,22 +7100,22 @@
         <v>273</v>
       </c>
       <c r="F88" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" t="s">
         <v>274</v>
       </c>
-      <c r="G88" t="s">
+      <c r="I88" t="s">
         <v>275</v>
       </c>
-      <c r="H88" t="s">
+      <c r="J88" t="s">
         <v>382</v>
       </c>
-      <c r="I88" t="s">
-        <v>20</v>
-      </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>277</v>
-      </c>
-      <c r="K88" t="s">
-        <v>21</v>
       </c>
       <c r="L88" t="s">
         <v>278</v>
@@ -7141,22 +7141,22 @@
         <v>273</v>
       </c>
       <c r="F89" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" t="s">
         <v>274</v>
       </c>
-      <c r="G89" t="s">
+      <c r="I89" t="s">
         <v>275</v>
       </c>
-      <c r="H89" t="s">
+      <c r="J89" t="s">
         <v>386</v>
       </c>
-      <c r="I89" t="s">
-        <v>20</v>
-      </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>277</v>
-      </c>
-      <c r="K89" t="s">
-        <v>21</v>
       </c>
       <c r="L89" t="s">
         <v>278</v>
@@ -7176,28 +7176,28 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E90" t="s">
         <v>273</v>
       </c>
       <c r="F90" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G90" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" t="s">
+        <v>274</v>
+      </c>
+      <c r="I90" t="s">
         <v>275</v>
       </c>
-      <c r="H90" t="s">
+      <c r="J90" t="s">
         <v>391</v>
       </c>
-      <c r="I90" t="s">
-        <v>20</v>
-      </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>392</v>
-      </c>
-      <c r="K90" t="s">
-        <v>21</v>
       </c>
       <c r="L90" t="s">
         <v>278</v>
@@ -7217,28 +7217,28 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E91" t="s">
         <v>273</v>
       </c>
       <c r="F91" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G91" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" t="s">
+        <v>274</v>
+      </c>
+      <c r="I91" t="s">
         <v>275</v>
       </c>
-      <c r="H91" t="s">
+      <c r="J91" t="s">
         <v>396</v>
       </c>
-      <c r="I91" t="s">
-        <v>20</v>
-      </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>392</v>
-      </c>
-      <c r="K91" t="s">
-        <v>21</v>
       </c>
       <c r="L91" t="s">
         <v>278</v>
@@ -7258,28 +7258,28 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E92" t="s">
         <v>273</v>
       </c>
       <c r="F92" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G92" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" t="s">
+        <v>274</v>
+      </c>
+      <c r="I92" t="s">
         <v>275</v>
       </c>
-      <c r="H92" t="s">
+      <c r="J92" t="s">
         <v>400</v>
       </c>
-      <c r="I92" t="s">
-        <v>20</v>
-      </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>392</v>
-      </c>
-      <c r="K92" t="s">
-        <v>21</v>
       </c>
       <c r="L92" t="s">
         <v>278</v>
@@ -7299,28 +7299,28 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E93" t="s">
         <v>273</v>
       </c>
       <c r="F93" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G93" t="s">
+        <v>18</v>
+      </c>
+      <c r="H93" t="s">
+        <v>274</v>
+      </c>
+      <c r="I93" t="s">
         <v>275</v>
       </c>
-      <c r="H93" t="s">
+      <c r="J93" t="s">
         <v>404</v>
       </c>
-      <c r="I93" t="s">
-        <v>20</v>
-      </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>392</v>
-      </c>
-      <c r="K93" t="s">
-        <v>21</v>
       </c>
       <c r="L93" t="s">
         <v>278</v>
@@ -7340,28 +7340,28 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E94" t="s">
         <v>273</v>
       </c>
       <c r="F94" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G94" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94" t="s">
+        <v>274</v>
+      </c>
+      <c r="I94" t="s">
         <v>275</v>
       </c>
-      <c r="H94" t="s">
+      <c r="J94" t="s">
         <v>408</v>
       </c>
-      <c r="I94" t="s">
-        <v>20</v>
-      </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>392</v>
-      </c>
-      <c r="K94" t="s">
-        <v>21</v>
       </c>
       <c r="L94" t="s">
         <v>278</v>
@@ -7381,28 +7381,28 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E95" t="s">
         <v>273</v>
       </c>
       <c r="F95" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G95" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" t="s">
+        <v>274</v>
+      </c>
+      <c r="I95" t="s">
         <v>275</v>
       </c>
-      <c r="H95" t="s">
+      <c r="J95" t="s">
         <v>412</v>
       </c>
-      <c r="I95" t="s">
-        <v>20</v>
-      </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>392</v>
-      </c>
-      <c r="K95" t="s">
-        <v>21</v>
       </c>
       <c r="L95" t="s">
         <v>278</v>
@@ -7422,28 +7422,28 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E96" t="s">
         <v>273</v>
       </c>
       <c r="F96" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G96" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" t="s">
+        <v>274</v>
+      </c>
+      <c r="I96" t="s">
         <v>275</v>
       </c>
-      <c r="H96" t="s">
+      <c r="J96" t="s">
         <v>416</v>
       </c>
-      <c r="I96" t="s">
-        <v>20</v>
-      </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>392</v>
-      </c>
-      <c r="K96" t="s">
-        <v>21</v>
       </c>
       <c r="L96" t="s">
         <v>278</v>
@@ -7463,28 +7463,28 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E97" t="s">
         <v>273</v>
       </c>
       <c r="F97" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="G97" t="s">
+        <v>18</v>
+      </c>
+      <c r="H97" t="s">
+        <v>274</v>
+      </c>
+      <c r="I97" t="s">
         <v>275</v>
       </c>
-      <c r="H97" t="s">
+      <c r="J97" t="s">
         <v>420</v>
       </c>
-      <c r="I97" t="s">
-        <v>20</v>
-      </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>392</v>
-      </c>
-      <c r="K97" t="s">
-        <v>21</v>
       </c>
       <c r="L97" t="s">
         <v>278</v>
@@ -7504,28 +7504,28 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E98" t="s">
         <v>273</v>
       </c>
       <c r="F98" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G98" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" t="s">
+        <v>274</v>
+      </c>
+      <c r="I98" t="s">
         <v>275</v>
       </c>
-      <c r="H98" t="s">
+      <c r="J98" t="s">
         <v>425</v>
       </c>
-      <c r="I98" t="s">
-        <v>20</v>
-      </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>426</v>
-      </c>
-      <c r="K98" t="s">
-        <v>21</v>
       </c>
       <c r="L98" t="s">
         <v>278</v>
@@ -7545,28 +7545,28 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E99" t="s">
         <v>273</v>
       </c>
       <c r="F99" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G99" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" t="s">
+        <v>274</v>
+      </c>
+      <c r="I99" t="s">
         <v>275</v>
       </c>
-      <c r="H99" t="s">
+      <c r="J99" t="s">
         <v>430</v>
       </c>
-      <c r="I99" t="s">
-        <v>20</v>
-      </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>426</v>
-      </c>
-      <c r="K99" t="s">
-        <v>21</v>
       </c>
       <c r="L99" t="s">
         <v>278</v>
@@ -7586,28 +7586,28 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E100" t="s">
         <v>273</v>
       </c>
       <c r="F100" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G100" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" t="s">
+        <v>274</v>
+      </c>
+      <c r="I100" t="s">
         <v>275</v>
       </c>
-      <c r="H100" t="s">
+      <c r="J100" t="s">
         <v>434</v>
       </c>
-      <c r="I100" t="s">
-        <v>20</v>
-      </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>426</v>
-      </c>
-      <c r="K100" t="s">
-        <v>21</v>
       </c>
       <c r="L100" t="s">
         <v>278</v>
@@ -7627,28 +7627,28 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E101" t="s">
         <v>273</v>
       </c>
       <c r="F101" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" t="s">
+        <v>274</v>
+      </c>
+      <c r="I101" t="s">
         <v>275</v>
       </c>
-      <c r="H101" t="s">
+      <c r="J101" t="s">
         <v>438</v>
       </c>
-      <c r="I101" t="s">
-        <v>20</v>
-      </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>426</v>
-      </c>
-      <c r="K101" t="s">
-        <v>21</v>
       </c>
       <c r="L101" t="s">
         <v>278</v>
@@ -7668,28 +7668,28 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E102" t="s">
         <v>273</v>
       </c>
       <c r="F102" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G102" t="s">
+        <v>18</v>
+      </c>
+      <c r="H102" t="s">
+        <v>274</v>
+      </c>
+      <c r="I102" t="s">
         <v>275</v>
       </c>
-      <c r="H102" t="s">
+      <c r="J102" t="s">
         <v>442</v>
       </c>
-      <c r="I102" t="s">
-        <v>20</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>426</v>
-      </c>
-      <c r="K102" t="s">
-        <v>21</v>
       </c>
       <c r="L102" t="s">
         <v>278</v>
@@ -7709,28 +7709,28 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E103" t="s">
         <v>273</v>
       </c>
       <c r="F103" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G103" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103" t="s">
+        <v>274</v>
+      </c>
+      <c r="I103" t="s">
         <v>275</v>
       </c>
-      <c r="H103" t="s">
+      <c r="J103" t="s">
         <v>446</v>
       </c>
-      <c r="I103" t="s">
-        <v>20</v>
-      </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>426</v>
-      </c>
-      <c r="K103" t="s">
-        <v>21</v>
       </c>
       <c r="L103" t="s">
         <v>278</v>
@@ -7750,28 +7750,28 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E104" t="s">
         <v>273</v>
       </c>
       <c r="F104" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G104" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104" t="s">
+        <v>274</v>
+      </c>
+      <c r="I104" t="s">
         <v>275</v>
       </c>
-      <c r="H104" t="s">
+      <c r="J104" t="s">
         <v>450</v>
       </c>
-      <c r="I104" t="s">
-        <v>20</v>
-      </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>426</v>
-      </c>
-      <c r="K104" t="s">
-        <v>21</v>
       </c>
       <c r="L104" t="s">
         <v>278</v>
@@ -7791,28 +7791,28 @@
         <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E105" t="s">
         <v>273</v>
       </c>
       <c r="F105" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G105" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" t="s">
+        <v>274</v>
+      </c>
+      <c r="I105" t="s">
         <v>275</v>
       </c>
-      <c r="H105" t="s">
+      <c r="J105" t="s">
         <v>454</v>
       </c>
-      <c r="I105" t="s">
-        <v>20</v>
-      </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>426</v>
-      </c>
-      <c r="K105" t="s">
-        <v>21</v>
       </c>
       <c r="L105" t="s">
         <v>278</v>
@@ -7832,28 +7832,28 @@
         <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E106" t="s">
         <v>273</v>
       </c>
       <c r="F106" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G106" t="s">
+        <v>18</v>
+      </c>
+      <c r="H106" t="s">
+        <v>274</v>
+      </c>
+      <c r="I106" t="s">
         <v>275</v>
       </c>
-      <c r="H106" t="s">
+      <c r="J106" t="s">
         <v>458</v>
       </c>
-      <c r="I106" t="s">
-        <v>20</v>
-      </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>426</v>
-      </c>
-      <c r="K106" t="s">
-        <v>21</v>
       </c>
       <c r="L106" t="s">
         <v>278</v>
@@ -7873,28 +7873,28 @@
         <v>15</v>
       </c>
       <c r="D107" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E107" t="s">
         <v>273</v>
       </c>
       <c r="F107" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G107" t="s">
+        <v>18</v>
+      </c>
+      <c r="H107" t="s">
+        <v>274</v>
+      </c>
+      <c r="I107" t="s">
         <v>275</v>
       </c>
-      <c r="H107" t="s">
+      <c r="J107" t="s">
         <v>462</v>
       </c>
-      <c r="I107" t="s">
-        <v>20</v>
-      </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>426</v>
-      </c>
-      <c r="K107" t="s">
-        <v>21</v>
       </c>
       <c r="L107" t="s">
         <v>278</v>
@@ -7914,28 +7914,28 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E108" t="s">
         <v>273</v>
       </c>
       <c r="F108" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G108" t="s">
+        <v>18</v>
+      </c>
+      <c r="H108" t="s">
+        <v>274</v>
+      </c>
+      <c r="I108" t="s">
         <v>275</v>
       </c>
-      <c r="H108" t="s">
+      <c r="J108" t="s">
         <v>466</v>
       </c>
-      <c r="I108" t="s">
-        <v>20</v>
-      </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>426</v>
-      </c>
-      <c r="K108" t="s">
-        <v>21</v>
       </c>
       <c r="L108" t="s">
         <v>278</v>
@@ -7955,28 +7955,28 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E109" t="s">
         <v>273</v>
       </c>
       <c r="F109" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G109" t="s">
+        <v>18</v>
+      </c>
+      <c r="H109" t="s">
+        <v>274</v>
+      </c>
+      <c r="I109" t="s">
         <v>275</v>
       </c>
-      <c r="H109" t="s">
+      <c r="J109" t="s">
         <v>470</v>
       </c>
-      <c r="I109" t="s">
-        <v>20</v>
-      </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>426</v>
-      </c>
-      <c r="K109" t="s">
-        <v>21</v>
       </c>
       <c r="L109" t="s">
         <v>278</v>
@@ -7996,28 +7996,28 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E110" t="s">
         <v>273</v>
       </c>
       <c r="F110" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G110" t="s">
+        <v>18</v>
+      </c>
+      <c r="H110" t="s">
+        <v>274</v>
+      </c>
+      <c r="I110" t="s">
         <v>275</v>
       </c>
-      <c r="H110" t="s">
+      <c r="J110" t="s">
         <v>474</v>
       </c>
-      <c r="I110" t="s">
-        <v>20</v>
-      </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>426</v>
-      </c>
-      <c r="K110" t="s">
-        <v>21</v>
       </c>
       <c r="L110" t="s">
         <v>278</v>
@@ -8037,28 +8037,28 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E111" t="s">
         <v>273</v>
       </c>
       <c r="F111" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H111" t="s">
+        <v>274</v>
+      </c>
+      <c r="I111" t="s">
         <v>275</v>
       </c>
-      <c r="H111" t="s">
+      <c r="J111" t="s">
         <v>478</v>
       </c>
-      <c r="I111" t="s">
-        <v>20</v>
-      </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>426</v>
-      </c>
-      <c r="K111" t="s">
-        <v>21</v>
       </c>
       <c r="L111" t="s">
         <v>278</v>
@@ -8078,28 +8078,28 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E112" t="s">
         <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G112" t="s">
+        <v>18</v>
+      </c>
+      <c r="H112" t="s">
+        <v>274</v>
+      </c>
+      <c r="I112" t="s">
         <v>275</v>
       </c>
-      <c r="H112" t="s">
+      <c r="J112" t="s">
         <v>482</v>
       </c>
-      <c r="I112" t="s">
-        <v>20</v>
-      </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>426</v>
-      </c>
-      <c r="K112" t="s">
-        <v>21</v>
       </c>
       <c r="L112" t="s">
         <v>278</v>
@@ -8119,28 +8119,28 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="E113" t="s">
         <v>273</v>
       </c>
       <c r="F113" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="G113" t="s">
+        <v>18</v>
+      </c>
+      <c r="H113" t="s">
+        <v>274</v>
+      </c>
+      <c r="I113" t="s">
         <v>275</v>
       </c>
-      <c r="H113" t="s">
+      <c r="J113" t="s">
         <v>486</v>
       </c>
-      <c r="I113" t="s">
-        <v>20</v>
-      </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>426</v>
-      </c>
-      <c r="K113" t="s">
-        <v>21</v>
       </c>
       <c r="L113" t="s">
         <v>278</v>
@@ -8159,23 +8159,23 @@
       <c r="C114" t="s">
         <v>15</v>
       </c>
-      <c r="D114" t="s">
-        <v>490</v>
-      </c>
       <c r="E114" t="s">
         <v>273</v>
       </c>
+      <c r="F114" t="s">
+        <v>17</v>
+      </c>
       <c r="G114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H114" t="s">
+        <v>490</v>
+      </c>
+      <c r="I114" t="s">
         <v>491</v>
       </c>
-      <c r="H114" t="s">
+      <c r="J114" t="s">
         <v>492</v>
-      </c>
-      <c r="I114" t="s">
-        <v>20</v>
-      </c>
-      <c r="K114" t="s">
-        <v>21</v>
       </c>
       <c r="L114" t="s">
         <v>278</v>
@@ -8194,23 +8194,23 @@
       <c r="C115" t="s">
         <v>15</v>
       </c>
-      <c r="D115" t="s">
-        <v>490</v>
-      </c>
       <c r="E115" t="s">
         <v>273</v>
       </c>
+      <c r="F115" t="s">
+        <v>17</v>
+      </c>
       <c r="G115" t="s">
+        <v>18</v>
+      </c>
+      <c r="H115" t="s">
+        <v>490</v>
+      </c>
+      <c r="I115" t="s">
         <v>491</v>
       </c>
-      <c r="H115" t="s">
+      <c r="J115" t="s">
         <v>496</v>
-      </c>
-      <c r="I115" t="s">
-        <v>20</v>
-      </c>
-      <c r="K115" t="s">
-        <v>21</v>
       </c>
       <c r="L115" t="s">
         <v>278</v>
@@ -8229,23 +8229,23 @@
       <c r="C116" t="s">
         <v>15</v>
       </c>
-      <c r="D116" t="s">
-        <v>490</v>
-      </c>
       <c r="E116" t="s">
         <v>273</v>
       </c>
+      <c r="F116" t="s">
+        <v>17</v>
+      </c>
       <c r="G116" t="s">
+        <v>18</v>
+      </c>
+      <c r="H116" t="s">
+        <v>490</v>
+      </c>
+      <c r="I116" t="s">
         <v>491</v>
       </c>
-      <c r="H116" t="s">
+      <c r="J116" t="s">
         <v>500</v>
-      </c>
-      <c r="I116" t="s">
-        <v>20</v>
-      </c>
-      <c r="K116" t="s">
-        <v>21</v>
       </c>
       <c r="L116" t="s">
         <v>278</v>
@@ -8264,23 +8264,23 @@
       <c r="C117" t="s">
         <v>15</v>
       </c>
-      <c r="D117" t="s">
-        <v>490</v>
-      </c>
       <c r="E117" t="s">
         <v>273</v>
       </c>
+      <c r="F117" t="s">
+        <v>17</v>
+      </c>
       <c r="G117" t="s">
+        <v>18</v>
+      </c>
+      <c r="H117" t="s">
+        <v>490</v>
+      </c>
+      <c r="I117" t="s">
         <v>491</v>
       </c>
-      <c r="H117" t="s">
+      <c r="J117" t="s">
         <v>504</v>
-      </c>
-      <c r="I117" t="s">
-        <v>20</v>
-      </c>
-      <c r="K117" t="s">
-        <v>21</v>
       </c>
       <c r="L117" t="s">
         <v>278</v>
@@ -8299,23 +8299,23 @@
       <c r="C118" t="s">
         <v>15</v>
       </c>
-      <c r="D118" t="s">
-        <v>490</v>
-      </c>
       <c r="E118" t="s">
         <v>273</v>
       </c>
+      <c r="F118" t="s">
+        <v>17</v>
+      </c>
       <c r="G118" t="s">
+        <v>18</v>
+      </c>
+      <c r="H118" t="s">
+        <v>490</v>
+      </c>
+      <c r="I118" t="s">
         <v>491</v>
       </c>
-      <c r="H118" t="s">
+      <c r="J118" t="s">
         <v>508</v>
-      </c>
-      <c r="I118" t="s">
-        <v>20</v>
-      </c>
-      <c r="K118" t="s">
-        <v>21</v>
       </c>
       <c r="L118" t="s">
         <v>278</v>
@@ -8334,14 +8334,14 @@
       <c r="C119" t="s">
         <v>15</v>
       </c>
-      <c r="H119" t="s">
+      <c r="F119" t="s">
+        <v>17</v>
+      </c>
+      <c r="G119" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" t="s">
         <v>512</v>
-      </c>
-      <c r="I119" t="s">
-        <v>20</v>
-      </c>
-      <c r="K119" t="s">
-        <v>21</v>
       </c>
       <c r="M119" t="s">
         <v>513</v>
@@ -8357,23 +8357,23 @@
       <c r="C120" t="s">
         <v>15</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>516</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
+        <v>17</v>
+      </c>
+      <c r="G120" t="s">
+        <v>18</v>
+      </c>
+      <c r="H120" t="s">
         <v>517</v>
       </c>
-      <c r="G120" t="s">
+      <c r="I120" t="s">
         <v>518</v>
       </c>
-      <c r="H120" t="s">
+      <c r="J120" t="s">
         <v>519</v>
-      </c>
-      <c r="I120" t="s">
-        <v>20</v>
-      </c>
-      <c r="K120" t="s">
-        <v>21</v>
       </c>
       <c r="L120" t="s">
         <v>520</v>
@@ -8392,23 +8392,23 @@
       <c r="C121" t="s">
         <v>15</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>516</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
+        <v>17</v>
+      </c>
+      <c r="G121" t="s">
+        <v>18</v>
+      </c>
+      <c r="H121" t="s">
         <v>517</v>
       </c>
-      <c r="G121" t="s">
+      <c r="I121" t="s">
         <v>518</v>
       </c>
-      <c r="H121" t="s">
+      <c r="J121" t="s">
         <v>524</v>
-      </c>
-      <c r="I121" t="s">
-        <v>20</v>
-      </c>
-      <c r="K121" t="s">
-        <v>21</v>
       </c>
       <c r="L121" t="s">
         <v>520</v>
@@ -8427,23 +8427,23 @@
       <c r="C122" t="s">
         <v>15</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>516</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
+        <v>17</v>
+      </c>
+      <c r="G122" t="s">
+        <v>18</v>
+      </c>
+      <c r="H122" t="s">
         <v>517</v>
       </c>
-      <c r="G122" t="s">
+      <c r="I122" t="s">
         <v>518</v>
       </c>
-      <c r="H122" t="s">
+      <c r="J122" t="s">
         <v>528</v>
-      </c>
-      <c r="I122" t="s">
-        <v>20</v>
-      </c>
-      <c r="K122" t="s">
-        <v>21</v>
       </c>
       <c r="L122" t="s">
         <v>520</v>
@@ -8462,23 +8462,23 @@
       <c r="C123" t="s">
         <v>15</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>516</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>17</v>
+      </c>
+      <c r="G123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H123" t="s">
         <v>517</v>
       </c>
-      <c r="G123" t="s">
+      <c r="I123" t="s">
         <v>518</v>
       </c>
-      <c r="H123" t="s">
+      <c r="J123" t="s">
         <v>532</v>
-      </c>
-      <c r="I123" t="s">
-        <v>20</v>
-      </c>
-      <c r="K123" t="s">
-        <v>21</v>
       </c>
       <c r="L123" t="s">
         <v>520</v>
@@ -8497,23 +8497,23 @@
       <c r="C124" t="s">
         <v>15</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>516</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
+        <v>17</v>
+      </c>
+      <c r="G124" t="s">
+        <v>18</v>
+      </c>
+      <c r="H124" t="s">
         <v>517</v>
       </c>
-      <c r="G124" t="s">
+      <c r="I124" t="s">
         <v>518</v>
       </c>
-      <c r="H124" t="s">
+      <c r="J124" t="s">
         <v>536</v>
-      </c>
-      <c r="I124" t="s">
-        <v>20</v>
-      </c>
-      <c r="K124" t="s">
-        <v>21</v>
       </c>
       <c r="L124" t="s">
         <v>520</v>
@@ -8532,23 +8532,23 @@
       <c r="C125" t="s">
         <v>15</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
+        <v>516</v>
+      </c>
+      <c r="F125" t="s">
+        <v>17</v>
+      </c>
+      <c r="G125" t="s">
+        <v>18</v>
+      </c>
+      <c r="H125" t="s">
         <v>540</v>
       </c>
-      <c r="E125" t="s">
-        <v>517</v>
-      </c>
-      <c r="G125" t="s">
+      <c r="I125" t="s">
         <v>541</v>
       </c>
-      <c r="H125" t="s">
+      <c r="J125" t="s">
         <v>542</v>
-      </c>
-      <c r="I125" t="s">
-        <v>20</v>
-      </c>
-      <c r="K125" t="s">
-        <v>21</v>
       </c>
       <c r="L125" t="s">
         <v>520</v>
@@ -8567,23 +8567,23 @@
       <c r="C126" t="s">
         <v>15</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
+        <v>516</v>
+      </c>
+      <c r="F126" t="s">
+        <v>17</v>
+      </c>
+      <c r="G126" t="s">
+        <v>18</v>
+      </c>
+      <c r="H126" t="s">
         <v>540</v>
       </c>
-      <c r="E126" t="s">
-        <v>517</v>
-      </c>
-      <c r="G126" t="s">
+      <c r="I126" t="s">
         <v>541</v>
       </c>
-      <c r="H126" t="s">
+      <c r="J126" t="s">
         <v>546</v>
-      </c>
-      <c r="I126" t="s">
-        <v>20</v>
-      </c>
-      <c r="K126" t="s">
-        <v>21</v>
       </c>
       <c r="L126" t="s">
         <v>520</v>
@@ -8602,23 +8602,23 @@
       <c r="C127" t="s">
         <v>15</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
+        <v>516</v>
+      </c>
+      <c r="F127" t="s">
+        <v>17</v>
+      </c>
+      <c r="G127" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" t="s">
         <v>540</v>
       </c>
-      <c r="E127" t="s">
-        <v>517</v>
-      </c>
-      <c r="G127" t="s">
+      <c r="I127" t="s">
         <v>541</v>
       </c>
-      <c r="H127" t="s">
+      <c r="J127" t="s">
         <v>550</v>
-      </c>
-      <c r="I127" t="s">
-        <v>20</v>
-      </c>
-      <c r="K127" t="s">
-        <v>21</v>
       </c>
       <c r="L127" t="s">
         <v>520</v>
@@ -8637,23 +8637,23 @@
       <c r="C128" t="s">
         <v>15</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
+        <v>516</v>
+      </c>
+      <c r="F128" t="s">
+        <v>17</v>
+      </c>
+      <c r="G128" t="s">
+        <v>18</v>
+      </c>
+      <c r="H128" t="s">
         <v>540</v>
       </c>
-      <c r="E128" t="s">
-        <v>517</v>
-      </c>
-      <c r="G128" t="s">
+      <c r="I128" t="s">
         <v>541</v>
       </c>
-      <c r="H128" t="s">
+      <c r="J128" t="s">
         <v>554</v>
-      </c>
-      <c r="I128" t="s">
-        <v>20</v>
-      </c>
-      <c r="K128" t="s">
-        <v>21</v>
       </c>
       <c r="L128" t="s">
         <v>520</v>
@@ -8672,23 +8672,23 @@
       <c r="C129" t="s">
         <v>15</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
+        <v>516</v>
+      </c>
+      <c r="F129" t="s">
+        <v>17</v>
+      </c>
+      <c r="G129" t="s">
+        <v>18</v>
+      </c>
+      <c r="H129" t="s">
         <v>540</v>
       </c>
-      <c r="E129" t="s">
-        <v>517</v>
-      </c>
-      <c r="G129" t="s">
+      <c r="I129" t="s">
         <v>541</v>
       </c>
-      <c r="H129" t="s">
+      <c r="J129" t="s">
         <v>558</v>
-      </c>
-      <c r="I129" t="s">
-        <v>20</v>
-      </c>
-      <c r="K129" t="s">
-        <v>21</v>
       </c>
       <c r="L129" t="s">
         <v>520</v>
@@ -8707,23 +8707,23 @@
       <c r="C130" t="s">
         <v>15</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
+        <v>516</v>
+      </c>
+      <c r="F130" t="s">
+        <v>17</v>
+      </c>
+      <c r="G130" t="s">
+        <v>18</v>
+      </c>
+      <c r="H130" t="s">
         <v>540</v>
       </c>
-      <c r="E130" t="s">
-        <v>517</v>
-      </c>
-      <c r="G130" t="s">
+      <c r="I130" t="s">
         <v>541</v>
       </c>
-      <c r="H130" t="s">
+      <c r="J130" t="s">
         <v>562</v>
-      </c>
-      <c r="I130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K130" t="s">
-        <v>21</v>
       </c>
       <c r="L130" t="s">
         <v>520</v>
@@ -8742,23 +8742,23 @@
       <c r="C131" t="s">
         <v>15</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
+        <v>516</v>
+      </c>
+      <c r="F131" t="s">
+        <v>17</v>
+      </c>
+      <c r="G131" t="s">
+        <v>18</v>
+      </c>
+      <c r="H131" t="s">
         <v>540</v>
       </c>
-      <c r="E131" t="s">
-        <v>517</v>
-      </c>
-      <c r="G131" t="s">
+      <c r="I131" t="s">
         <v>541</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
         <v>566</v>
-      </c>
-      <c r="I131" t="s">
-        <v>20</v>
-      </c>
-      <c r="K131" t="s">
-        <v>21</v>
       </c>
       <c r="L131" t="s">
         <v>520</v>
@@ -8777,23 +8777,23 @@
       <c r="C132" t="s">
         <v>15</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
+        <v>516</v>
+      </c>
+      <c r="F132" t="s">
+        <v>17</v>
+      </c>
+      <c r="G132" t="s">
+        <v>18</v>
+      </c>
+      <c r="H132" t="s">
         <v>570</v>
       </c>
-      <c r="E132" t="s">
-        <v>517</v>
-      </c>
-      <c r="G132" t="s">
+      <c r="I132" t="s">
         <v>571</v>
       </c>
-      <c r="H132" t="s">
+      <c r="J132" t="s">
         <v>572</v>
-      </c>
-      <c r="I132" t="s">
-        <v>20</v>
-      </c>
-      <c r="K132" t="s">
-        <v>21</v>
       </c>
       <c r="L132" t="s">
         <v>520</v>
@@ -8812,23 +8812,23 @@
       <c r="C133" t="s">
         <v>15</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>516</v>
+      </c>
+      <c r="F133" t="s">
+        <v>17</v>
+      </c>
+      <c r="G133" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133" t="s">
         <v>570</v>
       </c>
-      <c r="E133" t="s">
-        <v>517</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="I133" t="s">
         <v>571</v>
       </c>
-      <c r="H133" t="s">
+      <c r="J133" t="s">
         <v>576</v>
-      </c>
-      <c r="I133" t="s">
-        <v>20</v>
-      </c>
-      <c r="K133" t="s">
-        <v>21</v>
       </c>
       <c r="L133" t="s">
         <v>520</v>
@@ -8847,23 +8847,23 @@
       <c r="C134" t="s">
         <v>15</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
+        <v>516</v>
+      </c>
+      <c r="F134" t="s">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134" t="s">
         <v>570</v>
       </c>
-      <c r="E134" t="s">
-        <v>517</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="I134" t="s">
         <v>571</v>
       </c>
-      <c r="H134" t="s">
+      <c r="J134" t="s">
         <v>580</v>
-      </c>
-      <c r="I134" t="s">
-        <v>20</v>
-      </c>
-      <c r="K134" t="s">
-        <v>21</v>
       </c>
       <c r="L134" t="s">
         <v>520</v>
@@ -8882,23 +8882,23 @@
       <c r="C135" t="s">
         <v>15</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
+        <v>516</v>
+      </c>
+      <c r="F135" t="s">
+        <v>17</v>
+      </c>
+      <c r="G135" t="s">
+        <v>18</v>
+      </c>
+      <c r="H135" t="s">
         <v>570</v>
       </c>
-      <c r="E135" t="s">
-        <v>517</v>
-      </c>
-      <c r="G135" t="s">
+      <c r="I135" t="s">
         <v>571</v>
       </c>
-      <c r="H135" t="s">
+      <c r="J135" t="s">
         <v>584</v>
-      </c>
-      <c r="I135" t="s">
-        <v>20</v>
-      </c>
-      <c r="K135" t="s">
-        <v>21</v>
       </c>
       <c r="L135" t="s">
         <v>520</v>
@@ -8917,23 +8917,23 @@
       <c r="C136" t="s">
         <v>15</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
+        <v>516</v>
+      </c>
+      <c r="F136" t="s">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s">
+        <v>18</v>
+      </c>
+      <c r="H136" t="s">
         <v>570</v>
       </c>
-      <c r="E136" t="s">
-        <v>517</v>
-      </c>
-      <c r="G136" t="s">
+      <c r="I136" t="s">
         <v>571</v>
       </c>
-      <c r="H136" t="s">
+      <c r="J136" t="s">
         <v>588</v>
-      </c>
-      <c r="I136" t="s">
-        <v>20</v>
-      </c>
-      <c r="K136" t="s">
-        <v>21</v>
       </c>
       <c r="L136" t="s">
         <v>520</v>
@@ -8952,23 +8952,23 @@
       <c r="C137" t="s">
         <v>15</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
+        <v>516</v>
+      </c>
+      <c r="F137" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" t="s">
+        <v>18</v>
+      </c>
+      <c r="H137" t="s">
         <v>570</v>
       </c>
-      <c r="E137" t="s">
-        <v>517</v>
-      </c>
-      <c r="G137" t="s">
+      <c r="I137" t="s">
         <v>571</v>
       </c>
-      <c r="H137" t="s">
+      <c r="J137" t="s">
         <v>592</v>
-      </c>
-      <c r="I137" t="s">
-        <v>20</v>
-      </c>
-      <c r="K137" t="s">
-        <v>21</v>
       </c>
       <c r="L137" t="s">
         <v>520</v>
@@ -8987,23 +8987,23 @@
       <c r="C138" t="s">
         <v>15</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
+        <v>516</v>
+      </c>
+      <c r="F138" t="s">
+        <v>17</v>
+      </c>
+      <c r="G138" t="s">
+        <v>18</v>
+      </c>
+      <c r="H138" t="s">
         <v>570</v>
       </c>
-      <c r="E138" t="s">
-        <v>517</v>
-      </c>
-      <c r="G138" t="s">
+      <c r="I138" t="s">
         <v>571</v>
       </c>
-      <c r="H138" t="s">
+      <c r="J138" t="s">
         <v>596</v>
-      </c>
-      <c r="I138" t="s">
-        <v>20</v>
-      </c>
-      <c r="K138" t="s">
-        <v>21</v>
       </c>
       <c r="L138" t="s">
         <v>520</v>
@@ -9022,23 +9022,23 @@
       <c r="C139" t="s">
         <v>15</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
+        <v>516</v>
+      </c>
+      <c r="F139" t="s">
+        <v>17</v>
+      </c>
+      <c r="G139" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139" t="s">
         <v>570</v>
       </c>
-      <c r="E139" t="s">
-        <v>517</v>
-      </c>
-      <c r="G139" t="s">
+      <c r="I139" t="s">
         <v>571</v>
       </c>
-      <c r="H139" t="s">
+      <c r="J139" t="s">
         <v>600</v>
-      </c>
-      <c r="I139" t="s">
-        <v>20</v>
-      </c>
-      <c r="K139" t="s">
-        <v>21</v>
       </c>
       <c r="L139" t="s">
         <v>520</v>
@@ -9057,23 +9057,23 @@
       <c r="C140" t="s">
         <v>15</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
+        <v>516</v>
+      </c>
+      <c r="F140" t="s">
+        <v>17</v>
+      </c>
+      <c r="G140" t="s">
+        <v>18</v>
+      </c>
+      <c r="H140" t="s">
         <v>570</v>
       </c>
-      <c r="E140" t="s">
-        <v>517</v>
-      </c>
-      <c r="G140" t="s">
+      <c r="I140" t="s">
         <v>571</v>
       </c>
-      <c r="H140" t="s">
+      <c r="J140" t="s">
         <v>604</v>
-      </c>
-      <c r="I140" t="s">
-        <v>20</v>
-      </c>
-      <c r="K140" t="s">
-        <v>21</v>
       </c>
       <c r="L140" t="s">
         <v>520</v>
@@ -9092,23 +9092,23 @@
       <c r="C141" t="s">
         <v>15</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
+        <v>516</v>
+      </c>
+      <c r="F141" t="s">
+        <v>17</v>
+      </c>
+      <c r="G141" t="s">
+        <v>18</v>
+      </c>
+      <c r="H141" t="s">
         <v>570</v>
       </c>
-      <c r="E141" t="s">
-        <v>517</v>
-      </c>
-      <c r="G141" t="s">
+      <c r="I141" t="s">
         <v>571</v>
       </c>
-      <c r="H141" t="s">
+      <c r="J141" t="s">
         <v>608</v>
-      </c>
-      <c r="I141" t="s">
-        <v>20</v>
-      </c>
-      <c r="K141" t="s">
-        <v>21</v>
       </c>
       <c r="L141" t="s">
         <v>520</v>
@@ -9127,23 +9127,23 @@
       <c r="C142" t="s">
         <v>15</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
+        <v>516</v>
+      </c>
+      <c r="F142" t="s">
+        <v>17</v>
+      </c>
+      <c r="G142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H142" t="s">
         <v>570</v>
       </c>
-      <c r="E142" t="s">
-        <v>517</v>
-      </c>
-      <c r="G142" t="s">
+      <c r="I142" t="s">
         <v>571</v>
       </c>
-      <c r="H142" t="s">
+      <c r="J142" t="s">
         <v>612</v>
-      </c>
-      <c r="I142" t="s">
-        <v>20</v>
-      </c>
-      <c r="K142" t="s">
-        <v>21</v>
       </c>
       <c r="L142" t="s">
         <v>520</v>
@@ -9162,23 +9162,23 @@
       <c r="C143" t="s">
         <v>15</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
+        <v>516</v>
+      </c>
+      <c r="F143" t="s">
+        <v>17</v>
+      </c>
+      <c r="G143" t="s">
+        <v>18</v>
+      </c>
+      <c r="H143" t="s">
         <v>616</v>
       </c>
-      <c r="E143" t="s">
-        <v>517</v>
-      </c>
-      <c r="G143" t="s">
+      <c r="I143" t="s">
         <v>617</v>
       </c>
-      <c r="H143" t="s">
+      <c r="J143" t="s">
         <v>618</v>
-      </c>
-      <c r="I143" t="s">
-        <v>20</v>
-      </c>
-      <c r="K143" t="s">
-        <v>21</v>
       </c>
       <c r="L143" t="s">
         <v>520</v>
@@ -9197,23 +9197,23 @@
       <c r="C144" t="s">
         <v>15</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
+        <v>516</v>
+      </c>
+      <c r="F144" t="s">
+        <v>17</v>
+      </c>
+      <c r="G144" t="s">
+        <v>18</v>
+      </c>
+      <c r="H144" t="s">
         <v>616</v>
       </c>
-      <c r="E144" t="s">
-        <v>517</v>
-      </c>
-      <c r="G144" t="s">
+      <c r="I144" t="s">
         <v>617</v>
       </c>
-      <c r="H144" t="s">
+      <c r="J144" t="s">
         <v>622</v>
-      </c>
-      <c r="I144" t="s">
-        <v>20</v>
-      </c>
-      <c r="K144" t="s">
-        <v>21</v>
       </c>
       <c r="L144" t="s">
         <v>520</v>
@@ -9232,23 +9232,23 @@
       <c r="C145" t="s">
         <v>15</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
+        <v>516</v>
+      </c>
+      <c r="F145" t="s">
+        <v>17</v>
+      </c>
+      <c r="G145" t="s">
+        <v>18</v>
+      </c>
+      <c r="H145" t="s">
         <v>616</v>
       </c>
-      <c r="E145" t="s">
-        <v>517</v>
-      </c>
-      <c r="G145" t="s">
+      <c r="I145" t="s">
         <v>617</v>
       </c>
-      <c r="H145" t="s">
+      <c r="J145" t="s">
         <v>626</v>
-      </c>
-      <c r="I145" t="s">
-        <v>20</v>
-      </c>
-      <c r="K145" t="s">
-        <v>21</v>
       </c>
       <c r="L145" t="s">
         <v>520</v>
@@ -9267,23 +9267,23 @@
       <c r="C146" t="s">
         <v>15</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
+        <v>516</v>
+      </c>
+      <c r="F146" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" t="s">
+        <v>18</v>
+      </c>
+      <c r="H146" t="s">
         <v>616</v>
       </c>
-      <c r="E146" t="s">
-        <v>517</v>
-      </c>
-      <c r="G146" t="s">
+      <c r="I146" t="s">
         <v>617</v>
       </c>
-      <c r="H146" t="s">
+      <c r="J146" t="s">
         <v>630</v>
-      </c>
-      <c r="I146" t="s">
-        <v>20</v>
-      </c>
-      <c r="K146" t="s">
-        <v>21</v>
       </c>
       <c r="L146" t="s">
         <v>520</v>
@@ -9302,23 +9302,23 @@
       <c r="C147" t="s">
         <v>15</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
+        <v>516</v>
+      </c>
+      <c r="F147" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" t="s">
+        <v>18</v>
+      </c>
+      <c r="H147" t="s">
         <v>616</v>
       </c>
-      <c r="E147" t="s">
-        <v>517</v>
-      </c>
-      <c r="G147" t="s">
+      <c r="I147" t="s">
         <v>617</v>
       </c>
-      <c r="H147" t="s">
+      <c r="J147" t="s">
         <v>634</v>
-      </c>
-      <c r="I147" t="s">
-        <v>20</v>
-      </c>
-      <c r="K147" t="s">
-        <v>21</v>
       </c>
       <c r="L147" t="s">
         <v>520</v>
@@ -9337,23 +9337,23 @@
       <c r="C148" t="s">
         <v>15</v>
       </c>
-      <c r="D148" t="s">
+      <c r="E148" t="s">
+        <v>516</v>
+      </c>
+      <c r="F148" t="s">
+        <v>17</v>
+      </c>
+      <c r="G148" t="s">
+        <v>18</v>
+      </c>
+      <c r="H148" t="s">
         <v>616</v>
       </c>
-      <c r="E148" t="s">
-        <v>517</v>
-      </c>
-      <c r="G148" t="s">
+      <c r="I148" t="s">
         <v>617</v>
       </c>
-      <c r="H148" t="s">
+      <c r="J148" t="s">
         <v>638</v>
-      </c>
-      <c r="I148" t="s">
-        <v>20</v>
-      </c>
-      <c r="K148" t="s">
-        <v>21</v>
       </c>
       <c r="L148" t="s">
         <v>520</v>
@@ -9372,23 +9372,23 @@
       <c r="C149" t="s">
         <v>15</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
+        <v>516</v>
+      </c>
+      <c r="F149" t="s">
+        <v>17</v>
+      </c>
+      <c r="G149" t="s">
+        <v>18</v>
+      </c>
+      <c r="H149" t="s">
         <v>616</v>
       </c>
-      <c r="E149" t="s">
-        <v>517</v>
-      </c>
-      <c r="G149" t="s">
+      <c r="I149" t="s">
         <v>617</v>
       </c>
-      <c r="H149" t="s">
+      <c r="J149" t="s">
         <v>642</v>
-      </c>
-      <c r="I149" t="s">
-        <v>20</v>
-      </c>
-      <c r="K149" t="s">
-        <v>21</v>
       </c>
       <c r="L149" t="s">
         <v>520</v>
@@ -9407,23 +9407,23 @@
       <c r="C150" t="s">
         <v>15</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
+        <v>516</v>
+      </c>
+      <c r="F150" t="s">
+        <v>17</v>
+      </c>
+      <c r="G150" t="s">
+        <v>18</v>
+      </c>
+      <c r="H150" t="s">
         <v>616</v>
       </c>
-      <c r="E150" t="s">
-        <v>517</v>
-      </c>
-      <c r="G150" t="s">
+      <c r="I150" t="s">
         <v>617</v>
       </c>
-      <c r="H150" t="s">
+      <c r="J150" t="s">
         <v>646</v>
-      </c>
-      <c r="I150" t="s">
-        <v>20</v>
-      </c>
-      <c r="K150" t="s">
-        <v>21</v>
       </c>
       <c r="L150" t="s">
         <v>520</v>
@@ -9442,23 +9442,23 @@
       <c r="C151" t="s">
         <v>15</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
+        <v>516</v>
+      </c>
+      <c r="F151" t="s">
+        <v>17</v>
+      </c>
+      <c r="G151" t="s">
+        <v>18</v>
+      </c>
+      <c r="H151" t="s">
         <v>616</v>
       </c>
-      <c r="E151" t="s">
-        <v>517</v>
-      </c>
-      <c r="G151" t="s">
+      <c r="I151" t="s">
         <v>617</v>
       </c>
-      <c r="H151" t="s">
+      <c r="J151" t="s">
         <v>650</v>
-      </c>
-      <c r="I151" t="s">
-        <v>20</v>
-      </c>
-      <c r="K151" t="s">
-        <v>21</v>
       </c>
       <c r="L151" t="s">
         <v>520</v>
@@ -9477,23 +9477,23 @@
       <c r="C152" t="s">
         <v>15</v>
       </c>
-      <c r="D152" t="s">
+      <c r="E152" t="s">
+        <v>516</v>
+      </c>
+      <c r="F152" t="s">
+        <v>17</v>
+      </c>
+      <c r="G152" t="s">
+        <v>18</v>
+      </c>
+      <c r="H152" t="s">
         <v>654</v>
       </c>
-      <c r="E152" t="s">
-        <v>517</v>
-      </c>
-      <c r="G152" t="s">
+      <c r="I152" t="s">
         <v>655</v>
       </c>
-      <c r="H152" t="s">
+      <c r="J152" t="s">
         <v>656</v>
-      </c>
-      <c r="I152" t="s">
-        <v>20</v>
-      </c>
-      <c r="K152" t="s">
-        <v>21</v>
       </c>
       <c r="L152" t="s">
         <v>520</v>
@@ -9512,23 +9512,23 @@
       <c r="C153" t="s">
         <v>15</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
+        <v>516</v>
+      </c>
+      <c r="F153" t="s">
+        <v>17</v>
+      </c>
+      <c r="G153" t="s">
+        <v>18</v>
+      </c>
+      <c r="H153" t="s">
         <v>654</v>
       </c>
-      <c r="E153" t="s">
-        <v>517</v>
-      </c>
-      <c r="G153" t="s">
+      <c r="I153" t="s">
         <v>655</v>
       </c>
-      <c r="H153" t="s">
+      <c r="J153" t="s">
         <v>660</v>
-      </c>
-      <c r="I153" t="s">
-        <v>20</v>
-      </c>
-      <c r="K153" t="s">
-        <v>21</v>
       </c>
       <c r="L153" t="s">
         <v>520</v>
@@ -9547,23 +9547,23 @@
       <c r="C154" t="s">
         <v>15</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
+        <v>516</v>
+      </c>
+      <c r="F154" t="s">
+        <v>17</v>
+      </c>
+      <c r="G154" t="s">
+        <v>18</v>
+      </c>
+      <c r="H154" t="s">
         <v>654</v>
       </c>
-      <c r="E154" t="s">
-        <v>517</v>
-      </c>
-      <c r="G154" t="s">
+      <c r="I154" t="s">
         <v>655</v>
       </c>
-      <c r="H154" t="s">
+      <c r="J154" t="s">
         <v>664</v>
-      </c>
-      <c r="I154" t="s">
-        <v>20</v>
-      </c>
-      <c r="K154" t="s">
-        <v>21</v>
       </c>
       <c r="L154" t="s">
         <v>520</v>
@@ -9582,23 +9582,23 @@
       <c r="C155" t="s">
         <v>15</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
+        <v>516</v>
+      </c>
+      <c r="F155" t="s">
+        <v>17</v>
+      </c>
+      <c r="G155" t="s">
+        <v>18</v>
+      </c>
+      <c r="H155" t="s">
         <v>654</v>
       </c>
-      <c r="E155" t="s">
-        <v>517</v>
-      </c>
-      <c r="G155" t="s">
+      <c r="I155" t="s">
         <v>655</v>
       </c>
-      <c r="H155" t="s">
+      <c r="J155" t="s">
         <v>668</v>
-      </c>
-      <c r="I155" t="s">
-        <v>20</v>
-      </c>
-      <c r="K155" t="s">
-        <v>21</v>
       </c>
       <c r="L155" t="s">
         <v>520</v>
@@ -9617,23 +9617,23 @@
       <c r="C156" t="s">
         <v>15</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
+        <v>516</v>
+      </c>
+      <c r="F156" t="s">
+        <v>17</v>
+      </c>
+      <c r="G156" t="s">
+        <v>18</v>
+      </c>
+      <c r="H156" t="s">
         <v>654</v>
       </c>
-      <c r="E156" t="s">
-        <v>517</v>
-      </c>
-      <c r="G156" t="s">
+      <c r="I156" t="s">
         <v>655</v>
       </c>
-      <c r="H156" t="s">
+      <c r="J156" t="s">
         <v>672</v>
-      </c>
-      <c r="I156" t="s">
-        <v>20</v>
-      </c>
-      <c r="K156" t="s">
-        <v>21</v>
       </c>
       <c r="L156" t="s">
         <v>520</v>
@@ -9652,23 +9652,23 @@
       <c r="C157" t="s">
         <v>15</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
+        <v>516</v>
+      </c>
+      <c r="F157" t="s">
+        <v>17</v>
+      </c>
+      <c r="G157" t="s">
+        <v>18</v>
+      </c>
+      <c r="H157" t="s">
         <v>654</v>
       </c>
-      <c r="E157" t="s">
-        <v>517</v>
-      </c>
-      <c r="G157" t="s">
+      <c r="I157" t="s">
         <v>655</v>
       </c>
-      <c r="H157" t="s">
+      <c r="J157" t="s">
         <v>676</v>
-      </c>
-      <c r="I157" t="s">
-        <v>20</v>
-      </c>
-      <c r="K157" t="s">
-        <v>21</v>
       </c>
       <c r="L157" t="s">
         <v>520</v>
@@ -9687,23 +9687,23 @@
       <c r="C158" t="s">
         <v>15</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>516</v>
+      </c>
+      <c r="F158" t="s">
+        <v>17</v>
+      </c>
+      <c r="G158" t="s">
+        <v>18</v>
+      </c>
+      <c r="H158" t="s">
         <v>654</v>
       </c>
-      <c r="E158" t="s">
-        <v>517</v>
-      </c>
-      <c r="G158" t="s">
+      <c r="I158" t="s">
         <v>655</v>
       </c>
-      <c r="H158" t="s">
+      <c r="J158" t="s">
         <v>680</v>
-      </c>
-      <c r="I158" t="s">
-        <v>20</v>
-      </c>
-      <c r="K158" t="s">
-        <v>21</v>
       </c>
       <c r="L158" t="s">
         <v>520</v>
@@ -9722,23 +9722,23 @@
       <c r="C159" t="s">
         <v>15</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
+        <v>516</v>
+      </c>
+      <c r="F159" t="s">
+        <v>17</v>
+      </c>
+      <c r="G159" t="s">
+        <v>18</v>
+      </c>
+      <c r="H159" t="s">
         <v>654</v>
       </c>
-      <c r="E159" t="s">
-        <v>517</v>
-      </c>
-      <c r="G159" t="s">
+      <c r="I159" t="s">
         <v>655</v>
       </c>
-      <c r="H159" t="s">
+      <c r="J159" t="s">
         <v>684</v>
-      </c>
-      <c r="I159" t="s">
-        <v>20</v>
-      </c>
-      <c r="K159" t="s">
-        <v>21</v>
       </c>
       <c r="L159" t="s">
         <v>520</v>
@@ -9757,23 +9757,23 @@
       <c r="C160" t="s">
         <v>15</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
+        <v>516</v>
+      </c>
+      <c r="F160" t="s">
+        <v>17</v>
+      </c>
+      <c r="G160" t="s">
+        <v>18</v>
+      </c>
+      <c r="H160" t="s">
         <v>654</v>
       </c>
-      <c r="E160" t="s">
-        <v>517</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="I160" t="s">
         <v>655</v>
       </c>
-      <c r="H160" t="s">
+      <c r="J160" t="s">
         <v>688</v>
-      </c>
-      <c r="I160" t="s">
-        <v>20</v>
-      </c>
-      <c r="K160" t="s">
-        <v>21</v>
       </c>
       <c r="L160" t="s">
         <v>520</v>
@@ -9792,23 +9792,23 @@
       <c r="C161" t="s">
         <v>15</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
+        <v>516</v>
+      </c>
+      <c r="F161" t="s">
+        <v>17</v>
+      </c>
+      <c r="G161" t="s">
+        <v>18</v>
+      </c>
+      <c r="H161" t="s">
         <v>654</v>
       </c>
-      <c r="E161" t="s">
-        <v>517</v>
-      </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
         <v>655</v>
       </c>
-      <c r="H161" t="s">
+      <c r="J161" t="s">
         <v>692</v>
-      </c>
-      <c r="I161" t="s">
-        <v>20</v>
-      </c>
-      <c r="K161" t="s">
-        <v>21</v>
       </c>
       <c r="L161" t="s">
         <v>520</v>
@@ -9827,23 +9827,23 @@
       <c r="C162" t="s">
         <v>15</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
+        <v>516</v>
+      </c>
+      <c r="F162" t="s">
+        <v>17</v>
+      </c>
+      <c r="G162" t="s">
+        <v>18</v>
+      </c>
+      <c r="H162" t="s">
         <v>654</v>
       </c>
-      <c r="E162" t="s">
-        <v>517</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="I162" t="s">
         <v>655</v>
       </c>
-      <c r="H162" t="s">
+      <c r="J162" t="s">
         <v>696</v>
-      </c>
-      <c r="I162" t="s">
-        <v>20</v>
-      </c>
-      <c r="K162" t="s">
-        <v>21</v>
       </c>
       <c r="L162" t="s">
         <v>520</v>
@@ -9862,23 +9862,23 @@
       <c r="C163" t="s">
         <v>15</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
+        <v>516</v>
+      </c>
+      <c r="F163" t="s">
+        <v>17</v>
+      </c>
+      <c r="G163" t="s">
+        <v>18</v>
+      </c>
+      <c r="H163" t="s">
         <v>654</v>
       </c>
-      <c r="E163" t="s">
-        <v>517</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
         <v>655</v>
       </c>
-      <c r="H163" t="s">
+      <c r="J163" t="s">
         <v>700</v>
-      </c>
-      <c r="I163" t="s">
-        <v>20</v>
-      </c>
-      <c r="K163" t="s">
-        <v>21</v>
       </c>
       <c r="L163" t="s">
         <v>520</v>
@@ -9897,23 +9897,23 @@
       <c r="C164" t="s">
         <v>15</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
+        <v>516</v>
+      </c>
+      <c r="F164" t="s">
+        <v>17</v>
+      </c>
+      <c r="G164" t="s">
+        <v>18</v>
+      </c>
+      <c r="H164" t="s">
         <v>654</v>
       </c>
-      <c r="E164" t="s">
-        <v>517</v>
-      </c>
-      <c r="G164" t="s">
+      <c r="I164" t="s">
         <v>655</v>
       </c>
-      <c r="H164" t="s">
+      <c r="J164" t="s">
         <v>704</v>
-      </c>
-      <c r="I164" t="s">
-        <v>20</v>
-      </c>
-      <c r="K164" t="s">
-        <v>21</v>
       </c>
       <c r="L164" t="s">
         <v>520</v>
@@ -9932,23 +9932,23 @@
       <c r="C165" t="s">
         <v>15</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
+        <v>516</v>
+      </c>
+      <c r="F165" t="s">
+        <v>17</v>
+      </c>
+      <c r="G165" t="s">
+        <v>18</v>
+      </c>
+      <c r="H165" t="s">
         <v>654</v>
       </c>
-      <c r="E165" t="s">
-        <v>517</v>
-      </c>
-      <c r="G165" t="s">
+      <c r="I165" t="s">
         <v>655</v>
       </c>
-      <c r="H165" t="s">
+      <c r="J165" t="s">
         <v>708</v>
-      </c>
-      <c r="I165" t="s">
-        <v>20</v>
-      </c>
-      <c r="K165" t="s">
-        <v>21</v>
       </c>
       <c r="L165" t="s">
         <v>520</v>
@@ -9967,23 +9967,23 @@
       <c r="C166" t="s">
         <v>15</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
+        <v>516</v>
+      </c>
+      <c r="F166" t="s">
+        <v>17</v>
+      </c>
+      <c r="G166" t="s">
+        <v>18</v>
+      </c>
+      <c r="H166" t="s">
         <v>654</v>
       </c>
-      <c r="E166" t="s">
-        <v>517</v>
-      </c>
-      <c r="G166" t="s">
+      <c r="I166" t="s">
         <v>655</v>
       </c>
-      <c r="H166" t="s">
+      <c r="J166" t="s">
         <v>712</v>
-      </c>
-      <c r="I166" t="s">
-        <v>20</v>
-      </c>
-      <c r="K166" t="s">
-        <v>21</v>
       </c>
       <c r="L166" t="s">
         <v>520</v>
@@ -10002,23 +10002,23 @@
       <c r="C167" t="s">
         <v>15</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
+        <v>516</v>
+      </c>
+      <c r="F167" t="s">
+        <v>17</v>
+      </c>
+      <c r="G167" t="s">
+        <v>18</v>
+      </c>
+      <c r="H167" t="s">
         <v>654</v>
       </c>
-      <c r="E167" t="s">
-        <v>517</v>
-      </c>
-      <c r="G167" t="s">
+      <c r="I167" t="s">
         <v>655</v>
       </c>
-      <c r="H167" t="s">
+      <c r="J167" t="s">
         <v>716</v>
-      </c>
-      <c r="I167" t="s">
-        <v>20</v>
-      </c>
-      <c r="K167" t="s">
-        <v>21</v>
       </c>
       <c r="L167" t="s">
         <v>520</v>
@@ -10037,23 +10037,23 @@
       <c r="C168" t="s">
         <v>15</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
+        <v>516</v>
+      </c>
+      <c r="F168" t="s">
+        <v>17</v>
+      </c>
+      <c r="G168" t="s">
+        <v>18</v>
+      </c>
+      <c r="H168" t="s">
         <v>654</v>
       </c>
-      <c r="E168" t="s">
-        <v>517</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="I168" t="s">
         <v>655</v>
       </c>
-      <c r="H168" t="s">
+      <c r="J168" t="s">
         <v>720</v>
-      </c>
-      <c r="I168" t="s">
-        <v>20</v>
-      </c>
-      <c r="K168" t="s">
-        <v>21</v>
       </c>
       <c r="L168" t="s">
         <v>520</v>
@@ -10072,23 +10072,23 @@
       <c r="C169" t="s">
         <v>15</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
+        <v>516</v>
+      </c>
+      <c r="F169" t="s">
+        <v>17</v>
+      </c>
+      <c r="G169" t="s">
+        <v>18</v>
+      </c>
+      <c r="H169" t="s">
         <v>654</v>
       </c>
-      <c r="E169" t="s">
-        <v>517</v>
-      </c>
-      <c r="G169" t="s">
+      <c r="I169" t="s">
         <v>655</v>
       </c>
-      <c r="H169" t="s">
+      <c r="J169" t="s">
         <v>724</v>
-      </c>
-      <c r="I169" t="s">
-        <v>20</v>
-      </c>
-      <c r="K169" t="s">
-        <v>21</v>
       </c>
       <c r="L169" t="s">
         <v>520</v>
@@ -10107,23 +10107,23 @@
       <c r="C170" t="s">
         <v>15</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
         <v>728</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
+        <v>17</v>
+      </c>
+      <c r="G170" t="s">
+        <v>18</v>
+      </c>
+      <c r="H170" t="s">
         <v>729</v>
       </c>
-      <c r="G170" t="s">
+      <c r="I170" t="s">
         <v>730</v>
       </c>
-      <c r="H170" t="s">
+      <c r="J170" t="s">
         <v>731</v>
-      </c>
-      <c r="I170" t="s">
-        <v>20</v>
-      </c>
-      <c r="K170" t="s">
-        <v>21</v>
       </c>
       <c r="L170" t="s">
         <v>732</v>
@@ -10142,23 +10142,23 @@
       <c r="C171" t="s">
         <v>15</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>728</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
+        <v>17</v>
+      </c>
+      <c r="G171" t="s">
+        <v>18</v>
+      </c>
+      <c r="H171" t="s">
         <v>729</v>
       </c>
-      <c r="G171" t="s">
+      <c r="I171" t="s">
         <v>730</v>
       </c>
-      <c r="H171" t="s">
+      <c r="J171" t="s">
         <v>736</v>
-      </c>
-      <c r="I171" t="s">
-        <v>20</v>
-      </c>
-      <c r="K171" t="s">
-        <v>21</v>
       </c>
       <c r="L171" t="s">
         <v>732</v>
@@ -10177,23 +10177,23 @@
       <c r="C172" t="s">
         <v>15</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>728</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
+        <v>17</v>
+      </c>
+      <c r="G172" t="s">
+        <v>18</v>
+      </c>
+      <c r="H172" t="s">
         <v>729</v>
       </c>
-      <c r="G172" t="s">
+      <c r="I172" t="s">
         <v>730</v>
       </c>
-      <c r="H172" t="s">
+      <c r="J172" t="s">
         <v>740</v>
-      </c>
-      <c r="I172" t="s">
-        <v>20</v>
-      </c>
-      <c r="K172" t="s">
-        <v>21</v>
       </c>
       <c r="L172" t="s">
         <v>732</v>
@@ -10212,23 +10212,23 @@
       <c r="C173" t="s">
         <v>15</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>728</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
+        <v>17</v>
+      </c>
+      <c r="G173" t="s">
+        <v>18</v>
+      </c>
+      <c r="H173" t="s">
         <v>729</v>
       </c>
-      <c r="G173" t="s">
+      <c r="I173" t="s">
         <v>730</v>
       </c>
-      <c r="H173" t="s">
+      <c r="J173" t="s">
         <v>744</v>
-      </c>
-      <c r="I173" t="s">
-        <v>20</v>
-      </c>
-      <c r="K173" t="s">
-        <v>21</v>
       </c>
       <c r="L173" t="s">
         <v>732</v>
@@ -10247,23 +10247,23 @@
       <c r="C174" t="s">
         <v>15</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>728</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
+        <v>17</v>
+      </c>
+      <c r="G174" t="s">
+        <v>18</v>
+      </c>
+      <c r="H174" t="s">
         <v>729</v>
       </c>
-      <c r="G174" t="s">
+      <c r="I174" t="s">
         <v>730</v>
       </c>
-      <c r="H174" t="s">
+      <c r="J174" t="s">
         <v>748</v>
-      </c>
-      <c r="I174" t="s">
-        <v>20</v>
-      </c>
-      <c r="K174" t="s">
-        <v>21</v>
       </c>
       <c r="L174" t="s">
         <v>732</v>
@@ -10282,23 +10282,23 @@
       <c r="C175" t="s">
         <v>15</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>728</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
+        <v>17</v>
+      </c>
+      <c r="G175" t="s">
+        <v>18</v>
+      </c>
+      <c r="H175" t="s">
         <v>729</v>
       </c>
-      <c r="G175" t="s">
+      <c r="I175" t="s">
         <v>730</v>
       </c>
-      <c r="H175" t="s">
+      <c r="J175" t="s">
         <v>752</v>
-      </c>
-      <c r="I175" t="s">
-        <v>20</v>
-      </c>
-      <c r="K175" t="s">
-        <v>21</v>
       </c>
       <c r="L175" t="s">
         <v>732</v>
@@ -10317,23 +10317,23 @@
       <c r="C176" t="s">
         <v>15</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>728</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
+        <v>17</v>
+      </c>
+      <c r="G176" t="s">
+        <v>18</v>
+      </c>
+      <c r="H176" t="s">
         <v>729</v>
       </c>
-      <c r="G176" t="s">
+      <c r="I176" t="s">
         <v>730</v>
       </c>
-      <c r="H176" t="s">
+      <c r="J176" t="s">
         <v>756</v>
-      </c>
-      <c r="I176" t="s">
-        <v>20</v>
-      </c>
-      <c r="K176" t="s">
-        <v>21</v>
       </c>
       <c r="L176" t="s">
         <v>732</v>
@@ -10352,23 +10352,23 @@
       <c r="C177" t="s">
         <v>15</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>728</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
+        <v>17</v>
+      </c>
+      <c r="G177" t="s">
+        <v>18</v>
+      </c>
+      <c r="H177" t="s">
         <v>729</v>
       </c>
-      <c r="G177" t="s">
+      <c r="I177" t="s">
         <v>730</v>
       </c>
-      <c r="H177" t="s">
+      <c r="J177" t="s">
         <v>760</v>
-      </c>
-      <c r="I177" t="s">
-        <v>20</v>
-      </c>
-      <c r="K177" t="s">
-        <v>21</v>
       </c>
       <c r="L177" t="s">
         <v>732</v>
@@ -10387,23 +10387,23 @@
       <c r="C178" t="s">
         <v>15</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>728</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
+        <v>17</v>
+      </c>
+      <c r="G178" t="s">
+        <v>18</v>
+      </c>
+      <c r="H178" t="s">
         <v>729</v>
       </c>
-      <c r="G178" t="s">
+      <c r="I178" t="s">
         <v>730</v>
       </c>
-      <c r="H178" t="s">
+      <c r="J178" t="s">
         <v>764</v>
-      </c>
-      <c r="I178" t="s">
-        <v>20</v>
-      </c>
-      <c r="K178" t="s">
-        <v>21</v>
       </c>
       <c r="L178" t="s">
         <v>732</v>
@@ -10422,23 +10422,23 @@
       <c r="C179" t="s">
         <v>15</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>728</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
+        <v>17</v>
+      </c>
+      <c r="G179" t="s">
+        <v>18</v>
+      </c>
+      <c r="H179" t="s">
         <v>729</v>
       </c>
-      <c r="G179" t="s">
+      <c r="I179" t="s">
         <v>730</v>
       </c>
-      <c r="H179" t="s">
+      <c r="J179" t="s">
         <v>768</v>
-      </c>
-      <c r="I179" t="s">
-        <v>20</v>
-      </c>
-      <c r="K179" t="s">
-        <v>21</v>
       </c>
       <c r="L179" t="s">
         <v>732</v>
@@ -10457,23 +10457,23 @@
       <c r="C180" t="s">
         <v>15</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
+        <v>728</v>
+      </c>
+      <c r="F180" t="s">
+        <v>17</v>
+      </c>
+      <c r="G180" t="s">
+        <v>18</v>
+      </c>
+      <c r="H180" t="s">
         <v>772</v>
       </c>
-      <c r="E180" t="s">
-        <v>729</v>
-      </c>
-      <c r="G180" t="s">
+      <c r="I180" t="s">
         <v>773</v>
       </c>
-      <c r="H180" t="s">
+      <c r="J180" t="s">
         <v>774</v>
-      </c>
-      <c r="I180" t="s">
-        <v>20</v>
-      </c>
-      <c r="K180" t="s">
-        <v>21</v>
       </c>
       <c r="L180" t="s">
         <v>732</v>
@@ -10493,28 +10493,28 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
+        <v>778</v>
+      </c>
+      <c r="E181" t="s">
+        <v>728</v>
+      </c>
+      <c r="F181" t="s">
+        <v>17</v>
+      </c>
+      <c r="G181" t="s">
+        <v>18</v>
+      </c>
+      <c r="H181" t="s">
         <v>772</v>
       </c>
-      <c r="E181" t="s">
-        <v>729</v>
-      </c>
-      <c r="F181" t="s">
-        <v>778</v>
-      </c>
-      <c r="G181" t="s">
+      <c r="I181" t="s">
         <v>773</v>
       </c>
-      <c r="H181" t="s">
+      <c r="J181" t="s">
         <v>779</v>
       </c>
-      <c r="I181" t="s">
-        <v>20</v>
-      </c>
-      <c r="J181" t="s">
+      <c r="K181" t="s">
         <v>780</v>
-      </c>
-      <c r="K181" t="s">
-        <v>21</v>
       </c>
       <c r="L181" t="s">
         <v>732</v>
@@ -10534,28 +10534,28 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
+        <v>778</v>
+      </c>
+      <c r="E182" t="s">
+        <v>728</v>
+      </c>
+      <c r="F182" t="s">
+        <v>17</v>
+      </c>
+      <c r="G182" t="s">
+        <v>18</v>
+      </c>
+      <c r="H182" t="s">
         <v>772</v>
       </c>
-      <c r="E182" t="s">
-        <v>729</v>
-      </c>
-      <c r="F182" t="s">
-        <v>778</v>
-      </c>
-      <c r="G182" t="s">
+      <c r="I182" t="s">
         <v>773</v>
       </c>
-      <c r="H182" t="s">
+      <c r="J182" t="s">
         <v>784</v>
       </c>
-      <c r="I182" t="s">
-        <v>20</v>
-      </c>
-      <c r="J182" t="s">
+      <c r="K182" t="s">
         <v>780</v>
-      </c>
-      <c r="K182" t="s">
-        <v>21</v>
       </c>
       <c r="L182" t="s">
         <v>732</v>
@@ -10575,25 +10575,25 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
+        <v>778</v>
+      </c>
+      <c r="E183" t="s">
+        <v>728</v>
+      </c>
+      <c r="F183" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" t="s">
+        <v>18</v>
+      </c>
+      <c r="H183" t="s">
         <v>772</v>
       </c>
-      <c r="E183" t="s">
-        <v>729</v>
-      </c>
-      <c r="F183" t="s">
-        <v>778</v>
-      </c>
-      <c r="G183" t="s">
+      <c r="I183" t="s">
         <v>773</v>
       </c>
-      <c r="I183" t="s">
-        <v>20</v>
-      </c>
-      <c r="J183" t="s">
+      <c r="K183" t="s">
         <v>780</v>
-      </c>
-      <c r="K183" t="s">
-        <v>21</v>
       </c>
       <c r="L183" t="s">
         <v>732</v>
@@ -10609,23 +10609,23 @@
       <c r="C184" t="s">
         <v>15</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
+        <v>728</v>
+      </c>
+      <c r="F184" t="s">
+        <v>17</v>
+      </c>
+      <c r="G184" t="s">
+        <v>18</v>
+      </c>
+      <c r="H184" t="s">
         <v>772</v>
       </c>
-      <c r="E184" t="s">
-        <v>729</v>
-      </c>
-      <c r="G184" t="s">
+      <c r="I184" t="s">
         <v>773</v>
       </c>
-      <c r="H184" t="s">
+      <c r="J184" t="s">
         <v>790</v>
-      </c>
-      <c r="I184" t="s">
-        <v>20</v>
-      </c>
-      <c r="K184" t="s">
-        <v>21</v>
       </c>
       <c r="L184" t="s">
         <v>732</v>
@@ -10644,23 +10644,23 @@
       <c r="C185" t="s">
         <v>15</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
+        <v>728</v>
+      </c>
+      <c r="F185" t="s">
+        <v>17</v>
+      </c>
+      <c r="G185" t="s">
+        <v>18</v>
+      </c>
+      <c r="H185" t="s">
         <v>772</v>
       </c>
-      <c r="E185" t="s">
-        <v>729</v>
-      </c>
-      <c r="G185" t="s">
+      <c r="I185" t="s">
         <v>773</v>
       </c>
-      <c r="H185" t="s">
+      <c r="J185" t="s">
         <v>794</v>
-      </c>
-      <c r="I185" t="s">
-        <v>20</v>
-      </c>
-      <c r="K185" t="s">
-        <v>21</v>
       </c>
       <c r="L185" t="s">
         <v>732</v>
@@ -10679,23 +10679,23 @@
       <c r="C186" t="s">
         <v>15</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
+        <v>728</v>
+      </c>
+      <c r="F186" t="s">
+        <v>17</v>
+      </c>
+      <c r="G186" t="s">
+        <v>18</v>
+      </c>
+      <c r="H186" t="s">
         <v>772</v>
       </c>
-      <c r="E186" t="s">
-        <v>729</v>
-      </c>
-      <c r="G186" t="s">
+      <c r="I186" t="s">
         <v>773</v>
       </c>
-      <c r="H186" t="s">
+      <c r="J186" t="s">
         <v>798</v>
-      </c>
-      <c r="I186" t="s">
-        <v>20</v>
-      </c>
-      <c r="K186" t="s">
-        <v>21</v>
       </c>
       <c r="L186" t="s">
         <v>732</v>
@@ -10714,23 +10714,23 @@
       <c r="C187" t="s">
         <v>15</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
+        <v>728</v>
+      </c>
+      <c r="F187" t="s">
+        <v>17</v>
+      </c>
+      <c r="G187" t="s">
+        <v>18</v>
+      </c>
+      <c r="H187" t="s">
         <v>772</v>
       </c>
-      <c r="E187" t="s">
-        <v>729</v>
-      </c>
-      <c r="G187" t="s">
+      <c r="I187" t="s">
         <v>773</v>
       </c>
-      <c r="H187" t="s">
+      <c r="J187" t="s">
         <v>802</v>
-      </c>
-      <c r="I187" t="s">
-        <v>20</v>
-      </c>
-      <c r="K187" t="s">
-        <v>21</v>
       </c>
       <c r="L187" t="s">
         <v>732</v>
@@ -10749,23 +10749,23 @@
       <c r="C188" t="s">
         <v>15</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
+        <v>728</v>
+      </c>
+      <c r="F188" t="s">
+        <v>17</v>
+      </c>
+      <c r="G188" t="s">
+        <v>18</v>
+      </c>
+      <c r="H188" t="s">
         <v>772</v>
       </c>
-      <c r="E188" t="s">
-        <v>729</v>
-      </c>
-      <c r="G188" t="s">
+      <c r="I188" t="s">
         <v>773</v>
       </c>
-      <c r="H188" t="s">
+      <c r="J188" t="s">
         <v>806</v>
-      </c>
-      <c r="I188" t="s">
-        <v>20</v>
-      </c>
-      <c r="K188" t="s">
-        <v>21</v>
       </c>
       <c r="L188" t="s">
         <v>732</v>
@@ -10784,23 +10784,23 @@
       <c r="C189" t="s">
         <v>15</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
+        <v>728</v>
+      </c>
+      <c r="F189" t="s">
+        <v>17</v>
+      </c>
+      <c r="G189" t="s">
+        <v>18</v>
+      </c>
+      <c r="H189" t="s">
         <v>772</v>
       </c>
-      <c r="E189" t="s">
-        <v>729</v>
-      </c>
-      <c r="G189" t="s">
+      <c r="I189" t="s">
         <v>773</v>
       </c>
-      <c r="H189" t="s">
+      <c r="J189" t="s">
         <v>810</v>
-      </c>
-      <c r="I189" t="s">
-        <v>20</v>
-      </c>
-      <c r="K189" t="s">
-        <v>21</v>
       </c>
       <c r="L189" t="s">
         <v>732</v>
@@ -10819,23 +10819,23 @@
       <c r="C190" t="s">
         <v>15</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
+        <v>728</v>
+      </c>
+      <c r="F190" t="s">
+        <v>17</v>
+      </c>
+      <c r="G190" t="s">
+        <v>18</v>
+      </c>
+      <c r="H190" t="s">
         <v>772</v>
       </c>
-      <c r="E190" t="s">
-        <v>729</v>
-      </c>
-      <c r="G190" t="s">
+      <c r="I190" t="s">
         <v>773</v>
       </c>
-      <c r="H190" t="s">
+      <c r="J190" t="s">
         <v>814</v>
-      </c>
-      <c r="I190" t="s">
-        <v>20</v>
-      </c>
-      <c r="K190" t="s">
-        <v>21</v>
       </c>
       <c r="L190" t="s">
         <v>732</v>
@@ -10854,23 +10854,23 @@
       <c r="C191" t="s">
         <v>15</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
+        <v>728</v>
+      </c>
+      <c r="F191" t="s">
+        <v>17</v>
+      </c>
+      <c r="G191" t="s">
+        <v>18</v>
+      </c>
+      <c r="H191" t="s">
         <v>772</v>
       </c>
-      <c r="E191" t="s">
-        <v>729</v>
-      </c>
-      <c r="G191" t="s">
+      <c r="I191" t="s">
         <v>773</v>
       </c>
-      <c r="H191" t="s">
+      <c r="J191" t="s">
         <v>818</v>
-      </c>
-      <c r="I191" t="s">
-        <v>20</v>
-      </c>
-      <c r="K191" t="s">
-        <v>21</v>
       </c>
       <c r="L191" t="s">
         <v>732</v>
@@ -10889,23 +10889,23 @@
       <c r="C192" t="s">
         <v>15</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
+        <v>728</v>
+      </c>
+      <c r="F192" t="s">
+        <v>17</v>
+      </c>
+      <c r="G192" t="s">
+        <v>18</v>
+      </c>
+      <c r="H192" t="s">
         <v>772</v>
       </c>
-      <c r="E192" t="s">
-        <v>729</v>
-      </c>
-      <c r="G192" t="s">
+      <c r="I192" t="s">
         <v>773</v>
       </c>
-      <c r="H192" t="s">
+      <c r="J192" t="s">
         <v>822</v>
-      </c>
-      <c r="I192" t="s">
-        <v>20</v>
-      </c>
-      <c r="K192" t="s">
-        <v>21</v>
       </c>
       <c r="L192" t="s">
         <v>732</v>
@@ -10924,23 +10924,23 @@
       <c r="C193" t="s">
         <v>15</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
+        <v>728</v>
+      </c>
+      <c r="F193" t="s">
+        <v>17</v>
+      </c>
+      <c r="G193" t="s">
+        <v>18</v>
+      </c>
+      <c r="H193" t="s">
         <v>772</v>
       </c>
-      <c r="E193" t="s">
-        <v>729</v>
-      </c>
-      <c r="G193" t="s">
+      <c r="I193" t="s">
         <v>773</v>
       </c>
-      <c r="H193" t="s">
+      <c r="J193" t="s">
         <v>826</v>
-      </c>
-      <c r="I193" t="s">
-        <v>20</v>
-      </c>
-      <c r="K193" t="s">
-        <v>21</v>
       </c>
       <c r="L193" t="s">
         <v>732</v>
@@ -10959,23 +10959,23 @@
       <c r="C194" t="s">
         <v>15</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
+        <v>728</v>
+      </c>
+      <c r="F194" t="s">
+        <v>17</v>
+      </c>
+      <c r="G194" t="s">
+        <v>18</v>
+      </c>
+      <c r="H194" t="s">
         <v>772</v>
       </c>
-      <c r="E194" t="s">
-        <v>729</v>
-      </c>
-      <c r="G194" t="s">
+      <c r="I194" t="s">
         <v>773</v>
       </c>
-      <c r="H194" t="s">
+      <c r="J194" t="s">
         <v>830</v>
-      </c>
-      <c r="I194" t="s">
-        <v>20</v>
-      </c>
-      <c r="K194" t="s">
-        <v>21</v>
       </c>
       <c r="L194" t="s">
         <v>732</v>
@@ -10994,23 +10994,23 @@
       <c r="C195" t="s">
         <v>15</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
+        <v>728</v>
+      </c>
+      <c r="F195" t="s">
+        <v>17</v>
+      </c>
+      <c r="G195" t="s">
+        <v>18</v>
+      </c>
+      <c r="H195" t="s">
         <v>772</v>
       </c>
-      <c r="E195" t="s">
-        <v>729</v>
-      </c>
-      <c r="G195" t="s">
+      <c r="I195" t="s">
         <v>773</v>
       </c>
-      <c r="H195" t="s">
+      <c r="J195" t="s">
         <v>834</v>
-      </c>
-      <c r="I195" t="s">
-        <v>20</v>
-      </c>
-      <c r="K195" t="s">
-        <v>21</v>
       </c>
       <c r="L195" t="s">
         <v>732</v>
@@ -11029,23 +11029,23 @@
       <c r="C196" t="s">
         <v>15</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
+        <v>728</v>
+      </c>
+      <c r="F196" t="s">
+        <v>17</v>
+      </c>
+      <c r="G196" t="s">
+        <v>18</v>
+      </c>
+      <c r="H196" t="s">
         <v>772</v>
       </c>
-      <c r="E196" t="s">
-        <v>729</v>
-      </c>
-      <c r="G196" t="s">
+      <c r="I196" t="s">
         <v>773</v>
       </c>
-      <c r="H196" t="s">
+      <c r="J196" t="s">
         <v>838</v>
-      </c>
-      <c r="I196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K196" t="s">
-        <v>21</v>
       </c>
       <c r="L196" t="s">
         <v>732</v>
@@ -11064,23 +11064,23 @@
       <c r="C197" t="s">
         <v>15</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
+        <v>728</v>
+      </c>
+      <c r="F197" t="s">
+        <v>17</v>
+      </c>
+      <c r="G197" t="s">
+        <v>18</v>
+      </c>
+      <c r="H197" t="s">
         <v>842</v>
       </c>
-      <c r="E197" t="s">
-        <v>729</v>
-      </c>
-      <c r="G197" t="s">
+      <c r="I197" t="s">
         <v>843</v>
       </c>
-      <c r="H197" t="s">
+      <c r="J197" t="s">
         <v>844</v>
-      </c>
-      <c r="I197" t="s">
-        <v>20</v>
-      </c>
-      <c r="K197" t="s">
-        <v>21</v>
       </c>
       <c r="L197" t="s">
         <v>732</v>
@@ -11099,23 +11099,23 @@
       <c r="C198" t="s">
         <v>15</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
+        <v>728</v>
+      </c>
+      <c r="F198" t="s">
+        <v>17</v>
+      </c>
+      <c r="G198" t="s">
+        <v>18</v>
+      </c>
+      <c r="H198" t="s">
         <v>842</v>
       </c>
-      <c r="E198" t="s">
-        <v>729</v>
-      </c>
-      <c r="G198" t="s">
+      <c r="I198" t="s">
         <v>843</v>
       </c>
-      <c r="H198" t="s">
+      <c r="J198" t="s">
         <v>848</v>
-      </c>
-      <c r="I198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K198" t="s">
-        <v>21</v>
       </c>
       <c r="L198" t="s">
         <v>732</v>
@@ -11134,23 +11134,23 @@
       <c r="C199" t="s">
         <v>15</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
+        <v>728</v>
+      </c>
+      <c r="F199" t="s">
+        <v>17</v>
+      </c>
+      <c r="G199" t="s">
+        <v>18</v>
+      </c>
+      <c r="H199" t="s">
         <v>842</v>
       </c>
-      <c r="E199" t="s">
-        <v>729</v>
-      </c>
-      <c r="G199" t="s">
+      <c r="I199" t="s">
         <v>843</v>
       </c>
-      <c r="H199" t="s">
+      <c r="J199" t="s">
         <v>852</v>
-      </c>
-      <c r="I199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K199" t="s">
-        <v>21</v>
       </c>
       <c r="L199" t="s">
         <v>732</v>
@@ -11169,23 +11169,23 @@
       <c r="C200" t="s">
         <v>15</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
+        <v>728</v>
+      </c>
+      <c r="F200" t="s">
+        <v>17</v>
+      </c>
+      <c r="G200" t="s">
+        <v>18</v>
+      </c>
+      <c r="H200" t="s">
         <v>842</v>
       </c>
-      <c r="E200" t="s">
-        <v>729</v>
-      </c>
-      <c r="G200" t="s">
+      <c r="I200" t="s">
         <v>843</v>
       </c>
-      <c r="H200" t="s">
+      <c r="J200" t="s">
         <v>856</v>
-      </c>
-      <c r="I200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K200" t="s">
-        <v>21</v>
       </c>
       <c r="L200" t="s">
         <v>732</v>
@@ -11204,23 +11204,23 @@
       <c r="C201" t="s">
         <v>15</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
+        <v>728</v>
+      </c>
+      <c r="F201" t="s">
+        <v>17</v>
+      </c>
+      <c r="G201" t="s">
+        <v>18</v>
+      </c>
+      <c r="H201" t="s">
         <v>842</v>
       </c>
-      <c r="E201" t="s">
-        <v>729</v>
-      </c>
-      <c r="G201" t="s">
+      <c r="I201" t="s">
         <v>843</v>
       </c>
-      <c r="H201" t="s">
+      <c r="J201" t="s">
         <v>860</v>
-      </c>
-      <c r="I201" t="s">
-        <v>20</v>
-      </c>
-      <c r="K201" t="s">
-        <v>21</v>
       </c>
       <c r="L201" t="s">
         <v>732</v>
@@ -11239,23 +11239,23 @@
       <c r="C202" t="s">
         <v>15</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
+        <v>728</v>
+      </c>
+      <c r="F202" t="s">
+        <v>17</v>
+      </c>
+      <c r="G202" t="s">
+        <v>18</v>
+      </c>
+      <c r="H202" t="s">
         <v>842</v>
       </c>
-      <c r="E202" t="s">
-        <v>729</v>
-      </c>
-      <c r="G202" t="s">
+      <c r="I202" t="s">
         <v>843</v>
       </c>
-      <c r="H202" t="s">
+      <c r="J202" t="s">
         <v>864</v>
-      </c>
-      <c r="I202" t="s">
-        <v>20</v>
-      </c>
-      <c r="K202" t="s">
-        <v>21</v>
       </c>
       <c r="L202" t="s">
         <v>732</v>
@@ -11274,23 +11274,23 @@
       <c r="C203" t="s">
         <v>15</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
+        <v>728</v>
+      </c>
+      <c r="F203" t="s">
+        <v>17</v>
+      </c>
+      <c r="G203" t="s">
+        <v>18</v>
+      </c>
+      <c r="H203" t="s">
         <v>842</v>
       </c>
-      <c r="E203" t="s">
-        <v>729</v>
-      </c>
-      <c r="G203" t="s">
+      <c r="I203" t="s">
         <v>843</v>
       </c>
-      <c r="H203" t="s">
+      <c r="J203" t="s">
         <v>868</v>
-      </c>
-      <c r="I203" t="s">
-        <v>20</v>
-      </c>
-      <c r="K203" t="s">
-        <v>21</v>
       </c>
       <c r="L203" t="s">
         <v>732</v>
@@ -11309,23 +11309,23 @@
       <c r="C204" t="s">
         <v>15</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>728</v>
+      </c>
+      <c r="F204" t="s">
+        <v>17</v>
+      </c>
+      <c r="G204" t="s">
+        <v>18</v>
+      </c>
+      <c r="H204" t="s">
         <v>842</v>
       </c>
-      <c r="E204" t="s">
-        <v>729</v>
-      </c>
-      <c r="G204" t="s">
+      <c r="I204" t="s">
         <v>843</v>
       </c>
-      <c r="H204" t="s">
+      <c r="J204" t="s">
         <v>872</v>
-      </c>
-      <c r="I204" t="s">
-        <v>20</v>
-      </c>
-      <c r="K204" t="s">
-        <v>21</v>
       </c>
       <c r="L204" t="s">
         <v>732</v>
@@ -11344,23 +11344,23 @@
       <c r="C205" t="s">
         <v>15</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
+        <v>728</v>
+      </c>
+      <c r="F205" t="s">
+        <v>17</v>
+      </c>
+      <c r="G205" t="s">
+        <v>18</v>
+      </c>
+      <c r="H205" t="s">
         <v>842</v>
       </c>
-      <c r="E205" t="s">
-        <v>729</v>
-      </c>
-      <c r="G205" t="s">
+      <c r="I205" t="s">
         <v>843</v>
       </c>
-      <c r="H205" t="s">
+      <c r="J205" t="s">
         <v>876</v>
-      </c>
-      <c r="I205" t="s">
-        <v>20</v>
-      </c>
-      <c r="K205" t="s">
-        <v>21</v>
       </c>
       <c r="L205" t="s">
         <v>732</v>
@@ -11379,23 +11379,23 @@
       <c r="C206" t="s">
         <v>15</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
+        <v>728</v>
+      </c>
+      <c r="F206" t="s">
+        <v>17</v>
+      </c>
+      <c r="G206" t="s">
+        <v>18</v>
+      </c>
+      <c r="H206" t="s">
         <v>842</v>
       </c>
-      <c r="E206" t="s">
-        <v>729</v>
-      </c>
-      <c r="G206" t="s">
+      <c r="I206" t="s">
         <v>843</v>
       </c>
-      <c r="H206" t="s">
+      <c r="J206" t="s">
         <v>880</v>
-      </c>
-      <c r="I206" t="s">
-        <v>20</v>
-      </c>
-      <c r="K206" t="s">
-        <v>21</v>
       </c>
       <c r="L206" t="s">
         <v>732</v>
@@ -11414,23 +11414,23 @@
       <c r="C207" t="s">
         <v>15</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
+        <v>728</v>
+      </c>
+      <c r="F207" t="s">
+        <v>17</v>
+      </c>
+      <c r="G207" t="s">
+        <v>18</v>
+      </c>
+      <c r="H207" t="s">
         <v>842</v>
       </c>
-      <c r="E207" t="s">
-        <v>729</v>
-      </c>
-      <c r="G207" t="s">
+      <c r="I207" t="s">
         <v>843</v>
       </c>
-      <c r="H207" t="s">
+      <c r="J207" t="s">
         <v>884</v>
-      </c>
-      <c r="I207" t="s">
-        <v>20</v>
-      </c>
-      <c r="K207" t="s">
-        <v>21</v>
       </c>
       <c r="L207" t="s">
         <v>732</v>
@@ -11449,23 +11449,23 @@
       <c r="C208" t="s">
         <v>15</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
+        <v>728</v>
+      </c>
+      <c r="F208" t="s">
+        <v>17</v>
+      </c>
+      <c r="G208" t="s">
+        <v>18</v>
+      </c>
+      <c r="H208" t="s">
         <v>842</v>
       </c>
-      <c r="E208" t="s">
-        <v>729</v>
-      </c>
-      <c r="G208" t="s">
+      <c r="I208" t="s">
         <v>843</v>
       </c>
-      <c r="H208" t="s">
+      <c r="J208" t="s">
         <v>888</v>
-      </c>
-      <c r="I208" t="s">
-        <v>20</v>
-      </c>
-      <c r="K208" t="s">
-        <v>21</v>
       </c>
       <c r="L208" t="s">
         <v>732</v>
@@ -11484,23 +11484,23 @@
       <c r="C209" t="s">
         <v>15</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
+        <v>728</v>
+      </c>
+      <c r="F209" t="s">
+        <v>17</v>
+      </c>
+      <c r="G209" t="s">
+        <v>18</v>
+      </c>
+      <c r="H209" t="s">
         <v>842</v>
       </c>
-      <c r="E209" t="s">
-        <v>729</v>
-      </c>
-      <c r="G209" t="s">
+      <c r="I209" t="s">
         <v>843</v>
       </c>
-      <c r="H209" t="s">
+      <c r="J209" t="s">
         <v>892</v>
-      </c>
-      <c r="I209" t="s">
-        <v>20</v>
-      </c>
-      <c r="K209" t="s">
-        <v>21</v>
       </c>
       <c r="L209" t="s">
         <v>732</v>
@@ -11519,23 +11519,23 @@
       <c r="C210" t="s">
         <v>15</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
+        <v>728</v>
+      </c>
+      <c r="F210" t="s">
+        <v>17</v>
+      </c>
+      <c r="G210" t="s">
+        <v>18</v>
+      </c>
+      <c r="H210" t="s">
         <v>842</v>
       </c>
-      <c r="E210" t="s">
-        <v>729</v>
-      </c>
-      <c r="G210" t="s">
+      <c r="I210" t="s">
         <v>843</v>
       </c>
-      <c r="H210" t="s">
+      <c r="J210" t="s">
         <v>896</v>
-      </c>
-      <c r="I210" t="s">
-        <v>20</v>
-      </c>
-      <c r="K210" t="s">
-        <v>21</v>
       </c>
       <c r="L210" t="s">
         <v>732</v>
@@ -11554,23 +11554,23 @@
       <c r="C211" t="s">
         <v>15</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
+        <v>728</v>
+      </c>
+      <c r="F211" t="s">
+        <v>17</v>
+      </c>
+      <c r="G211" t="s">
+        <v>18</v>
+      </c>
+      <c r="H211" t="s">
         <v>842</v>
       </c>
-      <c r="E211" t="s">
-        <v>729</v>
-      </c>
-      <c r="G211" t="s">
+      <c r="I211" t="s">
         <v>843</v>
       </c>
-      <c r="H211" t="s">
+      <c r="J211" t="s">
         <v>900</v>
-      </c>
-      <c r="I211" t="s">
-        <v>20</v>
-      </c>
-      <c r="K211" t="s">
-        <v>21</v>
       </c>
       <c r="L211" t="s">
         <v>732</v>
@@ -11589,23 +11589,23 @@
       <c r="C212" t="s">
         <v>15</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
+        <v>728</v>
+      </c>
+      <c r="F212" t="s">
+        <v>17</v>
+      </c>
+      <c r="G212" t="s">
+        <v>18</v>
+      </c>
+      <c r="H212" t="s">
         <v>842</v>
       </c>
-      <c r="E212" t="s">
-        <v>729</v>
-      </c>
-      <c r="G212" t="s">
+      <c r="I212" t="s">
         <v>843</v>
       </c>
-      <c r="H212" t="s">
+      <c r="J212" t="s">
         <v>904</v>
-      </c>
-      <c r="I212" t="s">
-        <v>20</v>
-      </c>
-      <c r="K212" t="s">
-        <v>21</v>
       </c>
       <c r="L212" t="s">
         <v>732</v>
@@ -11624,23 +11624,23 @@
       <c r="C213" t="s">
         <v>15</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
+        <v>728</v>
+      </c>
+      <c r="F213" t="s">
+        <v>17</v>
+      </c>
+      <c r="G213" t="s">
+        <v>18</v>
+      </c>
+      <c r="H213" t="s">
         <v>908</v>
       </c>
-      <c r="E213" t="s">
-        <v>729</v>
-      </c>
-      <c r="G213" t="s">
+      <c r="I213" t="s">
         <v>909</v>
       </c>
-      <c r="H213" t="s">
+      <c r="J213" t="s">
         <v>910</v>
-      </c>
-      <c r="I213" t="s">
-        <v>20</v>
-      </c>
-      <c r="K213" t="s">
-        <v>21</v>
       </c>
       <c r="L213" t="s">
         <v>732</v>
@@ -11659,23 +11659,23 @@
       <c r="C214" t="s">
         <v>15</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
+        <v>728</v>
+      </c>
+      <c r="F214" t="s">
+        <v>17</v>
+      </c>
+      <c r="G214" t="s">
+        <v>18</v>
+      </c>
+      <c r="H214" t="s">
         <v>908</v>
       </c>
-      <c r="E214" t="s">
-        <v>729</v>
-      </c>
-      <c r="G214" t="s">
+      <c r="I214" t="s">
         <v>909</v>
       </c>
-      <c r="H214" t="s">
+      <c r="J214" t="s">
         <v>914</v>
-      </c>
-      <c r="I214" t="s">
-        <v>20</v>
-      </c>
-      <c r="K214" t="s">
-        <v>21</v>
       </c>
       <c r="L214" t="s">
         <v>732</v>
@@ -11694,23 +11694,23 @@
       <c r="C215" t="s">
         <v>15</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
+        <v>728</v>
+      </c>
+      <c r="F215" t="s">
+        <v>17</v>
+      </c>
+      <c r="G215" t="s">
+        <v>18</v>
+      </c>
+      <c r="H215" t="s">
         <v>908</v>
       </c>
-      <c r="E215" t="s">
-        <v>729</v>
-      </c>
-      <c r="G215" t="s">
+      <c r="I215" t="s">
         <v>909</v>
       </c>
-      <c r="H215" t="s">
+      <c r="J215" t="s">
         <v>918</v>
-      </c>
-      <c r="I215" t="s">
-        <v>20</v>
-      </c>
-      <c r="K215" t="s">
-        <v>21</v>
       </c>
       <c r="L215" t="s">
         <v>732</v>
@@ -11729,23 +11729,23 @@
       <c r="C216" t="s">
         <v>15</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
+        <v>728</v>
+      </c>
+      <c r="F216" t="s">
+        <v>17</v>
+      </c>
+      <c r="G216" t="s">
+        <v>18</v>
+      </c>
+      <c r="H216" t="s">
         <v>908</v>
       </c>
-      <c r="E216" t="s">
-        <v>729</v>
-      </c>
-      <c r="G216" t="s">
+      <c r="I216" t="s">
         <v>909</v>
       </c>
-      <c r="H216" t="s">
+      <c r="J216" t="s">
         <v>922</v>
-      </c>
-      <c r="I216" t="s">
-        <v>20</v>
-      </c>
-      <c r="K216" t="s">
-        <v>21</v>
       </c>
       <c r="L216" t="s">
         <v>732</v>
@@ -11764,23 +11764,23 @@
       <c r="C217" t="s">
         <v>15</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
+        <v>728</v>
+      </c>
+      <c r="F217" t="s">
+        <v>17</v>
+      </c>
+      <c r="G217" t="s">
+        <v>18</v>
+      </c>
+      <c r="H217" t="s">
         <v>908</v>
       </c>
-      <c r="E217" t="s">
-        <v>729</v>
-      </c>
-      <c r="G217" t="s">
+      <c r="I217" t="s">
         <v>909</v>
       </c>
-      <c r="H217" t="s">
+      <c r="J217" t="s">
         <v>926</v>
-      </c>
-      <c r="I217" t="s">
-        <v>20</v>
-      </c>
-      <c r="K217" t="s">
-        <v>21</v>
       </c>
       <c r="L217" t="s">
         <v>732</v>
@@ -11799,23 +11799,23 @@
       <c r="C218" t="s">
         <v>15</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
+        <v>728</v>
+      </c>
+      <c r="F218" t="s">
+        <v>17</v>
+      </c>
+      <c r="G218" t="s">
+        <v>18</v>
+      </c>
+      <c r="H218" t="s">
         <v>908</v>
       </c>
-      <c r="E218" t="s">
-        <v>729</v>
-      </c>
-      <c r="G218" t="s">
+      <c r="I218" t="s">
         <v>909</v>
       </c>
-      <c r="H218" t="s">
+      <c r="J218" t="s">
         <v>930</v>
-      </c>
-      <c r="I218" t="s">
-        <v>20</v>
-      </c>
-      <c r="K218" t="s">
-        <v>21</v>
       </c>
       <c r="L218" t="s">
         <v>732</v>
@@ -11834,23 +11834,23 @@
       <c r="C219" t="s">
         <v>15</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
+        <v>728</v>
+      </c>
+      <c r="F219" t="s">
+        <v>17</v>
+      </c>
+      <c r="G219" t="s">
+        <v>18</v>
+      </c>
+      <c r="H219" t="s">
         <v>908</v>
       </c>
-      <c r="E219" t="s">
-        <v>729</v>
-      </c>
-      <c r="G219" t="s">
+      <c r="I219" t="s">
         <v>909</v>
       </c>
-      <c r="H219" t="s">
+      <c r="J219" t="s">
         <v>934</v>
-      </c>
-      <c r="I219" t="s">
-        <v>20</v>
-      </c>
-      <c r="K219" t="s">
-        <v>21</v>
       </c>
       <c r="L219" t="s">
         <v>732</v>
@@ -11869,23 +11869,23 @@
       <c r="C220" t="s">
         <v>15</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
+        <v>728</v>
+      </c>
+      <c r="F220" t="s">
+        <v>17</v>
+      </c>
+      <c r="G220" t="s">
+        <v>18</v>
+      </c>
+      <c r="H220" t="s">
         <v>908</v>
       </c>
-      <c r="E220" t="s">
-        <v>729</v>
-      </c>
-      <c r="G220" t="s">
+      <c r="I220" t="s">
         <v>909</v>
       </c>
-      <c r="H220" t="s">
+      <c r="J220" t="s">
         <v>938</v>
-      </c>
-      <c r="I220" t="s">
-        <v>20</v>
-      </c>
-      <c r="K220" t="s">
-        <v>21</v>
       </c>
       <c r="L220" t="s">
         <v>732</v>
@@ -11904,23 +11904,23 @@
       <c r="C221" t="s">
         <v>15</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
+        <v>728</v>
+      </c>
+      <c r="F221" t="s">
+        <v>17</v>
+      </c>
+      <c r="G221" t="s">
+        <v>18</v>
+      </c>
+      <c r="H221" t="s">
         <v>908</v>
       </c>
-      <c r="E221" t="s">
-        <v>729</v>
-      </c>
-      <c r="G221" t="s">
+      <c r="I221" t="s">
         <v>909</v>
       </c>
-      <c r="H221" t="s">
+      <c r="J221" t="s">
         <v>942</v>
-      </c>
-      <c r="I221" t="s">
-        <v>20</v>
-      </c>
-      <c r="K221" t="s">
-        <v>21</v>
       </c>
       <c r="L221" t="s">
         <v>732</v>
@@ -11939,23 +11939,23 @@
       <c r="C222" t="s">
         <v>15</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>946</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
+        <v>17</v>
+      </c>
+      <c r="G222" t="s">
+        <v>18</v>
+      </c>
+      <c r="H222" t="s">
         <v>947</v>
       </c>
-      <c r="G222" t="s">
+      <c r="I222" t="s">
         <v>948</v>
       </c>
-      <c r="H222" t="s">
+      <c r="J222" t="s">
         <v>949</v>
-      </c>
-      <c r="I222" t="s">
-        <v>20</v>
-      </c>
-      <c r="K222" t="s">
-        <v>21</v>
       </c>
       <c r="L222" t="s">
         <v>950</v>
@@ -11974,23 +11974,23 @@
       <c r="C223" t="s">
         <v>15</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>946</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
+        <v>17</v>
+      </c>
+      <c r="G223" t="s">
+        <v>18</v>
+      </c>
+      <c r="H223" t="s">
         <v>947</v>
       </c>
-      <c r="G223" t="s">
+      <c r="I223" t="s">
         <v>948</v>
       </c>
-      <c r="H223" t="s">
+      <c r="J223" t="s">
         <v>954</v>
-      </c>
-      <c r="I223" t="s">
-        <v>20</v>
-      </c>
-      <c r="K223" t="s">
-        <v>21</v>
       </c>
       <c r="L223" t="s">
         <v>950</v>
@@ -12009,23 +12009,23 @@
       <c r="C224" t="s">
         <v>15</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>946</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
+        <v>17</v>
+      </c>
+      <c r="G224" t="s">
+        <v>18</v>
+      </c>
+      <c r="H224" t="s">
         <v>947</v>
       </c>
-      <c r="G224" t="s">
+      <c r="I224" t="s">
         <v>948</v>
       </c>
-      <c r="H224" t="s">
+      <c r="J224" t="s">
         <v>958</v>
-      </c>
-      <c r="I224" t="s">
-        <v>20</v>
-      </c>
-      <c r="K224" t="s">
-        <v>21</v>
       </c>
       <c r="L224" t="s">
         <v>950</v>
@@ -12044,23 +12044,23 @@
       <c r="C225" t="s">
         <v>15</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>946</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
+        <v>17</v>
+      </c>
+      <c r="G225" t="s">
+        <v>18</v>
+      </c>
+      <c r="H225" t="s">
         <v>947</v>
       </c>
-      <c r="G225" t="s">
+      <c r="I225" t="s">
         <v>948</v>
       </c>
-      <c r="H225" t="s">
+      <c r="J225" t="s">
         <v>962</v>
-      </c>
-      <c r="I225" t="s">
-        <v>20</v>
-      </c>
-      <c r="K225" t="s">
-        <v>21</v>
       </c>
       <c r="L225" t="s">
         <v>950</v>
@@ -12079,23 +12079,23 @@
       <c r="C226" t="s">
         <v>15</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
         <v>946</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
+        <v>17</v>
+      </c>
+      <c r="G226" t="s">
+        <v>18</v>
+      </c>
+      <c r="H226" t="s">
         <v>947</v>
       </c>
-      <c r="G226" t="s">
+      <c r="I226" t="s">
         <v>948</v>
       </c>
-      <c r="H226" t="s">
+      <c r="J226" t="s">
         <v>966</v>
-      </c>
-      <c r="I226" t="s">
-        <v>20</v>
-      </c>
-      <c r="K226" t="s">
-        <v>21</v>
       </c>
       <c r="L226" t="s">
         <v>950</v>
@@ -12114,23 +12114,23 @@
       <c r="C227" t="s">
         <v>15</v>
       </c>
-      <c r="D227" t="s">
+      <c r="E227" t="s">
         <v>946</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
+        <v>17</v>
+      </c>
+      <c r="G227" t="s">
+        <v>18</v>
+      </c>
+      <c r="H227" t="s">
         <v>947</v>
       </c>
-      <c r="G227" t="s">
+      <c r="I227" t="s">
         <v>948</v>
       </c>
-      <c r="H227" t="s">
+      <c r="J227" t="s">
         <v>970</v>
-      </c>
-      <c r="I227" t="s">
-        <v>20</v>
-      </c>
-      <c r="K227" t="s">
-        <v>21</v>
       </c>
       <c r="L227" t="s">
         <v>950</v>
@@ -12149,23 +12149,23 @@
       <c r="C228" t="s">
         <v>15</v>
       </c>
-      <c r="D228" t="s">
+      <c r="E228" t="s">
+        <v>946</v>
+      </c>
+      <c r="F228" t="s">
+        <v>17</v>
+      </c>
+      <c r="G228" t="s">
+        <v>18</v>
+      </c>
+      <c r="H228" t="s">
         <v>974</v>
       </c>
-      <c r="E228" t="s">
-        <v>947</v>
-      </c>
-      <c r="G228" t="s">
+      <c r="I228" t="s">
         <v>975</v>
       </c>
-      <c r="H228" t="s">
+      <c r="J228" t="s">
         <v>976</v>
-      </c>
-      <c r="I228" t="s">
-        <v>20</v>
-      </c>
-      <c r="K228" t="s">
-        <v>21</v>
       </c>
       <c r="L228" t="s">
         <v>950</v>
@@ -12184,23 +12184,23 @@
       <c r="C229" t="s">
         <v>15</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
+        <v>946</v>
+      </c>
+      <c r="F229" t="s">
+        <v>17</v>
+      </c>
+      <c r="G229" t="s">
+        <v>18</v>
+      </c>
+      <c r="H229" t="s">
         <v>974</v>
       </c>
-      <c r="E229" t="s">
-        <v>947</v>
-      </c>
-      <c r="G229" t="s">
+      <c r="I229" t="s">
         <v>975</v>
       </c>
-      <c r="H229" t="s">
+      <c r="J229" t="s">
         <v>980</v>
-      </c>
-      <c r="I229" t="s">
-        <v>20</v>
-      </c>
-      <c r="K229" t="s">
-        <v>21</v>
       </c>
       <c r="L229" t="s">
         <v>950</v>
@@ -12219,23 +12219,23 @@
       <c r="C230" t="s">
         <v>15</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
+        <v>946</v>
+      </c>
+      <c r="F230" t="s">
+        <v>17</v>
+      </c>
+      <c r="G230" t="s">
+        <v>18</v>
+      </c>
+      <c r="H230" t="s">
         <v>974</v>
       </c>
-      <c r="E230" t="s">
-        <v>947</v>
-      </c>
-      <c r="G230" t="s">
+      <c r="I230" t="s">
         <v>975</v>
       </c>
-      <c r="H230" t="s">
+      <c r="J230" t="s">
         <v>984</v>
-      </c>
-      <c r="I230" t="s">
-        <v>20</v>
-      </c>
-      <c r="K230" t="s">
-        <v>21</v>
       </c>
       <c r="L230" t="s">
         <v>950</v>
@@ -12254,23 +12254,23 @@
       <c r="C231" t="s">
         <v>15</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
+        <v>946</v>
+      </c>
+      <c r="F231" t="s">
+        <v>17</v>
+      </c>
+      <c r="G231" t="s">
+        <v>18</v>
+      </c>
+      <c r="H231" t="s">
         <v>974</v>
       </c>
-      <c r="E231" t="s">
-        <v>947</v>
-      </c>
-      <c r="G231" t="s">
+      <c r="I231" t="s">
         <v>975</v>
       </c>
-      <c r="H231" t="s">
+      <c r="J231" t="s">
         <v>988</v>
-      </c>
-      <c r="I231" t="s">
-        <v>20</v>
-      </c>
-      <c r="K231" t="s">
-        <v>21</v>
       </c>
       <c r="L231" t="s">
         <v>950</v>
@@ -12289,23 +12289,23 @@
       <c r="C232" t="s">
         <v>15</v>
       </c>
-      <c r="D232" t="s">
+      <c r="E232" t="s">
+        <v>946</v>
+      </c>
+      <c r="F232" t="s">
+        <v>17</v>
+      </c>
+      <c r="G232" t="s">
+        <v>18</v>
+      </c>
+      <c r="H232" t="s">
         <v>974</v>
       </c>
-      <c r="E232" t="s">
-        <v>947</v>
-      </c>
-      <c r="G232" t="s">
+      <c r="I232" t="s">
         <v>975</v>
       </c>
-      <c r="H232" t="s">
+      <c r="J232" t="s">
         <v>992</v>
-      </c>
-      <c r="I232" t="s">
-        <v>20</v>
-      </c>
-      <c r="K232" t="s">
-        <v>21</v>
       </c>
       <c r="L232" t="s">
         <v>950</v>
@@ -12324,23 +12324,23 @@
       <c r="C233" t="s">
         <v>15</v>
       </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
+        <v>946</v>
+      </c>
+      <c r="F233" t="s">
+        <v>17</v>
+      </c>
+      <c r="G233" t="s">
+        <v>18</v>
+      </c>
+      <c r="H233" t="s">
         <v>996</v>
       </c>
-      <c r="E233" t="s">
-        <v>947</v>
-      </c>
-      <c r="G233" t="s">
+      <c r="I233" t="s">
         <v>997</v>
       </c>
-      <c r="H233" t="s">
+      <c r="J233" t="s">
         <v>998</v>
-      </c>
-      <c r="I233" t="s">
-        <v>20</v>
-      </c>
-      <c r="K233" t="s">
-        <v>21</v>
       </c>
       <c r="L233" t="s">
         <v>950</v>
@@ -12359,23 +12359,23 @@
       <c r="C234" t="s">
         <v>15</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
+        <v>946</v>
+      </c>
+      <c r="F234" t="s">
+        <v>17</v>
+      </c>
+      <c r="G234" t="s">
+        <v>18</v>
+      </c>
+      <c r="H234" t="s">
         <v>996</v>
       </c>
-      <c r="E234" t="s">
-        <v>947</v>
-      </c>
-      <c r="G234" t="s">
+      <c r="I234" t="s">
         <v>997</v>
       </c>
-      <c r="H234" t="s">
+      <c r="J234" t="s">
         <v>1002</v>
-      </c>
-      <c r="I234" t="s">
-        <v>20</v>
-      </c>
-      <c r="K234" t="s">
-        <v>21</v>
       </c>
       <c r="L234" t="s">
         <v>950</v>
@@ -12394,23 +12394,23 @@
       <c r="C235" t="s">
         <v>15</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
+        <v>946</v>
+      </c>
+      <c r="F235" t="s">
+        <v>17</v>
+      </c>
+      <c r="G235" t="s">
+        <v>18</v>
+      </c>
+      <c r="H235" t="s">
         <v>996</v>
       </c>
-      <c r="E235" t="s">
-        <v>947</v>
-      </c>
-      <c r="G235" t="s">
+      <c r="I235" t="s">
         <v>997</v>
       </c>
-      <c r="H235" t="s">
+      <c r="J235" t="s">
         <v>1006</v>
-      </c>
-      <c r="I235" t="s">
-        <v>20</v>
-      </c>
-      <c r="K235" t="s">
-        <v>21</v>
       </c>
       <c r="L235" t="s">
         <v>950</v>
@@ -12429,23 +12429,23 @@
       <c r="C236" t="s">
         <v>15</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
+        <v>946</v>
+      </c>
+      <c r="F236" t="s">
+        <v>17</v>
+      </c>
+      <c r="G236" t="s">
+        <v>18</v>
+      </c>
+      <c r="H236" t="s">
         <v>996</v>
       </c>
-      <c r="E236" t="s">
-        <v>947</v>
-      </c>
-      <c r="G236" t="s">
+      <c r="I236" t="s">
         <v>997</v>
       </c>
-      <c r="H236" t="s">
+      <c r="J236" t="s">
         <v>1010</v>
-      </c>
-      <c r="I236" t="s">
-        <v>20</v>
-      </c>
-      <c r="K236" t="s">
-        <v>21</v>
       </c>
       <c r="L236" t="s">
         <v>950</v>
@@ -12464,23 +12464,23 @@
       <c r="C237" t="s">
         <v>15</v>
       </c>
-      <c r="D237" t="s">
+      <c r="E237" t="s">
+        <v>946</v>
+      </c>
+      <c r="F237" t="s">
+        <v>17</v>
+      </c>
+      <c r="G237" t="s">
+        <v>18</v>
+      </c>
+      <c r="H237" t="s">
         <v>996</v>
       </c>
-      <c r="E237" t="s">
-        <v>947</v>
-      </c>
-      <c r="G237" t="s">
+      <c r="I237" t="s">
         <v>997</v>
       </c>
-      <c r="H237" t="s">
+      <c r="J237" t="s">
         <v>1014</v>
-      </c>
-      <c r="I237" t="s">
-        <v>20</v>
-      </c>
-      <c r="K237" t="s">
-        <v>21</v>
       </c>
       <c r="L237" t="s">
         <v>950</v>
@@ -12499,23 +12499,23 @@
       <c r="C238" t="s">
         <v>15</v>
       </c>
-      <c r="D238" t="s">
+      <c r="E238" t="s">
+        <v>946</v>
+      </c>
+      <c r="F238" t="s">
+        <v>17</v>
+      </c>
+      <c r="G238" t="s">
+        <v>18</v>
+      </c>
+      <c r="H238" t="s">
         <v>996</v>
       </c>
-      <c r="E238" t="s">
-        <v>947</v>
-      </c>
-      <c r="G238" t="s">
+      <c r="I238" t="s">
         <v>997</v>
       </c>
-      <c r="H238" t="s">
+      <c r="J238" t="s">
         <v>1018</v>
-      </c>
-      <c r="I238" t="s">
-        <v>20</v>
-      </c>
-      <c r="K238" t="s">
-        <v>21</v>
       </c>
       <c r="L238" t="s">
         <v>950</v>
@@ -12534,23 +12534,23 @@
       <c r="C239" t="s">
         <v>15</v>
       </c>
-      <c r="D239" t="s">
+      <c r="E239" t="s">
+        <v>946</v>
+      </c>
+      <c r="F239" t="s">
+        <v>17</v>
+      </c>
+      <c r="G239" t="s">
+        <v>18</v>
+      </c>
+      <c r="H239" t="s">
         <v>996</v>
       </c>
-      <c r="E239" t="s">
-        <v>947</v>
-      </c>
-      <c r="G239" t="s">
+      <c r="I239" t="s">
         <v>997</v>
       </c>
-      <c r="H239" t="s">
+      <c r="J239" t="s">
         <v>1022</v>
-      </c>
-      <c r="I239" t="s">
-        <v>20</v>
-      </c>
-      <c r="K239" t="s">
-        <v>21</v>
       </c>
       <c r="L239" t="s">
         <v>950</v>
@@ -12569,23 +12569,23 @@
       <c r="C240" t="s">
         <v>15</v>
       </c>
-      <c r="D240" t="s">
+      <c r="E240" t="s">
+        <v>946</v>
+      </c>
+      <c r="F240" t="s">
+        <v>17</v>
+      </c>
+      <c r="G240" t="s">
+        <v>18</v>
+      </c>
+      <c r="H240" t="s">
         <v>996</v>
       </c>
-      <c r="E240" t="s">
-        <v>947</v>
-      </c>
-      <c r="G240" t="s">
+      <c r="I240" t="s">
         <v>997</v>
       </c>
-      <c r="H240" t="s">
+      <c r="J240" t="s">
         <v>1026</v>
-      </c>
-      <c r="I240" t="s">
-        <v>20</v>
-      </c>
-      <c r="K240" t="s">
-        <v>21</v>
       </c>
       <c r="L240" t="s">
         <v>950</v>
@@ -12604,23 +12604,23 @@
       <c r="C241" t="s">
         <v>15</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
+        <v>946</v>
+      </c>
+      <c r="F241" t="s">
+        <v>17</v>
+      </c>
+      <c r="G241" t="s">
+        <v>18</v>
+      </c>
+      <c r="H241" t="s">
         <v>1030</v>
       </c>
-      <c r="E241" t="s">
-        <v>947</v>
-      </c>
-      <c r="G241" t="s">
+      <c r="I241" t="s">
         <v>1031</v>
       </c>
-      <c r="H241" t="s">
+      <c r="J241" t="s">
         <v>1032</v>
-      </c>
-      <c r="I241" t="s">
-        <v>20</v>
-      </c>
-      <c r="K241" t="s">
-        <v>21</v>
       </c>
       <c r="L241" t="s">
         <v>950</v>
@@ -12639,23 +12639,23 @@
       <c r="C242" t="s">
         <v>15</v>
       </c>
-      <c r="D242" t="s">
+      <c r="E242" t="s">
+        <v>946</v>
+      </c>
+      <c r="F242" t="s">
+        <v>17</v>
+      </c>
+      <c r="G242" t="s">
+        <v>18</v>
+      </c>
+      <c r="H242" t="s">
         <v>1030</v>
       </c>
-      <c r="E242" t="s">
-        <v>947</v>
-      </c>
-      <c r="G242" t="s">
+      <c r="I242" t="s">
         <v>1031</v>
       </c>
-      <c r="H242" t="s">
+      <c r="J242" t="s">
         <v>1036</v>
-      </c>
-      <c r="I242" t="s">
-        <v>20</v>
-      </c>
-      <c r="K242" t="s">
-        <v>21</v>
       </c>
       <c r="L242" t="s">
         <v>950</v>
@@ -12674,23 +12674,23 @@
       <c r="C243" t="s">
         <v>15</v>
       </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
+        <v>946</v>
+      </c>
+      <c r="F243" t="s">
+        <v>17</v>
+      </c>
+      <c r="G243" t="s">
+        <v>18</v>
+      </c>
+      <c r="H243" t="s">
         <v>1030</v>
       </c>
-      <c r="E243" t="s">
-        <v>947</v>
-      </c>
-      <c r="G243" t="s">
+      <c r="I243" t="s">
         <v>1031</v>
       </c>
-      <c r="H243" t="s">
+      <c r="J243" t="s">
         <v>1040</v>
-      </c>
-      <c r="I243" t="s">
-        <v>20</v>
-      </c>
-      <c r="K243" t="s">
-        <v>21</v>
       </c>
       <c r="L243" t="s">
         <v>950</v>
@@ -12709,23 +12709,23 @@
       <c r="C244" t="s">
         <v>15</v>
       </c>
-      <c r="D244" t="s">
+      <c r="E244" t="s">
+        <v>946</v>
+      </c>
+      <c r="F244" t="s">
+        <v>17</v>
+      </c>
+      <c r="G244" t="s">
+        <v>18</v>
+      </c>
+      <c r="H244" t="s">
         <v>1030</v>
       </c>
-      <c r="E244" t="s">
-        <v>947</v>
-      </c>
-      <c r="G244" t="s">
+      <c r="I244" t="s">
         <v>1031</v>
       </c>
-      <c r="H244" t="s">
+      <c r="J244" t="s">
         <v>1044</v>
-      </c>
-      <c r="I244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K244" t="s">
-        <v>21</v>
       </c>
       <c r="L244" t="s">
         <v>950</v>
@@ -12744,23 +12744,23 @@
       <c r="C245" t="s">
         <v>15</v>
       </c>
-      <c r="D245" t="s">
+      <c r="E245" t="s">
+        <v>946</v>
+      </c>
+      <c r="F245" t="s">
+        <v>17</v>
+      </c>
+      <c r="G245" t="s">
+        <v>18</v>
+      </c>
+      <c r="H245" t="s">
         <v>1030</v>
       </c>
-      <c r="E245" t="s">
-        <v>947</v>
-      </c>
-      <c r="G245" t="s">
+      <c r="I245" t="s">
         <v>1031</v>
       </c>
-      <c r="H245" t="s">
+      <c r="J245" t="s">
         <v>1048</v>
-      </c>
-      <c r="I245" t="s">
-        <v>20</v>
-      </c>
-      <c r="K245" t="s">
-        <v>21</v>
       </c>
       <c r="L245" t="s">
         <v>950</v>
@@ -12779,23 +12779,23 @@
       <c r="C246" t="s">
         <v>15</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
+        <v>946</v>
+      </c>
+      <c r="F246" t="s">
+        <v>17</v>
+      </c>
+      <c r="G246" t="s">
+        <v>18</v>
+      </c>
+      <c r="H246" t="s">
         <v>1030</v>
       </c>
-      <c r="E246" t="s">
-        <v>947</v>
-      </c>
-      <c r="G246" t="s">
+      <c r="I246" t="s">
         <v>1031</v>
       </c>
-      <c r="H246" t="s">
+      <c r="J246" t="s">
         <v>1052</v>
-      </c>
-      <c r="I246" t="s">
-        <v>20</v>
-      </c>
-      <c r="K246" t="s">
-        <v>21</v>
       </c>
       <c r="L246" t="s">
         <v>950</v>
@@ -12814,23 +12814,23 @@
       <c r="C247" t="s">
         <v>15</v>
       </c>
-      <c r="D247" t="s">
+      <c r="E247" t="s">
+        <v>946</v>
+      </c>
+      <c r="F247" t="s">
+        <v>17</v>
+      </c>
+      <c r="G247" t="s">
+        <v>18</v>
+      </c>
+      <c r="H247" t="s">
         <v>1030</v>
       </c>
-      <c r="E247" t="s">
-        <v>947</v>
-      </c>
-      <c r="G247" t="s">
+      <c r="I247" t="s">
         <v>1031</v>
       </c>
-      <c r="H247" t="s">
+      <c r="J247" t="s">
         <v>1056</v>
-      </c>
-      <c r="I247" t="s">
-        <v>20</v>
-      </c>
-      <c r="K247" t="s">
-        <v>21</v>
       </c>
       <c r="L247" t="s">
         <v>950</v>
@@ -12849,23 +12849,23 @@
       <c r="C248" t="s">
         <v>15</v>
       </c>
-      <c r="D248" t="s">
+      <c r="E248" t="s">
+        <v>946</v>
+      </c>
+      <c r="F248" t="s">
+        <v>17</v>
+      </c>
+      <c r="G248" t="s">
+        <v>18</v>
+      </c>
+      <c r="H248" t="s">
         <v>1030</v>
       </c>
-      <c r="E248" t="s">
-        <v>947</v>
-      </c>
-      <c r="G248" t="s">
+      <c r="I248" t="s">
         <v>1031</v>
       </c>
-      <c r="H248" t="s">
+      <c r="J248" t="s">
         <v>1060</v>
-      </c>
-      <c r="I248" t="s">
-        <v>20</v>
-      </c>
-      <c r="K248" t="s">
-        <v>21</v>
       </c>
       <c r="L248" t="s">
         <v>950</v>
@@ -12884,23 +12884,23 @@
       <c r="C249" t="s">
         <v>15</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" t="s">
+        <v>946</v>
+      </c>
+      <c r="F249" t="s">
+        <v>17</v>
+      </c>
+      <c r="G249" t="s">
+        <v>18</v>
+      </c>
+      <c r="H249" t="s">
         <v>1030</v>
       </c>
-      <c r="E249" t="s">
-        <v>947</v>
-      </c>
-      <c r="G249" t="s">
+      <c r="I249" t="s">
         <v>1031</v>
       </c>
-      <c r="H249" t="s">
+      <c r="J249" t="s">
         <v>1064</v>
-      </c>
-      <c r="I249" t="s">
-        <v>20</v>
-      </c>
-      <c r="K249" t="s">
-        <v>21</v>
       </c>
       <c r="L249" t="s">
         <v>950</v>
@@ -12919,23 +12919,23 @@
       <c r="C250" t="s">
         <v>15</v>
       </c>
-      <c r="D250" t="s">
+      <c r="E250" t="s">
+        <v>946</v>
+      </c>
+      <c r="F250" t="s">
+        <v>17</v>
+      </c>
+      <c r="G250" t="s">
+        <v>18</v>
+      </c>
+      <c r="H250" t="s">
         <v>1030</v>
       </c>
-      <c r="E250" t="s">
-        <v>947</v>
-      </c>
-      <c r="G250" t="s">
+      <c r="I250" t="s">
         <v>1031</v>
       </c>
-      <c r="H250" t="s">
+      <c r="J250" t="s">
         <v>1068</v>
-      </c>
-      <c r="I250" t="s">
-        <v>20</v>
-      </c>
-      <c r="K250" t="s">
-        <v>21</v>
       </c>
       <c r="L250" t="s">
         <v>950</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,36 +25,36 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-code</t>
   </si>
   <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-name</t>
   </si>
   <si>
-    <t>codeforiati:sub-region-name</t>
+    <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
     <t>codeforiati:intermediate-region-name</t>
   </si>
   <si>
-    <t>codeforiati:sub-region-code</t>
+    <t>codeforiati:iso-alpha-2-code</t>
   </si>
   <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -64,30 +64,30 @@
     <t>active</t>
   </si>
   <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
     <t>001</t>
   </si>
   <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>015</t>
+    <t>DZ</t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>Sub-Saharan Africa</t>
   </si>
   <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>Eastern Africa</t>
   </si>
   <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
     <t>IO</t>
   </si>
   <si>
@@ -442,15 +442,15 @@
     <t>Angola</t>
   </si>
   <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>Middle Africa</t>
   </si>
   <si>
-    <t>AGO</t>
-  </si>
-  <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>AO</t>
   </si>
   <si>
@@ -556,15 +556,15 @@
     <t>Botswana</t>
   </si>
   <si>
+    <t>BWA</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>Southern Africa</t>
   </si>
   <si>
-    <t>BWA</t>
-  </si>
-  <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>BW</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>Benin</t>
   </si>
   <si>
+    <t>BEN</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>Western Africa</t>
   </si>
   <si>
-    <t>BEN</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>BJ</t>
   </si>
   <si>
@@ -835,27 +835,27 @@
     <t>Latin America and the Caribbean</t>
   </si>
   <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
     <t>Caribbean</t>
   </si>
   <si>
-    <t>419</t>
+    <t>AI</t>
   </si>
   <si>
     <t>019</t>
   </si>
   <si>
-    <t>AIA</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -1186,15 +1186,15 @@
     <t>Belize</t>
   </si>
   <si>
+    <t>BLZ</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>Central America</t>
   </si>
   <si>
-    <t>BLZ</t>
-  </si>
-  <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>BZ</t>
   </si>
   <si>
@@ -1288,15 +1288,15 @@
     <t>Argentina</t>
   </si>
   <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>South America</t>
   </si>
   <si>
-    <t>ARG</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>AR</t>
   </si>
   <si>
@@ -1570,18 +1570,18 @@
     <t>143</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
     <t>142</t>
   </si>
   <si>
-    <t>KAZ</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -2206,18 +2206,18 @@
     <t>151</t>
   </si>
   <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2350,15 +2350,15 @@
     <t>Guernsey</t>
   </si>
   <si>
+    <t>GGY</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
     <t>Channel Islands</t>
   </si>
   <si>
-    <t>GGY</t>
-  </si>
-  <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>GG</t>
   </si>
   <si>
@@ -2860,16 +2860,16 @@
     <t>053</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
     <t>009</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>Oceania</t>
   </si>
   <si>
     <t>162</t>
@@ -3618,13 +3618,13 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="L2" t="s">
@@ -3653,14 +3653,14 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
         <v>27</v>
@@ -3688,14 +3688,14 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
         <v>31</v>
@@ -3723,14 +3723,14 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
         <v>35</v>
@@ -3758,14 +3758,14 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
         <v>39</v>
@@ -3793,14 +3793,14 @@
       <c r="F7" t="s">
         <v>18</v>
       </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s">
         <v>43</v>
@@ -3828,14 +3828,14 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
         <v>47</v>
@@ -3855,22 +3855,22 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
         <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
         <v>53</v>
@@ -3896,25 +3896,25 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K10" t="s">
         <v>54</v>
@@ -3937,25 +3937,25 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
@@ -3978,25 +3978,25 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
@@ -4019,25 +4019,25 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
         <v>54</v>
@@ -4060,25 +4060,25 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="K14" t="s">
         <v>54</v>
@@ -4101,25 +4101,25 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K15" t="s">
         <v>54</v>
@@ -4142,25 +4142,25 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
         <v>54</v>
@@ -4183,25 +4183,25 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K17" t="s">
         <v>54</v>
@@ -4224,25 +4224,25 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K18" t="s">
         <v>54</v>
@@ -4265,25 +4265,25 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="K19" t="s">
         <v>54</v>
@@ -4306,25 +4306,25 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="K20" t="s">
         <v>54</v>
@@ -4347,25 +4347,25 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="K21" t="s">
         <v>54</v>
@@ -4388,25 +4388,25 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="K22" t="s">
         <v>54</v>
@@ -4429,25 +4429,25 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="K23" t="s">
         <v>54</v>
@@ -4470,25 +4470,25 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="K24" t="s">
         <v>54</v>
@@ -4511,25 +4511,25 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="K25" t="s">
         <v>54</v>
@@ -4552,25 +4552,25 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="K26" t="s">
         <v>54</v>
@@ -4593,25 +4593,25 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="K27" t="s">
         <v>54</v>
@@ -4634,25 +4634,25 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="K28" t="s">
         <v>54</v>
@@ -4675,25 +4675,25 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
         <v>54</v>
@@ -4716,25 +4716,25 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="K30" t="s">
         <v>54</v>
@@ -4757,22 +4757,22 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
         <v>142</v>
       </c>
-      <c r="H31" t="s">
-        <v>52</v>
-      </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
         <v>143</v>
@@ -4798,25 +4798,25 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K32" t="s">
         <v>144</v>
@@ -4839,25 +4839,25 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G33" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="I33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="K33" t="s">
         <v>144</v>
@@ -4880,25 +4880,25 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="K34" t="s">
         <v>144</v>
@@ -4921,25 +4921,25 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="I35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="K35" t="s">
         <v>144</v>
@@ -4962,25 +4962,25 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="K36" t="s">
         <v>144</v>
@@ -5003,25 +5003,25 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="K37" t="s">
         <v>144</v>
@@ -5044,25 +5044,25 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="K38" t="s">
         <v>144</v>
@@ -5085,25 +5085,25 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="I39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="K39" t="s">
         <v>144</v>
@@ -5126,22 +5126,22 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
         <v>180</v>
       </c>
-      <c r="H40" t="s">
-        <v>52</v>
-      </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
         <v>181</v>
@@ -5167,25 +5167,25 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>52</v>
+        <v>186</v>
       </c>
       <c r="I41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K41" t="s">
         <v>182</v>
@@ -5208,25 +5208,25 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="K42" t="s">
         <v>182</v>
@@ -5249,25 +5249,25 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F43" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>52</v>
+        <v>194</v>
       </c>
       <c r="I43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="K43" t="s">
         <v>182</v>
@@ -5290,25 +5290,25 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="K44" t="s">
         <v>182</v>
@@ -5331,22 +5331,22 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
         <v>202</v>
       </c>
-      <c r="H45" t="s">
-        <v>52</v>
-      </c>
       <c r="I45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s">
         <v>203</v>
@@ -5372,25 +5372,25 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F46" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K46" t="s">
         <v>204</v>
@@ -5413,25 +5413,25 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="I47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="K47" t="s">
         <v>204</v>
@@ -5454,25 +5454,25 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H48" t="s">
-        <v>52</v>
+        <v>216</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="K48" t="s">
         <v>204</v>
@@ -5495,25 +5495,25 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H49" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="K49" t="s">
         <v>204</v>
@@ -5536,25 +5536,25 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F50" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="K50" t="s">
         <v>204</v>
@@ -5577,25 +5577,25 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
-        <v>52</v>
+        <v>228</v>
       </c>
       <c r="I51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="K51" t="s">
         <v>204</v>
@@ -5618,25 +5618,25 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F52" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G52" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
-        <v>52</v>
+        <v>232</v>
       </c>
       <c r="I52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K52" t="s">
         <v>204</v>
@@ -5659,25 +5659,25 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G53" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="I53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="K53" t="s">
         <v>204</v>
@@ -5700,25 +5700,25 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H54" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="I54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="K54" t="s">
         <v>204</v>
@@ -5741,25 +5741,25 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G55" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H55" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
       <c r="K55" t="s">
         <v>204</v>
@@ -5782,25 +5782,25 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G56" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H56" t="s">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="K56" t="s">
         <v>204</v>
@@ -5823,25 +5823,25 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G57" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H57" t="s">
-        <v>52</v>
+        <v>252</v>
       </c>
       <c r="I57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="K57" t="s">
         <v>204</v>
@@ -5864,25 +5864,25 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F58" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H58" t="s">
-        <v>52</v>
+        <v>256</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="K58" t="s">
         <v>204</v>
@@ -5905,25 +5905,25 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F59" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="K59" t="s">
         <v>204</v>
@@ -5946,25 +5946,25 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H60" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>264</v>
+        <v>203</v>
       </c>
       <c r="K60" t="s">
         <v>204</v>
@@ -5987,25 +5987,25 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H61" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="K61" t="s">
         <v>204</v>
@@ -6028,22 +6028,22 @@
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F62" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G62" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I62" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
         <v>276</v>
@@ -6069,25 +6069,25 @@
         <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F63" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H63" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="I63" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K63" t="s">
         <v>277</v>
@@ -6110,25 +6110,25 @@
         <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F64" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H64" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="I64" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K64" t="s">
         <v>277</v>
@@ -6151,25 +6151,25 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F65" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H65" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="I65" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="K65" t="s">
         <v>277</v>
@@ -6192,25 +6192,25 @@
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F66" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H66" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="I66" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="K66" t="s">
         <v>277</v>
@@ -6233,25 +6233,25 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F67" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H67" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="I67" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="K67" t="s">
         <v>277</v>
@@ -6274,25 +6274,25 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F68" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H68" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="I68" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="K68" t="s">
         <v>277</v>
@@ -6315,25 +6315,25 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F69" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H69" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="I69" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="K69" t="s">
         <v>277</v>
@@ -6356,25 +6356,25 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F70" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G70" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H70" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="I70" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="K70" t="s">
         <v>277</v>
@@ -6397,25 +6397,25 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F71" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H71" t="s">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="I71" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="K71" t="s">
         <v>277</v>
@@ -6438,25 +6438,25 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F72" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G72" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H72" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="I72" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="K72" t="s">
         <v>277</v>
@@ -6479,25 +6479,25 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F73" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H73" t="s">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="I73" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="K73" t="s">
         <v>277</v>
@@ -6520,25 +6520,25 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F74" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H74" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="I74" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="K74" t="s">
         <v>277</v>
@@ -6561,25 +6561,25 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F75" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G75" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H75" t="s">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="I75" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="K75" t="s">
         <v>277</v>
@@ -6602,25 +6602,25 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F76" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H76" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="I76" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>334</v>
+        <v>276</v>
       </c>
       <c r="K76" t="s">
         <v>277</v>
@@ -6643,25 +6643,25 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F77" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G77" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H77" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="I77" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>338</v>
+        <v>276</v>
       </c>
       <c r="K77" t="s">
         <v>277</v>
@@ -6684,25 +6684,25 @@
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F78" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H78" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="I78" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>342</v>
+        <v>276</v>
       </c>
       <c r="K78" t="s">
         <v>277</v>
@@ -6725,25 +6725,25 @@
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F79" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H79" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="I79" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="K79" t="s">
         <v>277</v>
@@ -6766,25 +6766,25 @@
         <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F80" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G80" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H80" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="I80" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>350</v>
+        <v>276</v>
       </c>
       <c r="K80" t="s">
         <v>277</v>
@@ -6807,25 +6807,25 @@
         <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F81" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G81" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H81" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
       <c r="I81" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="K81" t="s">
         <v>277</v>
@@ -6848,25 +6848,25 @@
         <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F82" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H82" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="I82" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>358</v>
+        <v>276</v>
       </c>
       <c r="K82" t="s">
         <v>277</v>
@@ -6889,25 +6889,25 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F83" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H83" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="I83" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>362</v>
+        <v>276</v>
       </c>
       <c r="K83" t="s">
         <v>277</v>
@@ -6930,25 +6930,25 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F84" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H84" t="s">
-        <v>274</v>
+        <v>366</v>
       </c>
       <c r="I84" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>366</v>
+        <v>276</v>
       </c>
       <c r="K84" t="s">
         <v>277</v>
@@ -6971,25 +6971,25 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F85" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H85" t="s">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="I85" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>370</v>
+        <v>276</v>
       </c>
       <c r="K85" t="s">
         <v>277</v>
@@ -7012,25 +7012,25 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F86" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H86" t="s">
-        <v>274</v>
+        <v>374</v>
       </c>
       <c r="I86" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>374</v>
+        <v>276</v>
       </c>
       <c r="K86" t="s">
         <v>277</v>
@@ -7053,25 +7053,25 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F87" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H87" t="s">
-        <v>274</v>
+        <v>378</v>
       </c>
       <c r="I87" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="K87" t="s">
         <v>277</v>
@@ -7094,25 +7094,25 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F88" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H88" t="s">
-        <v>274</v>
+        <v>382</v>
       </c>
       <c r="I88" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>382</v>
+        <v>276</v>
       </c>
       <c r="K88" t="s">
         <v>277</v>
@@ -7135,25 +7135,25 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F89" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H89" t="s">
-        <v>274</v>
+        <v>386</v>
       </c>
       <c r="I89" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>386</v>
+        <v>276</v>
       </c>
       <c r="K89" t="s">
         <v>277</v>
@@ -7176,22 +7176,22 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F90" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G90" t="s">
+        <v>274</v>
+      </c>
+      <c r="H90" t="s">
         <v>390</v>
       </c>
-      <c r="H90" t="s">
-        <v>274</v>
-      </c>
       <c r="I90" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
         <v>391</v>
@@ -7217,25 +7217,25 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F91" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G91" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H91" t="s">
-        <v>274</v>
+        <v>396</v>
       </c>
       <c r="I91" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="K91" t="s">
         <v>392</v>
@@ -7258,25 +7258,25 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F92" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G92" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H92" t="s">
-        <v>274</v>
+        <v>400</v>
       </c>
       <c r="I92" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="K92" t="s">
         <v>392</v>
@@ -7299,25 +7299,25 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F93" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H93" t="s">
-        <v>274</v>
+        <v>404</v>
       </c>
       <c r="I93" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="K93" t="s">
         <v>392</v>
@@ -7340,25 +7340,25 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F94" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H94" t="s">
-        <v>274</v>
+        <v>408</v>
       </c>
       <c r="I94" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="K94" t="s">
         <v>392</v>
@@ -7381,25 +7381,25 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F95" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G95" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H95" t="s">
-        <v>274</v>
+        <v>412</v>
       </c>
       <c r="I95" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="K95" t="s">
         <v>392</v>
@@ -7422,25 +7422,25 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F96" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H96" t="s">
-        <v>274</v>
+        <v>416</v>
       </c>
       <c r="I96" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="K96" t="s">
         <v>392</v>
@@ -7463,25 +7463,25 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F97" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="H97" t="s">
-        <v>274</v>
+        <v>420</v>
       </c>
       <c r="I97" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="K97" t="s">
         <v>392</v>
@@ -7504,22 +7504,22 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F98" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G98" t="s">
+        <v>274</v>
+      </c>
+      <c r="H98" t="s">
         <v>424</v>
       </c>
-      <c r="H98" t="s">
-        <v>274</v>
-      </c>
       <c r="I98" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s">
         <v>425</v>
@@ -7545,25 +7545,25 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F99" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H99" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="I99" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="K99" t="s">
         <v>426</v>
@@ -7586,25 +7586,25 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F100" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H100" t="s">
-        <v>274</v>
+        <v>434</v>
       </c>
       <c r="I100" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J100" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="K100" t="s">
         <v>426</v>
@@ -7627,25 +7627,25 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F101" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H101" t="s">
-        <v>274</v>
+        <v>438</v>
       </c>
       <c r="I101" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J101" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="K101" t="s">
         <v>426</v>
@@ -7668,25 +7668,25 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F102" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H102" t="s">
-        <v>274</v>
+        <v>442</v>
       </c>
       <c r="I102" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J102" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="K102" t="s">
         <v>426</v>
@@ -7709,25 +7709,25 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F103" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H103" t="s">
-        <v>274</v>
+        <v>446</v>
       </c>
       <c r="I103" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J103" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="K103" t="s">
         <v>426</v>
@@ -7750,25 +7750,25 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F104" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H104" t="s">
-        <v>274</v>
+        <v>450</v>
       </c>
       <c r="I104" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J104" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="K104" t="s">
         <v>426</v>
@@ -7791,25 +7791,25 @@
         <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F105" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H105" t="s">
-        <v>274</v>
+        <v>454</v>
       </c>
       <c r="I105" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J105" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="K105" t="s">
         <v>426</v>
@@ -7832,25 +7832,25 @@
         <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F106" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H106" t="s">
-        <v>274</v>
+        <v>458</v>
       </c>
       <c r="I106" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J106" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="K106" t="s">
         <v>426</v>
@@ -7873,25 +7873,25 @@
         <v>15</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F107" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G107" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H107" t="s">
-        <v>274</v>
+        <v>462</v>
       </c>
       <c r="I107" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J107" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="K107" t="s">
         <v>426</v>
@@ -7914,25 +7914,25 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F108" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H108" t="s">
-        <v>274</v>
+        <v>466</v>
       </c>
       <c r="I108" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J108" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="K108" t="s">
         <v>426</v>
@@ -7955,25 +7955,25 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F109" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H109" t="s">
-        <v>274</v>
+        <v>470</v>
       </c>
       <c r="I109" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J109" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="K109" t="s">
         <v>426</v>
@@ -7996,25 +7996,25 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F110" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G110" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H110" t="s">
-        <v>274</v>
+        <v>474</v>
       </c>
       <c r="I110" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J110" t="s">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="K110" t="s">
         <v>426</v>
@@ -8037,25 +8037,25 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F111" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G111" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H111" t="s">
-        <v>274</v>
+        <v>478</v>
       </c>
       <c r="I111" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J111" t="s">
-        <v>478</v>
+        <v>425</v>
       </c>
       <c r="K111" t="s">
         <v>426</v>
@@ -8078,25 +8078,25 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G112" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H112" t="s">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="I112" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J112" t="s">
-        <v>482</v>
+        <v>425</v>
       </c>
       <c r="K112" t="s">
         <v>426</v>
@@ -8119,25 +8119,25 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="F113" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="G113" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="H113" t="s">
-        <v>274</v>
+        <v>486</v>
       </c>
       <c r="I113" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J113" t="s">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="K113" t="s">
         <v>426</v>
@@ -8160,22 +8160,22 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="F114" t="s">
-        <v>490</v>
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>274</v>
       </c>
       <c r="H114" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I114" t="s">
-        <v>275</v>
-      </c>
-      <c r="J114" t="s">
-        <v>492</v>
+        <v>21</v>
       </c>
       <c r="L114" t="s">
         <v>493</v>
@@ -8195,22 +8195,22 @@
         <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="F115" t="s">
-        <v>490</v>
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>274</v>
       </c>
       <c r="H115" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="I115" t="s">
-        <v>275</v>
-      </c>
-      <c r="J115" t="s">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="L115" t="s">
         <v>497</v>
@@ -8230,22 +8230,22 @@
         <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="F116" t="s">
-        <v>490</v>
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>274</v>
       </c>
       <c r="H116" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="I116" t="s">
-        <v>275</v>
-      </c>
-      <c r="J116" t="s">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="L116" t="s">
         <v>501</v>
@@ -8265,22 +8265,22 @@
         <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="F117" t="s">
-        <v>490</v>
+        <v>18</v>
+      </c>
+      <c r="G117" t="s">
+        <v>274</v>
       </c>
       <c r="H117" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="I117" t="s">
-        <v>275</v>
-      </c>
-      <c r="J117" t="s">
-        <v>504</v>
+        <v>21</v>
       </c>
       <c r="L117" t="s">
         <v>505</v>
@@ -8300,22 +8300,22 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="F118" t="s">
-        <v>490</v>
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>274</v>
       </c>
       <c r="H118" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="I118" t="s">
-        <v>275</v>
-      </c>
-      <c r="J118" t="s">
-        <v>508</v>
+        <v>21</v>
       </c>
       <c r="L118" t="s">
         <v>509</v>
@@ -8334,14 +8334,14 @@
       <c r="C119" t="s">
         <v>15</v>
       </c>
-      <c r="D119" t="s">
-        <v>16</v>
-      </c>
-      <c r="E119" t="s">
-        <v>17</v>
-      </c>
-      <c r="J119" t="s">
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
+      <c r="H119" t="s">
         <v>512</v>
+      </c>
+      <c r="I119" t="s">
+        <v>21</v>
       </c>
       <c r="L119" t="s">
         <v>513</v>
@@ -8358,22 +8358,22 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="F120" t="s">
-        <v>516</v>
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>518</v>
       </c>
       <c r="H120" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I120" t="s">
-        <v>518</v>
-      </c>
-      <c r="J120" t="s">
-        <v>519</v>
+        <v>21</v>
       </c>
       <c r="L120" t="s">
         <v>520</v>
@@ -8393,22 +8393,22 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="F121" t="s">
-        <v>516</v>
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>518</v>
       </c>
       <c r="H121" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="I121" t="s">
-        <v>518</v>
-      </c>
-      <c r="J121" t="s">
-        <v>524</v>
+        <v>21</v>
       </c>
       <c r="L121" t="s">
         <v>525</v>
@@ -8428,22 +8428,22 @@
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="F122" t="s">
-        <v>516</v>
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>518</v>
       </c>
       <c r="H122" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="I122" t="s">
-        <v>518</v>
-      </c>
-      <c r="J122" t="s">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="L122" t="s">
         <v>529</v>
@@ -8463,22 +8463,22 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="F123" t="s">
-        <v>516</v>
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>518</v>
       </c>
       <c r="H123" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="I123" t="s">
-        <v>518</v>
-      </c>
-      <c r="J123" t="s">
-        <v>532</v>
+        <v>21</v>
       </c>
       <c r="L123" t="s">
         <v>533</v>
@@ -8498,22 +8498,22 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="F124" t="s">
-        <v>516</v>
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>518</v>
       </c>
       <c r="H124" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="I124" t="s">
-        <v>518</v>
-      </c>
-      <c r="J124" t="s">
-        <v>536</v>
+        <v>21</v>
       </c>
       <c r="L124" t="s">
         <v>537</v>
@@ -8533,22 +8533,22 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F125" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>518</v>
       </c>
       <c r="H125" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I125" t="s">
-        <v>518</v>
-      </c>
-      <c r="J125" t="s">
-        <v>542</v>
+        <v>21</v>
       </c>
       <c r="L125" t="s">
         <v>543</v>
@@ -8568,22 +8568,22 @@
         <v>15</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F126" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>518</v>
       </c>
       <c r="H126" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="I126" t="s">
-        <v>518</v>
-      </c>
-      <c r="J126" t="s">
-        <v>546</v>
+        <v>21</v>
       </c>
       <c r="L126" t="s">
         <v>547</v>
@@ -8603,22 +8603,22 @@
         <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E127" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F127" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>518</v>
       </c>
       <c r="H127" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="I127" t="s">
-        <v>518</v>
-      </c>
-      <c r="J127" t="s">
-        <v>550</v>
+        <v>21</v>
       </c>
       <c r="L127" t="s">
         <v>551</v>
@@ -8638,22 +8638,22 @@
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E128" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F128" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>518</v>
       </c>
       <c r="H128" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="I128" t="s">
-        <v>518</v>
-      </c>
-      <c r="J128" t="s">
-        <v>554</v>
+        <v>21</v>
       </c>
       <c r="L128" t="s">
         <v>555</v>
@@ -8673,22 +8673,22 @@
         <v>15</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E129" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F129" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>518</v>
       </c>
       <c r="H129" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="I129" t="s">
-        <v>518</v>
-      </c>
-      <c r="J129" t="s">
-        <v>558</v>
+        <v>21</v>
       </c>
       <c r="L129" t="s">
         <v>559</v>
@@ -8708,22 +8708,22 @@
         <v>15</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F130" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>518</v>
       </c>
       <c r="H130" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="I130" t="s">
-        <v>518</v>
-      </c>
-      <c r="J130" t="s">
-        <v>562</v>
+        <v>21</v>
       </c>
       <c r="L130" t="s">
         <v>563</v>
@@ -8743,22 +8743,22 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>541</v>
       </c>
       <c r="F131" t="s">
-        <v>540</v>
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>518</v>
       </c>
       <c r="H131" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="I131" t="s">
-        <v>518</v>
-      </c>
-      <c r="J131" t="s">
-        <v>566</v>
+        <v>21</v>
       </c>
       <c r="L131" t="s">
         <v>567</v>
@@ -8778,22 +8778,22 @@
         <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E132" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F132" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G132" t="s">
+        <v>518</v>
       </c>
       <c r="H132" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I132" t="s">
-        <v>518</v>
-      </c>
-      <c r="J132" t="s">
-        <v>572</v>
+        <v>21</v>
       </c>
       <c r="L132" t="s">
         <v>573</v>
@@ -8813,22 +8813,22 @@
         <v>15</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E133" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F133" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G133" t="s">
+        <v>518</v>
       </c>
       <c r="H133" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I133" t="s">
-        <v>518</v>
-      </c>
-      <c r="J133" t="s">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="L133" t="s">
         <v>577</v>
@@ -8848,22 +8848,22 @@
         <v>15</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F134" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G134" t="s">
+        <v>518</v>
       </c>
       <c r="H134" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="I134" t="s">
-        <v>518</v>
-      </c>
-      <c r="J134" t="s">
-        <v>580</v>
+        <v>21</v>
       </c>
       <c r="L134" t="s">
         <v>581</v>
@@ -8883,22 +8883,22 @@
         <v>15</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F135" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G135" t="s">
+        <v>518</v>
       </c>
       <c r="H135" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="I135" t="s">
-        <v>518</v>
-      </c>
-      <c r="J135" t="s">
-        <v>584</v>
+        <v>21</v>
       </c>
       <c r="L135" t="s">
         <v>585</v>
@@ -8918,22 +8918,22 @@
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E136" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F136" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G136" t="s">
+        <v>518</v>
       </c>
       <c r="H136" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="I136" t="s">
-        <v>518</v>
-      </c>
-      <c r="J136" t="s">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="L136" t="s">
         <v>589</v>
@@ -8953,22 +8953,22 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E137" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F137" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G137" t="s">
+        <v>518</v>
       </c>
       <c r="H137" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="I137" t="s">
-        <v>518</v>
-      </c>
-      <c r="J137" t="s">
-        <v>592</v>
+        <v>21</v>
       </c>
       <c r="L137" t="s">
         <v>593</v>
@@ -8988,22 +8988,22 @@
         <v>15</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E138" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F138" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>518</v>
       </c>
       <c r="H138" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="I138" t="s">
-        <v>518</v>
-      </c>
-      <c r="J138" t="s">
-        <v>596</v>
+        <v>21</v>
       </c>
       <c r="L138" t="s">
         <v>597</v>
@@ -9023,22 +9023,22 @@
         <v>15</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F139" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G139" t="s">
+        <v>518</v>
       </c>
       <c r="H139" t="s">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="I139" t="s">
-        <v>518</v>
-      </c>
-      <c r="J139" t="s">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="L139" t="s">
         <v>601</v>
@@ -9058,22 +9058,22 @@
         <v>15</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F140" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G140" t="s">
+        <v>518</v>
       </c>
       <c r="H140" t="s">
-        <v>571</v>
+        <v>604</v>
       </c>
       <c r="I140" t="s">
-        <v>518</v>
-      </c>
-      <c r="J140" t="s">
-        <v>604</v>
+        <v>21</v>
       </c>
       <c r="L140" t="s">
         <v>605</v>
@@ -9093,22 +9093,22 @@
         <v>15</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F141" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G141" t="s">
+        <v>518</v>
       </c>
       <c r="H141" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="I141" t="s">
-        <v>518</v>
-      </c>
-      <c r="J141" t="s">
-        <v>608</v>
+        <v>21</v>
       </c>
       <c r="L141" t="s">
         <v>609</v>
@@ -9128,22 +9128,22 @@
         <v>15</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="F142" t="s">
-        <v>570</v>
+        <v>18</v>
+      </c>
+      <c r="G142" t="s">
+        <v>518</v>
       </c>
       <c r="H142" t="s">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="I142" t="s">
-        <v>518</v>
-      </c>
-      <c r="J142" t="s">
-        <v>612</v>
+        <v>21</v>
       </c>
       <c r="L142" t="s">
         <v>613</v>
@@ -9163,22 +9163,22 @@
         <v>15</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E143" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F143" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G143" t="s">
+        <v>518</v>
       </c>
       <c r="H143" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I143" t="s">
-        <v>518</v>
-      </c>
-      <c r="J143" t="s">
-        <v>618</v>
+        <v>21</v>
       </c>
       <c r="L143" t="s">
         <v>619</v>
@@ -9198,22 +9198,22 @@
         <v>15</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E144" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F144" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G144" t="s">
+        <v>518</v>
       </c>
       <c r="H144" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="I144" t="s">
-        <v>518</v>
-      </c>
-      <c r="J144" t="s">
-        <v>622</v>
+        <v>21</v>
       </c>
       <c r="L144" t="s">
         <v>623</v>
@@ -9233,22 +9233,22 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F145" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G145" t="s">
+        <v>518</v>
       </c>
       <c r="H145" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="I145" t="s">
-        <v>518</v>
-      </c>
-      <c r="J145" t="s">
-        <v>626</v>
+        <v>21</v>
       </c>
       <c r="L145" t="s">
         <v>627</v>
@@ -9268,22 +9268,22 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E146" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F146" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G146" t="s">
+        <v>518</v>
       </c>
       <c r="H146" t="s">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="I146" t="s">
-        <v>518</v>
-      </c>
-      <c r="J146" t="s">
-        <v>630</v>
+        <v>21</v>
       </c>
       <c r="L146" t="s">
         <v>631</v>
@@ -9303,22 +9303,22 @@
         <v>15</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F147" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G147" t="s">
+        <v>518</v>
       </c>
       <c r="H147" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="I147" t="s">
-        <v>518</v>
-      </c>
-      <c r="J147" t="s">
-        <v>634</v>
+        <v>21</v>
       </c>
       <c r="L147" t="s">
         <v>635</v>
@@ -9338,22 +9338,22 @@
         <v>15</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E148" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F148" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G148" t="s">
+        <v>518</v>
       </c>
       <c r="H148" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="I148" t="s">
-        <v>518</v>
-      </c>
-      <c r="J148" t="s">
-        <v>638</v>
+        <v>21</v>
       </c>
       <c r="L148" t="s">
         <v>639</v>
@@ -9373,22 +9373,22 @@
         <v>15</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E149" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F149" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G149" t="s">
+        <v>518</v>
       </c>
       <c r="H149" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="I149" t="s">
-        <v>518</v>
-      </c>
-      <c r="J149" t="s">
-        <v>642</v>
+        <v>21</v>
       </c>
       <c r="L149" t="s">
         <v>643</v>
@@ -9408,22 +9408,22 @@
         <v>15</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E150" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F150" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>518</v>
       </c>
       <c r="H150" t="s">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="I150" t="s">
-        <v>518</v>
-      </c>
-      <c r="J150" t="s">
-        <v>646</v>
+        <v>21</v>
       </c>
       <c r="L150" t="s">
         <v>647</v>
@@ -9443,22 +9443,22 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E151" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="F151" t="s">
-        <v>616</v>
+        <v>18</v>
+      </c>
+      <c r="G151" t="s">
+        <v>518</v>
       </c>
       <c r="H151" t="s">
-        <v>617</v>
+        <v>650</v>
       </c>
       <c r="I151" t="s">
-        <v>518</v>
-      </c>
-      <c r="J151" t="s">
-        <v>650</v>
+        <v>21</v>
       </c>
       <c r="L151" t="s">
         <v>651</v>
@@ -9478,22 +9478,22 @@
         <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E152" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F152" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G152" t="s">
+        <v>518</v>
       </c>
       <c r="H152" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I152" t="s">
-        <v>518</v>
-      </c>
-      <c r="J152" t="s">
-        <v>656</v>
+        <v>21</v>
       </c>
       <c r="L152" t="s">
         <v>657</v>
@@ -9513,22 +9513,22 @@
         <v>15</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E153" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F153" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G153" t="s">
+        <v>518</v>
       </c>
       <c r="H153" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="I153" t="s">
-        <v>518</v>
-      </c>
-      <c r="J153" t="s">
-        <v>660</v>
+        <v>21</v>
       </c>
       <c r="L153" t="s">
         <v>661</v>
@@ -9548,22 +9548,22 @@
         <v>15</v>
       </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F154" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G154" t="s">
+        <v>518</v>
       </c>
       <c r="H154" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="I154" t="s">
-        <v>518</v>
-      </c>
-      <c r="J154" t="s">
-        <v>664</v>
+        <v>21</v>
       </c>
       <c r="L154" t="s">
         <v>665</v>
@@ -9583,22 +9583,22 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F155" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>518</v>
       </c>
       <c r="H155" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="I155" t="s">
-        <v>518</v>
-      </c>
-      <c r="J155" t="s">
-        <v>668</v>
+        <v>21</v>
       </c>
       <c r="L155" t="s">
         <v>669</v>
@@ -9618,22 +9618,22 @@
         <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E156" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F156" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>518</v>
       </c>
       <c r="H156" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="I156" t="s">
-        <v>518</v>
-      </c>
-      <c r="J156" t="s">
-        <v>672</v>
+        <v>21</v>
       </c>
       <c r="L156" t="s">
         <v>673</v>
@@ -9653,22 +9653,22 @@
         <v>15</v>
       </c>
       <c r="D157" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F157" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>518</v>
       </c>
       <c r="H157" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
       <c r="I157" t="s">
-        <v>518</v>
-      </c>
-      <c r="J157" t="s">
-        <v>676</v>
+        <v>21</v>
       </c>
       <c r="L157" t="s">
         <v>677</v>
@@ -9688,22 +9688,22 @@
         <v>15</v>
       </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F158" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>518</v>
       </c>
       <c r="H158" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="I158" t="s">
-        <v>518</v>
-      </c>
-      <c r="J158" t="s">
-        <v>680</v>
+        <v>21</v>
       </c>
       <c r="L158" t="s">
         <v>681</v>
@@ -9723,22 +9723,22 @@
         <v>15</v>
       </c>
       <c r="D159" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F159" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>518</v>
       </c>
       <c r="H159" t="s">
-        <v>655</v>
+        <v>684</v>
       </c>
       <c r="I159" t="s">
-        <v>518</v>
-      </c>
-      <c r="J159" t="s">
-        <v>684</v>
+        <v>21</v>
       </c>
       <c r="L159" t="s">
         <v>685</v>
@@ -9758,22 +9758,22 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F160" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>518</v>
       </c>
       <c r="H160" t="s">
-        <v>655</v>
+        <v>688</v>
       </c>
       <c r="I160" t="s">
-        <v>518</v>
-      </c>
-      <c r="J160" t="s">
-        <v>688</v>
+        <v>21</v>
       </c>
       <c r="L160" t="s">
         <v>689</v>
@@ -9793,22 +9793,22 @@
         <v>15</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F161" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>518</v>
       </c>
       <c r="H161" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="I161" t="s">
-        <v>518</v>
-      </c>
-      <c r="J161" t="s">
-        <v>692</v>
+        <v>21</v>
       </c>
       <c r="L161" t="s">
         <v>693</v>
@@ -9828,22 +9828,22 @@
         <v>15</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F162" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>518</v>
       </c>
       <c r="H162" t="s">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="I162" t="s">
-        <v>518</v>
-      </c>
-      <c r="J162" t="s">
-        <v>696</v>
+        <v>21</v>
       </c>
       <c r="L162" t="s">
         <v>697</v>
@@ -9863,22 +9863,22 @@
         <v>15</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F163" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>518</v>
       </c>
       <c r="H163" t="s">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="I163" t="s">
-        <v>518</v>
-      </c>
-      <c r="J163" t="s">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="L163" t="s">
         <v>701</v>
@@ -9898,22 +9898,22 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F164" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G164" t="s">
+        <v>518</v>
       </c>
       <c r="H164" t="s">
-        <v>655</v>
+        <v>704</v>
       </c>
       <c r="I164" t="s">
-        <v>518</v>
-      </c>
-      <c r="J164" t="s">
-        <v>704</v>
+        <v>21</v>
       </c>
       <c r="L164" t="s">
         <v>705</v>
@@ -9933,22 +9933,22 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F165" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G165" t="s">
+        <v>518</v>
       </c>
       <c r="H165" t="s">
-        <v>655</v>
+        <v>708</v>
       </c>
       <c r="I165" t="s">
-        <v>518</v>
-      </c>
-      <c r="J165" t="s">
-        <v>708</v>
+        <v>21</v>
       </c>
       <c r="L165" t="s">
         <v>709</v>
@@ -9968,22 +9968,22 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F166" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G166" t="s">
+        <v>518</v>
       </c>
       <c r="H166" t="s">
-        <v>655</v>
+        <v>712</v>
       </c>
       <c r="I166" t="s">
-        <v>518</v>
-      </c>
-      <c r="J166" t="s">
-        <v>712</v>
+        <v>21</v>
       </c>
       <c r="L166" t="s">
         <v>713</v>
@@ -10003,22 +10003,22 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E167" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F167" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G167" t="s">
+        <v>518</v>
       </c>
       <c r="H167" t="s">
-        <v>655</v>
+        <v>716</v>
       </c>
       <c r="I167" t="s">
-        <v>518</v>
-      </c>
-      <c r="J167" t="s">
-        <v>716</v>
+        <v>21</v>
       </c>
       <c r="L167" t="s">
         <v>717</v>
@@ -10038,22 +10038,22 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E168" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F168" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G168" t="s">
+        <v>518</v>
       </c>
       <c r="H168" t="s">
-        <v>655</v>
+        <v>720</v>
       </c>
       <c r="I168" t="s">
-        <v>518</v>
-      </c>
-      <c r="J168" t="s">
-        <v>720</v>
+        <v>21</v>
       </c>
       <c r="L168" t="s">
         <v>721</v>
@@ -10073,22 +10073,22 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E169" t="s">
-        <v>17</v>
+        <v>655</v>
       </c>
       <c r="F169" t="s">
-        <v>654</v>
+        <v>18</v>
+      </c>
+      <c r="G169" t="s">
+        <v>518</v>
       </c>
       <c r="H169" t="s">
-        <v>655</v>
+        <v>724</v>
       </c>
       <c r="I169" t="s">
-        <v>518</v>
-      </c>
-      <c r="J169" t="s">
-        <v>724</v>
+        <v>21</v>
       </c>
       <c r="L169" t="s">
         <v>725</v>
@@ -10108,22 +10108,22 @@
         <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F170" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G170" t="s">
+        <v>730</v>
       </c>
       <c r="H170" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="I170" t="s">
-        <v>730</v>
-      </c>
-      <c r="J170" t="s">
-        <v>731</v>
+        <v>21</v>
       </c>
       <c r="L170" t="s">
         <v>732</v>
@@ -10143,22 +10143,22 @@
         <v>15</v>
       </c>
       <c r="D171" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E171" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F171" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G171" t="s">
+        <v>730</v>
       </c>
       <c r="H171" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="I171" t="s">
-        <v>730</v>
-      </c>
-      <c r="J171" t="s">
-        <v>736</v>
+        <v>21</v>
       </c>
       <c r="L171" t="s">
         <v>737</v>
@@ -10178,22 +10178,22 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E172" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F172" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G172" t="s">
+        <v>730</v>
       </c>
       <c r="H172" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="I172" t="s">
-        <v>730</v>
-      </c>
-      <c r="J172" t="s">
-        <v>740</v>
+        <v>21</v>
       </c>
       <c r="L172" t="s">
         <v>741</v>
@@ -10213,22 +10213,22 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F173" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G173" t="s">
+        <v>730</v>
       </c>
       <c r="H173" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="I173" t="s">
-        <v>730</v>
-      </c>
-      <c r="J173" t="s">
-        <v>744</v>
+        <v>21</v>
       </c>
       <c r="L173" t="s">
         <v>745</v>
@@ -10248,22 +10248,22 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E174" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F174" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G174" t="s">
+        <v>730</v>
       </c>
       <c r="H174" t="s">
-        <v>729</v>
+        <v>748</v>
       </c>
       <c r="I174" t="s">
-        <v>730</v>
-      </c>
-      <c r="J174" t="s">
-        <v>748</v>
+        <v>21</v>
       </c>
       <c r="L174" t="s">
         <v>749</v>
@@ -10283,22 +10283,22 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E175" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F175" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G175" t="s">
+        <v>730</v>
       </c>
       <c r="H175" t="s">
-        <v>729</v>
+        <v>752</v>
       </c>
       <c r="I175" t="s">
-        <v>730</v>
-      </c>
-      <c r="J175" t="s">
-        <v>752</v>
+        <v>21</v>
       </c>
       <c r="L175" t="s">
         <v>753</v>
@@ -10318,22 +10318,22 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E176" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F176" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G176" t="s">
+        <v>730</v>
       </c>
       <c r="H176" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="I176" t="s">
-        <v>730</v>
-      </c>
-      <c r="J176" t="s">
-        <v>756</v>
+        <v>21</v>
       </c>
       <c r="L176" t="s">
         <v>757</v>
@@ -10353,22 +10353,22 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F177" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G177" t="s">
+        <v>730</v>
       </c>
       <c r="H177" t="s">
-        <v>729</v>
+        <v>760</v>
       </c>
       <c r="I177" t="s">
-        <v>730</v>
-      </c>
-      <c r="J177" t="s">
-        <v>760</v>
+        <v>21</v>
       </c>
       <c r="L177" t="s">
         <v>761</v>
@@ -10388,22 +10388,22 @@
         <v>15</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F178" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G178" t="s">
+        <v>730</v>
       </c>
       <c r="H178" t="s">
-        <v>729</v>
+        <v>764</v>
       </c>
       <c r="I178" t="s">
-        <v>730</v>
-      </c>
-      <c r="J178" t="s">
-        <v>764</v>
+        <v>21</v>
       </c>
       <c r="L178" t="s">
         <v>765</v>
@@ -10423,22 +10423,22 @@
         <v>15</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>729</v>
       </c>
       <c r="F179" t="s">
-        <v>728</v>
+        <v>18</v>
+      </c>
+      <c r="G179" t="s">
+        <v>730</v>
       </c>
       <c r="H179" t="s">
-        <v>729</v>
+        <v>768</v>
       </c>
       <c r="I179" t="s">
-        <v>730</v>
-      </c>
-      <c r="J179" t="s">
-        <v>768</v>
+        <v>21</v>
       </c>
       <c r="L179" t="s">
         <v>769</v>
@@ -10458,22 +10458,22 @@
         <v>15</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F180" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G180" t="s">
+        <v>730</v>
       </c>
       <c r="H180" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I180" t="s">
-        <v>730</v>
-      </c>
-      <c r="J180" t="s">
-        <v>774</v>
+        <v>21</v>
       </c>
       <c r="L180" t="s">
         <v>775</v>
@@ -10493,22 +10493,22 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F181" t="s">
-        <v>772</v>
+        <v>18</v>
       </c>
       <c r="G181" t="s">
+        <v>730</v>
+      </c>
+      <c r="H181" t="s">
         <v>778</v>
       </c>
-      <c r="H181" t="s">
-        <v>773</v>
-      </c>
       <c r="I181" t="s">
-        <v>730</v>
+        <v>21</v>
       </c>
       <c r="J181" t="s">
         <v>779</v>
@@ -10534,25 +10534,25 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F182" t="s">
-        <v>772</v>
+        <v>18</v>
       </c>
       <c r="G182" t="s">
-        <v>778</v>
+        <v>730</v>
       </c>
       <c r="H182" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="I182" t="s">
-        <v>730</v>
+        <v>21</v>
       </c>
       <c r="J182" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="K182" t="s">
         <v>780</v>
@@ -10575,22 +10575,22 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E183" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F183" t="s">
-        <v>772</v>
+        <v>18</v>
       </c>
       <c r="G183" t="s">
-        <v>778</v>
-      </c>
-      <c r="H183" t="s">
-        <v>773</v>
+        <v>730</v>
       </c>
       <c r="I183" t="s">
-        <v>730</v>
+        <v>21</v>
+      </c>
+      <c r="J183" t="s">
+        <v>779</v>
       </c>
       <c r="K183" t="s">
         <v>780</v>
@@ -10610,22 +10610,22 @@
         <v>15</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F184" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G184" t="s">
+        <v>730</v>
       </c>
       <c r="H184" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="I184" t="s">
-        <v>730</v>
-      </c>
-      <c r="J184" t="s">
-        <v>790</v>
+        <v>21</v>
       </c>
       <c r="L184" t="s">
         <v>791</v>
@@ -10645,22 +10645,22 @@
         <v>15</v>
       </c>
       <c r="D185" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E185" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F185" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G185" t="s">
+        <v>730</v>
       </c>
       <c r="H185" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="I185" t="s">
-        <v>730</v>
-      </c>
-      <c r="J185" t="s">
-        <v>794</v>
+        <v>21</v>
       </c>
       <c r="L185" t="s">
         <v>795</v>
@@ -10680,22 +10680,22 @@
         <v>15</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E186" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F186" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G186" t="s">
+        <v>730</v>
       </c>
       <c r="H186" t="s">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="I186" t="s">
-        <v>730</v>
-      </c>
-      <c r="J186" t="s">
-        <v>798</v>
+        <v>21</v>
       </c>
       <c r="L186" t="s">
         <v>799</v>
@@ -10715,22 +10715,22 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F187" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G187" t="s">
+        <v>730</v>
       </c>
       <c r="H187" t="s">
-        <v>773</v>
+        <v>802</v>
       </c>
       <c r="I187" t="s">
-        <v>730</v>
-      </c>
-      <c r="J187" t="s">
-        <v>802</v>
+        <v>21</v>
       </c>
       <c r="L187" t="s">
         <v>803</v>
@@ -10750,22 +10750,22 @@
         <v>15</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E188" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F188" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G188" t="s">
+        <v>730</v>
       </c>
       <c r="H188" t="s">
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="I188" t="s">
-        <v>730</v>
-      </c>
-      <c r="J188" t="s">
-        <v>806</v>
+        <v>21</v>
       </c>
       <c r="L188" t="s">
         <v>807</v>
@@ -10785,22 +10785,22 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E189" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F189" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G189" t="s">
+        <v>730</v>
       </c>
       <c r="H189" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="I189" t="s">
-        <v>730</v>
-      </c>
-      <c r="J189" t="s">
-        <v>810</v>
+        <v>21</v>
       </c>
       <c r="L189" t="s">
         <v>811</v>
@@ -10820,22 +10820,22 @@
         <v>15</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E190" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F190" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G190" t="s">
+        <v>730</v>
       </c>
       <c r="H190" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="I190" t="s">
-        <v>730</v>
-      </c>
-      <c r="J190" t="s">
-        <v>814</v>
+        <v>21</v>
       </c>
       <c r="L190" t="s">
         <v>815</v>
@@ -10855,22 +10855,22 @@
         <v>15</v>
       </c>
       <c r="D191" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E191" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F191" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G191" t="s">
+        <v>730</v>
       </c>
       <c r="H191" t="s">
-        <v>773</v>
+        <v>818</v>
       </c>
       <c r="I191" t="s">
-        <v>730</v>
-      </c>
-      <c r="J191" t="s">
-        <v>818</v>
+        <v>21</v>
       </c>
       <c r="L191" t="s">
         <v>819</v>
@@ -10890,22 +10890,22 @@
         <v>15</v>
       </c>
       <c r="D192" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F192" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G192" t="s">
+        <v>730</v>
       </c>
       <c r="H192" t="s">
-        <v>773</v>
+        <v>822</v>
       </c>
       <c r="I192" t="s">
-        <v>730</v>
-      </c>
-      <c r="J192" t="s">
-        <v>822</v>
+        <v>21</v>
       </c>
       <c r="L192" t="s">
         <v>823</v>
@@ -10925,22 +10925,22 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F193" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G193" t="s">
+        <v>730</v>
       </c>
       <c r="H193" t="s">
-        <v>773</v>
+        <v>826</v>
       </c>
       <c r="I193" t="s">
-        <v>730</v>
-      </c>
-      <c r="J193" t="s">
-        <v>826</v>
+        <v>21</v>
       </c>
       <c r="L193" t="s">
         <v>827</v>
@@ -10960,22 +10960,22 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F194" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G194" t="s">
+        <v>730</v>
       </c>
       <c r="H194" t="s">
-        <v>773</v>
+        <v>830</v>
       </c>
       <c r="I194" t="s">
-        <v>730</v>
-      </c>
-      <c r="J194" t="s">
-        <v>830</v>
+        <v>21</v>
       </c>
       <c r="L194" t="s">
         <v>831</v>
@@ -10995,22 +10995,22 @@
         <v>15</v>
       </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F195" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G195" t="s">
+        <v>730</v>
       </c>
       <c r="H195" t="s">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="I195" t="s">
-        <v>730</v>
-      </c>
-      <c r="J195" t="s">
-        <v>834</v>
+        <v>21</v>
       </c>
       <c r="L195" t="s">
         <v>835</v>
@@ -11030,22 +11030,22 @@
         <v>15</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>773</v>
       </c>
       <c r="F196" t="s">
-        <v>772</v>
+        <v>18</v>
+      </c>
+      <c r="G196" t="s">
+        <v>730</v>
       </c>
       <c r="H196" t="s">
-        <v>773</v>
+        <v>838</v>
       </c>
       <c r="I196" t="s">
-        <v>730</v>
-      </c>
-      <c r="J196" t="s">
-        <v>838</v>
+        <v>21</v>
       </c>
       <c r="L196" t="s">
         <v>839</v>
@@ -11065,22 +11065,22 @@
         <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E197" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F197" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G197" t="s">
+        <v>730</v>
       </c>
       <c r="H197" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="I197" t="s">
-        <v>730</v>
-      </c>
-      <c r="J197" t="s">
-        <v>844</v>
+        <v>21</v>
       </c>
       <c r="L197" t="s">
         <v>845</v>
@@ -11100,22 +11100,22 @@
         <v>15</v>
       </c>
       <c r="D198" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E198" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F198" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G198" t="s">
+        <v>730</v>
       </c>
       <c r="H198" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="I198" t="s">
-        <v>730</v>
-      </c>
-      <c r="J198" t="s">
-        <v>848</v>
+        <v>21</v>
       </c>
       <c r="L198" t="s">
         <v>849</v>
@@ -11135,22 +11135,22 @@
         <v>15</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F199" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G199" t="s">
+        <v>730</v>
       </c>
       <c r="H199" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="I199" t="s">
-        <v>730</v>
-      </c>
-      <c r="J199" t="s">
-        <v>852</v>
+        <v>21</v>
       </c>
       <c r="L199" t="s">
         <v>853</v>
@@ -11170,22 +11170,22 @@
         <v>15</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E200" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F200" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G200" t="s">
+        <v>730</v>
       </c>
       <c r="H200" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="I200" t="s">
-        <v>730</v>
-      </c>
-      <c r="J200" t="s">
-        <v>856</v>
+        <v>21</v>
       </c>
       <c r="L200" t="s">
         <v>857</v>
@@ -11205,22 +11205,22 @@
         <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F201" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G201" t="s">
+        <v>730</v>
       </c>
       <c r="H201" t="s">
-        <v>843</v>
+        <v>860</v>
       </c>
       <c r="I201" t="s">
-        <v>730</v>
-      </c>
-      <c r="J201" t="s">
-        <v>860</v>
+        <v>21</v>
       </c>
       <c r="L201" t="s">
         <v>861</v>
@@ -11240,22 +11240,22 @@
         <v>15</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F202" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G202" t="s">
+        <v>730</v>
       </c>
       <c r="H202" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="I202" t="s">
-        <v>730</v>
-      </c>
-      <c r="J202" t="s">
-        <v>864</v>
+        <v>21</v>
       </c>
       <c r="L202" t="s">
         <v>865</v>
@@ -11275,22 +11275,22 @@
         <v>15</v>
       </c>
       <c r="D203" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F203" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G203" t="s">
+        <v>730</v>
       </c>
       <c r="H203" t="s">
-        <v>843</v>
+        <v>868</v>
       </c>
       <c r="I203" t="s">
-        <v>730</v>
-      </c>
-      <c r="J203" t="s">
-        <v>868</v>
+        <v>21</v>
       </c>
       <c r="L203" t="s">
         <v>869</v>
@@ -11310,22 +11310,22 @@
         <v>15</v>
       </c>
       <c r="D204" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F204" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G204" t="s">
+        <v>730</v>
       </c>
       <c r="H204" t="s">
-        <v>843</v>
+        <v>872</v>
       </c>
       <c r="I204" t="s">
-        <v>730</v>
-      </c>
-      <c r="J204" t="s">
-        <v>872</v>
+        <v>21</v>
       </c>
       <c r="L204" t="s">
         <v>873</v>
@@ -11345,22 +11345,22 @@
         <v>15</v>
       </c>
       <c r="D205" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F205" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G205" t="s">
+        <v>730</v>
       </c>
       <c r="H205" t="s">
-        <v>843</v>
+        <v>876</v>
       </c>
       <c r="I205" t="s">
-        <v>730</v>
-      </c>
-      <c r="J205" t="s">
-        <v>876</v>
+        <v>21</v>
       </c>
       <c r="L205" t="s">
         <v>877</v>
@@ -11380,22 +11380,22 @@
         <v>15</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E206" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F206" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G206" t="s">
+        <v>730</v>
       </c>
       <c r="H206" t="s">
-        <v>843</v>
+        <v>880</v>
       </c>
       <c r="I206" t="s">
-        <v>730</v>
-      </c>
-      <c r="J206" t="s">
-        <v>880</v>
+        <v>21</v>
       </c>
       <c r="L206" t="s">
         <v>881</v>
@@ -11415,22 +11415,22 @@
         <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E207" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F207" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G207" t="s">
+        <v>730</v>
       </c>
       <c r="H207" t="s">
-        <v>843</v>
+        <v>884</v>
       </c>
       <c r="I207" t="s">
-        <v>730</v>
-      </c>
-      <c r="J207" t="s">
-        <v>884</v>
+        <v>21</v>
       </c>
       <c r="L207" t="s">
         <v>885</v>
@@ -11450,22 +11450,22 @@
         <v>15</v>
       </c>
       <c r="D208" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F208" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G208" t="s">
+        <v>730</v>
       </c>
       <c r="H208" t="s">
-        <v>843</v>
+        <v>888</v>
       </c>
       <c r="I208" t="s">
-        <v>730</v>
-      </c>
-      <c r="J208" t="s">
-        <v>888</v>
+        <v>21</v>
       </c>
       <c r="L208" t="s">
         <v>889</v>
@@ -11485,22 +11485,22 @@
         <v>15</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F209" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G209" t="s">
+        <v>730</v>
       </c>
       <c r="H209" t="s">
-        <v>843</v>
+        <v>892</v>
       </c>
       <c r="I209" t="s">
-        <v>730</v>
-      </c>
-      <c r="J209" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="L209" t="s">
         <v>893</v>
@@ -11520,22 +11520,22 @@
         <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E210" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F210" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G210" t="s">
+        <v>730</v>
       </c>
       <c r="H210" t="s">
-        <v>843</v>
+        <v>896</v>
       </c>
       <c r="I210" t="s">
-        <v>730</v>
-      </c>
-      <c r="J210" t="s">
-        <v>896</v>
+        <v>21</v>
       </c>
       <c r="L210" t="s">
         <v>897</v>
@@ -11555,22 +11555,22 @@
         <v>15</v>
       </c>
       <c r="D211" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F211" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G211" t="s">
+        <v>730</v>
       </c>
       <c r="H211" t="s">
-        <v>843</v>
+        <v>900</v>
       </c>
       <c r="I211" t="s">
-        <v>730</v>
-      </c>
-      <c r="J211" t="s">
-        <v>900</v>
+        <v>21</v>
       </c>
       <c r="L211" t="s">
         <v>901</v>
@@ -11590,22 +11590,22 @@
         <v>15</v>
       </c>
       <c r="D212" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="F212" t="s">
-        <v>842</v>
+        <v>18</v>
+      </c>
+      <c r="G212" t="s">
+        <v>730</v>
       </c>
       <c r="H212" t="s">
-        <v>843</v>
+        <v>904</v>
       </c>
       <c r="I212" t="s">
-        <v>730</v>
-      </c>
-      <c r="J212" t="s">
-        <v>904</v>
+        <v>21</v>
       </c>
       <c r="L212" t="s">
         <v>905</v>
@@ -11625,22 +11625,22 @@
         <v>15</v>
       </c>
       <c r="D213" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F213" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G213" t="s">
+        <v>730</v>
       </c>
       <c r="H213" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="I213" t="s">
-        <v>730</v>
-      </c>
-      <c r="J213" t="s">
-        <v>910</v>
+        <v>21</v>
       </c>
       <c r="L213" t="s">
         <v>911</v>
@@ -11660,22 +11660,22 @@
         <v>15</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F214" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G214" t="s">
+        <v>730</v>
       </c>
       <c r="H214" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="I214" t="s">
-        <v>730</v>
-      </c>
-      <c r="J214" t="s">
-        <v>914</v>
+        <v>21</v>
       </c>
       <c r="L214" t="s">
         <v>915</v>
@@ -11695,22 +11695,22 @@
         <v>15</v>
       </c>
       <c r="D215" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E215" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F215" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G215" t="s">
+        <v>730</v>
       </c>
       <c r="H215" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="I215" t="s">
-        <v>730</v>
-      </c>
-      <c r="J215" t="s">
-        <v>918</v>
+        <v>21</v>
       </c>
       <c r="L215" t="s">
         <v>919</v>
@@ -11730,22 +11730,22 @@
         <v>15</v>
       </c>
       <c r="D216" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F216" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G216" t="s">
+        <v>730</v>
       </c>
       <c r="H216" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="I216" t="s">
-        <v>730</v>
-      </c>
-      <c r="J216" t="s">
-        <v>922</v>
+        <v>21</v>
       </c>
       <c r="L216" t="s">
         <v>923</v>
@@ -11765,22 +11765,22 @@
         <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E217" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F217" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G217" t="s">
+        <v>730</v>
       </c>
       <c r="H217" t="s">
-        <v>909</v>
+        <v>926</v>
       </c>
       <c r="I217" t="s">
-        <v>730</v>
-      </c>
-      <c r="J217" t="s">
-        <v>926</v>
+        <v>21</v>
       </c>
       <c r="L217" t="s">
         <v>927</v>
@@ -11800,22 +11800,22 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F218" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G218" t="s">
+        <v>730</v>
       </c>
       <c r="H218" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="I218" t="s">
-        <v>730</v>
-      </c>
-      <c r="J218" t="s">
-        <v>930</v>
+        <v>21</v>
       </c>
       <c r="L218" t="s">
         <v>931</v>
@@ -11835,22 +11835,22 @@
         <v>15</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E219" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F219" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G219" t="s">
+        <v>730</v>
       </c>
       <c r="H219" t="s">
-        <v>909</v>
+        <v>934</v>
       </c>
       <c r="I219" t="s">
-        <v>730</v>
-      </c>
-      <c r="J219" t="s">
-        <v>934</v>
+        <v>21</v>
       </c>
       <c r="L219" t="s">
         <v>935</v>
@@ -11870,22 +11870,22 @@
         <v>15</v>
       </c>
       <c r="D220" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E220" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F220" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G220" t="s">
+        <v>730</v>
       </c>
       <c r="H220" t="s">
-        <v>909</v>
+        <v>938</v>
       </c>
       <c r="I220" t="s">
-        <v>730</v>
-      </c>
-      <c r="J220" t="s">
-        <v>938</v>
+        <v>21</v>
       </c>
       <c r="L220" t="s">
         <v>939</v>
@@ -11905,22 +11905,22 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>909</v>
       </c>
       <c r="F221" t="s">
-        <v>908</v>
+        <v>18</v>
+      </c>
+      <c r="G221" t="s">
+        <v>730</v>
       </c>
       <c r="H221" t="s">
-        <v>909</v>
+        <v>942</v>
       </c>
       <c r="I221" t="s">
-        <v>730</v>
-      </c>
-      <c r="J221" t="s">
-        <v>942</v>
+        <v>21</v>
       </c>
       <c r="L221" t="s">
         <v>943</v>
@@ -11940,22 +11940,22 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E222" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F222" t="s">
-        <v>946</v>
+        <v>18</v>
+      </c>
+      <c r="G222" t="s">
+        <v>948</v>
       </c>
       <c r="H222" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="I222" t="s">
-        <v>948</v>
-      </c>
-      <c r="J222" t="s">
-        <v>949</v>
+        <v>21</v>
       </c>
       <c r="L222" t="s">
         <v>950</v>
@@ -11975,22 +11975,22 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E223" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F223" t="s">
-        <v>946</v>
+        <v>18</v>
+      </c>
+      <c r="G223" t="s">
+        <v>948</v>
       </c>
       <c r="H223" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="I223" t="s">
-        <v>948</v>
-      </c>
-      <c r="J223" t="s">
-        <v>954</v>
+        <v>21</v>
       </c>
       <c r="L223" t="s">
         <v>955</v>
@@ -12010,22 +12010,22 @@
         <v>15</v>
       </c>
       <c r="D224" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E224" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F224" t="s">
-        <v>946</v>
+        <v>18</v>
+      </c>
+      <c r="G224" t="s">
+        <v>948</v>
       </c>
       <c r="H224" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="I224" t="s">
-        <v>948</v>
-      </c>
-      <c r="J224" t="s">
-        <v>958</v>
+        <v>21</v>
       </c>
       <c r="L224" t="s">
         <v>959</v>
@@ -12045,22 +12045,22 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E225" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F225" t="s">
-        <v>946</v>
+        <v>18</v>
+      </c>
+      <c r="G225" t="s">
+        <v>948</v>
       </c>
       <c r="H225" t="s">
-        <v>947</v>
+        <v>962</v>
       </c>
       <c r="I225" t="s">
-        <v>948</v>
-      </c>
-      <c r="J225" t="s">
-        <v>962</v>
+        <v>21</v>
       </c>
       <c r="L225" t="s">
         <v>963</v>
@@ -12080,22 +12080,22 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F226" t="s">
-        <v>946</v>
+        <v>18</v>
+      </c>
+      <c r="G226" t="s">
+        <v>948</v>
       </c>
       <c r="H226" t="s">
-        <v>947</v>
+        <v>966</v>
       </c>
       <c r="I226" t="s">
-        <v>948</v>
-      </c>
-      <c r="J226" t="s">
-        <v>966</v>
+        <v>21</v>
       </c>
       <c r="L226" t="s">
         <v>967</v>
@@ -12115,22 +12115,22 @@
         <v>15</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="F227" t="s">
-        <v>946</v>
+        <v>18</v>
+      </c>
+      <c r="G227" t="s">
+        <v>948</v>
       </c>
       <c r="H227" t="s">
-        <v>947</v>
+        <v>970</v>
       </c>
       <c r="I227" t="s">
-        <v>948</v>
-      </c>
-      <c r="J227" t="s">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="L227" t="s">
         <v>971</v>
@@ -12150,22 +12150,22 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E228" t="s">
-        <v>17</v>
+        <v>975</v>
       </c>
       <c r="F228" t="s">
-        <v>974</v>
+        <v>18</v>
+      </c>
+      <c r="G228" t="s">
+        <v>948</v>
       </c>
       <c r="H228" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="I228" t="s">
-        <v>948</v>
-      </c>
-      <c r="J228" t="s">
-        <v>976</v>
+        <v>21</v>
       </c>
       <c r="L228" t="s">
         <v>977</v>
@@ -12185,22 +12185,22 @@
         <v>15</v>
       </c>
       <c r="D229" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E229" t="s">
-        <v>17</v>
+        <v>975</v>
       </c>
       <c r="F229" t="s">
-        <v>974</v>
+        <v>18</v>
+      </c>
+      <c r="G229" t="s">
+        <v>948</v>
       </c>
       <c r="H229" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="I229" t="s">
-        <v>948</v>
-      </c>
-      <c r="J229" t="s">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="L229" t="s">
         <v>981</v>
@@ -12220,22 +12220,22 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E230" t="s">
-        <v>17</v>
+        <v>975</v>
       </c>
       <c r="F230" t="s">
-        <v>974</v>
+        <v>18</v>
+      </c>
+      <c r="G230" t="s">
+        <v>948</v>
       </c>
       <c r="H230" t="s">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="I230" t="s">
-        <v>948</v>
-      </c>
-      <c r="J230" t="s">
-        <v>984</v>
+        <v>21</v>
       </c>
       <c r="L230" t="s">
         <v>985</v>
@@ -12255,22 +12255,22 @@
         <v>15</v>
       </c>
       <c r="D231" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>975</v>
       </c>
       <c r="F231" t="s">
-        <v>974</v>
+        <v>18</v>
+      </c>
+      <c r="G231" t="s">
+        <v>948</v>
       </c>
       <c r="H231" t="s">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="I231" t="s">
-        <v>948</v>
-      </c>
-      <c r="J231" t="s">
-        <v>988</v>
+        <v>21</v>
       </c>
       <c r="L231" t="s">
         <v>989</v>
@@ -12290,22 +12290,22 @@
         <v>15</v>
       </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E232" t="s">
-        <v>17</v>
+        <v>975</v>
       </c>
       <c r="F232" t="s">
-        <v>974</v>
+        <v>18</v>
+      </c>
+      <c r="G232" t="s">
+        <v>948</v>
       </c>
       <c r="H232" t="s">
-        <v>975</v>
+        <v>992</v>
       </c>
       <c r="I232" t="s">
-        <v>948</v>
-      </c>
-      <c r="J232" t="s">
-        <v>992</v>
+        <v>21</v>
       </c>
       <c r="L232" t="s">
         <v>993</v>
@@ -12325,22 +12325,22 @@
         <v>15</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E233" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F233" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G233" t="s">
+        <v>948</v>
       </c>
       <c r="H233" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I233" t="s">
-        <v>948</v>
-      </c>
-      <c r="J233" t="s">
-        <v>998</v>
+        <v>21</v>
       </c>
       <c r="L233" t="s">
         <v>999</v>
@@ -12360,22 +12360,22 @@
         <v>15</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E234" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F234" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G234" t="s">
+        <v>948</v>
       </c>
       <c r="H234" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="I234" t="s">
-        <v>948</v>
-      </c>
-      <c r="J234" t="s">
-        <v>1002</v>
+        <v>21</v>
       </c>
       <c r="L234" t="s">
         <v>1003</v>
@@ -12395,22 +12395,22 @@
         <v>15</v>
       </c>
       <c r="D235" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E235" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F235" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G235" t="s">
+        <v>948</v>
       </c>
       <c r="H235" t="s">
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="I235" t="s">
-        <v>948</v>
-      </c>
-      <c r="J235" t="s">
-        <v>1006</v>
+        <v>21</v>
       </c>
       <c r="L235" t="s">
         <v>1007</v>
@@ -12430,22 +12430,22 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E236" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F236" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G236" t="s">
+        <v>948</v>
       </c>
       <c r="H236" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="I236" t="s">
-        <v>948</v>
-      </c>
-      <c r="J236" t="s">
-        <v>1010</v>
+        <v>21</v>
       </c>
       <c r="L236" t="s">
         <v>1011</v>
@@ -12465,22 +12465,22 @@
         <v>15</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E237" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F237" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G237" t="s">
+        <v>948</v>
       </c>
       <c r="H237" t="s">
-        <v>997</v>
+        <v>1014</v>
       </c>
       <c r="I237" t="s">
-        <v>948</v>
-      </c>
-      <c r="J237" t="s">
-        <v>1014</v>
+        <v>21</v>
       </c>
       <c r="L237" t="s">
         <v>1015</v>
@@ -12500,22 +12500,22 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E238" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F238" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G238" t="s">
+        <v>948</v>
       </c>
       <c r="H238" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="I238" t="s">
-        <v>948</v>
-      </c>
-      <c r="J238" t="s">
-        <v>1018</v>
+        <v>21</v>
       </c>
       <c r="L238" t="s">
         <v>1019</v>
@@ -12535,22 +12535,22 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E239" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F239" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G239" t="s">
+        <v>948</v>
       </c>
       <c r="H239" t="s">
-        <v>997</v>
+        <v>1022</v>
       </c>
       <c r="I239" t="s">
-        <v>948</v>
-      </c>
-      <c r="J239" t="s">
-        <v>1022</v>
+        <v>21</v>
       </c>
       <c r="L239" t="s">
         <v>1023</v>
@@ -12570,22 +12570,22 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E240" t="s">
-        <v>17</v>
+        <v>997</v>
       </c>
       <c r="F240" t="s">
-        <v>996</v>
+        <v>18</v>
+      </c>
+      <c r="G240" t="s">
+        <v>948</v>
       </c>
       <c r="H240" t="s">
-        <v>997</v>
+        <v>1026</v>
       </c>
       <c r="I240" t="s">
-        <v>948</v>
-      </c>
-      <c r="J240" t="s">
-        <v>1026</v>
+        <v>21</v>
       </c>
       <c r="L240" t="s">
         <v>1027</v>
@@ -12605,22 +12605,22 @@
         <v>15</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F241" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G241" t="s">
+        <v>948</v>
       </c>
       <c r="H241" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="I241" t="s">
-        <v>948</v>
-      </c>
-      <c r="J241" t="s">
-        <v>1032</v>
+        <v>21</v>
       </c>
       <c r="L241" t="s">
         <v>1033</v>
@@ -12640,22 +12640,22 @@
         <v>15</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E242" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F242" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G242" t="s">
+        <v>948</v>
       </c>
       <c r="H242" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="I242" t="s">
-        <v>948</v>
-      </c>
-      <c r="J242" t="s">
-        <v>1036</v>
+        <v>21</v>
       </c>
       <c r="L242" t="s">
         <v>1037</v>
@@ -12675,22 +12675,22 @@
         <v>15</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E243" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F243" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G243" t="s">
+        <v>948</v>
       </c>
       <c r="H243" t="s">
-        <v>1031</v>
+        <v>1040</v>
       </c>
       <c r="I243" t="s">
-        <v>948</v>
-      </c>
-      <c r="J243" t="s">
-        <v>1040</v>
+        <v>21</v>
       </c>
       <c r="L243" t="s">
         <v>1041</v>
@@ -12710,22 +12710,22 @@
         <v>15</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E244" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F244" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G244" t="s">
+        <v>948</v>
       </c>
       <c r="H244" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="I244" t="s">
-        <v>948</v>
-      </c>
-      <c r="J244" t="s">
-        <v>1044</v>
+        <v>21</v>
       </c>
       <c r="L244" t="s">
         <v>1045</v>
@@ -12745,22 +12745,22 @@
         <v>15</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E245" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F245" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G245" t="s">
+        <v>948</v>
       </c>
       <c r="H245" t="s">
-        <v>1031</v>
+        <v>1048</v>
       </c>
       <c r="I245" t="s">
-        <v>948</v>
-      </c>
-      <c r="J245" t="s">
-        <v>1048</v>
+        <v>21</v>
       </c>
       <c r="L245" t="s">
         <v>1049</v>
@@ -12780,22 +12780,22 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E246" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F246" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G246" t="s">
+        <v>948</v>
       </c>
       <c r="H246" t="s">
-        <v>1031</v>
+        <v>1052</v>
       </c>
       <c r="I246" t="s">
-        <v>948</v>
-      </c>
-      <c r="J246" t="s">
-        <v>1052</v>
+        <v>21</v>
       </c>
       <c r="L246" t="s">
         <v>1053</v>
@@ -12815,22 +12815,22 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E247" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F247" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G247" t="s">
+        <v>948</v>
       </c>
       <c r="H247" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="I247" t="s">
-        <v>948</v>
-      </c>
-      <c r="J247" t="s">
-        <v>1056</v>
+        <v>21</v>
       </c>
       <c r="L247" t="s">
         <v>1057</v>
@@ -12850,22 +12850,22 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F248" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G248" t="s">
+        <v>948</v>
       </c>
       <c r="H248" t="s">
-        <v>1031</v>
+        <v>1060</v>
       </c>
       <c r="I248" t="s">
-        <v>948</v>
-      </c>
-      <c r="J248" t="s">
-        <v>1060</v>
+        <v>21</v>
       </c>
       <c r="L248" t="s">
         <v>1061</v>
@@ -12885,22 +12885,22 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E249" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F249" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G249" t="s">
+        <v>948</v>
       </c>
       <c r="H249" t="s">
-        <v>1031</v>
+        <v>1064</v>
       </c>
       <c r="I249" t="s">
-        <v>948</v>
-      </c>
-      <c r="J249" t="s">
-        <v>1064</v>
+        <v>21</v>
       </c>
       <c r="L249" t="s">
         <v>1065</v>
@@ -12920,22 +12920,22 @@
         <v>15</v>
       </c>
       <c r="D250" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E250" t="s">
-        <v>17</v>
+        <v>1031</v>
       </c>
       <c r="F250" t="s">
-        <v>1030</v>
+        <v>18</v>
+      </c>
+      <c r="G250" t="s">
+        <v>948</v>
       </c>
       <c r="H250" t="s">
-        <v>1031</v>
+        <v>1068</v>
       </c>
       <c r="I250" t="s">
-        <v>948</v>
-      </c>
-      <c r="J250" t="s">
-        <v>1068</v>
+        <v>21</v>
       </c>
       <c r="L250" t="s">
         <v>1069</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -28,33 +28,33 @@
     <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:global-name</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
     <t>codeforiati:sub-region-name</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:global-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -67,27 +67,27 @@
     <t>DZA</t>
   </si>
   <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
     <t>Northern Africa</t>
   </si>
   <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -169,21 +169,21 @@
     <t>IOT</t>
   </si>
   <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
     <t>Sub-Saharan Africa</t>
   </si>
   <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -445,15 +445,15 @@
     <t>AGO</t>
   </si>
   <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>AO</t>
   </si>
   <si>
     <t>Middle Africa</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -559,15 +559,15 @@
     <t>BWA</t>
   </si>
   <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>BW</t>
   </si>
   <si>
     <t>Southern Africa</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -625,15 +625,15 @@
     <t>BEN</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>BJ</t>
   </si>
   <si>
     <t>Western Africa</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -835,27 +835,27 @@
     <t>AIA</t>
   </si>
   <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>Americas</t>
+  </si>
+  <si>
     <t>Latin America and the Caribbean</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -1189,15 +1189,15 @@
     <t>BLZ</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>BZ</t>
   </si>
   <si>
     <t>Central America</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -1291,15 +1291,15 @@
     <t>ARG</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>AR</t>
   </si>
   <si>
     <t>South America</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1489,15 +1489,15 @@
     <t>BMU</t>
   </si>
   <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
     <t>Northern America</t>
   </si>
   <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>021</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1567,21 +1567,21 @@
     <t>KAZ</t>
   </si>
   <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
     <t>Central Asia</t>
   </si>
   <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1639,15 +1639,15 @@
     <t>CHN</t>
   </si>
   <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
     <t>Eastern Asia</t>
   </si>
   <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1729,15 +1729,15 @@
     <t>BRN</t>
   </si>
   <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
     <t>South-eastern Asia</t>
   </si>
   <si>
-    <t>BN</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1867,15 +1867,15 @@
     <t>AFG</t>
   </si>
   <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
     <t>Southern Asia</t>
   </si>
   <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1981,15 +1981,15 @@
     <t>ARM</t>
   </si>
   <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
     <t>Western Asia</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -2203,21 +2203,21 @@
     <t>BLR</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
     <t>Eastern Europe</t>
   </si>
   <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2335,15 +2335,15 @@
     <t>ALA</t>
   </si>
   <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
     <t>Northern Europe</t>
   </si>
   <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
@@ -2353,15 +2353,15 @@
     <t>GGY</t>
   </si>
   <si>
+    <t>830</t>
+  </si>
+  <si>
     <t>GG</t>
   </si>
   <si>
     <t>Channel Islands</t>
   </si>
   <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>832</t>
   </si>
   <si>
@@ -2545,15 +2545,15 @@
     <t>ALB</t>
   </si>
   <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
     <t>Southern Europe</t>
   </si>
   <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2743,15 +2743,15 @@
     <t>AUT</t>
   </si>
   <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
     <t>Western Europe</t>
   </si>
   <si>
-    <t>AT</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2857,21 +2857,21 @@
     <t>AUS</t>
   </si>
   <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
     <t>Australia and New Zealand</t>
   </si>
   <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>009</t>
-  </si>
-  <si>
     <t>162</t>
   </si>
   <si>
@@ -2941,15 +2941,15 @@
     <t>FJI</t>
   </si>
   <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>FJ</t>
+  </si>
+  <si>
     <t>Melanesia</t>
   </si>
   <si>
-    <t>FJ</t>
-  </si>
-  <si>
-    <t>054</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -3007,15 +3007,15 @@
     <t>GUM</t>
   </si>
   <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>GU</t>
+  </si>
+  <si>
     <t>Micronesia</t>
   </si>
   <si>
-    <t>GU</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -3109,13 +3109,13 @@
     <t>ASM</t>
   </si>
   <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
     <t>Polynesia</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>061</t>
   </si>
   <si>
     <t>184</t>
@@ -3615,7 +3615,7 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
       <c r="H2" t="s">
@@ -3624,7 +3624,7 @@
       <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
       <c r="L2" t="s">
@@ -3650,7 +3650,7 @@
       <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
       <c r="H3" t="s">
@@ -3659,7 +3659,7 @@
       <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
@@ -3685,7 +3685,7 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>31</v>
       </c>
       <c r="H4" t="s">
@@ -3694,7 +3694,7 @@
       <c r="I4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>21</v>
       </c>
       <c r="L4" t="s">
@@ -3720,7 +3720,7 @@
       <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>35</v>
       </c>
       <c r="H5" t="s">
@@ -3729,7 +3729,7 @@
       <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>21</v>
       </c>
       <c r="L5" t="s">
@@ -3755,7 +3755,7 @@
       <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
       <c r="H6" t="s">
@@ -3764,7 +3764,7 @@
       <c r="I6" t="s">
         <v>20</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>21</v>
       </c>
       <c r="L6" t="s">
@@ -3790,7 +3790,7 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>43</v>
       </c>
       <c r="H7" t="s">
@@ -3799,7 +3799,7 @@
       <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7" t="s">
@@ -3825,7 +3825,7 @@
       <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>47</v>
       </c>
       <c r="H8" t="s">
@@ -3834,7 +3834,7 @@
       <c r="I8" t="s">
         <v>20</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>21</v>
       </c>
       <c r="L8" t="s">
@@ -3867,22 +3867,22 @@
         <v>53</v>
       </c>
       <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
         <v>54</v>
       </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>21</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
         <v>55</v>
-      </c>
-      <c r="L9" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3902,28 +3902,28 @@
         <v>51</v>
       </c>
       <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="G10" t="s">
-        <v>53</v>
-      </c>
       <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
         <v>54</v>
       </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>21</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
         <v>55</v>
-      </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3943,28 +3943,28 @@
         <v>51</v>
       </c>
       <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
         <v>63</v>
       </c>
-      <c r="G11" t="s">
-        <v>53</v>
-      </c>
       <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
         <v>54</v>
       </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>21</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
         <v>55</v>
-      </c>
-      <c r="L11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3984,28 +3984,28 @@
         <v>51</v>
       </c>
       <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
         <v>67</v>
       </c>
-      <c r="G12" t="s">
-        <v>53</v>
-      </c>
       <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
         <v>54</v>
       </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>21</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
         <v>55</v>
-      </c>
-      <c r="L12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4025,28 +4025,28 @@
         <v>51</v>
       </c>
       <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" t="s">
         <v>71</v>
       </c>
-      <c r="G13" t="s">
-        <v>53</v>
-      </c>
       <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
         <v>54</v>
       </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>21</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
         <v>55</v>
-      </c>
-      <c r="L13" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -4066,28 +4066,28 @@
         <v>51</v>
       </c>
       <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
         <v>75</v>
       </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
       <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
         <v>54</v>
       </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>21</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
         <v>55</v>
-      </c>
-      <c r="L14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4107,28 +4107,28 @@
         <v>51</v>
       </c>
       <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
         <v>79</v>
       </c>
-      <c r="G15" t="s">
-        <v>53</v>
-      </c>
       <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
         <v>54</v>
       </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>21</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
         <v>55</v>
-      </c>
-      <c r="L15" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4148,28 +4148,28 @@
         <v>51</v>
       </c>
       <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
         <v>83</v>
       </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
       <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" t="s">
         <v>54</v>
       </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>21</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
         <v>55</v>
-      </c>
-      <c r="L16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4189,28 +4189,28 @@
         <v>51</v>
       </c>
       <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
         <v>87</v>
       </c>
-      <c r="G17" t="s">
-        <v>53</v>
-      </c>
       <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" t="s">
         <v>54</v>
       </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>21</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" t="s">
         <v>55</v>
-      </c>
-      <c r="L17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4230,28 +4230,28 @@
         <v>51</v>
       </c>
       <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s">
         <v>91</v>
       </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
       <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s">
         <v>54</v>
       </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>21</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
         <v>55</v>
-      </c>
-      <c r="L18" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -4271,28 +4271,28 @@
         <v>51</v>
       </c>
       <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" t="s">
         <v>95</v>
       </c>
-      <c r="G19" t="s">
-        <v>53</v>
-      </c>
       <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
         <v>54</v>
       </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>21</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" t="s">
         <v>55</v>
-      </c>
-      <c r="L19" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4312,28 +4312,28 @@
         <v>51</v>
       </c>
       <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" t="s">
         <v>99</v>
       </c>
-      <c r="G20" t="s">
-        <v>53</v>
-      </c>
       <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s">
         <v>54</v>
       </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>21</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" t="s">
         <v>55</v>
-      </c>
-      <c r="L20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4353,28 +4353,28 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" t="s">
         <v>103</v>
       </c>
-      <c r="G21" t="s">
-        <v>53</v>
-      </c>
       <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
         <v>54</v>
       </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>21</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" t="s">
         <v>55</v>
-      </c>
-      <c r="L21" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4394,28 +4394,28 @@
         <v>51</v>
       </c>
       <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" t="s">
         <v>107</v>
       </c>
-      <c r="G22" t="s">
-        <v>53</v>
-      </c>
       <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" t="s">
         <v>54</v>
       </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>21</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" t="s">
         <v>55</v>
-      </c>
-      <c r="L22" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4435,28 +4435,28 @@
         <v>51</v>
       </c>
       <c r="F23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" t="s">
         <v>111</v>
       </c>
-      <c r="G23" t="s">
-        <v>53</v>
-      </c>
       <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
         <v>54</v>
       </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>21</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" t="s">
         <v>55</v>
-      </c>
-      <c r="L23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M23" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -4476,28 +4476,28 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" t="s">
         <v>115</v>
       </c>
-      <c r="G24" t="s">
-        <v>53</v>
-      </c>
       <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" t="s">
         <v>54</v>
       </c>
-      <c r="I24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>21</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
         <v>55</v>
-      </c>
-      <c r="L24" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -4517,28 +4517,28 @@
         <v>51</v>
       </c>
       <c r="F25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" t="s">
         <v>119</v>
       </c>
-      <c r="G25" t="s">
-        <v>53</v>
-      </c>
       <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" t="s">
         <v>54</v>
       </c>
-      <c r="I25" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>21</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
         <v>55</v>
-      </c>
-      <c r="L25" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -4558,28 +4558,28 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
         <v>123</v>
       </c>
-      <c r="G26" t="s">
-        <v>53</v>
-      </c>
       <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" t="s">
         <v>54</v>
       </c>
-      <c r="I26" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>21</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
         <v>55</v>
-      </c>
-      <c r="L26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -4599,28 +4599,28 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" t="s">
         <v>127</v>
       </c>
-      <c r="G27" t="s">
-        <v>53</v>
-      </c>
       <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" t="s">
         <v>54</v>
       </c>
-      <c r="I27" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>21</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
         <v>55</v>
-      </c>
-      <c r="L27" t="s">
-        <v>22</v>
-      </c>
-      <c r="M27" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4640,28 +4640,28 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" t="s">
         <v>131</v>
       </c>
-      <c r="G28" t="s">
-        <v>53</v>
-      </c>
       <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" t="s">
         <v>54</v>
       </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>21</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
         <v>55</v>
-      </c>
-      <c r="L28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M28" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4681,28 +4681,28 @@
         <v>51</v>
       </c>
       <c r="F29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" t="s">
         <v>135</v>
       </c>
-      <c r="G29" t="s">
-        <v>53</v>
-      </c>
       <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" t="s">
         <v>54</v>
       </c>
-      <c r="I29" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>21</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" t="s">
         <v>55</v>
-      </c>
-      <c r="L29" t="s">
-        <v>22</v>
-      </c>
-      <c r="M29" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -4722,28 +4722,28 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" t="s">
         <v>139</v>
       </c>
-      <c r="G30" t="s">
-        <v>53</v>
-      </c>
       <c r="H30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" t="s">
         <v>54</v>
       </c>
-      <c r="I30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>21</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
         <v>55</v>
-      </c>
-      <c r="L30" t="s">
-        <v>22</v>
-      </c>
-      <c r="M30" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4769,22 +4769,22 @@
         <v>144</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
         <v>20</v>
       </c>
       <c r="J31" t="s">
+        <v>145</v>
+      </c>
+      <c r="K31" t="s">
         <v>21</v>
       </c>
-      <c r="K31" t="s">
-        <v>145</v>
-      </c>
       <c r="L31" t="s">
         <v>22</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4804,28 +4804,28 @@
         <v>51</v>
       </c>
       <c r="F32" t="s">
+        <v>143</v>
+      </c>
+      <c r="G32" t="s">
         <v>149</v>
       </c>
-      <c r="G32" t="s">
-        <v>144</v>
-      </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
         <v>20</v>
       </c>
       <c r="J32" t="s">
+        <v>145</v>
+      </c>
+      <c r="K32" t="s">
         <v>21</v>
       </c>
-      <c r="K32" t="s">
-        <v>145</v>
-      </c>
       <c r="L32" t="s">
         <v>22</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4845,28 +4845,28 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" t="s">
         <v>153</v>
       </c>
-      <c r="G33" t="s">
-        <v>144</v>
-      </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
         <v>20</v>
       </c>
       <c r="J33" t="s">
+        <v>145</v>
+      </c>
+      <c r="K33" t="s">
         <v>21</v>
       </c>
-      <c r="K33" t="s">
-        <v>145</v>
-      </c>
       <c r="L33" t="s">
         <v>22</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4886,28 +4886,28 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" t="s">
         <v>157</v>
       </c>
-      <c r="G34" t="s">
-        <v>144</v>
-      </c>
       <c r="H34" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
         <v>20</v>
       </c>
       <c r="J34" t="s">
+        <v>145</v>
+      </c>
+      <c r="K34" t="s">
         <v>21</v>
       </c>
-      <c r="K34" t="s">
-        <v>145</v>
-      </c>
       <c r="L34" t="s">
         <v>22</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -4927,28 +4927,28 @@
         <v>51</v>
       </c>
       <c r="F35" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" t="s">
         <v>161</v>
       </c>
-      <c r="G35" t="s">
-        <v>144</v>
-      </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
         <v>20</v>
       </c>
       <c r="J35" t="s">
+        <v>145</v>
+      </c>
+      <c r="K35" t="s">
         <v>21</v>
       </c>
-      <c r="K35" t="s">
-        <v>145</v>
-      </c>
       <c r="L35" t="s">
         <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -4968,28 +4968,28 @@
         <v>51</v>
       </c>
       <c r="F36" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" t="s">
         <v>165</v>
       </c>
-      <c r="G36" t="s">
-        <v>144</v>
-      </c>
       <c r="H36" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s">
         <v>20</v>
       </c>
       <c r="J36" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" t="s">
         <v>21</v>
       </c>
-      <c r="K36" t="s">
-        <v>145</v>
-      </c>
       <c r="L36" t="s">
         <v>22</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5009,28 +5009,28 @@
         <v>51</v>
       </c>
       <c r="F37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" t="s">
         <v>169</v>
       </c>
-      <c r="G37" t="s">
-        <v>144</v>
-      </c>
       <c r="H37" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
       </c>
       <c r="J37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K37" t="s">
         <v>21</v>
       </c>
-      <c r="K37" t="s">
-        <v>145</v>
-      </c>
       <c r="L37" t="s">
         <v>22</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5050,28 +5050,28 @@
         <v>51</v>
       </c>
       <c r="F38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" t="s">
         <v>173</v>
       </c>
-      <c r="G38" t="s">
-        <v>144</v>
-      </c>
       <c r="H38" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s">
         <v>20</v>
       </c>
       <c r="J38" t="s">
+        <v>145</v>
+      </c>
+      <c r="K38" t="s">
         <v>21</v>
       </c>
-      <c r="K38" t="s">
-        <v>145</v>
-      </c>
       <c r="L38" t="s">
         <v>22</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -5091,28 +5091,28 @@
         <v>51</v>
       </c>
       <c r="F39" t="s">
+        <v>143</v>
+      </c>
+      <c r="G39" t="s">
         <v>177</v>
       </c>
-      <c r="G39" t="s">
-        <v>144</v>
-      </c>
       <c r="H39" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I39" t="s">
         <v>20</v>
       </c>
       <c r="J39" t="s">
+        <v>145</v>
+      </c>
+      <c r="K39" t="s">
         <v>21</v>
       </c>
-      <c r="K39" t="s">
-        <v>145</v>
-      </c>
       <c r="L39" t="s">
         <v>22</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -5138,22 +5138,22 @@
         <v>182</v>
       </c>
       <c r="H40" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
         <v>20</v>
       </c>
       <c r="J40" t="s">
+        <v>183</v>
+      </c>
+      <c r="K40" t="s">
         <v>21</v>
       </c>
-      <c r="K40" t="s">
-        <v>183</v>
-      </c>
       <c r="L40" t="s">
         <v>22</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -5173,28 +5173,28 @@
         <v>51</v>
       </c>
       <c r="F41" t="s">
+        <v>181</v>
+      </c>
+      <c r="G41" t="s">
         <v>187</v>
       </c>
-      <c r="G41" t="s">
-        <v>182</v>
-      </c>
       <c r="H41" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s">
         <v>20</v>
       </c>
       <c r="J41" t="s">
+        <v>183</v>
+      </c>
+      <c r="K41" t="s">
         <v>21</v>
       </c>
-      <c r="K41" t="s">
-        <v>183</v>
-      </c>
       <c r="L41" t="s">
         <v>22</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5214,28 +5214,28 @@
         <v>51</v>
       </c>
       <c r="F42" t="s">
+        <v>181</v>
+      </c>
+      <c r="G42" t="s">
         <v>191</v>
       </c>
-      <c r="G42" t="s">
-        <v>182</v>
-      </c>
       <c r="H42" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I42" t="s">
         <v>20</v>
       </c>
       <c r="J42" t="s">
+        <v>183</v>
+      </c>
+      <c r="K42" t="s">
         <v>21</v>
       </c>
-      <c r="K42" t="s">
-        <v>183</v>
-      </c>
       <c r="L42" t="s">
         <v>22</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5255,28 +5255,28 @@
         <v>51</v>
       </c>
       <c r="F43" t="s">
+        <v>181</v>
+      </c>
+      <c r="G43" t="s">
         <v>195</v>
       </c>
-      <c r="G43" t="s">
-        <v>182</v>
-      </c>
       <c r="H43" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
         <v>20</v>
       </c>
       <c r="J43" t="s">
+        <v>183</v>
+      </c>
+      <c r="K43" t="s">
         <v>21</v>
       </c>
-      <c r="K43" t="s">
-        <v>183</v>
-      </c>
       <c r="L43" t="s">
         <v>22</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5296,28 +5296,28 @@
         <v>51</v>
       </c>
       <c r="F44" t="s">
+        <v>181</v>
+      </c>
+      <c r="G44" t="s">
         <v>199</v>
       </c>
-      <c r="G44" t="s">
-        <v>182</v>
-      </c>
       <c r="H44" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s">
         <v>20</v>
       </c>
       <c r="J44" t="s">
+        <v>183</v>
+      </c>
+      <c r="K44" t="s">
         <v>21</v>
       </c>
-      <c r="K44" t="s">
-        <v>183</v>
-      </c>
       <c r="L44" t="s">
         <v>22</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -5343,22 +5343,22 @@
         <v>204</v>
       </c>
       <c r="H45" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I45" t="s">
         <v>20</v>
       </c>
       <c r="J45" t="s">
+        <v>205</v>
+      </c>
+      <c r="K45" t="s">
         <v>21</v>
       </c>
-      <c r="K45" t="s">
-        <v>205</v>
-      </c>
       <c r="L45" t="s">
         <v>22</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -5378,28 +5378,28 @@
         <v>51</v>
       </c>
       <c r="F46" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" t="s">
         <v>209</v>
       </c>
-      <c r="G46" t="s">
-        <v>204</v>
-      </c>
       <c r="H46" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
       </c>
       <c r="J46" t="s">
+        <v>205</v>
+      </c>
+      <c r="K46" t="s">
         <v>21</v>
       </c>
-      <c r="K46" t="s">
-        <v>205</v>
-      </c>
       <c r="L46" t="s">
         <v>22</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -5419,28 +5419,28 @@
         <v>51</v>
       </c>
       <c r="F47" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" t="s">
         <v>213</v>
       </c>
-      <c r="G47" t="s">
-        <v>204</v>
-      </c>
       <c r="H47" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
       </c>
       <c r="J47" t="s">
+        <v>205</v>
+      </c>
+      <c r="K47" t="s">
         <v>21</v>
       </c>
-      <c r="K47" t="s">
-        <v>205</v>
-      </c>
       <c r="L47" t="s">
         <v>22</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -5460,28 +5460,28 @@
         <v>51</v>
       </c>
       <c r="F48" t="s">
+        <v>203</v>
+      </c>
+      <c r="G48" t="s">
         <v>217</v>
       </c>
-      <c r="G48" t="s">
-        <v>204</v>
-      </c>
       <c r="H48" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
       </c>
       <c r="J48" t="s">
+        <v>205</v>
+      </c>
+      <c r="K48" t="s">
         <v>21</v>
       </c>
-      <c r="K48" t="s">
-        <v>205</v>
-      </c>
       <c r="L48" t="s">
         <v>22</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -5501,28 +5501,28 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
+        <v>203</v>
+      </c>
+      <c r="G49" t="s">
         <v>221</v>
       </c>
-      <c r="G49" t="s">
-        <v>204</v>
-      </c>
       <c r="H49" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
         <v>20</v>
       </c>
       <c r="J49" t="s">
+        <v>205</v>
+      </c>
+      <c r="K49" t="s">
         <v>21</v>
       </c>
-      <c r="K49" t="s">
-        <v>205</v>
-      </c>
       <c r="L49" t="s">
         <v>22</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -5542,28 +5542,28 @@
         <v>51</v>
       </c>
       <c r="F50" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" t="s">
         <v>225</v>
       </c>
-      <c r="G50" t="s">
-        <v>204</v>
-      </c>
       <c r="H50" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
         <v>20</v>
       </c>
       <c r="J50" t="s">
+        <v>205</v>
+      </c>
+      <c r="K50" t="s">
         <v>21</v>
       </c>
-      <c r="K50" t="s">
-        <v>205</v>
-      </c>
       <c r="L50" t="s">
         <v>22</v>
       </c>
       <c r="M50" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -5583,28 +5583,28 @@
         <v>51</v>
       </c>
       <c r="F51" t="s">
+        <v>203</v>
+      </c>
+      <c r="G51" t="s">
         <v>229</v>
       </c>
-      <c r="G51" t="s">
-        <v>204</v>
-      </c>
       <c r="H51" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
         <v>20</v>
       </c>
       <c r="J51" t="s">
+        <v>205</v>
+      </c>
+      <c r="K51" t="s">
         <v>21</v>
       </c>
-      <c r="K51" t="s">
-        <v>205</v>
-      </c>
       <c r="L51" t="s">
         <v>22</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -5624,28 +5624,28 @@
         <v>51</v>
       </c>
       <c r="F52" t="s">
+        <v>203</v>
+      </c>
+      <c r="G52" t="s">
         <v>233</v>
       </c>
-      <c r="G52" t="s">
-        <v>204</v>
-      </c>
       <c r="H52" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
       </c>
       <c r="J52" t="s">
+        <v>205</v>
+      </c>
+      <c r="K52" t="s">
         <v>21</v>
       </c>
-      <c r="K52" t="s">
-        <v>205</v>
-      </c>
       <c r="L52" t="s">
         <v>22</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -5665,28 +5665,28 @@
         <v>51</v>
       </c>
       <c r="F53" t="s">
+        <v>203</v>
+      </c>
+      <c r="G53" t="s">
         <v>237</v>
       </c>
-      <c r="G53" t="s">
-        <v>204</v>
-      </c>
       <c r="H53" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
       </c>
       <c r="J53" t="s">
+        <v>205</v>
+      </c>
+      <c r="K53" t="s">
         <v>21</v>
       </c>
-      <c r="K53" t="s">
-        <v>205</v>
-      </c>
       <c r="L53" t="s">
         <v>22</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5706,28 +5706,28 @@
         <v>51</v>
       </c>
       <c r="F54" t="s">
+        <v>203</v>
+      </c>
+      <c r="G54" t="s">
         <v>241</v>
       </c>
-      <c r="G54" t="s">
-        <v>204</v>
-      </c>
       <c r="H54" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
         <v>20</v>
       </c>
       <c r="J54" t="s">
+        <v>205</v>
+      </c>
+      <c r="K54" t="s">
         <v>21</v>
       </c>
-      <c r="K54" t="s">
-        <v>205</v>
-      </c>
       <c r="L54" t="s">
         <v>22</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -5747,28 +5747,28 @@
         <v>51</v>
       </c>
       <c r="F55" t="s">
+        <v>203</v>
+      </c>
+      <c r="G55" t="s">
         <v>245</v>
       </c>
-      <c r="G55" t="s">
-        <v>204</v>
-      </c>
       <c r="H55" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
         <v>20</v>
       </c>
       <c r="J55" t="s">
+        <v>205</v>
+      </c>
+      <c r="K55" t="s">
         <v>21</v>
       </c>
-      <c r="K55" t="s">
-        <v>205</v>
-      </c>
       <c r="L55" t="s">
         <v>22</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -5788,28 +5788,28 @@
         <v>51</v>
       </c>
       <c r="F56" t="s">
+        <v>203</v>
+      </c>
+      <c r="G56" t="s">
         <v>249</v>
       </c>
-      <c r="G56" t="s">
-        <v>204</v>
-      </c>
       <c r="H56" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
         <v>20</v>
       </c>
       <c r="J56" t="s">
+        <v>205</v>
+      </c>
+      <c r="K56" t="s">
         <v>21</v>
       </c>
-      <c r="K56" t="s">
-        <v>205</v>
-      </c>
       <c r="L56" t="s">
         <v>22</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -5829,28 +5829,28 @@
         <v>51</v>
       </c>
       <c r="F57" t="s">
+        <v>203</v>
+      </c>
+      <c r="G57" t="s">
         <v>253</v>
       </c>
-      <c r="G57" t="s">
-        <v>204</v>
-      </c>
       <c r="H57" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
       </c>
       <c r="J57" t="s">
+        <v>205</v>
+      </c>
+      <c r="K57" t="s">
         <v>21</v>
       </c>
-      <c r="K57" t="s">
-        <v>205</v>
-      </c>
       <c r="L57" t="s">
         <v>22</v>
       </c>
       <c r="M57" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -5870,28 +5870,28 @@
         <v>51</v>
       </c>
       <c r="F58" t="s">
+        <v>203</v>
+      </c>
+      <c r="G58" t="s">
         <v>257</v>
       </c>
-      <c r="G58" t="s">
-        <v>204</v>
-      </c>
       <c r="H58" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s">
         <v>20</v>
       </c>
       <c r="J58" t="s">
+        <v>205</v>
+      </c>
+      <c r="K58" t="s">
         <v>21</v>
       </c>
-      <c r="K58" t="s">
-        <v>205</v>
-      </c>
       <c r="L58" t="s">
         <v>22</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -5911,28 +5911,28 @@
         <v>51</v>
       </c>
       <c r="F59" t="s">
+        <v>203</v>
+      </c>
+      <c r="G59" t="s">
         <v>261</v>
       </c>
-      <c r="G59" t="s">
-        <v>204</v>
-      </c>
       <c r="H59" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
       </c>
       <c r="J59" t="s">
+        <v>205</v>
+      </c>
+      <c r="K59" t="s">
         <v>21</v>
       </c>
-      <c r="K59" t="s">
-        <v>205</v>
-      </c>
       <c r="L59" t="s">
         <v>22</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -5952,28 +5952,28 @@
         <v>51</v>
       </c>
       <c r="F60" t="s">
+        <v>203</v>
+      </c>
+      <c r="G60" t="s">
         <v>265</v>
       </c>
-      <c r="G60" t="s">
-        <v>204</v>
-      </c>
       <c r="H60" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s">
         <v>20</v>
       </c>
       <c r="J60" t="s">
+        <v>205</v>
+      </c>
+      <c r="K60" t="s">
         <v>21</v>
       </c>
-      <c r="K60" t="s">
-        <v>205</v>
-      </c>
       <c r="L60" t="s">
         <v>22</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -5993,28 +5993,28 @@
         <v>51</v>
       </c>
       <c r="F61" t="s">
+        <v>203</v>
+      </c>
+      <c r="G61" t="s">
         <v>269</v>
       </c>
-      <c r="G61" t="s">
-        <v>204</v>
-      </c>
       <c r="H61" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
       </c>
       <c r="J61" t="s">
+        <v>205</v>
+      </c>
+      <c r="K61" t="s">
         <v>21</v>
       </c>
-      <c r="K61" t="s">
-        <v>205</v>
-      </c>
       <c r="L61" t="s">
         <v>22</v>
       </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6043,19 +6043,19 @@
         <v>276</v>
       </c>
       <c r="I62" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s">
         <v>277</v>
-      </c>
-      <c r="J62" t="s">
-        <v>21</v>
       </c>
       <c r="K62" t="s">
         <v>278</v>
       </c>
       <c r="L62" t="s">
+        <v>22</v>
+      </c>
+      <c r="M62" t="s">
         <v>279</v>
-      </c>
-      <c r="M62" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6075,28 +6075,28 @@
         <v>273</v>
       </c>
       <c r="F63" t="s">
+        <v>274</v>
+      </c>
+      <c r="G63" t="s">
         <v>283</v>
-      </c>
-      <c r="G63" t="s">
-        <v>275</v>
       </c>
       <c r="H63" t="s">
         <v>276</v>
       </c>
       <c r="I63" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s">
         <v>277</v>
-      </c>
-      <c r="J63" t="s">
-        <v>21</v>
       </c>
       <c r="K63" t="s">
         <v>278</v>
       </c>
       <c r="L63" t="s">
+        <v>22</v>
+      </c>
+      <c r="M63" t="s">
         <v>279</v>
-      </c>
-      <c r="M63" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6116,28 +6116,28 @@
         <v>273</v>
       </c>
       <c r="F64" t="s">
+        <v>274</v>
+      </c>
+      <c r="G64" t="s">
         <v>287</v>
-      </c>
-      <c r="G64" t="s">
-        <v>275</v>
       </c>
       <c r="H64" t="s">
         <v>276</v>
       </c>
       <c r="I64" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s">
         <v>277</v>
-      </c>
-      <c r="J64" t="s">
-        <v>21</v>
       </c>
       <c r="K64" t="s">
         <v>278</v>
       </c>
       <c r="L64" t="s">
+        <v>22</v>
+      </c>
+      <c r="M64" t="s">
         <v>279</v>
-      </c>
-      <c r="M64" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6157,28 +6157,28 @@
         <v>273</v>
       </c>
       <c r="F65" t="s">
+        <v>274</v>
+      </c>
+      <c r="G65" t="s">
         <v>291</v>
-      </c>
-      <c r="G65" t="s">
-        <v>275</v>
       </c>
       <c r="H65" t="s">
         <v>276</v>
       </c>
       <c r="I65" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s">
         <v>277</v>
-      </c>
-      <c r="J65" t="s">
-        <v>21</v>
       </c>
       <c r="K65" t="s">
         <v>278</v>
       </c>
       <c r="L65" t="s">
+        <v>22</v>
+      </c>
+      <c r="M65" t="s">
         <v>279</v>
-      </c>
-      <c r="M65" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6198,28 +6198,28 @@
         <v>273</v>
       </c>
       <c r="F66" t="s">
+        <v>274</v>
+      </c>
+      <c r="G66" t="s">
         <v>295</v>
-      </c>
-      <c r="G66" t="s">
-        <v>275</v>
       </c>
       <c r="H66" t="s">
         <v>276</v>
       </c>
       <c r="I66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s">
         <v>277</v>
-      </c>
-      <c r="J66" t="s">
-        <v>21</v>
       </c>
       <c r="K66" t="s">
         <v>278</v>
       </c>
       <c r="L66" t="s">
+        <v>22</v>
+      </c>
+      <c r="M66" t="s">
         <v>279</v>
-      </c>
-      <c r="M66" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6239,28 +6239,28 @@
         <v>273</v>
       </c>
       <c r="F67" t="s">
+        <v>274</v>
+      </c>
+      <c r="G67" t="s">
         <v>299</v>
-      </c>
-      <c r="G67" t="s">
-        <v>275</v>
       </c>
       <c r="H67" t="s">
         <v>276</v>
       </c>
       <c r="I67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s">
         <v>277</v>
-      </c>
-      <c r="J67" t="s">
-        <v>21</v>
       </c>
       <c r="K67" t="s">
         <v>278</v>
       </c>
       <c r="L67" t="s">
+        <v>22</v>
+      </c>
+      <c r="M67" t="s">
         <v>279</v>
-      </c>
-      <c r="M67" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6280,28 +6280,28 @@
         <v>273</v>
       </c>
       <c r="F68" t="s">
+        <v>274</v>
+      </c>
+      <c r="G68" t="s">
         <v>303</v>
-      </c>
-      <c r="G68" t="s">
-        <v>275</v>
       </c>
       <c r="H68" t="s">
         <v>276</v>
       </c>
       <c r="I68" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" t="s">
         <v>277</v>
-      </c>
-      <c r="J68" t="s">
-        <v>21</v>
       </c>
       <c r="K68" t="s">
         <v>278</v>
       </c>
       <c r="L68" t="s">
+        <v>22</v>
+      </c>
+      <c r="M68" t="s">
         <v>279</v>
-      </c>
-      <c r="M68" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6321,28 +6321,28 @@
         <v>273</v>
       </c>
       <c r="F69" t="s">
+        <v>274</v>
+      </c>
+      <c r="G69" t="s">
         <v>307</v>
-      </c>
-      <c r="G69" t="s">
-        <v>275</v>
       </c>
       <c r="H69" t="s">
         <v>276</v>
       </c>
       <c r="I69" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s">
         <v>277</v>
-      </c>
-      <c r="J69" t="s">
-        <v>21</v>
       </c>
       <c r="K69" t="s">
         <v>278</v>
       </c>
       <c r="L69" t="s">
+        <v>22</v>
+      </c>
+      <c r="M69" t="s">
         <v>279</v>
-      </c>
-      <c r="M69" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6362,28 +6362,28 @@
         <v>273</v>
       </c>
       <c r="F70" t="s">
+        <v>274</v>
+      </c>
+      <c r="G70" t="s">
         <v>311</v>
-      </c>
-      <c r="G70" t="s">
-        <v>275</v>
       </c>
       <c r="H70" t="s">
         <v>276</v>
       </c>
       <c r="I70" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s">
         <v>277</v>
-      </c>
-      <c r="J70" t="s">
-        <v>21</v>
       </c>
       <c r="K70" t="s">
         <v>278</v>
       </c>
       <c r="L70" t="s">
+        <v>22</v>
+      </c>
+      <c r="M70" t="s">
         <v>279</v>
-      </c>
-      <c r="M70" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6403,28 +6403,28 @@
         <v>273</v>
       </c>
       <c r="F71" t="s">
+        <v>274</v>
+      </c>
+      <c r="G71" t="s">
         <v>315</v>
-      </c>
-      <c r="G71" t="s">
-        <v>275</v>
       </c>
       <c r="H71" t="s">
         <v>276</v>
       </c>
       <c r="I71" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s">
         <v>277</v>
-      </c>
-      <c r="J71" t="s">
-        <v>21</v>
       </c>
       <c r="K71" t="s">
         <v>278</v>
       </c>
       <c r="L71" t="s">
+        <v>22</v>
+      </c>
+      <c r="M71" t="s">
         <v>279</v>
-      </c>
-      <c r="M71" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -6444,28 +6444,28 @@
         <v>273</v>
       </c>
       <c r="F72" t="s">
+        <v>274</v>
+      </c>
+      <c r="G72" t="s">
         <v>319</v>
-      </c>
-      <c r="G72" t="s">
-        <v>275</v>
       </c>
       <c r="H72" t="s">
         <v>276</v>
       </c>
       <c r="I72" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s">
         <v>277</v>
-      </c>
-      <c r="J72" t="s">
-        <v>21</v>
       </c>
       <c r="K72" t="s">
         <v>278</v>
       </c>
       <c r="L72" t="s">
+        <v>22</v>
+      </c>
+      <c r="M72" t="s">
         <v>279</v>
-      </c>
-      <c r="M72" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -6485,28 +6485,28 @@
         <v>273</v>
       </c>
       <c r="F73" t="s">
+        <v>274</v>
+      </c>
+      <c r="G73" t="s">
         <v>323</v>
-      </c>
-      <c r="G73" t="s">
-        <v>275</v>
       </c>
       <c r="H73" t="s">
         <v>276</v>
       </c>
       <c r="I73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s">
         <v>277</v>
-      </c>
-      <c r="J73" t="s">
-        <v>21</v>
       </c>
       <c r="K73" t="s">
         <v>278</v>
       </c>
       <c r="L73" t="s">
+        <v>22</v>
+      </c>
+      <c r="M73" t="s">
         <v>279</v>
-      </c>
-      <c r="M73" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -6526,28 +6526,28 @@
         <v>273</v>
       </c>
       <c r="F74" t="s">
+        <v>274</v>
+      </c>
+      <c r="G74" t="s">
         <v>327</v>
-      </c>
-      <c r="G74" t="s">
-        <v>275</v>
       </c>
       <c r="H74" t="s">
         <v>276</v>
       </c>
       <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s">
         <v>277</v>
-      </c>
-      <c r="J74" t="s">
-        <v>21</v>
       </c>
       <c r="K74" t="s">
         <v>278</v>
       </c>
       <c r="L74" t="s">
+        <v>22</v>
+      </c>
+      <c r="M74" t="s">
         <v>279</v>
-      </c>
-      <c r="M74" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -6567,28 +6567,28 @@
         <v>273</v>
       </c>
       <c r="F75" t="s">
+        <v>274</v>
+      </c>
+      <c r="G75" t="s">
         <v>331</v>
-      </c>
-      <c r="G75" t="s">
-        <v>275</v>
       </c>
       <c r="H75" t="s">
         <v>276</v>
       </c>
       <c r="I75" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s">
         <v>277</v>
-      </c>
-      <c r="J75" t="s">
-        <v>21</v>
       </c>
       <c r="K75" t="s">
         <v>278</v>
       </c>
       <c r="L75" t="s">
+        <v>22</v>
+      </c>
+      <c r="M75" t="s">
         <v>279</v>
-      </c>
-      <c r="M75" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -6608,28 +6608,28 @@
         <v>273</v>
       </c>
       <c r="F76" t="s">
+        <v>274</v>
+      </c>
+      <c r="G76" t="s">
         <v>335</v>
-      </c>
-      <c r="G76" t="s">
-        <v>275</v>
       </c>
       <c r="H76" t="s">
         <v>276</v>
       </c>
       <c r="I76" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s">
         <v>277</v>
-      </c>
-      <c r="J76" t="s">
-        <v>21</v>
       </c>
       <c r="K76" t="s">
         <v>278</v>
       </c>
       <c r="L76" t="s">
+        <v>22</v>
+      </c>
+      <c r="M76" t="s">
         <v>279</v>
-      </c>
-      <c r="M76" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -6649,28 +6649,28 @@
         <v>273</v>
       </c>
       <c r="F77" t="s">
+        <v>274</v>
+      </c>
+      <c r="G77" t="s">
         <v>339</v>
-      </c>
-      <c r="G77" t="s">
-        <v>275</v>
       </c>
       <c r="H77" t="s">
         <v>276</v>
       </c>
       <c r="I77" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s">
         <v>277</v>
-      </c>
-      <c r="J77" t="s">
-        <v>21</v>
       </c>
       <c r="K77" t="s">
         <v>278</v>
       </c>
       <c r="L77" t="s">
+        <v>22</v>
+      </c>
+      <c r="M77" t="s">
         <v>279</v>
-      </c>
-      <c r="M77" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6690,28 +6690,28 @@
         <v>273</v>
       </c>
       <c r="F78" t="s">
+        <v>274</v>
+      </c>
+      <c r="G78" t="s">
         <v>343</v>
-      </c>
-      <c r="G78" t="s">
-        <v>275</v>
       </c>
       <c r="H78" t="s">
         <v>276</v>
       </c>
       <c r="I78" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s">
         <v>277</v>
-      </c>
-      <c r="J78" t="s">
-        <v>21</v>
       </c>
       <c r="K78" t="s">
         <v>278</v>
       </c>
       <c r="L78" t="s">
+        <v>22</v>
+      </c>
+      <c r="M78" t="s">
         <v>279</v>
-      </c>
-      <c r="M78" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -6731,28 +6731,28 @@
         <v>273</v>
       </c>
       <c r="F79" t="s">
+        <v>274</v>
+      </c>
+      <c r="G79" t="s">
         <v>347</v>
-      </c>
-      <c r="G79" t="s">
-        <v>275</v>
       </c>
       <c r="H79" t="s">
         <v>276</v>
       </c>
       <c r="I79" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" t="s">
         <v>277</v>
-      </c>
-      <c r="J79" t="s">
-        <v>21</v>
       </c>
       <c r="K79" t="s">
         <v>278</v>
       </c>
       <c r="L79" t="s">
+        <v>22</v>
+      </c>
+      <c r="M79" t="s">
         <v>279</v>
-      </c>
-      <c r="M79" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -6772,28 +6772,28 @@
         <v>273</v>
       </c>
       <c r="F80" t="s">
+        <v>274</v>
+      </c>
+      <c r="G80" t="s">
         <v>351</v>
-      </c>
-      <c r="G80" t="s">
-        <v>275</v>
       </c>
       <c r="H80" t="s">
         <v>276</v>
       </c>
       <c r="I80" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s">
         <v>277</v>
-      </c>
-      <c r="J80" t="s">
-        <v>21</v>
       </c>
       <c r="K80" t="s">
         <v>278</v>
       </c>
       <c r="L80" t="s">
+        <v>22</v>
+      </c>
+      <c r="M80" t="s">
         <v>279</v>
-      </c>
-      <c r="M80" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -6813,28 +6813,28 @@
         <v>273</v>
       </c>
       <c r="F81" t="s">
+        <v>274</v>
+      </c>
+      <c r="G81" t="s">
         <v>355</v>
-      </c>
-      <c r="G81" t="s">
-        <v>275</v>
       </c>
       <c r="H81" t="s">
         <v>276</v>
       </c>
       <c r="I81" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s">
         <v>277</v>
-      </c>
-      <c r="J81" t="s">
-        <v>21</v>
       </c>
       <c r="K81" t="s">
         <v>278</v>
       </c>
       <c r="L81" t="s">
+        <v>22</v>
+      </c>
+      <c r="M81" t="s">
         <v>279</v>
-      </c>
-      <c r="M81" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -6854,28 +6854,28 @@
         <v>273</v>
       </c>
       <c r="F82" t="s">
+        <v>274</v>
+      </c>
+      <c r="G82" t="s">
         <v>359</v>
-      </c>
-      <c r="G82" t="s">
-        <v>275</v>
       </c>
       <c r="H82" t="s">
         <v>276</v>
       </c>
       <c r="I82" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s">
         <v>277</v>
-      </c>
-      <c r="J82" t="s">
-        <v>21</v>
       </c>
       <c r="K82" t="s">
         <v>278</v>
       </c>
       <c r="L82" t="s">
+        <v>22</v>
+      </c>
+      <c r="M82" t="s">
         <v>279</v>
-      </c>
-      <c r="M82" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6895,28 +6895,28 @@
         <v>273</v>
       </c>
       <c r="F83" t="s">
+        <v>274</v>
+      </c>
+      <c r="G83" t="s">
         <v>363</v>
-      </c>
-      <c r="G83" t="s">
-        <v>275</v>
       </c>
       <c r="H83" t="s">
         <v>276</v>
       </c>
       <c r="I83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s">
         <v>277</v>
-      </c>
-      <c r="J83" t="s">
-        <v>21</v>
       </c>
       <c r="K83" t="s">
         <v>278</v>
       </c>
       <c r="L83" t="s">
+        <v>22</v>
+      </c>
+      <c r="M83" t="s">
         <v>279</v>
-      </c>
-      <c r="M83" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -6936,28 +6936,28 @@
         <v>273</v>
       </c>
       <c r="F84" t="s">
+        <v>274</v>
+      </c>
+      <c r="G84" t="s">
         <v>367</v>
-      </c>
-      <c r="G84" t="s">
-        <v>275</v>
       </c>
       <c r="H84" t="s">
         <v>276</v>
       </c>
       <c r="I84" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s">
         <v>277</v>
-      </c>
-      <c r="J84" t="s">
-        <v>21</v>
       </c>
       <c r="K84" t="s">
         <v>278</v>
       </c>
       <c r="L84" t="s">
+        <v>22</v>
+      </c>
+      <c r="M84" t="s">
         <v>279</v>
-      </c>
-      <c r="M84" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -6977,28 +6977,28 @@
         <v>273</v>
       </c>
       <c r="F85" t="s">
+        <v>274</v>
+      </c>
+      <c r="G85" t="s">
         <v>371</v>
-      </c>
-      <c r="G85" t="s">
-        <v>275</v>
       </c>
       <c r="H85" t="s">
         <v>276</v>
       </c>
       <c r="I85" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" t="s">
         <v>277</v>
-      </c>
-      <c r="J85" t="s">
-        <v>21</v>
       </c>
       <c r="K85" t="s">
         <v>278</v>
       </c>
       <c r="L85" t="s">
+        <v>22</v>
+      </c>
+      <c r="M85" t="s">
         <v>279</v>
-      </c>
-      <c r="M85" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7018,28 +7018,28 @@
         <v>273</v>
       </c>
       <c r="F86" t="s">
+        <v>274</v>
+      </c>
+      <c r="G86" t="s">
         <v>375</v>
-      </c>
-      <c r="G86" t="s">
-        <v>275</v>
       </c>
       <c r="H86" t="s">
         <v>276</v>
       </c>
       <c r="I86" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" t="s">
         <v>277</v>
-      </c>
-      <c r="J86" t="s">
-        <v>21</v>
       </c>
       <c r="K86" t="s">
         <v>278</v>
       </c>
       <c r="L86" t="s">
+        <v>22</v>
+      </c>
+      <c r="M86" t="s">
         <v>279</v>
-      </c>
-      <c r="M86" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7059,28 +7059,28 @@
         <v>273</v>
       </c>
       <c r="F87" t="s">
+        <v>274</v>
+      </c>
+      <c r="G87" t="s">
         <v>379</v>
-      </c>
-      <c r="G87" t="s">
-        <v>275</v>
       </c>
       <c r="H87" t="s">
         <v>276</v>
       </c>
       <c r="I87" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" t="s">
         <v>277</v>
-      </c>
-      <c r="J87" t="s">
-        <v>21</v>
       </c>
       <c r="K87" t="s">
         <v>278</v>
       </c>
       <c r="L87" t="s">
+        <v>22</v>
+      </c>
+      <c r="M87" t="s">
         <v>279</v>
-      </c>
-      <c r="M87" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7100,28 +7100,28 @@
         <v>273</v>
       </c>
       <c r="F88" t="s">
+        <v>274</v>
+      </c>
+      <c r="G88" t="s">
         <v>383</v>
-      </c>
-      <c r="G88" t="s">
-        <v>275</v>
       </c>
       <c r="H88" t="s">
         <v>276</v>
       </c>
       <c r="I88" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" t="s">
         <v>277</v>
-      </c>
-      <c r="J88" t="s">
-        <v>21</v>
       </c>
       <c r="K88" t="s">
         <v>278</v>
       </c>
       <c r="L88" t="s">
+        <v>22</v>
+      </c>
+      <c r="M88" t="s">
         <v>279</v>
-      </c>
-      <c r="M88" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7141,28 +7141,28 @@
         <v>273</v>
       </c>
       <c r="F89" t="s">
+        <v>274</v>
+      </c>
+      <c r="G89" t="s">
         <v>387</v>
-      </c>
-      <c r="G89" t="s">
-        <v>275</v>
       </c>
       <c r="H89" t="s">
         <v>276</v>
       </c>
       <c r="I89" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" t="s">
         <v>277</v>
-      </c>
-      <c r="J89" t="s">
-        <v>21</v>
       </c>
       <c r="K89" t="s">
         <v>278</v>
       </c>
       <c r="L89" t="s">
+        <v>22</v>
+      </c>
+      <c r="M89" t="s">
         <v>279</v>
-      </c>
-      <c r="M89" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7191,19 +7191,19 @@
         <v>276</v>
       </c>
       <c r="I90" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J90" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K90" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L90" t="s">
+        <v>22</v>
+      </c>
+      <c r="M90" t="s">
         <v>279</v>
-      </c>
-      <c r="M90" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7223,28 +7223,28 @@
         <v>273</v>
       </c>
       <c r="F91" t="s">
+        <v>391</v>
+      </c>
+      <c r="G91" t="s">
         <v>397</v>
-      </c>
-      <c r="G91" t="s">
-        <v>392</v>
       </c>
       <c r="H91" t="s">
         <v>276</v>
       </c>
       <c r="I91" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J91" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K91" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L91" t="s">
+        <v>22</v>
+      </c>
+      <c r="M91" t="s">
         <v>279</v>
-      </c>
-      <c r="M91" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7264,28 +7264,28 @@
         <v>273</v>
       </c>
       <c r="F92" t="s">
+        <v>391</v>
+      </c>
+      <c r="G92" t="s">
         <v>401</v>
-      </c>
-      <c r="G92" t="s">
-        <v>392</v>
       </c>
       <c r="H92" t="s">
         <v>276</v>
       </c>
       <c r="I92" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J92" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K92" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L92" t="s">
+        <v>22</v>
+      </c>
+      <c r="M92" t="s">
         <v>279</v>
-      </c>
-      <c r="M92" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7305,28 +7305,28 @@
         <v>273</v>
       </c>
       <c r="F93" t="s">
+        <v>391</v>
+      </c>
+      <c r="G93" t="s">
         <v>405</v>
-      </c>
-      <c r="G93" t="s">
-        <v>392</v>
       </c>
       <c r="H93" t="s">
         <v>276</v>
       </c>
       <c r="I93" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J93" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K93" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L93" t="s">
+        <v>22</v>
+      </c>
+      <c r="M93" t="s">
         <v>279</v>
-      </c>
-      <c r="M93" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7346,28 +7346,28 @@
         <v>273</v>
       </c>
       <c r="F94" t="s">
+        <v>391</v>
+      </c>
+      <c r="G94" t="s">
         <v>409</v>
-      </c>
-      <c r="G94" t="s">
-        <v>392</v>
       </c>
       <c r="H94" t="s">
         <v>276</v>
       </c>
       <c r="I94" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J94" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K94" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L94" t="s">
+        <v>22</v>
+      </c>
+      <c r="M94" t="s">
         <v>279</v>
-      </c>
-      <c r="M94" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7387,28 +7387,28 @@
         <v>273</v>
       </c>
       <c r="F95" t="s">
+        <v>391</v>
+      </c>
+      <c r="G95" t="s">
         <v>413</v>
-      </c>
-      <c r="G95" t="s">
-        <v>392</v>
       </c>
       <c r="H95" t="s">
         <v>276</v>
       </c>
       <c r="I95" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J95" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K95" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L95" t="s">
+        <v>22</v>
+      </c>
+      <c r="M95" t="s">
         <v>279</v>
-      </c>
-      <c r="M95" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7428,28 +7428,28 @@
         <v>273</v>
       </c>
       <c r="F96" t="s">
+        <v>391</v>
+      </c>
+      <c r="G96" t="s">
         <v>417</v>
-      </c>
-      <c r="G96" t="s">
-        <v>392</v>
       </c>
       <c r="H96" t="s">
         <v>276</v>
       </c>
       <c r="I96" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J96" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K96" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s">
+        <v>22</v>
+      </c>
+      <c r="M96" t="s">
         <v>279</v>
-      </c>
-      <c r="M96" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -7469,28 +7469,28 @@
         <v>273</v>
       </c>
       <c r="F97" t="s">
+        <v>391</v>
+      </c>
+      <c r="G97" t="s">
         <v>421</v>
-      </c>
-      <c r="G97" t="s">
-        <v>392</v>
       </c>
       <c r="H97" t="s">
         <v>276</v>
       </c>
       <c r="I97" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J97" t="s">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="K97" t="s">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="L97" t="s">
+        <v>22</v>
+      </c>
+      <c r="M97" t="s">
         <v>279</v>
-      </c>
-      <c r="M97" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7519,19 +7519,19 @@
         <v>276</v>
       </c>
       <c r="I98" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J98" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K98" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L98" t="s">
+        <v>22</v>
+      </c>
+      <c r="M98" t="s">
         <v>279</v>
-      </c>
-      <c r="M98" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -7551,28 +7551,28 @@
         <v>273</v>
       </c>
       <c r="F99" t="s">
+        <v>425</v>
+      </c>
+      <c r="G99" t="s">
         <v>431</v>
-      </c>
-      <c r="G99" t="s">
-        <v>426</v>
       </c>
       <c r="H99" t="s">
         <v>276</v>
       </c>
       <c r="I99" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J99" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K99" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L99" t="s">
+        <v>22</v>
+      </c>
+      <c r="M99" t="s">
         <v>279</v>
-      </c>
-      <c r="M99" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -7592,28 +7592,28 @@
         <v>273</v>
       </c>
       <c r="F100" t="s">
+        <v>425</v>
+      </c>
+      <c r="G100" t="s">
         <v>435</v>
-      </c>
-      <c r="G100" t="s">
-        <v>426</v>
       </c>
       <c r="H100" t="s">
         <v>276</v>
       </c>
       <c r="I100" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J100" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K100" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L100" t="s">
+        <v>22</v>
+      </c>
+      <c r="M100" t="s">
         <v>279</v>
-      </c>
-      <c r="M100" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -7633,28 +7633,28 @@
         <v>273</v>
       </c>
       <c r="F101" t="s">
+        <v>425</v>
+      </c>
+      <c r="G101" t="s">
         <v>439</v>
-      </c>
-      <c r="G101" t="s">
-        <v>426</v>
       </c>
       <c r="H101" t="s">
         <v>276</v>
       </c>
       <c r="I101" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J101" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K101" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L101" t="s">
+        <v>22</v>
+      </c>
+      <c r="M101" t="s">
         <v>279</v>
-      </c>
-      <c r="M101" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -7674,28 +7674,28 @@
         <v>273</v>
       </c>
       <c r="F102" t="s">
+        <v>425</v>
+      </c>
+      <c r="G102" t="s">
         <v>443</v>
-      </c>
-      <c r="G102" t="s">
-        <v>426</v>
       </c>
       <c r="H102" t="s">
         <v>276</v>
       </c>
       <c r="I102" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J102" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K102" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L102" t="s">
+        <v>22</v>
+      </c>
+      <c r="M102" t="s">
         <v>279</v>
-      </c>
-      <c r="M102" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -7715,28 +7715,28 @@
         <v>273</v>
       </c>
       <c r="F103" t="s">
+        <v>425</v>
+      </c>
+      <c r="G103" t="s">
         <v>447</v>
-      </c>
-      <c r="G103" t="s">
-        <v>426</v>
       </c>
       <c r="H103" t="s">
         <v>276</v>
       </c>
       <c r="I103" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J103" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K103" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L103" t="s">
+        <v>22</v>
+      </c>
+      <c r="M103" t="s">
         <v>279</v>
-      </c>
-      <c r="M103" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -7756,28 +7756,28 @@
         <v>273</v>
       </c>
       <c r="F104" t="s">
+        <v>425</v>
+      </c>
+      <c r="G104" t="s">
         <v>451</v>
-      </c>
-      <c r="G104" t="s">
-        <v>426</v>
       </c>
       <c r="H104" t="s">
         <v>276</v>
       </c>
       <c r="I104" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J104" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K104" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L104" t="s">
+        <v>22</v>
+      </c>
+      <c r="M104" t="s">
         <v>279</v>
-      </c>
-      <c r="M104" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -7797,28 +7797,28 @@
         <v>273</v>
       </c>
       <c r="F105" t="s">
+        <v>425</v>
+      </c>
+      <c r="G105" t="s">
         <v>455</v>
-      </c>
-      <c r="G105" t="s">
-        <v>426</v>
       </c>
       <c r="H105" t="s">
         <v>276</v>
       </c>
       <c r="I105" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J105" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K105" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L105" t="s">
+        <v>22</v>
+      </c>
+      <c r="M105" t="s">
         <v>279</v>
-      </c>
-      <c r="M105" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -7838,28 +7838,28 @@
         <v>273</v>
       </c>
       <c r="F106" t="s">
+        <v>425</v>
+      </c>
+      <c r="G106" t="s">
         <v>459</v>
-      </c>
-      <c r="G106" t="s">
-        <v>426</v>
       </c>
       <c r="H106" t="s">
         <v>276</v>
       </c>
       <c r="I106" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J106" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K106" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L106" t="s">
+        <v>22</v>
+      </c>
+      <c r="M106" t="s">
         <v>279</v>
-      </c>
-      <c r="M106" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -7879,28 +7879,28 @@
         <v>273</v>
       </c>
       <c r="F107" t="s">
+        <v>425</v>
+      </c>
+      <c r="G107" t="s">
         <v>463</v>
-      </c>
-      <c r="G107" t="s">
-        <v>426</v>
       </c>
       <c r="H107" t="s">
         <v>276</v>
       </c>
       <c r="I107" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J107" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K107" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L107" t="s">
+        <v>22</v>
+      </c>
+      <c r="M107" t="s">
         <v>279</v>
-      </c>
-      <c r="M107" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -7920,28 +7920,28 @@
         <v>273</v>
       </c>
       <c r="F108" t="s">
+        <v>425</v>
+      </c>
+      <c r="G108" t="s">
         <v>467</v>
-      </c>
-      <c r="G108" t="s">
-        <v>426</v>
       </c>
       <c r="H108" t="s">
         <v>276</v>
       </c>
       <c r="I108" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J108" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K108" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L108" t="s">
+        <v>22</v>
+      </c>
+      <c r="M108" t="s">
         <v>279</v>
-      </c>
-      <c r="M108" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -7961,28 +7961,28 @@
         <v>273</v>
       </c>
       <c r="F109" t="s">
+        <v>425</v>
+      </c>
+      <c r="G109" t="s">
         <v>471</v>
-      </c>
-      <c r="G109" t="s">
-        <v>426</v>
       </c>
       <c r="H109" t="s">
         <v>276</v>
       </c>
       <c r="I109" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J109" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K109" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L109" t="s">
+        <v>22</v>
+      </c>
+      <c r="M109" t="s">
         <v>279</v>
-      </c>
-      <c r="M109" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -8002,28 +8002,28 @@
         <v>273</v>
       </c>
       <c r="F110" t="s">
+        <v>425</v>
+      </c>
+      <c r="G110" t="s">
         <v>475</v>
-      </c>
-      <c r="G110" t="s">
-        <v>426</v>
       </c>
       <c r="H110" t="s">
         <v>276</v>
       </c>
       <c r="I110" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J110" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K110" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L110" t="s">
+        <v>22</v>
+      </c>
+      <c r="M110" t="s">
         <v>279</v>
-      </c>
-      <c r="M110" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -8043,28 +8043,28 @@
         <v>273</v>
       </c>
       <c r="F111" t="s">
+        <v>425</v>
+      </c>
+      <c r="G111" t="s">
         <v>479</v>
-      </c>
-      <c r="G111" t="s">
-        <v>426</v>
       </c>
       <c r="H111" t="s">
         <v>276</v>
       </c>
       <c r="I111" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J111" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K111" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L111" t="s">
+        <v>22</v>
+      </c>
+      <c r="M111" t="s">
         <v>279</v>
-      </c>
-      <c r="M111" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -8084,28 +8084,28 @@
         <v>273</v>
       </c>
       <c r="F112" t="s">
+        <v>425</v>
+      </c>
+      <c r="G112" t="s">
         <v>483</v>
-      </c>
-      <c r="G112" t="s">
-        <v>426</v>
       </c>
       <c r="H112" t="s">
         <v>276</v>
       </c>
       <c r="I112" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J112" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K112" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L112" t="s">
+        <v>22</v>
+      </c>
+      <c r="M112" t="s">
         <v>279</v>
-      </c>
-      <c r="M112" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -8125,28 +8125,28 @@
         <v>273</v>
       </c>
       <c r="F113" t="s">
+        <v>425</v>
+      </c>
+      <c r="G113" t="s">
         <v>487</v>
-      </c>
-      <c r="G113" t="s">
-        <v>426</v>
       </c>
       <c r="H113" t="s">
         <v>276</v>
       </c>
       <c r="I113" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="J113" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="K113" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="L113" t="s">
+        <v>22</v>
+      </c>
+      <c r="M113" t="s">
         <v>279</v>
-      </c>
-      <c r="M113" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -8165,23 +8165,23 @@
       <c r="E114" t="s">
         <v>491</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>492</v>
       </c>
       <c r="H114" t="s">
+        <v>276</v>
+      </c>
+      <c r="I114" t="s">
+        <v>20</v>
+      </c>
+      <c r="K114" t="s">
+        <v>278</v>
+      </c>
+      <c r="L114" t="s">
+        <v>22</v>
+      </c>
+      <c r="M114" t="s">
         <v>493</v>
-      </c>
-      <c r="I114" t="s">
-        <v>277</v>
-      </c>
-      <c r="J114" t="s">
-        <v>21</v>
-      </c>
-      <c r="L114" t="s">
-        <v>279</v>
-      </c>
-      <c r="M114" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -8200,23 +8200,23 @@
       <c r="E115" t="s">
         <v>491</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>497</v>
       </c>
       <c r="H115" t="s">
+        <v>276</v>
+      </c>
+      <c r="I115" t="s">
+        <v>20</v>
+      </c>
+      <c r="K115" t="s">
+        <v>278</v>
+      </c>
+      <c r="L115" t="s">
+        <v>22</v>
+      </c>
+      <c r="M115" t="s">
         <v>493</v>
-      </c>
-      <c r="I115" t="s">
-        <v>277</v>
-      </c>
-      <c r="J115" t="s">
-        <v>21</v>
-      </c>
-      <c r="L115" t="s">
-        <v>279</v>
-      </c>
-      <c r="M115" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -8235,23 +8235,23 @@
       <c r="E116" t="s">
         <v>491</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>501</v>
       </c>
       <c r="H116" t="s">
+        <v>276</v>
+      </c>
+      <c r="I116" t="s">
+        <v>20</v>
+      </c>
+      <c r="K116" t="s">
+        <v>278</v>
+      </c>
+      <c r="L116" t="s">
+        <v>22</v>
+      </c>
+      <c r="M116" t="s">
         <v>493</v>
-      </c>
-      <c r="I116" t="s">
-        <v>277</v>
-      </c>
-      <c r="J116" t="s">
-        <v>21</v>
-      </c>
-      <c r="L116" t="s">
-        <v>279</v>
-      </c>
-      <c r="M116" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -8270,23 +8270,23 @@
       <c r="E117" t="s">
         <v>491</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>505</v>
       </c>
       <c r="H117" t="s">
+        <v>276</v>
+      </c>
+      <c r="I117" t="s">
+        <v>20</v>
+      </c>
+      <c r="K117" t="s">
+        <v>278</v>
+      </c>
+      <c r="L117" t="s">
+        <v>22</v>
+      </c>
+      <c r="M117" t="s">
         <v>493</v>
-      </c>
-      <c r="I117" t="s">
-        <v>277</v>
-      </c>
-      <c r="J117" t="s">
-        <v>21</v>
-      </c>
-      <c r="L117" t="s">
-        <v>279</v>
-      </c>
-      <c r="M117" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -8305,23 +8305,23 @@
       <c r="E118" t="s">
         <v>491</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>509</v>
       </c>
       <c r="H118" t="s">
+        <v>276</v>
+      </c>
+      <c r="I118" t="s">
+        <v>20</v>
+      </c>
+      <c r="K118" t="s">
+        <v>278</v>
+      </c>
+      <c r="L118" t="s">
+        <v>22</v>
+      </c>
+      <c r="M118" t="s">
         <v>493</v>
-      </c>
-      <c r="I118" t="s">
-        <v>277</v>
-      </c>
-      <c r="J118" t="s">
-        <v>21</v>
-      </c>
-      <c r="L118" t="s">
-        <v>279</v>
-      </c>
-      <c r="M118" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -8337,14 +8337,14 @@
       <c r="D119" t="s">
         <v>512</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>513</v>
       </c>
-      <c r="J119" t="s">
-        <v>21</v>
-      </c>
-      <c r="M119" t="s">
-        <v>23</v>
+      <c r="I119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L119" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -8363,23 +8363,23 @@
       <c r="E120" t="s">
         <v>517</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>518</v>
       </c>
       <c r="H120" t="s">
         <v>519</v>
       </c>
       <c r="I120" t="s">
+        <v>20</v>
+      </c>
+      <c r="K120" t="s">
         <v>520</v>
       </c>
-      <c r="J120" t="s">
-        <v>21</v>
-      </c>
       <c r="L120" t="s">
+        <v>22</v>
+      </c>
+      <c r="M120" t="s">
         <v>521</v>
-      </c>
-      <c r="M120" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -8398,23 +8398,23 @@
       <c r="E121" t="s">
         <v>517</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>525</v>
       </c>
       <c r="H121" t="s">
         <v>519</v>
       </c>
       <c r="I121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K121" t="s">
         <v>520</v>
       </c>
-      <c r="J121" t="s">
-        <v>21</v>
-      </c>
       <c r="L121" t="s">
+        <v>22</v>
+      </c>
+      <c r="M121" t="s">
         <v>521</v>
-      </c>
-      <c r="M121" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -8433,23 +8433,23 @@
       <c r="E122" t="s">
         <v>517</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>529</v>
       </c>
       <c r="H122" t="s">
         <v>519</v>
       </c>
       <c r="I122" t="s">
+        <v>20</v>
+      </c>
+      <c r="K122" t="s">
         <v>520</v>
       </c>
-      <c r="J122" t="s">
-        <v>21</v>
-      </c>
       <c r="L122" t="s">
+        <v>22</v>
+      </c>
+      <c r="M122" t="s">
         <v>521</v>
-      </c>
-      <c r="M122" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -8468,23 +8468,23 @@
       <c r="E123" t="s">
         <v>517</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>533</v>
       </c>
       <c r="H123" t="s">
         <v>519</v>
       </c>
       <c r="I123" t="s">
+        <v>20</v>
+      </c>
+      <c r="K123" t="s">
         <v>520</v>
       </c>
-      <c r="J123" t="s">
-        <v>21</v>
-      </c>
       <c r="L123" t="s">
+        <v>22</v>
+      </c>
+      <c r="M123" t="s">
         <v>521</v>
-      </c>
-      <c r="M123" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -8503,23 +8503,23 @@
       <c r="E124" t="s">
         <v>517</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>537</v>
       </c>
       <c r="H124" t="s">
         <v>519</v>
       </c>
       <c r="I124" t="s">
+        <v>20</v>
+      </c>
+      <c r="K124" t="s">
         <v>520</v>
       </c>
-      <c r="J124" t="s">
-        <v>21</v>
-      </c>
       <c r="L124" t="s">
+        <v>22</v>
+      </c>
+      <c r="M124" t="s">
         <v>521</v>
-      </c>
-      <c r="M124" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -8538,23 +8538,23 @@
       <c r="E125" t="s">
         <v>541</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>542</v>
       </c>
       <c r="H125" t="s">
+        <v>519</v>
+      </c>
+      <c r="I125" t="s">
+        <v>20</v>
+      </c>
+      <c r="K125" t="s">
+        <v>520</v>
+      </c>
+      <c r="L125" t="s">
+        <v>22</v>
+      </c>
+      <c r="M125" t="s">
         <v>543</v>
-      </c>
-      <c r="I125" t="s">
-        <v>520</v>
-      </c>
-      <c r="J125" t="s">
-        <v>21</v>
-      </c>
-      <c r="L125" t="s">
-        <v>521</v>
-      </c>
-      <c r="M125" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -8573,23 +8573,23 @@
       <c r="E126" t="s">
         <v>541</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>547</v>
       </c>
       <c r="H126" t="s">
+        <v>519</v>
+      </c>
+      <c r="I126" t="s">
+        <v>20</v>
+      </c>
+      <c r="K126" t="s">
+        <v>520</v>
+      </c>
+      <c r="L126" t="s">
+        <v>22</v>
+      </c>
+      <c r="M126" t="s">
         <v>543</v>
-      </c>
-      <c r="I126" t="s">
-        <v>520</v>
-      </c>
-      <c r="J126" t="s">
-        <v>21</v>
-      </c>
-      <c r="L126" t="s">
-        <v>521</v>
-      </c>
-      <c r="M126" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -8608,23 +8608,23 @@
       <c r="E127" t="s">
         <v>541</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>551</v>
       </c>
       <c r="H127" t="s">
+        <v>519</v>
+      </c>
+      <c r="I127" t="s">
+        <v>20</v>
+      </c>
+      <c r="K127" t="s">
+        <v>520</v>
+      </c>
+      <c r="L127" t="s">
+        <v>22</v>
+      </c>
+      <c r="M127" t="s">
         <v>543</v>
-      </c>
-      <c r="I127" t="s">
-        <v>520</v>
-      </c>
-      <c r="J127" t="s">
-        <v>21</v>
-      </c>
-      <c r="L127" t="s">
-        <v>521</v>
-      </c>
-      <c r="M127" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -8643,23 +8643,23 @@
       <c r="E128" t="s">
         <v>541</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>555</v>
       </c>
       <c r="H128" t="s">
+        <v>519</v>
+      </c>
+      <c r="I128" t="s">
+        <v>20</v>
+      </c>
+      <c r="K128" t="s">
+        <v>520</v>
+      </c>
+      <c r="L128" t="s">
+        <v>22</v>
+      </c>
+      <c r="M128" t="s">
         <v>543</v>
-      </c>
-      <c r="I128" t="s">
-        <v>520</v>
-      </c>
-      <c r="J128" t="s">
-        <v>21</v>
-      </c>
-      <c r="L128" t="s">
-        <v>521</v>
-      </c>
-      <c r="M128" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -8678,23 +8678,23 @@
       <c r="E129" t="s">
         <v>541</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>559</v>
       </c>
       <c r="H129" t="s">
+        <v>519</v>
+      </c>
+      <c r="I129" t="s">
+        <v>20</v>
+      </c>
+      <c r="K129" t="s">
+        <v>520</v>
+      </c>
+      <c r="L129" t="s">
+        <v>22</v>
+      </c>
+      <c r="M129" t="s">
         <v>543</v>
-      </c>
-      <c r="I129" t="s">
-        <v>520</v>
-      </c>
-      <c r="J129" t="s">
-        <v>21</v>
-      </c>
-      <c r="L129" t="s">
-        <v>521</v>
-      </c>
-      <c r="M129" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -8713,23 +8713,23 @@
       <c r="E130" t="s">
         <v>541</v>
       </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>563</v>
       </c>
       <c r="H130" t="s">
+        <v>519</v>
+      </c>
+      <c r="I130" t="s">
+        <v>20</v>
+      </c>
+      <c r="K130" t="s">
+        <v>520</v>
+      </c>
+      <c r="L130" t="s">
+        <v>22</v>
+      </c>
+      <c r="M130" t="s">
         <v>543</v>
-      </c>
-      <c r="I130" t="s">
-        <v>520</v>
-      </c>
-      <c r="J130" t="s">
-        <v>21</v>
-      </c>
-      <c r="L130" t="s">
-        <v>521</v>
-      </c>
-      <c r="M130" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -8748,23 +8748,23 @@
       <c r="E131" t="s">
         <v>541</v>
       </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
         <v>567</v>
       </c>
       <c r="H131" t="s">
+        <v>519</v>
+      </c>
+      <c r="I131" t="s">
+        <v>20</v>
+      </c>
+      <c r="K131" t="s">
+        <v>520</v>
+      </c>
+      <c r="L131" t="s">
+        <v>22</v>
+      </c>
+      <c r="M131" t="s">
         <v>543</v>
-      </c>
-      <c r="I131" t="s">
-        <v>520</v>
-      </c>
-      <c r="J131" t="s">
-        <v>21</v>
-      </c>
-      <c r="L131" t="s">
-        <v>521</v>
-      </c>
-      <c r="M131" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -8783,23 +8783,23 @@
       <c r="E132" t="s">
         <v>571</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>572</v>
       </c>
       <c r="H132" t="s">
+        <v>519</v>
+      </c>
+      <c r="I132" t="s">
+        <v>20</v>
+      </c>
+      <c r="K132" t="s">
+        <v>520</v>
+      </c>
+      <c r="L132" t="s">
+        <v>22</v>
+      </c>
+      <c r="M132" t="s">
         <v>573</v>
-      </c>
-      <c r="I132" t="s">
-        <v>520</v>
-      </c>
-      <c r="J132" t="s">
-        <v>21</v>
-      </c>
-      <c r="L132" t="s">
-        <v>521</v>
-      </c>
-      <c r="M132" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -8818,23 +8818,23 @@
       <c r="E133" t="s">
         <v>571</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>577</v>
       </c>
       <c r="H133" t="s">
+        <v>519</v>
+      </c>
+      <c r="I133" t="s">
+        <v>20</v>
+      </c>
+      <c r="K133" t="s">
+        <v>520</v>
+      </c>
+      <c r="L133" t="s">
+        <v>22</v>
+      </c>
+      <c r="M133" t="s">
         <v>573</v>
-      </c>
-      <c r="I133" t="s">
-        <v>520</v>
-      </c>
-      <c r="J133" t="s">
-        <v>21</v>
-      </c>
-      <c r="L133" t="s">
-        <v>521</v>
-      </c>
-      <c r="M133" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -8853,23 +8853,23 @@
       <c r="E134" t="s">
         <v>571</v>
       </c>
-      <c r="F134" t="s">
+      <c r="G134" t="s">
         <v>581</v>
       </c>
       <c r="H134" t="s">
+        <v>519</v>
+      </c>
+      <c r="I134" t="s">
+        <v>20</v>
+      </c>
+      <c r="K134" t="s">
+        <v>520</v>
+      </c>
+      <c r="L134" t="s">
+        <v>22</v>
+      </c>
+      <c r="M134" t="s">
         <v>573</v>
-      </c>
-      <c r="I134" t="s">
-        <v>520</v>
-      </c>
-      <c r="J134" t="s">
-        <v>21</v>
-      </c>
-      <c r="L134" t="s">
-        <v>521</v>
-      </c>
-      <c r="M134" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -8888,23 +8888,23 @@
       <c r="E135" t="s">
         <v>571</v>
       </c>
-      <c r="F135" t="s">
+      <c r="G135" t="s">
         <v>585</v>
       </c>
       <c r="H135" t="s">
+        <v>519</v>
+      </c>
+      <c r="I135" t="s">
+        <v>20</v>
+      </c>
+      <c r="K135" t="s">
+        <v>520</v>
+      </c>
+      <c r="L135" t="s">
+        <v>22</v>
+      </c>
+      <c r="M135" t="s">
         <v>573</v>
-      </c>
-      <c r="I135" t="s">
-        <v>520</v>
-      </c>
-      <c r="J135" t="s">
-        <v>21</v>
-      </c>
-      <c r="L135" t="s">
-        <v>521</v>
-      </c>
-      <c r="M135" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -8923,23 +8923,23 @@
       <c r="E136" t="s">
         <v>571</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
         <v>589</v>
       </c>
       <c r="H136" t="s">
+        <v>519</v>
+      </c>
+      <c r="I136" t="s">
+        <v>20</v>
+      </c>
+      <c r="K136" t="s">
+        <v>520</v>
+      </c>
+      <c r="L136" t="s">
+        <v>22</v>
+      </c>
+      <c r="M136" t="s">
         <v>573</v>
-      </c>
-      <c r="I136" t="s">
-        <v>520</v>
-      </c>
-      <c r="J136" t="s">
-        <v>21</v>
-      </c>
-      <c r="L136" t="s">
-        <v>521</v>
-      </c>
-      <c r="M136" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -8958,23 +8958,23 @@
       <c r="E137" t="s">
         <v>571</v>
       </c>
-      <c r="F137" t="s">
+      <c r="G137" t="s">
         <v>593</v>
       </c>
       <c r="H137" t="s">
+        <v>519</v>
+      </c>
+      <c r="I137" t="s">
+        <v>20</v>
+      </c>
+      <c r="K137" t="s">
+        <v>520</v>
+      </c>
+      <c r="L137" t="s">
+        <v>22</v>
+      </c>
+      <c r="M137" t="s">
         <v>573</v>
-      </c>
-      <c r="I137" t="s">
-        <v>520</v>
-      </c>
-      <c r="J137" t="s">
-        <v>21</v>
-      </c>
-      <c r="L137" t="s">
-        <v>521</v>
-      </c>
-      <c r="M137" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -8993,23 +8993,23 @@
       <c r="E138" t="s">
         <v>571</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>597</v>
       </c>
       <c r="H138" t="s">
+        <v>519</v>
+      </c>
+      <c r="I138" t="s">
+        <v>20</v>
+      </c>
+      <c r="K138" t="s">
+        <v>520</v>
+      </c>
+      <c r="L138" t="s">
+        <v>22</v>
+      </c>
+      <c r="M138" t="s">
         <v>573</v>
-      </c>
-      <c r="I138" t="s">
-        <v>520</v>
-      </c>
-      <c r="J138" t="s">
-        <v>21</v>
-      </c>
-      <c r="L138" t="s">
-        <v>521</v>
-      </c>
-      <c r="M138" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -9028,23 +9028,23 @@
       <c r="E139" t="s">
         <v>571</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>601</v>
       </c>
       <c r="H139" t="s">
+        <v>519</v>
+      </c>
+      <c r="I139" t="s">
+        <v>20</v>
+      </c>
+      <c r="K139" t="s">
+        <v>520</v>
+      </c>
+      <c r="L139" t="s">
+        <v>22</v>
+      </c>
+      <c r="M139" t="s">
         <v>573</v>
-      </c>
-      <c r="I139" t="s">
-        <v>520</v>
-      </c>
-      <c r="J139" t="s">
-        <v>21</v>
-      </c>
-      <c r="L139" t="s">
-        <v>521</v>
-      </c>
-      <c r="M139" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -9063,23 +9063,23 @@
       <c r="E140" t="s">
         <v>571</v>
       </c>
-      <c r="F140" t="s">
+      <c r="G140" t="s">
         <v>605</v>
       </c>
       <c r="H140" t="s">
+        <v>519</v>
+      </c>
+      <c r="I140" t="s">
+        <v>20</v>
+      </c>
+      <c r="K140" t="s">
+        <v>520</v>
+      </c>
+      <c r="L140" t="s">
+        <v>22</v>
+      </c>
+      <c r="M140" t="s">
         <v>573</v>
-      </c>
-      <c r="I140" t="s">
-        <v>520</v>
-      </c>
-      <c r="J140" t="s">
-        <v>21</v>
-      </c>
-      <c r="L140" t="s">
-        <v>521</v>
-      </c>
-      <c r="M140" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -9098,23 +9098,23 @@
       <c r="E141" t="s">
         <v>571</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>609</v>
       </c>
       <c r="H141" t="s">
+        <v>519</v>
+      </c>
+      <c r="I141" t="s">
+        <v>20</v>
+      </c>
+      <c r="K141" t="s">
+        <v>520</v>
+      </c>
+      <c r="L141" t="s">
+        <v>22</v>
+      </c>
+      <c r="M141" t="s">
         <v>573</v>
-      </c>
-      <c r="I141" t="s">
-        <v>520</v>
-      </c>
-      <c r="J141" t="s">
-        <v>21</v>
-      </c>
-      <c r="L141" t="s">
-        <v>521</v>
-      </c>
-      <c r="M141" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -9133,23 +9133,23 @@
       <c r="E142" t="s">
         <v>571</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>613</v>
       </c>
       <c r="H142" t="s">
+        <v>519</v>
+      </c>
+      <c r="I142" t="s">
+        <v>20</v>
+      </c>
+      <c r="K142" t="s">
+        <v>520</v>
+      </c>
+      <c r="L142" t="s">
+        <v>22</v>
+      </c>
+      <c r="M142" t="s">
         <v>573</v>
-      </c>
-      <c r="I142" t="s">
-        <v>520</v>
-      </c>
-      <c r="J142" t="s">
-        <v>21</v>
-      </c>
-      <c r="L142" t="s">
-        <v>521</v>
-      </c>
-      <c r="M142" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -9168,23 +9168,23 @@
       <c r="E143" t="s">
         <v>617</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>618</v>
       </c>
       <c r="H143" t="s">
+        <v>519</v>
+      </c>
+      <c r="I143" t="s">
+        <v>20</v>
+      </c>
+      <c r="K143" t="s">
+        <v>520</v>
+      </c>
+      <c r="L143" t="s">
+        <v>22</v>
+      </c>
+      <c r="M143" t="s">
         <v>619</v>
-      </c>
-      <c r="I143" t="s">
-        <v>520</v>
-      </c>
-      <c r="J143" t="s">
-        <v>21</v>
-      </c>
-      <c r="L143" t="s">
-        <v>521</v>
-      </c>
-      <c r="M143" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -9203,23 +9203,23 @@
       <c r="E144" t="s">
         <v>617</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>623</v>
       </c>
       <c r="H144" t="s">
+        <v>519</v>
+      </c>
+      <c r="I144" t="s">
+        <v>20</v>
+      </c>
+      <c r="K144" t="s">
+        <v>520</v>
+      </c>
+      <c r="L144" t="s">
+        <v>22</v>
+      </c>
+      <c r="M144" t="s">
         <v>619</v>
-      </c>
-      <c r="I144" t="s">
-        <v>520</v>
-      </c>
-      <c r="J144" t="s">
-        <v>21</v>
-      </c>
-      <c r="L144" t="s">
-        <v>521</v>
-      </c>
-      <c r="M144" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -9238,23 +9238,23 @@
       <c r="E145" t="s">
         <v>617</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>627</v>
       </c>
       <c r="H145" t="s">
+        <v>519</v>
+      </c>
+      <c r="I145" t="s">
+        <v>20</v>
+      </c>
+      <c r="K145" t="s">
+        <v>520</v>
+      </c>
+      <c r="L145" t="s">
+        <v>22</v>
+      </c>
+      <c r="M145" t="s">
         <v>619</v>
-      </c>
-      <c r="I145" t="s">
-        <v>520</v>
-      </c>
-      <c r="J145" t="s">
-        <v>21</v>
-      </c>
-      <c r="L145" t="s">
-        <v>521</v>
-      </c>
-      <c r="M145" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -9273,23 +9273,23 @@
       <c r="E146" t="s">
         <v>617</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>631</v>
       </c>
       <c r="H146" t="s">
+        <v>519</v>
+      </c>
+      <c r="I146" t="s">
+        <v>20</v>
+      </c>
+      <c r="K146" t="s">
+        <v>520</v>
+      </c>
+      <c r="L146" t="s">
+        <v>22</v>
+      </c>
+      <c r="M146" t="s">
         <v>619</v>
-      </c>
-      <c r="I146" t="s">
-        <v>520</v>
-      </c>
-      <c r="J146" t="s">
-        <v>21</v>
-      </c>
-      <c r="L146" t="s">
-        <v>521</v>
-      </c>
-      <c r="M146" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -9308,23 +9308,23 @@
       <c r="E147" t="s">
         <v>617</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>635</v>
       </c>
       <c r="H147" t="s">
+        <v>519</v>
+      </c>
+      <c r="I147" t="s">
+        <v>20</v>
+      </c>
+      <c r="K147" t="s">
+        <v>520</v>
+      </c>
+      <c r="L147" t="s">
+        <v>22</v>
+      </c>
+      <c r="M147" t="s">
         <v>619</v>
-      </c>
-      <c r="I147" t="s">
-        <v>520</v>
-      </c>
-      <c r="J147" t="s">
-        <v>21</v>
-      </c>
-      <c r="L147" t="s">
-        <v>521</v>
-      </c>
-      <c r="M147" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -9343,23 +9343,23 @@
       <c r="E148" t="s">
         <v>617</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>639</v>
       </c>
       <c r="H148" t="s">
+        <v>519</v>
+      </c>
+      <c r="I148" t="s">
+        <v>20</v>
+      </c>
+      <c r="K148" t="s">
+        <v>520</v>
+      </c>
+      <c r="L148" t="s">
+        <v>22</v>
+      </c>
+      <c r="M148" t="s">
         <v>619</v>
-      </c>
-      <c r="I148" t="s">
-        <v>520</v>
-      </c>
-      <c r="J148" t="s">
-        <v>21</v>
-      </c>
-      <c r="L148" t="s">
-        <v>521</v>
-      </c>
-      <c r="M148" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -9378,23 +9378,23 @@
       <c r="E149" t="s">
         <v>617</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>643</v>
       </c>
       <c r="H149" t="s">
+        <v>519</v>
+      </c>
+      <c r="I149" t="s">
+        <v>20</v>
+      </c>
+      <c r="K149" t="s">
+        <v>520</v>
+      </c>
+      <c r="L149" t="s">
+        <v>22</v>
+      </c>
+      <c r="M149" t="s">
         <v>619</v>
-      </c>
-      <c r="I149" t="s">
-        <v>520</v>
-      </c>
-      <c r="J149" t="s">
-        <v>21</v>
-      </c>
-      <c r="L149" t="s">
-        <v>521</v>
-      </c>
-      <c r="M149" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -9413,23 +9413,23 @@
       <c r="E150" t="s">
         <v>617</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>647</v>
       </c>
       <c r="H150" t="s">
+        <v>519</v>
+      </c>
+      <c r="I150" t="s">
+        <v>20</v>
+      </c>
+      <c r="K150" t="s">
+        <v>520</v>
+      </c>
+      <c r="L150" t="s">
+        <v>22</v>
+      </c>
+      <c r="M150" t="s">
         <v>619</v>
-      </c>
-      <c r="I150" t="s">
-        <v>520</v>
-      </c>
-      <c r="J150" t="s">
-        <v>21</v>
-      </c>
-      <c r="L150" t="s">
-        <v>521</v>
-      </c>
-      <c r="M150" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -9448,23 +9448,23 @@
       <c r="E151" t="s">
         <v>617</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>651</v>
       </c>
       <c r="H151" t="s">
+        <v>519</v>
+      </c>
+      <c r="I151" t="s">
+        <v>20</v>
+      </c>
+      <c r="K151" t="s">
+        <v>520</v>
+      </c>
+      <c r="L151" t="s">
+        <v>22</v>
+      </c>
+      <c r="M151" t="s">
         <v>619</v>
-      </c>
-      <c r="I151" t="s">
-        <v>520</v>
-      </c>
-      <c r="J151" t="s">
-        <v>21</v>
-      </c>
-      <c r="L151" t="s">
-        <v>521</v>
-      </c>
-      <c r="M151" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -9483,23 +9483,23 @@
       <c r="E152" t="s">
         <v>655</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>656</v>
       </c>
       <c r="H152" t="s">
+        <v>519</v>
+      </c>
+      <c r="I152" t="s">
+        <v>20</v>
+      </c>
+      <c r="K152" t="s">
+        <v>520</v>
+      </c>
+      <c r="L152" t="s">
+        <v>22</v>
+      </c>
+      <c r="M152" t="s">
         <v>657</v>
-      </c>
-      <c r="I152" t="s">
-        <v>520</v>
-      </c>
-      <c r="J152" t="s">
-        <v>21</v>
-      </c>
-      <c r="L152" t="s">
-        <v>521</v>
-      </c>
-      <c r="M152" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -9518,23 +9518,23 @@
       <c r="E153" t="s">
         <v>655</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>661</v>
       </c>
       <c r="H153" t="s">
+        <v>519</v>
+      </c>
+      <c r="I153" t="s">
+        <v>20</v>
+      </c>
+      <c r="K153" t="s">
+        <v>520</v>
+      </c>
+      <c r="L153" t="s">
+        <v>22</v>
+      </c>
+      <c r="M153" t="s">
         <v>657</v>
-      </c>
-      <c r="I153" t="s">
-        <v>520</v>
-      </c>
-      <c r="J153" t="s">
-        <v>21</v>
-      </c>
-      <c r="L153" t="s">
-        <v>521</v>
-      </c>
-      <c r="M153" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -9553,23 +9553,23 @@
       <c r="E154" t="s">
         <v>655</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>665</v>
       </c>
       <c r="H154" t="s">
+        <v>519</v>
+      </c>
+      <c r="I154" t="s">
+        <v>20</v>
+      </c>
+      <c r="K154" t="s">
+        <v>520</v>
+      </c>
+      <c r="L154" t="s">
+        <v>22</v>
+      </c>
+      <c r="M154" t="s">
         <v>657</v>
-      </c>
-      <c r="I154" t="s">
-        <v>520</v>
-      </c>
-      <c r="J154" t="s">
-        <v>21</v>
-      </c>
-      <c r="L154" t="s">
-        <v>521</v>
-      </c>
-      <c r="M154" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -9588,23 +9588,23 @@
       <c r="E155" t="s">
         <v>655</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>669</v>
       </c>
       <c r="H155" t="s">
+        <v>519</v>
+      </c>
+      <c r="I155" t="s">
+        <v>20</v>
+      </c>
+      <c r="K155" t="s">
+        <v>520</v>
+      </c>
+      <c r="L155" t="s">
+        <v>22</v>
+      </c>
+      <c r="M155" t="s">
         <v>657</v>
-      </c>
-      <c r="I155" t="s">
-        <v>520</v>
-      </c>
-      <c r="J155" t="s">
-        <v>21</v>
-      </c>
-      <c r="L155" t="s">
-        <v>521</v>
-      </c>
-      <c r="M155" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -9623,23 +9623,23 @@
       <c r="E156" t="s">
         <v>655</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>673</v>
       </c>
       <c r="H156" t="s">
+        <v>519</v>
+      </c>
+      <c r="I156" t="s">
+        <v>20</v>
+      </c>
+      <c r="K156" t="s">
+        <v>520</v>
+      </c>
+      <c r="L156" t="s">
+        <v>22</v>
+      </c>
+      <c r="M156" t="s">
         <v>657</v>
-      </c>
-      <c r="I156" t="s">
-        <v>520</v>
-      </c>
-      <c r="J156" t="s">
-        <v>21</v>
-      </c>
-      <c r="L156" t="s">
-        <v>521</v>
-      </c>
-      <c r="M156" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -9658,23 +9658,23 @@
       <c r="E157" t="s">
         <v>655</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>677</v>
       </c>
       <c r="H157" t="s">
+        <v>519</v>
+      </c>
+      <c r="I157" t="s">
+        <v>20</v>
+      </c>
+      <c r="K157" t="s">
+        <v>520</v>
+      </c>
+      <c r="L157" t="s">
+        <v>22</v>
+      </c>
+      <c r="M157" t="s">
         <v>657</v>
-      </c>
-      <c r="I157" t="s">
-        <v>520</v>
-      </c>
-      <c r="J157" t="s">
-        <v>21</v>
-      </c>
-      <c r="L157" t="s">
-        <v>521</v>
-      </c>
-      <c r="M157" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -9693,23 +9693,23 @@
       <c r="E158" t="s">
         <v>655</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>681</v>
       </c>
       <c r="H158" t="s">
+        <v>519</v>
+      </c>
+      <c r="I158" t="s">
+        <v>20</v>
+      </c>
+      <c r="K158" t="s">
+        <v>520</v>
+      </c>
+      <c r="L158" t="s">
+        <v>22</v>
+      </c>
+      <c r="M158" t="s">
         <v>657</v>
-      </c>
-      <c r="I158" t="s">
-        <v>520</v>
-      </c>
-      <c r="J158" t="s">
-        <v>21</v>
-      </c>
-      <c r="L158" t="s">
-        <v>521</v>
-      </c>
-      <c r="M158" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -9728,23 +9728,23 @@
       <c r="E159" t="s">
         <v>655</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
         <v>685</v>
       </c>
       <c r="H159" t="s">
+        <v>519</v>
+      </c>
+      <c r="I159" t="s">
+        <v>20</v>
+      </c>
+      <c r="K159" t="s">
+        <v>520</v>
+      </c>
+      <c r="L159" t="s">
+        <v>22</v>
+      </c>
+      <c r="M159" t="s">
         <v>657</v>
-      </c>
-      <c r="I159" t="s">
-        <v>520</v>
-      </c>
-      <c r="J159" t="s">
-        <v>21</v>
-      </c>
-      <c r="L159" t="s">
-        <v>521</v>
-      </c>
-      <c r="M159" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -9763,23 +9763,23 @@
       <c r="E160" t="s">
         <v>655</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>689</v>
       </c>
       <c r="H160" t="s">
+        <v>519</v>
+      </c>
+      <c r="I160" t="s">
+        <v>20</v>
+      </c>
+      <c r="K160" t="s">
+        <v>520</v>
+      </c>
+      <c r="L160" t="s">
+        <v>22</v>
+      </c>
+      <c r="M160" t="s">
         <v>657</v>
-      </c>
-      <c r="I160" t="s">
-        <v>520</v>
-      </c>
-      <c r="J160" t="s">
-        <v>21</v>
-      </c>
-      <c r="L160" t="s">
-        <v>521</v>
-      </c>
-      <c r="M160" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -9798,23 +9798,23 @@
       <c r="E161" t="s">
         <v>655</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>693</v>
       </c>
       <c r="H161" t="s">
+        <v>519</v>
+      </c>
+      <c r="I161" t="s">
+        <v>20</v>
+      </c>
+      <c r="K161" t="s">
+        <v>520</v>
+      </c>
+      <c r="L161" t="s">
+        <v>22</v>
+      </c>
+      <c r="M161" t="s">
         <v>657</v>
-      </c>
-      <c r="I161" t="s">
-        <v>520</v>
-      </c>
-      <c r="J161" t="s">
-        <v>21</v>
-      </c>
-      <c r="L161" t="s">
-        <v>521</v>
-      </c>
-      <c r="M161" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -9833,23 +9833,23 @@
       <c r="E162" t="s">
         <v>655</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>697</v>
       </c>
       <c r="H162" t="s">
+        <v>519</v>
+      </c>
+      <c r="I162" t="s">
+        <v>20</v>
+      </c>
+      <c r="K162" t="s">
+        <v>520</v>
+      </c>
+      <c r="L162" t="s">
+        <v>22</v>
+      </c>
+      <c r="M162" t="s">
         <v>657</v>
-      </c>
-      <c r="I162" t="s">
-        <v>520</v>
-      </c>
-      <c r="J162" t="s">
-        <v>21</v>
-      </c>
-      <c r="L162" t="s">
-        <v>521</v>
-      </c>
-      <c r="M162" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -9868,23 +9868,23 @@
       <c r="E163" t="s">
         <v>655</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>701</v>
       </c>
       <c r="H163" t="s">
+        <v>519</v>
+      </c>
+      <c r="I163" t="s">
+        <v>20</v>
+      </c>
+      <c r="K163" t="s">
+        <v>520</v>
+      </c>
+      <c r="L163" t="s">
+        <v>22</v>
+      </c>
+      <c r="M163" t="s">
         <v>657</v>
-      </c>
-      <c r="I163" t="s">
-        <v>520</v>
-      </c>
-      <c r="J163" t="s">
-        <v>21</v>
-      </c>
-      <c r="L163" t="s">
-        <v>521</v>
-      </c>
-      <c r="M163" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -9903,23 +9903,23 @@
       <c r="E164" t="s">
         <v>655</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>705</v>
       </c>
       <c r="H164" t="s">
+        <v>519</v>
+      </c>
+      <c r="I164" t="s">
+        <v>20</v>
+      </c>
+      <c r="K164" t="s">
+        <v>520</v>
+      </c>
+      <c r="L164" t="s">
+        <v>22</v>
+      </c>
+      <c r="M164" t="s">
         <v>657</v>
-      </c>
-      <c r="I164" t="s">
-        <v>520</v>
-      </c>
-      <c r="J164" t="s">
-        <v>21</v>
-      </c>
-      <c r="L164" t="s">
-        <v>521</v>
-      </c>
-      <c r="M164" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -9938,23 +9938,23 @@
       <c r="E165" t="s">
         <v>655</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>709</v>
       </c>
       <c r="H165" t="s">
+        <v>519</v>
+      </c>
+      <c r="I165" t="s">
+        <v>20</v>
+      </c>
+      <c r="K165" t="s">
+        <v>520</v>
+      </c>
+      <c r="L165" t="s">
+        <v>22</v>
+      </c>
+      <c r="M165" t="s">
         <v>657</v>
-      </c>
-      <c r="I165" t="s">
-        <v>520</v>
-      </c>
-      <c r="J165" t="s">
-        <v>21</v>
-      </c>
-      <c r="L165" t="s">
-        <v>521</v>
-      </c>
-      <c r="M165" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -9973,23 +9973,23 @@
       <c r="E166" t="s">
         <v>655</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>713</v>
       </c>
       <c r="H166" t="s">
+        <v>519</v>
+      </c>
+      <c r="I166" t="s">
+        <v>20</v>
+      </c>
+      <c r="K166" t="s">
+        <v>520</v>
+      </c>
+      <c r="L166" t="s">
+        <v>22</v>
+      </c>
+      <c r="M166" t="s">
         <v>657</v>
-      </c>
-      <c r="I166" t="s">
-        <v>520</v>
-      </c>
-      <c r="J166" t="s">
-        <v>21</v>
-      </c>
-      <c r="L166" t="s">
-        <v>521</v>
-      </c>
-      <c r="M166" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -10008,23 +10008,23 @@
       <c r="E167" t="s">
         <v>655</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>717</v>
       </c>
       <c r="H167" t="s">
+        <v>519</v>
+      </c>
+      <c r="I167" t="s">
+        <v>20</v>
+      </c>
+      <c r="K167" t="s">
+        <v>520</v>
+      </c>
+      <c r="L167" t="s">
+        <v>22</v>
+      </c>
+      <c r="M167" t="s">
         <v>657</v>
-      </c>
-      <c r="I167" t="s">
-        <v>520</v>
-      </c>
-      <c r="J167" t="s">
-        <v>21</v>
-      </c>
-      <c r="L167" t="s">
-        <v>521</v>
-      </c>
-      <c r="M167" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -10043,23 +10043,23 @@
       <c r="E168" t="s">
         <v>655</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>721</v>
       </c>
       <c r="H168" t="s">
+        <v>519</v>
+      </c>
+      <c r="I168" t="s">
+        <v>20</v>
+      </c>
+      <c r="K168" t="s">
+        <v>520</v>
+      </c>
+      <c r="L168" t="s">
+        <v>22</v>
+      </c>
+      <c r="M168" t="s">
         <v>657</v>
-      </c>
-      <c r="I168" t="s">
-        <v>520</v>
-      </c>
-      <c r="J168" t="s">
-        <v>21</v>
-      </c>
-      <c r="L168" t="s">
-        <v>521</v>
-      </c>
-      <c r="M168" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -10078,23 +10078,23 @@
       <c r="E169" t="s">
         <v>655</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>725</v>
       </c>
       <c r="H169" t="s">
+        <v>519</v>
+      </c>
+      <c r="I169" t="s">
+        <v>20</v>
+      </c>
+      <c r="K169" t="s">
+        <v>520</v>
+      </c>
+      <c r="L169" t="s">
+        <v>22</v>
+      </c>
+      <c r="M169" t="s">
         <v>657</v>
-      </c>
-      <c r="I169" t="s">
-        <v>520</v>
-      </c>
-      <c r="J169" t="s">
-        <v>21</v>
-      </c>
-      <c r="L169" t="s">
-        <v>521</v>
-      </c>
-      <c r="M169" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -10113,23 +10113,23 @@
       <c r="E170" t="s">
         <v>729</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>730</v>
       </c>
       <c r="H170" t="s">
         <v>731</v>
       </c>
       <c r="I170" t="s">
+        <v>20</v>
+      </c>
+      <c r="K170" t="s">
         <v>732</v>
       </c>
-      <c r="J170" t="s">
-        <v>21</v>
-      </c>
       <c r="L170" t="s">
+        <v>22</v>
+      </c>
+      <c r="M170" t="s">
         <v>733</v>
-      </c>
-      <c r="M170" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -10148,23 +10148,23 @@
       <c r="E171" t="s">
         <v>729</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>737</v>
       </c>
       <c r="H171" t="s">
         <v>731</v>
       </c>
       <c r="I171" t="s">
+        <v>20</v>
+      </c>
+      <c r="K171" t="s">
         <v>732</v>
       </c>
-      <c r="J171" t="s">
-        <v>21</v>
-      </c>
       <c r="L171" t="s">
+        <v>22</v>
+      </c>
+      <c r="M171" t="s">
         <v>733</v>
-      </c>
-      <c r="M171" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:13">
@@ -10183,23 +10183,23 @@
       <c r="E172" t="s">
         <v>729</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>741</v>
       </c>
       <c r="H172" t="s">
         <v>731</v>
       </c>
       <c r="I172" t="s">
+        <v>20</v>
+      </c>
+      <c r="K172" t="s">
         <v>732</v>
       </c>
-      <c r="J172" t="s">
-        <v>21</v>
-      </c>
       <c r="L172" t="s">
+        <v>22</v>
+      </c>
+      <c r="M172" t="s">
         <v>733</v>
-      </c>
-      <c r="M172" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -10218,23 +10218,23 @@
       <c r="E173" t="s">
         <v>729</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>745</v>
       </c>
       <c r="H173" t="s">
         <v>731</v>
       </c>
       <c r="I173" t="s">
+        <v>20</v>
+      </c>
+      <c r="K173" t="s">
         <v>732</v>
       </c>
-      <c r="J173" t="s">
-        <v>21</v>
-      </c>
       <c r="L173" t="s">
+        <v>22</v>
+      </c>
+      <c r="M173" t="s">
         <v>733</v>
-      </c>
-      <c r="M173" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -10253,23 +10253,23 @@
       <c r="E174" t="s">
         <v>729</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>749</v>
       </c>
       <c r="H174" t="s">
         <v>731</v>
       </c>
       <c r="I174" t="s">
+        <v>20</v>
+      </c>
+      <c r="K174" t="s">
         <v>732</v>
       </c>
-      <c r="J174" t="s">
-        <v>21</v>
-      </c>
       <c r="L174" t="s">
+        <v>22</v>
+      </c>
+      <c r="M174" t="s">
         <v>733</v>
-      </c>
-      <c r="M174" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -10288,23 +10288,23 @@
       <c r="E175" t="s">
         <v>729</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>753</v>
       </c>
       <c r="H175" t="s">
         <v>731</v>
       </c>
       <c r="I175" t="s">
+        <v>20</v>
+      </c>
+      <c r="K175" t="s">
         <v>732</v>
       </c>
-      <c r="J175" t="s">
-        <v>21</v>
-      </c>
       <c r="L175" t="s">
+        <v>22</v>
+      </c>
+      <c r="M175" t="s">
         <v>733</v>
-      </c>
-      <c r="M175" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -10323,23 +10323,23 @@
       <c r="E176" t="s">
         <v>729</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>757</v>
       </c>
       <c r="H176" t="s">
         <v>731</v>
       </c>
       <c r="I176" t="s">
+        <v>20</v>
+      </c>
+      <c r="K176" t="s">
         <v>732</v>
       </c>
-      <c r="J176" t="s">
-        <v>21</v>
-      </c>
       <c r="L176" t="s">
+        <v>22</v>
+      </c>
+      <c r="M176" t="s">
         <v>733</v>
-      </c>
-      <c r="M176" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -10358,23 +10358,23 @@
       <c r="E177" t="s">
         <v>729</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>761</v>
       </c>
       <c r="H177" t="s">
         <v>731</v>
       </c>
       <c r="I177" t="s">
+        <v>20</v>
+      </c>
+      <c r="K177" t="s">
         <v>732</v>
       </c>
-      <c r="J177" t="s">
-        <v>21</v>
-      </c>
       <c r="L177" t="s">
+        <v>22</v>
+      </c>
+      <c r="M177" t="s">
         <v>733</v>
-      </c>
-      <c r="M177" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -10393,23 +10393,23 @@
       <c r="E178" t="s">
         <v>729</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>765</v>
       </c>
       <c r="H178" t="s">
         <v>731</v>
       </c>
       <c r="I178" t="s">
+        <v>20</v>
+      </c>
+      <c r="K178" t="s">
         <v>732</v>
       </c>
-      <c r="J178" t="s">
-        <v>21</v>
-      </c>
       <c r="L178" t="s">
+        <v>22</v>
+      </c>
+      <c r="M178" t="s">
         <v>733</v>
-      </c>
-      <c r="M178" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -10428,23 +10428,23 @@
       <c r="E179" t="s">
         <v>729</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
         <v>769</v>
       </c>
       <c r="H179" t="s">
         <v>731</v>
       </c>
       <c r="I179" t="s">
+        <v>20</v>
+      </c>
+      <c r="K179" t="s">
         <v>732</v>
       </c>
-      <c r="J179" t="s">
-        <v>21</v>
-      </c>
       <c r="L179" t="s">
+        <v>22</v>
+      </c>
+      <c r="M179" t="s">
         <v>733</v>
-      </c>
-      <c r="M179" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -10463,23 +10463,23 @@
       <c r="E180" t="s">
         <v>773</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>774</v>
       </c>
       <c r="H180" t="s">
+        <v>731</v>
+      </c>
+      <c r="I180" t="s">
+        <v>20</v>
+      </c>
+      <c r="K180" t="s">
+        <v>732</v>
+      </c>
+      <c r="L180" t="s">
+        <v>22</v>
+      </c>
+      <c r="M180" t="s">
         <v>775</v>
-      </c>
-      <c r="I180" t="s">
-        <v>732</v>
-      </c>
-      <c r="J180" t="s">
-        <v>21</v>
-      </c>
-      <c r="L180" t="s">
-        <v>733</v>
-      </c>
-      <c r="M180" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -10505,22 +10505,22 @@
         <v>780</v>
       </c>
       <c r="H181" t="s">
+        <v>731</v>
+      </c>
+      <c r="I181" t="s">
+        <v>20</v>
+      </c>
+      <c r="J181" t="s">
+        <v>781</v>
+      </c>
+      <c r="K181" t="s">
+        <v>732</v>
+      </c>
+      <c r="L181" t="s">
+        <v>22</v>
+      </c>
+      <c r="M181" t="s">
         <v>775</v>
-      </c>
-      <c r="I181" t="s">
-        <v>732</v>
-      </c>
-      <c r="J181" t="s">
-        <v>21</v>
-      </c>
-      <c r="K181" t="s">
-        <v>781</v>
-      </c>
-      <c r="L181" t="s">
-        <v>733</v>
-      </c>
-      <c r="M181" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -10540,28 +10540,28 @@
         <v>773</v>
       </c>
       <c r="F182" t="s">
+        <v>779</v>
+      </c>
+      <c r="G182" t="s">
         <v>785</v>
       </c>
-      <c r="G182" t="s">
-        <v>780</v>
-      </c>
       <c r="H182" t="s">
+        <v>731</v>
+      </c>
+      <c r="I182" t="s">
+        <v>20</v>
+      </c>
+      <c r="J182" t="s">
+        <v>781</v>
+      </c>
+      <c r="K182" t="s">
+        <v>732</v>
+      </c>
+      <c r="L182" t="s">
+        <v>22</v>
+      </c>
+      <c r="M182" t="s">
         <v>775</v>
-      </c>
-      <c r="I182" t="s">
-        <v>732</v>
-      </c>
-      <c r="J182" t="s">
-        <v>21</v>
-      </c>
-      <c r="K182" t="s">
-        <v>781</v>
-      </c>
-      <c r="L182" t="s">
-        <v>733</v>
-      </c>
-      <c r="M182" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -10577,26 +10577,26 @@
       <c r="E183" t="s">
         <v>773</v>
       </c>
-      <c r="G183" t="s">
-        <v>780</v>
+      <c r="F183" t="s">
+        <v>779</v>
       </c>
       <c r="H183" t="s">
+        <v>731</v>
+      </c>
+      <c r="I183" t="s">
+        <v>20</v>
+      </c>
+      <c r="J183" t="s">
+        <v>781</v>
+      </c>
+      <c r="K183" t="s">
+        <v>732</v>
+      </c>
+      <c r="L183" t="s">
+        <v>22</v>
+      </c>
+      <c r="M183" t="s">
         <v>775</v>
-      </c>
-      <c r="I183" t="s">
-        <v>732</v>
-      </c>
-      <c r="J183" t="s">
-        <v>21</v>
-      </c>
-      <c r="K183" t="s">
-        <v>781</v>
-      </c>
-      <c r="L183" t="s">
-        <v>733</v>
-      </c>
-      <c r="M183" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -10615,23 +10615,23 @@
       <c r="E184" t="s">
         <v>773</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>791</v>
       </c>
       <c r="H184" t="s">
+        <v>731</v>
+      </c>
+      <c r="I184" t="s">
+        <v>20</v>
+      </c>
+      <c r="K184" t="s">
+        <v>732</v>
+      </c>
+      <c r="L184" t="s">
+        <v>22</v>
+      </c>
+      <c r="M184" t="s">
         <v>775</v>
-      </c>
-      <c r="I184" t="s">
-        <v>732</v>
-      </c>
-      <c r="J184" t="s">
-        <v>21</v>
-      </c>
-      <c r="L184" t="s">
-        <v>733</v>
-      </c>
-      <c r="M184" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -10650,23 +10650,23 @@
       <c r="E185" t="s">
         <v>773</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>795</v>
       </c>
       <c r="H185" t="s">
+        <v>731</v>
+      </c>
+      <c r="I185" t="s">
+        <v>20</v>
+      </c>
+      <c r="K185" t="s">
+        <v>732</v>
+      </c>
+      <c r="L185" t="s">
+        <v>22</v>
+      </c>
+      <c r="M185" t="s">
         <v>775</v>
-      </c>
-      <c r="I185" t="s">
-        <v>732</v>
-      </c>
-      <c r="J185" t="s">
-        <v>21</v>
-      </c>
-      <c r="L185" t="s">
-        <v>733</v>
-      </c>
-      <c r="M185" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -10685,23 +10685,23 @@
       <c r="E186" t="s">
         <v>773</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>799</v>
       </c>
       <c r="H186" t="s">
+        <v>731</v>
+      </c>
+      <c r="I186" t="s">
+        <v>20</v>
+      </c>
+      <c r="K186" t="s">
+        <v>732</v>
+      </c>
+      <c r="L186" t="s">
+        <v>22</v>
+      </c>
+      <c r="M186" t="s">
         <v>775</v>
-      </c>
-      <c r="I186" t="s">
-        <v>732</v>
-      </c>
-      <c r="J186" t="s">
-        <v>21</v>
-      </c>
-      <c r="L186" t="s">
-        <v>733</v>
-      </c>
-      <c r="M186" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -10720,23 +10720,23 @@
       <c r="E187" t="s">
         <v>773</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>803</v>
       </c>
       <c r="H187" t="s">
+        <v>731</v>
+      </c>
+      <c r="I187" t="s">
+        <v>20</v>
+      </c>
+      <c r="K187" t="s">
+        <v>732</v>
+      </c>
+      <c r="L187" t="s">
+        <v>22</v>
+      </c>
+      <c r="M187" t="s">
         <v>775</v>
-      </c>
-      <c r="I187" t="s">
-        <v>732</v>
-      </c>
-      <c r="J187" t="s">
-        <v>21</v>
-      </c>
-      <c r="L187" t="s">
-        <v>733</v>
-      </c>
-      <c r="M187" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -10755,23 +10755,23 @@
       <c r="E188" t="s">
         <v>773</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>807</v>
       </c>
       <c r="H188" t="s">
+        <v>731</v>
+      </c>
+      <c r="I188" t="s">
+        <v>20</v>
+      </c>
+      <c r="K188" t="s">
+        <v>732</v>
+      </c>
+      <c r="L188" t="s">
+        <v>22</v>
+      </c>
+      <c r="M188" t="s">
         <v>775</v>
-      </c>
-      <c r="I188" t="s">
-        <v>732</v>
-      </c>
-      <c r="J188" t="s">
-        <v>21</v>
-      </c>
-      <c r="L188" t="s">
-        <v>733</v>
-      </c>
-      <c r="M188" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -10790,23 +10790,23 @@
       <c r="E189" t="s">
         <v>773</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>811</v>
       </c>
       <c r="H189" t="s">
+        <v>731</v>
+      </c>
+      <c r="I189" t="s">
+        <v>20</v>
+      </c>
+      <c r="K189" t="s">
+        <v>732</v>
+      </c>
+      <c r="L189" t="s">
+        <v>22</v>
+      </c>
+      <c r="M189" t="s">
         <v>775</v>
-      </c>
-      <c r="I189" t="s">
-        <v>732</v>
-      </c>
-      <c r="J189" t="s">
-        <v>21</v>
-      </c>
-      <c r="L189" t="s">
-        <v>733</v>
-      </c>
-      <c r="M189" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -10825,23 +10825,23 @@
       <c r="E190" t="s">
         <v>773</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>815</v>
       </c>
       <c r="H190" t="s">
+        <v>731</v>
+      </c>
+      <c r="I190" t="s">
+        <v>20</v>
+      </c>
+      <c r="K190" t="s">
+        <v>732</v>
+      </c>
+      <c r="L190" t="s">
+        <v>22</v>
+      </c>
+      <c r="M190" t="s">
         <v>775</v>
-      </c>
-      <c r="I190" t="s">
-        <v>732</v>
-      </c>
-      <c r="J190" t="s">
-        <v>21</v>
-      </c>
-      <c r="L190" t="s">
-        <v>733</v>
-      </c>
-      <c r="M190" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -10860,23 +10860,23 @@
       <c r="E191" t="s">
         <v>773</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>819</v>
       </c>
       <c r="H191" t="s">
+        <v>731</v>
+      </c>
+      <c r="I191" t="s">
+        <v>20</v>
+      </c>
+      <c r="K191" t="s">
+        <v>732</v>
+      </c>
+      <c r="L191" t="s">
+        <v>22</v>
+      </c>
+      <c r="M191" t="s">
         <v>775</v>
-      </c>
-      <c r="I191" t="s">
-        <v>732</v>
-      </c>
-      <c r="J191" t="s">
-        <v>21</v>
-      </c>
-      <c r="L191" t="s">
-        <v>733</v>
-      </c>
-      <c r="M191" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -10895,23 +10895,23 @@
       <c r="E192" t="s">
         <v>773</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>823</v>
       </c>
       <c r="H192" t="s">
+        <v>731</v>
+      </c>
+      <c r="I192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K192" t="s">
+        <v>732</v>
+      </c>
+      <c r="L192" t="s">
+        <v>22</v>
+      </c>
+      <c r="M192" t="s">
         <v>775</v>
-      </c>
-      <c r="I192" t="s">
-        <v>732</v>
-      </c>
-      <c r="J192" t="s">
-        <v>21</v>
-      </c>
-      <c r="L192" t="s">
-        <v>733</v>
-      </c>
-      <c r="M192" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -10930,23 +10930,23 @@
       <c r="E193" t="s">
         <v>773</v>
       </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
         <v>827</v>
       </c>
       <c r="H193" t="s">
+        <v>731</v>
+      </c>
+      <c r="I193" t="s">
+        <v>20</v>
+      </c>
+      <c r="K193" t="s">
+        <v>732</v>
+      </c>
+      <c r="L193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M193" t="s">
         <v>775</v>
-      </c>
-      <c r="I193" t="s">
-        <v>732</v>
-      </c>
-      <c r="J193" t="s">
-        <v>21</v>
-      </c>
-      <c r="L193" t="s">
-        <v>733</v>
-      </c>
-      <c r="M193" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -10965,23 +10965,23 @@
       <c r="E194" t="s">
         <v>773</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>831</v>
       </c>
       <c r="H194" t="s">
+        <v>731</v>
+      </c>
+      <c r="I194" t="s">
+        <v>20</v>
+      </c>
+      <c r="K194" t="s">
+        <v>732</v>
+      </c>
+      <c r="L194" t="s">
+        <v>22</v>
+      </c>
+      <c r="M194" t="s">
         <v>775</v>
-      </c>
-      <c r="I194" t="s">
-        <v>732</v>
-      </c>
-      <c r="J194" t="s">
-        <v>21</v>
-      </c>
-      <c r="L194" t="s">
-        <v>733</v>
-      </c>
-      <c r="M194" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -11000,23 +11000,23 @@
       <c r="E195" t="s">
         <v>773</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>835</v>
       </c>
       <c r="H195" t="s">
+        <v>731</v>
+      </c>
+      <c r="I195" t="s">
+        <v>20</v>
+      </c>
+      <c r="K195" t="s">
+        <v>732</v>
+      </c>
+      <c r="L195" t="s">
+        <v>22</v>
+      </c>
+      <c r="M195" t="s">
         <v>775</v>
-      </c>
-      <c r="I195" t="s">
-        <v>732</v>
-      </c>
-      <c r="J195" t="s">
-        <v>21</v>
-      </c>
-      <c r="L195" t="s">
-        <v>733</v>
-      </c>
-      <c r="M195" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -11035,23 +11035,23 @@
       <c r="E196" t="s">
         <v>773</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>839</v>
       </c>
       <c r="H196" t="s">
+        <v>731</v>
+      </c>
+      <c r="I196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K196" t="s">
+        <v>732</v>
+      </c>
+      <c r="L196" t="s">
+        <v>22</v>
+      </c>
+      <c r="M196" t="s">
         <v>775</v>
-      </c>
-      <c r="I196" t="s">
-        <v>732</v>
-      </c>
-      <c r="J196" t="s">
-        <v>21</v>
-      </c>
-      <c r="L196" t="s">
-        <v>733</v>
-      </c>
-      <c r="M196" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -11070,23 +11070,23 @@
       <c r="E197" t="s">
         <v>843</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>844</v>
       </c>
       <c r="H197" t="s">
+        <v>731</v>
+      </c>
+      <c r="I197" t="s">
+        <v>20</v>
+      </c>
+      <c r="K197" t="s">
+        <v>732</v>
+      </c>
+      <c r="L197" t="s">
+        <v>22</v>
+      </c>
+      <c r="M197" t="s">
         <v>845</v>
-      </c>
-      <c r="I197" t="s">
-        <v>732</v>
-      </c>
-      <c r="J197" t="s">
-        <v>21</v>
-      </c>
-      <c r="L197" t="s">
-        <v>733</v>
-      </c>
-      <c r="M197" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -11105,23 +11105,23 @@
       <c r="E198" t="s">
         <v>843</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>849</v>
       </c>
       <c r="H198" t="s">
+        <v>731</v>
+      </c>
+      <c r="I198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K198" t="s">
+        <v>732</v>
+      </c>
+      <c r="L198" t="s">
+        <v>22</v>
+      </c>
+      <c r="M198" t="s">
         <v>845</v>
-      </c>
-      <c r="I198" t="s">
-        <v>732</v>
-      </c>
-      <c r="J198" t="s">
-        <v>21</v>
-      </c>
-      <c r="L198" t="s">
-        <v>733</v>
-      </c>
-      <c r="M198" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -11140,23 +11140,23 @@
       <c r="E199" t="s">
         <v>843</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>853</v>
       </c>
       <c r="H199" t="s">
+        <v>731</v>
+      </c>
+      <c r="I199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K199" t="s">
+        <v>732</v>
+      </c>
+      <c r="L199" t="s">
+        <v>22</v>
+      </c>
+      <c r="M199" t="s">
         <v>845</v>
-      </c>
-      <c r="I199" t="s">
-        <v>732</v>
-      </c>
-      <c r="J199" t="s">
-        <v>21</v>
-      </c>
-      <c r="L199" t="s">
-        <v>733</v>
-      </c>
-      <c r="M199" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -11175,23 +11175,23 @@
       <c r="E200" t="s">
         <v>843</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>857</v>
       </c>
       <c r="H200" t="s">
+        <v>731</v>
+      </c>
+      <c r="I200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K200" t="s">
+        <v>732</v>
+      </c>
+      <c r="L200" t="s">
+        <v>22</v>
+      </c>
+      <c r="M200" t="s">
         <v>845</v>
-      </c>
-      <c r="I200" t="s">
-        <v>732</v>
-      </c>
-      <c r="J200" t="s">
-        <v>21</v>
-      </c>
-      <c r="L200" t="s">
-        <v>733</v>
-      </c>
-      <c r="M200" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -11210,23 +11210,23 @@
       <c r="E201" t="s">
         <v>843</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>861</v>
       </c>
       <c r="H201" t="s">
+        <v>731</v>
+      </c>
+      <c r="I201" t="s">
+        <v>20</v>
+      </c>
+      <c r="K201" t="s">
+        <v>732</v>
+      </c>
+      <c r="L201" t="s">
+        <v>22</v>
+      </c>
+      <c r="M201" t="s">
         <v>845</v>
-      </c>
-      <c r="I201" t="s">
-        <v>732</v>
-      </c>
-      <c r="J201" t="s">
-        <v>21</v>
-      </c>
-      <c r="L201" t="s">
-        <v>733</v>
-      </c>
-      <c r="M201" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -11245,23 +11245,23 @@
       <c r="E202" t="s">
         <v>843</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>865</v>
       </c>
       <c r="H202" t="s">
+        <v>731</v>
+      </c>
+      <c r="I202" t="s">
+        <v>20</v>
+      </c>
+      <c r="K202" t="s">
+        <v>732</v>
+      </c>
+      <c r="L202" t="s">
+        <v>22</v>
+      </c>
+      <c r="M202" t="s">
         <v>845</v>
-      </c>
-      <c r="I202" t="s">
-        <v>732</v>
-      </c>
-      <c r="J202" t="s">
-        <v>21</v>
-      </c>
-      <c r="L202" t="s">
-        <v>733</v>
-      </c>
-      <c r="M202" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -11280,23 +11280,23 @@
       <c r="E203" t="s">
         <v>843</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
         <v>869</v>
       </c>
       <c r="H203" t="s">
+        <v>731</v>
+      </c>
+      <c r="I203" t="s">
+        <v>20</v>
+      </c>
+      <c r="K203" t="s">
+        <v>732</v>
+      </c>
+      <c r="L203" t="s">
+        <v>22</v>
+      </c>
+      <c r="M203" t="s">
         <v>845</v>
-      </c>
-      <c r="I203" t="s">
-        <v>732</v>
-      </c>
-      <c r="J203" t="s">
-        <v>21</v>
-      </c>
-      <c r="L203" t="s">
-        <v>733</v>
-      </c>
-      <c r="M203" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -11315,23 +11315,23 @@
       <c r="E204" t="s">
         <v>843</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>873</v>
       </c>
       <c r="H204" t="s">
+        <v>731</v>
+      </c>
+      <c r="I204" t="s">
+        <v>20</v>
+      </c>
+      <c r="K204" t="s">
+        <v>732</v>
+      </c>
+      <c r="L204" t="s">
+        <v>22</v>
+      </c>
+      <c r="M204" t="s">
         <v>845</v>
-      </c>
-      <c r="I204" t="s">
-        <v>732</v>
-      </c>
-      <c r="J204" t="s">
-        <v>21</v>
-      </c>
-      <c r="L204" t="s">
-        <v>733</v>
-      </c>
-      <c r="M204" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -11350,23 +11350,23 @@
       <c r="E205" t="s">
         <v>843</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>877</v>
       </c>
       <c r="H205" t="s">
+        <v>731</v>
+      </c>
+      <c r="I205" t="s">
+        <v>20</v>
+      </c>
+      <c r="K205" t="s">
+        <v>732</v>
+      </c>
+      <c r="L205" t="s">
+        <v>22</v>
+      </c>
+      <c r="M205" t="s">
         <v>845</v>
-      </c>
-      <c r="I205" t="s">
-        <v>732</v>
-      </c>
-      <c r="J205" t="s">
-        <v>21</v>
-      </c>
-      <c r="L205" t="s">
-        <v>733</v>
-      </c>
-      <c r="M205" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -11385,23 +11385,23 @@
       <c r="E206" t="s">
         <v>843</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>881</v>
       </c>
       <c r="H206" t="s">
+        <v>731</v>
+      </c>
+      <c r="I206" t="s">
+        <v>20</v>
+      </c>
+      <c r="K206" t="s">
+        <v>732</v>
+      </c>
+      <c r="L206" t="s">
+        <v>22</v>
+      </c>
+      <c r="M206" t="s">
         <v>845</v>
-      </c>
-      <c r="I206" t="s">
-        <v>732</v>
-      </c>
-      <c r="J206" t="s">
-        <v>21</v>
-      </c>
-      <c r="L206" t="s">
-        <v>733</v>
-      </c>
-      <c r="M206" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -11420,23 +11420,23 @@
       <c r="E207" t="s">
         <v>843</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>885</v>
       </c>
       <c r="H207" t="s">
+        <v>731</v>
+      </c>
+      <c r="I207" t="s">
+        <v>20</v>
+      </c>
+      <c r="K207" t="s">
+        <v>732</v>
+      </c>
+      <c r="L207" t="s">
+        <v>22</v>
+      </c>
+      <c r="M207" t="s">
         <v>845</v>
-      </c>
-      <c r="I207" t="s">
-        <v>732</v>
-      </c>
-      <c r="J207" t="s">
-        <v>21</v>
-      </c>
-      <c r="L207" t="s">
-        <v>733</v>
-      </c>
-      <c r="M207" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -11455,23 +11455,23 @@
       <c r="E208" t="s">
         <v>843</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
         <v>889</v>
       </c>
       <c r="H208" t="s">
+        <v>731</v>
+      </c>
+      <c r="I208" t="s">
+        <v>20</v>
+      </c>
+      <c r="K208" t="s">
+        <v>732</v>
+      </c>
+      <c r="L208" t="s">
+        <v>22</v>
+      </c>
+      <c r="M208" t="s">
         <v>845</v>
-      </c>
-      <c r="I208" t="s">
-        <v>732</v>
-      </c>
-      <c r="J208" t="s">
-        <v>21</v>
-      </c>
-      <c r="L208" t="s">
-        <v>733</v>
-      </c>
-      <c r="M208" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -11490,23 +11490,23 @@
       <c r="E209" t="s">
         <v>843</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>893</v>
       </c>
       <c r="H209" t="s">
+        <v>731</v>
+      </c>
+      <c r="I209" t="s">
+        <v>20</v>
+      </c>
+      <c r="K209" t="s">
+        <v>732</v>
+      </c>
+      <c r="L209" t="s">
+        <v>22</v>
+      </c>
+      <c r="M209" t="s">
         <v>845</v>
-      </c>
-      <c r="I209" t="s">
-        <v>732</v>
-      </c>
-      <c r="J209" t="s">
-        <v>21</v>
-      </c>
-      <c r="L209" t="s">
-        <v>733</v>
-      </c>
-      <c r="M209" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -11525,23 +11525,23 @@
       <c r="E210" t="s">
         <v>843</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>897</v>
       </c>
       <c r="H210" t="s">
+        <v>731</v>
+      </c>
+      <c r="I210" t="s">
+        <v>20</v>
+      </c>
+      <c r="K210" t="s">
+        <v>732</v>
+      </c>
+      <c r="L210" t="s">
+        <v>22</v>
+      </c>
+      <c r="M210" t="s">
         <v>845</v>
-      </c>
-      <c r="I210" t="s">
-        <v>732</v>
-      </c>
-      <c r="J210" t="s">
-        <v>21</v>
-      </c>
-      <c r="L210" t="s">
-        <v>733</v>
-      </c>
-      <c r="M210" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -11560,23 +11560,23 @@
       <c r="E211" t="s">
         <v>843</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>901</v>
       </c>
       <c r="H211" t="s">
+        <v>731</v>
+      </c>
+      <c r="I211" t="s">
+        <v>20</v>
+      </c>
+      <c r="K211" t="s">
+        <v>732</v>
+      </c>
+      <c r="L211" t="s">
+        <v>22</v>
+      </c>
+      <c r="M211" t="s">
         <v>845</v>
-      </c>
-      <c r="I211" t="s">
-        <v>732</v>
-      </c>
-      <c r="J211" t="s">
-        <v>21</v>
-      </c>
-      <c r="L211" t="s">
-        <v>733</v>
-      </c>
-      <c r="M211" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -11595,23 +11595,23 @@
       <c r="E212" t="s">
         <v>843</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>905</v>
       </c>
       <c r="H212" t="s">
+        <v>731</v>
+      </c>
+      <c r="I212" t="s">
+        <v>20</v>
+      </c>
+      <c r="K212" t="s">
+        <v>732</v>
+      </c>
+      <c r="L212" t="s">
+        <v>22</v>
+      </c>
+      <c r="M212" t="s">
         <v>845</v>
-      </c>
-      <c r="I212" t="s">
-        <v>732</v>
-      </c>
-      <c r="J212" t="s">
-        <v>21</v>
-      </c>
-      <c r="L212" t="s">
-        <v>733</v>
-      </c>
-      <c r="M212" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -11630,23 +11630,23 @@
       <c r="E213" t="s">
         <v>909</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>910</v>
       </c>
       <c r="H213" t="s">
+        <v>731</v>
+      </c>
+      <c r="I213" t="s">
+        <v>20</v>
+      </c>
+      <c r="K213" t="s">
+        <v>732</v>
+      </c>
+      <c r="L213" t="s">
+        <v>22</v>
+      </c>
+      <c r="M213" t="s">
         <v>911</v>
-      </c>
-      <c r="I213" t="s">
-        <v>732</v>
-      </c>
-      <c r="J213" t="s">
-        <v>21</v>
-      </c>
-      <c r="L213" t="s">
-        <v>733</v>
-      </c>
-      <c r="M213" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -11665,23 +11665,23 @@
       <c r="E214" t="s">
         <v>909</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>915</v>
       </c>
       <c r="H214" t="s">
+        <v>731</v>
+      </c>
+      <c r="I214" t="s">
+        <v>20</v>
+      </c>
+      <c r="K214" t="s">
+        <v>732</v>
+      </c>
+      <c r="L214" t="s">
+        <v>22</v>
+      </c>
+      <c r="M214" t="s">
         <v>911</v>
-      </c>
-      <c r="I214" t="s">
-        <v>732</v>
-      </c>
-      <c r="J214" t="s">
-        <v>21</v>
-      </c>
-      <c r="L214" t="s">
-        <v>733</v>
-      </c>
-      <c r="M214" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -11700,23 +11700,23 @@
       <c r="E215" t="s">
         <v>909</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>919</v>
       </c>
       <c r="H215" t="s">
+        <v>731</v>
+      </c>
+      <c r="I215" t="s">
+        <v>20</v>
+      </c>
+      <c r="K215" t="s">
+        <v>732</v>
+      </c>
+      <c r="L215" t="s">
+        <v>22</v>
+      </c>
+      <c r="M215" t="s">
         <v>911</v>
-      </c>
-      <c r="I215" t="s">
-        <v>732</v>
-      </c>
-      <c r="J215" t="s">
-        <v>21</v>
-      </c>
-      <c r="L215" t="s">
-        <v>733</v>
-      </c>
-      <c r="M215" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -11735,23 +11735,23 @@
       <c r="E216" t="s">
         <v>909</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>923</v>
       </c>
       <c r="H216" t="s">
+        <v>731</v>
+      </c>
+      <c r="I216" t="s">
+        <v>20</v>
+      </c>
+      <c r="K216" t="s">
+        <v>732</v>
+      </c>
+      <c r="L216" t="s">
+        <v>22</v>
+      </c>
+      <c r="M216" t="s">
         <v>911</v>
-      </c>
-      <c r="I216" t="s">
-        <v>732</v>
-      </c>
-      <c r="J216" t="s">
-        <v>21</v>
-      </c>
-      <c r="L216" t="s">
-        <v>733</v>
-      </c>
-      <c r="M216" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -11770,23 +11770,23 @@
       <c r="E217" t="s">
         <v>909</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>927</v>
       </c>
       <c r="H217" t="s">
+        <v>731</v>
+      </c>
+      <c r="I217" t="s">
+        <v>20</v>
+      </c>
+      <c r="K217" t="s">
+        <v>732</v>
+      </c>
+      <c r="L217" t="s">
+        <v>22</v>
+      </c>
+      <c r="M217" t="s">
         <v>911</v>
-      </c>
-      <c r="I217" t="s">
-        <v>732</v>
-      </c>
-      <c r="J217" t="s">
-        <v>21</v>
-      </c>
-      <c r="L217" t="s">
-        <v>733</v>
-      </c>
-      <c r="M217" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -11805,23 +11805,23 @@
       <c r="E218" t="s">
         <v>909</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>931</v>
       </c>
       <c r="H218" t="s">
+        <v>731</v>
+      </c>
+      <c r="I218" t="s">
+        <v>20</v>
+      </c>
+      <c r="K218" t="s">
+        <v>732</v>
+      </c>
+      <c r="L218" t="s">
+        <v>22</v>
+      </c>
+      <c r="M218" t="s">
         <v>911</v>
-      </c>
-      <c r="I218" t="s">
-        <v>732</v>
-      </c>
-      <c r="J218" t="s">
-        <v>21</v>
-      </c>
-      <c r="L218" t="s">
-        <v>733</v>
-      </c>
-      <c r="M218" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -11840,23 +11840,23 @@
       <c r="E219" t="s">
         <v>909</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>935</v>
       </c>
       <c r="H219" t="s">
+        <v>731</v>
+      </c>
+      <c r="I219" t="s">
+        <v>20</v>
+      </c>
+      <c r="K219" t="s">
+        <v>732</v>
+      </c>
+      <c r="L219" t="s">
+        <v>22</v>
+      </c>
+      <c r="M219" t="s">
         <v>911</v>
-      </c>
-      <c r="I219" t="s">
-        <v>732</v>
-      </c>
-      <c r="J219" t="s">
-        <v>21</v>
-      </c>
-      <c r="L219" t="s">
-        <v>733</v>
-      </c>
-      <c r="M219" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -11875,23 +11875,23 @@
       <c r="E220" t="s">
         <v>909</v>
       </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>939</v>
       </c>
       <c r="H220" t="s">
+        <v>731</v>
+      </c>
+      <c r="I220" t="s">
+        <v>20</v>
+      </c>
+      <c r="K220" t="s">
+        <v>732</v>
+      </c>
+      <c r="L220" t="s">
+        <v>22</v>
+      </c>
+      <c r="M220" t="s">
         <v>911</v>
-      </c>
-      <c r="I220" t="s">
-        <v>732</v>
-      </c>
-      <c r="J220" t="s">
-        <v>21</v>
-      </c>
-      <c r="L220" t="s">
-        <v>733</v>
-      </c>
-      <c r="M220" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -11910,23 +11910,23 @@
       <c r="E221" t="s">
         <v>909</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>943</v>
       </c>
       <c r="H221" t="s">
+        <v>731</v>
+      </c>
+      <c r="I221" t="s">
+        <v>20</v>
+      </c>
+      <c r="K221" t="s">
+        <v>732</v>
+      </c>
+      <c r="L221" t="s">
+        <v>22</v>
+      </c>
+      <c r="M221" t="s">
         <v>911</v>
-      </c>
-      <c r="I221" t="s">
-        <v>732</v>
-      </c>
-      <c r="J221" t="s">
-        <v>21</v>
-      </c>
-      <c r="L221" t="s">
-        <v>733</v>
-      </c>
-      <c r="M221" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -11945,23 +11945,23 @@
       <c r="E222" t="s">
         <v>947</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>948</v>
       </c>
       <c r="H222" t="s">
         <v>949</v>
       </c>
       <c r="I222" t="s">
+        <v>20</v>
+      </c>
+      <c r="K222" t="s">
         <v>950</v>
       </c>
-      <c r="J222" t="s">
-        <v>21</v>
-      </c>
       <c r="L222" t="s">
+        <v>22</v>
+      </c>
+      <c r="M222" t="s">
         <v>951</v>
-      </c>
-      <c r="M222" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -11980,23 +11980,23 @@
       <c r="E223" t="s">
         <v>947</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>955</v>
       </c>
       <c r="H223" t="s">
         <v>949</v>
       </c>
       <c r="I223" t="s">
+        <v>20</v>
+      </c>
+      <c r="K223" t="s">
         <v>950</v>
       </c>
-      <c r="J223" t="s">
-        <v>21</v>
-      </c>
       <c r="L223" t="s">
+        <v>22</v>
+      </c>
+      <c r="M223" t="s">
         <v>951</v>
-      </c>
-      <c r="M223" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -12015,23 +12015,23 @@
       <c r="E224" t="s">
         <v>947</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>959</v>
       </c>
       <c r="H224" t="s">
         <v>949</v>
       </c>
       <c r="I224" t="s">
+        <v>20</v>
+      </c>
+      <c r="K224" t="s">
         <v>950</v>
       </c>
-      <c r="J224" t="s">
-        <v>21</v>
-      </c>
       <c r="L224" t="s">
+        <v>22</v>
+      </c>
+      <c r="M224" t="s">
         <v>951</v>
-      </c>
-      <c r="M224" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -12050,23 +12050,23 @@
       <c r="E225" t="s">
         <v>947</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>963</v>
       </c>
       <c r="H225" t="s">
         <v>949</v>
       </c>
       <c r="I225" t="s">
+        <v>20</v>
+      </c>
+      <c r="K225" t="s">
         <v>950</v>
       </c>
-      <c r="J225" t="s">
-        <v>21</v>
-      </c>
       <c r="L225" t="s">
+        <v>22</v>
+      </c>
+      <c r="M225" t="s">
         <v>951</v>
-      </c>
-      <c r="M225" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -12085,23 +12085,23 @@
       <c r="E226" t="s">
         <v>947</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>967</v>
       </c>
       <c r="H226" t="s">
         <v>949</v>
       </c>
       <c r="I226" t="s">
+        <v>20</v>
+      </c>
+      <c r="K226" t="s">
         <v>950</v>
       </c>
-      <c r="J226" t="s">
-        <v>21</v>
-      </c>
       <c r="L226" t="s">
+        <v>22</v>
+      </c>
+      <c r="M226" t="s">
         <v>951</v>
-      </c>
-      <c r="M226" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -12120,23 +12120,23 @@
       <c r="E227" t="s">
         <v>947</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>971</v>
       </c>
       <c r="H227" t="s">
         <v>949</v>
       </c>
       <c r="I227" t="s">
+        <v>20</v>
+      </c>
+      <c r="K227" t="s">
         <v>950</v>
       </c>
-      <c r="J227" t="s">
-        <v>21</v>
-      </c>
       <c r="L227" t="s">
+        <v>22</v>
+      </c>
+      <c r="M227" t="s">
         <v>951</v>
-      </c>
-      <c r="M227" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -12155,23 +12155,23 @@
       <c r="E228" t="s">
         <v>975</v>
       </c>
-      <c r="F228" t="s">
+      <c r="G228" t="s">
         <v>976</v>
       </c>
       <c r="H228" t="s">
+        <v>949</v>
+      </c>
+      <c r="I228" t="s">
+        <v>20</v>
+      </c>
+      <c r="K228" t="s">
+        <v>950</v>
+      </c>
+      <c r="L228" t="s">
+        <v>22</v>
+      </c>
+      <c r="M228" t="s">
         <v>977</v>
-      </c>
-      <c r="I228" t="s">
-        <v>950</v>
-      </c>
-      <c r="J228" t="s">
-        <v>21</v>
-      </c>
-      <c r="L228" t="s">
-        <v>951</v>
-      </c>
-      <c r="M228" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -12190,23 +12190,23 @@
       <c r="E229" t="s">
         <v>975</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>981</v>
       </c>
       <c r="H229" t="s">
+        <v>949</v>
+      </c>
+      <c r="I229" t="s">
+        <v>20</v>
+      </c>
+      <c r="K229" t="s">
+        <v>950</v>
+      </c>
+      <c r="L229" t="s">
+        <v>22</v>
+      </c>
+      <c r="M229" t="s">
         <v>977</v>
-      </c>
-      <c r="I229" t="s">
-        <v>950</v>
-      </c>
-      <c r="J229" t="s">
-        <v>21</v>
-      </c>
-      <c r="L229" t="s">
-        <v>951</v>
-      </c>
-      <c r="M229" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -12225,23 +12225,23 @@
       <c r="E230" t="s">
         <v>975</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>985</v>
       </c>
       <c r="H230" t="s">
+        <v>949</v>
+      </c>
+      <c r="I230" t="s">
+        <v>20</v>
+      </c>
+      <c r="K230" t="s">
+        <v>950</v>
+      </c>
+      <c r="L230" t="s">
+        <v>22</v>
+      </c>
+      <c r="M230" t="s">
         <v>977</v>
-      </c>
-      <c r="I230" t="s">
-        <v>950</v>
-      </c>
-      <c r="J230" t="s">
-        <v>21</v>
-      </c>
-      <c r="L230" t="s">
-        <v>951</v>
-      </c>
-      <c r="M230" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -12260,23 +12260,23 @@
       <c r="E231" t="s">
         <v>975</v>
       </c>
-      <c r="F231" t="s">
+      <c r="G231" t="s">
         <v>989</v>
       </c>
       <c r="H231" t="s">
+        <v>949</v>
+      </c>
+      <c r="I231" t="s">
+        <v>20</v>
+      </c>
+      <c r="K231" t="s">
+        <v>950</v>
+      </c>
+      <c r="L231" t="s">
+        <v>22</v>
+      </c>
+      <c r="M231" t="s">
         <v>977</v>
-      </c>
-      <c r="I231" t="s">
-        <v>950</v>
-      </c>
-      <c r="J231" t="s">
-        <v>21</v>
-      </c>
-      <c r="L231" t="s">
-        <v>951</v>
-      </c>
-      <c r="M231" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -12295,23 +12295,23 @@
       <c r="E232" t="s">
         <v>975</v>
       </c>
-      <c r="F232" t="s">
+      <c r="G232" t="s">
         <v>993</v>
       </c>
       <c r="H232" t="s">
+        <v>949</v>
+      </c>
+      <c r="I232" t="s">
+        <v>20</v>
+      </c>
+      <c r="K232" t="s">
+        <v>950</v>
+      </c>
+      <c r="L232" t="s">
+        <v>22</v>
+      </c>
+      <c r="M232" t="s">
         <v>977</v>
-      </c>
-      <c r="I232" t="s">
-        <v>950</v>
-      </c>
-      <c r="J232" t="s">
-        <v>21</v>
-      </c>
-      <c r="L232" t="s">
-        <v>951</v>
-      </c>
-      <c r="M232" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -12330,23 +12330,23 @@
       <c r="E233" t="s">
         <v>997</v>
       </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
         <v>998</v>
       </c>
       <c r="H233" t="s">
+        <v>949</v>
+      </c>
+      <c r="I233" t="s">
+        <v>20</v>
+      </c>
+      <c r="K233" t="s">
+        <v>950</v>
+      </c>
+      <c r="L233" t="s">
+        <v>22</v>
+      </c>
+      <c r="M233" t="s">
         <v>999</v>
-      </c>
-      <c r="I233" t="s">
-        <v>950</v>
-      </c>
-      <c r="J233" t="s">
-        <v>21</v>
-      </c>
-      <c r="L233" t="s">
-        <v>951</v>
-      </c>
-      <c r="M233" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -12365,23 +12365,23 @@
       <c r="E234" t="s">
         <v>997</v>
       </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
         <v>1003</v>
       </c>
       <c r="H234" t="s">
+        <v>949</v>
+      </c>
+      <c r="I234" t="s">
+        <v>20</v>
+      </c>
+      <c r="K234" t="s">
+        <v>950</v>
+      </c>
+      <c r="L234" t="s">
+        <v>22</v>
+      </c>
+      <c r="M234" t="s">
         <v>999</v>
-      </c>
-      <c r="I234" t="s">
-        <v>950</v>
-      </c>
-      <c r="J234" t="s">
-        <v>21</v>
-      </c>
-      <c r="L234" t="s">
-        <v>951</v>
-      </c>
-      <c r="M234" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -12400,23 +12400,23 @@
       <c r="E235" t="s">
         <v>997</v>
       </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
         <v>1007</v>
       </c>
       <c r="H235" t="s">
+        <v>949</v>
+      </c>
+      <c r="I235" t="s">
+        <v>20</v>
+      </c>
+      <c r="K235" t="s">
+        <v>950</v>
+      </c>
+      <c r="L235" t="s">
+        <v>22</v>
+      </c>
+      <c r="M235" t="s">
         <v>999</v>
-      </c>
-      <c r="I235" t="s">
-        <v>950</v>
-      </c>
-      <c r="J235" t="s">
-        <v>21</v>
-      </c>
-      <c r="L235" t="s">
-        <v>951</v>
-      </c>
-      <c r="M235" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -12435,23 +12435,23 @@
       <c r="E236" t="s">
         <v>997</v>
       </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
         <v>1011</v>
       </c>
       <c r="H236" t="s">
+        <v>949</v>
+      </c>
+      <c r="I236" t="s">
+        <v>20</v>
+      </c>
+      <c r="K236" t="s">
+        <v>950</v>
+      </c>
+      <c r="L236" t="s">
+        <v>22</v>
+      </c>
+      <c r="M236" t="s">
         <v>999</v>
-      </c>
-      <c r="I236" t="s">
-        <v>950</v>
-      </c>
-      <c r="J236" t="s">
-        <v>21</v>
-      </c>
-      <c r="L236" t="s">
-        <v>951</v>
-      </c>
-      <c r="M236" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -12470,23 +12470,23 @@
       <c r="E237" t="s">
         <v>997</v>
       </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>1015</v>
       </c>
       <c r="H237" t="s">
+        <v>949</v>
+      </c>
+      <c r="I237" t="s">
+        <v>20</v>
+      </c>
+      <c r="K237" t="s">
+        <v>950</v>
+      </c>
+      <c r="L237" t="s">
+        <v>22</v>
+      </c>
+      <c r="M237" t="s">
         <v>999</v>
-      </c>
-      <c r="I237" t="s">
-        <v>950</v>
-      </c>
-      <c r="J237" t="s">
-        <v>21</v>
-      </c>
-      <c r="L237" t="s">
-        <v>951</v>
-      </c>
-      <c r="M237" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -12505,23 +12505,23 @@
       <c r="E238" t="s">
         <v>997</v>
       </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
         <v>1019</v>
       </c>
       <c r="H238" t="s">
+        <v>949</v>
+      </c>
+      <c r="I238" t="s">
+        <v>20</v>
+      </c>
+      <c r="K238" t="s">
+        <v>950</v>
+      </c>
+      <c r="L238" t="s">
+        <v>22</v>
+      </c>
+      <c r="M238" t="s">
         <v>999</v>
-      </c>
-      <c r="I238" t="s">
-        <v>950</v>
-      </c>
-      <c r="J238" t="s">
-        <v>21</v>
-      </c>
-      <c r="L238" t="s">
-        <v>951</v>
-      </c>
-      <c r="M238" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -12540,23 +12540,23 @@
       <c r="E239" t="s">
         <v>997</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>1023</v>
       </c>
       <c r="H239" t="s">
+        <v>949</v>
+      </c>
+      <c r="I239" t="s">
+        <v>20</v>
+      </c>
+      <c r="K239" t="s">
+        <v>950</v>
+      </c>
+      <c r="L239" t="s">
+        <v>22</v>
+      </c>
+      <c r="M239" t="s">
         <v>999</v>
-      </c>
-      <c r="I239" t="s">
-        <v>950</v>
-      </c>
-      <c r="J239" t="s">
-        <v>21</v>
-      </c>
-      <c r="L239" t="s">
-        <v>951</v>
-      </c>
-      <c r="M239" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -12575,23 +12575,23 @@
       <c r="E240" t="s">
         <v>997</v>
       </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>1027</v>
       </c>
       <c r="H240" t="s">
+        <v>949</v>
+      </c>
+      <c r="I240" t="s">
+        <v>20</v>
+      </c>
+      <c r="K240" t="s">
+        <v>950</v>
+      </c>
+      <c r="L240" t="s">
+        <v>22</v>
+      </c>
+      <c r="M240" t="s">
         <v>999</v>
-      </c>
-      <c r="I240" t="s">
-        <v>950</v>
-      </c>
-      <c r="J240" t="s">
-        <v>21</v>
-      </c>
-      <c r="L240" t="s">
-        <v>951</v>
-      </c>
-      <c r="M240" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -12610,23 +12610,23 @@
       <c r="E241" t="s">
         <v>1031</v>
       </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>1032</v>
       </c>
       <c r="H241" t="s">
+        <v>949</v>
+      </c>
+      <c r="I241" t="s">
+        <v>20</v>
+      </c>
+      <c r="K241" t="s">
+        <v>950</v>
+      </c>
+      <c r="L241" t="s">
+        <v>22</v>
+      </c>
+      <c r="M241" t="s">
         <v>1033</v>
-      </c>
-      <c r="I241" t="s">
-        <v>950</v>
-      </c>
-      <c r="J241" t="s">
-        <v>21</v>
-      </c>
-      <c r="L241" t="s">
-        <v>951</v>
-      </c>
-      <c r="M241" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -12645,23 +12645,23 @@
       <c r="E242" t="s">
         <v>1031</v>
       </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>1037</v>
       </c>
       <c r="H242" t="s">
+        <v>949</v>
+      </c>
+      <c r="I242" t="s">
+        <v>20</v>
+      </c>
+      <c r="K242" t="s">
+        <v>950</v>
+      </c>
+      <c r="L242" t="s">
+        <v>22</v>
+      </c>
+      <c r="M242" t="s">
         <v>1033</v>
-      </c>
-      <c r="I242" t="s">
-        <v>950</v>
-      </c>
-      <c r="J242" t="s">
-        <v>21</v>
-      </c>
-      <c r="L242" t="s">
-        <v>951</v>
-      </c>
-      <c r="M242" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -12680,23 +12680,23 @@
       <c r="E243" t="s">
         <v>1031</v>
       </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>1041</v>
       </c>
       <c r="H243" t="s">
+        <v>949</v>
+      </c>
+      <c r="I243" t="s">
+        <v>20</v>
+      </c>
+      <c r="K243" t="s">
+        <v>950</v>
+      </c>
+      <c r="L243" t="s">
+        <v>22</v>
+      </c>
+      <c r="M243" t="s">
         <v>1033</v>
-      </c>
-      <c r="I243" t="s">
-        <v>950</v>
-      </c>
-      <c r="J243" t="s">
-        <v>21</v>
-      </c>
-      <c r="L243" t="s">
-        <v>951</v>
-      </c>
-      <c r="M243" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -12715,23 +12715,23 @@
       <c r="E244" t="s">
         <v>1031</v>
       </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>1045</v>
       </c>
       <c r="H244" t="s">
+        <v>949</v>
+      </c>
+      <c r="I244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K244" t="s">
+        <v>950</v>
+      </c>
+      <c r="L244" t="s">
+        <v>22</v>
+      </c>
+      <c r="M244" t="s">
         <v>1033</v>
-      </c>
-      <c r="I244" t="s">
-        <v>950</v>
-      </c>
-      <c r="J244" t="s">
-        <v>21</v>
-      </c>
-      <c r="L244" t="s">
-        <v>951</v>
-      </c>
-      <c r="M244" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -12750,23 +12750,23 @@
       <c r="E245" t="s">
         <v>1031</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>1049</v>
       </c>
       <c r="H245" t="s">
+        <v>949</v>
+      </c>
+      <c r="I245" t="s">
+        <v>20</v>
+      </c>
+      <c r="K245" t="s">
+        <v>950</v>
+      </c>
+      <c r="L245" t="s">
+        <v>22</v>
+      </c>
+      <c r="M245" t="s">
         <v>1033</v>
-      </c>
-      <c r="I245" t="s">
-        <v>950</v>
-      </c>
-      <c r="J245" t="s">
-        <v>21</v>
-      </c>
-      <c r="L245" t="s">
-        <v>951</v>
-      </c>
-      <c r="M245" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -12785,23 +12785,23 @@
       <c r="E246" t="s">
         <v>1031</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>1053</v>
       </c>
       <c r="H246" t="s">
+        <v>949</v>
+      </c>
+      <c r="I246" t="s">
+        <v>20</v>
+      </c>
+      <c r="K246" t="s">
+        <v>950</v>
+      </c>
+      <c r="L246" t="s">
+        <v>22</v>
+      </c>
+      <c r="M246" t="s">
         <v>1033</v>
-      </c>
-      <c r="I246" t="s">
-        <v>950</v>
-      </c>
-      <c r="J246" t="s">
-        <v>21</v>
-      </c>
-      <c r="L246" t="s">
-        <v>951</v>
-      </c>
-      <c r="M246" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -12820,23 +12820,23 @@
       <c r="E247" t="s">
         <v>1031</v>
       </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
         <v>1057</v>
       </c>
       <c r="H247" t="s">
+        <v>949</v>
+      </c>
+      <c r="I247" t="s">
+        <v>20</v>
+      </c>
+      <c r="K247" t="s">
+        <v>950</v>
+      </c>
+      <c r="L247" t="s">
+        <v>22</v>
+      </c>
+      <c r="M247" t="s">
         <v>1033</v>
-      </c>
-      <c r="I247" t="s">
-        <v>950</v>
-      </c>
-      <c r="J247" t="s">
-        <v>21</v>
-      </c>
-      <c r="L247" t="s">
-        <v>951</v>
-      </c>
-      <c r="M247" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -12855,23 +12855,23 @@
       <c r="E248" t="s">
         <v>1031</v>
       </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
         <v>1061</v>
       </c>
       <c r="H248" t="s">
+        <v>949</v>
+      </c>
+      <c r="I248" t="s">
+        <v>20</v>
+      </c>
+      <c r="K248" t="s">
+        <v>950</v>
+      </c>
+      <c r="L248" t="s">
+        <v>22</v>
+      </c>
+      <c r="M248" t="s">
         <v>1033</v>
-      </c>
-      <c r="I248" t="s">
-        <v>950</v>
-      </c>
-      <c r="J248" t="s">
-        <v>21</v>
-      </c>
-      <c r="L248" t="s">
-        <v>951</v>
-      </c>
-      <c r="M248" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -12890,23 +12890,23 @@
       <c r="E249" t="s">
         <v>1031</v>
       </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
         <v>1065</v>
       </c>
       <c r="H249" t="s">
+        <v>949</v>
+      </c>
+      <c r="I249" t="s">
+        <v>20</v>
+      </c>
+      <c r="K249" t="s">
+        <v>950</v>
+      </c>
+      <c r="L249" t="s">
+        <v>22</v>
+      </c>
+      <c r="M249" t="s">
         <v>1033</v>
-      </c>
-      <c r="I249" t="s">
-        <v>950</v>
-      </c>
-      <c r="J249" t="s">
-        <v>21</v>
-      </c>
-      <c r="L249" t="s">
-        <v>951</v>
-      </c>
-      <c r="M249" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -12925,23 +12925,23 @@
       <c r="E250" t="s">
         <v>1031</v>
       </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
         <v>1069</v>
       </c>
       <c r="H250" t="s">
+        <v>949</v>
+      </c>
+      <c r="I250" t="s">
+        <v>20</v>
+      </c>
+      <c r="K250" t="s">
+        <v>950</v>
+      </c>
+      <c r="L250" t="s">
+        <v>22</v>
+      </c>
+      <c r="M250" t="s">
         <v>1033</v>
-      </c>
-      <c r="I250" t="s">
-        <v>950</v>
-      </c>
-      <c r="J250" t="s">
-        <v>21</v>
-      </c>
-      <c r="L250" t="s">
-        <v>951</v>
-      </c>
-      <c r="M250" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,36 +25,36 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-name</t>
   </si>
   <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -64,30 +64,30 @@
     <t>active</t>
   </si>
   <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -169,21 +169,21 @@
     <t>IO</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -445,15 +445,15 @@
     <t>AO</t>
   </si>
   <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>Middle Africa</t>
   </si>
   <si>
     <t>AGO</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -559,15 +559,15 @@
     <t>BW</t>
   </si>
   <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>Southern Africa</t>
   </si>
   <si>
     <t>BWA</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -625,15 +625,15 @@
     <t>BJ</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>Western Africa</t>
   </si>
   <si>
     <t>BEN</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -832,30 +832,30 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
     <t>019</t>
   </si>
   <si>
-    <t>AI</t>
+    <t>Americas</t>
   </si>
   <si>
     <t>419</t>
   </si>
   <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>AIA</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -1189,15 +1189,15 @@
     <t>BZ</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>Central America</t>
   </si>
   <si>
     <t>BLZ</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -1291,15 +1291,15 @@
     <t>AR</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>South America</t>
   </si>
   <si>
     <t>ARG</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1489,15 +1489,15 @@
     <t>BM</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
+    <t>BMU</t>
+  </si>
+  <si>
     <t>021</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
-    <t>BMU</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1564,24 +1564,24 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>142</t>
   </si>
   <si>
-    <t>KZ</t>
+    <t>Asia</t>
   </si>
   <si>
     <t>143</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>KAZ</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1639,15 +1639,15 @@
     <t>CN</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
-    <t>CHN</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1729,15 +1729,15 @@
     <t>BN</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
+    <t>BRN</t>
+  </si>
+  <si>
     <t>035</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
-    <t>BRN</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1867,15 +1867,15 @@
     <t>AF</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
+    <t>AFG</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
-    <t>AFG</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1981,15 +1981,15 @@
     <t>AM</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
-    <t>ARM</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -2200,24 +2200,24 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>BY</t>
+    <t>Europe</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2335,15 +2335,15 @@
     <t>AX</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
+    <t>ALA</t>
+  </si>
+  <si>
     <t>154</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
-    <t>ALA</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
@@ -2353,15 +2353,15 @@
     <t>GG</t>
   </si>
   <si>
+    <t>830</t>
+  </si>
+  <si>
     <t>Channel Islands</t>
   </si>
   <si>
     <t>GGY</t>
   </si>
   <si>
-    <t>830</t>
-  </si>
-  <si>
     <t>832</t>
   </si>
   <si>
@@ -2545,15 +2545,15 @@
     <t>AL</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
     <t>039</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2743,15 +2743,15 @@
     <t>AT</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2854,24 +2854,24 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
     <t>009</t>
   </si>
   <si>
-    <t>AU</t>
+    <t>Oceania</t>
   </si>
   <si>
     <t>053</t>
   </si>
   <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
     <t>162</t>
   </si>
   <si>
@@ -2941,15 +2941,15 @@
     <t>FJ</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
+    <t>FJI</t>
+  </si>
+  <si>
     <t>054</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
-    <t>FJI</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -3007,15 +3007,15 @@
     <t>GU</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
+    <t>GUM</t>
+  </si>
+  <si>
     <t>057</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
-    <t>GUM</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -3109,13 +3109,13 @@
     <t>AS</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
+    <t>ASM</t>
+  </si>
+  <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
-  </si>
-  <si>
-    <t>ASM</t>
   </si>
   <si>
     <t>184</t>
@@ -3618,16 +3618,16 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
       <c r="M2" t="s">
@@ -3645,24 +3645,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
       <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
@@ -3680,24 +3680,24 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
       <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
@@ -3715,24 +3715,24 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
       <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
         <v>22</v>
       </c>
       <c r="M5" t="s">
@@ -3750,24 +3750,24 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
         <v>20</v>
       </c>
-      <c r="J6" t="s">
-        <v>39</v>
-      </c>
       <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
         <v>22</v>
       </c>
       <c r="M6" t="s">
@@ -3785,24 +3785,24 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
       <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
         <v>22</v>
       </c>
       <c r="M7" t="s">
@@ -3820,24 +3820,24 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
         <v>20</v>
       </c>
-      <c r="J8" t="s">
-        <v>47</v>
-      </c>
       <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
         <v>22</v>
       </c>
       <c r="M8" t="s">
@@ -3855,28 +3855,28 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>55</v>
@@ -3896,28 +3896,28 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
         <v>55</v>
@@ -3937,28 +3937,28 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="K11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>55</v>
@@ -3978,28 +3978,28 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I12" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
         <v>55</v>
@@ -4019,28 +4019,28 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
         <v>55</v>
@@ -4060,28 +4060,28 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="J14" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L14" t="s">
         <v>55</v>
@@ -4101,28 +4101,28 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I15" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
         <v>55</v>
@@ -4142,28 +4142,28 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I16" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L16" t="s">
         <v>55</v>
@@ -4183,28 +4183,28 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I17" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
@@ -4224,28 +4224,28 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L18" t="s">
         <v>55</v>
@@ -4265,28 +4265,28 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L19" t="s">
         <v>55</v>
@@ -4306,28 +4306,28 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I20" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
         <v>55</v>
@@ -4347,28 +4347,28 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L21" t="s">
         <v>55</v>
@@ -4388,28 +4388,28 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I22" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L22" t="s">
         <v>55</v>
@@ -4429,28 +4429,28 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I23" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="J23" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" t="s">
         <v>55</v>
@@ -4470,28 +4470,28 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="J24" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L24" t="s">
         <v>55</v>
@@ -4511,28 +4511,28 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
         <v>55</v>
@@ -4552,28 +4552,28 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
         <v>55</v>
@@ -4593,28 +4593,28 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I27" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="J27" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
         <v>55</v>
@@ -4634,28 +4634,28 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I28" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="J28" t="s">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L28" t="s">
         <v>55</v>
@@ -4675,28 +4675,28 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I29" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="J29" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L29" t="s">
         <v>55</v>
@@ -4716,28 +4716,28 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I30" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L30" t="s">
         <v>55</v>
@@ -4757,31 +4757,31 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H31" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J31" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M31" t="s">
         <v>23</v>
@@ -4798,31 +4798,31 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J32" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M32" t="s">
         <v>23</v>
@@ -4839,31 +4839,31 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I33" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="J33" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M33" t="s">
         <v>23</v>
@@ -4880,31 +4880,31 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H34" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I34" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="J34" t="s">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M34" t="s">
         <v>23</v>
@@ -4921,31 +4921,31 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H35" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I35" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="J35" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L35" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M35" t="s">
         <v>23</v>
@@ -4962,31 +4962,31 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H36" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I36" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M36" t="s">
         <v>23</v>
@@ -5003,31 +5003,31 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I37" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="J37" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L37" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M37" t="s">
         <v>23</v>
@@ -5044,31 +5044,31 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H38" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -5085,31 +5085,31 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I39" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="J39" t="s">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -5126,31 +5126,31 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H40" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="I40" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J40" t="s">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L40" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -5167,31 +5167,31 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H41" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="I41" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J41" t="s">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L41" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -5208,31 +5208,31 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F42" t="s">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H42" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="I42" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="J42" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L42" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -5249,31 +5249,31 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F43" t="s">
-        <v>194</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H43" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="I43" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J43" t="s">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
@@ -5290,31 +5290,31 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="H44" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="I44" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="J44" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L44" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
@@ -5331,31 +5331,31 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H45" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I45" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J45" t="s">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L45" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -5372,31 +5372,31 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F46" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H46" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I46" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J46" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L46" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -5413,31 +5413,31 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F47" t="s">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H47" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I47" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L47" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
@@ -5454,31 +5454,31 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F48" t="s">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H48" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I48" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="J48" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L48" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
@@ -5495,31 +5495,31 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H49" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I49" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="J49" t="s">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L49" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
@@ -5536,31 +5536,31 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F50" t="s">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H50" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I50" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L50" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
@@ -5577,31 +5577,31 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F51" t="s">
-        <v>228</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H51" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I51" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="J51" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L51" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -5618,31 +5618,31 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>232</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F52" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="G52" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H52" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I52" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="J52" t="s">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L52" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -5659,31 +5659,31 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>236</v>
+        <v>18</v>
       </c>
       <c r="G53" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H53" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="J53" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L53" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M53" t="s">
         <v>23</v>
@@ -5700,31 +5700,31 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H54" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I54" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="J54" t="s">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L54" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M54" t="s">
         <v>23</v>
@@ -5741,31 +5741,31 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="G55" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H55" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I55" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="J55" t="s">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L55" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M55" t="s">
         <v>23</v>
@@ -5782,31 +5782,31 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>248</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H56" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I56" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="J56" t="s">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
@@ -5823,31 +5823,31 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>252</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="G57" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H57" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I57" t="s">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="J57" t="s">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L57" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
@@ -5864,31 +5864,31 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F58" t="s">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H58" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I58" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="J58" t="s">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="K58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L58" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -5905,31 +5905,31 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F59" t="s">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H59" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I59" t="s">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="J59" t="s">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L59" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
@@ -5946,31 +5946,31 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>264</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H60" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I60" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="J60" t="s">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
@@ -5987,31 +5987,31 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="H61" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="I61" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="J61" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L61" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -6028,13 +6028,13 @@
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F62" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="G62" t="s">
         <v>274</v>
@@ -6069,13 +6069,13 @@
         <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>282</v>
       </c>
       <c r="E63" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F63" t="s">
-        <v>282</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
         <v>274</v>
@@ -6084,10 +6084,10 @@
         <v>275</v>
       </c>
       <c r="I63" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="J63" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="K63" t="s">
         <v>278</v>
@@ -6110,13 +6110,13 @@
         <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="E64" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F64" t="s">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
         <v>274</v>
@@ -6125,10 +6125,10 @@
         <v>275</v>
       </c>
       <c r="I64" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="J64" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="K64" t="s">
         <v>278</v>
@@ -6151,13 +6151,13 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>290</v>
       </c>
       <c r="E65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F65" t="s">
-        <v>290</v>
+        <v>18</v>
       </c>
       <c r="G65" t="s">
         <v>274</v>
@@ -6166,10 +6166,10 @@
         <v>275</v>
       </c>
       <c r="I65" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="J65" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="K65" t="s">
         <v>278</v>
@@ -6192,13 +6192,13 @@
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>294</v>
       </c>
       <c r="E66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F66" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
         <v>274</v>
@@ -6207,10 +6207,10 @@
         <v>275</v>
       </c>
       <c r="I66" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="J66" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="K66" t="s">
         <v>278</v>
@@ -6233,13 +6233,13 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F67" t="s">
-        <v>298</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
         <v>274</v>
@@ -6248,10 +6248,10 @@
         <v>275</v>
       </c>
       <c r="I67" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="J67" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="K67" t="s">
         <v>278</v>
@@ -6274,13 +6274,13 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c r="E68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F68" t="s">
-        <v>302</v>
+        <v>18</v>
       </c>
       <c r="G68" t="s">
         <v>274</v>
@@ -6289,10 +6289,10 @@
         <v>275</v>
       </c>
       <c r="I68" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="J68" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="K68" t="s">
         <v>278</v>
@@ -6315,13 +6315,13 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>306</v>
       </c>
       <c r="E69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F69" t="s">
-        <v>306</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
         <v>274</v>
@@ -6330,10 +6330,10 @@
         <v>275</v>
       </c>
       <c r="I69" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="J69" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="K69" t="s">
         <v>278</v>
@@ -6356,13 +6356,13 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="E70" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F70" t="s">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="G70" t="s">
         <v>274</v>
@@ -6371,10 +6371,10 @@
         <v>275</v>
       </c>
       <c r="I70" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="J70" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="K70" t="s">
         <v>278</v>
@@ -6397,13 +6397,13 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>314</v>
       </c>
       <c r="E71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F71" t="s">
-        <v>314</v>
+        <v>18</v>
       </c>
       <c r="G71" t="s">
         <v>274</v>
@@ -6412,10 +6412,10 @@
         <v>275</v>
       </c>
       <c r="I71" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="J71" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="K71" t="s">
         <v>278</v>
@@ -6438,13 +6438,13 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="E72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F72" t="s">
-        <v>318</v>
+        <v>18</v>
       </c>
       <c r="G72" t="s">
         <v>274</v>
@@ -6453,10 +6453,10 @@
         <v>275</v>
       </c>
       <c r="I72" t="s">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="J72" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="K72" t="s">
         <v>278</v>
@@ -6479,13 +6479,13 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>322</v>
       </c>
       <c r="E73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F73" t="s">
-        <v>322</v>
+        <v>18</v>
       </c>
       <c r="G73" t="s">
         <v>274</v>
@@ -6494,10 +6494,10 @@
         <v>275</v>
       </c>
       <c r="I73" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="J73" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="K73" t="s">
         <v>278</v>
@@ -6520,13 +6520,13 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c r="E74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F74" t="s">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="G74" t="s">
         <v>274</v>
@@ -6535,10 +6535,10 @@
         <v>275</v>
       </c>
       <c r="I74" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="J74" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="K74" t="s">
         <v>278</v>
@@ -6561,13 +6561,13 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F75" t="s">
-        <v>330</v>
+        <v>18</v>
       </c>
       <c r="G75" t="s">
         <v>274</v>
@@ -6576,10 +6576,10 @@
         <v>275</v>
       </c>
       <c r="I75" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="J75" t="s">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="K75" t="s">
         <v>278</v>
@@ -6602,13 +6602,13 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>334</v>
       </c>
       <c r="E76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F76" t="s">
-        <v>334</v>
+        <v>18</v>
       </c>
       <c r="G76" t="s">
         <v>274</v>
@@ -6617,10 +6617,10 @@
         <v>275</v>
       </c>
       <c r="I76" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="J76" t="s">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="K76" t="s">
         <v>278</v>
@@ -6643,13 +6643,13 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>338</v>
       </c>
       <c r="E77" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F77" t="s">
-        <v>338</v>
+        <v>18</v>
       </c>
       <c r="G77" t="s">
         <v>274</v>
@@ -6658,10 +6658,10 @@
         <v>275</v>
       </c>
       <c r="I77" t="s">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="J77" t="s">
-        <v>339</v>
+        <v>277</v>
       </c>
       <c r="K77" t="s">
         <v>278</v>
@@ -6684,13 +6684,13 @@
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>342</v>
       </c>
       <c r="E78" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F78" t="s">
-        <v>342</v>
+        <v>18</v>
       </c>
       <c r="G78" t="s">
         <v>274</v>
@@ -6699,10 +6699,10 @@
         <v>275</v>
       </c>
       <c r="I78" t="s">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="J78" t="s">
-        <v>343</v>
+        <v>277</v>
       </c>
       <c r="K78" t="s">
         <v>278</v>
@@ -6725,13 +6725,13 @@
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>346</v>
       </c>
       <c r="E79" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F79" t="s">
-        <v>346</v>
+        <v>18</v>
       </c>
       <c r="G79" t="s">
         <v>274</v>
@@ -6740,10 +6740,10 @@
         <v>275</v>
       </c>
       <c r="I79" t="s">
-        <v>276</v>
+        <v>347</v>
       </c>
       <c r="J79" t="s">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="K79" t="s">
         <v>278</v>
@@ -6766,13 +6766,13 @@
         <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c r="E80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" t="s">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="G80" t="s">
         <v>274</v>
@@ -6781,10 +6781,10 @@
         <v>275</v>
       </c>
       <c r="I80" t="s">
-        <v>276</v>
+        <v>351</v>
       </c>
       <c r="J80" t="s">
-        <v>351</v>
+        <v>277</v>
       </c>
       <c r="K80" t="s">
         <v>278</v>
@@ -6807,13 +6807,13 @@
         <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="E81" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F81" t="s">
-        <v>354</v>
+        <v>18</v>
       </c>
       <c r="G81" t="s">
         <v>274</v>
@@ -6822,10 +6822,10 @@
         <v>275</v>
       </c>
       <c r="I81" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="J81" t="s">
-        <v>355</v>
+        <v>277</v>
       </c>
       <c r="K81" t="s">
         <v>278</v>
@@ -6848,13 +6848,13 @@
         <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>358</v>
       </c>
       <c r="E82" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F82" t="s">
-        <v>358</v>
+        <v>18</v>
       </c>
       <c r="G82" t="s">
         <v>274</v>
@@ -6863,10 +6863,10 @@
         <v>275</v>
       </c>
       <c r="I82" t="s">
-        <v>276</v>
+        <v>359</v>
       </c>
       <c r="J82" t="s">
-        <v>359</v>
+        <v>277</v>
       </c>
       <c r="K82" t="s">
         <v>278</v>
@@ -6889,13 +6889,13 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>362</v>
       </c>
       <c r="E83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F83" t="s">
-        <v>362</v>
+        <v>18</v>
       </c>
       <c r="G83" t="s">
         <v>274</v>
@@ -6904,10 +6904,10 @@
         <v>275</v>
       </c>
       <c r="I83" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="J83" t="s">
-        <v>363</v>
+        <v>277</v>
       </c>
       <c r="K83" t="s">
         <v>278</v>
@@ -6930,13 +6930,13 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>366</v>
       </c>
       <c r="E84" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F84" t="s">
-        <v>366</v>
+        <v>18</v>
       </c>
       <c r="G84" t="s">
         <v>274</v>
@@ -6945,10 +6945,10 @@
         <v>275</v>
       </c>
       <c r="I84" t="s">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="J84" t="s">
-        <v>367</v>
+        <v>277</v>
       </c>
       <c r="K84" t="s">
         <v>278</v>
@@ -6971,13 +6971,13 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>370</v>
       </c>
       <c r="E85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F85" t="s">
-        <v>370</v>
+        <v>18</v>
       </c>
       <c r="G85" t="s">
         <v>274</v>
@@ -6986,10 +6986,10 @@
         <v>275</v>
       </c>
       <c r="I85" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="J85" t="s">
-        <v>371</v>
+        <v>277</v>
       </c>
       <c r="K85" t="s">
         <v>278</v>
@@ -7012,13 +7012,13 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>374</v>
       </c>
       <c r="E86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F86" t="s">
-        <v>374</v>
+        <v>18</v>
       </c>
       <c r="G86" t="s">
         <v>274</v>
@@ -7027,10 +7027,10 @@
         <v>275</v>
       </c>
       <c r="I86" t="s">
-        <v>276</v>
+        <v>375</v>
       </c>
       <c r="J86" t="s">
-        <v>375</v>
+        <v>277</v>
       </c>
       <c r="K86" t="s">
         <v>278</v>
@@ -7053,13 +7053,13 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>378</v>
       </c>
       <c r="E87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F87" t="s">
-        <v>378</v>
+        <v>18</v>
       </c>
       <c r="G87" t="s">
         <v>274</v>
@@ -7068,10 +7068,10 @@
         <v>275</v>
       </c>
       <c r="I87" t="s">
-        <v>276</v>
+        <v>379</v>
       </c>
       <c r="J87" t="s">
-        <v>379</v>
+        <v>277</v>
       </c>
       <c r="K87" t="s">
         <v>278</v>
@@ -7094,13 +7094,13 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>382</v>
       </c>
       <c r="E88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" t="s">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="G88" t="s">
         <v>274</v>
@@ -7109,10 +7109,10 @@
         <v>275</v>
       </c>
       <c r="I88" t="s">
-        <v>276</v>
+        <v>383</v>
       </c>
       <c r="J88" t="s">
-        <v>383</v>
+        <v>277</v>
       </c>
       <c r="K88" t="s">
         <v>278</v>
@@ -7135,13 +7135,13 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="E89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F89" t="s">
-        <v>386</v>
+        <v>18</v>
       </c>
       <c r="G89" t="s">
         <v>274</v>
@@ -7150,10 +7150,10 @@
         <v>275</v>
       </c>
       <c r="I89" t="s">
-        <v>276</v>
+        <v>387</v>
       </c>
       <c r="J89" t="s">
-        <v>387</v>
+        <v>277</v>
       </c>
       <c r="K89" t="s">
         <v>278</v>
@@ -7176,31 +7176,31 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>390</v>
       </c>
       <c r="E90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F90" t="s">
-        <v>390</v>
+        <v>18</v>
       </c>
       <c r="G90" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H90" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I90" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J90" t="s">
-        <v>392</v>
+        <v>277</v>
       </c>
       <c r="K90" t="s">
         <v>278</v>
       </c>
       <c r="L90" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M90" t="s">
         <v>23</v>
@@ -7217,31 +7217,31 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="E91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="G91" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H91" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I91" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="J91" t="s">
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="K91" t="s">
         <v>278</v>
       </c>
       <c r="L91" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M91" t="s">
         <v>23</v>
@@ -7258,31 +7258,31 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="E92" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F92" t="s">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="G92" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H92" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I92" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="J92" t="s">
-        <v>401</v>
+        <v>277</v>
       </c>
       <c r="K92" t="s">
         <v>278</v>
       </c>
       <c r="L92" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M92" t="s">
         <v>23</v>
@@ -7299,31 +7299,31 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="E93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F93" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H93" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I93" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="J93" t="s">
-        <v>405</v>
+        <v>277</v>
       </c>
       <c r="K93" t="s">
         <v>278</v>
       </c>
       <c r="L93" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M93" t="s">
         <v>23</v>
@@ -7340,31 +7340,31 @@
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>408</v>
       </c>
       <c r="E94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F94" t="s">
-        <v>408</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H94" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I94" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="J94" t="s">
-        <v>409</v>
+        <v>277</v>
       </c>
       <c r="K94" t="s">
         <v>278</v>
       </c>
       <c r="L94" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M94" t="s">
         <v>23</v>
@@ -7381,31 +7381,31 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>412</v>
       </c>
       <c r="E95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F95" t="s">
-        <v>412</v>
+        <v>18</v>
       </c>
       <c r="G95" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H95" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I95" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="J95" t="s">
-        <v>413</v>
+        <v>277</v>
       </c>
       <c r="K95" t="s">
         <v>278</v>
       </c>
       <c r="L95" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M95" t="s">
         <v>23</v>
@@ -7422,31 +7422,31 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="E96" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F96" t="s">
-        <v>416</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H96" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I96" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="J96" t="s">
-        <v>417</v>
+        <v>277</v>
       </c>
       <c r="K96" t="s">
         <v>278</v>
       </c>
       <c r="L96" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M96" t="s">
         <v>23</v>
@@ -7463,31 +7463,31 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>420</v>
       </c>
       <c r="E97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F97" t="s">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="H97" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="I97" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="J97" t="s">
-        <v>421</v>
+        <v>277</v>
       </c>
       <c r="K97" t="s">
         <v>278</v>
       </c>
       <c r="L97" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="M97" t="s">
         <v>23</v>
@@ -7504,31 +7504,31 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>424</v>
       </c>
       <c r="E98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F98" t="s">
-        <v>424</v>
+        <v>18</v>
       </c>
       <c r="G98" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H98" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I98" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J98" t="s">
-        <v>426</v>
+        <v>277</v>
       </c>
       <c r="K98" t="s">
         <v>278</v>
       </c>
       <c r="L98" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M98" t="s">
         <v>23</v>
@@ -7545,31 +7545,31 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
       <c r="E99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F99" t="s">
-        <v>430</v>
+        <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H99" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I99" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="J99" t="s">
-        <v>431</v>
+        <v>277</v>
       </c>
       <c r="K99" t="s">
         <v>278</v>
       </c>
       <c r="L99" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M99" t="s">
         <v>23</v>
@@ -7586,31 +7586,31 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>434</v>
       </c>
       <c r="E100" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F100" t="s">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H100" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I100" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="J100" t="s">
-        <v>435</v>
+        <v>277</v>
       </c>
       <c r="K100" t="s">
         <v>278</v>
       </c>
       <c r="L100" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M100" t="s">
         <v>23</v>
@@ -7627,31 +7627,31 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>438</v>
       </c>
       <c r="E101" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F101" t="s">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H101" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I101" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="J101" t="s">
-        <v>439</v>
+        <v>277</v>
       </c>
       <c r="K101" t="s">
         <v>278</v>
       </c>
       <c r="L101" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M101" t="s">
         <v>23</v>
@@ -7668,31 +7668,31 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>442</v>
       </c>
       <c r="E102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102" t="s">
-        <v>442</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H102" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I102" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J102" t="s">
-        <v>443</v>
+        <v>277</v>
       </c>
       <c r="K102" t="s">
         <v>278</v>
       </c>
       <c r="L102" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M102" t="s">
         <v>23</v>
@@ -7709,31 +7709,31 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>446</v>
       </c>
       <c r="E103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F103" t="s">
-        <v>446</v>
+        <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H103" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I103" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="J103" t="s">
-        <v>447</v>
+        <v>277</v>
       </c>
       <c r="K103" t="s">
         <v>278</v>
       </c>
       <c r="L103" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M103" t="s">
         <v>23</v>
@@ -7750,31 +7750,31 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>450</v>
       </c>
       <c r="E104" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F104" t="s">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H104" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I104" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="J104" t="s">
-        <v>451</v>
+        <v>277</v>
       </c>
       <c r="K104" t="s">
         <v>278</v>
       </c>
       <c r="L104" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M104" t="s">
         <v>23</v>
@@ -7791,31 +7791,31 @@
         <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>454</v>
       </c>
       <c r="E105" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F105" t="s">
-        <v>454</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H105" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I105" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="J105" t="s">
-        <v>455</v>
+        <v>277</v>
       </c>
       <c r="K105" t="s">
         <v>278</v>
       </c>
       <c r="L105" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M105" t="s">
         <v>23</v>
@@ -7832,31 +7832,31 @@
         <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>458</v>
       </c>
       <c r="E106" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F106" t="s">
-        <v>458</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H106" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I106" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="J106" t="s">
-        <v>459</v>
+        <v>277</v>
       </c>
       <c r="K106" t="s">
         <v>278</v>
       </c>
       <c r="L106" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M106" t="s">
         <v>23</v>
@@ -7873,31 +7873,31 @@
         <v>15</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>462</v>
       </c>
       <c r="E107" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F107" t="s">
-        <v>462</v>
+        <v>18</v>
       </c>
       <c r="G107" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H107" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I107" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="J107" t="s">
-        <v>463</v>
+        <v>277</v>
       </c>
       <c r="K107" t="s">
         <v>278</v>
       </c>
       <c r="L107" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M107" t="s">
         <v>23</v>
@@ -7914,31 +7914,31 @@
         <v>15</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>466</v>
       </c>
       <c r="E108" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F108" t="s">
-        <v>466</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H108" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I108" t="s">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="J108" t="s">
-        <v>467</v>
+        <v>277</v>
       </c>
       <c r="K108" t="s">
         <v>278</v>
       </c>
       <c r="L108" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M108" t="s">
         <v>23</v>
@@ -7955,31 +7955,31 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>16</v>
+        <v>470</v>
       </c>
       <c r="E109" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F109" t="s">
-        <v>470</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H109" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I109" t="s">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="J109" t="s">
-        <v>471</v>
+        <v>277</v>
       </c>
       <c r="K109" t="s">
         <v>278</v>
       </c>
       <c r="L109" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M109" t="s">
         <v>23</v>
@@ -7996,31 +7996,31 @@
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>474</v>
       </c>
       <c r="E110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F110" t="s">
-        <v>474</v>
+        <v>18</v>
       </c>
       <c r="G110" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H110" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I110" t="s">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="J110" t="s">
-        <v>475</v>
+        <v>277</v>
       </c>
       <c r="K110" t="s">
         <v>278</v>
       </c>
       <c r="L110" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M110" t="s">
         <v>23</v>
@@ -8037,31 +8037,31 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>478</v>
       </c>
       <c r="E111" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F111" t="s">
-        <v>478</v>
+        <v>18</v>
       </c>
       <c r="G111" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H111" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I111" t="s">
-        <v>425</v>
+        <v>479</v>
       </c>
       <c r="J111" t="s">
-        <v>479</v>
+        <v>277</v>
       </c>
       <c r="K111" t="s">
         <v>278</v>
       </c>
       <c r="L111" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M111" t="s">
         <v>23</v>
@@ -8078,31 +8078,31 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>482</v>
       </c>
       <c r="E112" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>482</v>
+        <v>18</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H112" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I112" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="J112" t="s">
-        <v>483</v>
+        <v>277</v>
       </c>
       <c r="K112" t="s">
         <v>278</v>
       </c>
       <c r="L112" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M112" t="s">
         <v>23</v>
@@ -8119,31 +8119,31 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>486</v>
       </c>
       <c r="E113" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F113" t="s">
-        <v>486</v>
+        <v>18</v>
       </c>
       <c r="G113" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="H113" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="I113" t="s">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="J113" t="s">
-        <v>487</v>
+        <v>277</v>
       </c>
       <c r="K113" t="s">
         <v>278</v>
       </c>
       <c r="L113" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M113" t="s">
         <v>23</v>
@@ -8160,25 +8160,25 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="E114" t="s">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="F114" t="s">
-        <v>490</v>
-      </c>
-      <c r="G114" t="s">
-        <v>491</v>
-      </c>
-      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
         <v>492</v>
       </c>
       <c r="J114" t="s">
-        <v>493</v>
+        <v>277</v>
       </c>
       <c r="K114" t="s">
         <v>278</v>
+      </c>
+      <c r="L114" t="s">
+        <v>493</v>
       </c>
       <c r="M114" t="s">
         <v>23</v>
@@ -8195,25 +8195,25 @@
         <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>496</v>
       </c>
       <c r="E115" t="s">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="F115" t="s">
-        <v>496</v>
-      </c>
-      <c r="G115" t="s">
-        <v>491</v>
-      </c>
-      <c r="H115" t="s">
-        <v>492</v>
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>497</v>
       </c>
       <c r="J115" t="s">
-        <v>497</v>
+        <v>277</v>
       </c>
       <c r="K115" t="s">
         <v>278</v>
+      </c>
+      <c r="L115" t="s">
+        <v>493</v>
       </c>
       <c r="M115" t="s">
         <v>23</v>
@@ -8230,25 +8230,25 @@
         <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="E116" t="s">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="F116" t="s">
-        <v>500</v>
-      </c>
-      <c r="G116" t="s">
-        <v>491</v>
-      </c>
-      <c r="H116" t="s">
-        <v>492</v>
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>501</v>
       </c>
       <c r="J116" t="s">
-        <v>501</v>
+        <v>277</v>
       </c>
       <c r="K116" t="s">
         <v>278</v>
+      </c>
+      <c r="L116" t="s">
+        <v>493</v>
       </c>
       <c r="M116" t="s">
         <v>23</v>
@@ -8265,25 +8265,25 @@
         <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="E117" t="s">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="F117" t="s">
-        <v>504</v>
-      </c>
-      <c r="G117" t="s">
-        <v>491</v>
-      </c>
-      <c r="H117" t="s">
-        <v>492</v>
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>505</v>
       </c>
       <c r="J117" t="s">
-        <v>505</v>
+        <v>277</v>
       </c>
       <c r="K117" t="s">
         <v>278</v>
+      </c>
+      <c r="L117" t="s">
+        <v>493</v>
       </c>
       <c r="M117" t="s">
         <v>23</v>
@@ -8300,25 +8300,25 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E118" t="s">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="F118" t="s">
-        <v>508</v>
-      </c>
-      <c r="G118" t="s">
-        <v>491</v>
-      </c>
-      <c r="H118" t="s">
-        <v>492</v>
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>509</v>
       </c>
       <c r="J118" t="s">
-        <v>509</v>
+        <v>277</v>
       </c>
       <c r="K118" t="s">
         <v>278</v>
+      </c>
+      <c r="L118" t="s">
+        <v>493</v>
       </c>
       <c r="M118" t="s">
         <v>23</v>
@@ -8335,12 +8335,12 @@
         <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="F119" t="s">
-        <v>512</v>
-      </c>
-      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
         <v>513</v>
       </c>
       <c r="M119" t="s">
@@ -8358,24 +8358,24 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>16</v>
+        <v>516</v>
       </c>
       <c r="E120" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F120" t="s">
-        <v>517</v>
-      </c>
-      <c r="G120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
         <v>518</v>
       </c>
-      <c r="H120" t="s">
+      <c r="J120" t="s">
         <v>519</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>520</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>521</v>
       </c>
       <c r="M120" t="s">
@@ -8393,24 +8393,24 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>524</v>
       </c>
       <c r="E121" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F121" t="s">
-        <v>524</v>
-      </c>
-      <c r="G121" t="s">
-        <v>518</v>
-      </c>
-      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>525</v>
+      </c>
+      <c r="J121" t="s">
         <v>519</v>
       </c>
-      <c r="J121" t="s">
-        <v>525</v>
-      </c>
       <c r="K121" t="s">
+        <v>520</v>
+      </c>
+      <c r="L121" t="s">
         <v>521</v>
       </c>
       <c r="M121" t="s">
@@ -8428,24 +8428,24 @@
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>528</v>
       </c>
       <c r="E122" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F122" t="s">
-        <v>528</v>
-      </c>
-      <c r="G122" t="s">
-        <v>518</v>
-      </c>
-      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>529</v>
+      </c>
+      <c r="J122" t="s">
         <v>519</v>
       </c>
-      <c r="J122" t="s">
-        <v>529</v>
-      </c>
       <c r="K122" t="s">
+        <v>520</v>
+      </c>
+      <c r="L122" t="s">
         <v>521</v>
       </c>
       <c r="M122" t="s">
@@ -8463,24 +8463,24 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>532</v>
       </c>
       <c r="E123" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F123" t="s">
-        <v>532</v>
-      </c>
-      <c r="G123" t="s">
-        <v>518</v>
-      </c>
-      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>533</v>
+      </c>
+      <c r="J123" t="s">
         <v>519</v>
       </c>
-      <c r="J123" t="s">
-        <v>533</v>
-      </c>
       <c r="K123" t="s">
+        <v>520</v>
+      </c>
+      <c r="L123" t="s">
         <v>521</v>
       </c>
       <c r="M123" t="s">
@@ -8498,24 +8498,24 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>536</v>
       </c>
       <c r="E124" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F124" t="s">
-        <v>536</v>
-      </c>
-      <c r="G124" t="s">
-        <v>518</v>
-      </c>
-      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>537</v>
+      </c>
+      <c r="J124" t="s">
         <v>519</v>
       </c>
-      <c r="J124" t="s">
-        <v>537</v>
-      </c>
       <c r="K124" t="s">
+        <v>520</v>
+      </c>
+      <c r="L124" t="s">
         <v>521</v>
       </c>
       <c r="M124" t="s">
@@ -8533,25 +8533,25 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="E125" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F125" t="s">
-        <v>540</v>
-      </c>
-      <c r="G125" t="s">
-        <v>541</v>
-      </c>
-      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
         <v>542</v>
       </c>
       <c r="J125" t="s">
+        <v>519</v>
+      </c>
+      <c r="K125" t="s">
+        <v>520</v>
+      </c>
+      <c r="L125" t="s">
         <v>543</v>
-      </c>
-      <c r="K125" t="s">
-        <v>521</v>
       </c>
       <c r="M125" t="s">
         <v>23</v>
@@ -8568,25 +8568,25 @@
         <v>15</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>546</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F126" t="s">
-        <v>546</v>
-      </c>
-      <c r="G126" t="s">
-        <v>541</v>
-      </c>
-      <c r="H126" t="s">
-        <v>542</v>
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>547</v>
       </c>
       <c r="J126" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="K126" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L126" t="s">
+        <v>543</v>
       </c>
       <c r="M126" t="s">
         <v>23</v>
@@ -8603,25 +8603,25 @@
         <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>550</v>
       </c>
       <c r="E127" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F127" t="s">
-        <v>550</v>
-      </c>
-      <c r="G127" t="s">
-        <v>541</v>
-      </c>
-      <c r="H127" t="s">
-        <v>542</v>
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>551</v>
       </c>
       <c r="J127" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="K127" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L127" t="s">
+        <v>543</v>
       </c>
       <c r="M127" t="s">
         <v>23</v>
@@ -8638,25 +8638,25 @@
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>554</v>
       </c>
       <c r="E128" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F128" t="s">
-        <v>554</v>
-      </c>
-      <c r="G128" t="s">
-        <v>541</v>
-      </c>
-      <c r="H128" t="s">
-        <v>542</v>
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>555</v>
       </c>
       <c r="J128" t="s">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="K128" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L128" t="s">
+        <v>543</v>
       </c>
       <c r="M128" t="s">
         <v>23</v>
@@ -8673,25 +8673,25 @@
         <v>15</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>558</v>
       </c>
       <c r="E129" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F129" t="s">
-        <v>558</v>
-      </c>
-      <c r="G129" t="s">
-        <v>541</v>
-      </c>
-      <c r="H129" t="s">
-        <v>542</v>
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>559</v>
       </c>
       <c r="J129" t="s">
-        <v>559</v>
+        <v>519</v>
       </c>
       <c r="K129" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L129" t="s">
+        <v>543</v>
       </c>
       <c r="M129" t="s">
         <v>23</v>
@@ -8708,25 +8708,25 @@
         <v>15</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>562</v>
       </c>
       <c r="E130" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F130" t="s">
-        <v>562</v>
-      </c>
-      <c r="G130" t="s">
-        <v>541</v>
-      </c>
-      <c r="H130" t="s">
-        <v>542</v>
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>563</v>
       </c>
       <c r="J130" t="s">
-        <v>563</v>
+        <v>519</v>
       </c>
       <c r="K130" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L130" t="s">
+        <v>543</v>
       </c>
       <c r="M130" t="s">
         <v>23</v>
@@ -8743,25 +8743,25 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>566</v>
       </c>
       <c r="E131" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F131" t="s">
-        <v>566</v>
-      </c>
-      <c r="G131" t="s">
-        <v>541</v>
-      </c>
-      <c r="H131" t="s">
-        <v>542</v>
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>567</v>
       </c>
       <c r="J131" t="s">
-        <v>567</v>
+        <v>519</v>
       </c>
       <c r="K131" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L131" t="s">
+        <v>543</v>
       </c>
       <c r="M131" t="s">
         <v>23</v>
@@ -8778,25 +8778,25 @@
         <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>570</v>
       </c>
       <c r="E132" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F132" t="s">
-        <v>570</v>
-      </c>
-      <c r="G132" t="s">
-        <v>571</v>
-      </c>
-      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
         <v>572</v>
       </c>
       <c r="J132" t="s">
+        <v>519</v>
+      </c>
+      <c r="K132" t="s">
+        <v>520</v>
+      </c>
+      <c r="L132" t="s">
         <v>573</v>
-      </c>
-      <c r="K132" t="s">
-        <v>521</v>
       </c>
       <c r="M132" t="s">
         <v>23</v>
@@ -8813,25 +8813,25 @@
         <v>15</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>576</v>
       </c>
       <c r="E133" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F133" t="s">
-        <v>576</v>
-      </c>
-      <c r="G133" t="s">
-        <v>571</v>
-      </c>
-      <c r="H133" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>577</v>
       </c>
       <c r="J133" t="s">
-        <v>577</v>
+        <v>519</v>
       </c>
       <c r="K133" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L133" t="s">
+        <v>573</v>
       </c>
       <c r="M133" t="s">
         <v>23</v>
@@ -8848,25 +8848,25 @@
         <v>15</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>580</v>
       </c>
       <c r="E134" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F134" t="s">
-        <v>580</v>
-      </c>
-      <c r="G134" t="s">
-        <v>571</v>
-      </c>
-      <c r="H134" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>581</v>
       </c>
       <c r="J134" t="s">
-        <v>581</v>
+        <v>519</v>
       </c>
       <c r="K134" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L134" t="s">
+        <v>573</v>
       </c>
       <c r="M134" t="s">
         <v>23</v>
@@ -8883,25 +8883,25 @@
         <v>15</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>584</v>
       </c>
       <c r="E135" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F135" t="s">
-        <v>584</v>
-      </c>
-      <c r="G135" t="s">
-        <v>571</v>
-      </c>
-      <c r="H135" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>585</v>
       </c>
       <c r="J135" t="s">
-        <v>585</v>
+        <v>519</v>
       </c>
       <c r="K135" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L135" t="s">
+        <v>573</v>
       </c>
       <c r="M135" t="s">
         <v>23</v>
@@ -8918,25 +8918,25 @@
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>588</v>
       </c>
       <c r="E136" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F136" t="s">
-        <v>588</v>
-      </c>
-      <c r="G136" t="s">
-        <v>571</v>
-      </c>
-      <c r="H136" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>589</v>
       </c>
       <c r="J136" t="s">
-        <v>589</v>
+        <v>519</v>
       </c>
       <c r="K136" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L136" t="s">
+        <v>573</v>
       </c>
       <c r="M136" t="s">
         <v>23</v>
@@ -8953,25 +8953,25 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>592</v>
       </c>
       <c r="E137" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F137" t="s">
-        <v>592</v>
-      </c>
-      <c r="G137" t="s">
-        <v>571</v>
-      </c>
-      <c r="H137" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>593</v>
       </c>
       <c r="J137" t="s">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="K137" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L137" t="s">
+        <v>573</v>
       </c>
       <c r="M137" t="s">
         <v>23</v>
@@ -8988,25 +8988,25 @@
         <v>15</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>596</v>
       </c>
       <c r="E138" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F138" t="s">
-        <v>596</v>
-      </c>
-      <c r="G138" t="s">
-        <v>571</v>
-      </c>
-      <c r="H138" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>597</v>
       </c>
       <c r="J138" t="s">
-        <v>597</v>
+        <v>519</v>
       </c>
       <c r="K138" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L138" t="s">
+        <v>573</v>
       </c>
       <c r="M138" t="s">
         <v>23</v>
@@ -9023,25 +9023,25 @@
         <v>15</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="E139" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F139" t="s">
-        <v>600</v>
-      </c>
-      <c r="G139" t="s">
-        <v>571</v>
-      </c>
-      <c r="H139" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>601</v>
       </c>
       <c r="J139" t="s">
-        <v>601</v>
+        <v>519</v>
       </c>
       <c r="K139" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L139" t="s">
+        <v>573</v>
       </c>
       <c r="M139" t="s">
         <v>23</v>
@@ -9058,25 +9058,25 @@
         <v>15</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="E140" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F140" t="s">
-        <v>604</v>
-      </c>
-      <c r="G140" t="s">
-        <v>571</v>
-      </c>
-      <c r="H140" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>605</v>
       </c>
       <c r="J140" t="s">
-        <v>605</v>
+        <v>519</v>
       </c>
       <c r="K140" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L140" t="s">
+        <v>573</v>
       </c>
       <c r="M140" t="s">
         <v>23</v>
@@ -9093,25 +9093,25 @@
         <v>15</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>608</v>
       </c>
       <c r="E141" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F141" t="s">
-        <v>608</v>
-      </c>
-      <c r="G141" t="s">
-        <v>571</v>
-      </c>
-      <c r="H141" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>609</v>
       </c>
       <c r="J141" t="s">
-        <v>609</v>
+        <v>519</v>
       </c>
       <c r="K141" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L141" t="s">
+        <v>573</v>
       </c>
       <c r="M141" t="s">
         <v>23</v>
@@ -9128,25 +9128,25 @@
         <v>15</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>612</v>
       </c>
       <c r="E142" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="F142" t="s">
-        <v>612</v>
-      </c>
-      <c r="G142" t="s">
-        <v>571</v>
-      </c>
-      <c r="H142" t="s">
-        <v>572</v>
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>613</v>
       </c>
       <c r="J142" t="s">
-        <v>613</v>
+        <v>519</v>
       </c>
       <c r="K142" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L142" t="s">
+        <v>573</v>
       </c>
       <c r="M142" t="s">
         <v>23</v>
@@ -9163,25 +9163,25 @@
         <v>15</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="E143" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F143" t="s">
-        <v>616</v>
-      </c>
-      <c r="G143" t="s">
-        <v>617</v>
-      </c>
-      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
         <v>618</v>
       </c>
       <c r="J143" t="s">
+        <v>519</v>
+      </c>
+      <c r="K143" t="s">
+        <v>520</v>
+      </c>
+      <c r="L143" t="s">
         <v>619</v>
-      </c>
-      <c r="K143" t="s">
-        <v>521</v>
       </c>
       <c r="M143" t="s">
         <v>23</v>
@@ -9198,25 +9198,25 @@
         <v>15</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>622</v>
       </c>
       <c r="E144" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F144" t="s">
-        <v>622</v>
-      </c>
-      <c r="G144" t="s">
-        <v>617</v>
-      </c>
-      <c r="H144" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>623</v>
       </c>
       <c r="J144" t="s">
-        <v>623</v>
+        <v>519</v>
       </c>
       <c r="K144" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L144" t="s">
+        <v>619</v>
       </c>
       <c r="M144" t="s">
         <v>23</v>
@@ -9233,25 +9233,25 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="E145" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F145" t="s">
-        <v>626</v>
-      </c>
-      <c r="G145" t="s">
-        <v>617</v>
-      </c>
-      <c r="H145" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>627</v>
       </c>
       <c r="J145" t="s">
-        <v>627</v>
+        <v>519</v>
       </c>
       <c r="K145" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L145" t="s">
+        <v>619</v>
       </c>
       <c r="M145" t="s">
         <v>23</v>
@@ -9268,25 +9268,25 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>630</v>
       </c>
       <c r="E146" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F146" t="s">
-        <v>630</v>
-      </c>
-      <c r="G146" t="s">
-        <v>617</v>
-      </c>
-      <c r="H146" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>631</v>
       </c>
       <c r="J146" t="s">
-        <v>631</v>
+        <v>519</v>
       </c>
       <c r="K146" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L146" t="s">
+        <v>619</v>
       </c>
       <c r="M146" t="s">
         <v>23</v>
@@ -9303,25 +9303,25 @@
         <v>15</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>634</v>
       </c>
       <c r="E147" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F147" t="s">
-        <v>634</v>
-      </c>
-      <c r="G147" t="s">
-        <v>617</v>
-      </c>
-      <c r="H147" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>635</v>
       </c>
       <c r="J147" t="s">
-        <v>635</v>
+        <v>519</v>
       </c>
       <c r="K147" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L147" t="s">
+        <v>619</v>
       </c>
       <c r="M147" t="s">
         <v>23</v>
@@ -9338,25 +9338,25 @@
         <v>15</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
+        <v>638</v>
       </c>
       <c r="E148" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F148" t="s">
-        <v>638</v>
-      </c>
-      <c r="G148" t="s">
-        <v>617</v>
-      </c>
-      <c r="H148" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>639</v>
       </c>
       <c r="J148" t="s">
-        <v>639</v>
+        <v>519</v>
       </c>
       <c r="K148" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L148" t="s">
+        <v>619</v>
       </c>
       <c r="M148" t="s">
         <v>23</v>
@@ -9373,25 +9373,25 @@
         <v>15</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>642</v>
       </c>
       <c r="E149" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F149" t="s">
-        <v>642</v>
-      </c>
-      <c r="G149" t="s">
-        <v>617</v>
-      </c>
-      <c r="H149" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>643</v>
       </c>
       <c r="J149" t="s">
-        <v>643</v>
+        <v>519</v>
       </c>
       <c r="K149" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L149" t="s">
+        <v>619</v>
       </c>
       <c r="M149" t="s">
         <v>23</v>
@@ -9408,25 +9408,25 @@
         <v>15</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>646</v>
       </c>
       <c r="E150" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F150" t="s">
-        <v>646</v>
-      </c>
-      <c r="G150" t="s">
-        <v>617</v>
-      </c>
-      <c r="H150" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>647</v>
       </c>
       <c r="J150" t="s">
-        <v>647</v>
+        <v>519</v>
       </c>
       <c r="K150" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L150" t="s">
+        <v>619</v>
       </c>
       <c r="M150" t="s">
         <v>23</v>
@@ -9443,25 +9443,25 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>16</v>
+        <v>650</v>
       </c>
       <c r="E151" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="F151" t="s">
-        <v>650</v>
-      </c>
-      <c r="G151" t="s">
-        <v>617</v>
-      </c>
-      <c r="H151" t="s">
-        <v>618</v>
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>651</v>
       </c>
       <c r="J151" t="s">
-        <v>651</v>
+        <v>519</v>
       </c>
       <c r="K151" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L151" t="s">
+        <v>619</v>
       </c>
       <c r="M151" t="s">
         <v>23</v>
@@ -9478,25 +9478,25 @@
         <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>654</v>
       </c>
       <c r="E152" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F152" t="s">
-        <v>654</v>
-      </c>
-      <c r="G152" t="s">
-        <v>655</v>
-      </c>
-      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
         <v>656</v>
       </c>
       <c r="J152" t="s">
+        <v>519</v>
+      </c>
+      <c r="K152" t="s">
+        <v>520</v>
+      </c>
+      <c r="L152" t="s">
         <v>657</v>
-      </c>
-      <c r="K152" t="s">
-        <v>521</v>
       </c>
       <c r="M152" t="s">
         <v>23</v>
@@ -9513,25 +9513,25 @@
         <v>15</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>660</v>
       </c>
       <c r="E153" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F153" t="s">
-        <v>660</v>
-      </c>
-      <c r="G153" t="s">
-        <v>655</v>
-      </c>
-      <c r="H153" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>661</v>
       </c>
       <c r="J153" t="s">
-        <v>661</v>
+        <v>519</v>
       </c>
       <c r="K153" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L153" t="s">
+        <v>657</v>
       </c>
       <c r="M153" t="s">
         <v>23</v>
@@ -9548,25 +9548,25 @@
         <v>15</v>
       </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>664</v>
       </c>
       <c r="E154" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F154" t="s">
-        <v>664</v>
-      </c>
-      <c r="G154" t="s">
-        <v>655</v>
-      </c>
-      <c r="H154" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>665</v>
       </c>
       <c r="J154" t="s">
-        <v>665</v>
+        <v>519</v>
       </c>
       <c r="K154" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L154" t="s">
+        <v>657</v>
       </c>
       <c r="M154" t="s">
         <v>23</v>
@@ -9583,25 +9583,25 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>668</v>
       </c>
       <c r="E155" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F155" t="s">
-        <v>668</v>
-      </c>
-      <c r="G155" t="s">
-        <v>655</v>
-      </c>
-      <c r="H155" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>669</v>
       </c>
       <c r="J155" t="s">
-        <v>669</v>
+        <v>519</v>
       </c>
       <c r="K155" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L155" t="s">
+        <v>657</v>
       </c>
       <c r="M155" t="s">
         <v>23</v>
@@ -9618,25 +9618,25 @@
         <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>16</v>
+        <v>672</v>
       </c>
       <c r="E156" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F156" t="s">
-        <v>672</v>
-      </c>
-      <c r="G156" t="s">
-        <v>655</v>
-      </c>
-      <c r="H156" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>673</v>
       </c>
       <c r="J156" t="s">
-        <v>673</v>
+        <v>519</v>
       </c>
       <c r="K156" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L156" t="s">
+        <v>657</v>
       </c>
       <c r="M156" t="s">
         <v>23</v>
@@ -9653,25 +9653,25 @@
         <v>15</v>
       </c>
       <c r="D157" t="s">
-        <v>16</v>
+        <v>676</v>
       </c>
       <c r="E157" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F157" t="s">
-        <v>676</v>
-      </c>
-      <c r="G157" t="s">
-        <v>655</v>
-      </c>
-      <c r="H157" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>677</v>
       </c>
       <c r="J157" t="s">
-        <v>677</v>
+        <v>519</v>
       </c>
       <c r="K157" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L157" t="s">
+        <v>657</v>
       </c>
       <c r="M157" t="s">
         <v>23</v>
@@ -9688,25 +9688,25 @@
         <v>15</v>
       </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>680</v>
       </c>
       <c r="E158" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F158" t="s">
-        <v>680</v>
-      </c>
-      <c r="G158" t="s">
-        <v>655</v>
-      </c>
-      <c r="H158" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>681</v>
       </c>
       <c r="J158" t="s">
-        <v>681</v>
+        <v>519</v>
       </c>
       <c r="K158" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L158" t="s">
+        <v>657</v>
       </c>
       <c r="M158" t="s">
         <v>23</v>
@@ -9723,25 +9723,25 @@
         <v>15</v>
       </c>
       <c r="D159" t="s">
-        <v>16</v>
+        <v>684</v>
       </c>
       <c r="E159" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F159" t="s">
-        <v>684</v>
-      </c>
-      <c r="G159" t="s">
-        <v>655</v>
-      </c>
-      <c r="H159" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>685</v>
       </c>
       <c r="J159" t="s">
-        <v>685</v>
+        <v>519</v>
       </c>
       <c r="K159" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L159" t="s">
+        <v>657</v>
       </c>
       <c r="M159" t="s">
         <v>23</v>
@@ -9758,25 +9758,25 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>688</v>
       </c>
       <c r="E160" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F160" t="s">
-        <v>688</v>
-      </c>
-      <c r="G160" t="s">
-        <v>655</v>
-      </c>
-      <c r="H160" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>689</v>
       </c>
       <c r="J160" t="s">
-        <v>689</v>
+        <v>519</v>
       </c>
       <c r="K160" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L160" t="s">
+        <v>657</v>
       </c>
       <c r="M160" t="s">
         <v>23</v>
@@ -9793,25 +9793,25 @@
         <v>15</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>692</v>
       </c>
       <c r="E161" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F161" t="s">
-        <v>692</v>
-      </c>
-      <c r="G161" t="s">
-        <v>655</v>
-      </c>
-      <c r="H161" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>693</v>
       </c>
       <c r="J161" t="s">
-        <v>693</v>
+        <v>519</v>
       </c>
       <c r="K161" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L161" t="s">
+        <v>657</v>
       </c>
       <c r="M161" t="s">
         <v>23</v>
@@ -9828,25 +9828,25 @@
         <v>15</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>696</v>
       </c>
       <c r="E162" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F162" t="s">
-        <v>696</v>
-      </c>
-      <c r="G162" t="s">
-        <v>655</v>
-      </c>
-      <c r="H162" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>697</v>
       </c>
       <c r="J162" t="s">
-        <v>697</v>
+        <v>519</v>
       </c>
       <c r="K162" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L162" t="s">
+        <v>657</v>
       </c>
       <c r="M162" t="s">
         <v>23</v>
@@ -9863,25 +9863,25 @@
         <v>15</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>700</v>
       </c>
       <c r="E163" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F163" t="s">
-        <v>700</v>
-      </c>
-      <c r="G163" t="s">
-        <v>655</v>
-      </c>
-      <c r="H163" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>701</v>
       </c>
       <c r="J163" t="s">
-        <v>701</v>
+        <v>519</v>
       </c>
       <c r="K163" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L163" t="s">
+        <v>657</v>
       </c>
       <c r="M163" t="s">
         <v>23</v>
@@ -9898,25 +9898,25 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="E164" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F164" t="s">
-        <v>704</v>
-      </c>
-      <c r="G164" t="s">
-        <v>655</v>
-      </c>
-      <c r="H164" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>705</v>
       </c>
       <c r="J164" t="s">
-        <v>705</v>
+        <v>519</v>
       </c>
       <c r="K164" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L164" t="s">
+        <v>657</v>
       </c>
       <c r="M164" t="s">
         <v>23</v>
@@ -9933,25 +9933,25 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>708</v>
       </c>
       <c r="E165" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F165" t="s">
-        <v>708</v>
-      </c>
-      <c r="G165" t="s">
-        <v>655</v>
-      </c>
-      <c r="H165" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>709</v>
       </c>
       <c r="J165" t="s">
-        <v>709</v>
+        <v>519</v>
       </c>
       <c r="K165" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L165" t="s">
+        <v>657</v>
       </c>
       <c r="M165" t="s">
         <v>23</v>
@@ -9968,25 +9968,25 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>712</v>
       </c>
       <c r="E166" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F166" t="s">
-        <v>712</v>
-      </c>
-      <c r="G166" t="s">
-        <v>655</v>
-      </c>
-      <c r="H166" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>713</v>
       </c>
       <c r="J166" t="s">
-        <v>713</v>
+        <v>519</v>
       </c>
       <c r="K166" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L166" t="s">
+        <v>657</v>
       </c>
       <c r="M166" t="s">
         <v>23</v>
@@ -10003,25 +10003,25 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>716</v>
       </c>
       <c r="E167" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F167" t="s">
-        <v>716</v>
-      </c>
-      <c r="G167" t="s">
-        <v>655</v>
-      </c>
-      <c r="H167" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>717</v>
       </c>
       <c r="J167" t="s">
-        <v>717</v>
+        <v>519</v>
       </c>
       <c r="K167" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L167" t="s">
+        <v>657</v>
       </c>
       <c r="M167" t="s">
         <v>23</v>
@@ -10038,25 +10038,25 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>16</v>
+        <v>720</v>
       </c>
       <c r="E168" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F168" t="s">
-        <v>720</v>
-      </c>
-      <c r="G168" t="s">
-        <v>655</v>
-      </c>
-      <c r="H168" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>721</v>
       </c>
       <c r="J168" t="s">
-        <v>721</v>
+        <v>519</v>
       </c>
       <c r="K168" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L168" t="s">
+        <v>657</v>
       </c>
       <c r="M168" t="s">
         <v>23</v>
@@ -10073,25 +10073,25 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>724</v>
       </c>
       <c r="E169" t="s">
-        <v>516</v>
+        <v>655</v>
       </c>
       <c r="F169" t="s">
-        <v>724</v>
-      </c>
-      <c r="G169" t="s">
-        <v>655</v>
-      </c>
-      <c r="H169" t="s">
-        <v>656</v>
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>725</v>
       </c>
       <c r="J169" t="s">
-        <v>725</v>
+        <v>519</v>
       </c>
       <c r="K169" t="s">
-        <v>521</v>
+        <v>520</v>
+      </c>
+      <c r="L169" t="s">
+        <v>657</v>
       </c>
       <c r="M169" t="s">
         <v>23</v>
@@ -10108,24 +10108,24 @@
         <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="E170" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F170" t="s">
-        <v>729</v>
-      </c>
-      <c r="G170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
         <v>730</v>
       </c>
-      <c r="H170" t="s">
+      <c r="J170" t="s">
         <v>731</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>732</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" t="s">
         <v>733</v>
       </c>
       <c r="M170" t="s">
@@ -10143,24 +10143,24 @@
         <v>15</v>
       </c>
       <c r="D171" t="s">
-        <v>16</v>
+        <v>736</v>
       </c>
       <c r="E171" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F171" t="s">
-        <v>736</v>
-      </c>
-      <c r="G171" t="s">
-        <v>730</v>
-      </c>
-      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>737</v>
+      </c>
+      <c r="J171" t="s">
         <v>731</v>
       </c>
-      <c r="J171" t="s">
-        <v>737</v>
-      </c>
       <c r="K171" t="s">
+        <v>732</v>
+      </c>
+      <c r="L171" t="s">
         <v>733</v>
       </c>
       <c r="M171" t="s">
@@ -10178,24 +10178,24 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>16</v>
+        <v>740</v>
       </c>
       <c r="E172" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F172" t="s">
-        <v>740</v>
-      </c>
-      <c r="G172" t="s">
-        <v>730</v>
-      </c>
-      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>741</v>
+      </c>
+      <c r="J172" t="s">
         <v>731</v>
       </c>
-      <c r="J172" t="s">
-        <v>741</v>
-      </c>
       <c r="K172" t="s">
+        <v>732</v>
+      </c>
+      <c r="L172" t="s">
         <v>733</v>
       </c>
       <c r="M172" t="s">
@@ -10213,24 +10213,24 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>744</v>
       </c>
       <c r="E173" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F173" t="s">
-        <v>744</v>
-      </c>
-      <c r="G173" t="s">
-        <v>730</v>
-      </c>
-      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>745</v>
+      </c>
+      <c r="J173" t="s">
         <v>731</v>
       </c>
-      <c r="J173" t="s">
-        <v>745</v>
-      </c>
       <c r="K173" t="s">
+        <v>732</v>
+      </c>
+      <c r="L173" t="s">
         <v>733</v>
       </c>
       <c r="M173" t="s">
@@ -10248,24 +10248,24 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>16</v>
+        <v>748</v>
       </c>
       <c r="E174" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F174" t="s">
-        <v>748</v>
-      </c>
-      <c r="G174" t="s">
-        <v>730</v>
-      </c>
-      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>749</v>
+      </c>
+      <c r="J174" t="s">
         <v>731</v>
       </c>
-      <c r="J174" t="s">
-        <v>749</v>
-      </c>
       <c r="K174" t="s">
+        <v>732</v>
+      </c>
+      <c r="L174" t="s">
         <v>733</v>
       </c>
       <c r="M174" t="s">
@@ -10283,24 +10283,24 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>752</v>
       </c>
       <c r="E175" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F175" t="s">
-        <v>752</v>
-      </c>
-      <c r="G175" t="s">
-        <v>730</v>
-      </c>
-      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>753</v>
+      </c>
+      <c r="J175" t="s">
         <v>731</v>
       </c>
-      <c r="J175" t="s">
-        <v>753</v>
-      </c>
       <c r="K175" t="s">
+        <v>732</v>
+      </c>
+      <c r="L175" t="s">
         <v>733</v>
       </c>
       <c r="M175" t="s">
@@ -10318,24 +10318,24 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>16</v>
+        <v>756</v>
       </c>
       <c r="E176" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F176" t="s">
-        <v>756</v>
-      </c>
-      <c r="G176" t="s">
-        <v>730</v>
-      </c>
-      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>757</v>
+      </c>
+      <c r="J176" t="s">
         <v>731</v>
       </c>
-      <c r="J176" t="s">
-        <v>757</v>
-      </c>
       <c r="K176" t="s">
+        <v>732</v>
+      </c>
+      <c r="L176" t="s">
         <v>733</v>
       </c>
       <c r="M176" t="s">
@@ -10353,24 +10353,24 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>760</v>
       </c>
       <c r="E177" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F177" t="s">
-        <v>760</v>
-      </c>
-      <c r="G177" t="s">
-        <v>730</v>
-      </c>
-      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>761</v>
+      </c>
+      <c r="J177" t="s">
         <v>731</v>
       </c>
-      <c r="J177" t="s">
-        <v>761</v>
-      </c>
       <c r="K177" t="s">
+        <v>732</v>
+      </c>
+      <c r="L177" t="s">
         <v>733</v>
       </c>
       <c r="M177" t="s">
@@ -10388,24 +10388,24 @@
         <v>15</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="E178" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F178" t="s">
-        <v>764</v>
-      </c>
-      <c r="G178" t="s">
-        <v>730</v>
-      </c>
-      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>765</v>
+      </c>
+      <c r="J178" t="s">
         <v>731</v>
       </c>
-      <c r="J178" t="s">
-        <v>765</v>
-      </c>
       <c r="K178" t="s">
+        <v>732</v>
+      </c>
+      <c r="L178" t="s">
         <v>733</v>
       </c>
       <c r="M178" t="s">
@@ -10423,24 +10423,24 @@
         <v>15</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
+        <v>768</v>
       </c>
       <c r="E179" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F179" t="s">
-        <v>768</v>
-      </c>
-      <c r="G179" t="s">
-        <v>730</v>
-      </c>
-      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>769</v>
+      </c>
+      <c r="J179" t="s">
         <v>731</v>
       </c>
-      <c r="J179" t="s">
-        <v>769</v>
-      </c>
       <c r="K179" t="s">
+        <v>732</v>
+      </c>
+      <c r="L179" t="s">
         <v>733</v>
       </c>
       <c r="M179" t="s">
@@ -10458,25 +10458,25 @@
         <v>15</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="E180" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F180" t="s">
-        <v>772</v>
-      </c>
-      <c r="G180" t="s">
-        <v>773</v>
-      </c>
-      <c r="H180" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" t="s">
         <v>774</v>
       </c>
       <c r="J180" t="s">
+        <v>731</v>
+      </c>
+      <c r="K180" t="s">
+        <v>732</v>
+      </c>
+      <c r="L180" t="s">
         <v>775</v>
-      </c>
-      <c r="K180" t="s">
-        <v>733</v>
       </c>
       <c r="M180" t="s">
         <v>23</v>
@@ -10493,31 +10493,31 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E181" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F181" t="s">
-        <v>778</v>
+        <v>18</v>
       </c>
       <c r="G181" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H181" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="I181" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="J181" t="s">
-        <v>780</v>
+        <v>731</v>
       </c>
       <c r="K181" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L181" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="M181" t="s">
         <v>23</v>
@@ -10534,31 +10534,31 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
-        <v>16</v>
+        <v>784</v>
       </c>
       <c r="E182" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F182" t="s">
-        <v>784</v>
+        <v>18</v>
       </c>
       <c r="G182" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H182" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="I182" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="J182" t="s">
-        <v>785</v>
+        <v>731</v>
       </c>
       <c r="K182" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L182" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="M182" t="s">
         <v>23</v>
@@ -10574,26 +10574,26 @@
       <c r="C183" t="s">
         <v>15</v>
       </c>
-      <c r="D183" t="s">
-        <v>16</v>
-      </c>
       <c r="E183" t="s">
-        <v>728</v>
+        <v>773</v>
+      </c>
+      <c r="F183" t="s">
+        <v>18</v>
       </c>
       <c r="G183" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H183" t="s">
-        <v>774</v>
-      </c>
-      <c r="I183" t="s">
-        <v>779</v>
+        <v>780</v>
+      </c>
+      <c r="J183" t="s">
+        <v>731</v>
       </c>
       <c r="K183" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L183" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="M183" t="s">
         <v>23</v>
@@ -10610,25 +10610,25 @@
         <v>15</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>790</v>
       </c>
       <c r="E184" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F184" t="s">
-        <v>790</v>
-      </c>
-      <c r="G184" t="s">
-        <v>773</v>
-      </c>
-      <c r="H184" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I184" t="s">
+        <v>791</v>
       </c>
       <c r="J184" t="s">
-        <v>791</v>
+        <v>731</v>
       </c>
       <c r="K184" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L184" t="s">
+        <v>775</v>
       </c>
       <c r="M184" t="s">
         <v>23</v>
@@ -10645,25 +10645,25 @@
         <v>15</v>
       </c>
       <c r="D185" t="s">
-        <v>16</v>
+        <v>794</v>
       </c>
       <c r="E185" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F185" t="s">
-        <v>794</v>
-      </c>
-      <c r="G185" t="s">
-        <v>773</v>
-      </c>
-      <c r="H185" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
+        <v>795</v>
       </c>
       <c r="J185" t="s">
-        <v>795</v>
+        <v>731</v>
       </c>
       <c r="K185" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L185" t="s">
+        <v>775</v>
       </c>
       <c r="M185" t="s">
         <v>23</v>
@@ -10680,25 +10680,25 @@
         <v>15</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>798</v>
       </c>
       <c r="E186" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F186" t="s">
-        <v>798</v>
-      </c>
-      <c r="G186" t="s">
-        <v>773</v>
-      </c>
-      <c r="H186" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
+        <v>799</v>
       </c>
       <c r="J186" t="s">
-        <v>799</v>
+        <v>731</v>
       </c>
       <c r="K186" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L186" t="s">
+        <v>775</v>
       </c>
       <c r="M186" t="s">
         <v>23</v>
@@ -10715,25 +10715,25 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>802</v>
       </c>
       <c r="E187" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F187" t="s">
-        <v>802</v>
-      </c>
-      <c r="G187" t="s">
-        <v>773</v>
-      </c>
-      <c r="H187" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I187" t="s">
+        <v>803</v>
       </c>
       <c r="J187" t="s">
-        <v>803</v>
+        <v>731</v>
       </c>
       <c r="K187" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L187" t="s">
+        <v>775</v>
       </c>
       <c r="M187" t="s">
         <v>23</v>
@@ -10750,25 +10750,25 @@
         <v>15</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
+        <v>806</v>
       </c>
       <c r="E188" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F188" t="s">
-        <v>806</v>
-      </c>
-      <c r="G188" t="s">
-        <v>773</v>
-      </c>
-      <c r="H188" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I188" t="s">
+        <v>807</v>
       </c>
       <c r="J188" t="s">
-        <v>807</v>
+        <v>731</v>
       </c>
       <c r="K188" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L188" t="s">
+        <v>775</v>
       </c>
       <c r="M188" t="s">
         <v>23</v>
@@ -10785,25 +10785,25 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="E189" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F189" t="s">
-        <v>810</v>
-      </c>
-      <c r="G189" t="s">
-        <v>773</v>
-      </c>
-      <c r="H189" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I189" t="s">
+        <v>811</v>
       </c>
       <c r="J189" t="s">
-        <v>811</v>
+        <v>731</v>
       </c>
       <c r="K189" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L189" t="s">
+        <v>775</v>
       </c>
       <c r="M189" t="s">
         <v>23</v>
@@ -10820,25 +10820,25 @@
         <v>15</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>814</v>
       </c>
       <c r="E190" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F190" t="s">
-        <v>814</v>
-      </c>
-      <c r="G190" t="s">
-        <v>773</v>
-      </c>
-      <c r="H190" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I190" t="s">
+        <v>815</v>
       </c>
       <c r="J190" t="s">
-        <v>815</v>
+        <v>731</v>
       </c>
       <c r="K190" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L190" t="s">
+        <v>775</v>
       </c>
       <c r="M190" t="s">
         <v>23</v>
@@ -10855,25 +10855,25 @@
         <v>15</v>
       </c>
       <c r="D191" t="s">
-        <v>16</v>
+        <v>818</v>
       </c>
       <c r="E191" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F191" t="s">
-        <v>818</v>
-      </c>
-      <c r="G191" t="s">
-        <v>773</v>
-      </c>
-      <c r="H191" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>819</v>
       </c>
       <c r="J191" t="s">
-        <v>819</v>
+        <v>731</v>
       </c>
       <c r="K191" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L191" t="s">
+        <v>775</v>
       </c>
       <c r="M191" t="s">
         <v>23</v>
@@ -10890,25 +10890,25 @@
         <v>15</v>
       </c>
       <c r="D192" t="s">
-        <v>16</v>
+        <v>822</v>
       </c>
       <c r="E192" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F192" t="s">
-        <v>822</v>
-      </c>
-      <c r="G192" t="s">
-        <v>773</v>
-      </c>
-      <c r="H192" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I192" t="s">
+        <v>823</v>
       </c>
       <c r="J192" t="s">
-        <v>823</v>
+        <v>731</v>
       </c>
       <c r="K192" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L192" t="s">
+        <v>775</v>
       </c>
       <c r="M192" t="s">
         <v>23</v>
@@ -10925,25 +10925,25 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>826</v>
       </c>
       <c r="E193" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F193" t="s">
-        <v>826</v>
-      </c>
-      <c r="G193" t="s">
-        <v>773</v>
-      </c>
-      <c r="H193" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>827</v>
       </c>
       <c r="J193" t="s">
-        <v>827</v>
+        <v>731</v>
       </c>
       <c r="K193" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L193" t="s">
+        <v>775</v>
       </c>
       <c r="M193" t="s">
         <v>23</v>
@@ -10960,25 +10960,25 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>830</v>
       </c>
       <c r="E194" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F194" t="s">
-        <v>830</v>
-      </c>
-      <c r="G194" t="s">
-        <v>773</v>
-      </c>
-      <c r="H194" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>831</v>
       </c>
       <c r="J194" t="s">
-        <v>831</v>
+        <v>731</v>
       </c>
       <c r="K194" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L194" t="s">
+        <v>775</v>
       </c>
       <c r="M194" t="s">
         <v>23</v>
@@ -10995,25 +10995,25 @@
         <v>15</v>
       </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>834</v>
       </c>
       <c r="E195" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F195" t="s">
-        <v>834</v>
-      </c>
-      <c r="G195" t="s">
-        <v>773</v>
-      </c>
-      <c r="H195" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>835</v>
       </c>
       <c r="J195" t="s">
-        <v>835</v>
+        <v>731</v>
       </c>
       <c r="K195" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L195" t="s">
+        <v>775</v>
       </c>
       <c r="M195" t="s">
         <v>23</v>
@@ -11030,25 +11030,25 @@
         <v>15</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>838</v>
       </c>
       <c r="E196" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="F196" t="s">
-        <v>838</v>
-      </c>
-      <c r="G196" t="s">
-        <v>773</v>
-      </c>
-      <c r="H196" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
+        <v>839</v>
       </c>
       <c r="J196" t="s">
-        <v>839</v>
+        <v>731</v>
       </c>
       <c r="K196" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L196" t="s">
+        <v>775</v>
       </c>
       <c r="M196" t="s">
         <v>23</v>
@@ -11065,25 +11065,25 @@
         <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>16</v>
+        <v>842</v>
       </c>
       <c r="E197" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F197" t="s">
-        <v>842</v>
-      </c>
-      <c r="G197" t="s">
-        <v>843</v>
-      </c>
-      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
         <v>844</v>
       </c>
       <c r="J197" t="s">
+        <v>731</v>
+      </c>
+      <c r="K197" t="s">
+        <v>732</v>
+      </c>
+      <c r="L197" t="s">
         <v>845</v>
-      </c>
-      <c r="K197" t="s">
-        <v>733</v>
       </c>
       <c r="M197" t="s">
         <v>23</v>
@@ -11100,25 +11100,25 @@
         <v>15</v>
       </c>
       <c r="D198" t="s">
-        <v>16</v>
+        <v>848</v>
       </c>
       <c r="E198" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F198" t="s">
-        <v>848</v>
-      </c>
-      <c r="G198" t="s">
-        <v>843</v>
-      </c>
-      <c r="H198" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I198" t="s">
+        <v>849</v>
       </c>
       <c r="J198" t="s">
-        <v>849</v>
+        <v>731</v>
       </c>
       <c r="K198" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L198" t="s">
+        <v>845</v>
       </c>
       <c r="M198" t="s">
         <v>23</v>
@@ -11135,25 +11135,25 @@
         <v>15</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>852</v>
       </c>
       <c r="E199" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F199" t="s">
-        <v>852</v>
-      </c>
-      <c r="G199" t="s">
-        <v>843</v>
-      </c>
-      <c r="H199" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>853</v>
       </c>
       <c r="J199" t="s">
-        <v>853</v>
+        <v>731</v>
       </c>
       <c r="K199" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L199" t="s">
+        <v>845</v>
       </c>
       <c r="M199" t="s">
         <v>23</v>
@@ -11170,25 +11170,25 @@
         <v>15</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
+        <v>856</v>
       </c>
       <c r="E200" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F200" t="s">
-        <v>856</v>
-      </c>
-      <c r="G200" t="s">
-        <v>843</v>
-      </c>
-      <c r="H200" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>857</v>
       </c>
       <c r="J200" t="s">
-        <v>857</v>
+        <v>731</v>
       </c>
       <c r="K200" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L200" t="s">
+        <v>845</v>
       </c>
       <c r="M200" t="s">
         <v>23</v>
@@ -11205,25 +11205,25 @@
         <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>860</v>
       </c>
       <c r="E201" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F201" t="s">
-        <v>860</v>
-      </c>
-      <c r="G201" t="s">
-        <v>843</v>
-      </c>
-      <c r="H201" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
+        <v>861</v>
       </c>
       <c r="J201" t="s">
-        <v>861</v>
+        <v>731</v>
       </c>
       <c r="K201" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L201" t="s">
+        <v>845</v>
       </c>
       <c r="M201" t="s">
         <v>23</v>
@@ -11240,25 +11240,25 @@
         <v>15</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
+        <v>864</v>
       </c>
       <c r="E202" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F202" t="s">
-        <v>864</v>
-      </c>
-      <c r="G202" t="s">
-        <v>843</v>
-      </c>
-      <c r="H202" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I202" t="s">
+        <v>865</v>
       </c>
       <c r="J202" t="s">
-        <v>865</v>
+        <v>731</v>
       </c>
       <c r="K202" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L202" t="s">
+        <v>845</v>
       </c>
       <c r="M202" t="s">
         <v>23</v>
@@ -11275,25 +11275,25 @@
         <v>15</v>
       </c>
       <c r="D203" t="s">
-        <v>16</v>
+        <v>868</v>
       </c>
       <c r="E203" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F203" t="s">
-        <v>868</v>
-      </c>
-      <c r="G203" t="s">
-        <v>843</v>
-      </c>
-      <c r="H203" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>869</v>
       </c>
       <c r="J203" t="s">
-        <v>869</v>
+        <v>731</v>
       </c>
       <c r="K203" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L203" t="s">
+        <v>845</v>
       </c>
       <c r="M203" t="s">
         <v>23</v>
@@ -11310,25 +11310,25 @@
         <v>15</v>
       </c>
       <c r="D204" t="s">
-        <v>16</v>
+        <v>872</v>
       </c>
       <c r="E204" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F204" t="s">
-        <v>872</v>
-      </c>
-      <c r="G204" t="s">
-        <v>843</v>
-      </c>
-      <c r="H204" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I204" t="s">
+        <v>873</v>
       </c>
       <c r="J204" t="s">
-        <v>873</v>
+        <v>731</v>
       </c>
       <c r="K204" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L204" t="s">
+        <v>845</v>
       </c>
       <c r="M204" t="s">
         <v>23</v>
@@ -11345,25 +11345,25 @@
         <v>15</v>
       </c>
       <c r="D205" t="s">
-        <v>16</v>
+        <v>876</v>
       </c>
       <c r="E205" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F205" t="s">
-        <v>876</v>
-      </c>
-      <c r="G205" t="s">
-        <v>843</v>
-      </c>
-      <c r="H205" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I205" t="s">
+        <v>877</v>
       </c>
       <c r="J205" t="s">
-        <v>877</v>
+        <v>731</v>
       </c>
       <c r="K205" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L205" t="s">
+        <v>845</v>
       </c>
       <c r="M205" t="s">
         <v>23</v>
@@ -11380,25 +11380,25 @@
         <v>15</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="E206" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F206" t="s">
-        <v>880</v>
-      </c>
-      <c r="G206" t="s">
-        <v>843</v>
-      </c>
-      <c r="H206" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I206" t="s">
+        <v>881</v>
       </c>
       <c r="J206" t="s">
-        <v>881</v>
+        <v>731</v>
       </c>
       <c r="K206" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L206" t="s">
+        <v>845</v>
       </c>
       <c r="M206" t="s">
         <v>23</v>
@@ -11415,25 +11415,25 @@
         <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>16</v>
+        <v>884</v>
       </c>
       <c r="E207" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F207" t="s">
-        <v>884</v>
-      </c>
-      <c r="G207" t="s">
-        <v>843</v>
-      </c>
-      <c r="H207" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I207" t="s">
+        <v>885</v>
       </c>
       <c r="J207" t="s">
-        <v>885</v>
+        <v>731</v>
       </c>
       <c r="K207" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L207" t="s">
+        <v>845</v>
       </c>
       <c r="M207" t="s">
         <v>23</v>
@@ -11450,25 +11450,25 @@
         <v>15</v>
       </c>
       <c r="D208" t="s">
-        <v>16</v>
+        <v>888</v>
       </c>
       <c r="E208" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F208" t="s">
-        <v>888</v>
-      </c>
-      <c r="G208" t="s">
-        <v>843</v>
-      </c>
-      <c r="H208" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I208" t="s">
+        <v>889</v>
       </c>
       <c r="J208" t="s">
-        <v>889</v>
+        <v>731</v>
       </c>
       <c r="K208" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L208" t="s">
+        <v>845</v>
       </c>
       <c r="M208" t="s">
         <v>23</v>
@@ -11485,25 +11485,25 @@
         <v>15</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
+        <v>892</v>
       </c>
       <c r="E209" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F209" t="s">
-        <v>892</v>
-      </c>
-      <c r="G209" t="s">
-        <v>843</v>
-      </c>
-      <c r="H209" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I209" t="s">
+        <v>893</v>
       </c>
       <c r="J209" t="s">
-        <v>893</v>
+        <v>731</v>
       </c>
       <c r="K209" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L209" t="s">
+        <v>845</v>
       </c>
       <c r="M209" t="s">
         <v>23</v>
@@ -11520,25 +11520,25 @@
         <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>16</v>
+        <v>896</v>
       </c>
       <c r="E210" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F210" t="s">
-        <v>896</v>
-      </c>
-      <c r="G210" t="s">
-        <v>843</v>
-      </c>
-      <c r="H210" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I210" t="s">
+        <v>897</v>
       </c>
       <c r="J210" t="s">
-        <v>897</v>
+        <v>731</v>
       </c>
       <c r="K210" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L210" t="s">
+        <v>845</v>
       </c>
       <c r="M210" t="s">
         <v>23</v>
@@ -11555,25 +11555,25 @@
         <v>15</v>
       </c>
       <c r="D211" t="s">
-        <v>16</v>
+        <v>900</v>
       </c>
       <c r="E211" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F211" t="s">
-        <v>900</v>
-      </c>
-      <c r="G211" t="s">
-        <v>843</v>
-      </c>
-      <c r="H211" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I211" t="s">
+        <v>901</v>
       </c>
       <c r="J211" t="s">
-        <v>901</v>
+        <v>731</v>
       </c>
       <c r="K211" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L211" t="s">
+        <v>845</v>
       </c>
       <c r="M211" t="s">
         <v>23</v>
@@ -11590,25 +11590,25 @@
         <v>15</v>
       </c>
       <c r="D212" t="s">
-        <v>16</v>
+        <v>904</v>
       </c>
       <c r="E212" t="s">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="F212" t="s">
-        <v>904</v>
-      </c>
-      <c r="G212" t="s">
-        <v>843</v>
-      </c>
-      <c r="H212" t="s">
-        <v>844</v>
+        <v>18</v>
+      </c>
+      <c r="I212" t="s">
+        <v>905</v>
       </c>
       <c r="J212" t="s">
-        <v>905</v>
+        <v>731</v>
       </c>
       <c r="K212" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L212" t="s">
+        <v>845</v>
       </c>
       <c r="M212" t="s">
         <v>23</v>
@@ -11625,25 +11625,25 @@
         <v>15</v>
       </c>
       <c r="D213" t="s">
-        <v>16</v>
+        <v>908</v>
       </c>
       <c r="E213" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F213" t="s">
-        <v>908</v>
-      </c>
-      <c r="G213" t="s">
-        <v>909</v>
-      </c>
-      <c r="H213" t="s">
+        <v>18</v>
+      </c>
+      <c r="I213" t="s">
         <v>910</v>
       </c>
       <c r="J213" t="s">
+        <v>731</v>
+      </c>
+      <c r="K213" t="s">
+        <v>732</v>
+      </c>
+      <c r="L213" t="s">
         <v>911</v>
-      </c>
-      <c r="K213" t="s">
-        <v>733</v>
       </c>
       <c r="M213" t="s">
         <v>23</v>
@@ -11660,25 +11660,25 @@
         <v>15</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>914</v>
       </c>
       <c r="E214" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F214" t="s">
-        <v>914</v>
-      </c>
-      <c r="G214" t="s">
-        <v>909</v>
-      </c>
-      <c r="H214" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I214" t="s">
+        <v>915</v>
       </c>
       <c r="J214" t="s">
-        <v>915</v>
+        <v>731</v>
       </c>
       <c r="K214" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L214" t="s">
+        <v>911</v>
       </c>
       <c r="M214" t="s">
         <v>23</v>
@@ -11695,25 +11695,25 @@
         <v>15</v>
       </c>
       <c r="D215" t="s">
-        <v>16</v>
+        <v>918</v>
       </c>
       <c r="E215" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F215" t="s">
-        <v>918</v>
-      </c>
-      <c r="G215" t="s">
-        <v>909</v>
-      </c>
-      <c r="H215" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I215" t="s">
+        <v>919</v>
       </c>
       <c r="J215" t="s">
-        <v>919</v>
+        <v>731</v>
       </c>
       <c r="K215" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L215" t="s">
+        <v>911</v>
       </c>
       <c r="M215" t="s">
         <v>23</v>
@@ -11730,25 +11730,25 @@
         <v>15</v>
       </c>
       <c r="D216" t="s">
-        <v>16</v>
+        <v>922</v>
       </c>
       <c r="E216" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F216" t="s">
-        <v>922</v>
-      </c>
-      <c r="G216" t="s">
-        <v>909</v>
-      </c>
-      <c r="H216" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I216" t="s">
+        <v>923</v>
       </c>
       <c r="J216" t="s">
-        <v>923</v>
+        <v>731</v>
       </c>
       <c r="K216" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L216" t="s">
+        <v>911</v>
       </c>
       <c r="M216" t="s">
         <v>23</v>
@@ -11765,25 +11765,25 @@
         <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
+        <v>926</v>
       </c>
       <c r="E217" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F217" t="s">
-        <v>926</v>
-      </c>
-      <c r="G217" t="s">
-        <v>909</v>
-      </c>
-      <c r="H217" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I217" t="s">
+        <v>927</v>
       </c>
       <c r="J217" t="s">
-        <v>927</v>
+        <v>731</v>
       </c>
       <c r="K217" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L217" t="s">
+        <v>911</v>
       </c>
       <c r="M217" t="s">
         <v>23</v>
@@ -11800,25 +11800,25 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>930</v>
       </c>
       <c r="E218" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F218" t="s">
-        <v>930</v>
-      </c>
-      <c r="G218" t="s">
-        <v>909</v>
-      </c>
-      <c r="H218" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I218" t="s">
+        <v>931</v>
       </c>
       <c r="J218" t="s">
-        <v>931</v>
+        <v>731</v>
       </c>
       <c r="K218" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L218" t="s">
+        <v>911</v>
       </c>
       <c r="M218" t="s">
         <v>23</v>
@@ -11835,25 +11835,25 @@
         <v>15</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>934</v>
       </c>
       <c r="E219" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F219" t="s">
-        <v>934</v>
-      </c>
-      <c r="G219" t="s">
-        <v>909</v>
-      </c>
-      <c r="H219" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I219" t="s">
+        <v>935</v>
       </c>
       <c r="J219" t="s">
-        <v>935</v>
+        <v>731</v>
       </c>
       <c r="K219" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L219" t="s">
+        <v>911</v>
       </c>
       <c r="M219" t="s">
         <v>23</v>
@@ -11870,25 +11870,25 @@
         <v>15</v>
       </c>
       <c r="D220" t="s">
-        <v>16</v>
+        <v>938</v>
       </c>
       <c r="E220" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F220" t="s">
-        <v>938</v>
-      </c>
-      <c r="G220" t="s">
-        <v>909</v>
-      </c>
-      <c r="H220" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I220" t="s">
+        <v>939</v>
       </c>
       <c r="J220" t="s">
-        <v>939</v>
+        <v>731</v>
       </c>
       <c r="K220" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L220" t="s">
+        <v>911</v>
       </c>
       <c r="M220" t="s">
         <v>23</v>
@@ -11905,25 +11905,25 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>942</v>
       </c>
       <c r="E221" t="s">
-        <v>728</v>
+        <v>909</v>
       </c>
       <c r="F221" t="s">
-        <v>942</v>
-      </c>
-      <c r="G221" t="s">
-        <v>909</v>
-      </c>
-      <c r="H221" t="s">
-        <v>910</v>
+        <v>18</v>
+      </c>
+      <c r="I221" t="s">
+        <v>943</v>
       </c>
       <c r="J221" t="s">
-        <v>943</v>
+        <v>731</v>
       </c>
       <c r="K221" t="s">
-        <v>733</v>
+        <v>732</v>
+      </c>
+      <c r="L221" t="s">
+        <v>911</v>
       </c>
       <c r="M221" t="s">
         <v>23</v>
@@ -11940,24 +11940,24 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
       <c r="E222" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F222" t="s">
-        <v>947</v>
-      </c>
-      <c r="G222" t="s">
+        <v>18</v>
+      </c>
+      <c r="I222" t="s">
         <v>948</v>
       </c>
-      <c r="H222" t="s">
+      <c r="J222" t="s">
         <v>949</v>
       </c>
-      <c r="J222" t="s">
+      <c r="K222" t="s">
         <v>950</v>
       </c>
-      <c r="K222" t="s">
+      <c r="L222" t="s">
         <v>951</v>
       </c>
       <c r="M222" t="s">
@@ -11975,24 +11975,24 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
-        <v>16</v>
+        <v>954</v>
       </c>
       <c r="E223" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F223" t="s">
-        <v>954</v>
-      </c>
-      <c r="G223" t="s">
-        <v>948</v>
-      </c>
-      <c r="H223" t="s">
+        <v>18</v>
+      </c>
+      <c r="I223" t="s">
+        <v>955</v>
+      </c>
+      <c r="J223" t="s">
         <v>949</v>
       </c>
-      <c r="J223" t="s">
-        <v>955</v>
-      </c>
       <c r="K223" t="s">
+        <v>950</v>
+      </c>
+      <c r="L223" t="s">
         <v>951</v>
       </c>
       <c r="M223" t="s">
@@ -12010,24 +12010,24 @@
         <v>15</v>
       </c>
       <c r="D224" t="s">
-        <v>16</v>
+        <v>958</v>
       </c>
       <c r="E224" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F224" t="s">
-        <v>958</v>
-      </c>
-      <c r="G224" t="s">
-        <v>948</v>
-      </c>
-      <c r="H224" t="s">
+        <v>18</v>
+      </c>
+      <c r="I224" t="s">
+        <v>959</v>
+      </c>
+      <c r="J224" t="s">
         <v>949</v>
       </c>
-      <c r="J224" t="s">
-        <v>959</v>
-      </c>
       <c r="K224" t="s">
+        <v>950</v>
+      </c>
+      <c r="L224" t="s">
         <v>951</v>
       </c>
       <c r="M224" t="s">
@@ -12045,24 +12045,24 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>16</v>
+        <v>962</v>
       </c>
       <c r="E225" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F225" t="s">
-        <v>962</v>
-      </c>
-      <c r="G225" t="s">
-        <v>948</v>
-      </c>
-      <c r="H225" t="s">
+        <v>18</v>
+      </c>
+      <c r="I225" t="s">
+        <v>963</v>
+      </c>
+      <c r="J225" t="s">
         <v>949</v>
       </c>
-      <c r="J225" t="s">
-        <v>963</v>
-      </c>
       <c r="K225" t="s">
+        <v>950</v>
+      </c>
+      <c r="L225" t="s">
         <v>951</v>
       </c>
       <c r="M225" t="s">
@@ -12080,24 +12080,24 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>966</v>
       </c>
       <c r="E226" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F226" t="s">
-        <v>966</v>
-      </c>
-      <c r="G226" t="s">
-        <v>948</v>
-      </c>
-      <c r="H226" t="s">
+        <v>18</v>
+      </c>
+      <c r="I226" t="s">
+        <v>967</v>
+      </c>
+      <c r="J226" t="s">
         <v>949</v>
       </c>
-      <c r="J226" t="s">
-        <v>967</v>
-      </c>
       <c r="K226" t="s">
+        <v>950</v>
+      </c>
+      <c r="L226" t="s">
         <v>951</v>
       </c>
       <c r="M226" t="s">
@@ -12115,24 +12115,24 @@
         <v>15</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="E227" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F227" t="s">
-        <v>970</v>
-      </c>
-      <c r="G227" t="s">
-        <v>948</v>
-      </c>
-      <c r="H227" t="s">
+        <v>18</v>
+      </c>
+      <c r="I227" t="s">
+        <v>971</v>
+      </c>
+      <c r="J227" t="s">
         <v>949</v>
       </c>
-      <c r="J227" t="s">
-        <v>971</v>
-      </c>
       <c r="K227" t="s">
+        <v>950</v>
+      </c>
+      <c r="L227" t="s">
         <v>951</v>
       </c>
       <c r="M227" t="s">
@@ -12150,25 +12150,25 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>16</v>
+        <v>974</v>
       </c>
       <c r="E228" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
       <c r="F228" t="s">
-        <v>974</v>
-      </c>
-      <c r="G228" t="s">
-        <v>975</v>
-      </c>
-      <c r="H228" t="s">
+        <v>18</v>
+      </c>
+      <c r="I228" t="s">
         <v>976</v>
       </c>
       <c r="J228" t="s">
+        <v>949</v>
+      </c>
+      <c r="K228" t="s">
+        <v>950</v>
+      </c>
+      <c r="L228" t="s">
         <v>977</v>
-      </c>
-      <c r="K228" t="s">
-        <v>951</v>
       </c>
       <c r="M228" t="s">
         <v>23</v>
@@ -12185,25 +12185,25 @@
         <v>15</v>
       </c>
       <c r="D229" t="s">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="E229" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
       <c r="F229" t="s">
-        <v>980</v>
-      </c>
-      <c r="G229" t="s">
-        <v>975</v>
-      </c>
-      <c r="H229" t="s">
-        <v>976</v>
+        <v>18</v>
+      </c>
+      <c r="I229" t="s">
+        <v>981</v>
       </c>
       <c r="J229" t="s">
-        <v>981</v>
+        <v>949</v>
       </c>
       <c r="K229" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L229" t="s">
+        <v>977</v>
       </c>
       <c r="M229" t="s">
         <v>23</v>
@@ -12220,25 +12220,25 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>984</v>
       </c>
       <c r="E230" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
       <c r="F230" t="s">
-        <v>984</v>
-      </c>
-      <c r="G230" t="s">
-        <v>975</v>
-      </c>
-      <c r="H230" t="s">
-        <v>976</v>
+        <v>18</v>
+      </c>
+      <c r="I230" t="s">
+        <v>985</v>
       </c>
       <c r="J230" t="s">
-        <v>985</v>
+        <v>949</v>
       </c>
       <c r="K230" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L230" t="s">
+        <v>977</v>
       </c>
       <c r="M230" t="s">
         <v>23</v>
@@ -12255,25 +12255,25 @@
         <v>15</v>
       </c>
       <c r="D231" t="s">
-        <v>16</v>
+        <v>988</v>
       </c>
       <c r="E231" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
       <c r="F231" t="s">
-        <v>988</v>
-      </c>
-      <c r="G231" t="s">
-        <v>975</v>
-      </c>
-      <c r="H231" t="s">
-        <v>976</v>
+        <v>18</v>
+      </c>
+      <c r="I231" t="s">
+        <v>989</v>
       </c>
       <c r="J231" t="s">
-        <v>989</v>
+        <v>949</v>
       </c>
       <c r="K231" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L231" t="s">
+        <v>977</v>
       </c>
       <c r="M231" t="s">
         <v>23</v>
@@ -12290,25 +12290,25 @@
         <v>15</v>
       </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>992</v>
       </c>
       <c r="E232" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
       <c r="F232" t="s">
-        <v>992</v>
-      </c>
-      <c r="G232" t="s">
-        <v>975</v>
-      </c>
-      <c r="H232" t="s">
-        <v>976</v>
+        <v>18</v>
+      </c>
+      <c r="I232" t="s">
+        <v>993</v>
       </c>
       <c r="J232" t="s">
-        <v>993</v>
+        <v>949</v>
       </c>
       <c r="K232" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L232" t="s">
+        <v>977</v>
       </c>
       <c r="M232" t="s">
         <v>23</v>
@@ -12325,25 +12325,25 @@
         <v>15</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>996</v>
       </c>
       <c r="E233" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F233" t="s">
-        <v>996</v>
-      </c>
-      <c r="G233" t="s">
-        <v>997</v>
-      </c>
-      <c r="H233" t="s">
+        <v>18</v>
+      </c>
+      <c r="I233" t="s">
         <v>998</v>
       </c>
       <c r="J233" t="s">
+        <v>949</v>
+      </c>
+      <c r="K233" t="s">
+        <v>950</v>
+      </c>
+      <c r="L233" t="s">
         <v>999</v>
-      </c>
-      <c r="K233" t="s">
-        <v>951</v>
       </c>
       <c r="M233" t="s">
         <v>23</v>
@@ -12360,25 +12360,25 @@
         <v>15</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
+        <v>1002</v>
       </c>
       <c r="E234" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F234" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G234" t="s">
-        <v>997</v>
-      </c>
-      <c r="H234" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I234" t="s">
+        <v>1003</v>
       </c>
       <c r="J234" t="s">
-        <v>1003</v>
+        <v>949</v>
       </c>
       <c r="K234" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L234" t="s">
+        <v>999</v>
       </c>
       <c r="M234" t="s">
         <v>23</v>
@@ -12395,25 +12395,25 @@
         <v>15</v>
       </c>
       <c r="D235" t="s">
-        <v>16</v>
+        <v>1006</v>
       </c>
       <c r="E235" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F235" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G235" t="s">
-        <v>997</v>
-      </c>
-      <c r="H235" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I235" t="s">
+        <v>1007</v>
       </c>
       <c r="J235" t="s">
-        <v>1007</v>
+        <v>949</v>
       </c>
       <c r="K235" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L235" t="s">
+        <v>999</v>
       </c>
       <c r="M235" t="s">
         <v>23</v>
@@ -12430,25 +12430,25 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>1010</v>
       </c>
       <c r="E236" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F236" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G236" t="s">
-        <v>997</v>
-      </c>
-      <c r="H236" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I236" t="s">
+        <v>1011</v>
       </c>
       <c r="J236" t="s">
-        <v>1011</v>
+        <v>949</v>
       </c>
       <c r="K236" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L236" t="s">
+        <v>999</v>
       </c>
       <c r="M236" t="s">
         <v>23</v>
@@ -12465,25 +12465,25 @@
         <v>15</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>1014</v>
       </c>
       <c r="E237" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F237" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G237" t="s">
-        <v>997</v>
-      </c>
-      <c r="H237" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I237" t="s">
+        <v>1015</v>
       </c>
       <c r="J237" t="s">
-        <v>1015</v>
+        <v>949</v>
       </c>
       <c r="K237" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L237" t="s">
+        <v>999</v>
       </c>
       <c r="M237" t="s">
         <v>23</v>
@@ -12500,25 +12500,25 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>16</v>
+        <v>1018</v>
       </c>
       <c r="E238" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F238" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G238" t="s">
-        <v>997</v>
-      </c>
-      <c r="H238" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I238" t="s">
+        <v>1019</v>
       </c>
       <c r="J238" t="s">
-        <v>1019</v>
+        <v>949</v>
       </c>
       <c r="K238" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L238" t="s">
+        <v>999</v>
       </c>
       <c r="M238" t="s">
         <v>23</v>
@@ -12535,25 +12535,25 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>16</v>
+        <v>1022</v>
       </c>
       <c r="E239" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F239" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G239" t="s">
-        <v>997</v>
-      </c>
-      <c r="H239" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I239" t="s">
+        <v>1023</v>
       </c>
       <c r="J239" t="s">
-        <v>1023</v>
+        <v>949</v>
       </c>
       <c r="K239" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L239" t="s">
+        <v>999</v>
       </c>
       <c r="M239" t="s">
         <v>23</v>
@@ -12570,25 +12570,25 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>16</v>
+        <v>1026</v>
       </c>
       <c r="E240" t="s">
-        <v>946</v>
+        <v>997</v>
       </c>
       <c r="F240" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G240" t="s">
-        <v>997</v>
-      </c>
-      <c r="H240" t="s">
-        <v>998</v>
+        <v>18</v>
+      </c>
+      <c r="I240" t="s">
+        <v>1027</v>
       </c>
       <c r="J240" t="s">
-        <v>1027</v>
+        <v>949</v>
       </c>
       <c r="K240" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L240" t="s">
+        <v>999</v>
       </c>
       <c r="M240" t="s">
         <v>23</v>
@@ -12605,25 +12605,25 @@
         <v>15</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="E241" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F241" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G241" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H241" t="s">
+        <v>18</v>
+      </c>
+      <c r="I241" t="s">
         <v>1032</v>
       </c>
       <c r="J241" t="s">
+        <v>949</v>
+      </c>
+      <c r="K241" t="s">
+        <v>950</v>
+      </c>
+      <c r="L241" t="s">
         <v>1033</v>
-      </c>
-      <c r="K241" t="s">
-        <v>951</v>
       </c>
       <c r="M241" t="s">
         <v>23</v>
@@ -12640,25 +12640,25 @@
         <v>15</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>1036</v>
       </c>
       <c r="E242" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F242" t="s">
-        <v>1036</v>
-      </c>
-      <c r="G242" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H242" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I242" t="s">
+        <v>1037</v>
       </c>
       <c r="J242" t="s">
-        <v>1037</v>
+        <v>949</v>
       </c>
       <c r="K242" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1033</v>
       </c>
       <c r="M242" t="s">
         <v>23</v>
@@ -12675,25 +12675,25 @@
         <v>15</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
+        <v>1040</v>
       </c>
       <c r="E243" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F243" t="s">
-        <v>1040</v>
-      </c>
-      <c r="G243" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H243" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I243" t="s">
+        <v>1041</v>
       </c>
       <c r="J243" t="s">
-        <v>1041</v>
+        <v>949</v>
       </c>
       <c r="K243" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1033</v>
       </c>
       <c r="M243" t="s">
         <v>23</v>
@@ -12710,25 +12710,25 @@
         <v>15</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
+        <v>1044</v>
       </c>
       <c r="E244" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F244" t="s">
-        <v>1044</v>
-      </c>
-      <c r="G244" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H244" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I244" t="s">
+        <v>1045</v>
       </c>
       <c r="J244" t="s">
-        <v>1045</v>
+        <v>949</v>
       </c>
       <c r="K244" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1033</v>
       </c>
       <c r="M244" t="s">
         <v>23</v>
@@ -12745,25 +12745,25 @@
         <v>15</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>1048</v>
       </c>
       <c r="E245" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F245" t="s">
-        <v>1048</v>
-      </c>
-      <c r="G245" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H245" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I245" t="s">
+        <v>1049</v>
       </c>
       <c r="J245" t="s">
-        <v>1049</v>
+        <v>949</v>
       </c>
       <c r="K245" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1033</v>
       </c>
       <c r="M245" t="s">
         <v>23</v>
@@ -12780,25 +12780,25 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>1052</v>
       </c>
       <c r="E246" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F246" t="s">
-        <v>1052</v>
-      </c>
-      <c r="G246" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H246" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I246" t="s">
+        <v>1053</v>
       </c>
       <c r="J246" t="s">
-        <v>1053</v>
+        <v>949</v>
       </c>
       <c r="K246" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L246" t="s">
+        <v>1033</v>
       </c>
       <c r="M246" t="s">
         <v>23</v>
@@ -12815,25 +12815,25 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>1056</v>
       </c>
       <c r="E247" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F247" t="s">
-        <v>1056</v>
-      </c>
-      <c r="G247" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H247" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I247" t="s">
+        <v>1057</v>
       </c>
       <c r="J247" t="s">
-        <v>1057</v>
+        <v>949</v>
       </c>
       <c r="K247" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L247" t="s">
+        <v>1033</v>
       </c>
       <c r="M247" t="s">
         <v>23</v>
@@ -12850,25 +12850,25 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>1060</v>
       </c>
       <c r="E248" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F248" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G248" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H248" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I248" t="s">
+        <v>1061</v>
       </c>
       <c r="J248" t="s">
-        <v>1061</v>
+        <v>949</v>
       </c>
       <c r="K248" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L248" t="s">
+        <v>1033</v>
       </c>
       <c r="M248" t="s">
         <v>23</v>
@@ -12885,25 +12885,25 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>1064</v>
       </c>
       <c r="E249" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F249" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G249" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H249" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I249" t="s">
+        <v>1065</v>
       </c>
       <c r="J249" t="s">
-        <v>1065</v>
+        <v>949</v>
       </c>
       <c r="K249" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L249" t="s">
+        <v>1033</v>
       </c>
       <c r="M249" t="s">
         <v>23</v>
@@ -12920,25 +12920,25 @@
         <v>15</v>
       </c>
       <c r="D250" t="s">
-        <v>16</v>
+        <v>1068</v>
       </c>
       <c r="E250" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
       <c r="F250" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G250" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H250" t="s">
-        <v>1032</v>
+        <v>18</v>
+      </c>
+      <c r="I250" t="s">
+        <v>1069</v>
       </c>
       <c r="J250" t="s">
-        <v>1069</v>
+        <v>949</v>
       </c>
       <c r="K250" t="s">
-        <v>951</v>
+        <v>950</v>
+      </c>
+      <c r="L250" t="s">
+        <v>1033</v>
       </c>
       <c r="M250" t="s">
         <v>23</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,33 +25,33 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
     <t>codeforiati:global-name</t>
   </si>
   <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
@@ -64,27 +64,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
     <t>015</t>
   </si>
   <si>
     <t>World</t>
   </si>
   <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>DZA</t>
   </si>
   <si>
@@ -166,21 +166,21 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
     <t>419</t>
   </si>
   <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
     <t>AIA</t>
   </si>
   <si>
@@ -1486,15 +1486,15 @@
     <t>Bermuda</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
     <t>021</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
     <t>BMU</t>
   </si>
   <si>
@@ -1564,21 +1564,21 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
     <t>KAZ</t>
   </si>
   <si>
@@ -1636,15 +1636,15 @@
     <t>China</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
     <t>CHN</t>
   </si>
   <si>
@@ -1726,15 +1726,15 @@
     <t>Brunei Darussalam</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
     <t>035</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
-    <t>BN</t>
-  </si>
-  <si>
     <t>BRN</t>
   </si>
   <si>
@@ -1864,15 +1864,15 @@
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
     <t>AFG</t>
   </si>
   <si>
@@ -1978,15 +1978,15 @@
     <t>Armenia</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
     <t>ARM</t>
   </si>
   <si>
@@ -2200,21 +2200,21 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>BLR</t>
   </si>
   <si>
@@ -2332,15 +2332,15 @@
     <t>Åland Islands</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
     <t>154</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
     <t>ALA</t>
   </si>
   <si>
@@ -2542,15 +2542,15 @@
     <t>Albania</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
     <t>039</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
     <t>ALB</t>
   </si>
   <si>
@@ -2740,15 +2740,15 @@
     <t>Austria</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
-    <t>AT</t>
-  </si>
-  <si>
     <t>AUT</t>
   </si>
   <si>
@@ -2854,21 +2854,21 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>009</t>
-  </si>
-  <si>
     <t>AUS</t>
   </si>
   <si>
@@ -2938,15 +2938,15 @@
     <t>Fiji</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
+    <t>FJ</t>
+  </si>
+  <si>
     <t>054</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
-    <t>FJ</t>
-  </si>
-  <si>
     <t>FJI</t>
   </si>
   <si>
@@ -3004,15 +3004,15 @@
     <t>Guam</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
+    <t>GU</t>
+  </si>
+  <si>
     <t>057</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
-    <t>GU</t>
-  </si>
-  <si>
     <t>GUM</t>
   </si>
   <si>
@@ -3106,13 +3106,13 @@
     <t>American Samoa</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
-  </si>
-  <si>
-    <t>AS</t>
   </si>
   <si>
     <t>ASM</t>
@@ -3624,7 +3624,7 @@
       <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
       <c r="L2" t="s">
@@ -3654,12 +3654,12 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
@@ -3689,12 +3689,12 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>21</v>
       </c>
       <c r="L4" t="s">
@@ -3724,12 +3724,12 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>21</v>
       </c>
       <c r="L5" t="s">
@@ -3759,12 +3759,12 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
         <v>38</v>
       </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>21</v>
       </c>
       <c r="L6" t="s">
@@ -3794,12 +3794,12 @@
         <v>18</v>
       </c>
       <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
         <v>42</v>
       </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7" t="s">
@@ -3829,12 +3829,12 @@
         <v>18</v>
       </c>
       <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s">
         <v>46</v>
       </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>21</v>
       </c>
       <c r="L8" t="s">
@@ -3864,16 +3864,16 @@
         <v>51</v>
       </c>
       <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s">
         <v>52</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>53</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>21</v>
       </c>
       <c r="K9" t="s">
         <v>54</v>
@@ -3905,16 +3905,16 @@
         <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
         <v>58</v>
       </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K10" t="s">
         <v>54</v>
@@ -3946,16 +3946,16 @@
         <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
         <v>62</v>
       </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
@@ -3987,16 +3987,16 @@
         <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
         <v>66</v>
       </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
@@ -4028,16 +4028,16 @@
         <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
         <v>70</v>
       </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
         <v>54</v>
@@ -4069,16 +4069,16 @@
         <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
         <v>74</v>
       </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K14" t="s">
         <v>54</v>
@@ -4110,16 +4110,16 @@
         <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
         <v>78</v>
       </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K15" t="s">
         <v>54</v>
@@ -4151,16 +4151,16 @@
         <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
         <v>82</v>
       </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
         <v>54</v>
@@ -4192,16 +4192,16 @@
         <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
         <v>86</v>
       </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
       <c r="J17" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K17" t="s">
         <v>54</v>
@@ -4233,16 +4233,16 @@
         <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
         <v>90</v>
       </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
       <c r="J18" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K18" t="s">
         <v>54</v>
@@ -4274,16 +4274,16 @@
         <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
         <v>94</v>
       </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K19" t="s">
         <v>54</v>
@@ -4315,16 +4315,16 @@
         <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
         <v>98</v>
       </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
       <c r="J20" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K20" t="s">
         <v>54</v>
@@ -4356,16 +4356,16 @@
         <v>51</v>
       </c>
       <c r="G21" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
         <v>102</v>
       </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
       <c r="J21" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K21" t="s">
         <v>54</v>
@@ -4397,16 +4397,16 @@
         <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
         <v>106</v>
       </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
       <c r="J22" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K22" t="s">
         <v>54</v>
@@ -4438,16 +4438,16 @@
         <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
         <v>110</v>
       </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
       <c r="J23" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K23" t="s">
         <v>54</v>
@@ -4479,16 +4479,16 @@
         <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
         <v>114</v>
       </c>
-      <c r="I24" t="s">
-        <v>20</v>
-      </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K24" t="s">
         <v>54</v>
@@ -4520,16 +4520,16 @@
         <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
         <v>118</v>
       </c>
-      <c r="I25" t="s">
-        <v>20</v>
-      </c>
       <c r="J25" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K25" t="s">
         <v>54</v>
@@ -4561,16 +4561,16 @@
         <v>51</v>
       </c>
       <c r="G26" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
         <v>122</v>
       </c>
-      <c r="I26" t="s">
-        <v>20</v>
-      </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K26" t="s">
         <v>54</v>
@@ -4602,16 +4602,16 @@
         <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
         <v>126</v>
       </c>
-      <c r="I27" t="s">
-        <v>20</v>
-      </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K27" t="s">
         <v>54</v>
@@ -4643,16 +4643,16 @@
         <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" t="s">
         <v>130</v>
       </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
       <c r="J28" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K28" t="s">
         <v>54</v>
@@ -4684,16 +4684,16 @@
         <v>51</v>
       </c>
       <c r="G29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" t="s">
         <v>134</v>
       </c>
-      <c r="I29" t="s">
-        <v>20</v>
-      </c>
       <c r="J29" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
         <v>54</v>
@@ -4725,16 +4725,16 @@
         <v>51</v>
       </c>
       <c r="G30" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s">
         <v>138</v>
       </c>
-      <c r="I30" t="s">
-        <v>20</v>
-      </c>
       <c r="J30" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K30" t="s">
         <v>54</v>
@@ -4766,19 +4766,19 @@
         <v>142</v>
       </c>
       <c r="G31" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" t="s">
         <v>143</v>
       </c>
-      <c r="I31" t="s">
-        <v>20</v>
-      </c>
       <c r="J31" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K31" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
@@ -4807,19 +4807,19 @@
         <v>142</v>
       </c>
       <c r="G32" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" t="s">
         <v>148</v>
       </c>
-      <c r="I32" t="s">
-        <v>20</v>
-      </c>
       <c r="J32" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K32" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -4848,19 +4848,19 @@
         <v>142</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" t="s">
         <v>152</v>
       </c>
-      <c r="I33" t="s">
-        <v>20</v>
-      </c>
       <c r="J33" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K33" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -4889,19 +4889,19 @@
         <v>142</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H34" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" t="s">
         <v>156</v>
       </c>
-      <c r="I34" t="s">
-        <v>20</v>
-      </c>
       <c r="J34" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K34" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
@@ -4930,19 +4930,19 @@
         <v>142</v>
       </c>
       <c r="G35" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H35" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" t="s">
         <v>160</v>
       </c>
-      <c r="I35" t="s">
-        <v>20</v>
-      </c>
       <c r="J35" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K35" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
@@ -4971,19 +4971,19 @@
         <v>142</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" t="s">
         <v>164</v>
       </c>
-      <c r="I36" t="s">
-        <v>20</v>
-      </c>
       <c r="J36" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K36" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L36" t="s">
         <v>22</v>
@@ -5012,19 +5012,19 @@
         <v>142</v>
       </c>
       <c r="G37" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H37" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" t="s">
         <v>168</v>
       </c>
-      <c r="I37" t="s">
-        <v>20</v>
-      </c>
       <c r="J37" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K37" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L37" t="s">
         <v>22</v>
@@ -5053,19 +5053,19 @@
         <v>142</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H38" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" t="s">
         <v>172</v>
       </c>
-      <c r="I38" t="s">
-        <v>20</v>
-      </c>
       <c r="J38" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K38" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L38" t="s">
         <v>22</v>
@@ -5094,19 +5094,19 @@
         <v>142</v>
       </c>
       <c r="G39" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H39" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" t="s">
         <v>176</v>
       </c>
-      <c r="I39" t="s">
-        <v>20</v>
-      </c>
       <c r="J39" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K39" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="L39" t="s">
         <v>22</v>
@@ -5135,19 +5135,19 @@
         <v>180</v>
       </c>
       <c r="G40" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
         <v>181</v>
       </c>
-      <c r="I40" t="s">
-        <v>20</v>
-      </c>
       <c r="J40" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="K40" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="L40" t="s">
         <v>22</v>
@@ -5176,19 +5176,19 @@
         <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" t="s">
         <v>186</v>
       </c>
-      <c r="I41" t="s">
-        <v>20</v>
-      </c>
       <c r="J41" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="K41" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -5217,19 +5217,19 @@
         <v>180</v>
       </c>
       <c r="G42" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" t="s">
         <v>190</v>
       </c>
-      <c r="I42" t="s">
-        <v>20</v>
-      </c>
       <c r="J42" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="K42" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="L42" t="s">
         <v>22</v>
@@ -5258,19 +5258,19 @@
         <v>180</v>
       </c>
       <c r="G43" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H43" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" t="s">
         <v>194</v>
       </c>
-      <c r="I43" t="s">
-        <v>20</v>
-      </c>
       <c r="J43" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="K43" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
@@ -5299,19 +5299,19 @@
         <v>180</v>
       </c>
       <c r="G44" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" t="s">
         <v>198</v>
       </c>
-      <c r="I44" t="s">
-        <v>20</v>
-      </c>
       <c r="J44" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="K44" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
@@ -5340,19 +5340,19 @@
         <v>202</v>
       </c>
       <c r="G45" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
         <v>203</v>
       </c>
-      <c r="I45" t="s">
-        <v>20</v>
-      </c>
       <c r="J45" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K45" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -5381,19 +5381,19 @@
         <v>202</v>
       </c>
       <c r="G46" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" t="s">
         <v>208</v>
       </c>
-      <c r="I46" t="s">
-        <v>20</v>
-      </c>
       <c r="J46" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K46" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L46" t="s">
         <v>22</v>
@@ -5422,19 +5422,19 @@
         <v>202</v>
       </c>
       <c r="G47" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" t="s">
         <v>212</v>
       </c>
-      <c r="I47" t="s">
-        <v>20</v>
-      </c>
       <c r="J47" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K47" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L47" t="s">
         <v>22</v>
@@ -5463,19 +5463,19 @@
         <v>202</v>
       </c>
       <c r="G48" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H48" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" t="s">
         <v>216</v>
       </c>
-      <c r="I48" t="s">
-        <v>20</v>
-      </c>
       <c r="J48" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K48" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L48" t="s">
         <v>22</v>
@@ -5504,19 +5504,19 @@
         <v>202</v>
       </c>
       <c r="G49" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H49" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" t="s">
         <v>220</v>
       </c>
-      <c r="I49" t="s">
-        <v>20</v>
-      </c>
       <c r="J49" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K49" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L49" t="s">
         <v>22</v>
@@ -5545,19 +5545,19 @@
         <v>202</v>
       </c>
       <c r="G50" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H50" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" t="s">
         <v>224</v>
       </c>
-      <c r="I50" t="s">
-        <v>20</v>
-      </c>
       <c r="J50" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K50" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L50" t="s">
         <v>22</v>
@@ -5586,19 +5586,19 @@
         <v>202</v>
       </c>
       <c r="G51" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H51" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" t="s">
         <v>228</v>
       </c>
-      <c r="I51" t="s">
-        <v>20</v>
-      </c>
       <c r="J51" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K51" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L51" t="s">
         <v>22</v>
@@ -5627,19 +5627,19 @@
         <v>202</v>
       </c>
       <c r="G52" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H52" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" t="s">
         <v>232</v>
       </c>
-      <c r="I52" t="s">
-        <v>20</v>
-      </c>
       <c r="J52" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K52" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L52" t="s">
         <v>22</v>
@@ -5668,19 +5668,19 @@
         <v>202</v>
       </c>
       <c r="G53" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H53" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" t="s">
         <v>236</v>
       </c>
-      <c r="I53" t="s">
-        <v>20</v>
-      </c>
       <c r="J53" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K53" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L53" t="s">
         <v>22</v>
@@ -5709,19 +5709,19 @@
         <v>202</v>
       </c>
       <c r="G54" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" t="s">
         <v>240</v>
       </c>
-      <c r="I54" t="s">
-        <v>20</v>
-      </c>
       <c r="J54" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K54" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L54" t="s">
         <v>22</v>
@@ -5750,19 +5750,19 @@
         <v>202</v>
       </c>
       <c r="G55" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H55" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" t="s">
         <v>244</v>
       </c>
-      <c r="I55" t="s">
-        <v>20</v>
-      </c>
       <c r="J55" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K55" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L55" t="s">
         <v>22</v>
@@ -5791,19 +5791,19 @@
         <v>202</v>
       </c>
       <c r="G56" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" t="s">
         <v>248</v>
       </c>
-      <c r="I56" t="s">
-        <v>20</v>
-      </c>
       <c r="J56" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K56" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L56" t="s">
         <v>22</v>
@@ -5832,19 +5832,19 @@
         <v>202</v>
       </c>
       <c r="G57" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H57" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" t="s">
         <v>252</v>
       </c>
-      <c r="I57" t="s">
-        <v>20</v>
-      </c>
       <c r="J57" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K57" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L57" t="s">
         <v>22</v>
@@ -5873,19 +5873,19 @@
         <v>202</v>
       </c>
       <c r="G58" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" t="s">
         <v>256</v>
       </c>
-      <c r="I58" t="s">
-        <v>20</v>
-      </c>
       <c r="J58" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K58" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L58" t="s">
         <v>22</v>
@@ -5914,19 +5914,19 @@
         <v>202</v>
       </c>
       <c r="G59" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" t="s">
         <v>260</v>
       </c>
-      <c r="I59" t="s">
-        <v>20</v>
-      </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K59" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L59" t="s">
         <v>22</v>
@@ -5955,19 +5955,19 @@
         <v>202</v>
       </c>
       <c r="G60" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" t="s">
         <v>264</v>
       </c>
-      <c r="I60" t="s">
-        <v>20</v>
-      </c>
       <c r="J60" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L60" t="s">
         <v>22</v>
@@ -5996,19 +5996,19 @@
         <v>202</v>
       </c>
       <c r="G61" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H61" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" t="s">
         <v>268</v>
       </c>
-      <c r="I61" t="s">
-        <v>20</v>
-      </c>
       <c r="J61" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="K61" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L61" t="s">
         <v>22</v>
@@ -6081,10 +6081,10 @@
         <v>274</v>
       </c>
       <c r="H63" t="s">
+        <v>275</v>
+      </c>
+      <c r="I63" t="s">
         <v>282</v>
-      </c>
-      <c r="I63" t="s">
-        <v>276</v>
       </c>
       <c r="J63" t="s">
         <v>277</v>
@@ -6122,10 +6122,10 @@
         <v>274</v>
       </c>
       <c r="H64" t="s">
+        <v>275</v>
+      </c>
+      <c r="I64" t="s">
         <v>286</v>
-      </c>
-      <c r="I64" t="s">
-        <v>276</v>
       </c>
       <c r="J64" t="s">
         <v>277</v>
@@ -6163,10 +6163,10 @@
         <v>274</v>
       </c>
       <c r="H65" t="s">
+        <v>275</v>
+      </c>
+      <c r="I65" t="s">
         <v>290</v>
-      </c>
-      <c r="I65" t="s">
-        <v>276</v>
       </c>
       <c r="J65" t="s">
         <v>277</v>
@@ -6204,10 +6204,10 @@
         <v>274</v>
       </c>
       <c r="H66" t="s">
+        <v>275</v>
+      </c>
+      <c r="I66" t="s">
         <v>294</v>
-      </c>
-      <c r="I66" t="s">
-        <v>276</v>
       </c>
       <c r="J66" t="s">
         <v>277</v>
@@ -6245,10 +6245,10 @@
         <v>274</v>
       </c>
       <c r="H67" t="s">
+        <v>275</v>
+      </c>
+      <c r="I67" t="s">
         <v>298</v>
-      </c>
-      <c r="I67" t="s">
-        <v>276</v>
       </c>
       <c r="J67" t="s">
         <v>277</v>
@@ -6286,10 +6286,10 @@
         <v>274</v>
       </c>
       <c r="H68" t="s">
+        <v>275</v>
+      </c>
+      <c r="I68" t="s">
         <v>302</v>
-      </c>
-      <c r="I68" t="s">
-        <v>276</v>
       </c>
       <c r="J68" t="s">
         <v>277</v>
@@ -6327,10 +6327,10 @@
         <v>274</v>
       </c>
       <c r="H69" t="s">
+        <v>275</v>
+      </c>
+      <c r="I69" t="s">
         <v>306</v>
-      </c>
-      <c r="I69" t="s">
-        <v>276</v>
       </c>
       <c r="J69" t="s">
         <v>277</v>
@@ -6368,10 +6368,10 @@
         <v>274</v>
       </c>
       <c r="H70" t="s">
+        <v>275</v>
+      </c>
+      <c r="I70" t="s">
         <v>310</v>
-      </c>
-      <c r="I70" t="s">
-        <v>276</v>
       </c>
       <c r="J70" t="s">
         <v>277</v>
@@ -6409,10 +6409,10 @@
         <v>274</v>
       </c>
       <c r="H71" t="s">
+        <v>275</v>
+      </c>
+      <c r="I71" t="s">
         <v>314</v>
-      </c>
-      <c r="I71" t="s">
-        <v>276</v>
       </c>
       <c r="J71" t="s">
         <v>277</v>
@@ -6450,10 +6450,10 @@
         <v>274</v>
       </c>
       <c r="H72" t="s">
+        <v>275</v>
+      </c>
+      <c r="I72" t="s">
         <v>318</v>
-      </c>
-      <c r="I72" t="s">
-        <v>276</v>
       </c>
       <c r="J72" t="s">
         <v>277</v>
@@ -6491,10 +6491,10 @@
         <v>274</v>
       </c>
       <c r="H73" t="s">
+        <v>275</v>
+      </c>
+      <c r="I73" t="s">
         <v>322</v>
-      </c>
-      <c r="I73" t="s">
-        <v>276</v>
       </c>
       <c r="J73" t="s">
         <v>277</v>
@@ -6532,10 +6532,10 @@
         <v>274</v>
       </c>
       <c r="H74" t="s">
+        <v>275</v>
+      </c>
+      <c r="I74" t="s">
         <v>326</v>
-      </c>
-      <c r="I74" t="s">
-        <v>276</v>
       </c>
       <c r="J74" t="s">
         <v>277</v>
@@ -6573,10 +6573,10 @@
         <v>274</v>
       </c>
       <c r="H75" t="s">
+        <v>275</v>
+      </c>
+      <c r="I75" t="s">
         <v>330</v>
-      </c>
-      <c r="I75" t="s">
-        <v>276</v>
       </c>
       <c r="J75" t="s">
         <v>277</v>
@@ -6614,10 +6614,10 @@
         <v>274</v>
       </c>
       <c r="H76" t="s">
+        <v>275</v>
+      </c>
+      <c r="I76" t="s">
         <v>334</v>
-      </c>
-      <c r="I76" t="s">
-        <v>276</v>
       </c>
       <c r="J76" t="s">
         <v>277</v>
@@ -6655,10 +6655,10 @@
         <v>274</v>
       </c>
       <c r="H77" t="s">
+        <v>275</v>
+      </c>
+      <c r="I77" t="s">
         <v>338</v>
-      </c>
-      <c r="I77" t="s">
-        <v>276</v>
       </c>
       <c r="J77" t="s">
         <v>277</v>
@@ -6696,10 +6696,10 @@
         <v>274</v>
       </c>
       <c r="H78" t="s">
+        <v>275</v>
+      </c>
+      <c r="I78" t="s">
         <v>342</v>
-      </c>
-      <c r="I78" t="s">
-        <v>276</v>
       </c>
       <c r="J78" t="s">
         <v>277</v>
@@ -6737,10 +6737,10 @@
         <v>274</v>
       </c>
       <c r="H79" t="s">
+        <v>275</v>
+      </c>
+      <c r="I79" t="s">
         <v>346</v>
-      </c>
-      <c r="I79" t="s">
-        <v>276</v>
       </c>
       <c r="J79" t="s">
         <v>277</v>
@@ -6778,10 +6778,10 @@
         <v>274</v>
       </c>
       <c r="H80" t="s">
+        <v>275</v>
+      </c>
+      <c r="I80" t="s">
         <v>350</v>
-      </c>
-      <c r="I80" t="s">
-        <v>276</v>
       </c>
       <c r="J80" t="s">
         <v>277</v>
@@ -6819,10 +6819,10 @@
         <v>274</v>
       </c>
       <c r="H81" t="s">
+        <v>275</v>
+      </c>
+      <c r="I81" t="s">
         <v>354</v>
-      </c>
-      <c r="I81" t="s">
-        <v>276</v>
       </c>
       <c r="J81" t="s">
         <v>277</v>
@@ -6860,10 +6860,10 @@
         <v>274</v>
       </c>
       <c r="H82" t="s">
+        <v>275</v>
+      </c>
+      <c r="I82" t="s">
         <v>358</v>
-      </c>
-      <c r="I82" t="s">
-        <v>276</v>
       </c>
       <c r="J82" t="s">
         <v>277</v>
@@ -6901,10 +6901,10 @@
         <v>274</v>
       </c>
       <c r="H83" t="s">
+        <v>275</v>
+      </c>
+      <c r="I83" t="s">
         <v>362</v>
-      </c>
-      <c r="I83" t="s">
-        <v>276</v>
       </c>
       <c r="J83" t="s">
         <v>277</v>
@@ -6942,10 +6942,10 @@
         <v>274</v>
       </c>
       <c r="H84" t="s">
+        <v>275</v>
+      </c>
+      <c r="I84" t="s">
         <v>366</v>
-      </c>
-      <c r="I84" t="s">
-        <v>276</v>
       </c>
       <c r="J84" t="s">
         <v>277</v>
@@ -6983,10 +6983,10 @@
         <v>274</v>
       </c>
       <c r="H85" t="s">
+        <v>275</v>
+      </c>
+      <c r="I85" t="s">
         <v>370</v>
-      </c>
-      <c r="I85" t="s">
-        <v>276</v>
       </c>
       <c r="J85" t="s">
         <v>277</v>
@@ -7024,10 +7024,10 @@
         <v>274</v>
       </c>
       <c r="H86" t="s">
+        <v>275</v>
+      </c>
+      <c r="I86" t="s">
         <v>374</v>
-      </c>
-      <c r="I86" t="s">
-        <v>276</v>
       </c>
       <c r="J86" t="s">
         <v>277</v>
@@ -7065,10 +7065,10 @@
         <v>274</v>
       </c>
       <c r="H87" t="s">
+        <v>275</v>
+      </c>
+      <c r="I87" t="s">
         <v>378</v>
-      </c>
-      <c r="I87" t="s">
-        <v>276</v>
       </c>
       <c r="J87" t="s">
         <v>277</v>
@@ -7106,10 +7106,10 @@
         <v>274</v>
       </c>
       <c r="H88" t="s">
+        <v>275</v>
+      </c>
+      <c r="I88" t="s">
         <v>382</v>
-      </c>
-      <c r="I88" t="s">
-        <v>276</v>
       </c>
       <c r="J88" t="s">
         <v>277</v>
@@ -7147,10 +7147,10 @@
         <v>274</v>
       </c>
       <c r="H89" t="s">
+        <v>275</v>
+      </c>
+      <c r="I89" t="s">
         <v>386</v>
-      </c>
-      <c r="I89" t="s">
-        <v>276</v>
       </c>
       <c r="J89" t="s">
         <v>277</v>
@@ -7188,16 +7188,16 @@
         <v>274</v>
       </c>
       <c r="H90" t="s">
+        <v>275</v>
+      </c>
+      <c r="I90" t="s">
         <v>391</v>
       </c>
-      <c r="I90" t="s">
-        <v>276</v>
-      </c>
       <c r="J90" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K90" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L90" t="s">
         <v>22</v>
@@ -7229,16 +7229,16 @@
         <v>274</v>
       </c>
       <c r="H91" t="s">
+        <v>275</v>
+      </c>
+      <c r="I91" t="s">
         <v>396</v>
       </c>
-      <c r="I91" t="s">
-        <v>276</v>
-      </c>
       <c r="J91" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K91" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L91" t="s">
         <v>22</v>
@@ -7270,16 +7270,16 @@
         <v>274</v>
       </c>
       <c r="H92" t="s">
+        <v>275</v>
+      </c>
+      <c r="I92" t="s">
         <v>400</v>
       </c>
-      <c r="I92" t="s">
-        <v>276</v>
-      </c>
       <c r="J92" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K92" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L92" t="s">
         <v>22</v>
@@ -7311,16 +7311,16 @@
         <v>274</v>
       </c>
       <c r="H93" t="s">
+        <v>275</v>
+      </c>
+      <c r="I93" t="s">
         <v>404</v>
       </c>
-      <c r="I93" t="s">
-        <v>276</v>
-      </c>
       <c r="J93" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K93" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L93" t="s">
         <v>22</v>
@@ -7352,16 +7352,16 @@
         <v>274</v>
       </c>
       <c r="H94" t="s">
+        <v>275</v>
+      </c>
+      <c r="I94" t="s">
         <v>408</v>
       </c>
-      <c r="I94" t="s">
-        <v>276</v>
-      </c>
       <c r="J94" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K94" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L94" t="s">
         <v>22</v>
@@ -7393,16 +7393,16 @@
         <v>274</v>
       </c>
       <c r="H95" t="s">
+        <v>275</v>
+      </c>
+      <c r="I95" t="s">
         <v>412</v>
       </c>
-      <c r="I95" t="s">
-        <v>276</v>
-      </c>
       <c r="J95" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K95" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L95" t="s">
         <v>22</v>
@@ -7434,16 +7434,16 @@
         <v>274</v>
       </c>
       <c r="H96" t="s">
+        <v>275</v>
+      </c>
+      <c r="I96" t="s">
         <v>416</v>
       </c>
-      <c r="I96" t="s">
-        <v>276</v>
-      </c>
       <c r="J96" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K96" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s">
         <v>22</v>
@@ -7475,16 +7475,16 @@
         <v>274</v>
       </c>
       <c r="H97" t="s">
+        <v>275</v>
+      </c>
+      <c r="I97" t="s">
         <v>420</v>
       </c>
-      <c r="I97" t="s">
-        <v>276</v>
-      </c>
       <c r="J97" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="K97" t="s">
-        <v>392</v>
+        <v>278</v>
       </c>
       <c r="L97" t="s">
         <v>22</v>
@@ -7516,16 +7516,16 @@
         <v>274</v>
       </c>
       <c r="H98" t="s">
+        <v>275</v>
+      </c>
+      <c r="I98" t="s">
         <v>425</v>
       </c>
-      <c r="I98" t="s">
-        <v>276</v>
-      </c>
       <c r="J98" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K98" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L98" t="s">
         <v>22</v>
@@ -7557,16 +7557,16 @@
         <v>274</v>
       </c>
       <c r="H99" t="s">
+        <v>275</v>
+      </c>
+      <c r="I99" t="s">
         <v>430</v>
       </c>
-      <c r="I99" t="s">
-        <v>276</v>
-      </c>
       <c r="J99" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K99" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L99" t="s">
         <v>22</v>
@@ -7598,16 +7598,16 @@
         <v>274</v>
       </c>
       <c r="H100" t="s">
+        <v>275</v>
+      </c>
+      <c r="I100" t="s">
         <v>434</v>
       </c>
-      <c r="I100" t="s">
-        <v>276</v>
-      </c>
       <c r="J100" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K100" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L100" t="s">
         <v>22</v>
@@ -7639,16 +7639,16 @@
         <v>274</v>
       </c>
       <c r="H101" t="s">
+        <v>275</v>
+      </c>
+      <c r="I101" t="s">
         <v>438</v>
       </c>
-      <c r="I101" t="s">
-        <v>276</v>
-      </c>
       <c r="J101" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K101" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L101" t="s">
         <v>22</v>
@@ -7680,16 +7680,16 @@
         <v>274</v>
       </c>
       <c r="H102" t="s">
+        <v>275</v>
+      </c>
+      <c r="I102" t="s">
         <v>442</v>
       </c>
-      <c r="I102" t="s">
-        <v>276</v>
-      </c>
       <c r="J102" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K102" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L102" t="s">
         <v>22</v>
@@ -7721,16 +7721,16 @@
         <v>274</v>
       </c>
       <c r="H103" t="s">
+        <v>275</v>
+      </c>
+      <c r="I103" t="s">
         <v>446</v>
       </c>
-      <c r="I103" t="s">
-        <v>276</v>
-      </c>
       <c r="J103" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K103" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L103" t="s">
         <v>22</v>
@@ -7762,16 +7762,16 @@
         <v>274</v>
       </c>
       <c r="H104" t="s">
+        <v>275</v>
+      </c>
+      <c r="I104" t="s">
         <v>450</v>
       </c>
-      <c r="I104" t="s">
-        <v>276</v>
-      </c>
       <c r="J104" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K104" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L104" t="s">
         <v>22</v>
@@ -7803,16 +7803,16 @@
         <v>274</v>
       </c>
       <c r="H105" t="s">
+        <v>275</v>
+      </c>
+      <c r="I105" t="s">
         <v>454</v>
       </c>
-      <c r="I105" t="s">
-        <v>276</v>
-      </c>
       <c r="J105" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K105" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L105" t="s">
         <v>22</v>
@@ -7844,16 +7844,16 @@
         <v>274</v>
       </c>
       <c r="H106" t="s">
+        <v>275</v>
+      </c>
+      <c r="I106" t="s">
         <v>458</v>
       </c>
-      <c r="I106" t="s">
-        <v>276</v>
-      </c>
       <c r="J106" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K106" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L106" t="s">
         <v>22</v>
@@ -7885,16 +7885,16 @@
         <v>274</v>
       </c>
       <c r="H107" t="s">
+        <v>275</v>
+      </c>
+      <c r="I107" t="s">
         <v>462</v>
       </c>
-      <c r="I107" t="s">
-        <v>276</v>
-      </c>
       <c r="J107" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K107" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L107" t="s">
         <v>22</v>
@@ -7926,16 +7926,16 @@
         <v>274</v>
       </c>
       <c r="H108" t="s">
+        <v>275</v>
+      </c>
+      <c r="I108" t="s">
         <v>466</v>
       </c>
-      <c r="I108" t="s">
-        <v>276</v>
-      </c>
       <c r="J108" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K108" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L108" t="s">
         <v>22</v>
@@ -7967,16 +7967,16 @@
         <v>274</v>
       </c>
       <c r="H109" t="s">
+        <v>275</v>
+      </c>
+      <c r="I109" t="s">
         <v>470</v>
       </c>
-      <c r="I109" t="s">
-        <v>276</v>
-      </c>
       <c r="J109" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K109" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L109" t="s">
         <v>22</v>
@@ -8008,16 +8008,16 @@
         <v>274</v>
       </c>
       <c r="H110" t="s">
+        <v>275</v>
+      </c>
+      <c r="I110" t="s">
         <v>474</v>
       </c>
-      <c r="I110" t="s">
-        <v>276</v>
-      </c>
       <c r="J110" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K110" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L110" t="s">
         <v>22</v>
@@ -8049,16 +8049,16 @@
         <v>274</v>
       </c>
       <c r="H111" t="s">
+        <v>275</v>
+      </c>
+      <c r="I111" t="s">
         <v>478</v>
       </c>
-      <c r="I111" t="s">
-        <v>276</v>
-      </c>
       <c r="J111" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K111" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L111" t="s">
         <v>22</v>
@@ -8090,16 +8090,16 @@
         <v>274</v>
       </c>
       <c r="H112" t="s">
+        <v>275</v>
+      </c>
+      <c r="I112" t="s">
         <v>482</v>
       </c>
-      <c r="I112" t="s">
-        <v>276</v>
-      </c>
       <c r="J112" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K112" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L112" t="s">
         <v>22</v>
@@ -8131,16 +8131,16 @@
         <v>274</v>
       </c>
       <c r="H113" t="s">
+        <v>275</v>
+      </c>
+      <c r="I113" t="s">
         <v>486</v>
       </c>
-      <c r="I113" t="s">
-        <v>276</v>
-      </c>
       <c r="J113" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="K113" t="s">
-        <v>426</v>
+        <v>278</v>
       </c>
       <c r="L113" t="s">
         <v>22</v>
@@ -8166,16 +8166,16 @@
         <v>17</v>
       </c>
       <c r="G114" t="s">
+        <v>274</v>
+      </c>
+      <c r="H114" t="s">
+        <v>275</v>
+      </c>
+      <c r="I114" t="s">
         <v>491</v>
       </c>
-      <c r="H114" t="s">
+      <c r="K114" t="s">
         <v>492</v>
-      </c>
-      <c r="I114" t="s">
-        <v>276</v>
-      </c>
-      <c r="J114" t="s">
-        <v>277</v>
       </c>
       <c r="L114" t="s">
         <v>22</v>
@@ -8201,16 +8201,16 @@
         <v>17</v>
       </c>
       <c r="G115" t="s">
-        <v>491</v>
+        <v>274</v>
       </c>
       <c r="H115" t="s">
+        <v>275</v>
+      </c>
+      <c r="I115" t="s">
         <v>496</v>
       </c>
-      <c r="I115" t="s">
-        <v>276</v>
-      </c>
-      <c r="J115" t="s">
-        <v>277</v>
+      <c r="K115" t="s">
+        <v>492</v>
       </c>
       <c r="L115" t="s">
         <v>22</v>
@@ -8236,16 +8236,16 @@
         <v>17</v>
       </c>
       <c r="G116" t="s">
-        <v>491</v>
+        <v>274</v>
       </c>
       <c r="H116" t="s">
+        <v>275</v>
+      </c>
+      <c r="I116" t="s">
         <v>500</v>
       </c>
-      <c r="I116" t="s">
-        <v>276</v>
-      </c>
-      <c r="J116" t="s">
-        <v>277</v>
+      <c r="K116" t="s">
+        <v>492</v>
       </c>
       <c r="L116" t="s">
         <v>22</v>
@@ -8271,16 +8271,16 @@
         <v>17</v>
       </c>
       <c r="G117" t="s">
-        <v>491</v>
+        <v>274</v>
       </c>
       <c r="H117" t="s">
+        <v>275</v>
+      </c>
+      <c r="I117" t="s">
         <v>504</v>
       </c>
-      <c r="I117" t="s">
-        <v>276</v>
-      </c>
-      <c r="J117" t="s">
-        <v>277</v>
+      <c r="K117" t="s">
+        <v>492</v>
       </c>
       <c r="L117" t="s">
         <v>22</v>
@@ -8306,16 +8306,16 @@
         <v>17</v>
       </c>
       <c r="G118" t="s">
-        <v>491</v>
+        <v>274</v>
       </c>
       <c r="H118" t="s">
+        <v>275</v>
+      </c>
+      <c r="I118" t="s">
         <v>508</v>
       </c>
-      <c r="I118" t="s">
-        <v>276</v>
-      </c>
-      <c r="J118" t="s">
-        <v>277</v>
+      <c r="K118" t="s">
+        <v>492</v>
       </c>
       <c r="L118" t="s">
         <v>22</v>
@@ -8337,7 +8337,7 @@
       <c r="E119" t="s">
         <v>17</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
         <v>512</v>
       </c>
       <c r="L119" t="s">
@@ -8372,7 +8372,7 @@
       <c r="I120" t="s">
         <v>519</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>520</v>
       </c>
       <c r="L120" t="s">
@@ -8402,12 +8402,12 @@
         <v>517</v>
       </c>
       <c r="H121" t="s">
+        <v>518</v>
+      </c>
+      <c r="I121" t="s">
         <v>524</v>
       </c>
-      <c r="I121" t="s">
-        <v>519</v>
-      </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>520</v>
       </c>
       <c r="L121" t="s">
@@ -8437,12 +8437,12 @@
         <v>517</v>
       </c>
       <c r="H122" t="s">
+        <v>518</v>
+      </c>
+      <c r="I122" t="s">
         <v>528</v>
       </c>
-      <c r="I122" t="s">
-        <v>519</v>
-      </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>520</v>
       </c>
       <c r="L122" t="s">
@@ -8472,12 +8472,12 @@
         <v>517</v>
       </c>
       <c r="H123" t="s">
+        <v>518</v>
+      </c>
+      <c r="I123" t="s">
         <v>532</v>
       </c>
-      <c r="I123" t="s">
-        <v>519</v>
-      </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>520</v>
       </c>
       <c r="L123" t="s">
@@ -8507,12 +8507,12 @@
         <v>517</v>
       </c>
       <c r="H124" t="s">
+        <v>518</v>
+      </c>
+      <c r="I124" t="s">
         <v>536</v>
       </c>
-      <c r="I124" t="s">
-        <v>519</v>
-      </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>520</v>
       </c>
       <c r="L124" t="s">
@@ -8539,16 +8539,16 @@
         <v>17</v>
       </c>
       <c r="G125" t="s">
+        <v>517</v>
+      </c>
+      <c r="H125" t="s">
+        <v>518</v>
+      </c>
+      <c r="I125" t="s">
         <v>541</v>
       </c>
-      <c r="H125" t="s">
+      <c r="K125" t="s">
         <v>542</v>
-      </c>
-      <c r="I125" t="s">
-        <v>519</v>
-      </c>
-      <c r="J125" t="s">
-        <v>520</v>
       </c>
       <c r="L125" t="s">
         <v>22</v>
@@ -8574,16 +8574,16 @@
         <v>17</v>
       </c>
       <c r="G126" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="H126" t="s">
+        <v>518</v>
+      </c>
+      <c r="I126" t="s">
         <v>546</v>
       </c>
-      <c r="I126" t="s">
-        <v>519</v>
-      </c>
-      <c r="J126" t="s">
-        <v>520</v>
+      <c r="K126" t="s">
+        <v>542</v>
       </c>
       <c r="L126" t="s">
         <v>22</v>
@@ -8609,16 +8609,16 @@
         <v>17</v>
       </c>
       <c r="G127" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="H127" t="s">
+        <v>518</v>
+      </c>
+      <c r="I127" t="s">
         <v>550</v>
       </c>
-      <c r="I127" t="s">
-        <v>519</v>
-      </c>
-      <c r="J127" t="s">
-        <v>520</v>
+      <c r="K127" t="s">
+        <v>542</v>
       </c>
       <c r="L127" t="s">
         <v>22</v>
@@ -8644,16 +8644,16 @@
         <v>17</v>
       </c>
       <c r="G128" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="H128" t="s">
+        <v>518</v>
+      </c>
+      <c r="I128" t="s">
         <v>554</v>
       </c>
-      <c r="I128" t="s">
-        <v>519</v>
-      </c>
-      <c r="J128" t="s">
-        <v>520</v>
+      <c r="K128" t="s">
+        <v>542</v>
       </c>
       <c r="L128" t="s">
         <v>22</v>
@@ -8679,16 +8679,16 @@
         <v>17</v>
       </c>
       <c r="G129" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="H129" t="s">
+        <v>518</v>
+      </c>
+      <c r="I129" t="s">
         <v>558</v>
       </c>
-      <c r="I129" t="s">
-        <v>519</v>
-      </c>
-      <c r="J129" t="s">
-        <v>520</v>
+      <c r="K129" t="s">
+        <v>542</v>
       </c>
       <c r="L129" t="s">
         <v>22</v>
@@ -8714,16 +8714,16 @@
         <v>17</v>
       </c>
       <c r="G130" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="H130" t="s">
+        <v>518</v>
+      </c>
+      <c r="I130" t="s">
         <v>562</v>
       </c>
-      <c r="I130" t="s">
-        <v>519</v>
-      </c>
-      <c r="J130" t="s">
-        <v>520</v>
+      <c r="K130" t="s">
+        <v>542</v>
       </c>
       <c r="L130" t="s">
         <v>22</v>
@@ -8749,16 +8749,16 @@
         <v>17</v>
       </c>
       <c r="G131" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="H131" t="s">
+        <v>518</v>
+      </c>
+      <c r="I131" t="s">
         <v>566</v>
       </c>
-      <c r="I131" t="s">
-        <v>519</v>
-      </c>
-      <c r="J131" t="s">
-        <v>520</v>
+      <c r="K131" t="s">
+        <v>542</v>
       </c>
       <c r="L131" t="s">
         <v>22</v>
@@ -8784,16 +8784,16 @@
         <v>17</v>
       </c>
       <c r="G132" t="s">
+        <v>517</v>
+      </c>
+      <c r="H132" t="s">
+        <v>518</v>
+      </c>
+      <c r="I132" t="s">
         <v>571</v>
       </c>
-      <c r="H132" t="s">
+      <c r="K132" t="s">
         <v>572</v>
-      </c>
-      <c r="I132" t="s">
-        <v>519</v>
-      </c>
-      <c r="J132" t="s">
-        <v>520</v>
       </c>
       <c r="L132" t="s">
         <v>22</v>
@@ -8819,16 +8819,16 @@
         <v>17</v>
       </c>
       <c r="G133" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H133" t="s">
+        <v>518</v>
+      </c>
+      <c r="I133" t="s">
         <v>576</v>
       </c>
-      <c r="I133" t="s">
-        <v>519</v>
-      </c>
-      <c r="J133" t="s">
-        <v>520</v>
+      <c r="K133" t="s">
+        <v>572</v>
       </c>
       <c r="L133" t="s">
         <v>22</v>
@@ -8854,16 +8854,16 @@
         <v>17</v>
       </c>
       <c r="G134" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H134" t="s">
+        <v>518</v>
+      </c>
+      <c r="I134" t="s">
         <v>580</v>
       </c>
-      <c r="I134" t="s">
-        <v>519</v>
-      </c>
-      <c r="J134" t="s">
-        <v>520</v>
+      <c r="K134" t="s">
+        <v>572</v>
       </c>
       <c r="L134" t="s">
         <v>22</v>
@@ -8889,16 +8889,16 @@
         <v>17</v>
       </c>
       <c r="G135" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H135" t="s">
+        <v>518</v>
+      </c>
+      <c r="I135" t="s">
         <v>584</v>
       </c>
-      <c r="I135" t="s">
-        <v>519</v>
-      </c>
-      <c r="J135" t="s">
-        <v>520</v>
+      <c r="K135" t="s">
+        <v>572</v>
       </c>
       <c r="L135" t="s">
         <v>22</v>
@@ -8924,16 +8924,16 @@
         <v>17</v>
       </c>
       <c r="G136" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H136" t="s">
+        <v>518</v>
+      </c>
+      <c r="I136" t="s">
         <v>588</v>
       </c>
-      <c r="I136" t="s">
-        <v>519</v>
-      </c>
-      <c r="J136" t="s">
-        <v>520</v>
+      <c r="K136" t="s">
+        <v>572</v>
       </c>
       <c r="L136" t="s">
         <v>22</v>
@@ -8959,16 +8959,16 @@
         <v>17</v>
       </c>
       <c r="G137" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H137" t="s">
+        <v>518</v>
+      </c>
+      <c r="I137" t="s">
         <v>592</v>
       </c>
-      <c r="I137" t="s">
-        <v>519</v>
-      </c>
-      <c r="J137" t="s">
-        <v>520</v>
+      <c r="K137" t="s">
+        <v>572</v>
       </c>
       <c r="L137" t="s">
         <v>22</v>
@@ -8994,16 +8994,16 @@
         <v>17</v>
       </c>
       <c r="G138" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H138" t="s">
+        <v>518</v>
+      </c>
+      <c r="I138" t="s">
         <v>596</v>
       </c>
-      <c r="I138" t="s">
-        <v>519</v>
-      </c>
-      <c r="J138" t="s">
-        <v>520</v>
+      <c r="K138" t="s">
+        <v>572</v>
       </c>
       <c r="L138" t="s">
         <v>22</v>
@@ -9029,16 +9029,16 @@
         <v>17</v>
       </c>
       <c r="G139" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H139" t="s">
+        <v>518</v>
+      </c>
+      <c r="I139" t="s">
         <v>600</v>
       </c>
-      <c r="I139" t="s">
-        <v>519</v>
-      </c>
-      <c r="J139" t="s">
-        <v>520</v>
+      <c r="K139" t="s">
+        <v>572</v>
       </c>
       <c r="L139" t="s">
         <v>22</v>
@@ -9064,16 +9064,16 @@
         <v>17</v>
       </c>
       <c r="G140" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H140" t="s">
+        <v>518</v>
+      </c>
+      <c r="I140" t="s">
         <v>604</v>
       </c>
-      <c r="I140" t="s">
-        <v>519</v>
-      </c>
-      <c r="J140" t="s">
-        <v>520</v>
+      <c r="K140" t="s">
+        <v>572</v>
       </c>
       <c r="L140" t="s">
         <v>22</v>
@@ -9099,16 +9099,16 @@
         <v>17</v>
       </c>
       <c r="G141" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H141" t="s">
+        <v>518</v>
+      </c>
+      <c r="I141" t="s">
         <v>608</v>
       </c>
-      <c r="I141" t="s">
-        <v>519</v>
-      </c>
-      <c r="J141" t="s">
-        <v>520</v>
+      <c r="K141" t="s">
+        <v>572</v>
       </c>
       <c r="L141" t="s">
         <v>22</v>
@@ -9134,16 +9134,16 @@
         <v>17</v>
       </c>
       <c r="G142" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="H142" t="s">
+        <v>518</v>
+      </c>
+      <c r="I142" t="s">
         <v>612</v>
       </c>
-      <c r="I142" t="s">
-        <v>519</v>
-      </c>
-      <c r="J142" t="s">
-        <v>520</v>
+      <c r="K142" t="s">
+        <v>572</v>
       </c>
       <c r="L142" t="s">
         <v>22</v>
@@ -9169,16 +9169,16 @@
         <v>17</v>
       </c>
       <c r="G143" t="s">
+        <v>517</v>
+      </c>
+      <c r="H143" t="s">
+        <v>518</v>
+      </c>
+      <c r="I143" t="s">
         <v>617</v>
       </c>
-      <c r="H143" t="s">
+      <c r="K143" t="s">
         <v>618</v>
-      </c>
-      <c r="I143" t="s">
-        <v>519</v>
-      </c>
-      <c r="J143" t="s">
-        <v>520</v>
       </c>
       <c r="L143" t="s">
         <v>22</v>
@@ -9204,16 +9204,16 @@
         <v>17</v>
       </c>
       <c r="G144" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H144" t="s">
+        <v>518</v>
+      </c>
+      <c r="I144" t="s">
         <v>622</v>
       </c>
-      <c r="I144" t="s">
-        <v>519</v>
-      </c>
-      <c r="J144" t="s">
-        <v>520</v>
+      <c r="K144" t="s">
+        <v>618</v>
       </c>
       <c r="L144" t="s">
         <v>22</v>
@@ -9239,16 +9239,16 @@
         <v>17</v>
       </c>
       <c r="G145" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H145" t="s">
+        <v>518</v>
+      </c>
+      <c r="I145" t="s">
         <v>626</v>
       </c>
-      <c r="I145" t="s">
-        <v>519</v>
-      </c>
-      <c r="J145" t="s">
-        <v>520</v>
+      <c r="K145" t="s">
+        <v>618</v>
       </c>
       <c r="L145" t="s">
         <v>22</v>
@@ -9274,16 +9274,16 @@
         <v>17</v>
       </c>
       <c r="G146" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H146" t="s">
+        <v>518</v>
+      </c>
+      <c r="I146" t="s">
         <v>630</v>
       </c>
-      <c r="I146" t="s">
-        <v>519</v>
-      </c>
-      <c r="J146" t="s">
-        <v>520</v>
+      <c r="K146" t="s">
+        <v>618</v>
       </c>
       <c r="L146" t="s">
         <v>22</v>
@@ -9309,16 +9309,16 @@
         <v>17</v>
       </c>
       <c r="G147" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H147" t="s">
+        <v>518</v>
+      </c>
+      <c r="I147" t="s">
         <v>634</v>
       </c>
-      <c r="I147" t="s">
-        <v>519</v>
-      </c>
-      <c r="J147" t="s">
-        <v>520</v>
+      <c r="K147" t="s">
+        <v>618</v>
       </c>
       <c r="L147" t="s">
         <v>22</v>
@@ -9344,16 +9344,16 @@
         <v>17</v>
       </c>
       <c r="G148" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H148" t="s">
+        <v>518</v>
+      </c>
+      <c r="I148" t="s">
         <v>638</v>
       </c>
-      <c r="I148" t="s">
-        <v>519</v>
-      </c>
-      <c r="J148" t="s">
-        <v>520</v>
+      <c r="K148" t="s">
+        <v>618</v>
       </c>
       <c r="L148" t="s">
         <v>22</v>
@@ -9379,16 +9379,16 @@
         <v>17</v>
       </c>
       <c r="G149" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H149" t="s">
+        <v>518</v>
+      </c>
+      <c r="I149" t="s">
         <v>642</v>
       </c>
-      <c r="I149" t="s">
-        <v>519</v>
-      </c>
-      <c r="J149" t="s">
-        <v>520</v>
+      <c r="K149" t="s">
+        <v>618</v>
       </c>
       <c r="L149" t="s">
         <v>22</v>
@@ -9414,16 +9414,16 @@
         <v>17</v>
       </c>
       <c r="G150" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H150" t="s">
+        <v>518</v>
+      </c>
+      <c r="I150" t="s">
         <v>646</v>
       </c>
-      <c r="I150" t="s">
-        <v>519</v>
-      </c>
-      <c r="J150" t="s">
-        <v>520</v>
+      <c r="K150" t="s">
+        <v>618</v>
       </c>
       <c r="L150" t="s">
         <v>22</v>
@@ -9449,16 +9449,16 @@
         <v>17</v>
       </c>
       <c r="G151" t="s">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="H151" t="s">
+        <v>518</v>
+      </c>
+      <c r="I151" t="s">
         <v>650</v>
       </c>
-      <c r="I151" t="s">
-        <v>519</v>
-      </c>
-      <c r="J151" t="s">
-        <v>520</v>
+      <c r="K151" t="s">
+        <v>618</v>
       </c>
       <c r="L151" t="s">
         <v>22</v>
@@ -9484,16 +9484,16 @@
         <v>17</v>
       </c>
       <c r="G152" t="s">
+        <v>517</v>
+      </c>
+      <c r="H152" t="s">
+        <v>518</v>
+      </c>
+      <c r="I152" t="s">
         <v>655</v>
       </c>
-      <c r="H152" t="s">
+      <c r="K152" t="s">
         <v>656</v>
-      </c>
-      <c r="I152" t="s">
-        <v>519</v>
-      </c>
-      <c r="J152" t="s">
-        <v>520</v>
       </c>
       <c r="L152" t="s">
         <v>22</v>
@@ -9519,16 +9519,16 @@
         <v>17</v>
       </c>
       <c r="G153" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H153" t="s">
+        <v>518</v>
+      </c>
+      <c r="I153" t="s">
         <v>660</v>
       </c>
-      <c r="I153" t="s">
-        <v>519</v>
-      </c>
-      <c r="J153" t="s">
-        <v>520</v>
+      <c r="K153" t="s">
+        <v>656</v>
       </c>
       <c r="L153" t="s">
         <v>22</v>
@@ -9554,16 +9554,16 @@
         <v>17</v>
       </c>
       <c r="G154" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H154" t="s">
+        <v>518</v>
+      </c>
+      <c r="I154" t="s">
         <v>664</v>
       </c>
-      <c r="I154" t="s">
-        <v>519</v>
-      </c>
-      <c r="J154" t="s">
-        <v>520</v>
+      <c r="K154" t="s">
+        <v>656</v>
       </c>
       <c r="L154" t="s">
         <v>22</v>
@@ -9589,16 +9589,16 @@
         <v>17</v>
       </c>
       <c r="G155" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H155" t="s">
+        <v>518</v>
+      </c>
+      <c r="I155" t="s">
         <v>668</v>
       </c>
-      <c r="I155" t="s">
-        <v>519</v>
-      </c>
-      <c r="J155" t="s">
-        <v>520</v>
+      <c r="K155" t="s">
+        <v>656</v>
       </c>
       <c r="L155" t="s">
         <v>22</v>
@@ -9624,16 +9624,16 @@
         <v>17</v>
       </c>
       <c r="G156" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H156" t="s">
+        <v>518</v>
+      </c>
+      <c r="I156" t="s">
         <v>672</v>
       </c>
-      <c r="I156" t="s">
-        <v>519</v>
-      </c>
-      <c r="J156" t="s">
-        <v>520</v>
+      <c r="K156" t="s">
+        <v>656</v>
       </c>
       <c r="L156" t="s">
         <v>22</v>
@@ -9659,16 +9659,16 @@
         <v>17</v>
       </c>
       <c r="G157" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H157" t="s">
+        <v>518</v>
+      </c>
+      <c r="I157" t="s">
         <v>676</v>
       </c>
-      <c r="I157" t="s">
-        <v>519</v>
-      </c>
-      <c r="J157" t="s">
-        <v>520</v>
+      <c r="K157" t="s">
+        <v>656</v>
       </c>
       <c r="L157" t="s">
         <v>22</v>
@@ -9694,16 +9694,16 @@
         <v>17</v>
       </c>
       <c r="G158" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H158" t="s">
+        <v>518</v>
+      </c>
+      <c r="I158" t="s">
         <v>680</v>
       </c>
-      <c r="I158" t="s">
-        <v>519</v>
-      </c>
-      <c r="J158" t="s">
-        <v>520</v>
+      <c r="K158" t="s">
+        <v>656</v>
       </c>
       <c r="L158" t="s">
         <v>22</v>
@@ -9729,16 +9729,16 @@
         <v>17</v>
       </c>
       <c r="G159" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H159" t="s">
+        <v>518</v>
+      </c>
+      <c r="I159" t="s">
         <v>684</v>
       </c>
-      <c r="I159" t="s">
-        <v>519</v>
-      </c>
-      <c r="J159" t="s">
-        <v>520</v>
+      <c r="K159" t="s">
+        <v>656</v>
       </c>
       <c r="L159" t="s">
         <v>22</v>
@@ -9764,16 +9764,16 @@
         <v>17</v>
       </c>
       <c r="G160" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H160" t="s">
+        <v>518</v>
+      </c>
+      <c r="I160" t="s">
         <v>688</v>
       </c>
-      <c r="I160" t="s">
-        <v>519</v>
-      </c>
-      <c r="J160" t="s">
-        <v>520</v>
+      <c r="K160" t="s">
+        <v>656</v>
       </c>
       <c r="L160" t="s">
         <v>22</v>
@@ -9799,16 +9799,16 @@
         <v>17</v>
       </c>
       <c r="G161" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H161" t="s">
+        <v>518</v>
+      </c>
+      <c r="I161" t="s">
         <v>692</v>
       </c>
-      <c r="I161" t="s">
-        <v>519</v>
-      </c>
-      <c r="J161" t="s">
-        <v>520</v>
+      <c r="K161" t="s">
+        <v>656</v>
       </c>
       <c r="L161" t="s">
         <v>22</v>
@@ -9834,16 +9834,16 @@
         <v>17</v>
       </c>
       <c r="G162" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H162" t="s">
+        <v>518</v>
+      </c>
+      <c r="I162" t="s">
         <v>696</v>
       </c>
-      <c r="I162" t="s">
-        <v>519</v>
-      </c>
-      <c r="J162" t="s">
-        <v>520</v>
+      <c r="K162" t="s">
+        <v>656</v>
       </c>
       <c r="L162" t="s">
         <v>22</v>
@@ -9869,16 +9869,16 @@
         <v>17</v>
       </c>
       <c r="G163" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H163" t="s">
+        <v>518</v>
+      </c>
+      <c r="I163" t="s">
         <v>700</v>
       </c>
-      <c r="I163" t="s">
-        <v>519</v>
-      </c>
-      <c r="J163" t="s">
-        <v>520</v>
+      <c r="K163" t="s">
+        <v>656</v>
       </c>
       <c r="L163" t="s">
         <v>22</v>
@@ -9904,16 +9904,16 @@
         <v>17</v>
       </c>
       <c r="G164" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H164" t="s">
+        <v>518</v>
+      </c>
+      <c r="I164" t="s">
         <v>704</v>
       </c>
-      <c r="I164" t="s">
-        <v>519</v>
-      </c>
-      <c r="J164" t="s">
-        <v>520</v>
+      <c r="K164" t="s">
+        <v>656</v>
       </c>
       <c r="L164" t="s">
         <v>22</v>
@@ -9939,16 +9939,16 @@
         <v>17</v>
       </c>
       <c r="G165" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H165" t="s">
+        <v>518</v>
+      </c>
+      <c r="I165" t="s">
         <v>708</v>
       </c>
-      <c r="I165" t="s">
-        <v>519</v>
-      </c>
-      <c r="J165" t="s">
-        <v>520</v>
+      <c r="K165" t="s">
+        <v>656</v>
       </c>
       <c r="L165" t="s">
         <v>22</v>
@@ -9974,16 +9974,16 @@
         <v>17</v>
       </c>
       <c r="G166" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H166" t="s">
+        <v>518</v>
+      </c>
+      <c r="I166" t="s">
         <v>712</v>
       </c>
-      <c r="I166" t="s">
-        <v>519</v>
-      </c>
-      <c r="J166" t="s">
-        <v>520</v>
+      <c r="K166" t="s">
+        <v>656</v>
       </c>
       <c r="L166" t="s">
         <v>22</v>
@@ -10009,16 +10009,16 @@
         <v>17</v>
       </c>
       <c r="G167" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H167" t="s">
+        <v>518</v>
+      </c>
+      <c r="I167" t="s">
         <v>716</v>
       </c>
-      <c r="I167" t="s">
-        <v>519</v>
-      </c>
-      <c r="J167" t="s">
-        <v>520</v>
+      <c r="K167" t="s">
+        <v>656</v>
       </c>
       <c r="L167" t="s">
         <v>22</v>
@@ -10044,16 +10044,16 @@
         <v>17</v>
       </c>
       <c r="G168" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H168" t="s">
+        <v>518</v>
+      </c>
+      <c r="I168" t="s">
         <v>720</v>
       </c>
-      <c r="I168" t="s">
-        <v>519</v>
-      </c>
-      <c r="J168" t="s">
-        <v>520</v>
+      <c r="K168" t="s">
+        <v>656</v>
       </c>
       <c r="L168" t="s">
         <v>22</v>
@@ -10079,16 +10079,16 @@
         <v>17</v>
       </c>
       <c r="G169" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="H169" t="s">
+        <v>518</v>
+      </c>
+      <c r="I169" t="s">
         <v>724</v>
       </c>
-      <c r="I169" t="s">
-        <v>519</v>
-      </c>
-      <c r="J169" t="s">
-        <v>520</v>
+      <c r="K169" t="s">
+        <v>656</v>
       </c>
       <c r="L169" t="s">
         <v>22</v>
@@ -10122,7 +10122,7 @@
       <c r="I170" t="s">
         <v>731</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>732</v>
       </c>
       <c r="L170" t="s">
@@ -10152,12 +10152,12 @@
         <v>729</v>
       </c>
       <c r="H171" t="s">
+        <v>730</v>
+      </c>
+      <c r="I171" t="s">
         <v>736</v>
       </c>
-      <c r="I171" t="s">
-        <v>731</v>
-      </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>732</v>
       </c>
       <c r="L171" t="s">
@@ -10187,12 +10187,12 @@
         <v>729</v>
       </c>
       <c r="H172" t="s">
+        <v>730</v>
+      </c>
+      <c r="I172" t="s">
         <v>740</v>
       </c>
-      <c r="I172" t="s">
-        <v>731</v>
-      </c>
-      <c r="J172" t="s">
+      <c r="K172" t="s">
         <v>732</v>
       </c>
       <c r="L172" t="s">
@@ -10222,12 +10222,12 @@
         <v>729</v>
       </c>
       <c r="H173" t="s">
+        <v>730</v>
+      </c>
+      <c r="I173" t="s">
         <v>744</v>
       </c>
-      <c r="I173" t="s">
-        <v>731</v>
-      </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>732</v>
       </c>
       <c r="L173" t="s">
@@ -10257,12 +10257,12 @@
         <v>729</v>
       </c>
       <c r="H174" t="s">
+        <v>730</v>
+      </c>
+      <c r="I174" t="s">
         <v>748</v>
       </c>
-      <c r="I174" t="s">
-        <v>731</v>
-      </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>732</v>
       </c>
       <c r="L174" t="s">
@@ -10292,12 +10292,12 @@
         <v>729</v>
       </c>
       <c r="H175" t="s">
+        <v>730</v>
+      </c>
+      <c r="I175" t="s">
         <v>752</v>
       </c>
-      <c r="I175" t="s">
-        <v>731</v>
-      </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>732</v>
       </c>
       <c r="L175" t="s">
@@ -10327,12 +10327,12 @@
         <v>729</v>
       </c>
       <c r="H176" t="s">
+        <v>730</v>
+      </c>
+      <c r="I176" t="s">
         <v>756</v>
       </c>
-      <c r="I176" t="s">
-        <v>731</v>
-      </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>732</v>
       </c>
       <c r="L176" t="s">
@@ -10362,12 +10362,12 @@
         <v>729</v>
       </c>
       <c r="H177" t="s">
+        <v>730</v>
+      </c>
+      <c r="I177" t="s">
         <v>760</v>
       </c>
-      <c r="I177" t="s">
-        <v>731</v>
-      </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>732</v>
       </c>
       <c r="L177" t="s">
@@ -10397,12 +10397,12 @@
         <v>729</v>
       </c>
       <c r="H178" t="s">
+        <v>730</v>
+      </c>
+      <c r="I178" t="s">
         <v>764</v>
       </c>
-      <c r="I178" t="s">
-        <v>731</v>
-      </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>732</v>
       </c>
       <c r="L178" t="s">
@@ -10432,12 +10432,12 @@
         <v>729</v>
       </c>
       <c r="H179" t="s">
+        <v>730</v>
+      </c>
+      <c r="I179" t="s">
         <v>768</v>
       </c>
-      <c r="I179" t="s">
-        <v>731</v>
-      </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>732</v>
       </c>
       <c r="L179" t="s">
@@ -10464,16 +10464,16 @@
         <v>17</v>
       </c>
       <c r="G180" t="s">
+        <v>729</v>
+      </c>
+      <c r="H180" t="s">
+        <v>730</v>
+      </c>
+      <c r="I180" t="s">
         <v>773</v>
       </c>
-      <c r="H180" t="s">
+      <c r="K180" t="s">
         <v>774</v>
-      </c>
-      <c r="I180" t="s">
-        <v>731</v>
-      </c>
-      <c r="J180" t="s">
-        <v>732</v>
       </c>
       <c r="L180" t="s">
         <v>22</v>
@@ -10502,19 +10502,19 @@
         <v>778</v>
       </c>
       <c r="G181" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H181" t="s">
+        <v>730</v>
+      </c>
+      <c r="I181" t="s">
         <v>779</v>
       </c>
-      <c r="I181" t="s">
-        <v>731</v>
-      </c>
       <c r="J181" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
       <c r="K181" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="L181" t="s">
         <v>22</v>
@@ -10543,19 +10543,19 @@
         <v>778</v>
       </c>
       <c r="G182" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H182" t="s">
+        <v>730</v>
+      </c>
+      <c r="I182" t="s">
         <v>784</v>
       </c>
-      <c r="I182" t="s">
-        <v>731</v>
-      </c>
       <c r="J182" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
       <c r="K182" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="L182" t="s">
         <v>22</v>
@@ -10584,16 +10584,16 @@
         <v>778</v>
       </c>
       <c r="G183" t="s">
-        <v>773</v>
-      </c>
-      <c r="I183" t="s">
-        <v>731</v>
+        <v>729</v>
+      </c>
+      <c r="H183" t="s">
+        <v>730</v>
       </c>
       <c r="J183" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
       <c r="K183" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="L183" t="s">
         <v>22</v>
@@ -10616,16 +10616,16 @@
         <v>17</v>
       </c>
       <c r="G184" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H184" t="s">
+        <v>730</v>
+      </c>
+      <c r="I184" t="s">
         <v>790</v>
       </c>
-      <c r="I184" t="s">
-        <v>731</v>
-      </c>
-      <c r="J184" t="s">
-        <v>732</v>
+      <c r="K184" t="s">
+        <v>774</v>
       </c>
       <c r="L184" t="s">
         <v>22</v>
@@ -10651,16 +10651,16 @@
         <v>17</v>
       </c>
       <c r="G185" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H185" t="s">
+        <v>730</v>
+      </c>
+      <c r="I185" t="s">
         <v>794</v>
       </c>
-      <c r="I185" t="s">
-        <v>731</v>
-      </c>
-      <c r="J185" t="s">
-        <v>732</v>
+      <c r="K185" t="s">
+        <v>774</v>
       </c>
       <c r="L185" t="s">
         <v>22</v>
@@ -10686,16 +10686,16 @@
         <v>17</v>
       </c>
       <c r="G186" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H186" t="s">
+        <v>730</v>
+      </c>
+      <c r="I186" t="s">
         <v>798</v>
       </c>
-      <c r="I186" t="s">
-        <v>731</v>
-      </c>
-      <c r="J186" t="s">
-        <v>732</v>
+      <c r="K186" t="s">
+        <v>774</v>
       </c>
       <c r="L186" t="s">
         <v>22</v>
@@ -10721,16 +10721,16 @@
         <v>17</v>
       </c>
       <c r="G187" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H187" t="s">
+        <v>730</v>
+      </c>
+      <c r="I187" t="s">
         <v>802</v>
       </c>
-      <c r="I187" t="s">
-        <v>731</v>
-      </c>
-      <c r="J187" t="s">
-        <v>732</v>
+      <c r="K187" t="s">
+        <v>774</v>
       </c>
       <c r="L187" t="s">
         <v>22</v>
@@ -10756,16 +10756,16 @@
         <v>17</v>
       </c>
       <c r="G188" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H188" t="s">
+        <v>730</v>
+      </c>
+      <c r="I188" t="s">
         <v>806</v>
       </c>
-      <c r="I188" t="s">
-        <v>731</v>
-      </c>
-      <c r="J188" t="s">
-        <v>732</v>
+      <c r="K188" t="s">
+        <v>774</v>
       </c>
       <c r="L188" t="s">
         <v>22</v>
@@ -10791,16 +10791,16 @@
         <v>17</v>
       </c>
       <c r="G189" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H189" t="s">
+        <v>730</v>
+      </c>
+      <c r="I189" t="s">
         <v>810</v>
       </c>
-      <c r="I189" t="s">
-        <v>731</v>
-      </c>
-      <c r="J189" t="s">
-        <v>732</v>
+      <c r="K189" t="s">
+        <v>774</v>
       </c>
       <c r="L189" t="s">
         <v>22</v>
@@ -10826,16 +10826,16 @@
         <v>17</v>
       </c>
       <c r="G190" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H190" t="s">
+        <v>730</v>
+      </c>
+      <c r="I190" t="s">
         <v>814</v>
       </c>
-      <c r="I190" t="s">
-        <v>731</v>
-      </c>
-      <c r="J190" t="s">
-        <v>732</v>
+      <c r="K190" t="s">
+        <v>774</v>
       </c>
       <c r="L190" t="s">
         <v>22</v>
@@ -10861,16 +10861,16 @@
         <v>17</v>
       </c>
       <c r="G191" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H191" t="s">
+        <v>730</v>
+      </c>
+      <c r="I191" t="s">
         <v>818</v>
       </c>
-      <c r="I191" t="s">
-        <v>731</v>
-      </c>
-      <c r="J191" t="s">
-        <v>732</v>
+      <c r="K191" t="s">
+        <v>774</v>
       </c>
       <c r="L191" t="s">
         <v>22</v>
@@ -10896,16 +10896,16 @@
         <v>17</v>
       </c>
       <c r="G192" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H192" t="s">
+        <v>730</v>
+      </c>
+      <c r="I192" t="s">
         <v>822</v>
       </c>
-      <c r="I192" t="s">
-        <v>731</v>
-      </c>
-      <c r="J192" t="s">
-        <v>732</v>
+      <c r="K192" t="s">
+        <v>774</v>
       </c>
       <c r="L192" t="s">
         <v>22</v>
@@ -10931,16 +10931,16 @@
         <v>17</v>
       </c>
       <c r="G193" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H193" t="s">
+        <v>730</v>
+      </c>
+      <c r="I193" t="s">
         <v>826</v>
       </c>
-      <c r="I193" t="s">
-        <v>731</v>
-      </c>
-      <c r="J193" t="s">
-        <v>732</v>
+      <c r="K193" t="s">
+        <v>774</v>
       </c>
       <c r="L193" t="s">
         <v>22</v>
@@ -10966,16 +10966,16 @@
         <v>17</v>
       </c>
       <c r="G194" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H194" t="s">
+        <v>730</v>
+      </c>
+      <c r="I194" t="s">
         <v>830</v>
       </c>
-      <c r="I194" t="s">
-        <v>731</v>
-      </c>
-      <c r="J194" t="s">
-        <v>732</v>
+      <c r="K194" t="s">
+        <v>774</v>
       </c>
       <c r="L194" t="s">
         <v>22</v>
@@ -11001,16 +11001,16 @@
         <v>17</v>
       </c>
       <c r="G195" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H195" t="s">
+        <v>730</v>
+      </c>
+      <c r="I195" t="s">
         <v>834</v>
       </c>
-      <c r="I195" t="s">
-        <v>731</v>
-      </c>
-      <c r="J195" t="s">
-        <v>732</v>
+      <c r="K195" t="s">
+        <v>774</v>
       </c>
       <c r="L195" t="s">
         <v>22</v>
@@ -11036,16 +11036,16 @@
         <v>17</v>
       </c>
       <c r="G196" t="s">
-        <v>773</v>
+        <v>729</v>
       </c>
       <c r="H196" t="s">
+        <v>730</v>
+      </c>
+      <c r="I196" t="s">
         <v>838</v>
       </c>
-      <c r="I196" t="s">
-        <v>731</v>
-      </c>
-      <c r="J196" t="s">
-        <v>732</v>
+      <c r="K196" t="s">
+        <v>774</v>
       </c>
       <c r="L196" t="s">
         <v>22</v>
@@ -11071,16 +11071,16 @@
         <v>17</v>
       </c>
       <c r="G197" t="s">
+        <v>729</v>
+      </c>
+      <c r="H197" t="s">
+        <v>730</v>
+      </c>
+      <c r="I197" t="s">
         <v>843</v>
       </c>
-      <c r="H197" t="s">
+      <c r="K197" t="s">
         <v>844</v>
-      </c>
-      <c r="I197" t="s">
-        <v>731</v>
-      </c>
-      <c r="J197" t="s">
-        <v>732</v>
       </c>
       <c r="L197" t="s">
         <v>22</v>
@@ -11106,16 +11106,16 @@
         <v>17</v>
       </c>
       <c r="G198" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H198" t="s">
+        <v>730</v>
+      </c>
+      <c r="I198" t="s">
         <v>848</v>
       </c>
-      <c r="I198" t="s">
-        <v>731</v>
-      </c>
-      <c r="J198" t="s">
-        <v>732</v>
+      <c r="K198" t="s">
+        <v>844</v>
       </c>
       <c r="L198" t="s">
         <v>22</v>
@@ -11141,16 +11141,16 @@
         <v>17</v>
       </c>
       <c r="G199" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H199" t="s">
+        <v>730</v>
+      </c>
+      <c r="I199" t="s">
         <v>852</v>
       </c>
-      <c r="I199" t="s">
-        <v>731</v>
-      </c>
-      <c r="J199" t="s">
-        <v>732</v>
+      <c r="K199" t="s">
+        <v>844</v>
       </c>
       <c r="L199" t="s">
         <v>22</v>
@@ -11176,16 +11176,16 @@
         <v>17</v>
       </c>
       <c r="G200" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H200" t="s">
+        <v>730</v>
+      </c>
+      <c r="I200" t="s">
         <v>856</v>
       </c>
-      <c r="I200" t="s">
-        <v>731</v>
-      </c>
-      <c r="J200" t="s">
-        <v>732</v>
+      <c r="K200" t="s">
+        <v>844</v>
       </c>
       <c r="L200" t="s">
         <v>22</v>
@@ -11211,16 +11211,16 @@
         <v>17</v>
       </c>
       <c r="G201" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H201" t="s">
+        <v>730</v>
+      </c>
+      <c r="I201" t="s">
         <v>860</v>
       </c>
-      <c r="I201" t="s">
-        <v>731</v>
-      </c>
-      <c r="J201" t="s">
-        <v>732</v>
+      <c r="K201" t="s">
+        <v>844</v>
       </c>
       <c r="L201" t="s">
         <v>22</v>
@@ -11246,16 +11246,16 @@
         <v>17</v>
       </c>
       <c r="G202" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H202" t="s">
+        <v>730</v>
+      </c>
+      <c r="I202" t="s">
         <v>864</v>
       </c>
-      <c r="I202" t="s">
-        <v>731</v>
-      </c>
-      <c r="J202" t="s">
-        <v>732</v>
+      <c r="K202" t="s">
+        <v>844</v>
       </c>
       <c r="L202" t="s">
         <v>22</v>
@@ -11281,16 +11281,16 @@
         <v>17</v>
       </c>
       <c r="G203" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H203" t="s">
+        <v>730</v>
+      </c>
+      <c r="I203" t="s">
         <v>868</v>
       </c>
-      <c r="I203" t="s">
-        <v>731</v>
-      </c>
-      <c r="J203" t="s">
-        <v>732</v>
+      <c r="K203" t="s">
+        <v>844</v>
       </c>
       <c r="L203" t="s">
         <v>22</v>
@@ -11316,16 +11316,16 @@
         <v>17</v>
       </c>
       <c r="G204" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H204" t="s">
+        <v>730</v>
+      </c>
+      <c r="I204" t="s">
         <v>872</v>
       </c>
-      <c r="I204" t="s">
-        <v>731</v>
-      </c>
-      <c r="J204" t="s">
-        <v>732</v>
+      <c r="K204" t="s">
+        <v>844</v>
       </c>
       <c r="L204" t="s">
         <v>22</v>
@@ -11351,16 +11351,16 @@
         <v>17</v>
       </c>
       <c r="G205" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H205" t="s">
+        <v>730</v>
+      </c>
+      <c r="I205" t="s">
         <v>876</v>
       </c>
-      <c r="I205" t="s">
-        <v>731</v>
-      </c>
-      <c r="J205" t="s">
-        <v>732</v>
+      <c r="K205" t="s">
+        <v>844</v>
       </c>
       <c r="L205" t="s">
         <v>22</v>
@@ -11386,16 +11386,16 @@
         <v>17</v>
       </c>
       <c r="G206" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H206" t="s">
+        <v>730</v>
+      </c>
+      <c r="I206" t="s">
         <v>880</v>
       </c>
-      <c r="I206" t="s">
-        <v>731</v>
-      </c>
-      <c r="J206" t="s">
-        <v>732</v>
+      <c r="K206" t="s">
+        <v>844</v>
       </c>
       <c r="L206" t="s">
         <v>22</v>
@@ -11421,16 +11421,16 @@
         <v>17</v>
       </c>
       <c r="G207" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H207" t="s">
+        <v>730</v>
+      </c>
+      <c r="I207" t="s">
         <v>884</v>
       </c>
-      <c r="I207" t="s">
-        <v>731</v>
-      </c>
-      <c r="J207" t="s">
-        <v>732</v>
+      <c r="K207" t="s">
+        <v>844</v>
       </c>
       <c r="L207" t="s">
         <v>22</v>
@@ -11456,16 +11456,16 @@
         <v>17</v>
       </c>
       <c r="G208" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H208" t="s">
+        <v>730</v>
+      </c>
+      <c r="I208" t="s">
         <v>888</v>
       </c>
-      <c r="I208" t="s">
-        <v>731</v>
-      </c>
-      <c r="J208" t="s">
-        <v>732</v>
+      <c r="K208" t="s">
+        <v>844</v>
       </c>
       <c r="L208" t="s">
         <v>22</v>
@@ -11491,16 +11491,16 @@
         <v>17</v>
       </c>
       <c r="G209" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H209" t="s">
+        <v>730</v>
+      </c>
+      <c r="I209" t="s">
         <v>892</v>
       </c>
-      <c r="I209" t="s">
-        <v>731</v>
-      </c>
-      <c r="J209" t="s">
-        <v>732</v>
+      <c r="K209" t="s">
+        <v>844</v>
       </c>
       <c r="L209" t="s">
         <v>22</v>
@@ -11526,16 +11526,16 @@
         <v>17</v>
       </c>
       <c r="G210" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H210" t="s">
+        <v>730</v>
+      </c>
+      <c r="I210" t="s">
         <v>896</v>
       </c>
-      <c r="I210" t="s">
-        <v>731</v>
-      </c>
-      <c r="J210" t="s">
-        <v>732</v>
+      <c r="K210" t="s">
+        <v>844</v>
       </c>
       <c r="L210" t="s">
         <v>22</v>
@@ -11561,16 +11561,16 @@
         <v>17</v>
       </c>
       <c r="G211" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H211" t="s">
+        <v>730</v>
+      </c>
+      <c r="I211" t="s">
         <v>900</v>
       </c>
-      <c r="I211" t="s">
-        <v>731</v>
-      </c>
-      <c r="J211" t="s">
-        <v>732</v>
+      <c r="K211" t="s">
+        <v>844</v>
       </c>
       <c r="L211" t="s">
         <v>22</v>
@@ -11596,16 +11596,16 @@
         <v>17</v>
       </c>
       <c r="G212" t="s">
-        <v>843</v>
+        <v>729</v>
       </c>
       <c r="H212" t="s">
+        <v>730</v>
+      </c>
+      <c r="I212" t="s">
         <v>904</v>
       </c>
-      <c r="I212" t="s">
-        <v>731</v>
-      </c>
-      <c r="J212" t="s">
-        <v>732</v>
+      <c r="K212" t="s">
+        <v>844</v>
       </c>
       <c r="L212" t="s">
         <v>22</v>
@@ -11631,16 +11631,16 @@
         <v>17</v>
       </c>
       <c r="G213" t="s">
+        <v>729</v>
+      </c>
+      <c r="H213" t="s">
+        <v>730</v>
+      </c>
+      <c r="I213" t="s">
         <v>909</v>
       </c>
-      <c r="H213" t="s">
+      <c r="K213" t="s">
         <v>910</v>
-      </c>
-      <c r="I213" t="s">
-        <v>731</v>
-      </c>
-      <c r="J213" t="s">
-        <v>732</v>
       </c>
       <c r="L213" t="s">
         <v>22</v>
@@ -11666,16 +11666,16 @@
         <v>17</v>
       </c>
       <c r="G214" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H214" t="s">
+        <v>730</v>
+      </c>
+      <c r="I214" t="s">
         <v>914</v>
       </c>
-      <c r="I214" t="s">
-        <v>731</v>
-      </c>
-      <c r="J214" t="s">
-        <v>732</v>
+      <c r="K214" t="s">
+        <v>910</v>
       </c>
       <c r="L214" t="s">
         <v>22</v>
@@ -11701,16 +11701,16 @@
         <v>17</v>
       </c>
       <c r="G215" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H215" t="s">
+        <v>730</v>
+      </c>
+      <c r="I215" t="s">
         <v>918</v>
       </c>
-      <c r="I215" t="s">
-        <v>731</v>
-      </c>
-      <c r="J215" t="s">
-        <v>732</v>
+      <c r="K215" t="s">
+        <v>910</v>
       </c>
       <c r="L215" t="s">
         <v>22</v>
@@ -11736,16 +11736,16 @@
         <v>17</v>
       </c>
       <c r="G216" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H216" t="s">
+        <v>730</v>
+      </c>
+      <c r="I216" t="s">
         <v>922</v>
       </c>
-      <c r="I216" t="s">
-        <v>731</v>
-      </c>
-      <c r="J216" t="s">
-        <v>732</v>
+      <c r="K216" t="s">
+        <v>910</v>
       </c>
       <c r="L216" t="s">
         <v>22</v>
@@ -11771,16 +11771,16 @@
         <v>17</v>
       </c>
       <c r="G217" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H217" t="s">
+        <v>730</v>
+      </c>
+      <c r="I217" t="s">
         <v>926</v>
       </c>
-      <c r="I217" t="s">
-        <v>731</v>
-      </c>
-      <c r="J217" t="s">
-        <v>732</v>
+      <c r="K217" t="s">
+        <v>910</v>
       </c>
       <c r="L217" t="s">
         <v>22</v>
@@ -11806,16 +11806,16 @@
         <v>17</v>
       </c>
       <c r="G218" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H218" t="s">
+        <v>730</v>
+      </c>
+      <c r="I218" t="s">
         <v>930</v>
       </c>
-      <c r="I218" t="s">
-        <v>731</v>
-      </c>
-      <c r="J218" t="s">
-        <v>732</v>
+      <c r="K218" t="s">
+        <v>910</v>
       </c>
       <c r="L218" t="s">
         <v>22</v>
@@ -11841,16 +11841,16 @@
         <v>17</v>
       </c>
       <c r="G219" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H219" t="s">
+        <v>730</v>
+      </c>
+      <c r="I219" t="s">
         <v>934</v>
       </c>
-      <c r="I219" t="s">
-        <v>731</v>
-      </c>
-      <c r="J219" t="s">
-        <v>732</v>
+      <c r="K219" t="s">
+        <v>910</v>
       </c>
       <c r="L219" t="s">
         <v>22</v>
@@ -11876,16 +11876,16 @@
         <v>17</v>
       </c>
       <c r="G220" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H220" t="s">
+        <v>730</v>
+      </c>
+      <c r="I220" t="s">
         <v>938</v>
       </c>
-      <c r="I220" t="s">
-        <v>731</v>
-      </c>
-      <c r="J220" t="s">
-        <v>732</v>
+      <c r="K220" t="s">
+        <v>910</v>
       </c>
       <c r="L220" t="s">
         <v>22</v>
@@ -11911,16 +11911,16 @@
         <v>17</v>
       </c>
       <c r="G221" t="s">
-        <v>909</v>
+        <v>729</v>
       </c>
       <c r="H221" t="s">
+        <v>730</v>
+      </c>
+      <c r="I221" t="s">
         <v>942</v>
       </c>
-      <c r="I221" t="s">
-        <v>731</v>
-      </c>
-      <c r="J221" t="s">
-        <v>732</v>
+      <c r="K221" t="s">
+        <v>910</v>
       </c>
       <c r="L221" t="s">
         <v>22</v>
@@ -11954,7 +11954,7 @@
       <c r="I222" t="s">
         <v>949</v>
       </c>
-      <c r="J222" t="s">
+      <c r="K222" t="s">
         <v>950</v>
       </c>
       <c r="L222" t="s">
@@ -11984,12 +11984,12 @@
         <v>947</v>
       </c>
       <c r="H223" t="s">
+        <v>948</v>
+      </c>
+      <c r="I223" t="s">
         <v>954</v>
       </c>
-      <c r="I223" t="s">
-        <v>949</v>
-      </c>
-      <c r="J223" t="s">
+      <c r="K223" t="s">
         <v>950</v>
       </c>
       <c r="L223" t="s">
@@ -12019,12 +12019,12 @@
         <v>947</v>
       </c>
       <c r="H224" t="s">
+        <v>948</v>
+      </c>
+      <c r="I224" t="s">
         <v>958</v>
       </c>
-      <c r="I224" t="s">
-        <v>949</v>
-      </c>
-      <c r="J224" t="s">
+      <c r="K224" t="s">
         <v>950</v>
       </c>
       <c r="L224" t="s">
@@ -12054,12 +12054,12 @@
         <v>947</v>
       </c>
       <c r="H225" t="s">
+        <v>948</v>
+      </c>
+      <c r="I225" t="s">
         <v>962</v>
       </c>
-      <c r="I225" t="s">
-        <v>949</v>
-      </c>
-      <c r="J225" t="s">
+      <c r="K225" t="s">
         <v>950</v>
       </c>
       <c r="L225" t="s">
@@ -12089,12 +12089,12 @@
         <v>947</v>
       </c>
       <c r="H226" t="s">
+        <v>948</v>
+      </c>
+      <c r="I226" t="s">
         <v>966</v>
       </c>
-      <c r="I226" t="s">
-        <v>949</v>
-      </c>
-      <c r="J226" t="s">
+      <c r="K226" t="s">
         <v>950</v>
       </c>
       <c r="L226" t="s">
@@ -12124,12 +12124,12 @@
         <v>947</v>
       </c>
       <c r="H227" t="s">
+        <v>948</v>
+      </c>
+      <c r="I227" t="s">
         <v>970</v>
       </c>
-      <c r="I227" t="s">
-        <v>949</v>
-      </c>
-      <c r="J227" t="s">
+      <c r="K227" t="s">
         <v>950</v>
       </c>
       <c r="L227" t="s">
@@ -12156,16 +12156,16 @@
         <v>17</v>
       </c>
       <c r="G228" t="s">
+        <v>947</v>
+      </c>
+      <c r="H228" t="s">
+        <v>948</v>
+      </c>
+      <c r="I228" t="s">
         <v>975</v>
       </c>
-      <c r="H228" t="s">
+      <c r="K228" t="s">
         <v>976</v>
-      </c>
-      <c r="I228" t="s">
-        <v>949</v>
-      </c>
-      <c r="J228" t="s">
-        <v>950</v>
       </c>
       <c r="L228" t="s">
         <v>22</v>
@@ -12191,16 +12191,16 @@
         <v>17</v>
       </c>
       <c r="G229" t="s">
-        <v>975</v>
+        <v>947</v>
       </c>
       <c r="H229" t="s">
+        <v>948</v>
+      </c>
+      <c r="I229" t="s">
         <v>980</v>
       </c>
-      <c r="I229" t="s">
-        <v>949</v>
-      </c>
-      <c r="J229" t="s">
-        <v>950</v>
+      <c r="K229" t="s">
+        <v>976</v>
       </c>
       <c r="L229" t="s">
         <v>22</v>
@@ -12226,16 +12226,16 @@
         <v>17</v>
       </c>
       <c r="G230" t="s">
-        <v>975</v>
+        <v>947</v>
       </c>
       <c r="H230" t="s">
+        <v>948</v>
+      </c>
+      <c r="I230" t="s">
         <v>984</v>
       </c>
-      <c r="I230" t="s">
-        <v>949</v>
-      </c>
-      <c r="J230" t="s">
-        <v>950</v>
+      <c r="K230" t="s">
+        <v>976</v>
       </c>
       <c r="L230" t="s">
         <v>22</v>
@@ -12261,16 +12261,16 @@
         <v>17</v>
       </c>
       <c r="G231" t="s">
-        <v>975</v>
+        <v>947</v>
       </c>
       <c r="H231" t="s">
+        <v>948</v>
+      </c>
+      <c r="I231" t="s">
         <v>988</v>
       </c>
-      <c r="I231" t="s">
-        <v>949</v>
-      </c>
-      <c r="J231" t="s">
-        <v>950</v>
+      <c r="K231" t="s">
+        <v>976</v>
       </c>
       <c r="L231" t="s">
         <v>22</v>
@@ -12296,16 +12296,16 @@
         <v>17</v>
       </c>
       <c r="G232" t="s">
-        <v>975</v>
+        <v>947</v>
       </c>
       <c r="H232" t="s">
+        <v>948</v>
+      </c>
+      <c r="I232" t="s">
         <v>992</v>
       </c>
-      <c r="I232" t="s">
-        <v>949</v>
-      </c>
-      <c r="J232" t="s">
-        <v>950</v>
+      <c r="K232" t="s">
+        <v>976</v>
       </c>
       <c r="L232" t="s">
         <v>22</v>
@@ -12331,16 +12331,16 @@
         <v>17</v>
       </c>
       <c r="G233" t="s">
+        <v>947</v>
+      </c>
+      <c r="H233" t="s">
+        <v>948</v>
+      </c>
+      <c r="I233" t="s">
         <v>997</v>
       </c>
-      <c r="H233" t="s">
+      <c r="K233" t="s">
         <v>998</v>
-      </c>
-      <c r="I233" t="s">
-        <v>949</v>
-      </c>
-      <c r="J233" t="s">
-        <v>950</v>
       </c>
       <c r="L233" t="s">
         <v>22</v>
@@ -12366,16 +12366,16 @@
         <v>17</v>
       </c>
       <c r="G234" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H234" t="s">
+        <v>948</v>
+      </c>
+      <c r="I234" t="s">
         <v>1002</v>
       </c>
-      <c r="I234" t="s">
-        <v>949</v>
-      </c>
-      <c r="J234" t="s">
-        <v>950</v>
+      <c r="K234" t="s">
+        <v>998</v>
       </c>
       <c r="L234" t="s">
         <v>22</v>
@@ -12401,16 +12401,16 @@
         <v>17</v>
       </c>
       <c r="G235" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H235" t="s">
+        <v>948</v>
+      </c>
+      <c r="I235" t="s">
         <v>1006</v>
       </c>
-      <c r="I235" t="s">
-        <v>949</v>
-      </c>
-      <c r="J235" t="s">
-        <v>950</v>
+      <c r="K235" t="s">
+        <v>998</v>
       </c>
       <c r="L235" t="s">
         <v>22</v>
@@ -12436,16 +12436,16 @@
         <v>17</v>
       </c>
       <c r="G236" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H236" t="s">
+        <v>948</v>
+      </c>
+      <c r="I236" t="s">
         <v>1010</v>
       </c>
-      <c r="I236" t="s">
-        <v>949</v>
-      </c>
-      <c r="J236" t="s">
-        <v>950</v>
+      <c r="K236" t="s">
+        <v>998</v>
       </c>
       <c r="L236" t="s">
         <v>22</v>
@@ -12471,16 +12471,16 @@
         <v>17</v>
       </c>
       <c r="G237" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H237" t="s">
+        <v>948</v>
+      </c>
+      <c r="I237" t="s">
         <v>1014</v>
       </c>
-      <c r="I237" t="s">
-        <v>949</v>
-      </c>
-      <c r="J237" t="s">
-        <v>950</v>
+      <c r="K237" t="s">
+        <v>998</v>
       </c>
       <c r="L237" t="s">
         <v>22</v>
@@ -12506,16 +12506,16 @@
         <v>17</v>
       </c>
       <c r="G238" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H238" t="s">
+        <v>948</v>
+      </c>
+      <c r="I238" t="s">
         <v>1018</v>
       </c>
-      <c r="I238" t="s">
-        <v>949</v>
-      </c>
-      <c r="J238" t="s">
-        <v>950</v>
+      <c r="K238" t="s">
+        <v>998</v>
       </c>
       <c r="L238" t="s">
         <v>22</v>
@@ -12541,16 +12541,16 @@
         <v>17</v>
       </c>
       <c r="G239" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H239" t="s">
+        <v>948</v>
+      </c>
+      <c r="I239" t="s">
         <v>1022</v>
       </c>
-      <c r="I239" t="s">
-        <v>949</v>
-      </c>
-      <c r="J239" t="s">
-        <v>950</v>
+      <c r="K239" t="s">
+        <v>998</v>
       </c>
       <c r="L239" t="s">
         <v>22</v>
@@ -12576,16 +12576,16 @@
         <v>17</v>
       </c>
       <c r="G240" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="H240" t="s">
+        <v>948</v>
+      </c>
+      <c r="I240" t="s">
         <v>1026</v>
       </c>
-      <c r="I240" t="s">
-        <v>949</v>
-      </c>
-      <c r="J240" t="s">
-        <v>950</v>
+      <c r="K240" t="s">
+        <v>998</v>
       </c>
       <c r="L240" t="s">
         <v>22</v>
@@ -12611,16 +12611,16 @@
         <v>17</v>
       </c>
       <c r="G241" t="s">
+        <v>947</v>
+      </c>
+      <c r="H241" t="s">
+        <v>948</v>
+      </c>
+      <c r="I241" t="s">
         <v>1031</v>
       </c>
-      <c r="H241" t="s">
+      <c r="K241" t="s">
         <v>1032</v>
-      </c>
-      <c r="I241" t="s">
-        <v>949</v>
-      </c>
-      <c r="J241" t="s">
-        <v>950</v>
       </c>
       <c r="L241" t="s">
         <v>22</v>
@@ -12646,16 +12646,16 @@
         <v>17</v>
       </c>
       <c r="G242" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H242" t="s">
+        <v>948</v>
+      </c>
+      <c r="I242" t="s">
         <v>1036</v>
       </c>
-      <c r="I242" t="s">
-        <v>949</v>
-      </c>
-      <c r="J242" t="s">
-        <v>950</v>
+      <c r="K242" t="s">
+        <v>1032</v>
       </c>
       <c r="L242" t="s">
         <v>22</v>
@@ -12681,16 +12681,16 @@
         <v>17</v>
       </c>
       <c r="G243" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H243" t="s">
+        <v>948</v>
+      </c>
+      <c r="I243" t="s">
         <v>1040</v>
       </c>
-      <c r="I243" t="s">
-        <v>949</v>
-      </c>
-      <c r="J243" t="s">
-        <v>950</v>
+      <c r="K243" t="s">
+        <v>1032</v>
       </c>
       <c r="L243" t="s">
         <v>22</v>
@@ -12716,16 +12716,16 @@
         <v>17</v>
       </c>
       <c r="G244" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H244" t="s">
+        <v>948</v>
+      </c>
+      <c r="I244" t="s">
         <v>1044</v>
       </c>
-      <c r="I244" t="s">
-        <v>949</v>
-      </c>
-      <c r="J244" t="s">
-        <v>950</v>
+      <c r="K244" t="s">
+        <v>1032</v>
       </c>
       <c r="L244" t="s">
         <v>22</v>
@@ -12751,16 +12751,16 @@
         <v>17</v>
       </c>
       <c r="G245" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H245" t="s">
+        <v>948</v>
+      </c>
+      <c r="I245" t="s">
         <v>1048</v>
       </c>
-      <c r="I245" t="s">
-        <v>949</v>
-      </c>
-      <c r="J245" t="s">
-        <v>950</v>
+      <c r="K245" t="s">
+        <v>1032</v>
       </c>
       <c r="L245" t="s">
         <v>22</v>
@@ -12786,16 +12786,16 @@
         <v>17</v>
       </c>
       <c r="G246" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H246" t="s">
+        <v>948</v>
+      </c>
+      <c r="I246" t="s">
         <v>1052</v>
       </c>
-      <c r="I246" t="s">
-        <v>949</v>
-      </c>
-      <c r="J246" t="s">
-        <v>950</v>
+      <c r="K246" t="s">
+        <v>1032</v>
       </c>
       <c r="L246" t="s">
         <v>22</v>
@@ -12821,16 +12821,16 @@
         <v>17</v>
       </c>
       <c r="G247" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H247" t="s">
+        <v>948</v>
+      </c>
+      <c r="I247" t="s">
         <v>1056</v>
       </c>
-      <c r="I247" t="s">
-        <v>949</v>
-      </c>
-      <c r="J247" t="s">
-        <v>950</v>
+      <c r="K247" t="s">
+        <v>1032</v>
       </c>
       <c r="L247" t="s">
         <v>22</v>
@@ -12856,16 +12856,16 @@
         <v>17</v>
       </c>
       <c r="G248" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H248" t="s">
+        <v>948</v>
+      </c>
+      <c r="I248" t="s">
         <v>1060</v>
       </c>
-      <c r="I248" t="s">
-        <v>949</v>
-      </c>
-      <c r="J248" t="s">
-        <v>950</v>
+      <c r="K248" t="s">
+        <v>1032</v>
       </c>
       <c r="L248" t="s">
         <v>22</v>
@@ -12891,16 +12891,16 @@
         <v>17</v>
       </c>
       <c r="G249" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H249" t="s">
+        <v>948</v>
+      </c>
+      <c r="I249" t="s">
         <v>1064</v>
       </c>
-      <c r="I249" t="s">
-        <v>949</v>
-      </c>
-      <c r="J249" t="s">
-        <v>950</v>
+      <c r="K249" t="s">
+        <v>1032</v>
       </c>
       <c r="L249" t="s">
         <v>22</v>
@@ -12926,16 +12926,16 @@
         <v>17</v>
       </c>
       <c r="G250" t="s">
-        <v>1031</v>
+        <v>947</v>
       </c>
       <c r="H250" t="s">
+        <v>948</v>
+      </c>
+      <c r="I250" t="s">
         <v>1068</v>
       </c>
-      <c r="I250" t="s">
-        <v>949</v>
-      </c>
-      <c r="J250" t="s">
-        <v>950</v>
+      <c r="K250" t="s">
+        <v>1032</v>
       </c>
       <c r="L250" t="s">
         <v>22</v>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,36 +25,36 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
     <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
     <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
     <t>codeforiati:global-name</t>
   </si>
   <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -67,27 +67,27 @@
     <t>DZ</t>
   </si>
   <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>015</t>
   </si>
   <si>
-    <t>002</t>
-  </si>
-  <si>
     <t>DZA</t>
   </si>
   <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
@@ -442,15 +442,15 @@
     <t>Angola</t>
   </si>
   <si>
+    <t>Middle Africa</t>
+  </si>
+  <si>
+    <t>AO</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
-    <t>AO</t>
-  </si>
-  <si>
-    <t>Middle Africa</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
@@ -556,15 +556,15 @@
     <t>Botswana</t>
   </si>
   <si>
+    <t>Southern Africa</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
     <t>018</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>Southern Africa</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>Benin</t>
   </si>
   <si>
+    <t>Western Africa</t>
+  </si>
+  <si>
+    <t>BJ</t>
+  </si>
+  <si>
     <t>011</t>
   </si>
   <si>
-    <t>BJ</t>
-  </si>
-  <si>
-    <t>Western Africa</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
@@ -832,30 +832,30 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
     <t>029</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
     <t>AIA</t>
   </si>
   <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
     <t>Americas</t>
   </si>
   <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -1186,15 +1186,15 @@
     <t>Belize</t>
   </si>
   <si>
+    <t>Central America</t>
+  </si>
+  <si>
+    <t>BZ</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
-    <t>BZ</t>
-  </si>
-  <si>
-    <t>Central America</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
@@ -1288,15 +1288,15 @@
     <t>Argentina</t>
   </si>
   <si>
+    <t>South America</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>South America</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -1567,21 +1567,21 @@
     <t>KZ</t>
   </si>
   <si>
+    <t>142</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
-    <t>142</t>
-  </si>
-  <si>
     <t>KAZ</t>
   </si>
   <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
     <t>Asia</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -2203,21 +2203,21 @@
     <t>BY</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>BLR</t>
   </si>
   <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
     <t>Europe</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2350,15 +2350,15 @@
     <t>Guernsey</t>
   </si>
   <si>
+    <t>Channel Islands</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
     <t>830</t>
   </si>
   <si>
-    <t>GG</t>
-  </si>
-  <si>
-    <t>Channel Islands</t>
-  </si>
-  <si>
     <t>GGY</t>
   </si>
   <si>
@@ -2857,19 +2857,19 @@
     <t>AU</t>
   </si>
   <si>
+    <t>009</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
-    <t>009</t>
-  </si>
-  <si>
     <t>AUS</t>
   </si>
   <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
     <t>Oceania</t>
-  </si>
-  <si>
-    <t>Australia and New Zealand</t>
   </si>
   <si>
     <t>162</t>
@@ -3861,10 +3861,10 @@
         <v>51</v>
       </c>
       <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
         <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
       </c>
       <c r="H9" t="s">
         <v>53</v>
@@ -3873,7 +3873,7 @@
         <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -3882,7 +3882,7 @@
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3902,10 +3902,10 @@
         <v>58</v>
       </c>
       <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
         <v>52</v>
-      </c>
-      <c r="G10" t="s">
-        <v>18</v>
       </c>
       <c r="H10" t="s">
         <v>53</v>
@@ -3914,7 +3914,7 @@
         <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -3923,7 +3923,7 @@
         <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3943,10 +3943,10 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
         <v>52</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
       </c>
       <c r="H11" t="s">
         <v>53</v>
@@ -3955,7 +3955,7 @@
         <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
         <v>21</v>
@@ -3964,7 +3964,7 @@
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3984,10 +3984,10 @@
         <v>66</v>
       </c>
       <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
         <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
       </c>
       <c r="H12" t="s">
         <v>53</v>
@@ -3996,7 +3996,7 @@
         <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -4005,7 +4005,7 @@
         <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4025,10 +4025,10 @@
         <v>70</v>
       </c>
       <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
         <v>52</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
       </c>
       <c r="H13" t="s">
         <v>53</v>
@@ -4037,7 +4037,7 @@
         <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
@@ -4046,7 +4046,7 @@
         <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -4066,10 +4066,10 @@
         <v>74</v>
       </c>
       <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
         <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
       </c>
       <c r="H14" t="s">
         <v>53</v>
@@ -4078,7 +4078,7 @@
         <v>75</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
         <v>21</v>
@@ -4087,7 +4087,7 @@
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4107,10 +4107,10 @@
         <v>78</v>
       </c>
       <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
         <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
       </c>
       <c r="H15" t="s">
         <v>53</v>
@@ -4119,7 +4119,7 @@
         <v>79</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
@@ -4128,7 +4128,7 @@
         <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4148,10 +4148,10 @@
         <v>82</v>
       </c>
       <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
         <v>52</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
       </c>
       <c r="H16" t="s">
         <v>53</v>
@@ -4160,7 +4160,7 @@
         <v>83</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K16" t="s">
         <v>21</v>
@@ -4169,7 +4169,7 @@
         <v>22</v>
       </c>
       <c r="M16" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4189,10 +4189,10 @@
         <v>86</v>
       </c>
       <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
         <v>52</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
       </c>
       <c r="H17" t="s">
         <v>53</v>
@@ -4201,7 +4201,7 @@
         <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
         <v>21</v>
@@ -4210,7 +4210,7 @@
         <v>22</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4230,10 +4230,10 @@
         <v>90</v>
       </c>
       <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
         <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>18</v>
       </c>
       <c r="H18" t="s">
         <v>53</v>
@@ -4242,7 +4242,7 @@
         <v>91</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
         <v>21</v>
@@ -4251,7 +4251,7 @@
         <v>22</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -4271,10 +4271,10 @@
         <v>94</v>
       </c>
       <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
         <v>52</v>
-      </c>
-      <c r="G19" t="s">
-        <v>18</v>
       </c>
       <c r="H19" t="s">
         <v>53</v>
@@ -4283,7 +4283,7 @@
         <v>95</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K19" t="s">
         <v>21</v>
@@ -4292,7 +4292,7 @@
         <v>22</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4312,10 +4312,10 @@
         <v>98</v>
       </c>
       <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
         <v>52</v>
-      </c>
-      <c r="G20" t="s">
-        <v>18</v>
       </c>
       <c r="H20" t="s">
         <v>53</v>
@@ -4324,7 +4324,7 @@
         <v>99</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K20" t="s">
         <v>21</v>
@@ -4333,7 +4333,7 @@
         <v>22</v>
       </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4353,10 +4353,10 @@
         <v>102</v>
       </c>
       <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
         <v>52</v>
-      </c>
-      <c r="G21" t="s">
-        <v>18</v>
       </c>
       <c r="H21" t="s">
         <v>53</v>
@@ -4365,7 +4365,7 @@
         <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K21" t="s">
         <v>21</v>
@@ -4374,7 +4374,7 @@
         <v>22</v>
       </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4394,10 +4394,10 @@
         <v>106</v>
       </c>
       <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
         <v>52</v>
-      </c>
-      <c r="G22" t="s">
-        <v>18</v>
       </c>
       <c r="H22" t="s">
         <v>53</v>
@@ -4406,7 +4406,7 @@
         <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K22" t="s">
         <v>21</v>
@@ -4415,7 +4415,7 @@
         <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4435,10 +4435,10 @@
         <v>110</v>
       </c>
       <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
         <v>52</v>
-      </c>
-      <c r="G23" t="s">
-        <v>18</v>
       </c>
       <c r="H23" t="s">
         <v>53</v>
@@ -4447,7 +4447,7 @@
         <v>111</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
@@ -4456,7 +4456,7 @@
         <v>22</v>
       </c>
       <c r="M23" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -4476,10 +4476,10 @@
         <v>114</v>
       </c>
       <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
         <v>52</v>
-      </c>
-      <c r="G24" t="s">
-        <v>18</v>
       </c>
       <c r="H24" t="s">
         <v>53</v>
@@ -4488,7 +4488,7 @@
         <v>115</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K24" t="s">
         <v>21</v>
@@ -4497,7 +4497,7 @@
         <v>22</v>
       </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -4517,10 +4517,10 @@
         <v>118</v>
       </c>
       <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
         <v>52</v>
-      </c>
-      <c r="G25" t="s">
-        <v>18</v>
       </c>
       <c r="H25" t="s">
         <v>53</v>
@@ -4529,7 +4529,7 @@
         <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K25" t="s">
         <v>21</v>
@@ -4538,7 +4538,7 @@
         <v>22</v>
       </c>
       <c r="M25" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -4558,10 +4558,10 @@
         <v>122</v>
       </c>
       <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
         <v>52</v>
-      </c>
-      <c r="G26" t="s">
-        <v>18</v>
       </c>
       <c r="H26" t="s">
         <v>53</v>
@@ -4570,7 +4570,7 @@
         <v>123</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K26" t="s">
         <v>21</v>
@@ -4579,7 +4579,7 @@
         <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -4599,10 +4599,10 @@
         <v>126</v>
       </c>
       <c r="F27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" t="s">
         <v>52</v>
-      </c>
-      <c r="G27" t="s">
-        <v>18</v>
       </c>
       <c r="H27" t="s">
         <v>53</v>
@@ -4611,7 +4611,7 @@
         <v>127</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K27" t="s">
         <v>21</v>
@@ -4620,7 +4620,7 @@
         <v>22</v>
       </c>
       <c r="M27" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4640,10 +4640,10 @@
         <v>130</v>
       </c>
       <c r="F28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" t="s">
         <v>52</v>
-      </c>
-      <c r="G28" t="s">
-        <v>18</v>
       </c>
       <c r="H28" t="s">
         <v>53</v>
@@ -4652,7 +4652,7 @@
         <v>131</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K28" t="s">
         <v>21</v>
@@ -4661,7 +4661,7 @@
         <v>22</v>
       </c>
       <c r="M28" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4681,10 +4681,10 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" t="s">
         <v>52</v>
-      </c>
-      <c r="G29" t="s">
-        <v>18</v>
       </c>
       <c r="H29" t="s">
         <v>53</v>
@@ -4693,7 +4693,7 @@
         <v>135</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K29" t="s">
         <v>21</v>
@@ -4702,7 +4702,7 @@
         <v>22</v>
       </c>
       <c r="M29" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -4722,10 +4722,10 @@
         <v>138</v>
       </c>
       <c r="F30" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" t="s">
         <v>52</v>
-      </c>
-      <c r="G30" t="s">
-        <v>18</v>
       </c>
       <c r="H30" t="s">
         <v>53</v>
@@ -4734,7 +4734,7 @@
         <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K30" t="s">
         <v>21</v>
@@ -4743,7 +4743,7 @@
         <v>22</v>
       </c>
       <c r="M30" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4763,10 +4763,10 @@
         <v>143</v>
       </c>
       <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
         <v>52</v>
-      </c>
-      <c r="G31" t="s">
-        <v>18</v>
       </c>
       <c r="H31" t="s">
         <v>144</v>
@@ -4775,7 +4775,7 @@
         <v>145</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K31" t="s">
         <v>21</v>
@@ -4784,7 +4784,7 @@
         <v>22</v>
       </c>
       <c r="M31" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4804,10 +4804,10 @@
         <v>148</v>
       </c>
       <c r="F32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
         <v>52</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
       </c>
       <c r="H32" t="s">
         <v>144</v>
@@ -4816,7 +4816,7 @@
         <v>149</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K32" t="s">
         <v>21</v>
@@ -4825,7 +4825,7 @@
         <v>22</v>
       </c>
       <c r="M32" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4845,10 +4845,10 @@
         <v>152</v>
       </c>
       <c r="F33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" t="s">
         <v>52</v>
-      </c>
-      <c r="G33" t="s">
-        <v>18</v>
       </c>
       <c r="H33" t="s">
         <v>144</v>
@@ -4857,7 +4857,7 @@
         <v>153</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K33" t="s">
         <v>21</v>
@@ -4866,7 +4866,7 @@
         <v>22</v>
       </c>
       <c r="M33" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4886,10 +4886,10 @@
         <v>156</v>
       </c>
       <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" t="s">
         <v>52</v>
-      </c>
-      <c r="G34" t="s">
-        <v>18</v>
       </c>
       <c r="H34" t="s">
         <v>144</v>
@@ -4898,7 +4898,7 @@
         <v>157</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K34" t="s">
         <v>21</v>
@@ -4907,7 +4907,7 @@
         <v>22</v>
       </c>
       <c r="M34" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -4927,10 +4927,10 @@
         <v>160</v>
       </c>
       <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" t="s">
         <v>52</v>
-      </c>
-      <c r="G35" t="s">
-        <v>18</v>
       </c>
       <c r="H35" t="s">
         <v>144</v>
@@ -4939,7 +4939,7 @@
         <v>161</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K35" t="s">
         <v>21</v>
@@ -4948,7 +4948,7 @@
         <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -4968,10 +4968,10 @@
         <v>164</v>
       </c>
       <c r="F36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" t="s">
         <v>52</v>
-      </c>
-      <c r="G36" t="s">
-        <v>18</v>
       </c>
       <c r="H36" t="s">
         <v>144</v>
@@ -4980,7 +4980,7 @@
         <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K36" t="s">
         <v>21</v>
@@ -4989,7 +4989,7 @@
         <v>22</v>
       </c>
       <c r="M36" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5009,10 +5009,10 @@
         <v>168</v>
       </c>
       <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" t="s">
         <v>52</v>
-      </c>
-      <c r="G37" t="s">
-        <v>18</v>
       </c>
       <c r="H37" t="s">
         <v>144</v>
@@ -5021,7 +5021,7 @@
         <v>169</v>
       </c>
       <c r="J37" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K37" t="s">
         <v>21</v>
@@ -5030,7 +5030,7 @@
         <v>22</v>
       </c>
       <c r="M37" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5050,10 +5050,10 @@
         <v>172</v>
       </c>
       <c r="F38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" t="s">
         <v>52</v>
-      </c>
-      <c r="G38" t="s">
-        <v>18</v>
       </c>
       <c r="H38" t="s">
         <v>144</v>
@@ -5062,7 +5062,7 @@
         <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K38" t="s">
         <v>21</v>
@@ -5071,7 +5071,7 @@
         <v>22</v>
       </c>
       <c r="M38" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -5091,10 +5091,10 @@
         <v>176</v>
       </c>
       <c r="F39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" t="s">
         <v>52</v>
-      </c>
-      <c r="G39" t="s">
-        <v>18</v>
       </c>
       <c r="H39" t="s">
         <v>144</v>
@@ -5103,7 +5103,7 @@
         <v>177</v>
       </c>
       <c r="J39" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K39" t="s">
         <v>21</v>
@@ -5112,7 +5112,7 @@
         <v>22</v>
       </c>
       <c r="M39" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -5132,10 +5132,10 @@
         <v>181</v>
       </c>
       <c r="F40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" t="s">
         <v>52</v>
-      </c>
-      <c r="G40" t="s">
-        <v>18</v>
       </c>
       <c r="H40" t="s">
         <v>182</v>
@@ -5144,7 +5144,7 @@
         <v>183</v>
       </c>
       <c r="J40" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K40" t="s">
         <v>21</v>
@@ -5153,7 +5153,7 @@
         <v>22</v>
       </c>
       <c r="M40" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -5173,10 +5173,10 @@
         <v>186</v>
       </c>
       <c r="F41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" t="s">
         <v>52</v>
-      </c>
-      <c r="G41" t="s">
-        <v>18</v>
       </c>
       <c r="H41" t="s">
         <v>182</v>
@@ -5185,7 +5185,7 @@
         <v>187</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K41" t="s">
         <v>21</v>
@@ -5194,7 +5194,7 @@
         <v>22</v>
       </c>
       <c r="M41" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5214,10 +5214,10 @@
         <v>190</v>
       </c>
       <c r="F42" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" t="s">
         <v>52</v>
-      </c>
-      <c r="G42" t="s">
-        <v>18</v>
       </c>
       <c r="H42" t="s">
         <v>182</v>
@@ -5226,7 +5226,7 @@
         <v>191</v>
       </c>
       <c r="J42" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K42" t="s">
         <v>21</v>
@@ -5235,7 +5235,7 @@
         <v>22</v>
       </c>
       <c r="M42" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5255,10 +5255,10 @@
         <v>194</v>
       </c>
       <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
         <v>52</v>
-      </c>
-      <c r="G43" t="s">
-        <v>18</v>
       </c>
       <c r="H43" t="s">
         <v>182</v>
@@ -5267,7 +5267,7 @@
         <v>195</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K43" t="s">
         <v>21</v>
@@ -5276,7 +5276,7 @@
         <v>22</v>
       </c>
       <c r="M43" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5296,10 +5296,10 @@
         <v>198</v>
       </c>
       <c r="F44" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" t="s">
         <v>52</v>
-      </c>
-      <c r="G44" t="s">
-        <v>18</v>
       </c>
       <c r="H44" t="s">
         <v>182</v>
@@ -5308,7 +5308,7 @@
         <v>199</v>
       </c>
       <c r="J44" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K44" t="s">
         <v>21</v>
@@ -5317,7 +5317,7 @@
         <v>22</v>
       </c>
       <c r="M44" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -5337,10 +5337,10 @@
         <v>203</v>
       </c>
       <c r="F45" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" t="s">
         <v>52</v>
-      </c>
-      <c r="G45" t="s">
-        <v>18</v>
       </c>
       <c r="H45" t="s">
         <v>204</v>
@@ -5349,7 +5349,7 @@
         <v>205</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K45" t="s">
         <v>21</v>
@@ -5358,7 +5358,7 @@
         <v>22</v>
       </c>
       <c r="M45" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -5378,10 +5378,10 @@
         <v>208</v>
       </c>
       <c r="F46" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" t="s">
         <v>52</v>
-      </c>
-      <c r="G46" t="s">
-        <v>18</v>
       </c>
       <c r="H46" t="s">
         <v>204</v>
@@ -5390,7 +5390,7 @@
         <v>209</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K46" t="s">
         <v>21</v>
@@ -5399,7 +5399,7 @@
         <v>22</v>
       </c>
       <c r="M46" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -5419,10 +5419,10 @@
         <v>212</v>
       </c>
       <c r="F47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" t="s">
         <v>52</v>
-      </c>
-      <c r="G47" t="s">
-        <v>18</v>
       </c>
       <c r="H47" t="s">
         <v>204</v>
@@ -5431,7 +5431,7 @@
         <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K47" t="s">
         <v>21</v>
@@ -5440,7 +5440,7 @@
         <v>22</v>
       </c>
       <c r="M47" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -5460,10 +5460,10 @@
         <v>216</v>
       </c>
       <c r="F48" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" t="s">
         <v>52</v>
-      </c>
-      <c r="G48" t="s">
-        <v>18</v>
       </c>
       <c r="H48" t="s">
         <v>204</v>
@@ -5472,7 +5472,7 @@
         <v>217</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K48" t="s">
         <v>21</v>
@@ -5481,7 +5481,7 @@
         <v>22</v>
       </c>
       <c r="M48" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -5501,10 +5501,10 @@
         <v>220</v>
       </c>
       <c r="F49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" t="s">
         <v>52</v>
-      </c>
-      <c r="G49" t="s">
-        <v>18</v>
       </c>
       <c r="H49" t="s">
         <v>204</v>
@@ -5513,7 +5513,7 @@
         <v>221</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K49" t="s">
         <v>21</v>
@@ -5522,7 +5522,7 @@
         <v>22</v>
       </c>
       <c r="M49" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -5542,10 +5542,10 @@
         <v>224</v>
       </c>
       <c r="F50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" t="s">
         <v>52</v>
-      </c>
-      <c r="G50" t="s">
-        <v>18</v>
       </c>
       <c r="H50" t="s">
         <v>204</v>
@@ -5554,7 +5554,7 @@
         <v>225</v>
       </c>
       <c r="J50" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K50" t="s">
         <v>21</v>
@@ -5563,7 +5563,7 @@
         <v>22</v>
       </c>
       <c r="M50" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -5583,10 +5583,10 @@
         <v>228</v>
       </c>
       <c r="F51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" t="s">
         <v>52</v>
-      </c>
-      <c r="G51" t="s">
-        <v>18</v>
       </c>
       <c r="H51" t="s">
         <v>204</v>
@@ -5595,7 +5595,7 @@
         <v>229</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K51" t="s">
         <v>21</v>
@@ -5604,7 +5604,7 @@
         <v>22</v>
       </c>
       <c r="M51" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -5624,10 +5624,10 @@
         <v>232</v>
       </c>
       <c r="F52" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" t="s">
         <v>52</v>
-      </c>
-      <c r="G52" t="s">
-        <v>18</v>
       </c>
       <c r="H52" t="s">
         <v>204</v>
@@ -5636,7 +5636,7 @@
         <v>233</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K52" t="s">
         <v>21</v>
@@ -5645,7 +5645,7 @@
         <v>22</v>
       </c>
       <c r="M52" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -5665,10 +5665,10 @@
         <v>236</v>
       </c>
       <c r="F53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" t="s">
         <v>52</v>
-      </c>
-      <c r="G53" t="s">
-        <v>18</v>
       </c>
       <c r="H53" t="s">
         <v>204</v>
@@ -5677,7 +5677,7 @@
         <v>237</v>
       </c>
       <c r="J53" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K53" t="s">
         <v>21</v>
@@ -5686,7 +5686,7 @@
         <v>22</v>
       </c>
       <c r="M53" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5706,10 +5706,10 @@
         <v>240</v>
       </c>
       <c r="F54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" t="s">
         <v>52</v>
-      </c>
-      <c r="G54" t="s">
-        <v>18</v>
       </c>
       <c r="H54" t="s">
         <v>204</v>
@@ -5718,7 +5718,7 @@
         <v>241</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K54" t="s">
         <v>21</v>
@@ -5727,7 +5727,7 @@
         <v>22</v>
       </c>
       <c r="M54" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -5747,10 +5747,10 @@
         <v>244</v>
       </c>
       <c r="F55" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" t="s">
         <v>52</v>
-      </c>
-      <c r="G55" t="s">
-        <v>18</v>
       </c>
       <c r="H55" t="s">
         <v>204</v>
@@ -5759,7 +5759,7 @@
         <v>245</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K55" t="s">
         <v>21</v>
@@ -5768,7 +5768,7 @@
         <v>22</v>
       </c>
       <c r="M55" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -5788,10 +5788,10 @@
         <v>248</v>
       </c>
       <c r="F56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" t="s">
         <v>52</v>
-      </c>
-      <c r="G56" t="s">
-        <v>18</v>
       </c>
       <c r="H56" t="s">
         <v>204</v>
@@ -5800,7 +5800,7 @@
         <v>249</v>
       </c>
       <c r="J56" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K56" t="s">
         <v>21</v>
@@ -5809,7 +5809,7 @@
         <v>22</v>
       </c>
       <c r="M56" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -5829,10 +5829,10 @@
         <v>252</v>
       </c>
       <c r="F57" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" t="s">
         <v>52</v>
-      </c>
-      <c r="G57" t="s">
-        <v>18</v>
       </c>
       <c r="H57" t="s">
         <v>204</v>
@@ -5841,7 +5841,7 @@
         <v>253</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K57" t="s">
         <v>21</v>
@@ -5850,7 +5850,7 @@
         <v>22</v>
       </c>
       <c r="M57" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -5870,10 +5870,10 @@
         <v>256</v>
       </c>
       <c r="F58" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" t="s">
         <v>52</v>
-      </c>
-      <c r="G58" t="s">
-        <v>18</v>
       </c>
       <c r="H58" t="s">
         <v>204</v>
@@ -5882,7 +5882,7 @@
         <v>257</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K58" t="s">
         <v>21</v>
@@ -5891,7 +5891,7 @@
         <v>22</v>
       </c>
       <c r="M58" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -5911,10 +5911,10 @@
         <v>260</v>
       </c>
       <c r="F59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" t="s">
         <v>52</v>
-      </c>
-      <c r="G59" t="s">
-        <v>18</v>
       </c>
       <c r="H59" t="s">
         <v>204</v>
@@ -5923,7 +5923,7 @@
         <v>261</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K59" t="s">
         <v>21</v>
@@ -5932,7 +5932,7 @@
         <v>22</v>
       </c>
       <c r="M59" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -5952,10 +5952,10 @@
         <v>264</v>
       </c>
       <c r="F60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" t="s">
         <v>52</v>
-      </c>
-      <c r="G60" t="s">
-        <v>18</v>
       </c>
       <c r="H60" t="s">
         <v>204</v>
@@ -5964,7 +5964,7 @@
         <v>265</v>
       </c>
       <c r="J60" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K60" t="s">
         <v>21</v>
@@ -5973,7 +5973,7 @@
         <v>22</v>
       </c>
       <c r="M60" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -5993,10 +5993,10 @@
         <v>268</v>
       </c>
       <c r="F61" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" t="s">
         <v>52</v>
-      </c>
-      <c r="G61" t="s">
-        <v>18</v>
       </c>
       <c r="H61" t="s">
         <v>204</v>
@@ -6005,7 +6005,7 @@
         <v>269</v>
       </c>
       <c r="J61" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K61" t="s">
         <v>21</v>
@@ -6014,7 +6014,7 @@
         <v>22</v>
       </c>
       <c r="M61" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6046,16 +6046,16 @@
         <v>277</v>
       </c>
       <c r="J62" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K62" t="s">
         <v>21</v>
       </c>
       <c r="L62" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M62" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6087,16 +6087,16 @@
         <v>283</v>
       </c>
       <c r="J63" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K63" t="s">
         <v>21</v>
       </c>
       <c r="L63" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M63" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6128,16 +6128,16 @@
         <v>287</v>
       </c>
       <c r="J64" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K64" t="s">
         <v>21</v>
       </c>
       <c r="L64" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M64" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6169,16 +6169,16 @@
         <v>291</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K65" t="s">
         <v>21</v>
       </c>
       <c r="L65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M65" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6210,16 +6210,16 @@
         <v>295</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K66" t="s">
         <v>21</v>
       </c>
       <c r="L66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M66" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6251,16 +6251,16 @@
         <v>299</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K67" t="s">
         <v>21</v>
       </c>
       <c r="L67" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M67" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6292,16 +6292,16 @@
         <v>303</v>
       </c>
       <c r="J68" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K68" t="s">
         <v>21</v>
       </c>
       <c r="L68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M68" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6333,16 +6333,16 @@
         <v>307</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K69" t="s">
         <v>21</v>
       </c>
       <c r="L69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M69" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6374,16 +6374,16 @@
         <v>311</v>
       </c>
       <c r="J70" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K70" t="s">
         <v>21</v>
       </c>
       <c r="L70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M70" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6415,16 +6415,16 @@
         <v>315</v>
       </c>
       <c r="J71" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K71" t="s">
         <v>21</v>
       </c>
       <c r="L71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M71" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -6456,16 +6456,16 @@
         <v>319</v>
       </c>
       <c r="J72" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K72" t="s">
         <v>21</v>
       </c>
       <c r="L72" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M72" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -6497,16 +6497,16 @@
         <v>323</v>
       </c>
       <c r="J73" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K73" t="s">
         <v>21</v>
       </c>
       <c r="L73" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M73" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -6538,16 +6538,16 @@
         <v>327</v>
       </c>
       <c r="J74" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K74" t="s">
         <v>21</v>
       </c>
       <c r="L74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M74" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -6579,16 +6579,16 @@
         <v>331</v>
       </c>
       <c r="J75" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K75" t="s">
         <v>21</v>
       </c>
       <c r="L75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M75" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -6620,16 +6620,16 @@
         <v>335</v>
       </c>
       <c r="J76" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K76" t="s">
         <v>21</v>
       </c>
       <c r="L76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M76" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -6661,16 +6661,16 @@
         <v>339</v>
       </c>
       <c r="J77" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K77" t="s">
         <v>21</v>
       </c>
       <c r="L77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M77" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6702,16 +6702,16 @@
         <v>343</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K78" t="s">
         <v>21</v>
       </c>
       <c r="L78" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M78" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -6743,16 +6743,16 @@
         <v>347</v>
       </c>
       <c r="J79" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K79" t="s">
         <v>21</v>
       </c>
       <c r="L79" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M79" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -6784,16 +6784,16 @@
         <v>351</v>
       </c>
       <c r="J80" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K80" t="s">
         <v>21</v>
       </c>
       <c r="L80" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M80" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -6825,16 +6825,16 @@
         <v>355</v>
       </c>
       <c r="J81" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K81" t="s">
         <v>21</v>
       </c>
       <c r="L81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M81" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -6866,16 +6866,16 @@
         <v>359</v>
       </c>
       <c r="J82" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K82" t="s">
         <v>21</v>
       </c>
       <c r="L82" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M82" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6907,16 +6907,16 @@
         <v>363</v>
       </c>
       <c r="J83" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K83" t="s">
         <v>21</v>
       </c>
       <c r="L83" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M83" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -6948,16 +6948,16 @@
         <v>367</v>
       </c>
       <c r="J84" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K84" t="s">
         <v>21</v>
       </c>
       <c r="L84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M84" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -6989,16 +6989,16 @@
         <v>371</v>
       </c>
       <c r="J85" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K85" t="s">
         <v>21</v>
       </c>
       <c r="L85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M85" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7030,16 +7030,16 @@
         <v>375</v>
       </c>
       <c r="J86" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K86" t="s">
         <v>21</v>
       </c>
       <c r="L86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M86" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7071,16 +7071,16 @@
         <v>379</v>
       </c>
       <c r="J87" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K87" t="s">
         <v>21</v>
       </c>
       <c r="L87" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M87" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7112,16 +7112,16 @@
         <v>383</v>
       </c>
       <c r="J88" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K88" t="s">
         <v>21</v>
       </c>
       <c r="L88" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M88" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7153,16 +7153,16 @@
         <v>387</v>
       </c>
       <c r="J89" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K89" t="s">
         <v>21</v>
       </c>
       <c r="L89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M89" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7194,16 +7194,16 @@
         <v>393</v>
       </c>
       <c r="J90" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K90" t="s">
         <v>21</v>
       </c>
       <c r="L90" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M90" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7235,16 +7235,16 @@
         <v>397</v>
       </c>
       <c r="J91" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K91" t="s">
         <v>21</v>
       </c>
       <c r="L91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M91" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7276,16 +7276,16 @@
         <v>401</v>
       </c>
       <c r="J92" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K92" t="s">
         <v>21</v>
       </c>
       <c r="L92" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M92" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7317,16 +7317,16 @@
         <v>405</v>
       </c>
       <c r="J93" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K93" t="s">
         <v>21</v>
       </c>
       <c r="L93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M93" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7358,16 +7358,16 @@
         <v>409</v>
       </c>
       <c r="J94" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K94" t="s">
         <v>21</v>
       </c>
       <c r="L94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M94" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7399,16 +7399,16 @@
         <v>413</v>
       </c>
       <c r="J95" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K95" t="s">
         <v>21</v>
       </c>
       <c r="L95" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M95" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7440,16 +7440,16 @@
         <v>417</v>
       </c>
       <c r="J96" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K96" t="s">
         <v>21</v>
       </c>
       <c r="L96" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M96" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -7481,16 +7481,16 @@
         <v>421</v>
       </c>
       <c r="J97" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K97" t="s">
         <v>21</v>
       </c>
       <c r="L97" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M97" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7522,16 +7522,16 @@
         <v>427</v>
       </c>
       <c r="J98" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K98" t="s">
         <v>21</v>
       </c>
       <c r="L98" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M98" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -7563,16 +7563,16 @@
         <v>431</v>
       </c>
       <c r="J99" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K99" t="s">
         <v>21</v>
       </c>
       <c r="L99" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M99" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -7604,16 +7604,16 @@
         <v>435</v>
       </c>
       <c r="J100" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K100" t="s">
         <v>21</v>
       </c>
       <c r="L100" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M100" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -7645,16 +7645,16 @@
         <v>439</v>
       </c>
       <c r="J101" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K101" t="s">
         <v>21</v>
       </c>
       <c r="L101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M101" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -7686,16 +7686,16 @@
         <v>443</v>
       </c>
       <c r="J102" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K102" t="s">
         <v>21</v>
       </c>
       <c r="L102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M102" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -7727,16 +7727,16 @@
         <v>447</v>
       </c>
       <c r="J103" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K103" t="s">
         <v>21</v>
       </c>
       <c r="L103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M103" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -7768,16 +7768,16 @@
         <v>451</v>
       </c>
       <c r="J104" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K104" t="s">
         <v>21</v>
       </c>
       <c r="L104" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M104" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -7809,16 +7809,16 @@
         <v>455</v>
       </c>
       <c r="J105" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K105" t="s">
         <v>21</v>
       </c>
       <c r="L105" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M105" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -7850,16 +7850,16 @@
         <v>459</v>
       </c>
       <c r="J106" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K106" t="s">
         <v>21</v>
       </c>
       <c r="L106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M106" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -7891,16 +7891,16 @@
         <v>463</v>
       </c>
       <c r="J107" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K107" t="s">
         <v>21</v>
       </c>
       <c r="L107" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M107" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -7932,16 +7932,16 @@
         <v>467</v>
       </c>
       <c r="J108" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K108" t="s">
         <v>21</v>
       </c>
       <c r="L108" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M108" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -7973,16 +7973,16 @@
         <v>471</v>
       </c>
       <c r="J109" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K109" t="s">
         <v>21</v>
       </c>
       <c r="L109" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M109" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -8014,16 +8014,16 @@
         <v>475</v>
       </c>
       <c r="J110" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K110" t="s">
         <v>21</v>
       </c>
       <c r="L110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M110" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -8055,16 +8055,16 @@
         <v>479</v>
       </c>
       <c r="J111" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K111" t="s">
         <v>21</v>
       </c>
       <c r="L111" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M111" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -8096,16 +8096,16 @@
         <v>483</v>
       </c>
       <c r="J112" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K112" t="s">
         <v>21</v>
       </c>
       <c r="L112" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M112" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -8137,16 +8137,16 @@
         <v>487</v>
       </c>
       <c r="J113" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="K113" t="s">
         <v>21</v>
       </c>
       <c r="L113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M113" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -8163,25 +8163,25 @@
         <v>490</v>
       </c>
       <c r="F114" t="s">
+        <v>274</v>
+      </c>
+      <c r="G114" t="s">
         <v>491</v>
-      </c>
-      <c r="G114" t="s">
-        <v>275</v>
       </c>
       <c r="I114" t="s">
         <v>492</v>
       </c>
       <c r="J114" t="s">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="K114" t="s">
         <v>21</v>
       </c>
       <c r="L114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M114" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -8198,25 +8198,25 @@
         <v>496</v>
       </c>
       <c r="F115" t="s">
+        <v>274</v>
+      </c>
+      <c r="G115" t="s">
         <v>491</v>
-      </c>
-      <c r="G115" t="s">
-        <v>275</v>
       </c>
       <c r="I115" t="s">
         <v>497</v>
       </c>
       <c r="J115" t="s">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="K115" t="s">
         <v>21</v>
       </c>
       <c r="L115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M115" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -8233,25 +8233,25 @@
         <v>500</v>
       </c>
       <c r="F116" t="s">
+        <v>274</v>
+      </c>
+      <c r="G116" t="s">
         <v>491</v>
-      </c>
-      <c r="G116" t="s">
-        <v>275</v>
       </c>
       <c r="I116" t="s">
         <v>501</v>
       </c>
       <c r="J116" t="s">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="K116" t="s">
         <v>21</v>
       </c>
       <c r="L116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M116" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -8268,25 +8268,25 @@
         <v>504</v>
       </c>
       <c r="F117" t="s">
+        <v>274</v>
+      </c>
+      <c r="G117" t="s">
         <v>491</v>
-      </c>
-      <c r="G117" t="s">
-        <v>275</v>
       </c>
       <c r="I117" t="s">
         <v>505</v>
       </c>
       <c r="J117" t="s">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="K117" t="s">
         <v>21</v>
       </c>
       <c r="L117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M117" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -8303,25 +8303,25 @@
         <v>508</v>
       </c>
       <c r="F118" t="s">
+        <v>274</v>
+      </c>
+      <c r="G118" t="s">
         <v>491</v>
-      </c>
-      <c r="G118" t="s">
-        <v>275</v>
       </c>
       <c r="I118" t="s">
         <v>509</v>
       </c>
       <c r="J118" t="s">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="K118" t="s">
         <v>21</v>
       </c>
       <c r="L118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M118" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -8340,11 +8340,11 @@
       <c r="I119" t="s">
         <v>513</v>
       </c>
-      <c r="J119" t="s">
-        <v>20</v>
-      </c>
       <c r="K119" t="s">
         <v>21</v>
+      </c>
+      <c r="M119" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -8370,16 +8370,16 @@
         <v>519</v>
       </c>
       <c r="J120" t="s">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="K120" t="s">
         <v>21</v>
       </c>
       <c r="L120" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M120" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -8405,16 +8405,16 @@
         <v>525</v>
       </c>
       <c r="J121" t="s">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="K121" t="s">
         <v>21</v>
       </c>
       <c r="L121" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M121" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -8440,16 +8440,16 @@
         <v>529</v>
       </c>
       <c r="J122" t="s">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="K122" t="s">
         <v>21</v>
       </c>
       <c r="L122" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M122" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -8475,16 +8475,16 @@
         <v>533</v>
       </c>
       <c r="J123" t="s">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="K123" t="s">
         <v>21</v>
       </c>
       <c r="L123" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M123" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -8510,16 +8510,16 @@
         <v>537</v>
       </c>
       <c r="J124" t="s">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="K124" t="s">
         <v>21</v>
       </c>
       <c r="L124" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M124" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -8536,25 +8536,25 @@
         <v>540</v>
       </c>
       <c r="F125" t="s">
+        <v>517</v>
+      </c>
+      <c r="G125" t="s">
         <v>541</v>
-      </c>
-      <c r="G125" t="s">
-        <v>518</v>
       </c>
       <c r="I125" t="s">
         <v>542</v>
       </c>
       <c r="J125" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K125" t="s">
         <v>21</v>
       </c>
       <c r="L125" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M125" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -8571,25 +8571,25 @@
         <v>546</v>
       </c>
       <c r="F126" t="s">
+        <v>517</v>
+      </c>
+      <c r="G126" t="s">
         <v>541</v>
-      </c>
-      <c r="G126" t="s">
-        <v>518</v>
       </c>
       <c r="I126" t="s">
         <v>547</v>
       </c>
       <c r="J126" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K126" t="s">
         <v>21</v>
       </c>
       <c r="L126" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M126" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -8606,25 +8606,25 @@
         <v>550</v>
       </c>
       <c r="F127" t="s">
+        <v>517</v>
+      </c>
+      <c r="G127" t="s">
         <v>541</v>
-      </c>
-      <c r="G127" t="s">
-        <v>518</v>
       </c>
       <c r="I127" t="s">
         <v>551</v>
       </c>
       <c r="J127" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K127" t="s">
         <v>21</v>
       </c>
       <c r="L127" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M127" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -8641,25 +8641,25 @@
         <v>554</v>
       </c>
       <c r="F128" t="s">
+        <v>517</v>
+      </c>
+      <c r="G128" t="s">
         <v>541</v>
-      </c>
-      <c r="G128" t="s">
-        <v>518</v>
       </c>
       <c r="I128" t="s">
         <v>555</v>
       </c>
       <c r="J128" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K128" t="s">
         <v>21</v>
       </c>
       <c r="L128" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M128" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -8676,25 +8676,25 @@
         <v>558</v>
       </c>
       <c r="F129" t="s">
+        <v>517</v>
+      </c>
+      <c r="G129" t="s">
         <v>541</v>
-      </c>
-      <c r="G129" t="s">
-        <v>518</v>
       </c>
       <c r="I129" t="s">
         <v>559</v>
       </c>
       <c r="J129" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K129" t="s">
         <v>21</v>
       </c>
       <c r="L129" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M129" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -8711,25 +8711,25 @@
         <v>562</v>
       </c>
       <c r="F130" t="s">
+        <v>517</v>
+      </c>
+      <c r="G130" t="s">
         <v>541</v>
-      </c>
-      <c r="G130" t="s">
-        <v>518</v>
       </c>
       <c r="I130" t="s">
         <v>563</v>
       </c>
       <c r="J130" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K130" t="s">
         <v>21</v>
       </c>
       <c r="L130" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M130" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -8746,25 +8746,25 @@
         <v>566</v>
       </c>
       <c r="F131" t="s">
+        <v>517</v>
+      </c>
+      <c r="G131" t="s">
         <v>541</v>
-      </c>
-      <c r="G131" t="s">
-        <v>518</v>
       </c>
       <c r="I131" t="s">
         <v>567</v>
       </c>
       <c r="J131" t="s">
-        <v>20</v>
+        <v>543</v>
       </c>
       <c r="K131" t="s">
         <v>21</v>
       </c>
       <c r="L131" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M131" t="s">
-        <v>543</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -8781,25 +8781,25 @@
         <v>570</v>
       </c>
       <c r="F132" t="s">
+        <v>517</v>
+      </c>
+      <c r="G132" t="s">
         <v>571</v>
-      </c>
-      <c r="G132" t="s">
-        <v>518</v>
       </c>
       <c r="I132" t="s">
         <v>572</v>
       </c>
       <c r="J132" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K132" t="s">
         <v>21</v>
       </c>
       <c r="L132" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M132" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -8816,25 +8816,25 @@
         <v>576</v>
       </c>
       <c r="F133" t="s">
+        <v>517</v>
+      </c>
+      <c r="G133" t="s">
         <v>571</v>
-      </c>
-      <c r="G133" t="s">
-        <v>518</v>
       </c>
       <c r="I133" t="s">
         <v>577</v>
       </c>
       <c r="J133" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K133" t="s">
         <v>21</v>
       </c>
       <c r="L133" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M133" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -8851,25 +8851,25 @@
         <v>580</v>
       </c>
       <c r="F134" t="s">
+        <v>517</v>
+      </c>
+      <c r="G134" t="s">
         <v>571</v>
-      </c>
-      <c r="G134" t="s">
-        <v>518</v>
       </c>
       <c r="I134" t="s">
         <v>581</v>
       </c>
       <c r="J134" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K134" t="s">
         <v>21</v>
       </c>
       <c r="L134" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M134" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -8886,25 +8886,25 @@
         <v>584</v>
       </c>
       <c r="F135" t="s">
+        <v>517</v>
+      </c>
+      <c r="G135" t="s">
         <v>571</v>
-      </c>
-      <c r="G135" t="s">
-        <v>518</v>
       </c>
       <c r="I135" t="s">
         <v>585</v>
       </c>
       <c r="J135" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K135" t="s">
         <v>21</v>
       </c>
       <c r="L135" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M135" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -8921,25 +8921,25 @@
         <v>588</v>
       </c>
       <c r="F136" t="s">
+        <v>517</v>
+      </c>
+      <c r="G136" t="s">
         <v>571</v>
-      </c>
-      <c r="G136" t="s">
-        <v>518</v>
       </c>
       <c r="I136" t="s">
         <v>589</v>
       </c>
       <c r="J136" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K136" t="s">
         <v>21</v>
       </c>
       <c r="L136" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M136" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -8956,25 +8956,25 @@
         <v>592</v>
       </c>
       <c r="F137" t="s">
+        <v>517</v>
+      </c>
+      <c r="G137" t="s">
         <v>571</v>
-      </c>
-      <c r="G137" t="s">
-        <v>518</v>
       </c>
       <c r="I137" t="s">
         <v>593</v>
       </c>
       <c r="J137" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K137" t="s">
         <v>21</v>
       </c>
       <c r="L137" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M137" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -8991,25 +8991,25 @@
         <v>596</v>
       </c>
       <c r="F138" t="s">
+        <v>517</v>
+      </c>
+      <c r="G138" t="s">
         <v>571</v>
-      </c>
-      <c r="G138" t="s">
-        <v>518</v>
       </c>
       <c r="I138" t="s">
         <v>597</v>
       </c>
       <c r="J138" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K138" t="s">
         <v>21</v>
       </c>
       <c r="L138" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M138" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -9026,25 +9026,25 @@
         <v>600</v>
       </c>
       <c r="F139" t="s">
+        <v>517</v>
+      </c>
+      <c r="G139" t="s">
         <v>571</v>
-      </c>
-      <c r="G139" t="s">
-        <v>518</v>
       </c>
       <c r="I139" t="s">
         <v>601</v>
       </c>
       <c r="J139" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K139" t="s">
         <v>21</v>
       </c>
       <c r="L139" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M139" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -9061,25 +9061,25 @@
         <v>604</v>
       </c>
       <c r="F140" t="s">
+        <v>517</v>
+      </c>
+      <c r="G140" t="s">
         <v>571</v>
-      </c>
-      <c r="G140" t="s">
-        <v>518</v>
       </c>
       <c r="I140" t="s">
         <v>605</v>
       </c>
       <c r="J140" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K140" t="s">
         <v>21</v>
       </c>
       <c r="L140" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M140" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -9096,25 +9096,25 @@
         <v>608</v>
       </c>
       <c r="F141" t="s">
+        <v>517</v>
+      </c>
+      <c r="G141" t="s">
         <v>571</v>
-      </c>
-      <c r="G141" t="s">
-        <v>518</v>
       </c>
       <c r="I141" t="s">
         <v>609</v>
       </c>
       <c r="J141" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K141" t="s">
         <v>21</v>
       </c>
       <c r="L141" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M141" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -9131,25 +9131,25 @@
         <v>612</v>
       </c>
       <c r="F142" t="s">
+        <v>517</v>
+      </c>
+      <c r="G142" t="s">
         <v>571</v>
-      </c>
-      <c r="G142" t="s">
-        <v>518</v>
       </c>
       <c r="I142" t="s">
         <v>613</v>
       </c>
       <c r="J142" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="K142" t="s">
         <v>21</v>
       </c>
       <c r="L142" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M142" t="s">
-        <v>573</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -9166,25 +9166,25 @@
         <v>616</v>
       </c>
       <c r="F143" t="s">
+        <v>517</v>
+      </c>
+      <c r="G143" t="s">
         <v>617</v>
-      </c>
-      <c r="G143" t="s">
-        <v>518</v>
       </c>
       <c r="I143" t="s">
         <v>618</v>
       </c>
       <c r="J143" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K143" t="s">
         <v>21</v>
       </c>
       <c r="L143" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M143" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -9201,25 +9201,25 @@
         <v>622</v>
       </c>
       <c r="F144" t="s">
+        <v>517</v>
+      </c>
+      <c r="G144" t="s">
         <v>617</v>
-      </c>
-      <c r="G144" t="s">
-        <v>518</v>
       </c>
       <c r="I144" t="s">
         <v>623</v>
       </c>
       <c r="J144" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K144" t="s">
         <v>21</v>
       </c>
       <c r="L144" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M144" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -9236,25 +9236,25 @@
         <v>626</v>
       </c>
       <c r="F145" t="s">
+        <v>517</v>
+      </c>
+      <c r="G145" t="s">
         <v>617</v>
-      </c>
-      <c r="G145" t="s">
-        <v>518</v>
       </c>
       <c r="I145" t="s">
         <v>627</v>
       </c>
       <c r="J145" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K145" t="s">
         <v>21</v>
       </c>
       <c r="L145" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M145" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -9271,25 +9271,25 @@
         <v>630</v>
       </c>
       <c r="F146" t="s">
+        <v>517</v>
+      </c>
+      <c r="G146" t="s">
         <v>617</v>
-      </c>
-      <c r="G146" t="s">
-        <v>518</v>
       </c>
       <c r="I146" t="s">
         <v>631</v>
       </c>
       <c r="J146" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K146" t="s">
         <v>21</v>
       </c>
       <c r="L146" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M146" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -9306,25 +9306,25 @@
         <v>634</v>
       </c>
       <c r="F147" t="s">
+        <v>517</v>
+      </c>
+      <c r="G147" t="s">
         <v>617</v>
-      </c>
-      <c r="G147" t="s">
-        <v>518</v>
       </c>
       <c r="I147" t="s">
         <v>635</v>
       </c>
       <c r="J147" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K147" t="s">
         <v>21</v>
       </c>
       <c r="L147" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M147" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -9341,25 +9341,25 @@
         <v>638</v>
       </c>
       <c r="F148" t="s">
+        <v>517</v>
+      </c>
+      <c r="G148" t="s">
         <v>617</v>
-      </c>
-      <c r="G148" t="s">
-        <v>518</v>
       </c>
       <c r="I148" t="s">
         <v>639</v>
       </c>
       <c r="J148" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K148" t="s">
         <v>21</v>
       </c>
       <c r="L148" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M148" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -9376,25 +9376,25 @@
         <v>642</v>
       </c>
       <c r="F149" t="s">
+        <v>517</v>
+      </c>
+      <c r="G149" t="s">
         <v>617</v>
-      </c>
-      <c r="G149" t="s">
-        <v>518</v>
       </c>
       <c r="I149" t="s">
         <v>643</v>
       </c>
       <c r="J149" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K149" t="s">
         <v>21</v>
       </c>
       <c r="L149" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M149" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -9411,25 +9411,25 @@
         <v>646</v>
       </c>
       <c r="F150" t="s">
+        <v>517</v>
+      </c>
+      <c r="G150" t="s">
         <v>617</v>
-      </c>
-      <c r="G150" t="s">
-        <v>518</v>
       </c>
       <c r="I150" t="s">
         <v>647</v>
       </c>
       <c r="J150" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K150" t="s">
         <v>21</v>
       </c>
       <c r="L150" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M150" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -9446,25 +9446,25 @@
         <v>650</v>
       </c>
       <c r="F151" t="s">
+        <v>517</v>
+      </c>
+      <c r="G151" t="s">
         <v>617</v>
-      </c>
-      <c r="G151" t="s">
-        <v>518</v>
       </c>
       <c r="I151" t="s">
         <v>651</v>
       </c>
       <c r="J151" t="s">
-        <v>20</v>
+        <v>619</v>
       </c>
       <c r="K151" t="s">
         <v>21</v>
       </c>
       <c r="L151" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M151" t="s">
-        <v>619</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -9481,25 +9481,25 @@
         <v>654</v>
       </c>
       <c r="F152" t="s">
+        <v>517</v>
+      </c>
+      <c r="G152" t="s">
         <v>655</v>
-      </c>
-      <c r="G152" t="s">
-        <v>518</v>
       </c>
       <c r="I152" t="s">
         <v>656</v>
       </c>
       <c r="J152" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K152" t="s">
         <v>21</v>
       </c>
       <c r="L152" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M152" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -9516,25 +9516,25 @@
         <v>660</v>
       </c>
       <c r="F153" t="s">
+        <v>517</v>
+      </c>
+      <c r="G153" t="s">
         <v>655</v>
-      </c>
-      <c r="G153" t="s">
-        <v>518</v>
       </c>
       <c r="I153" t="s">
         <v>661</v>
       </c>
       <c r="J153" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K153" t="s">
         <v>21</v>
       </c>
       <c r="L153" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M153" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -9551,25 +9551,25 @@
         <v>664</v>
       </c>
       <c r="F154" t="s">
+        <v>517</v>
+      </c>
+      <c r="G154" t="s">
         <v>655</v>
-      </c>
-      <c r="G154" t="s">
-        <v>518</v>
       </c>
       <c r="I154" t="s">
         <v>665</v>
       </c>
       <c r="J154" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K154" t="s">
         <v>21</v>
       </c>
       <c r="L154" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M154" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -9586,25 +9586,25 @@
         <v>668</v>
       </c>
       <c r="F155" t="s">
+        <v>517</v>
+      </c>
+      <c r="G155" t="s">
         <v>655</v>
-      </c>
-      <c r="G155" t="s">
-        <v>518</v>
       </c>
       <c r="I155" t="s">
         <v>669</v>
       </c>
       <c r="J155" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K155" t="s">
         <v>21</v>
       </c>
       <c r="L155" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M155" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -9621,25 +9621,25 @@
         <v>672</v>
       </c>
       <c r="F156" t="s">
+        <v>517</v>
+      </c>
+      <c r="G156" t="s">
         <v>655</v>
-      </c>
-      <c r="G156" t="s">
-        <v>518</v>
       </c>
       <c r="I156" t="s">
         <v>673</v>
       </c>
       <c r="J156" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K156" t="s">
         <v>21</v>
       </c>
       <c r="L156" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M156" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -9656,25 +9656,25 @@
         <v>676</v>
       </c>
       <c r="F157" t="s">
+        <v>517</v>
+      </c>
+      <c r="G157" t="s">
         <v>655</v>
-      </c>
-      <c r="G157" t="s">
-        <v>518</v>
       </c>
       <c r="I157" t="s">
         <v>677</v>
       </c>
       <c r="J157" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K157" t="s">
         <v>21</v>
       </c>
       <c r="L157" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M157" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -9691,25 +9691,25 @@
         <v>680</v>
       </c>
       <c r="F158" t="s">
+        <v>517</v>
+      </c>
+      <c r="G158" t="s">
         <v>655</v>
-      </c>
-      <c r="G158" t="s">
-        <v>518</v>
       </c>
       <c r="I158" t="s">
         <v>681</v>
       </c>
       <c r="J158" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K158" t="s">
         <v>21</v>
       </c>
       <c r="L158" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M158" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -9726,25 +9726,25 @@
         <v>684</v>
       </c>
       <c r="F159" t="s">
+        <v>517</v>
+      </c>
+      <c r="G159" t="s">
         <v>655</v>
-      </c>
-      <c r="G159" t="s">
-        <v>518</v>
       </c>
       <c r="I159" t="s">
         <v>685</v>
       </c>
       <c r="J159" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K159" t="s">
         <v>21</v>
       </c>
       <c r="L159" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M159" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -9761,25 +9761,25 @@
         <v>688</v>
       </c>
       <c r="F160" t="s">
+        <v>517</v>
+      </c>
+      <c r="G160" t="s">
         <v>655</v>
-      </c>
-      <c r="G160" t="s">
-        <v>518</v>
       </c>
       <c r="I160" t="s">
         <v>689</v>
       </c>
       <c r="J160" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K160" t="s">
         <v>21</v>
       </c>
       <c r="L160" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M160" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -9796,25 +9796,25 @@
         <v>692</v>
       </c>
       <c r="F161" t="s">
+        <v>517</v>
+      </c>
+      <c r="G161" t="s">
         <v>655</v>
-      </c>
-      <c r="G161" t="s">
-        <v>518</v>
       </c>
       <c r="I161" t="s">
         <v>693</v>
       </c>
       <c r="J161" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K161" t="s">
         <v>21</v>
       </c>
       <c r="L161" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M161" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -9831,25 +9831,25 @@
         <v>696</v>
       </c>
       <c r="F162" t="s">
+        <v>517</v>
+      </c>
+      <c r="G162" t="s">
         <v>655</v>
-      </c>
-      <c r="G162" t="s">
-        <v>518</v>
       </c>
       <c r="I162" t="s">
         <v>697</v>
       </c>
       <c r="J162" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K162" t="s">
         <v>21</v>
       </c>
       <c r="L162" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M162" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -9866,25 +9866,25 @@
         <v>700</v>
       </c>
       <c r="F163" t="s">
+        <v>517</v>
+      </c>
+      <c r="G163" t="s">
         <v>655</v>
-      </c>
-      <c r="G163" t="s">
-        <v>518</v>
       </c>
       <c r="I163" t="s">
         <v>701</v>
       </c>
       <c r="J163" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K163" t="s">
         <v>21</v>
       </c>
       <c r="L163" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M163" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -9901,25 +9901,25 @@
         <v>704</v>
       </c>
       <c r="F164" t="s">
+        <v>517</v>
+      </c>
+      <c r="G164" t="s">
         <v>655</v>
-      </c>
-      <c r="G164" t="s">
-        <v>518</v>
       </c>
       <c r="I164" t="s">
         <v>705</v>
       </c>
       <c r="J164" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K164" t="s">
         <v>21</v>
       </c>
       <c r="L164" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M164" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -9936,25 +9936,25 @@
         <v>708</v>
       </c>
       <c r="F165" t="s">
+        <v>517</v>
+      </c>
+      <c r="G165" t="s">
         <v>655</v>
-      </c>
-      <c r="G165" t="s">
-        <v>518</v>
       </c>
       <c r="I165" t="s">
         <v>709</v>
       </c>
       <c r="J165" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K165" t="s">
         <v>21</v>
       </c>
       <c r="L165" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M165" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -9971,25 +9971,25 @@
         <v>712</v>
       </c>
       <c r="F166" t="s">
+        <v>517</v>
+      </c>
+      <c r="G166" t="s">
         <v>655</v>
-      </c>
-      <c r="G166" t="s">
-        <v>518</v>
       </c>
       <c r="I166" t="s">
         <v>713</v>
       </c>
       <c r="J166" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K166" t="s">
         <v>21</v>
       </c>
       <c r="L166" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M166" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -10006,25 +10006,25 @@
         <v>716</v>
       </c>
       <c r="F167" t="s">
+        <v>517</v>
+      </c>
+      <c r="G167" t="s">
         <v>655</v>
-      </c>
-      <c r="G167" t="s">
-        <v>518</v>
       </c>
       <c r="I167" t="s">
         <v>717</v>
       </c>
       <c r="J167" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K167" t="s">
         <v>21</v>
       </c>
       <c r="L167" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M167" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -10041,25 +10041,25 @@
         <v>720</v>
       </c>
       <c r="F168" t="s">
+        <v>517</v>
+      </c>
+      <c r="G168" t="s">
         <v>655</v>
-      </c>
-      <c r="G168" t="s">
-        <v>518</v>
       </c>
       <c r="I168" t="s">
         <v>721</v>
       </c>
       <c r="J168" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K168" t="s">
         <v>21</v>
       </c>
       <c r="L168" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M168" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -10076,25 +10076,25 @@
         <v>724</v>
       </c>
       <c r="F169" t="s">
+        <v>517</v>
+      </c>
+      <c r="G169" t="s">
         <v>655</v>
-      </c>
-      <c r="G169" t="s">
-        <v>518</v>
       </c>
       <c r="I169" t="s">
         <v>725</v>
       </c>
       <c r="J169" t="s">
-        <v>20</v>
+        <v>657</v>
       </c>
       <c r="K169" t="s">
         <v>21</v>
       </c>
       <c r="L169" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M169" t="s">
-        <v>657</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -10120,16 +10120,16 @@
         <v>731</v>
       </c>
       <c r="J170" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K170" t="s">
         <v>21</v>
       </c>
       <c r="L170" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M170" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -10155,16 +10155,16 @@
         <v>737</v>
       </c>
       <c r="J171" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K171" t="s">
         <v>21</v>
       </c>
       <c r="L171" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M171" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:13">
@@ -10190,16 +10190,16 @@
         <v>741</v>
       </c>
       <c r="J172" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K172" t="s">
         <v>21</v>
       </c>
       <c r="L172" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M172" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -10225,16 +10225,16 @@
         <v>745</v>
       </c>
       <c r="J173" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K173" t="s">
         <v>21</v>
       </c>
       <c r="L173" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M173" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -10260,16 +10260,16 @@
         <v>749</v>
       </c>
       <c r="J174" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K174" t="s">
         <v>21</v>
       </c>
       <c r="L174" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M174" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -10295,16 +10295,16 @@
         <v>753</v>
       </c>
       <c r="J175" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K175" t="s">
         <v>21</v>
       </c>
       <c r="L175" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M175" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -10330,16 +10330,16 @@
         <v>757</v>
       </c>
       <c r="J176" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K176" t="s">
         <v>21</v>
       </c>
       <c r="L176" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M176" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -10365,16 +10365,16 @@
         <v>761</v>
       </c>
       <c r="J177" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K177" t="s">
         <v>21</v>
       </c>
       <c r="L177" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M177" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -10400,16 +10400,16 @@
         <v>765</v>
       </c>
       <c r="J178" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K178" t="s">
         <v>21</v>
       </c>
       <c r="L178" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M178" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -10435,16 +10435,16 @@
         <v>769</v>
       </c>
       <c r="J179" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K179" t="s">
         <v>21</v>
       </c>
       <c r="L179" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M179" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -10461,25 +10461,25 @@
         <v>772</v>
       </c>
       <c r="F180" t="s">
+        <v>729</v>
+      </c>
+      <c r="G180" t="s">
         <v>773</v>
-      </c>
-      <c r="G180" t="s">
-        <v>730</v>
       </c>
       <c r="I180" t="s">
         <v>774</v>
       </c>
       <c r="J180" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K180" t="s">
         <v>21</v>
       </c>
       <c r="L180" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M180" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -10499,10 +10499,10 @@
         <v>779</v>
       </c>
       <c r="F181" t="s">
+        <v>729</v>
+      </c>
+      <c r="G181" t="s">
         <v>773</v>
-      </c>
-      <c r="G181" t="s">
-        <v>730</v>
       </c>
       <c r="H181" t="s">
         <v>780</v>
@@ -10511,16 +10511,16 @@
         <v>781</v>
       </c>
       <c r="J181" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K181" t="s">
         <v>21</v>
       </c>
       <c r="L181" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M181" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -10540,10 +10540,10 @@
         <v>784</v>
       </c>
       <c r="F182" t="s">
+        <v>729</v>
+      </c>
+      <c r="G182" t="s">
         <v>773</v>
-      </c>
-      <c r="G182" t="s">
-        <v>730</v>
       </c>
       <c r="H182" t="s">
         <v>780</v>
@@ -10552,16 +10552,16 @@
         <v>785</v>
       </c>
       <c r="J182" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K182" t="s">
         <v>21</v>
       </c>
       <c r="L182" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M182" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -10578,25 +10578,25 @@
         <v>778</v>
       </c>
       <c r="F183" t="s">
+        <v>729</v>
+      </c>
+      <c r="G183" t="s">
         <v>773</v>
-      </c>
-      <c r="G183" t="s">
-        <v>730</v>
       </c>
       <c r="H183" t="s">
         <v>780</v>
       </c>
       <c r="J183" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K183" t="s">
         <v>21</v>
       </c>
       <c r="L183" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M183" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -10613,25 +10613,25 @@
         <v>790</v>
       </c>
       <c r="F184" t="s">
+        <v>729</v>
+      </c>
+      <c r="G184" t="s">
         <v>773</v>
-      </c>
-      <c r="G184" t="s">
-        <v>730</v>
       </c>
       <c r="I184" t="s">
         <v>791</v>
       </c>
       <c r="J184" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K184" t="s">
         <v>21</v>
       </c>
       <c r="L184" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M184" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -10648,25 +10648,25 @@
         <v>794</v>
       </c>
       <c r="F185" t="s">
+        <v>729</v>
+      </c>
+      <c r="G185" t="s">
         <v>773</v>
-      </c>
-      <c r="G185" t="s">
-        <v>730</v>
       </c>
       <c r="I185" t="s">
         <v>795</v>
       </c>
       <c r="J185" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K185" t="s">
         <v>21</v>
       </c>
       <c r="L185" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M185" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -10683,25 +10683,25 @@
         <v>798</v>
       </c>
       <c r="F186" t="s">
+        <v>729</v>
+      </c>
+      <c r="G186" t="s">
         <v>773</v>
-      </c>
-      <c r="G186" t="s">
-        <v>730</v>
       </c>
       <c r="I186" t="s">
         <v>799</v>
       </c>
       <c r="J186" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K186" t="s">
         <v>21</v>
       </c>
       <c r="L186" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M186" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -10718,25 +10718,25 @@
         <v>802</v>
       </c>
       <c r="F187" t="s">
+        <v>729</v>
+      </c>
+      <c r="G187" t="s">
         <v>773</v>
-      </c>
-      <c r="G187" t="s">
-        <v>730</v>
       </c>
       <c r="I187" t="s">
         <v>803</v>
       </c>
       <c r="J187" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K187" t="s">
         <v>21</v>
       </c>
       <c r="L187" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M187" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -10753,25 +10753,25 @@
         <v>806</v>
       </c>
       <c r="F188" t="s">
+        <v>729</v>
+      </c>
+      <c r="G188" t="s">
         <v>773</v>
-      </c>
-      <c r="G188" t="s">
-        <v>730</v>
       </c>
       <c r="I188" t="s">
         <v>807</v>
       </c>
       <c r="J188" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K188" t="s">
         <v>21</v>
       </c>
       <c r="L188" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M188" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -10788,25 +10788,25 @@
         <v>810</v>
       </c>
       <c r="F189" t="s">
+        <v>729</v>
+      </c>
+      <c r="G189" t="s">
         <v>773</v>
-      </c>
-      <c r="G189" t="s">
-        <v>730</v>
       </c>
       <c r="I189" t="s">
         <v>811</v>
       </c>
       <c r="J189" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K189" t="s">
         <v>21</v>
       </c>
       <c r="L189" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M189" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -10823,25 +10823,25 @@
         <v>814</v>
       </c>
       <c r="F190" t="s">
+        <v>729</v>
+      </c>
+      <c r="G190" t="s">
         <v>773</v>
-      </c>
-      <c r="G190" t="s">
-        <v>730</v>
       </c>
       <c r="I190" t="s">
         <v>815</v>
       </c>
       <c r="J190" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K190" t="s">
         <v>21</v>
       </c>
       <c r="L190" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M190" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -10858,25 +10858,25 @@
         <v>818</v>
       </c>
       <c r="F191" t="s">
+        <v>729</v>
+      </c>
+      <c r="G191" t="s">
         <v>773</v>
-      </c>
-      <c r="G191" t="s">
-        <v>730</v>
       </c>
       <c r="I191" t="s">
         <v>819</v>
       </c>
       <c r="J191" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K191" t="s">
         <v>21</v>
       </c>
       <c r="L191" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M191" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -10893,25 +10893,25 @@
         <v>822</v>
       </c>
       <c r="F192" t="s">
+        <v>729</v>
+      </c>
+      <c r="G192" t="s">
         <v>773</v>
-      </c>
-      <c r="G192" t="s">
-        <v>730</v>
       </c>
       <c r="I192" t="s">
         <v>823</v>
       </c>
       <c r="J192" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K192" t="s">
         <v>21</v>
       </c>
       <c r="L192" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M192" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -10928,25 +10928,25 @@
         <v>826</v>
       </c>
       <c r="F193" t="s">
+        <v>729</v>
+      </c>
+      <c r="G193" t="s">
         <v>773</v>
-      </c>
-      <c r="G193" t="s">
-        <v>730</v>
       </c>
       <c r="I193" t="s">
         <v>827</v>
       </c>
       <c r="J193" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K193" t="s">
         <v>21</v>
       </c>
       <c r="L193" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M193" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -10963,25 +10963,25 @@
         <v>830</v>
       </c>
       <c r="F194" t="s">
+        <v>729</v>
+      </c>
+      <c r="G194" t="s">
         <v>773</v>
-      </c>
-      <c r="G194" t="s">
-        <v>730</v>
       </c>
       <c r="I194" t="s">
         <v>831</v>
       </c>
       <c r="J194" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K194" t="s">
         <v>21</v>
       </c>
       <c r="L194" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M194" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -10998,25 +10998,25 @@
         <v>834</v>
       </c>
       <c r="F195" t="s">
+        <v>729</v>
+      </c>
+      <c r="G195" t="s">
         <v>773</v>
-      </c>
-      <c r="G195" t="s">
-        <v>730</v>
       </c>
       <c r="I195" t="s">
         <v>835</v>
       </c>
       <c r="J195" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K195" t="s">
         <v>21</v>
       </c>
       <c r="L195" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M195" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -11033,25 +11033,25 @@
         <v>838</v>
       </c>
       <c r="F196" t="s">
+        <v>729</v>
+      </c>
+      <c r="G196" t="s">
         <v>773</v>
-      </c>
-      <c r="G196" t="s">
-        <v>730</v>
       </c>
       <c r="I196" t="s">
         <v>839</v>
       </c>
       <c r="J196" t="s">
-        <v>20</v>
+        <v>775</v>
       </c>
       <c r="K196" t="s">
         <v>21</v>
       </c>
       <c r="L196" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M196" t="s">
-        <v>775</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -11068,25 +11068,25 @@
         <v>842</v>
       </c>
       <c r="F197" t="s">
+        <v>729</v>
+      </c>
+      <c r="G197" t="s">
         <v>843</v>
-      </c>
-      <c r="G197" t="s">
-        <v>730</v>
       </c>
       <c r="I197" t="s">
         <v>844</v>
       </c>
       <c r="J197" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K197" t="s">
         <v>21</v>
       </c>
       <c r="L197" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M197" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -11103,25 +11103,25 @@
         <v>848</v>
       </c>
       <c r="F198" t="s">
+        <v>729</v>
+      </c>
+      <c r="G198" t="s">
         <v>843</v>
-      </c>
-      <c r="G198" t="s">
-        <v>730</v>
       </c>
       <c r="I198" t="s">
         <v>849</v>
       </c>
       <c r="J198" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K198" t="s">
         <v>21</v>
       </c>
       <c r="L198" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M198" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -11138,25 +11138,25 @@
         <v>852</v>
       </c>
       <c r="F199" t="s">
+        <v>729</v>
+      </c>
+      <c r="G199" t="s">
         <v>843</v>
-      </c>
-      <c r="G199" t="s">
-        <v>730</v>
       </c>
       <c r="I199" t="s">
         <v>853</v>
       </c>
       <c r="J199" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K199" t="s">
         <v>21</v>
       </c>
       <c r="L199" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M199" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -11173,25 +11173,25 @@
         <v>856</v>
       </c>
       <c r="F200" t="s">
+        <v>729</v>
+      </c>
+      <c r="G200" t="s">
         <v>843</v>
-      </c>
-      <c r="G200" t="s">
-        <v>730</v>
       </c>
       <c r="I200" t="s">
         <v>857</v>
       </c>
       <c r="J200" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K200" t="s">
         <v>21</v>
       </c>
       <c r="L200" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M200" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -11208,25 +11208,25 @@
         <v>860</v>
       </c>
       <c r="F201" t="s">
+        <v>729</v>
+      </c>
+      <c r="G201" t="s">
         <v>843</v>
-      </c>
-      <c r="G201" t="s">
-        <v>730</v>
       </c>
       <c r="I201" t="s">
         <v>861</v>
       </c>
       <c r="J201" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K201" t="s">
         <v>21</v>
       </c>
       <c r="L201" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M201" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -11243,25 +11243,25 @@
         <v>864</v>
       </c>
       <c r="F202" t="s">
+        <v>729</v>
+      </c>
+      <c r="G202" t="s">
         <v>843</v>
-      </c>
-      <c r="G202" t="s">
-        <v>730</v>
       </c>
       <c r="I202" t="s">
         <v>865</v>
       </c>
       <c r="J202" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K202" t="s">
         <v>21</v>
       </c>
       <c r="L202" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M202" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -11278,25 +11278,25 @@
         <v>868</v>
       </c>
       <c r="F203" t="s">
+        <v>729</v>
+      </c>
+      <c r="G203" t="s">
         <v>843</v>
-      </c>
-      <c r="G203" t="s">
-        <v>730</v>
       </c>
       <c r="I203" t="s">
         <v>869</v>
       </c>
       <c r="J203" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K203" t="s">
         <v>21</v>
       </c>
       <c r="L203" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M203" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -11313,25 +11313,25 @@
         <v>872</v>
       </c>
       <c r="F204" t="s">
+        <v>729</v>
+      </c>
+      <c r="G204" t="s">
         <v>843</v>
-      </c>
-      <c r="G204" t="s">
-        <v>730</v>
       </c>
       <c r="I204" t="s">
         <v>873</v>
       </c>
       <c r="J204" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K204" t="s">
         <v>21</v>
       </c>
       <c r="L204" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M204" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -11348,25 +11348,25 @@
         <v>876</v>
       </c>
       <c r="F205" t="s">
+        <v>729</v>
+      </c>
+      <c r="G205" t="s">
         <v>843</v>
-      </c>
-      <c r="G205" t="s">
-        <v>730</v>
       </c>
       <c r="I205" t="s">
         <v>877</v>
       </c>
       <c r="J205" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K205" t="s">
         <v>21</v>
       </c>
       <c r="L205" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M205" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -11383,25 +11383,25 @@
         <v>880</v>
       </c>
       <c r="F206" t="s">
+        <v>729</v>
+      </c>
+      <c r="G206" t="s">
         <v>843</v>
-      </c>
-      <c r="G206" t="s">
-        <v>730</v>
       </c>
       <c r="I206" t="s">
         <v>881</v>
       </c>
       <c r="J206" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K206" t="s">
         <v>21</v>
       </c>
       <c r="L206" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M206" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -11418,25 +11418,25 @@
         <v>884</v>
       </c>
       <c r="F207" t="s">
+        <v>729</v>
+      </c>
+      <c r="G207" t="s">
         <v>843</v>
-      </c>
-      <c r="G207" t="s">
-        <v>730</v>
       </c>
       <c r="I207" t="s">
         <v>885</v>
       </c>
       <c r="J207" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K207" t="s">
         <v>21</v>
       </c>
       <c r="L207" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M207" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -11453,25 +11453,25 @@
         <v>888</v>
       </c>
       <c r="F208" t="s">
+        <v>729</v>
+      </c>
+      <c r="G208" t="s">
         <v>843</v>
-      </c>
-      <c r="G208" t="s">
-        <v>730</v>
       </c>
       <c r="I208" t="s">
         <v>889</v>
       </c>
       <c r="J208" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K208" t="s">
         <v>21</v>
       </c>
       <c r="L208" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M208" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -11488,25 +11488,25 @@
         <v>892</v>
       </c>
       <c r="F209" t="s">
+        <v>729</v>
+      </c>
+      <c r="G209" t="s">
         <v>843</v>
-      </c>
-      <c r="G209" t="s">
-        <v>730</v>
       </c>
       <c r="I209" t="s">
         <v>893</v>
       </c>
       <c r="J209" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K209" t="s">
         <v>21</v>
       </c>
       <c r="L209" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M209" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -11523,25 +11523,25 @@
         <v>896</v>
       </c>
       <c r="F210" t="s">
+        <v>729</v>
+      </c>
+      <c r="G210" t="s">
         <v>843</v>
-      </c>
-      <c r="G210" t="s">
-        <v>730</v>
       </c>
       <c r="I210" t="s">
         <v>897</v>
       </c>
       <c r="J210" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K210" t="s">
         <v>21</v>
       </c>
       <c r="L210" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M210" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -11558,25 +11558,25 @@
         <v>900</v>
       </c>
       <c r="F211" t="s">
+        <v>729</v>
+      </c>
+      <c r="G211" t="s">
         <v>843</v>
-      </c>
-      <c r="G211" t="s">
-        <v>730</v>
       </c>
       <c r="I211" t="s">
         <v>901</v>
       </c>
       <c r="J211" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K211" t="s">
         <v>21</v>
       </c>
       <c r="L211" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M211" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -11593,25 +11593,25 @@
         <v>904</v>
       </c>
       <c r="F212" t="s">
+        <v>729</v>
+      </c>
+      <c r="G212" t="s">
         <v>843</v>
-      </c>
-      <c r="G212" t="s">
-        <v>730</v>
       </c>
       <c r="I212" t="s">
         <v>905</v>
       </c>
       <c r="J212" t="s">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="K212" t="s">
         <v>21</v>
       </c>
       <c r="L212" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M212" t="s">
-        <v>845</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -11628,25 +11628,25 @@
         <v>908</v>
       </c>
       <c r="F213" t="s">
+        <v>729</v>
+      </c>
+      <c r="G213" t="s">
         <v>909</v>
-      </c>
-      <c r="G213" t="s">
-        <v>730</v>
       </c>
       <c r="I213" t="s">
         <v>910</v>
       </c>
       <c r="J213" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K213" t="s">
         <v>21</v>
       </c>
       <c r="L213" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M213" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -11663,25 +11663,25 @@
         <v>914</v>
       </c>
       <c r="F214" t="s">
+        <v>729</v>
+      </c>
+      <c r="G214" t="s">
         <v>909</v>
-      </c>
-      <c r="G214" t="s">
-        <v>730</v>
       </c>
       <c r="I214" t="s">
         <v>915</v>
       </c>
       <c r="J214" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K214" t="s">
         <v>21</v>
       </c>
       <c r="L214" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M214" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -11698,25 +11698,25 @@
         <v>918</v>
       </c>
       <c r="F215" t="s">
+        <v>729</v>
+      </c>
+      <c r="G215" t="s">
         <v>909</v>
-      </c>
-      <c r="G215" t="s">
-        <v>730</v>
       </c>
       <c r="I215" t="s">
         <v>919</v>
       </c>
       <c r="J215" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K215" t="s">
         <v>21</v>
       </c>
       <c r="L215" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M215" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -11733,25 +11733,25 @@
         <v>922</v>
       </c>
       <c r="F216" t="s">
+        <v>729</v>
+      </c>
+      <c r="G216" t="s">
         <v>909</v>
-      </c>
-      <c r="G216" t="s">
-        <v>730</v>
       </c>
       <c r="I216" t="s">
         <v>923</v>
       </c>
       <c r="J216" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K216" t="s">
         <v>21</v>
       </c>
       <c r="L216" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M216" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -11768,25 +11768,25 @@
         <v>926</v>
       </c>
       <c r="F217" t="s">
+        <v>729</v>
+      </c>
+      <c r="G217" t="s">
         <v>909</v>
-      </c>
-      <c r="G217" t="s">
-        <v>730</v>
       </c>
       <c r="I217" t="s">
         <v>927</v>
       </c>
       <c r="J217" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K217" t="s">
         <v>21</v>
       </c>
       <c r="L217" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M217" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -11803,25 +11803,25 @@
         <v>930</v>
       </c>
       <c r="F218" t="s">
+        <v>729</v>
+      </c>
+      <c r="G218" t="s">
         <v>909</v>
-      </c>
-      <c r="G218" t="s">
-        <v>730</v>
       </c>
       <c r="I218" t="s">
         <v>931</v>
       </c>
       <c r="J218" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K218" t="s">
         <v>21</v>
       </c>
       <c r="L218" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M218" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -11838,25 +11838,25 @@
         <v>934</v>
       </c>
       <c r="F219" t="s">
+        <v>729</v>
+      </c>
+      <c r="G219" t="s">
         <v>909</v>
-      </c>
-      <c r="G219" t="s">
-        <v>730</v>
       </c>
       <c r="I219" t="s">
         <v>935</v>
       </c>
       <c r="J219" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K219" t="s">
         <v>21</v>
       </c>
       <c r="L219" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M219" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -11873,25 +11873,25 @@
         <v>938</v>
       </c>
       <c r="F220" t="s">
+        <v>729</v>
+      </c>
+      <c r="G220" t="s">
         <v>909</v>
-      </c>
-      <c r="G220" t="s">
-        <v>730</v>
       </c>
       <c r="I220" t="s">
         <v>939</v>
       </c>
       <c r="J220" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K220" t="s">
         <v>21</v>
       </c>
       <c r="L220" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M220" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -11908,25 +11908,25 @@
         <v>942</v>
       </c>
       <c r="F221" t="s">
+        <v>729</v>
+      </c>
+      <c r="G221" t="s">
         <v>909</v>
-      </c>
-      <c r="G221" t="s">
-        <v>730</v>
       </c>
       <c r="I221" t="s">
         <v>943</v>
       </c>
       <c r="J221" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="K221" t="s">
         <v>21</v>
       </c>
       <c r="L221" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M221" t="s">
-        <v>911</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -11952,16 +11952,16 @@
         <v>949</v>
       </c>
       <c r="J222" t="s">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="K222" t="s">
         <v>21</v>
       </c>
       <c r="L222" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M222" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -11987,16 +11987,16 @@
         <v>955</v>
       </c>
       <c r="J223" t="s">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="K223" t="s">
         <v>21</v>
       </c>
       <c r="L223" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M223" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -12022,16 +12022,16 @@
         <v>959</v>
       </c>
       <c r="J224" t="s">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="K224" t="s">
         <v>21</v>
       </c>
       <c r="L224" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M224" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -12057,16 +12057,16 @@
         <v>963</v>
       </c>
       <c r="J225" t="s">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="K225" t="s">
         <v>21</v>
       </c>
       <c r="L225" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M225" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -12092,16 +12092,16 @@
         <v>967</v>
       </c>
       <c r="J226" t="s">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="K226" t="s">
         <v>21</v>
       </c>
       <c r="L226" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M226" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -12127,16 +12127,16 @@
         <v>971</v>
       </c>
       <c r="J227" t="s">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="K227" t="s">
         <v>21</v>
       </c>
       <c r="L227" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M227" t="s">
-        <v>951</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -12153,25 +12153,25 @@
         <v>974</v>
       </c>
       <c r="F228" t="s">
+        <v>947</v>
+      </c>
+      <c r="G228" t="s">
         <v>975</v>
-      </c>
-      <c r="G228" t="s">
-        <v>948</v>
       </c>
       <c r="I228" t="s">
         <v>976</v>
       </c>
       <c r="J228" t="s">
-        <v>20</v>
+        <v>977</v>
       </c>
       <c r="K228" t="s">
         <v>21</v>
       </c>
       <c r="L228" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M228" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -12188,25 +12188,25 @@
         <v>980</v>
       </c>
       <c r="F229" t="s">
+        <v>947</v>
+      </c>
+      <c r="G229" t="s">
         <v>975</v>
-      </c>
-      <c r="G229" t="s">
-        <v>948</v>
       </c>
       <c r="I229" t="s">
         <v>981</v>
       </c>
       <c r="J229" t="s">
-        <v>20</v>
+        <v>977</v>
       </c>
       <c r="K229" t="s">
         <v>21</v>
       </c>
       <c r="L229" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M229" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -12223,25 +12223,25 @@
         <v>984</v>
       </c>
       <c r="F230" t="s">
+        <v>947</v>
+      </c>
+      <c r="G230" t="s">
         <v>975</v>
-      </c>
-      <c r="G230" t="s">
-        <v>948</v>
       </c>
       <c r="I230" t="s">
         <v>985</v>
       </c>
       <c r="J230" t="s">
-        <v>20</v>
+        <v>977</v>
       </c>
       <c r="K230" t="s">
         <v>21</v>
       </c>
       <c r="L230" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M230" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -12258,25 +12258,25 @@
         <v>988</v>
       </c>
       <c r="F231" t="s">
+        <v>947</v>
+      </c>
+      <c r="G231" t="s">
         <v>975</v>
-      </c>
-      <c r="G231" t="s">
-        <v>948</v>
       </c>
       <c r="I231" t="s">
         <v>989</v>
       </c>
       <c r="J231" t="s">
-        <v>20</v>
+        <v>977</v>
       </c>
       <c r="K231" t="s">
         <v>21</v>
       </c>
       <c r="L231" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M231" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -12293,25 +12293,25 @@
         <v>992</v>
       </c>
       <c r="F232" t="s">
+        <v>947</v>
+      </c>
+      <c r="G232" t="s">
         <v>975</v>
-      </c>
-      <c r="G232" t="s">
-        <v>948</v>
       </c>
       <c r="I232" t="s">
         <v>993</v>
       </c>
       <c r="J232" t="s">
-        <v>20</v>
+        <v>977</v>
       </c>
       <c r="K232" t="s">
         <v>21</v>
       </c>
       <c r="L232" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M232" t="s">
-        <v>977</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -12328,25 +12328,25 @@
         <v>996</v>
       </c>
       <c r="F233" t="s">
+        <v>947</v>
+      </c>
+      <c r="G233" t="s">
         <v>997</v>
-      </c>
-      <c r="G233" t="s">
-        <v>948</v>
       </c>
       <c r="I233" t="s">
         <v>998</v>
       </c>
       <c r="J233" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K233" t="s">
         <v>21</v>
       </c>
       <c r="L233" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M233" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -12363,25 +12363,25 @@
         <v>1002</v>
       </c>
       <c r="F234" t="s">
+        <v>947</v>
+      </c>
+      <c r="G234" t="s">
         <v>997</v>
-      </c>
-      <c r="G234" t="s">
-        <v>948</v>
       </c>
       <c r="I234" t="s">
         <v>1003</v>
       </c>
       <c r="J234" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K234" t="s">
         <v>21</v>
       </c>
       <c r="L234" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M234" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -12398,25 +12398,25 @@
         <v>1006</v>
       </c>
       <c r="F235" t="s">
+        <v>947</v>
+      </c>
+      <c r="G235" t="s">
         <v>997</v>
-      </c>
-      <c r="G235" t="s">
-        <v>948</v>
       </c>
       <c r="I235" t="s">
         <v>1007</v>
       </c>
       <c r="J235" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K235" t="s">
         <v>21</v>
       </c>
       <c r="L235" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M235" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -12433,25 +12433,25 @@
         <v>1010</v>
       </c>
       <c r="F236" t="s">
+        <v>947</v>
+      </c>
+      <c r="G236" t="s">
         <v>997</v>
-      </c>
-      <c r="G236" t="s">
-        <v>948</v>
       </c>
       <c r="I236" t="s">
         <v>1011</v>
       </c>
       <c r="J236" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K236" t="s">
         <v>21</v>
       </c>
       <c r="L236" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M236" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -12468,25 +12468,25 @@
         <v>1014</v>
       </c>
       <c r="F237" t="s">
+        <v>947</v>
+      </c>
+      <c r="G237" t="s">
         <v>997</v>
-      </c>
-      <c r="G237" t="s">
-        <v>948</v>
       </c>
       <c r="I237" t="s">
         <v>1015</v>
       </c>
       <c r="J237" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K237" t="s">
         <v>21</v>
       </c>
       <c r="L237" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M237" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -12503,25 +12503,25 @@
         <v>1018</v>
       </c>
       <c r="F238" t="s">
+        <v>947</v>
+      </c>
+      <c r="G238" t="s">
         <v>997</v>
-      </c>
-      <c r="G238" t="s">
-        <v>948</v>
       </c>
       <c r="I238" t="s">
         <v>1019</v>
       </c>
       <c r="J238" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K238" t="s">
         <v>21</v>
       </c>
       <c r="L238" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M238" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -12538,25 +12538,25 @@
         <v>1022</v>
       </c>
       <c r="F239" t="s">
+        <v>947</v>
+      </c>
+      <c r="G239" t="s">
         <v>997</v>
-      </c>
-      <c r="G239" t="s">
-        <v>948</v>
       </c>
       <c r="I239" t="s">
         <v>1023</v>
       </c>
       <c r="J239" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K239" t="s">
         <v>21</v>
       </c>
       <c r="L239" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M239" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -12573,25 +12573,25 @@
         <v>1026</v>
       </c>
       <c r="F240" t="s">
+        <v>947</v>
+      </c>
+      <c r="G240" t="s">
         <v>997</v>
-      </c>
-      <c r="G240" t="s">
-        <v>948</v>
       </c>
       <c r="I240" t="s">
         <v>1027</v>
       </c>
       <c r="J240" t="s">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="K240" t="s">
         <v>21</v>
       </c>
       <c r="L240" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M240" t="s">
-        <v>999</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -12608,25 +12608,25 @@
         <v>1030</v>
       </c>
       <c r="F241" t="s">
+        <v>947</v>
+      </c>
+      <c r="G241" t="s">
         <v>1031</v>
-      </c>
-      <c r="G241" t="s">
-        <v>948</v>
       </c>
       <c r="I241" t="s">
         <v>1032</v>
       </c>
       <c r="J241" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K241" t="s">
         <v>21</v>
       </c>
       <c r="L241" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M241" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -12643,25 +12643,25 @@
         <v>1036</v>
       </c>
       <c r="F242" t="s">
+        <v>947</v>
+      </c>
+      <c r="G242" t="s">
         <v>1031</v>
-      </c>
-      <c r="G242" t="s">
-        <v>948</v>
       </c>
       <c r="I242" t="s">
         <v>1037</v>
       </c>
       <c r="J242" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K242" t="s">
         <v>21</v>
       </c>
       <c r="L242" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M242" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -12678,25 +12678,25 @@
         <v>1040</v>
       </c>
       <c r="F243" t="s">
+        <v>947</v>
+      </c>
+      <c r="G243" t="s">
         <v>1031</v>
-      </c>
-      <c r="G243" t="s">
-        <v>948</v>
       </c>
       <c r="I243" t="s">
         <v>1041</v>
       </c>
       <c r="J243" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K243" t="s">
         <v>21</v>
       </c>
       <c r="L243" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M243" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -12713,25 +12713,25 @@
         <v>1044</v>
       </c>
       <c r="F244" t="s">
+        <v>947</v>
+      </c>
+      <c r="G244" t="s">
         <v>1031</v>
-      </c>
-      <c r="G244" t="s">
-        <v>948</v>
       </c>
       <c r="I244" t="s">
         <v>1045</v>
       </c>
       <c r="J244" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K244" t="s">
         <v>21</v>
       </c>
       <c r="L244" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M244" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -12748,25 +12748,25 @@
         <v>1048</v>
       </c>
       <c r="F245" t="s">
+        <v>947</v>
+      </c>
+      <c r="G245" t="s">
         <v>1031</v>
-      </c>
-      <c r="G245" t="s">
-        <v>948</v>
       </c>
       <c r="I245" t="s">
         <v>1049</v>
       </c>
       <c r="J245" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K245" t="s">
         <v>21</v>
       </c>
       <c r="L245" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M245" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -12783,25 +12783,25 @@
         <v>1052</v>
       </c>
       <c r="F246" t="s">
+        <v>947</v>
+      </c>
+      <c r="G246" t="s">
         <v>1031</v>
-      </c>
-      <c r="G246" t="s">
-        <v>948</v>
       </c>
       <c r="I246" t="s">
         <v>1053</v>
       </c>
       <c r="J246" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K246" t="s">
         <v>21</v>
       </c>
       <c r="L246" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M246" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -12818,25 +12818,25 @@
         <v>1056</v>
       </c>
       <c r="F247" t="s">
+        <v>947</v>
+      </c>
+      <c r="G247" t="s">
         <v>1031</v>
-      </c>
-      <c r="G247" t="s">
-        <v>948</v>
       </c>
       <c r="I247" t="s">
         <v>1057</v>
       </c>
       <c r="J247" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K247" t="s">
         <v>21</v>
       </c>
       <c r="L247" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M247" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -12853,25 +12853,25 @@
         <v>1060</v>
       </c>
       <c r="F248" t="s">
+        <v>947</v>
+      </c>
+      <c r="G248" t="s">
         <v>1031</v>
-      </c>
-      <c r="G248" t="s">
-        <v>948</v>
       </c>
       <c r="I248" t="s">
         <v>1061</v>
       </c>
       <c r="J248" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K248" t="s">
         <v>21</v>
       </c>
       <c r="L248" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M248" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -12888,25 +12888,25 @@
         <v>1064</v>
       </c>
       <c r="F249" t="s">
+        <v>947</v>
+      </c>
+      <c r="G249" t="s">
         <v>1031</v>
-      </c>
-      <c r="G249" t="s">
-        <v>948</v>
       </c>
       <c r="I249" t="s">
         <v>1065</v>
       </c>
       <c r="J249" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K249" t="s">
         <v>21</v>
       </c>
       <c r="L249" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M249" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -12923,25 +12923,25 @@
         <v>1068</v>
       </c>
       <c r="F250" t="s">
+        <v>947</v>
+      </c>
+      <c r="G250" t="s">
         <v>1031</v>
-      </c>
-      <c r="G250" t="s">
-        <v>948</v>
       </c>
       <c r="I250" t="s">
         <v>1069</v>
       </c>
       <c r="J250" t="s">
-        <v>20</v>
+        <v>1033</v>
       </c>
       <c r="K250" t="s">
         <v>21</v>
       </c>
       <c r="L250" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M250" t="s">
-        <v>1033</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/RegionM49.xlsx
+++ b/api/xlsx/en/RegionM49.xlsx
@@ -25,33 +25,33 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:global-name</t>
+  </si>
+  <si>
+    <t>codeforiati:region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-name</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
     <t>codeforiati:iso-alpha-2-code</t>
   </si>
   <si>
     <t>codeforiati:global-code</t>
   </si>
   <si>
-    <t>codeforiati:global-name</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-name</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-name</t>
-  </si>
-  <si>
     <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
@@ -64,27 +64,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>DZ</t>
   </si>
   <si>
     <t>001</t>
   </si>
   <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
     <t>DZA</t>
   </si>
   <si>
@@ -166,21 +166,21 @@
     <t>British Indian Ocean Territory</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Eastern Africa</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>IO</t>
   </si>
   <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>Eastern Africa</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
@@ -442,15 +442,15 @@
     <t>Angola</t>
   </si>
   <si>
+    <t>Middle Africa</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>AO</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
-    <t>Middle Africa</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
@@ -556,15 +556,15 @@
     <t>Botswana</t>
   </si>
   <si>
+    <t>Southern Africa</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>BW</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
-    <t>Southern Africa</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>Benin</t>
   </si>
   <si>
+    <t>Western Africa</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>BJ</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>Western Africa</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
@@ -832,27 +832,27 @@
     <t>Anguilla</t>
   </si>
   <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
     <t>AI</t>
   </si>
   <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
     <t>AIA</t>
   </si>
   <si>
@@ -1186,15 +1186,15 @@
     <t>Belize</t>
   </si>
   <si>
+    <t>Central America</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>BZ</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
-    <t>Central America</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
@@ -1288,15 +1288,15 @@
     <t>Argentina</t>
   </si>
   <si>
+    <t>South America</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>AR</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>South America</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -1486,15 +1486,15 @@
     <t>Bermuda</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
     <t>BM</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
-    <t>021</t>
-  </si>
-  <si>
     <t>BMU</t>
   </si>
   <si>
@@ -1564,21 +1564,21 @@
     <t>Kazakhstan</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
     <t>KZ</t>
   </si>
   <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>KAZ</t>
   </si>
   <si>
@@ -1636,15 +1636,15 @@
     <t>China</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
     <t>CHN</t>
   </si>
   <si>
@@ -1726,15 +1726,15 @@
     <t>Brunei Darussalam</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
     <t>BN</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
     <t>BRN</t>
   </si>
   <si>
@@ -1864,15 +1864,15 @@
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
     <t>AF</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
     <t>AFG</t>
   </si>
   <si>
@@ -1978,15 +1978,15 @@
     <t>Armenia</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
     <t>AM</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>ARM</t>
   </si>
   <si>
@@ -2200,21 +2200,21 @@
     <t>Belarus</t>
   </si>
   <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>BY</t>
   </si>
   <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
     <t>BLR</t>
   </si>
   <si>
@@ -2332,15 +2332,15 @@
     <t>Åland Islands</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
     <t>AX</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
     <t>ALA</t>
   </si>
   <si>
@@ -2350,15 +2350,15 @@
     <t>Guernsey</t>
   </si>
   <si>
+    <t>Channel Islands</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
     <t>GG</t>
   </si>
   <si>
-    <t>830</t>
-  </si>
-  <si>
-    <t>Channel Islands</t>
-  </si>
-  <si>
     <t>GGY</t>
   </si>
   <si>
@@ -2542,15 +2542,15 @@
     <t>Albania</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
     <t>AL</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
     <t>ALB</t>
   </si>
   <si>
@@ -2740,15 +2740,15 @@
     <t>Austria</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
     <t>AT</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>AUT</t>
   </si>
   <si>
@@ -2854,21 +2854,21 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
     <t>AU</t>
   </si>
   <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
     <t>AUS</t>
   </si>
   <si>
@@ -2938,15 +2938,15 @@
     <t>Fiji</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
     <t>FJ</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
-    <t>054</t>
-  </si>
-  <si>
     <t>FJI</t>
   </si>
   <si>
@@ -3004,15 +3004,15 @@
     <t>Guam</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
     <t>GU</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
     <t>GUM</t>
   </si>
   <si>
@@ -3106,13 +3106,13 @@
     <t>American Samoa</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
     <t>AS</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
-  </si>
-  <si>
-    <t>061</t>
   </si>
   <si>
     <t>ASM</t>
@@ -3645,7 +3645,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -3660,7 +3660,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -3680,7 +3680,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -3695,7 +3695,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -3715,7 +3715,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -3730,7 +3730,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -3750,7 +3750,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -3765,7 +3765,7 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L6" t="s">
         <v>22</v>
@@ -3785,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -3800,7 +3800,7 @@
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L7" t="s">
         <v>22</v>
@@ -3820,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -3835,7 +3835,7 @@
         <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="L8" t="s">
         <v>22</v>
@@ -3855,13 +3855,13 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
         <v>51</v>
@@ -3896,13 +3896,13 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
         <v>51</v>
@@ -3917,7 +3917,7 @@
         <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L10" t="s">
         <v>22</v>
@@ -3937,13 +3937,13 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
         <v>51</v>
@@ -3958,7 +3958,7 @@
         <v>20</v>
       </c>
       <c r="K11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L11" t="s">
         <v>22</v>
@@ -3978,13 +3978,13 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>51</v>
@@ -3999,7 +3999,7 @@
         <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="L12" t="s">
         <v>22</v>
@@ -4019,13 +4019,13 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
         <v>51</v>
@@ -4040,7 +4040,7 @@
         <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -4060,13 +4060,13 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
         <v>51</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
@@ -4101,13 +4101,13 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G15" t="s">
         <v>51</v>
@@ -4122,7 +4122,7 @@
         <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
@@ -4142,13 +4142,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G16" t="s">
         <v>51</v>
@@ -4163,7 +4163,7 @@
         <v>20</v>
       </c>
       <c r="K16" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
@@ -4183,13 +4183,13 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
         <v>51</v>
@@ -4204,7 +4204,7 @@
         <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="L17" t="s">
         <v>22</v>
@@ -4224,13 +4224,13 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G18" t="s">
         <v>51</v>
@@ -4245,7 +4245,7 @@
         <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
         <v>22</v>
@@ -4265,13 +4265,13 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G19" t="s">
         <v>51</v>
@@ -4286,7 +4286,7 @@
         <v>20</v>
       </c>
       <c r="K19" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="L19" t="s">
         <v>22</v>
@@ -4306,13 +4306,13 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G20" t="s">
         <v>51</v>
@@ -4327,7 +4327,7 @@
         <v>20</v>
       </c>
       <c r="K20" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
@@ -4347,13 +4347,13 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
         <v>51</v>
@@ -4368,7 +4368,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="L21" t="s">
         <v>22</v>
@@ -4388,13 +4388,13 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G22" t="s">
         <v>51</v>
@@ -4409,7 +4409,7 @@
         <v>20</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
@@ -4429,13 +4429,13 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G23" t="s">
         <v>51</v>
@@ -4450,7 +4450,7 @@
         <v>20</v>
       </c>
       <c r="K23" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
@@ -4470,13 +4470,13 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G24" t="s">
         <v>51</v>
@@ -4491,7 +4491,7 @@
         <v>20</v>
       </c>
       <c r="K24" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="L24" t="s">
         <v>22</v>
@@ -4511,13 +4511,13 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G25" t="s">
         <v>51</v>
@@ -4532,7 +4532,7 @@
         <v>20</v>
       </c>
       <c r="K25" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="L25" t="s">
         <v>22</v>
@@ -4552,13 +4552,13 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G26" t="s">
         <v>51</v>
@@ -4573,7 +4573,7 @@
         <v>20</v>
       </c>
       <c r="K26" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s">
         <v>22</v>
@@ -4593,13 +4593,13 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G27" t="s">
         <v>51</v>
@@ -4614,7 +4614,7 @@
         <v>20</v>
       </c>
       <c r="K27" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="L27" t="s">
         <v>22</v>
@@ -4634,13 +4634,13 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G28" t="s">
         <v>51</v>
@@ -4655,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="K28" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="L28" t="s">
         <v>22</v>
@@ -4675,13 +4675,13 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G29" t="s">
         <v>51</v>
@@ -4696,7 +4696,7 @@
         <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s">
         <v>22</v>
@@ -4716,13 +4716,13 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G30" t="s">
         <v>51</v>
@@ -4737,7 +4737,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="L30" t="s">
         <v>22</v>
@@ -4757,28 +4757,28 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G31" t="s">
         <v>51</v>
       </c>
       <c r="H31" t="s">
+        <v>142</v>
+      </c>
+      <c r="I31" t="s">
         <v>143</v>
-      </c>
-      <c r="I31" t="s">
-        <v>144</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
       </c>
       <c r="K31" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
@@ -4798,28 +4798,28 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G32" t="s">
         <v>51</v>
       </c>
       <c r="H32" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" t="s">
         <v>143</v>
-      </c>
-      <c r="I32" t="s">
-        <v>144</v>
       </c>
       <c r="J32" t="s">
         <v>20</v>
       </c>
       <c r="K32" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -4839,28 +4839,28 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G33" t="s">
         <v>51</v>
       </c>
       <c r="H33" t="s">
+        <v>142</v>
+      </c>
+      <c r="I33" t="s">
         <v>143</v>
-      </c>
-      <c r="I33" t="s">
-        <v>144</v>
       </c>
       <c r="J33" t="s">
         <v>20</v>
       </c>
       <c r="K33" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -4880,28 +4880,28 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G34" t="s">
         <v>51</v>
       </c>
       <c r="H34" t="s">
+        <v>142</v>
+      </c>
+      <c r="I34" t="s">
         <v>143</v>
-      </c>
-      <c r="I34" t="s">
-        <v>144</v>
       </c>
       <c r="J34" t="s">
         <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
@@ -4921,28 +4921,28 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G35" t="s">
         <v>51</v>
       </c>
       <c r="H35" t="s">
+        <v>142</v>
+      </c>
+      <c r="I35" t="s">
         <v>143</v>
-      </c>
-      <c r="I35" t="s">
-        <v>144</v>
       </c>
       <c r="J35" t="s">
         <v>20</v>
       </c>
       <c r="K35" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
@@ -4962,28 +4962,28 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s">
         <v>51</v>
       </c>
       <c r="H36" t="s">
+        <v>142</v>
+      </c>
+      <c r="I36" t="s">
         <v>143</v>
-      </c>
-      <c r="I36" t="s">
-        <v>144</v>
       </c>
       <c r="J36" t="s">
         <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="L36" t="s">
         <v>22</v>
@@ -5003,28 +5003,28 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G37" t="s">
         <v>51</v>
       </c>
       <c r="H37" t="s">
+        <v>142</v>
+      </c>
+      <c r="I37" t="s">
         <v>143</v>
-      </c>
-      <c r="I37" t="s">
-        <v>144</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
       </c>
       <c r="K37" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="L37" t="s">
         <v>22</v>
@@ -5044,28 +5044,28 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G38" t="s">
         <v>51</v>
       </c>
       <c r="H38" t="s">
+        <v>142</v>
+      </c>
+      <c r="I38" t="s">
         <v>143</v>
-      </c>
-      <c r="I38" t="s">
-        <v>144</v>
       </c>
       <c r="J38" t="s">
         <v>20</v>
       </c>
       <c r="K38" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="L38" t="s">
         <v>22</v>
@@ -5085,28 +5085,28 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G39" t="s">
         <v>51</v>
       </c>
       <c r="H39" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" t="s">
         <v>143</v>
-      </c>
-      <c r="I39" t="s">
-        <v>144</v>
       </c>
       <c r="J39" t="s">
         <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="L39" t="s">
         <v>22</v>
@@ -5126,28 +5126,28 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G40" t="s">
         <v>51</v>
       </c>
       <c r="H40" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40" t="s">
         <v>181</v>
-      </c>
-      <c r="I40" t="s">
-        <v>182</v>
       </c>
       <c r="J40" t="s">
         <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="L40" t="s">
         <v>22</v>
@@ -5167,28 +5167,28 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
         <v>51</v>
       </c>
       <c r="H41" t="s">
+        <v>180</v>
+      </c>
+      <c r="I41" t="s">
         <v>181</v>
-      </c>
-      <c r="I41" t="s">
-        <v>182</v>
       </c>
       <c r="J41" t="s">
         <v>20</v>
       </c>
       <c r="K41" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -5208,28 +5208,28 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G42" t="s">
         <v>51</v>
       </c>
       <c r="H42" t="s">
+        <v>180</v>
+      </c>
+      <c r="I42" t="s">
         <v>181</v>
-      </c>
-      <c r="I42" t="s">
-        <v>182</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s">
         <v>22</v>
@@ -5249,28 +5249,28 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G43" t="s">
         <v>51</v>
       </c>
       <c r="H43" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" t="s">
         <v>181</v>
-      </c>
-      <c r="I43" t="s">
-        <v>182</v>
       </c>
       <c r="J43" t="s">
         <v>20</v>
       </c>
       <c r="K43" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
@@ -5290,28 +5290,28 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G44" t="s">
         <v>51</v>
       </c>
       <c r="H44" t="s">
+        <v>180</v>
+      </c>
+      <c r="I44" t="s">
         <v>181</v>
-      </c>
-      <c r="I44" t="s">
-        <v>182</v>
       </c>
       <c r="J44" t="s">
         <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
@@ -5331,28 +5331,28 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G45" t="s">
         <v>51</v>
       </c>
       <c r="H45" t="s">
+        <v>202</v>
+      </c>
+      <c r="I45" t="s">
         <v>203</v>
-      </c>
-      <c r="I45" t="s">
-        <v>204</v>
       </c>
       <c r="J45" t="s">
         <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -5372,28 +5372,28 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G46" t="s">
         <v>51</v>
       </c>
       <c r="H46" t="s">
+        <v>202</v>
+      </c>
+      <c r="I46" t="s">
         <v>203</v>
-      </c>
-      <c r="I46" t="s">
-        <v>204</v>
       </c>
       <c r="J46" t="s">
         <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s">
         <v>22</v>
@@ -5413,28 +5413,28 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>212</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G47" t="s">
         <v>51</v>
       </c>
       <c r="H47" t="s">
+        <v>202</v>
+      </c>
+      <c r="I47" t="s">
         <v>203</v>
-      </c>
-      <c r="I47" t="s">
-        <v>204</v>
       </c>
       <c r="J47" t="s">
         <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="L47" t="s">
         <v>22</v>
@@ -5454,28 +5454,28 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G48" t="s">
         <v>51</v>
       </c>
       <c r="H48" t="s">
+        <v>202</v>
+      </c>
+      <c r="I48" t="s">
         <v>203</v>
-      </c>
-      <c r="I48" t="s">
-        <v>204</v>
       </c>
       <c r="J48" t="s">
         <v>20</v>
       </c>
       <c r="K48" t="s">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="L48" t="s">
         <v>22</v>
@@ -5495,28 +5495,28 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G49" t="s">
         <v>51</v>
       </c>
       <c r="H49" t="s">
+        <v>202</v>
+      </c>
+      <c r="I49" t="s">
         <v>203</v>
-      </c>
-      <c r="I49" t="s">
-        <v>204</v>
       </c>
       <c r="J49" t="s">
         <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>54</v>
+        <v>220</v>
       </c>
       <c r="L49" t="s">
         <v>22</v>
@@ -5536,28 +5536,28 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G50" t="s">
         <v>51</v>
       </c>
       <c r="H50" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" t="s">
         <v>203</v>
-      </c>
-      <c r="I50" t="s">
-        <v>204</v>
       </c>
       <c r="J50" t="s">
         <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>54</v>
+        <v>224</v>
       </c>
       <c r="L50" t="s">
         <v>22</v>
@@ -5577,28 +5577,28 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
       